--- a/Inputs/BD.xlsx
+++ b/Inputs/BD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/078e1a455e5c02ce/Documentos/GitHub/Proyecto_PIPC/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="332" documentId="13_ncr:1_{CF2C40B5-0007-4E87-85E3-0CDB05564647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74A2A6C4-9803-41B1-9CCE-216C45707E1B}"/>
+  <xr:revisionPtr revIDLastSave="337" documentId="13_ncr:1_{CF2C40B5-0007-4E87-85E3-0CDB05564647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C9CD797-6E54-4F62-8BA9-34B551057627}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3F095A75-F066-4695-8672-8D4315F1EF23}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{3F095A75-F066-4695-8672-8D4315F1EF23}"/>
   </bookViews>
   <sheets>
     <sheet name="BD" sheetId="1" r:id="rId1"/>
@@ -260,7 +260,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A78" authorId="0" shapeId="0" xr:uid="{733E70D1-98D2-4246-AFA3-A8F0F23DC8ED}">
+    <comment ref="A79" authorId="0" shapeId="0" xr:uid="{12F3D2AC-77D3-465B-9182-DE15CC16FEE6}">
       <text>
         <r>
           <rPr>
@@ -289,7 +289,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1804" uniqueCount="843">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1805" uniqueCount="845">
   <si>
     <t>dia</t>
   </si>
@@ -2818,6 +2818,12 @@
   </si>
   <si>
     <t>13 DE ABRIL DE 1999</t>
+  </si>
+  <si>
+    <t>mantto1</t>
+  </si>
+  <si>
+    <t>mantto2</t>
   </si>
 </sst>
 </file>
@@ -3071,6 +3077,10 @@
     <mc:Fallback/>
   </mc:AlternateContent>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19338,15 +19348,15 @@
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>723</v>
+        <v>843</v>
       </c>
       <c r="B77" t="str">
         <f t="shared" si="21"/>
-        <v>mantto.png</v>
+        <v>mantto1.png</v>
       </c>
       <c r="C77" t="str">
         <f t="shared" si="22"/>
-        <v>{{ mantto }}</v>
+        <v>{{ mantto1 }}</v>
       </c>
       <c r="D77">
         <v>190</v>
@@ -19363,60 +19373,60 @@
       </c>
       <c r="H77" t="str">
         <f t="shared" si="13"/>
-        <v>'mantto': mantto,</v>
+        <v>'mantto1': mantto1,</v>
       </c>
       <c r="I77" t="s">
         <v>565</v>
       </c>
       <c r="J77" t="str">
         <f t="shared" si="14"/>
-        <v>img_path_mantto = os.path.join(IMAGES_PATH, r_val["mantto"])</v>
+        <v>img_path_mantto1 = os.path.join(IMAGES_PATH, r_val["mantto1"])</v>
       </c>
       <c r="K77" t="str">
         <f t="shared" si="15"/>
-        <v>if os.path.exists(img_path_mantto):</v>
+        <v>if os.path.exists(img_path_mantto1):</v>
       </c>
       <c r="L77" t="str">
         <f t="shared" si="16"/>
-        <v>mantto = InlineImage(docx_tpl, img_path_mantto, height=Mm(190))</v>
+        <v>mantto1 = InlineImage(docx_tpl, img_path_mantto1, height=Mm(190))</v>
       </c>
       <c r="M77" t="s">
         <v>567</v>
       </c>
       <c r="N77" t="str">
         <f t="shared" si="17"/>
-        <v>print(f'Advertencia: No se encontró la imagen {r_val["mantto"]}')</v>
+        <v>print(f'Advertencia: No se encontró la imagen {r_val["mantto1"]}')</v>
       </c>
       <c r="O77" t="str">
         <f t="shared" si="18"/>
-        <v>mantto = ''</v>
+        <v>mantto1 = ''</v>
       </c>
       <c r="P77" t="s">
         <v>566</v>
       </c>
       <c r="Q77" t="str">
         <f t="shared" si="19"/>
-        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["mantto"]}: {e}')</v>
+        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["mantto1"]}: {e}')</v>
       </c>
       <c r="R77" t="str">
         <f t="shared" si="20"/>
-        <v>mantto = ''</v>
+        <v>mantto1 = ''</v>
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>724</v>
+        <v>844</v>
       </c>
       <c r="B78" t="str">
         <f t="shared" si="21"/>
-        <v>simulacro.png</v>
+        <v>mantto2.png</v>
       </c>
       <c r="C78" t="str">
         <f t="shared" si="22"/>
-        <v>{{ simulacro }}</v>
+        <v>{{ mantto2 }}</v>
       </c>
       <c r="D78">
-        <v>95</v>
+        <v>190</v>
       </c>
       <c r="E78" t="s">
         <v>582</v>
@@ -19430,57 +19440,57 @@
       </c>
       <c r="H78" t="str">
         <f t="shared" si="13"/>
-        <v>'simulacro': simulacro,</v>
+        <v>'mantto2': mantto2,</v>
       </c>
       <c r="I78" t="s">
         <v>565</v>
       </c>
       <c r="J78" t="str">
         <f t="shared" si="14"/>
-        <v>img_path_simulacro = os.path.join(IMAGES_PATH, r_val["simulacro"])</v>
+        <v>img_path_mantto2 = os.path.join(IMAGES_PATH, r_val["mantto2"])</v>
       </c>
       <c r="K78" t="str">
         <f t="shared" si="15"/>
-        <v>if os.path.exists(img_path_simulacro):</v>
+        <v>if os.path.exists(img_path_mantto2):</v>
       </c>
       <c r="L78" t="str">
         <f t="shared" si="16"/>
-        <v>simulacro = InlineImage(docx_tpl, img_path_simulacro, height=Mm(95))</v>
+        <v>mantto2 = InlineImage(docx_tpl, img_path_mantto2, height=Mm(190))</v>
       </c>
       <c r="M78" t="s">
         <v>567</v>
       </c>
       <c r="N78" t="str">
         <f t="shared" si="17"/>
-        <v>print(f'Advertencia: No se encontró la imagen {r_val["simulacro"]}')</v>
+        <v>print(f'Advertencia: No se encontró la imagen {r_val["mantto2"]}')</v>
       </c>
       <c r="O78" t="str">
         <f t="shared" si="18"/>
-        <v>simulacro = ''</v>
+        <v>mantto2 = ''</v>
       </c>
       <c r="P78" t="s">
         <v>566</v>
       </c>
       <c r="Q78" t="str">
         <f t="shared" si="19"/>
-        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["simulacro"]}: {e}')</v>
+        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["mantto2"]}: {e}')</v>
       </c>
       <c r="R78" t="str">
         <f t="shared" si="20"/>
-        <v>simulacro = ''</v>
+        <v>mantto2 = ''</v>
       </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B79" t="str">
-        <f t="shared" si="21"/>
-        <v>capacitacion.png</v>
+        <f t="shared" ref="B79:B91" si="23">+_xlfn.CONCAT(A79,".png")</f>
+        <v>simulacro.png</v>
       </c>
       <c r="C79" t="str">
-        <f t="shared" si="22"/>
-        <v>{{ capacitacion }}</v>
+        <f t="shared" ref="C79:C91" si="24">+_xlfn.CONCAT("{{ ",A79," }}")</f>
+        <v>{{ simulacro }}</v>
       </c>
       <c r="D79">
         <v>95</v>
@@ -19492,65 +19502,65 @@
         <v>580</v>
       </c>
       <c r="G79" t="str">
-        <f t="shared" ref="G79:G110" si="23">+_xlfn.CONCAT("'",E79,"' : r_val['",E79,"'],")</f>
+        <f t="shared" ref="G79:G110" si="25">+_xlfn.CONCAT("'",E79,"' : r_val['",E79,"'],")</f>
         <v>'ubicacion_site' : r_val['ubicacion_site'],</v>
       </c>
       <c r="H79" t="str">
         <f t="shared" si="13"/>
-        <v>'capacitacion': capacitacion,</v>
+        <v>'simulacro': simulacro,</v>
       </c>
       <c r="I79" t="s">
         <v>565</v>
       </c>
       <c r="J79" t="str">
         <f t="shared" si="14"/>
-        <v>img_path_capacitacion = os.path.join(IMAGES_PATH, r_val["capacitacion"])</v>
+        <v>img_path_simulacro = os.path.join(IMAGES_PATH, r_val["simulacro"])</v>
       </c>
       <c r="K79" t="str">
         <f t="shared" si="15"/>
-        <v>if os.path.exists(img_path_capacitacion):</v>
+        <v>if os.path.exists(img_path_simulacro):</v>
       </c>
       <c r="L79" t="str">
         <f t="shared" si="16"/>
-        <v>capacitacion = InlineImage(docx_tpl, img_path_capacitacion, height=Mm(95))</v>
+        <v>simulacro = InlineImage(docx_tpl, img_path_simulacro, height=Mm(95))</v>
       </c>
       <c r="M79" t="s">
         <v>567</v>
       </c>
       <c r="N79" t="str">
         <f t="shared" si="17"/>
-        <v>print(f'Advertencia: No se encontró la imagen {r_val["capacitacion"]}')</v>
+        <v>print(f'Advertencia: No se encontró la imagen {r_val["simulacro"]}')</v>
       </c>
       <c r="O79" t="str">
         <f t="shared" si="18"/>
-        <v>capacitacion = ''</v>
+        <v>simulacro = ''</v>
       </c>
       <c r="P79" t="s">
         <v>566</v>
       </c>
       <c r="Q79" t="str">
         <f t="shared" si="19"/>
-        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["capacitacion"]}: {e}')</v>
+        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["simulacro"]}: {e}')</v>
       </c>
       <c r="R79" t="str">
         <f t="shared" si="20"/>
-        <v>capacitacion = ''</v>
+        <v>simulacro = ''</v>
       </c>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B80" t="str">
-        <f t="shared" si="21"/>
-        <v>inv_quim.png</v>
+        <f t="shared" si="23"/>
+        <v>capacitacion.png</v>
       </c>
       <c r="C80" t="str">
-        <f t="shared" si="22"/>
-        <v>{{ inv_quim }}</v>
+        <f t="shared" si="24"/>
+        <v>{{ capacitacion }}</v>
       </c>
       <c r="D80">
-        <v>190</v>
+        <v>95</v>
       </c>
       <c r="E80" t="s">
         <v>15</v>
@@ -19559,62 +19569,62 @@
         <v>302</v>
       </c>
       <c r="G80" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>'hidrantes' : r_val['hidrantes'],</v>
       </c>
       <c r="H80" t="str">
         <f t="shared" si="13"/>
-        <v>'inv_quim': inv_quim,</v>
+        <v>'capacitacion': capacitacion,</v>
       </c>
       <c r="I80" t="s">
         <v>565</v>
       </c>
       <c r="J80" t="str">
         <f t="shared" si="14"/>
-        <v>img_path_inv_quim = os.path.join(IMAGES_PATH, r_val["inv_quim"])</v>
+        <v>img_path_capacitacion = os.path.join(IMAGES_PATH, r_val["capacitacion"])</v>
       </c>
       <c r="K80" t="str">
         <f t="shared" si="15"/>
-        <v>if os.path.exists(img_path_inv_quim):</v>
+        <v>if os.path.exists(img_path_capacitacion):</v>
       </c>
       <c r="L80" t="str">
         <f t="shared" si="16"/>
-        <v>inv_quim = InlineImage(docx_tpl, img_path_inv_quim, height=Mm(190))</v>
+        <v>capacitacion = InlineImage(docx_tpl, img_path_capacitacion, height=Mm(95))</v>
       </c>
       <c r="M80" t="s">
         <v>567</v>
       </c>
       <c r="N80" t="str">
         <f t="shared" si="17"/>
-        <v>print(f'Advertencia: No se encontró la imagen {r_val["inv_quim"]}')</v>
+        <v>print(f'Advertencia: No se encontró la imagen {r_val["capacitacion"]}')</v>
       </c>
       <c r="O80" t="str">
         <f t="shared" si="18"/>
-        <v>inv_quim = ''</v>
+        <v>capacitacion = ''</v>
       </c>
       <c r="P80" t="s">
         <v>566</v>
       </c>
       <c r="Q80" t="str">
         <f t="shared" si="19"/>
-        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["inv_quim"]}: {e}')</v>
+        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["capacitacion"]}: {e}')</v>
       </c>
       <c r="R80" t="str">
         <f t="shared" si="20"/>
-        <v>inv_quim = ''</v>
+        <v>capacitacion = ''</v>
       </c>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B81" t="str">
-        <f t="shared" si="21"/>
-        <v>inv_emer.png</v>
+        <f t="shared" si="23"/>
+        <v>inv_quim.png</v>
       </c>
       <c r="C81" t="str">
-        <f t="shared" si="22"/>
-        <v>{{ inv_emer }}</v>
+        <f t="shared" si="24"/>
+        <v>{{ inv_quim }}</v>
       </c>
       <c r="D81">
         <v>190</v>
@@ -19626,62 +19636,62 @@
         <v>303</v>
       </c>
       <c r="G81" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>'aspersores' : r_val['aspersores'],</v>
       </c>
       <c r="H81" t="str">
         <f t="shared" si="13"/>
-        <v>'inv_emer': inv_emer,</v>
+        <v>'inv_quim': inv_quim,</v>
       </c>
       <c r="I81" t="s">
         <v>565</v>
       </c>
       <c r="J81" t="str">
         <f t="shared" si="14"/>
-        <v>img_path_inv_emer = os.path.join(IMAGES_PATH, r_val["inv_emer"])</v>
+        <v>img_path_inv_quim = os.path.join(IMAGES_PATH, r_val["inv_quim"])</v>
       </c>
       <c r="K81" t="str">
         <f t="shared" si="15"/>
-        <v>if os.path.exists(img_path_inv_emer):</v>
+        <v>if os.path.exists(img_path_inv_quim):</v>
       </c>
       <c r="L81" t="str">
         <f t="shared" si="16"/>
-        <v>inv_emer = InlineImage(docx_tpl, img_path_inv_emer, height=Mm(190))</v>
+        <v>inv_quim = InlineImage(docx_tpl, img_path_inv_quim, height=Mm(190))</v>
       </c>
       <c r="M81" t="s">
         <v>567</v>
       </c>
       <c r="N81" t="str">
         <f t="shared" si="17"/>
-        <v>print(f'Advertencia: No se encontró la imagen {r_val["inv_emer"]}')</v>
+        <v>print(f'Advertencia: No se encontró la imagen {r_val["inv_quim"]}')</v>
       </c>
       <c r="O81" t="str">
         <f t="shared" si="18"/>
-        <v>inv_emer = ''</v>
+        <v>inv_quim = ''</v>
       </c>
       <c r="P81" t="s">
         <v>566</v>
       </c>
       <c r="Q81" t="str">
         <f t="shared" si="19"/>
-        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["inv_emer"]}: {e}')</v>
+        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["inv_quim"]}: {e}')</v>
       </c>
       <c r="R81" t="str">
         <f t="shared" si="20"/>
-        <v>inv_emer = ''</v>
+        <v>inv_quim = ''</v>
       </c>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B82" t="str">
-        <f t="shared" si="21"/>
-        <v>bit_emer.png</v>
+        <f t="shared" si="23"/>
+        <v>inv_emer.png</v>
       </c>
       <c r="C82" t="str">
-        <f t="shared" si="22"/>
-        <v>{{ bit_emer }}</v>
+        <f t="shared" si="24"/>
+        <v>{{ inv_emer }}</v>
       </c>
       <c r="D82">
         <v>190</v>
@@ -19693,62 +19703,62 @@
         <v>304</v>
       </c>
       <c r="G82" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>'bomberos' : r_val['bomberos'],</v>
       </c>
       <c r="H82" t="str">
         <f t="shared" si="13"/>
-        <v>'bit_emer': bit_emer,</v>
+        <v>'inv_emer': inv_emer,</v>
       </c>
       <c r="I82" t="s">
         <v>565</v>
       </c>
       <c r="J82" t="str">
         <f t="shared" si="14"/>
-        <v>img_path_bit_emer = os.path.join(IMAGES_PATH, r_val["bit_emer"])</v>
+        <v>img_path_inv_emer = os.path.join(IMAGES_PATH, r_val["inv_emer"])</v>
       </c>
       <c r="K82" t="str">
         <f t="shared" si="15"/>
-        <v>if os.path.exists(img_path_bit_emer):</v>
+        <v>if os.path.exists(img_path_inv_emer):</v>
       </c>
       <c r="L82" t="str">
         <f t="shared" si="16"/>
-        <v>bit_emer = InlineImage(docx_tpl, img_path_bit_emer, height=Mm(190))</v>
+        <v>inv_emer = InlineImage(docx_tpl, img_path_inv_emer, height=Mm(190))</v>
       </c>
       <c r="M82" t="s">
         <v>567</v>
       </c>
       <c r="N82" t="str">
         <f t="shared" si="17"/>
-        <v>print(f'Advertencia: No se encontró la imagen {r_val["bit_emer"]}')</v>
+        <v>print(f'Advertencia: No se encontró la imagen {r_val["inv_emer"]}')</v>
       </c>
       <c r="O82" t="str">
         <f t="shared" si="18"/>
-        <v>bit_emer = ''</v>
+        <v>inv_emer = ''</v>
       </c>
       <c r="P82" t="s">
         <v>566</v>
       </c>
       <c r="Q82" t="str">
         <f t="shared" si="19"/>
-        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["bit_emer"]}: {e}')</v>
+        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["inv_emer"]}: {e}')</v>
       </c>
       <c r="R82" t="str">
         <f t="shared" si="20"/>
-        <v>bit_emer = ''</v>
+        <v>inv_emer = ''</v>
       </c>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B83" t="str">
-        <f t="shared" si="21"/>
-        <v>insp_bot.png</v>
+        <f t="shared" si="23"/>
+        <v>bit_emer.png</v>
       </c>
       <c r="C83" t="str">
-        <f t="shared" si="22"/>
-        <v>{{ insp_bot }}</v>
+        <f t="shared" si="24"/>
+        <v>{{ bit_emer }}</v>
       </c>
       <c r="D83">
         <v>190</v>
@@ -19760,62 +19770,62 @@
         <v>572</v>
       </c>
       <c r="G83" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>'ubicacion_bombero' : r_val['ubicacion_bombero'],</v>
       </c>
       <c r="H83" t="str">
         <f t="shared" si="13"/>
-        <v>'insp_bot': insp_bot,</v>
+        <v>'bit_emer': bit_emer,</v>
       </c>
       <c r="I83" t="s">
         <v>565</v>
       </c>
       <c r="J83" t="str">
         <f t="shared" si="14"/>
-        <v>img_path_insp_bot = os.path.join(IMAGES_PATH, r_val["insp_bot"])</v>
+        <v>img_path_bit_emer = os.path.join(IMAGES_PATH, r_val["bit_emer"])</v>
       </c>
       <c r="K83" t="str">
         <f t="shared" si="15"/>
-        <v>if os.path.exists(img_path_insp_bot):</v>
+        <v>if os.path.exists(img_path_bit_emer):</v>
       </c>
       <c r="L83" t="str">
         <f t="shared" si="16"/>
-        <v>insp_bot = InlineImage(docx_tpl, img_path_insp_bot, height=Mm(190))</v>
+        <v>bit_emer = InlineImage(docx_tpl, img_path_bit_emer, height=Mm(190))</v>
       </c>
       <c r="M83" t="s">
         <v>567</v>
       </c>
       <c r="N83" t="str">
         <f t="shared" si="17"/>
-        <v>print(f'Advertencia: No se encontró la imagen {r_val["insp_bot"]}')</v>
+        <v>print(f'Advertencia: No se encontró la imagen {r_val["bit_emer"]}')</v>
       </c>
       <c r="O83" t="str">
         <f t="shared" si="18"/>
-        <v>insp_bot = ''</v>
+        <v>bit_emer = ''</v>
       </c>
       <c r="P83" t="s">
         <v>566</v>
       </c>
       <c r="Q83" t="str">
         <f t="shared" si="19"/>
-        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["insp_bot"]}: {e}')</v>
+        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["bit_emer"]}: {e}')</v>
       </c>
       <c r="R83" t="str">
         <f t="shared" si="20"/>
-        <v>insp_bot = ''</v>
+        <v>bit_emer = ''</v>
       </c>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B84" t="str">
-        <f t="shared" si="21"/>
-        <v>insp_ext.png</v>
+        <f t="shared" si="23"/>
+        <v>insp_bot.png</v>
       </c>
       <c r="C84" t="str">
-        <f t="shared" si="22"/>
-        <v>{{ insp_ext }}</v>
+        <f t="shared" si="24"/>
+        <v>{{ insp_bot }}</v>
       </c>
       <c r="D84">
         <v>190</v>
@@ -19827,62 +19837,62 @@
         <v>305</v>
       </c>
       <c r="G84" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>'detector_gas' : r_val['detector_gas'],</v>
       </c>
       <c r="H84" t="str">
         <f t="shared" si="13"/>
-        <v>'insp_ext': insp_ext,</v>
+        <v>'insp_bot': insp_bot,</v>
       </c>
       <c r="I84" t="s">
         <v>565</v>
       </c>
       <c r="J84" t="str">
         <f t="shared" si="14"/>
-        <v>img_path_insp_ext = os.path.join(IMAGES_PATH, r_val["insp_ext"])</v>
+        <v>img_path_insp_bot = os.path.join(IMAGES_PATH, r_val["insp_bot"])</v>
       </c>
       <c r="K84" t="str">
         <f t="shared" si="15"/>
-        <v>if os.path.exists(img_path_insp_ext):</v>
+        <v>if os.path.exists(img_path_insp_bot):</v>
       </c>
       <c r="L84" t="str">
         <f t="shared" si="16"/>
-        <v>insp_ext = InlineImage(docx_tpl, img_path_insp_ext, height=Mm(190))</v>
+        <v>insp_bot = InlineImage(docx_tpl, img_path_insp_bot, height=Mm(190))</v>
       </c>
       <c r="M84" t="s">
         <v>567</v>
       </c>
       <c r="N84" t="str">
         <f t="shared" si="17"/>
-        <v>print(f'Advertencia: No se encontró la imagen {r_val["insp_ext"]}')</v>
+        <v>print(f'Advertencia: No se encontró la imagen {r_val["insp_bot"]}')</v>
       </c>
       <c r="O84" t="str">
         <f t="shared" si="18"/>
-        <v>insp_ext = ''</v>
+        <v>insp_bot = ''</v>
       </c>
       <c r="P84" t="s">
         <v>566</v>
       </c>
       <c r="Q84" t="str">
         <f t="shared" si="19"/>
-        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["insp_ext"]}: {e}')</v>
+        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["insp_bot"]}: {e}')</v>
       </c>
       <c r="R84" t="str">
         <f t="shared" si="20"/>
-        <v>insp_ext = ''</v>
+        <v>insp_bot = ''</v>
       </c>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="B85" t="str">
-        <f t="shared" si="21"/>
-        <v>insp_dh.png</v>
+        <f t="shared" si="23"/>
+        <v>insp_ext.png</v>
       </c>
       <c r="C85" t="str">
-        <f t="shared" si="22"/>
-        <v>{{ insp_dh }}</v>
+        <f t="shared" si="24"/>
+        <v>{{ insp_ext }}</v>
       </c>
       <c r="D85">
         <v>190</v>
@@ -19894,62 +19904,62 @@
         <v>576</v>
       </c>
       <c r="G85" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>'ubicación_gas' : r_val['ubicación_gas'],</v>
       </c>
       <c r="H85" t="str">
         <f t="shared" si="13"/>
-        <v>'insp_dh': insp_dh,</v>
+        <v>'insp_ext': insp_ext,</v>
       </c>
       <c r="I85" t="s">
         <v>565</v>
       </c>
       <c r="J85" t="str">
         <f t="shared" si="14"/>
-        <v>img_path_insp_dh = os.path.join(IMAGES_PATH, r_val["insp_dh"])</v>
+        <v>img_path_insp_ext = os.path.join(IMAGES_PATH, r_val["insp_ext"])</v>
       </c>
       <c r="K85" t="str">
         <f t="shared" si="15"/>
-        <v>if os.path.exists(img_path_insp_dh):</v>
+        <v>if os.path.exists(img_path_insp_ext):</v>
       </c>
       <c r="L85" t="str">
         <f t="shared" si="16"/>
-        <v>insp_dh = InlineImage(docx_tpl, img_path_insp_dh, height=Mm(190))</v>
+        <v>insp_ext = InlineImage(docx_tpl, img_path_insp_ext, height=Mm(190))</v>
       </c>
       <c r="M85" t="s">
         <v>567</v>
       </c>
       <c r="N85" t="str">
         <f t="shared" si="17"/>
-        <v>print(f'Advertencia: No se encontró la imagen {r_val["insp_dh"]}')</v>
+        <v>print(f'Advertencia: No se encontró la imagen {r_val["insp_ext"]}')</v>
       </c>
       <c r="O85" t="str">
         <f t="shared" si="18"/>
-        <v>insp_dh = ''</v>
+        <v>insp_ext = ''</v>
       </c>
       <c r="P85" t="s">
         <v>566</v>
       </c>
       <c r="Q85" t="str">
         <f t="shared" si="19"/>
-        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["insp_dh"]}: {e}')</v>
+        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["insp_ext"]}: {e}')</v>
       </c>
       <c r="R85" t="str">
         <f t="shared" si="20"/>
-        <v>insp_dh = ''</v>
+        <v>insp_ext = ''</v>
       </c>
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B86" t="str">
-        <f t="shared" si="21"/>
-        <v>insp_lamp.png</v>
+        <f t="shared" si="23"/>
+        <v>insp_dh.png</v>
       </c>
       <c r="C86" t="str">
-        <f t="shared" si="22"/>
-        <v>{{ insp_lamp }}</v>
+        <f t="shared" si="24"/>
+        <v>{{ insp_dh }}</v>
       </c>
       <c r="D86">
         <v>190</v>
@@ -19961,62 +19971,62 @@
         <v>306</v>
       </c>
       <c r="G86" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>'equipo_brigada' : r_val['equipo_brigada'],</v>
       </c>
       <c r="H86" t="str">
         <f t="shared" si="13"/>
-        <v>'insp_lamp': insp_lamp,</v>
+        <v>'insp_dh': insp_dh,</v>
       </c>
       <c r="I86" t="s">
         <v>565</v>
       </c>
       <c r="J86" t="str">
         <f t="shared" si="14"/>
-        <v>img_path_insp_lamp = os.path.join(IMAGES_PATH, r_val["insp_lamp"])</v>
+        <v>img_path_insp_dh = os.path.join(IMAGES_PATH, r_val["insp_dh"])</v>
       </c>
       <c r="K86" t="str">
         <f t="shared" si="15"/>
-        <v>if os.path.exists(img_path_insp_lamp):</v>
+        <v>if os.path.exists(img_path_insp_dh):</v>
       </c>
       <c r="L86" t="str">
         <f t="shared" si="16"/>
-        <v>insp_lamp = InlineImage(docx_tpl, img_path_insp_lamp, height=Mm(190))</v>
+        <v>insp_dh = InlineImage(docx_tpl, img_path_insp_dh, height=Mm(190))</v>
       </c>
       <c r="M86" t="s">
         <v>567</v>
       </c>
       <c r="N86" t="str">
         <f t="shared" si="17"/>
-        <v>print(f'Advertencia: No se encontró la imagen {r_val["insp_lamp"]}')</v>
+        <v>print(f'Advertencia: No se encontró la imagen {r_val["insp_dh"]}')</v>
       </c>
       <c r="O86" t="str">
         <f t="shared" si="18"/>
-        <v>insp_lamp = ''</v>
+        <v>insp_dh = ''</v>
       </c>
       <c r="P86" t="s">
         <v>566</v>
       </c>
       <c r="Q86" t="str">
         <f t="shared" si="19"/>
-        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["insp_lamp"]}: {e}')</v>
+        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["insp_dh"]}: {e}')</v>
       </c>
       <c r="R86" t="str">
         <f t="shared" si="20"/>
-        <v>insp_lamp = ''</v>
+        <v>insp_dh = ''</v>
       </c>
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B87" t="str">
-        <f t="shared" si="21"/>
-        <v>insp_alarm.png</v>
+        <f t="shared" si="23"/>
+        <v>insp_lamp.png</v>
       </c>
       <c r="C87" t="str">
-        <f t="shared" si="22"/>
-        <v>{{ insp_alarm }}</v>
+        <f t="shared" si="24"/>
+        <v>{{ insp_lamp }}</v>
       </c>
       <c r="D87">
         <v>190</v>
@@ -20028,62 +20038,62 @@
         <v>584</v>
       </c>
       <c r="G87" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>'ubicacion_brigada' : r_val['ubicacion_brigada'],</v>
       </c>
       <c r="H87" t="str">
         <f t="shared" si="13"/>
-        <v>'insp_alarm': insp_alarm,</v>
+        <v>'insp_lamp': insp_lamp,</v>
       </c>
       <c r="I87" t="s">
         <v>565</v>
       </c>
       <c r="J87" t="str">
         <f t="shared" si="14"/>
-        <v>img_path_insp_alarm = os.path.join(IMAGES_PATH, r_val["insp_alarm"])</v>
+        <v>img_path_insp_lamp = os.path.join(IMAGES_PATH, r_val["insp_lamp"])</v>
       </c>
       <c r="K87" t="str">
         <f t="shared" si="15"/>
-        <v>if os.path.exists(img_path_insp_alarm):</v>
+        <v>if os.path.exists(img_path_insp_lamp):</v>
       </c>
       <c r="L87" t="str">
         <f t="shared" si="16"/>
-        <v>insp_alarm = InlineImage(docx_tpl, img_path_insp_alarm, height=Mm(190))</v>
+        <v>insp_lamp = InlineImage(docx_tpl, img_path_insp_lamp, height=Mm(190))</v>
       </c>
       <c r="M87" t="s">
         <v>567</v>
       </c>
       <c r="N87" t="str">
         <f t="shared" si="17"/>
-        <v>print(f'Advertencia: No se encontró la imagen {r_val["insp_alarm"]}')</v>
+        <v>print(f'Advertencia: No se encontró la imagen {r_val["insp_lamp"]}')</v>
       </c>
       <c r="O87" t="str">
         <f t="shared" si="18"/>
-        <v>insp_alarm = ''</v>
+        <v>insp_lamp = ''</v>
       </c>
       <c r="P87" t="s">
         <v>566</v>
       </c>
       <c r="Q87" t="str">
         <f t="shared" si="19"/>
-        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["insp_alarm"]}: {e}')</v>
+        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["insp_lamp"]}: {e}')</v>
       </c>
       <c r="R87" t="str">
         <f t="shared" si="20"/>
-        <v>insp_alarm = ''</v>
+        <v>insp_lamp = ''</v>
       </c>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>731</v>
+        <v>736</v>
       </c>
       <c r="B88" t="str">
-        <f t="shared" si="21"/>
-        <v>ev_sim1.png</v>
+        <f t="shared" si="23"/>
+        <v>insp_alarm.png</v>
       </c>
       <c r="C88" t="str">
-        <f t="shared" si="22"/>
-        <v>{{ ev_sim1 }}</v>
+        <f t="shared" si="24"/>
+        <v>{{ insp_alarm }}</v>
       </c>
       <c r="D88">
         <v>190</v>
@@ -20095,62 +20105,62 @@
         <v>716</v>
       </c>
       <c r="G88" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>'ubiacion_brigadas' : r_val['ubiacion_brigadas'],</v>
       </c>
       <c r="H88" t="str">
         <f t="shared" si="13"/>
-        <v>'ev_sim1': ev_sim1,</v>
+        <v>'insp_alarm': insp_alarm,</v>
       </c>
       <c r="I88" t="s">
         <v>565</v>
       </c>
       <c r="J88" t="str">
         <f t="shared" si="14"/>
-        <v>img_path_ev_sim1 = os.path.join(IMAGES_PATH, r_val["ev_sim1"])</v>
+        <v>img_path_insp_alarm = os.path.join(IMAGES_PATH, r_val["insp_alarm"])</v>
       </c>
       <c r="K88" t="str">
         <f t="shared" si="15"/>
-        <v>if os.path.exists(img_path_ev_sim1):</v>
+        <v>if os.path.exists(img_path_insp_alarm):</v>
       </c>
       <c r="L88" t="str">
         <f t="shared" si="16"/>
-        <v>ev_sim1 = InlineImage(docx_tpl, img_path_ev_sim1, height=Mm(190))</v>
+        <v>insp_alarm = InlineImage(docx_tpl, img_path_insp_alarm, height=Mm(190))</v>
       </c>
       <c r="M88" t="s">
         <v>567</v>
       </c>
       <c r="N88" t="str">
         <f t="shared" si="17"/>
-        <v>print(f'Advertencia: No se encontró la imagen {r_val["ev_sim1"]}')</v>
+        <v>print(f'Advertencia: No se encontró la imagen {r_val["insp_alarm"]}')</v>
       </c>
       <c r="O88" t="str">
         <f t="shared" si="18"/>
-        <v>ev_sim1 = ''</v>
+        <v>insp_alarm = ''</v>
       </c>
       <c r="P88" t="s">
         <v>566</v>
       </c>
       <c r="Q88" t="str">
         <f t="shared" si="19"/>
-        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["ev_sim1"]}: {e}')</v>
+        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["insp_alarm"]}: {e}')</v>
       </c>
       <c r="R88" t="str">
         <f t="shared" si="20"/>
-        <v>ev_sim1 = ''</v>
+        <v>insp_alarm = ''</v>
       </c>
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B89" t="str">
-        <f t="shared" si="21"/>
-        <v>ev_sim2.png</v>
+        <f t="shared" si="23"/>
+        <v>ev_sim1.png</v>
       </c>
       <c r="C89" t="str">
-        <f t="shared" si="22"/>
-        <v>{{ ev_sim2 }}</v>
+        <f t="shared" si="24"/>
+        <v>{{ ev_sim1 }}</v>
       </c>
       <c r="D89">
         <v>190</v>
@@ -20162,62 +20172,62 @@
         <v>307</v>
       </c>
       <c r="G89" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>'lampara' : r_val['lampara'],</v>
       </c>
       <c r="H89" t="str">
         <f t="shared" si="13"/>
-        <v>'ev_sim2': ev_sim2,</v>
+        <v>'ev_sim1': ev_sim1,</v>
       </c>
       <c r="I89" t="s">
         <v>565</v>
       </c>
       <c r="J89" t="str">
         <f t="shared" si="14"/>
-        <v>img_path_ev_sim2 = os.path.join(IMAGES_PATH, r_val["ev_sim2"])</v>
+        <v>img_path_ev_sim1 = os.path.join(IMAGES_PATH, r_val["ev_sim1"])</v>
       </c>
       <c r="K89" t="str">
         <f t="shared" si="15"/>
-        <v>if os.path.exists(img_path_ev_sim2):</v>
+        <v>if os.path.exists(img_path_ev_sim1):</v>
       </c>
       <c r="L89" t="str">
         <f t="shared" si="16"/>
-        <v>ev_sim2 = InlineImage(docx_tpl, img_path_ev_sim2, height=Mm(190))</v>
+        <v>ev_sim1 = InlineImage(docx_tpl, img_path_ev_sim1, height=Mm(190))</v>
       </c>
       <c r="M89" t="s">
         <v>567</v>
       </c>
       <c r="N89" t="str">
         <f t="shared" si="17"/>
-        <v>print(f'Advertencia: No se encontró la imagen {r_val["ev_sim2"]}')</v>
+        <v>print(f'Advertencia: No se encontró la imagen {r_val["ev_sim1"]}')</v>
       </c>
       <c r="O89" t="str">
         <f t="shared" si="18"/>
-        <v>ev_sim2 = ''</v>
+        <v>ev_sim1 = ''</v>
       </c>
       <c r="P89" t="s">
         <v>566</v>
       </c>
       <c r="Q89" t="str">
         <f t="shared" si="19"/>
-        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["ev_sim2"]}: {e}')</v>
+        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["ev_sim1"]}: {e}')</v>
       </c>
       <c r="R89" t="str">
         <f t="shared" si="20"/>
-        <v>ev_sim2 = ''</v>
+        <v>ev_sim1 = ''</v>
       </c>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B90" t="str">
-        <f t="shared" si="21"/>
-        <v>visitas.png</v>
+        <f t="shared" si="23"/>
+        <v>ev_sim2.png</v>
       </c>
       <c r="C90" t="str">
-        <f t="shared" si="22"/>
-        <v>{{ visitas }}</v>
+        <f t="shared" si="24"/>
+        <v>{{ ev_sim2 }}</v>
       </c>
       <c r="D90">
         <v>190</v>
@@ -20229,52 +20239,66 @@
         <v>568</v>
       </c>
       <c r="G90" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>'ubicacion_lampara' : r_val['ubicacion_lampara'],</v>
       </c>
       <c r="H90" t="str">
         <f t="shared" si="13"/>
-        <v>'visitas': visitas,</v>
+        <v>'ev_sim2': ev_sim2,</v>
       </c>
       <c r="I90" t="s">
         <v>565</v>
       </c>
       <c r="J90" t="str">
         <f t="shared" si="14"/>
-        <v>img_path_visitas = os.path.join(IMAGES_PATH, r_val["visitas"])</v>
+        <v>img_path_ev_sim2 = os.path.join(IMAGES_PATH, r_val["ev_sim2"])</v>
       </c>
       <c r="K90" t="str">
         <f t="shared" si="15"/>
-        <v>if os.path.exists(img_path_visitas):</v>
+        <v>if os.path.exists(img_path_ev_sim2):</v>
       </c>
       <c r="L90" t="str">
         <f t="shared" si="16"/>
-        <v>visitas = InlineImage(docx_tpl, img_path_visitas, height=Mm(190))</v>
+        <v>ev_sim2 = InlineImage(docx_tpl, img_path_ev_sim2, height=Mm(190))</v>
       </c>
       <c r="M90" t="s">
         <v>567</v>
       </c>
       <c r="N90" t="str">
         <f t="shared" si="17"/>
-        <v>print(f'Advertencia: No se encontró la imagen {r_val["visitas"]}')</v>
+        <v>print(f'Advertencia: No se encontró la imagen {r_val["ev_sim2"]}')</v>
       </c>
       <c r="O90" t="str">
         <f t="shared" si="18"/>
-        <v>visitas = ''</v>
+        <v>ev_sim2 = ''</v>
       </c>
       <c r="P90" t="s">
         <v>566</v>
       </c>
       <c r="Q90" t="str">
         <f t="shared" si="19"/>
-        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["visitas"]}: {e}')</v>
+        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["ev_sim2"]}: {e}')</v>
       </c>
       <c r="R90" t="str">
         <f t="shared" si="20"/>
-        <v>visitas = ''</v>
+        <v>ev_sim2 = ''</v>
       </c>
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>733</v>
+      </c>
+      <c r="B91" t="str">
+        <f t="shared" si="23"/>
+        <v>visitas.png</v>
+      </c>
+      <c r="C91" t="str">
+        <f t="shared" si="24"/>
+        <v>{{ visitas }}</v>
+      </c>
+      <c r="D91">
+        <v>190</v>
+      </c>
       <c r="E91" t="s">
         <v>22</v>
       </c>
@@ -20282,7 +20306,7 @@
         <v>308</v>
       </c>
       <c r="G91" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>'baterias' : r_val['baterias'],</v>
       </c>
     </row>
@@ -20294,7 +20318,7 @@
         <v>578</v>
       </c>
       <c r="G92" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>'ubiacion_baterias' : r_val['ubiacion_baterias'],</v>
       </c>
     </row>
@@ -20306,7 +20330,7 @@
         <v>309</v>
       </c>
       <c r="G93" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>'tambo_arena' : r_val['tambo_arena'],</v>
       </c>
     </row>
@@ -20318,7 +20342,7 @@
         <v>570</v>
       </c>
       <c r="G94" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>'ubicacion_tambo' : r_val['ubicacion_tambo'],</v>
       </c>
     </row>
@@ -20330,7 +20354,7 @@
         <v>310</v>
       </c>
       <c r="G95" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>'tanques' : r_val['tanques'],</v>
       </c>
     </row>
@@ -20342,7 +20366,7 @@
         <v>311</v>
       </c>
       <c r="G96" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>'tanque_1' : r_val['tanque_1'],</v>
       </c>
     </row>
@@ -20354,7 +20378,7 @@
         <v>312</v>
       </c>
       <c r="G97" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>'tanque_2' : r_val['tanque_2'],</v>
       </c>
     </row>
@@ -20366,7 +20390,7 @@
         <v>313</v>
       </c>
       <c r="G98" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>'tanque_3' : r_val['tanque_3'],</v>
       </c>
     </row>
@@ -20378,7 +20402,7 @@
         <v>314</v>
       </c>
       <c r="G99" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>'dia' : r_val['dia'],</v>
       </c>
     </row>
@@ -20390,7 +20414,7 @@
         <v>315</v>
       </c>
       <c r="G100" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>'mes' : r_val['mes'],</v>
       </c>
     </row>
@@ -20402,7 +20426,7 @@
         <v>316</v>
       </c>
       <c r="G101" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>'anio' : r_val['anio'],</v>
       </c>
     </row>
@@ -20414,7 +20438,7 @@
         <v>317</v>
       </c>
       <c r="G102" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>'coordenadas' : r_val['coordenadas'],</v>
       </c>
     </row>
@@ -20426,7 +20450,7 @@
         <v>318</v>
       </c>
       <c r="G103" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>'norte' : r_val['norte'],</v>
       </c>
     </row>
@@ -20438,7 +20462,7 @@
         <v>319</v>
       </c>
       <c r="G104" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>'sur' : r_val['sur'],</v>
       </c>
     </row>
@@ -20450,7 +20474,7 @@
         <v>320</v>
       </c>
       <c r="G105" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>'este' : r_val['este'],</v>
       </c>
     </row>
@@ -20462,7 +20486,7 @@
         <v>321</v>
       </c>
       <c r="G106" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>'oeste' : r_val['oeste'],</v>
       </c>
     </row>
@@ -20474,7 +20498,7 @@
         <v>605</v>
       </c>
       <c r="G107" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>'ref_llegar' : r_val['ref_llegar'],</v>
       </c>
     </row>
@@ -20486,7 +20510,7 @@
         <v>322</v>
       </c>
       <c r="G108" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>'ley' : r_val['ley'],</v>
       </c>
     </row>
@@ -20498,7 +20522,7 @@
         <v>323</v>
       </c>
       <c r="G109" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>'reglamento' : r_val['reglamento'],</v>
       </c>
     </row>
@@ -20510,7 +20534,7 @@
         <v>694</v>
       </c>
       <c r="G110" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>'m_dir' : r_val['m_dir'],</v>
       </c>
     </row>
@@ -20522,7 +20546,7 @@
         <v>324</v>
       </c>
       <c r="G111" t="str">
-        <f t="shared" ref="G111:G142" si="24">+_xlfn.CONCAT("'",E111,"' : r_val['",E111,"'],")</f>
+        <f t="shared" ref="G111:G142" si="26">+_xlfn.CONCAT("'",E111,"' : r_val['",E111,"'],")</f>
         <v>'coord_suplente' : r_val['coord_suplente'],</v>
       </c>
     </row>
@@ -20534,7 +20558,7 @@
         <v>695</v>
       </c>
       <c r="G112" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>'m_jef_caj' : r_val['m_jef_caj'],</v>
       </c>
     </row>
@@ -20546,7 +20570,7 @@
         <v>325</v>
       </c>
       <c r="G113" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>'evacuacion' : r_val['evacuacion'],</v>
       </c>
     </row>
@@ -20558,7 +20582,7 @@
         <v>596</v>
       </c>
       <c r="G114" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>'evac_puesto' : r_val['evac_puesto'],</v>
       </c>
     </row>
@@ -20570,7 +20594,7 @@
         <v>696</v>
       </c>
       <c r="G115" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>'m_evac' : r_val['m_evac'],</v>
       </c>
     </row>
@@ -20582,7 +20606,7 @@
         <v>326</v>
       </c>
       <c r="G116" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>'evac_suplente' : r_val['evac_suplente'],</v>
       </c>
     </row>
@@ -20594,7 +20618,7 @@
         <v>597</v>
       </c>
       <c r="G117" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>'supl_evac_pue' : r_val['supl_evac_pue'],</v>
       </c>
     </row>
@@ -20606,7 +20630,7 @@
         <v>697</v>
       </c>
       <c r="G118" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>'m_supl_evac' : r_val['m_supl_evac'],</v>
       </c>
     </row>
@@ -20618,7 +20642,7 @@
         <v>327</v>
       </c>
       <c r="G119" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>'incendios' : r_val['incendios'],</v>
       </c>
     </row>
@@ -20630,7 +20654,7 @@
         <v>598</v>
       </c>
       <c r="G120" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>'incen_puesto' : r_val['incen_puesto'],</v>
       </c>
     </row>
@@ -20642,7 +20666,7 @@
         <v>698</v>
       </c>
       <c r="G121" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>'m_inc' : r_val['m_inc'],</v>
       </c>
     </row>
@@ -20654,7 +20678,7 @@
         <v>328</v>
       </c>
       <c r="G122" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>'inc_suplente' : r_val['inc_suplente'],</v>
       </c>
     </row>
@@ -20666,7 +20690,7 @@
         <v>599</v>
       </c>
       <c r="G123" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>'supl_inc_puesto' : r_val['supl_inc_puesto'],</v>
       </c>
     </row>
@@ -20678,7 +20702,7 @@
         <v>699</v>
       </c>
       <c r="G124" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>'m_supl_inc' : r_val['m_supl_inc'],</v>
       </c>
     </row>
@@ -20690,7 +20714,7 @@
         <v>329</v>
       </c>
       <c r="G125" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>'primeros_auxilios' : r_val['primeros_auxilios'],</v>
       </c>
     </row>
@@ -20702,7 +20726,7 @@
         <v>600</v>
       </c>
       <c r="G126" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>'prim_aux_puesto' : r_val['prim_aux_puesto'],</v>
       </c>
     </row>
@@ -20714,7 +20738,7 @@
         <v>700</v>
       </c>
       <c r="G127" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>'m_prim_aux' : r_val['m_prim_aux'],</v>
       </c>
     </row>
@@ -20726,7 +20750,7 @@
         <v>330</v>
       </c>
       <c r="G128" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>'aux_suplente' : r_val['aux_suplente'],</v>
       </c>
     </row>
@@ -20738,7 +20762,7 @@
         <v>601</v>
       </c>
       <c r="G129" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>'supl_prim_aux_puesto' : r_val['supl_prim_aux_puesto'],</v>
       </c>
     </row>
@@ -20750,7 +20774,7 @@
         <v>701</v>
       </c>
       <c r="G130" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>'m_supl_paux' : r_val['m_supl_paux'],</v>
       </c>
     </row>
@@ -20762,7 +20786,7 @@
         <v>331</v>
       </c>
       <c r="G131" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>'busqueda' : r_val['busqueda'],</v>
       </c>
     </row>
@@ -20774,7 +20798,7 @@
         <v>602</v>
       </c>
       <c r="G132" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>'busq_puesto' : r_val['busq_puesto'],</v>
       </c>
     </row>
@@ -20786,7 +20810,7 @@
         <v>702</v>
       </c>
       <c r="G133" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>'m_busq' : r_val['m_busq'],</v>
       </c>
     </row>
@@ -20798,7 +20822,7 @@
         <v>332</v>
       </c>
       <c r="G134" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>'busq_suplente' : r_val['busq_suplente'],</v>
       </c>
     </row>
@@ -20810,7 +20834,7 @@
         <v>603</v>
       </c>
       <c r="G135" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>'supl_busq_puesto' : r_val['supl_busq_puesto'],</v>
       </c>
     </row>
@@ -20822,7 +20846,7 @@
         <v>703</v>
       </c>
       <c r="G136" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>'m_supl_busq' : r_val['m_supl_busq'],</v>
       </c>
     </row>
@@ -20834,7 +20858,7 @@
         <v>333</v>
       </c>
       <c r="G137" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>'descrip_gi' : r_val['descrip_gi'],</v>
       </c>
     </row>
@@ -20846,7 +20870,7 @@
         <v>334</v>
       </c>
       <c r="G138" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>'gas_inflamable' : r_val['gas_inflamable'],</v>
       </c>
     </row>
@@ -20858,7 +20882,7 @@
         <v>335</v>
       </c>
       <c r="G139" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>'valor_gi' : r_val['valor_gi'],</v>
       </c>
     </row>
@@ -20870,7 +20894,7 @@
         <v>336</v>
       </c>
       <c r="G140" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>'descrp_li' : r_val['descrp_li'],</v>
       </c>
     </row>
@@ -20882,7 +20906,7 @@
         <v>337</v>
       </c>
       <c r="G141" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>'liquido_inflamable' : r_val['liquido_inflamable'],</v>
       </c>
     </row>
@@ -20894,7 +20918,7 @@
         <v>338</v>
       </c>
       <c r="G142" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>'valor_li' : r_val['valor_li'],</v>
       </c>
     </row>
@@ -20906,7 +20930,7 @@
         <v>339</v>
       </c>
       <c r="G143" t="str">
-        <f t="shared" ref="G143:G179" si="25">+_xlfn.CONCAT("'",E143,"' : r_val['",E143,"'],")</f>
+        <f t="shared" ref="G143:G179" si="27">+_xlfn.CONCAT("'",E143,"' : r_val['",E143,"'],")</f>
         <v>'descrip_lc' : r_val['descrip_lc'],</v>
       </c>
     </row>
@@ -20918,7 +20942,7 @@
         <v>340</v>
       </c>
       <c r="G144" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>'liquido_combustible' : r_val['liquido_combustible'],</v>
       </c>
     </row>
@@ -20930,7 +20954,7 @@
         <v>341</v>
       </c>
       <c r="G145" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>'valor_lc' : r_val['valor_lc'],</v>
       </c>
     </row>
@@ -20942,7 +20966,7 @@
         <v>342</v>
       </c>
       <c r="G146" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>'descrip_sc' : r_val['descrip_sc'],</v>
       </c>
     </row>
@@ -20954,7 +20978,7 @@
         <v>343</v>
       </c>
       <c r="G147" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>'solido_combusible' : r_val['solido_combusible'],</v>
       </c>
     </row>
@@ -20966,7 +20990,7 @@
         <v>344</v>
       </c>
       <c r="G148" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>'valor_sc' : r_val['valor_sc'],</v>
       </c>
     </row>
@@ -20978,7 +21002,7 @@
         <v>345</v>
       </c>
       <c r="G149" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>'tipo_riesgo' : r_val['tipo_riesgo'],</v>
       </c>
     </row>
@@ -20990,7 +21014,7 @@
         <v>664</v>
       </c>
       <c r="G150" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>'nombre1' : r_val['nombre1'],</v>
       </c>
     </row>
@@ -21002,7 +21026,7 @@
         <v>665</v>
       </c>
       <c r="G151" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>'puesto1' : r_val['puesto1'],</v>
       </c>
     </row>
@@ -21014,7 +21038,7 @@
         <v>666</v>
       </c>
       <c r="G152" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>'m1' : r_val['m1'],</v>
       </c>
     </row>
@@ -21026,7 +21050,7 @@
         <v>667</v>
       </c>
       <c r="G153" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>'nombre2' : r_val['nombre2'],</v>
       </c>
     </row>
@@ -21038,7 +21062,7 @@
         <v>668</v>
       </c>
       <c r="G154" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>'puesto2' : r_val['puesto2'],</v>
       </c>
     </row>
@@ -21050,7 +21074,7 @@
         <v>669</v>
       </c>
       <c r="G155" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>'m2' : r_val['m2'],</v>
       </c>
     </row>
@@ -21062,7 +21086,7 @@
         <v>670</v>
       </c>
       <c r="G156" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>'nombre3' : r_val['nombre3'],</v>
       </c>
     </row>
@@ -21074,7 +21098,7 @@
         <v>671</v>
       </c>
       <c r="G157" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>'puesto3' : r_val['puesto3'],</v>
       </c>
     </row>
@@ -21086,7 +21110,7 @@
         <v>672</v>
       </c>
       <c r="G158" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>'m3' : r_val['m3'],</v>
       </c>
     </row>
@@ -21098,7 +21122,7 @@
         <v>673</v>
       </c>
       <c r="G159" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>'nombre4' : r_val['nombre4'],</v>
       </c>
     </row>
@@ -21110,7 +21134,7 @@
         <v>674</v>
       </c>
       <c r="G160" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>'puesto4' : r_val['puesto4'],</v>
       </c>
     </row>
@@ -21122,7 +21146,7 @@
         <v>675</v>
       </c>
       <c r="G161" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>'m4' : r_val['m4'],</v>
       </c>
     </row>
@@ -21134,7 +21158,7 @@
         <v>676</v>
       </c>
       <c r="G162" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>'nombre5' : r_val['nombre5'],</v>
       </c>
     </row>
@@ -21146,7 +21170,7 @@
         <v>677</v>
       </c>
       <c r="G163" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>'puesto5' : r_val['puesto5'],</v>
       </c>
     </row>
@@ -21158,7 +21182,7 @@
         <v>678</v>
       </c>
       <c r="G164" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>'m5' : r_val['m5'],</v>
       </c>
     </row>
@@ -21170,7 +21194,7 @@
         <v>679</v>
       </c>
       <c r="G165" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>'nombre6' : r_val['nombre6'],</v>
       </c>
     </row>
@@ -21182,7 +21206,7 @@
         <v>680</v>
       </c>
       <c r="G166" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>'puesto6' : r_val['puesto6'],</v>
       </c>
     </row>
@@ -21194,7 +21218,7 @@
         <v>681</v>
       </c>
       <c r="G167" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>'m6' : r_val['m6'],</v>
       </c>
     </row>
@@ -21206,7 +21230,7 @@
         <v>682</v>
       </c>
       <c r="G168" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>'nombre7' : r_val['nombre7'],</v>
       </c>
     </row>
@@ -21218,7 +21242,7 @@
         <v>683</v>
       </c>
       <c r="G169" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>'puesto7' : r_val['puesto7'],</v>
       </c>
     </row>
@@ -21230,7 +21254,7 @@
         <v>684</v>
       </c>
       <c r="G170" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>'m7' : r_val['m7'],</v>
       </c>
     </row>
@@ -21242,7 +21266,7 @@
         <v>685</v>
       </c>
       <c r="G171" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>'nombre8' : r_val['nombre8'],</v>
       </c>
     </row>
@@ -21254,7 +21278,7 @@
         <v>686</v>
       </c>
       <c r="G172" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>'puesto8' : r_val['puesto8'],</v>
       </c>
     </row>
@@ -21266,7 +21290,7 @@
         <v>687</v>
       </c>
       <c r="G173" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>'m8' : r_val['m8'],</v>
       </c>
     </row>
@@ -21278,7 +21302,7 @@
         <v>688</v>
       </c>
       <c r="G174" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>'nombre9' : r_val['nombre9'],</v>
       </c>
     </row>
@@ -21290,7 +21314,7 @@
         <v>689</v>
       </c>
       <c r="G175" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>'puesto9' : r_val['puesto9'],</v>
       </c>
     </row>
@@ -21302,7 +21326,7 @@
         <v>690</v>
       </c>
       <c r="G176" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>'m9' : r_val['m9'],</v>
       </c>
     </row>
@@ -21314,7 +21338,7 @@
         <v>691</v>
       </c>
       <c r="G177" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>'nombre10' : r_val['nombre10'],</v>
       </c>
     </row>
@@ -21326,7 +21350,7 @@
         <v>692</v>
       </c>
       <c r="G178" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>'puesto10' : r_val['puesto10'],</v>
       </c>
     </row>
@@ -21338,7 +21362,7 @@
         <v>693</v>
       </c>
       <c r="G179" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>'m10' : r_val['m10'],</v>
       </c>
     </row>

--- a/Inputs/BD.xlsx
+++ b/Inputs/BD.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/078e1a455e5c02ce/Documentos/GitHub/Proyecto_PIPC/Inputs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gutie\OneDrive\Documentos\GitHub\Proyecto_PIPC\Inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="904" documentId="13_ncr:1_{CF2C40B5-0007-4E87-85E3-0CDB05564647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9808526-DB16-45A8-9CC2-31AA882EC5E6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D3A426E-EC5E-453A-8CC7-F83B71F24F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3F095A75-F066-4695-8672-8D4315F1EF23}"/>
   </bookViews>
@@ -38,6 +38,40 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Luis G</author>
+  </authors>
+  <commentList>
+    <comment ref="DH25" authorId="0" shapeId="0" xr:uid="{74917839-16A8-46CF-9225-D9E52633B0E0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Luis G:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+CAJERO UNIVERSAL A</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Luis G</author>
@@ -313,7 +347,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2164" uniqueCount="1003">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2786" uniqueCount="1240">
   <si>
     <t>dia</t>
   </si>
@@ -2694,9 +2728,6 @@
     <t>13 DE ABRIL DE 2000</t>
   </si>
   <si>
-    <t>CARLOR GONZALEZ ROMERO</t>
-  </si>
-  <si>
     <t>BOMBAS, OFICINA, VENTEO</t>
   </si>
   <si>
@@ -2964,9 +2995,6 @@
     <t>ARACELI SANCHEZ BERMEO</t>
   </si>
   <si>
-    <t>CAJERO UNVIVERSAL B</t>
-  </si>
-  <si>
     <t>MB88229</t>
   </si>
   <si>
@@ -3063,18 +3091,12 @@
     <t>MI03847</t>
   </si>
   <si>
-    <t>CR 511 JUAREZ</t>
-  </si>
-  <si>
     <t xml:space="preserve"> AV. JUAREZ</t>
   </si>
   <si>
     <t>10 CAJONES</t>
   </si>
   <si>
-    <t>OFICINA DIRECTOR</t>
-  </si>
-  <si>
     <t>MB09216</t>
   </si>
   <si>
@@ -3168,9 +3190,6 @@
     <t>MI05214</t>
   </si>
   <si>
-    <t>CR 738 PLAZA ZAVALETA</t>
-  </si>
-  <si>
     <t>CALZADA ZAVALETA</t>
   </si>
   <si>
@@ -3243,18 +3262,9 @@
     <t>ANA YESSENIA CHAVARRIA CORONA</t>
   </si>
   <si>
-    <t>CR 2375 HIPOTECARIA SUR</t>
-  </si>
-  <si>
     <t>GABRIELA GUADARRAMA ISLAS</t>
   </si>
   <si>
-    <t>AREA INTERNA Y ESCRITORIOS</t>
-  </si>
-  <si>
-    <t>AREA INTERNA, ON LINE, AREA COMUN</t>
-  </si>
-  <si>
     <t>EN TODA LA OFICINA</t>
   </si>
   <si>
@@ -3322,6 +3332,741 @@
   </si>
   <si>
     <t>MI16323</t>
+  </si>
+  <si>
+    <t>9 SUR</t>
+  </si>
+  <si>
+    <t>LOCAL 14</t>
+  </si>
+  <si>
+    <t>LOCAL 1</t>
+  </si>
+  <si>
+    <t>LOCAL A</t>
+  </si>
+  <si>
+    <t>SAN BARTOLO COATEPEC</t>
+  </si>
+  <si>
+    <t>carolina.hernandez@bbva.com</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE BAUTISTA AYALA</t>
+  </si>
+  <si>
+    <t>ON LINE, AREA COMUN, AREA INTERNA</t>
+  </si>
+  <si>
+    <t>MB95345</t>
+  </si>
+  <si>
+    <t>CAROLINA HERNANDEZ CHAVEZ</t>
+  </si>
+  <si>
+    <t>M845648</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL AGUILAR P</t>
+  </si>
+  <si>
+    <t>MB87020</t>
+  </si>
+  <si>
+    <t>EDGAR TLACOMULCO PALACIOS</t>
+  </si>
+  <si>
+    <t>MI17234</t>
+  </si>
+  <si>
+    <t>DIANA LUZ HERNANDEZ BLANCO</t>
+  </si>
+  <si>
+    <t>MB97269</t>
+  </si>
+  <si>
+    <t>SERGIO ABEL RAMIREZ HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MI30098</t>
+  </si>
+  <si>
+    <t>FRANCISCO JAVIER MENDEZ HERNANDEZ</t>
+  </si>
+  <si>
+    <t>M912073</t>
+  </si>
+  <si>
+    <t>JESSICA MARLEN SALAMANCA SALGADO</t>
+  </si>
+  <si>
+    <t>MB61455</t>
+  </si>
+  <si>
+    <t>MARLEN SAGRARIO MORA QUIRVAN</t>
+  </si>
+  <si>
+    <t>MI15211</t>
+  </si>
+  <si>
+    <t>AMEYALI BERENICE NAVA ORTEGA</t>
+  </si>
+  <si>
+    <t>MB70606</t>
+  </si>
+  <si>
+    <t>POLONGACION 11 SUR</t>
+  </si>
+  <si>
+    <t>LOCAL B C D E</t>
+  </si>
+  <si>
+    <t>MAYORAZGO</t>
+  </si>
+  <si>
+    <t>marina.delao.1@bbva.com</t>
+  </si>
+  <si>
+    <t>ESCRITORIOS Y AREA INTERNA</t>
+  </si>
+  <si>
+    <t>AREA EXTERNA</t>
+  </si>
+  <si>
+    <t>FLORENCIO ORTIZ RAMIREZ</t>
+  </si>
+  <si>
+    <t>M284737</t>
+  </si>
+  <si>
+    <t>MARINA ABIGAIL DE LA O DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>M819010</t>
+  </si>
+  <si>
+    <t>MARTHA PEÑA GUTIERREZ</t>
+  </si>
+  <si>
+    <t>MI0377</t>
+  </si>
+  <si>
+    <t>TAMARA GIOVANNA QUINTERO DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>MB96020</t>
+  </si>
+  <si>
+    <t>MARIA DE LOURDES ROSAS CERON</t>
+  </si>
+  <si>
+    <t>MI22221</t>
+  </si>
+  <si>
+    <t>SONIA ORTEGA HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MB95249</t>
+  </si>
+  <si>
+    <t>JORGE GUADALUPE BELLO GONZALEZ</t>
+  </si>
+  <si>
+    <t>MB85011</t>
+  </si>
+  <si>
+    <t>SERGIO HERNANDEZ HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MI08650</t>
+  </si>
+  <si>
+    <t>KAREN LUCIA CRUZ HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MB57702</t>
+  </si>
+  <si>
+    <t>ABIGAIL CARMELA MONTAÑO MARTINEZ</t>
+  </si>
+  <si>
+    <t>M908040</t>
+  </si>
+  <si>
+    <t>CAROLINA MONTERROSAS PALACIOS</t>
+  </si>
+  <si>
+    <t>BANQUERO SR</t>
+  </si>
+  <si>
+    <t>MB38922</t>
+  </si>
+  <si>
+    <t>DANIELA FERNANDA HERNANDEZ SANABRIA</t>
+  </si>
+  <si>
+    <t>MI24483</t>
+  </si>
+  <si>
+    <t>CR 3738 PUEBLA 5 DE MAYO</t>
+  </si>
+  <si>
+    <t>BLVD HEROES DEL 5 DE MAYO</t>
+  </si>
+  <si>
+    <t>LADRILLERA DE BENITEZ</t>
+  </si>
+  <si>
+    <t>blanca.barroeta@bbva.com</t>
+  </si>
+  <si>
+    <t>CR 511 PUEBLA JUAREZ</t>
+  </si>
+  <si>
+    <t>CR 738 PUEBLA PLAZA ZAVALETA</t>
+  </si>
+  <si>
+    <t>CR 2375 HIPOTECARIA SUR PUEBLA</t>
+  </si>
+  <si>
+    <t>CR 4678 GRAN SUR PUEBLA</t>
+  </si>
+  <si>
+    <t>CR 3747 PUEBLA MAYORAZGO</t>
+  </si>
+  <si>
+    <t>CARLOS GONZALEZ ROMERO</t>
+  </si>
+  <si>
+    <t>LUCIA JIMENEZ HERRERA</t>
+  </si>
+  <si>
+    <t>M49565</t>
+  </si>
+  <si>
+    <t>BLANCA EVELIN BARROETA ESPINOSA</t>
+  </si>
+  <si>
+    <t>M284670</t>
+  </si>
+  <si>
+    <t>JESUS HERNANDEZ CABRERA</t>
+  </si>
+  <si>
+    <t>MI30978</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL GONZALEZ UREÑA</t>
+  </si>
+  <si>
+    <t>MI23088</t>
+  </si>
+  <si>
+    <t>VALERIA IRAIS PUENTES VALENCIA</t>
+  </si>
+  <si>
+    <t>MB93427</t>
+  </si>
+  <si>
+    <t>ANA LAURA SALDAÑA GUTIERREZ</t>
+  </si>
+  <si>
+    <t>MI26961</t>
+  </si>
+  <si>
+    <t>MAXIMILIANO ZENTENO PINEDA</t>
+  </si>
+  <si>
+    <t>MI05009</t>
+  </si>
+  <si>
+    <t>ORIENCIO CRUZ CRUZ</t>
+  </si>
+  <si>
+    <t>MB98003</t>
+  </si>
+  <si>
+    <t>GUILLERMINA MARTINEZ HUERTA</t>
+  </si>
+  <si>
+    <t>MB09243</t>
+  </si>
+  <si>
+    <t>ISAI TAPIA ROSAS</t>
+  </si>
+  <si>
+    <t>MB96606</t>
+  </si>
+  <si>
+    <t>ANA KAREN VARGAS GARFIAS</t>
+  </si>
+  <si>
+    <t>MB94208</t>
+  </si>
+  <si>
+    <t>ANDREA GONZALEZ HIDALGO Y COSTILLA</t>
+  </si>
+  <si>
+    <t>MI29896</t>
+  </si>
+  <si>
+    <t>OMAR ORNELAS LUNA</t>
+  </si>
+  <si>
+    <t>MI14975</t>
+  </si>
+  <si>
+    <t>CR 507 PUEBLA 43 ORIENTE</t>
+  </si>
+  <si>
+    <t>43 ORIENTE</t>
+  </si>
+  <si>
+    <t>HUEXOTITLA</t>
+  </si>
+  <si>
+    <t>luisa.massa@bbva.com</t>
+  </si>
+  <si>
+    <t>LUCIA CARRASCO GARCIA</t>
+  </si>
+  <si>
+    <t>MI5590</t>
+  </si>
+  <si>
+    <t>LUISA OLIVIA MASSA VALERA</t>
+  </si>
+  <si>
+    <t>M46450</t>
+  </si>
+  <si>
+    <t>DIANA LAURA BONILLA CASTILO</t>
+  </si>
+  <si>
+    <t>MB95026</t>
+  </si>
+  <si>
+    <t>SELENA GUADALUPE MANZO CISNEROS</t>
+  </si>
+  <si>
+    <t>MI31329</t>
+  </si>
+  <si>
+    <t>DANIEL ALEJANDRO MARTINEZ LEON</t>
+  </si>
+  <si>
+    <t>MB79132</t>
+  </si>
+  <si>
+    <t>DANIEL MORENO LUNA</t>
+  </si>
+  <si>
+    <t>MI00473</t>
+  </si>
+  <si>
+    <t>AURELIA JUAREZ RAMIREZ</t>
+  </si>
+  <si>
+    <t>M284491</t>
+  </si>
+  <si>
+    <t>ROSARIO VALERIA SUAREZ LUNA</t>
+  </si>
+  <si>
+    <t>MI01720</t>
+  </si>
+  <si>
+    <t>CR 4676 PLAZA SAN DIEGO</t>
+  </si>
+  <si>
+    <t>SUCURSAL BANCARIA</t>
+  </si>
+  <si>
+    <t>BLVD FORJADORES DE PUEBLA</t>
+  </si>
+  <si>
+    <t>LOCAL 8, 9 Y 10</t>
+  </si>
+  <si>
+    <t>MIGUEL JOSE GUZMAN CORDERO</t>
+  </si>
+  <si>
+    <t>MB60957</t>
+  </si>
+  <si>
+    <t>ANTONIO DE JESUS MONTES TORRES</t>
+  </si>
+  <si>
+    <t>M911390</t>
+  </si>
+  <si>
+    <t>ROGELIO GARCIA CUATECATL</t>
+  </si>
+  <si>
+    <t>MB88821</t>
+  </si>
+  <si>
+    <t>HUGO COYOTL CUAMANI</t>
+  </si>
+  <si>
+    <t>MI00816</t>
+  </si>
+  <si>
+    <t>LILIANA ANGELICA SID LINARES</t>
+  </si>
+  <si>
+    <t>M909954</t>
+  </si>
+  <si>
+    <t>BLANCA LETICIA TECUANHUEHUE CALDERON</t>
+  </si>
+  <si>
+    <t>MI30814</t>
+  </si>
+  <si>
+    <t>CAMILA GARCIA HUERTA</t>
+  </si>
+  <si>
+    <t>MI17782</t>
+  </si>
+  <si>
+    <t>EDNA CRISTELL RUIZ SANCHEZ</t>
+  </si>
+  <si>
+    <t>MB88936</t>
+  </si>
+  <si>
+    <t>SALVADOR ROSETE DE SANTIAGO</t>
+  </si>
+  <si>
+    <t>MI15642</t>
+  </si>
+  <si>
+    <t>JUAN ANTONIO TELLEZ MACEDA</t>
+  </si>
+  <si>
+    <t>MI02512</t>
+  </si>
+  <si>
+    <t>CR 527 PUEBLA LAS ANIMAS</t>
+  </si>
+  <si>
+    <t>BLVD ATLIXCO</t>
+  </si>
+  <si>
+    <t>B 11 - 20</t>
+  </si>
+  <si>
+    <t>LAS ANIMAS CENTRO COMERCIAL</t>
+  </si>
+  <si>
+    <t>yetzabelli.tolentino@bbva.com</t>
+  </si>
+  <si>
+    <t>antonio.montes@bbva.com</t>
+  </si>
+  <si>
+    <t>ANA ISABEL RODRIGUEZ PEREZ</t>
+  </si>
+  <si>
+    <t>MB59528</t>
+  </si>
+  <si>
+    <t>YETZABELLI TOLENTINO SAMPAYO</t>
+  </si>
+  <si>
+    <t>MB86288</t>
+  </si>
+  <si>
+    <t>MARIA SANDRA EVA GONZALEZ</t>
+  </si>
+  <si>
+    <t>EJECUTIVO</t>
+  </si>
+  <si>
+    <t>MI14128</t>
+  </si>
+  <si>
+    <t>SERGIO GUTIERREZ VAZQUEZ</t>
+  </si>
+  <si>
+    <t>MB71187</t>
+  </si>
+  <si>
+    <t>JULIO LOPEZ BEJARANO</t>
+  </si>
+  <si>
+    <t>MI13525</t>
+  </si>
+  <si>
+    <t>RUTH ESPINDOLA ALFARO</t>
+  </si>
+  <si>
+    <t>MB11542</t>
+  </si>
+  <si>
+    <t>HECTOR JAVIER RAMIREZ CAMACHO</t>
+  </si>
+  <si>
+    <t>MI19761</t>
+  </si>
+  <si>
+    <t>MARIA GUADALUPE CANSINO ANTONIO</t>
+  </si>
+  <si>
+    <t>MI17479</t>
+  </si>
+  <si>
+    <t>CR 3740 PUEBLA ANIMAS VERGEL</t>
+  </si>
+  <si>
+    <t>CIRCUITO JUAN PABLO II</t>
+  </si>
+  <si>
+    <t>31, 32, 33, 34, 109, 110, 111, 112</t>
+  </si>
+  <si>
+    <t>veronica.macias.1@bbva.com</t>
+  </si>
+  <si>
+    <t>LUIS MIGUEL PEREZ MARQUEZ</t>
+  </si>
+  <si>
+    <t>MB49528</t>
+  </si>
+  <si>
+    <t>VERONICA MIRIAM MACIAS FLORES</t>
+  </si>
+  <si>
+    <t>M818083</t>
+  </si>
+  <si>
+    <t>LETICIA BENITEZ RAMIREZ</t>
+  </si>
+  <si>
+    <t>MI02524</t>
+  </si>
+  <si>
+    <t>JESUS ENRIQUE GARCIA EMETERIO</t>
+  </si>
+  <si>
+    <t>MB69380</t>
+  </si>
+  <si>
+    <t>DIEGO ALTAMIRANO VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>MI19771</t>
+  </si>
+  <si>
+    <t>MARIBEL FIGUEROA TIRADO</t>
+  </si>
+  <si>
+    <t>MI220336</t>
+  </si>
+  <si>
+    <t>ARACELI HERNANDEZ BLANCO</t>
+  </si>
+  <si>
+    <t>M349577</t>
+  </si>
+  <si>
+    <t>BLANCA MELBA DOMINGUEZ ZAVALETA</t>
+  </si>
+  <si>
+    <t>MB98500</t>
+  </si>
+  <si>
+    <t>MYRNA PLIEGO ESCALANTE</t>
+  </si>
+  <si>
+    <t>M284103</t>
+  </si>
+  <si>
+    <t>GABRIELA HERNANDEZ SANCHEZ</t>
+  </si>
+  <si>
+    <t>AUXILIAR</t>
+  </si>
+  <si>
+    <t>M826406</t>
+  </si>
+  <si>
+    <t>ALONDRA GUADALUPE LOPEZ CABALLERO</t>
+  </si>
+  <si>
+    <t>MI08972</t>
+  </si>
+  <si>
+    <t>EMIGDIO FLORES AYALA</t>
+  </si>
+  <si>
+    <t>MB88825</t>
+  </si>
+  <si>
+    <t>CR 5045 PUEBLA CRUZ DEL SUR</t>
+  </si>
+  <si>
+    <t>SERVICIOS FINANCIEROS Y BANCARIOS</t>
+  </si>
+  <si>
+    <t>CENTRO COMERCIAL CRUZ DEL SUR</t>
+  </si>
+  <si>
+    <t>29 DE ABRIL DE 2011</t>
+  </si>
+  <si>
+    <t>HUGO AGUAS ROJAS</t>
+  </si>
+  <si>
+    <t>BRENDA MENDOZA VALDERRAMA</t>
+  </si>
+  <si>
+    <t>M903052</t>
+  </si>
+  <si>
+    <t>M816392</t>
+  </si>
+  <si>
+    <t>MARIBEL GONZALEZ PADILLA</t>
+  </si>
+  <si>
+    <t>MB95245</t>
+  </si>
+  <si>
+    <t>LUIS ANTONIO TAPIA SOLIS</t>
+  </si>
+  <si>
+    <t>MB91104</t>
+  </si>
+  <si>
+    <t>ARANZA IDALYTH HERNANDEZ IZQUIERDO</t>
+  </si>
+  <si>
+    <t>MI17354</t>
+  </si>
+  <si>
+    <t>CARLOS EDUARDO SANCHEZ CUAUTECATL</t>
+  </si>
+  <si>
+    <t>MI30096</t>
+  </si>
+  <si>
+    <t>PATRICIA RIVERA DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>MI06538</t>
+  </si>
+  <si>
+    <t>MA. CRISTINA XOCHIMITL C</t>
+  </si>
+  <si>
+    <t>MB65627</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL TORRES SALDAÑA</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL LOPEZ LADINO</t>
+  </si>
+  <si>
+    <t>MI26406</t>
+  </si>
+  <si>
+    <t>CR 5039 PUEBLA XILOTZINGO</t>
+  </si>
+  <si>
+    <t>BLVD CAPITAN CARLOS CAMACHO ESPIRITU</t>
+  </si>
+  <si>
+    <t>5, 6, 7, 8</t>
+  </si>
+  <si>
+    <t>BARRIO DE ARBOLEDAS</t>
+  </si>
+  <si>
+    <t>oscar.galicia@bbva.com</t>
+  </si>
+  <si>
+    <t>ALEXIS FERNANDEZ SANCHEZ</t>
+  </si>
+  <si>
+    <t>TODA LA OFICINA</t>
+  </si>
+  <si>
+    <t>MI12309</t>
+  </si>
+  <si>
+    <t>OSCAR GALICIA MEJIA</t>
+  </si>
+  <si>
+    <t>MB09774</t>
+  </si>
+  <si>
+    <t>OSCAR EDUARDO CRUZ MORA</t>
+  </si>
+  <si>
+    <t>MI12265</t>
+  </si>
+  <si>
+    <t>JANIS DELGADO MONROY</t>
+  </si>
+  <si>
+    <t>MB97288</t>
+  </si>
+  <si>
+    <t>CLAUDIA MANZANO PEREZ</t>
+  </si>
+  <si>
+    <t>MB73867</t>
+  </si>
+  <si>
+    <t>ALDO ESPEJEL LOZANO</t>
+  </si>
+  <si>
+    <t>MI25873</t>
+  </si>
+  <si>
+    <t>JORGE ALBERTO GONZALEZ LECHUGA</t>
+  </si>
+  <si>
+    <t>MI28325</t>
+  </si>
+  <si>
+    <t>DAVID VILLEGAS MONTES</t>
+  </si>
+  <si>
+    <t>MI23042</t>
+  </si>
+  <si>
+    <t>ROSA ESTHER VAZQUEZ TAMAYO</t>
+  </si>
+  <si>
+    <t>MARIA ISABEL GONZALEZ SANCHEZ</t>
+  </si>
+  <si>
+    <t>JEFE DE CAJAS</t>
+  </si>
+  <si>
+    <t>M284348</t>
+  </si>
+  <si>
+    <t>CR 529 IZUCAR DE MATAMOROS</t>
+  </si>
+  <si>
+    <t>INSTITUTCION DE BANCA MULTIPLE GRUPO FINANCIERO</t>
+  </si>
+  <si>
+    <t>IZUCAR DE MATAMOROS</t>
+  </si>
+  <si>
+    <t>LOCAL 1 ORIENTE</t>
+  </si>
+  <si>
+    <t>3 CAJONES</t>
+  </si>
+  <si>
+    <t>ROSA AURORA GARCIA LOPEZ</t>
   </si>
 </sst>
 </file>
@@ -3430,7 +4175,7 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
+          <bgColor rgb="FFFFFFCC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3496,7 +4241,7 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3586,10 +4331,6 @@
     <mc:Fallback/>
   </mc:AlternateContent>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6531,7 +7272,7 @@
         <v>752</v>
       </c>
       <c r="AF10" t="s">
-        <v>793</v>
+        <v>1062</v>
       </c>
       <c r="AG10">
         <v>9</v>
@@ -6592,13 +7333,13 @@
         <v>9</v>
       </c>
       <c r="AZ10" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="BA10">
         <v>3</v>
       </c>
       <c r="BB10" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="BE10">
         <v>1</v>
@@ -6668,16 +7409,16 @@
         <v>2024</v>
       </c>
       <c r="CY10" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="CZ10" t="s">
         <v>780</v>
       </c>
       <c r="DA10" t="s">
+        <v>796</v>
+      </c>
+      <c r="DB10" t="s">
         <v>797</v>
-      </c>
-      <c r="DB10" t="s">
-        <v>798</v>
       </c>
       <c r="DC10" t="s">
         <v>780</v>
@@ -6689,28 +7430,28 @@
         <v>443</v>
       </c>
       <c r="DH10" t="s">
+        <v>798</v>
+      </c>
+      <c r="DJ10" t="s">
         <v>799</v>
       </c>
-      <c r="DJ10" t="s">
+      <c r="DM10" t="s">
         <v>800</v>
       </c>
-      <c r="DM10" t="s">
+      <c r="DP10" t="s">
         <v>801</v>
       </c>
-      <c r="DP10" t="s">
+      <c r="DS10" t="s">
         <v>802</v>
       </c>
-      <c r="DS10" t="s">
+      <c r="DV10" t="s">
         <v>803</v>
       </c>
-      <c r="DV10" t="s">
+      <c r="DY10" t="s">
         <v>804</v>
       </c>
-      <c r="DY10" t="s">
-        <v>805</v>
-      </c>
       <c r="EB10" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="EI10">
         <v>0</v>
@@ -6762,34 +7503,34 @@
         <v>579</v>
       </c>
       <c r="C11" t="s">
+        <v>805</v>
+      </c>
+      <c r="D11" t="s">
+        <v>807</v>
+      </c>
+      <c r="E11" t="s">
+        <v>808</v>
+      </c>
+      <c r="F11" t="s">
         <v>806</v>
       </c>
-      <c r="D11" t="s">
-        <v>808</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="G11" t="s">
         <v>809</v>
-      </c>
-      <c r="F11" t="s">
-        <v>807</v>
-      </c>
-      <c r="G11" t="s">
-        <v>810</v>
       </c>
       <c r="H11" t="s">
         <v>745</v>
       </c>
       <c r="I11" t="s">
+        <v>810</v>
+      </c>
+      <c r="J11" t="s">
         <v>811</v>
       </c>
-      <c r="J11" t="s">
+      <c r="L11" t="s">
         <v>812</v>
       </c>
-      <c r="L11" t="s">
+      <c r="M11" t="s">
         <v>813</v>
-      </c>
-      <c r="M11" t="s">
-        <v>814</v>
       </c>
       <c r="N11" t="s">
         <v>424</v>
@@ -6798,16 +7539,16 @@
         <v>72760</v>
       </c>
       <c r="P11" t="s">
+        <v>814</v>
+      </c>
+      <c r="Q11" s="3" t="s">
         <v>815</v>
-      </c>
-      <c r="Q11" s="3" t="s">
-        <v>816</v>
       </c>
       <c r="R11">
         <v>29</v>
       </c>
       <c r="S11" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="V11">
         <v>4108.46</v>
@@ -6866,16 +7607,16 @@
         <v>2024</v>
       </c>
       <c r="CY11" t="s">
+        <v>817</v>
+      </c>
+      <c r="CZ11" t="s">
         <v>818</v>
       </c>
-      <c r="CZ11" t="s">
+      <c r="DA11" t="s">
         <v>819</v>
       </c>
-      <c r="DA11" t="s">
+      <c r="DB11" t="s">
         <v>820</v>
-      </c>
-      <c r="DB11" t="s">
-        <v>821</v>
       </c>
       <c r="DC11" t="s">
         <v>555</v>
@@ -6887,7 +7628,7 @@
         <v>443</v>
       </c>
       <c r="EH11" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="EJ11" s="4">
         <f t="shared" si="7"/>
@@ -6930,28 +7671,28 @@
         <v>785</v>
       </c>
       <c r="D12" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="E12" t="s">
         <v>787</v>
       </c>
       <c r="G12" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H12" t="s">
         <v>745</v>
       </c>
       <c r="I12" t="s">
+        <v>823</v>
+      </c>
+      <c r="J12" t="s">
         <v>824</v>
       </c>
-      <c r="J12" t="s">
+      <c r="L12" t="s">
         <v>825</v>
       </c>
-      <c r="L12" t="s">
+      <c r="M12" t="s">
         <v>826</v>
-      </c>
-      <c r="M12" t="s">
-        <v>827</v>
       </c>
       <c r="N12" t="s">
         <v>424</v>
@@ -6960,16 +7701,16 @@
         <v>74170</v>
       </c>
       <c r="P12" t="s">
+        <v>827</v>
+      </c>
+      <c r="Q12" s="3" t="s">
         <v>828</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>829</v>
       </c>
       <c r="R12">
         <v>24</v>
       </c>
       <c r="S12" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="V12">
         <v>2430</v>
@@ -7056,31 +7797,31 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
+        <v>845</v>
+      </c>
+      <c r="C13" t="s">
+        <v>950</v>
+      </c>
+      <c r="D13" t="s">
         <v>846</v>
       </c>
-      <c r="C13" t="s">
-        <v>955</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>847</v>
       </c>
-      <c r="E13" t="s">
+      <c r="G13" t="s">
         <v>848</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>849</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
         <v>850</v>
-      </c>
-      <c r="I13" t="s">
-        <v>851</v>
       </c>
       <c r="J13">
         <v>113</v>
       </c>
       <c r="K13" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="L13" t="s">
         <v>422</v>
@@ -7113,13 +7854,13 @@
         <v>0</v>
       </c>
       <c r="AD13" t="s">
+        <v>852</v>
+      </c>
+      <c r="AE13" t="s">
         <v>853</v>
       </c>
-      <c r="AE13" t="s">
+      <c r="AF13" t="s">
         <v>854</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>855</v>
       </c>
       <c r="AG13">
         <v>23</v>
@@ -7146,7 +7887,7 @@
         <v>534</v>
       </c>
       <c r="AQ13" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="AR13" s="4">
         <f t="shared" si="0"/>
@@ -7156,13 +7897,13 @@
         <v>2</v>
       </c>
       <c r="AT13" t="s">
-        <v>919</v>
+        <v>1027</v>
       </c>
       <c r="AU13">
         <v>7</v>
       </c>
       <c r="AV13" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="AW13">
         <v>6</v>
@@ -7174,19 +7915,19 @@
         <v>2</v>
       </c>
       <c r="BF13" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="BH13">
         <v>2</v>
       </c>
       <c r="BI13" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="BJ13">
         <v>19</v>
       </c>
       <c r="BK13" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="BL13">
         <v>7</v>
@@ -7220,25 +7961,25 @@
         <v>12</v>
       </c>
       <c r="CA13" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="CJ13">
         <v>4</v>
       </c>
       <c r="CK13" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="CN13">
         <v>2</v>
       </c>
       <c r="CO13" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="CV13">
         <v>9</v>
       </c>
       <c r="CW13" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="CX13">
         <v>2024</v>
@@ -7250,85 +7991,85 @@
         <v>443</v>
       </c>
       <c r="DG13" t="s">
+        <v>863</v>
+      </c>
+      <c r="DH13" t="s">
         <v>864</v>
       </c>
-      <c r="DH13" t="s">
+      <c r="DI13" t="s">
         <v>865</v>
       </c>
-      <c r="DI13" t="s">
+      <c r="DJ13" t="s">
         <v>866</v>
       </c>
-      <c r="DJ13" t="s">
+      <c r="DK13" t="s">
         <v>867</v>
       </c>
-      <c r="DK13" t="s">
+      <c r="DL13" t="s">
         <v>868</v>
       </c>
-      <c r="DL13" t="s">
+      <c r="DM13" t="s">
         <v>869</v>
       </c>
-      <c r="DM13" t="s">
+      <c r="DN13" t="s">
         <v>870</v>
       </c>
-      <c r="DN13" t="s">
+      <c r="DO13" t="s">
         <v>871</v>
       </c>
-      <c r="DO13" t="s">
+      <c r="DP13" t="s">
         <v>872</v>
       </c>
-      <c r="DP13" t="s">
+      <c r="DQ13" t="s">
         <v>873</v>
       </c>
-      <c r="DQ13" t="s">
+      <c r="DR13" t="s">
         <v>874</v>
       </c>
-      <c r="DR13" t="s">
+      <c r="DS13" t="s">
         <v>875</v>
       </c>
-      <c r="DS13" t="s">
+      <c r="DT13" t="s">
         <v>876</v>
       </c>
-      <c r="DT13" t="s">
+      <c r="DU13" t="s">
         <v>877</v>
       </c>
-      <c r="DU13" t="s">
+      <c r="DV13" t="s">
         <v>878</v>
       </c>
-      <c r="DV13" t="s">
+      <c r="DW13" t="s">
         <v>879</v>
       </c>
-      <c r="DW13" t="s">
+      <c r="DX13" t="s">
         <v>880</v>
       </c>
-      <c r="DX13" t="s">
+      <c r="DY13" t="s">
         <v>881</v>
       </c>
-      <c r="DY13" t="s">
+      <c r="DZ13" t="s">
+        <v>870</v>
+      </c>
+      <c r="EA13" t="s">
         <v>882</v>
       </c>
-      <c r="DZ13" t="s">
+      <c r="EB13" t="s">
         <v>883</v>
       </c>
-      <c r="EA13" t="s">
+      <c r="EC13" t="s">
+        <v>876</v>
+      </c>
+      <c r="ED13" t="s">
         <v>884</v>
       </c>
-      <c r="EB13" t="s">
+      <c r="EE13" t="s">
         <v>885</v>
       </c>
-      <c r="EC13" t="s">
-        <v>877</v>
-      </c>
-      <c r="ED13" t="s">
+      <c r="EF13" t="s">
         <v>886</v>
       </c>
-      <c r="EE13" t="s">
+      <c r="EG13" t="s">
         <v>887</v>
-      </c>
-      <c r="EF13" t="s">
-        <v>888</v>
-      </c>
-      <c r="EG13" t="s">
-        <v>889</v>
       </c>
       <c r="EI13">
         <v>0</v>
@@ -7363,121 +8104,121 @@
         <v>ORDINARIO</v>
       </c>
       <c r="EU13" t="s">
+        <v>888</v>
+      </c>
+      <c r="EV13" t="s">
+        <v>873</v>
+      </c>
+      <c r="EW13" t="s">
+        <v>889</v>
+      </c>
+      <c r="EX13" t="s">
         <v>890</v>
       </c>
-      <c r="EV13" t="s">
-        <v>874</v>
-      </c>
-      <c r="EW13" t="s">
+      <c r="EY13" t="s">
+        <v>879</v>
+      </c>
+      <c r="EZ13" t="s">
         <v>891</v>
       </c>
-      <c r="EX13" t="s">
+      <c r="FA13" t="s">
         <v>892</v>
       </c>
-      <c r="EY13" t="s">
-        <v>880</v>
-      </c>
-      <c r="EZ13" t="s">
+      <c r="FB13" t="s">
+        <v>879</v>
+      </c>
+      <c r="FC13" t="s">
         <v>893</v>
       </c>
-      <c r="FA13" t="s">
+      <c r="FD13" t="s">
         <v>894</v>
       </c>
-      <c r="FB13" t="s">
-        <v>880</v>
-      </c>
-      <c r="FC13" t="s">
+      <c r="FE13" t="s">
+        <v>879</v>
+      </c>
+      <c r="FF13" t="s">
         <v>895</v>
       </c>
-      <c r="FD13" t="s">
+      <c r="FG13" t="s">
         <v>896</v>
       </c>
-      <c r="FE13" t="s">
-        <v>880</v>
-      </c>
-      <c r="FF13" t="s">
+      <c r="FH13" t="s">
+        <v>867</v>
+      </c>
+      <c r="FI13" t="s">
         <v>897</v>
       </c>
-      <c r="FG13" t="s">
+      <c r="FJ13" t="s">
         <v>898</v>
       </c>
-      <c r="FH13" t="s">
-        <v>868</v>
-      </c>
-      <c r="FI13" t="s">
+      <c r="FK13" t="s">
+        <v>870</v>
+      </c>
+      <c r="FL13" t="s">
         <v>899</v>
       </c>
-      <c r="FJ13" t="s">
+      <c r="FM13" t="s">
         <v>900</v>
       </c>
-      <c r="FK13" t="s">
-        <v>871</v>
-      </c>
-      <c r="FL13" t="s">
+      <c r="FN13" t="s">
+        <v>870</v>
+      </c>
+      <c r="FO13" t="s">
         <v>901</v>
       </c>
-      <c r="FM13" t="s">
+      <c r="FP13" t="s">
         <v>902</v>
       </c>
-      <c r="FN13" t="s">
-        <v>871</v>
-      </c>
-      <c r="FO13" t="s">
+      <c r="FQ13" t="s">
+        <v>870</v>
+      </c>
+      <c r="FR13" t="s">
         <v>903</v>
       </c>
-      <c r="FP13" t="s">
+      <c r="FS13" t="s">
         <v>904</v>
       </c>
-      <c r="FQ13" t="s">
-        <v>871</v>
-      </c>
-      <c r="FR13" t="s">
+      <c r="FT13" t="s">
+        <v>870</v>
+      </c>
+      <c r="FU13" t="s">
         <v>905</v>
       </c>
-      <c r="FS13" t="s">
+      <c r="FV13" t="s">
         <v>906</v>
       </c>
-      <c r="FT13" t="s">
-        <v>871</v>
-      </c>
-      <c r="FU13" t="s">
+      <c r="FW13" t="s">
+        <v>870</v>
+      </c>
+      <c r="FX13" t="s">
         <v>907</v>
       </c>
-      <c r="FV13" t="s">
+      <c r="FY13" t="s">
         <v>908</v>
       </c>
-      <c r="FW13" t="s">
-        <v>871</v>
-      </c>
-      <c r="FX13" t="s">
+      <c r="FZ13" t="s">
+        <v>870</v>
+      </c>
+      <c r="GA13" t="s">
         <v>909</v>
       </c>
-      <c r="FY13" t="s">
+      <c r="GB13" t="s">
         <v>910</v>
       </c>
-      <c r="FZ13" t="s">
-        <v>871</v>
-      </c>
-      <c r="GA13" t="s">
+      <c r="GC13" t="s">
+        <v>876</v>
+      </c>
+      <c r="GD13" t="s">
         <v>911</v>
       </c>
-      <c r="GB13" t="s">
+      <c r="GE13" t="s">
         <v>912</v>
       </c>
-      <c r="GC13" t="s">
-        <v>877</v>
-      </c>
-      <c r="GD13" t="s">
+      <c r="GF13" t="s">
+        <v>876</v>
+      </c>
+      <c r="GG13" t="s">
         <v>913</v>
-      </c>
-      <c r="GE13" t="s">
-        <v>914</v>
-      </c>
-      <c r="GF13" t="s">
-        <v>877</v>
-      </c>
-      <c r="GG13" t="s">
-        <v>915</v>
       </c>
     </row>
     <row r="14" spans="1:221" x14ac:dyDescent="0.3">
@@ -7485,25 +8226,25 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C14" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="D14" t="s">
-        <v>916</v>
+        <v>1057</v>
       </c>
       <c r="E14" t="s">
+        <v>847</v>
+      </c>
+      <c r="G14" t="s">
         <v>848</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>849</v>
       </c>
-      <c r="H14" t="s">
-        <v>850</v>
-      </c>
       <c r="I14" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="J14">
         <v>1506</v>
@@ -7545,13 +8286,13 @@
         <v>0</v>
       </c>
       <c r="AD14" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
       <c r="AE14" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="AF14" t="s">
-        <v>959</v>
+        <v>954</v>
       </c>
       <c r="AG14">
         <v>15</v>
@@ -7578,7 +8319,7 @@
         <v>534</v>
       </c>
       <c r="AQ14" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="AR14" s="4">
         <f t="shared" si="0"/>
@@ -7588,13 +8329,13 @@
         <v>1</v>
       </c>
       <c r="AT14" t="s">
-        <v>919</v>
+        <v>1027</v>
       </c>
       <c r="AU14">
         <v>6</v>
       </c>
       <c r="AV14" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="AW14">
         <v>4</v>
@@ -7606,19 +8347,19 @@
         <v>2</v>
       </c>
       <c r="BF14" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="BH14">
         <v>2</v>
       </c>
       <c r="BI14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="BJ14">
         <v>19</v>
       </c>
       <c r="BK14" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="BL14">
         <v>19</v>
@@ -7652,25 +8393,25 @@
         <v>9</v>
       </c>
       <c r="CA14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="CJ14">
         <v>4</v>
       </c>
       <c r="CK14" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="CN14">
         <v>2</v>
       </c>
       <c r="CO14" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="CV14">
         <v>1</v>
       </c>
       <c r="CW14" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="CX14">
         <v>2024</v>
@@ -7682,85 +8423,85 @@
         <v>443</v>
       </c>
       <c r="DG14" t="s">
+        <v>916</v>
+      </c>
+      <c r="DH14" t="s">
+        <v>917</v>
+      </c>
+      <c r="DI14" t="s">
+        <v>918</v>
+      </c>
+      <c r="DJ14" t="s">
+        <v>919</v>
+      </c>
+      <c r="DK14" t="s">
+        <v>876</v>
+      </c>
+      <c r="DL14" t="s">
         <v>920</v>
       </c>
-      <c r="DH14" t="s">
+      <c r="DM14" t="s">
         <v>921</v>
       </c>
-      <c r="DI14" t="s">
+      <c r="DN14" t="s">
+        <v>870</v>
+      </c>
+      <c r="DO14" t="s">
         <v>922</v>
       </c>
-      <c r="DJ14" t="s">
+      <c r="DP14" t="s">
         <v>923</v>
       </c>
-      <c r="DK14" t="s">
-        <v>877</v>
-      </c>
-      <c r="DL14" t="s">
+      <c r="DQ14" t="s">
+        <v>870</v>
+      </c>
+      <c r="DR14" t="s">
         <v>924</v>
       </c>
-      <c r="DM14" t="s">
+      <c r="DS14" t="s">
         <v>925</v>
       </c>
-      <c r="DN14" t="s">
-        <v>871</v>
-      </c>
-      <c r="DO14" t="s">
+      <c r="DT14" t="s">
+        <v>870</v>
+      </c>
+      <c r="DU14" t="s">
         <v>926</v>
       </c>
-      <c r="DP14" t="s">
+      <c r="DV14" t="s">
         <v>927</v>
       </c>
-      <c r="DQ14" t="s">
-        <v>871</v>
-      </c>
-      <c r="DR14" t="s">
+      <c r="DW14" t="s">
         <v>928</v>
       </c>
-      <c r="DS14" t="s">
+      <c r="DX14" t="s">
         <v>929</v>
       </c>
-      <c r="DT14" t="s">
-        <v>871</v>
-      </c>
-      <c r="DU14" t="s">
+      <c r="DY14" t="s">
         <v>930</v>
       </c>
-      <c r="DV14" t="s">
+      <c r="DZ14" t="s">
+        <v>873</v>
+      </c>
+      <c r="EA14" t="s">
         <v>931</v>
       </c>
-      <c r="DW14" t="s">
+      <c r="EB14" t="s">
         <v>932</v>
       </c>
-      <c r="DX14" t="s">
+      <c r="EC14" t="s">
+        <v>876</v>
+      </c>
+      <c r="ED14" t="s">
         <v>933</v>
       </c>
-      <c r="DY14" t="s">
+      <c r="EE14" t="s">
         <v>934</v>
       </c>
-      <c r="DZ14" t="s">
-        <v>874</v>
-      </c>
-      <c r="EA14" t="s">
+      <c r="EF14" t="s">
+        <v>876</v>
+      </c>
+      <c r="EG14" t="s">
         <v>935</v>
-      </c>
-      <c r="EB14" t="s">
-        <v>936</v>
-      </c>
-      <c r="EC14" t="s">
-        <v>877</v>
-      </c>
-      <c r="ED14" t="s">
-        <v>937</v>
-      </c>
-      <c r="EE14" t="s">
-        <v>938</v>
-      </c>
-      <c r="EF14" t="s">
-        <v>877</v>
-      </c>
-      <c r="EG14" t="s">
-        <v>939</v>
       </c>
       <c r="EI14">
         <v>0</v>
@@ -7795,49 +8536,49 @@
         <v>ORDINARIO</v>
       </c>
       <c r="EU14" t="s">
+        <v>936</v>
+      </c>
+      <c r="EV14" t="s">
+        <v>870</v>
+      </c>
+      <c r="EW14" t="s">
+        <v>937</v>
+      </c>
+      <c r="EX14" t="s">
+        <v>938</v>
+      </c>
+      <c r="EY14" t="s">
+        <v>939</v>
+      </c>
+      <c r="EZ14" t="s">
         <v>940</v>
       </c>
-      <c r="EV14" t="s">
-        <v>871</v>
-      </c>
-      <c r="EW14" t="s">
+      <c r="FA14" t="s">
         <v>941</v>
       </c>
-      <c r="EX14" t="s">
+      <c r="FB14" t="s">
+        <v>870</v>
+      </c>
+      <c r="FC14" t="s">
         <v>942</v>
       </c>
-      <c r="EY14" t="s">
+      <c r="FD14" t="s">
         <v>943</v>
       </c>
-      <c r="EZ14" t="s">
+      <c r="FE14" t="s">
+        <v>870</v>
+      </c>
+      <c r="FF14" t="s">
         <v>944</v>
       </c>
-      <c r="FA14" t="s">
+      <c r="FG14" t="s">
         <v>945</v>
       </c>
-      <c r="FB14" t="s">
-        <v>871</v>
-      </c>
-      <c r="FC14" t="s">
+      <c r="FH14" t="s">
+        <v>873</v>
+      </c>
+      <c r="FI14" t="s">
         <v>946</v>
-      </c>
-      <c r="FD14" t="s">
-        <v>947</v>
-      </c>
-      <c r="FE14" t="s">
-        <v>871</v>
-      </c>
-      <c r="FF14" t="s">
-        <v>948</v>
-      </c>
-      <c r="FG14" t="s">
-        <v>949</v>
-      </c>
-      <c r="FH14" t="s">
-        <v>874</v>
-      </c>
-      <c r="FI14" t="s">
-        <v>950</v>
       </c>
     </row>
     <row r="15" spans="1:221" x14ac:dyDescent="0.3">
@@ -7845,34 +8586,34 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C15" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="D15" t="s">
-        <v>951</v>
+        <v>1058</v>
       </c>
       <c r="E15" t="s">
+        <v>847</v>
+      </c>
+      <c r="G15" t="s">
         <v>848</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>849</v>
       </c>
-      <c r="H15" t="s">
-        <v>850</v>
-      </c>
       <c r="I15" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="J15">
         <v>3710</v>
       </c>
       <c r="K15" t="s">
-        <v>852</v>
+        <v>998</v>
       </c>
       <c r="L15" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="M15" t="s">
         <v>424</v>
@@ -7899,13 +8640,13 @@
         <v>0</v>
       </c>
       <c r="AD15" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="AE15" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="AF15" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
       <c r="AG15">
         <v>9</v>
@@ -7932,7 +8673,7 @@
         <v>534</v>
       </c>
       <c r="AQ15" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="AR15" s="4">
         <f t="shared" si="0"/>
@@ -7942,13 +8683,13 @@
         <v>1</v>
       </c>
       <c r="AT15" t="s">
-        <v>919</v>
+        <v>1027</v>
       </c>
       <c r="AU15">
         <v>5</v>
       </c>
       <c r="AV15" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="AW15">
         <v>4</v>
@@ -7960,19 +8701,19 @@
         <v>2</v>
       </c>
       <c r="BF15" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="BG15">
         <v>2</v>
       </c>
       <c r="BI15" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="BJ15">
         <v>14</v>
       </c>
       <c r="BK15" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="BL15">
         <v>3</v>
@@ -8009,25 +8750,25 @@
         <v>5</v>
       </c>
       <c r="CA15" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="CJ15">
         <v>4</v>
       </c>
       <c r="CK15" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="CN15">
         <v>2</v>
       </c>
       <c r="CO15" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="CV15">
         <v>19</v>
       </c>
       <c r="CW15" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="CX15">
         <v>2024</v>
@@ -8039,82 +8780,94 @@
         <v>443</v>
       </c>
       <c r="DG15" t="s">
+        <v>956</v>
+      </c>
+      <c r="DH15" t="s">
+        <v>957</v>
+      </c>
+      <c r="DJ15" t="s">
+        <v>958</v>
+      </c>
+      <c r="DK15" t="s">
+        <v>876</v>
+      </c>
+      <c r="DL15" t="s">
+        <v>959</v>
+      </c>
+      <c r="DM15" t="s">
+        <v>960</v>
+      </c>
+      <c r="DN15" t="s">
+        <v>870</v>
+      </c>
+      <c r="DO15" t="s">
         <v>961</v>
       </c>
-      <c r="DH15" t="s">
+      <c r="DP15" t="s">
         <v>962</v>
       </c>
-      <c r="DJ15" t="s">
+      <c r="DQ15" t="s">
+        <v>886</v>
+      </c>
+      <c r="DR15" t="s">
         <v>963</v>
       </c>
-      <c r="DK15" t="s">
-        <v>877</v>
-      </c>
-      <c r="DL15" t="s">
+      <c r="DS15" t="s">
         <v>964</v>
       </c>
-      <c r="DM15" t="s">
+      <c r="DT15" t="s">
+        <v>879</v>
+      </c>
+      <c r="DU15" t="s">
         <v>965</v>
       </c>
-      <c r="DN15" t="s">
-        <v>871</v>
-      </c>
-      <c r="DO15" t="s">
+      <c r="DV15" t="s">
         <v>966</v>
       </c>
-      <c r="DP15" t="s">
+      <c r="DW15" t="s">
+        <v>876</v>
+      </c>
+      <c r="DX15" t="s">
         <v>967</v>
       </c>
-      <c r="DQ15" t="s">
-        <v>888</v>
-      </c>
-      <c r="DR15" t="s">
+      <c r="DY15" t="s">
         <v>968</v>
       </c>
-      <c r="DS15" t="s">
+      <c r="DZ15" t="s">
+        <v>879</v>
+      </c>
+      <c r="EA15" t="s">
         <v>969</v>
       </c>
-      <c r="DT15" t="s">
-        <v>880</v>
-      </c>
-      <c r="DU15" t="s">
+      <c r="EB15" t="s">
         <v>970</v>
       </c>
-      <c r="DV15" t="s">
-        <v>971</v>
-      </c>
-      <c r="DW15" t="s">
-        <v>877</v>
-      </c>
-      <c r="DX15" t="s">
-        <v>972</v>
-      </c>
-      <c r="DY15" t="s">
-        <v>973</v>
-      </c>
-      <c r="DZ15" t="s">
-        <v>880</v>
-      </c>
-      <c r="EA15" t="s">
-        <v>974</v>
-      </c>
-      <c r="EB15" t="s">
-        <v>975</v>
-      </c>
       <c r="EC15" t="s">
-        <v>871</v>
+        <v>870</v>
+      </c>
+      <c r="EI15">
+        <v>0</v>
       </c>
       <c r="EJ15" s="4">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
+      <c r="EL15">
+        <v>0</v>
+      </c>
       <c r="EM15" s="4">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
+      <c r="EO15">
+        <v>0</v>
+      </c>
       <c r="EP15" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
+      </c>
+      <c r="EQ15" t="s">
+        <v>455</v>
       </c>
       <c r="ES15" s="4">
         <f t="shared" si="10"/>
@@ -8130,34 +8883,34 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C16" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="D16" t="s">
-        <v>976</v>
+        <v>1059</v>
       </c>
       <c r="E16" t="s">
+        <v>847</v>
+      </c>
+      <c r="G16" t="s">
         <v>848</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>849</v>
       </c>
-      <c r="H16" t="s">
-        <v>850</v>
-      </c>
       <c r="I16" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="J16">
         <v>3922</v>
       </c>
-      <c r="K16">
-        <v>1</v>
+      <c r="K16" t="s">
+        <v>997</v>
       </c>
       <c r="L16" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="M16" t="s">
         <v>424</v>
@@ -8187,10 +8940,10 @@
         <v>463</v>
       </c>
       <c r="AE16" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="AF16" t="s">
-        <v>977</v>
+        <v>971</v>
       </c>
       <c r="AG16">
         <v>9</v>
@@ -8217,7 +8970,7 @@
         <v>534</v>
       </c>
       <c r="AQ16" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="AR16" s="4">
         <f t="shared" si="0"/>
@@ -8227,13 +8980,13 @@
         <v>2</v>
       </c>
       <c r="AT16" t="s">
-        <v>978</v>
+        <v>1026</v>
       </c>
       <c r="AU16">
         <v>6</v>
       </c>
       <c r="AV16" t="s">
-        <v>979</v>
+        <v>1002</v>
       </c>
       <c r="AW16">
         <v>5</v>
@@ -8245,19 +8998,19 @@
         <v>2</v>
       </c>
       <c r="BF16" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="BH16">
         <v>3</v>
       </c>
       <c r="BI16" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="BJ16">
         <v>12</v>
       </c>
       <c r="BK16" t="s">
-        <v>980</v>
+        <v>1214</v>
       </c>
       <c r="BL16">
         <v>4</v>
@@ -8288,25 +9041,25 @@
         <v>9</v>
       </c>
       <c r="CA16" t="s">
-        <v>980</v>
+        <v>972</v>
       </c>
       <c r="CJ16">
         <v>4</v>
       </c>
       <c r="CK16" t="s">
-        <v>981</v>
+        <v>973</v>
       </c>
       <c r="CN16">
         <v>2</v>
       </c>
       <c r="CO16" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="CV16">
         <v>19</v>
       </c>
       <c r="CW16" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="CX16">
         <v>2024</v>
@@ -8318,88 +9071,100 @@
         <v>443</v>
       </c>
       <c r="DG16" t="s">
+        <v>974</v>
+      </c>
+      <c r="DH16" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="DI16" t="s">
+        <v>977</v>
+      </c>
+      <c r="DJ16" t="s">
+        <v>978</v>
+      </c>
+      <c r="DK16" t="s">
+        <v>979</v>
+      </c>
+      <c r="DL16" t="s">
+        <v>980</v>
+      </c>
+      <c r="DM16" t="s">
+        <v>981</v>
+      </c>
+      <c r="DN16" t="s">
+        <v>979</v>
+      </c>
+      <c r="DO16" t="s">
         <v>982</v>
       </c>
-      <c r="DH16" s="1" t="s">
+      <c r="DP16" t="s">
         <v>983</v>
       </c>
-      <c r="DI16" t="s">
+      <c r="DQ16" t="s">
+        <v>979</v>
+      </c>
+      <c r="DR16" t="s">
+        <v>984</v>
+      </c>
+      <c r="DS16" t="s">
         <v>985</v>
       </c>
-      <c r="DJ16" t="s">
+      <c r="DT16" t="s">
+        <v>979</v>
+      </c>
+      <c r="DU16" t="s">
         <v>986</v>
       </c>
-      <c r="DK16" t="s">
+      <c r="DY16" t="s">
         <v>987</v>
       </c>
-      <c r="DL16" t="s">
+      <c r="DZ16" t="s">
+        <v>976</v>
+      </c>
+      <c r="EA16" t="s">
         <v>988</v>
       </c>
-      <c r="DM16" t="s">
+      <c r="EB16" t="s">
         <v>989</v>
       </c>
-      <c r="DN16" t="s">
-        <v>987</v>
-      </c>
-      <c r="DO16" t="s">
+      <c r="EC16" t="s">
+        <v>976</v>
+      </c>
+      <c r="ED16" t="s">
         <v>990</v>
       </c>
-      <c r="DP16" t="s">
+      <c r="EE16" t="s">
         <v>991</v>
       </c>
-      <c r="DQ16" t="s">
-        <v>987</v>
-      </c>
-      <c r="DR16" t="s">
+      <c r="EF16" t="s">
+        <v>976</v>
+      </c>
+      <c r="EG16" t="s">
         <v>992</v>
       </c>
-      <c r="DS16" t="s">
-        <v>993</v>
-      </c>
-      <c r="DT16" t="s">
-        <v>987</v>
-      </c>
-      <c r="DU16" t="s">
-        <v>994</v>
-      </c>
-      <c r="DY16" t="s">
-        <v>995</v>
-      </c>
-      <c r="DZ16" t="s">
-        <v>984</v>
-      </c>
-      <c r="EA16" t="s">
-        <v>996</v>
-      </c>
-      <c r="EB16" t="s">
-        <v>997</v>
-      </c>
-      <c r="EC16" t="s">
-        <v>984</v>
-      </c>
-      <c r="ED16" t="s">
-        <v>998</v>
-      </c>
-      <c r="EE16" t="s">
-        <v>999</v>
-      </c>
-      <c r="EF16" t="s">
-        <v>984</v>
-      </c>
-      <c r="EG16" t="s">
-        <v>1000</v>
+      <c r="EI16">
+        <v>0</v>
       </c>
       <c r="EJ16" s="4">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
+      <c r="EL16">
+        <v>0</v>
+      </c>
       <c r="EM16" s="4">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
+      <c r="EO16">
+        <v>0</v>
+      </c>
       <c r="EP16" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
+      </c>
+      <c r="EQ16" t="s">
+        <v>455</v>
       </c>
       <c r="ES16" s="4">
         <f t="shared" si="10"/>
@@ -8410,38 +9175,314 @@
         <v>ORDINARIO</v>
       </c>
       <c r="EU16" t="s">
-        <v>1001</v>
+        <v>993</v>
       </c>
       <c r="EV16" t="s">
-        <v>984</v>
+        <v>976</v>
       </c>
       <c r="EW16" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="17" spans="1:150" x14ac:dyDescent="0.3">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="17" spans="1:159" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>15</v>
       </c>
+      <c r="B17" t="s">
+        <v>845</v>
+      </c>
+      <c r="C17" t="s">
+        <v>950</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1060</v>
+      </c>
+      <c r="E17" t="s">
+        <v>847</v>
+      </c>
+      <c r="G17" t="s">
+        <v>848</v>
+      </c>
+      <c r="H17" t="s">
+        <v>849</v>
+      </c>
+      <c r="I17" t="s">
+        <v>995</v>
+      </c>
+      <c r="J17">
+        <v>11302</v>
+      </c>
+      <c r="K17" t="s">
+        <v>996</v>
+      </c>
+      <c r="L17" t="s">
+        <v>999</v>
+      </c>
+      <c r="M17" t="s">
+        <v>424</v>
+      </c>
+      <c r="N17" t="s">
+        <v>424</v>
+      </c>
+      <c r="P17">
+        <v>2223953433</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>1000</v>
+      </c>
+      <c r="X17">
+        <v>1</v>
+      </c>
+      <c r="Y17">
+        <v>1</v>
+      </c>
+      <c r="Z17">
+        <v>1</v>
+      </c>
+      <c r="AA17">
+        <v>1</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>915</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>853</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>1001</v>
+      </c>
+      <c r="AG17">
+        <v>10</v>
+      </c>
+      <c r="AH17">
+        <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>5</v>
+      </c>
+      <c r="AJ17">
+        <v>5</v>
+      </c>
+      <c r="AK17">
+        <v>0</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>1</v>
+      </c>
+      <c r="AP17" t="s">
+        <v>534</v>
+      </c>
+      <c r="AQ17" t="s">
+        <v>855</v>
+      </c>
       <c r="AR17" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c r="AS17">
+        <v>1</v>
+      </c>
+      <c r="AT17" t="s">
+        <v>1027</v>
+      </c>
+      <c r="AU17">
+        <v>6</v>
+      </c>
+      <c r="AV17" t="s">
+        <v>857</v>
+      </c>
+      <c r="AW17">
+        <v>5</v>
+      </c>
+      <c r="AX17">
+        <v>1</v>
+      </c>
+      <c r="BE17">
+        <v>3</v>
+      </c>
+      <c r="BF17" t="s">
+        <v>858</v>
+      </c>
+      <c r="BJ17">
+        <v>13</v>
+      </c>
+      <c r="BK17" t="s">
+        <v>860</v>
+      </c>
+      <c r="BL17">
+        <v>4</v>
+      </c>
+      <c r="BN17">
+        <v>2</v>
+      </c>
+      <c r="BQ17">
+        <v>3</v>
+      </c>
+      <c r="BR17">
+        <v>1</v>
       </c>
       <c r="BS17" s="4">
         <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="BT17">
+        <v>3</v>
+      </c>
+      <c r="BU17">
+        <v>1</v>
+      </c>
+      <c r="BW17">
+        <v>1</v>
+      </c>
+      <c r="BX17">
+        <v>1</v>
+      </c>
+      <c r="BZ17">
+        <v>4</v>
+      </c>
+      <c r="CA17" t="s">
+        <v>859</v>
+      </c>
+      <c r="CJ17">
+        <v>4</v>
+      </c>
+      <c r="CK17" t="s">
+        <v>861</v>
+      </c>
+      <c r="CN17">
+        <v>2</v>
+      </c>
+      <c r="CO17" t="s">
+        <v>862</v>
+      </c>
+      <c r="CV17">
+        <v>2</v>
+      </c>
+      <c r="CW17" t="s">
+        <v>856</v>
+      </c>
+      <c r="CX17">
+        <v>2024</v>
+      </c>
+      <c r="DE17" t="s">
+        <v>442</v>
+      </c>
+      <c r="DF17" t="s">
+        <v>443</v>
+      </c>
+      <c r="DG17" t="s">
+        <v>1003</v>
+      </c>
+      <c r="DH17" t="s">
+        <v>1004</v>
+      </c>
+      <c r="DI17" t="s">
+        <v>1005</v>
+      </c>
+      <c r="DJ17" t="s">
+        <v>1006</v>
+      </c>
+      <c r="DK17" t="s">
+        <v>876</v>
+      </c>
+      <c r="DL17" t="s">
+        <v>1007</v>
+      </c>
+      <c r="DM17" t="s">
+        <v>1008</v>
+      </c>
+      <c r="DN17" t="s">
+        <v>876</v>
+      </c>
+      <c r="DO17" t="s">
+        <v>1009</v>
+      </c>
+      <c r="DP17" t="s">
+        <v>1010</v>
+      </c>
+      <c r="DQ17" t="s">
+        <v>928</v>
+      </c>
+      <c r="DR17" t="s">
+        <v>1011</v>
+      </c>
+      <c r="DS17" t="s">
+        <v>1012</v>
+      </c>
+      <c r="DT17" t="s">
+        <v>928</v>
+      </c>
+      <c r="DU17" t="s">
+        <v>1013</v>
+      </c>
+      <c r="DV17" t="s">
+        <v>1014</v>
+      </c>
+      <c r="DW17" t="s">
+        <v>886</v>
+      </c>
+      <c r="DX17" t="s">
+        <v>1015</v>
+      </c>
+      <c r="DY17" t="s">
+        <v>1016</v>
+      </c>
+      <c r="DZ17" t="s">
+        <v>870</v>
+      </c>
+      <c r="EA17" t="s">
+        <v>1017</v>
+      </c>
+      <c r="EB17" t="s">
+        <v>1018</v>
+      </c>
+      <c r="EC17" t="s">
+        <v>876</v>
+      </c>
+      <c r="ED17" t="s">
+        <v>1019</v>
+      </c>
+      <c r="EE17" t="s">
+        <v>1020</v>
+      </c>
+      <c r="EF17" t="s">
+        <v>870</v>
+      </c>
+      <c r="EG17" t="s">
+        <v>1021</v>
+      </c>
+      <c r="EI17">
         <v>0</v>
       </c>
       <c r="EJ17" s="4">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
+      <c r="EL17">
+        <v>0</v>
+      </c>
       <c r="EM17" s="4">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
+      <c r="EO17">
+        <v>0</v>
+      </c>
       <c r="EP17" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
+      </c>
+      <c r="EQ17" t="s">
+        <v>455</v>
       </c>
       <c r="ES17" s="4">
         <f t="shared" si="10"/>
@@ -8452,29 +9493,305 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="18" spans="1:150" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:159" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>16</v>
       </c>
+      <c r="B18" t="s">
+        <v>845</v>
+      </c>
+      <c r="C18" t="s">
+        <v>950</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E18" t="s">
+        <v>847</v>
+      </c>
+      <c r="G18" t="s">
+        <v>848</v>
+      </c>
+      <c r="H18" t="s">
+        <v>849</v>
+      </c>
+      <c r="I18" t="s">
+        <v>1022</v>
+      </c>
+      <c r="J18">
+        <v>8310</v>
+      </c>
+      <c r="K18" t="s">
+        <v>1023</v>
+      </c>
+      <c r="L18" t="s">
+        <v>1024</v>
+      </c>
+      <c r="M18" t="s">
+        <v>424</v>
+      </c>
+      <c r="N18" t="s">
+        <v>424</v>
+      </c>
+      <c r="P18">
+        <v>2222287246</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>1025</v>
+      </c>
+      <c r="X18">
+        <v>1</v>
+      </c>
+      <c r="Y18">
+        <v>1</v>
+      </c>
+      <c r="Z18">
+        <v>1</v>
+      </c>
+      <c r="AA18">
+        <v>1</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>427</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>853</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>1028</v>
+      </c>
+      <c r="AG18">
+        <v>12</v>
+      </c>
+      <c r="AH18">
+        <v>0</v>
+      </c>
+      <c r="AI18">
+        <v>9</v>
+      </c>
+      <c r="AJ18">
+        <v>3</v>
+      </c>
+      <c r="AK18">
+        <v>0</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>1</v>
+      </c>
+      <c r="AP18" t="s">
+        <v>534</v>
+      </c>
+      <c r="AQ18" t="s">
+        <v>855</v>
+      </c>
       <c r="AR18" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="AS18">
+        <v>1</v>
+      </c>
+      <c r="AT18" t="s">
+        <v>1027</v>
+      </c>
+      <c r="AU18">
+        <v>5</v>
+      </c>
+      <c r="AV18" t="s">
+        <v>857</v>
+      </c>
+      <c r="AW18">
+        <v>4</v>
+      </c>
+      <c r="AX18">
+        <v>1</v>
+      </c>
+      <c r="BE18">
+        <v>2</v>
+      </c>
+      <c r="BF18" t="s">
+        <v>858</v>
+      </c>
+      <c r="BJ18">
+        <v>11</v>
+      </c>
+      <c r="BK18" t="s">
+        <v>860</v>
+      </c>
+      <c r="BL18">
+        <v>3</v>
+      </c>
+      <c r="BN18">
+        <v>2</v>
+      </c>
+      <c r="BQ18">
+        <v>3</v>
+      </c>
+      <c r="BR18">
+        <v>1</v>
       </c>
       <c r="BS18" s="4">
         <f t="shared" si="6"/>
+        <v>14</v>
+      </c>
+      <c r="BT18">
+        <v>6</v>
+      </c>
+      <c r="BU18">
+        <v>1</v>
+      </c>
+      <c r="BW18">
+        <v>4</v>
+      </c>
+      <c r="BX18">
+        <v>4</v>
+      </c>
+      <c r="BZ18">
+        <v>4</v>
+      </c>
+      <c r="CA18" t="s">
+        <v>859</v>
+      </c>
+      <c r="CJ18">
+        <v>4</v>
+      </c>
+      <c r="CK18" t="s">
+        <v>861</v>
+      </c>
+      <c r="CN18">
+        <v>2</v>
+      </c>
+      <c r="CO18" t="s">
+        <v>862</v>
+      </c>
+      <c r="CV18">
+        <v>2</v>
+      </c>
+      <c r="CW18" t="s">
+        <v>856</v>
+      </c>
+      <c r="CX18">
+        <v>2024</v>
+      </c>
+      <c r="DE18" t="s">
+        <v>442</v>
+      </c>
+      <c r="DF18" t="s">
+        <v>443</v>
+      </c>
+      <c r="DG18" t="s">
+        <v>1029</v>
+      </c>
+      <c r="DH18" t="s">
+        <v>1030</v>
+      </c>
+      <c r="DI18" t="s">
+        <v>1031</v>
+      </c>
+      <c r="DJ18" t="s">
+        <v>1032</v>
+      </c>
+      <c r="DK18" t="s">
+        <v>870</v>
+      </c>
+      <c r="DL18" t="s">
+        <v>1033</v>
+      </c>
+      <c r="DM18" t="s">
+        <v>1034</v>
+      </c>
+      <c r="DN18" t="s">
+        <v>870</v>
+      </c>
+      <c r="DO18" t="s">
+        <v>1035</v>
+      </c>
+      <c r="DP18" t="s">
+        <v>1036</v>
+      </c>
+      <c r="DQ18" t="s">
+        <v>876</v>
+      </c>
+      <c r="DR18" t="s">
+        <v>1037</v>
+      </c>
+      <c r="DS18" t="s">
+        <v>1038</v>
+      </c>
+      <c r="DT18" t="s">
+        <v>870</v>
+      </c>
+      <c r="DU18" t="s">
+        <v>1039</v>
+      </c>
+      <c r="DV18" t="s">
+        <v>1040</v>
+      </c>
+      <c r="DW18" t="s">
+        <v>876</v>
+      </c>
+      <c r="DX18" t="s">
+        <v>1041</v>
+      </c>
+      <c r="DY18" t="s">
+        <v>1042</v>
+      </c>
+      <c r="DZ18" t="s">
+        <v>876</v>
+      </c>
+      <c r="EA18" t="s">
+        <v>1043</v>
+      </c>
+      <c r="EB18" t="s">
+        <v>1044</v>
+      </c>
+      <c r="EC18" t="s">
+        <v>870</v>
+      </c>
+      <c r="ED18" t="s">
+        <v>1045</v>
+      </c>
+      <c r="EE18" t="s">
+        <v>1046</v>
+      </c>
+      <c r="EF18" t="s">
+        <v>886</v>
+      </c>
+      <c r="EG18" t="s">
+        <v>1047</v>
+      </c>
+      <c r="EI18">
         <v>0</v>
       </c>
       <c r="EJ18" s="4">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
+      <c r="EL18">
+        <v>0</v>
+      </c>
       <c r="EM18" s="4">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
+      <c r="EO18">
+        <v>0</v>
+      </c>
       <c r="EP18" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
+      </c>
+      <c r="EQ18" t="s">
+        <v>455</v>
       </c>
       <c r="ES18" s="4">
         <f t="shared" si="10"/>
@@ -8484,30 +9801,321 @@
         <f t="shared" si="11"/>
         <v>ORDINARIO</v>
       </c>
-    </row>
-    <row r="19" spans="1:150" x14ac:dyDescent="0.3">
+      <c r="EU18" t="s">
+        <v>1048</v>
+      </c>
+      <c r="EV18" t="s">
+        <v>1049</v>
+      </c>
+      <c r="EW18" t="s">
+        <v>1050</v>
+      </c>
+      <c r="EX18" t="s">
+        <v>1051</v>
+      </c>
+      <c r="EY18" t="s">
+        <v>928</v>
+      </c>
+      <c r="EZ18" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="19" spans="1:159" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>17</v>
       </c>
+      <c r="B19" t="s">
+        <v>845</v>
+      </c>
+      <c r="C19" t="s">
+        <v>950</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1053</v>
+      </c>
+      <c r="E19" t="s">
+        <v>847</v>
+      </c>
+      <c r="G19" t="s">
+        <v>848</v>
+      </c>
+      <c r="H19" t="s">
+        <v>849</v>
+      </c>
+      <c r="I19" t="s">
+        <v>1054</v>
+      </c>
+      <c r="J19">
+        <v>2510</v>
+      </c>
+      <c r="L19" t="s">
+        <v>1055</v>
+      </c>
+      <c r="M19" t="s">
+        <v>424</v>
+      </c>
+      <c r="N19" t="s">
+        <v>424</v>
+      </c>
+      <c r="P19">
+        <v>2222296000</v>
+      </c>
+      <c r="Q19" s="3" t="s">
+        <v>1056</v>
+      </c>
+      <c r="X19">
+        <v>1</v>
+      </c>
+      <c r="Y19">
+        <v>1</v>
+      </c>
+      <c r="Z19">
+        <v>1</v>
+      </c>
+      <c r="AA19">
+        <v>1</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>915</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>853</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>1063</v>
+      </c>
+      <c r="AG19">
+        <v>13</v>
+      </c>
+      <c r="AH19">
+        <v>0</v>
+      </c>
+      <c r="AI19">
+        <v>6</v>
+      </c>
+      <c r="AJ19">
+        <v>7</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>1</v>
+      </c>
+      <c r="AP19" t="s">
+        <v>534</v>
+      </c>
+      <c r="AQ19" t="s">
+        <v>855</v>
+      </c>
       <c r="AR19" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>29</v>
+      </c>
+      <c r="AS19">
+        <v>2</v>
+      </c>
+      <c r="AT19" t="s">
+        <v>1027</v>
+      </c>
+      <c r="AU19">
+        <v>7</v>
+      </c>
+      <c r="AV19" t="s">
+        <v>857</v>
+      </c>
+      <c r="AW19">
+        <v>6</v>
+      </c>
+      <c r="AX19">
+        <v>1</v>
+      </c>
+      <c r="BE19">
+        <v>4</v>
+      </c>
+      <c r="BF19" t="s">
+        <v>858</v>
+      </c>
+      <c r="BJ19">
+        <v>17</v>
+      </c>
+      <c r="BK19" t="s">
+        <v>860</v>
+      </c>
+      <c r="BL19">
+        <v>11</v>
+      </c>
+      <c r="BN19">
+        <v>2</v>
+      </c>
+      <c r="BQ19">
+        <v>3</v>
+      </c>
+      <c r="BR19">
+        <v>4</v>
       </c>
       <c r="BS19" s="4">
         <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="BT19">
+        <v>5</v>
+      </c>
+      <c r="BU19">
+        <v>2</v>
+      </c>
+      <c r="BW19">
+        <v>1</v>
+      </c>
+      <c r="BX19">
+        <v>1</v>
+      </c>
+      <c r="BZ19">
+        <v>4</v>
+      </c>
+      <c r="CA19" t="s">
+        <v>859</v>
+      </c>
+      <c r="CJ19">
+        <v>4</v>
+      </c>
+      <c r="CK19" t="s">
+        <v>861</v>
+      </c>
+      <c r="CN19">
+        <v>2</v>
+      </c>
+      <c r="CO19" t="s">
+        <v>862</v>
+      </c>
+      <c r="CV19">
+        <v>6</v>
+      </c>
+      <c r="CW19" t="s">
+        <v>856</v>
+      </c>
+      <c r="CX19">
+        <v>2024</v>
+      </c>
+      <c r="DE19" t="s">
+        <v>442</v>
+      </c>
+      <c r="DF19" t="s">
+        <v>443</v>
+      </c>
+      <c r="DG19" t="s">
+        <v>1064</v>
+      </c>
+      <c r="DH19" t="s">
+        <v>1065</v>
+      </c>
+      <c r="DI19" t="s">
+        <v>1066</v>
+      </c>
+      <c r="DJ19" t="s">
+        <v>1067</v>
+      </c>
+      <c r="DK19" t="s">
+        <v>870</v>
+      </c>
+      <c r="DL19" t="s">
+        <v>1068</v>
+      </c>
+      <c r="DM19" t="s">
+        <v>1069</v>
+      </c>
+      <c r="DN19" t="s">
+        <v>870</v>
+      </c>
+      <c r="DO19" t="s">
+        <v>1070</v>
+      </c>
+      <c r="DP19" t="s">
+        <v>1071</v>
+      </c>
+      <c r="DQ19" t="s">
+        <v>928</v>
+      </c>
+      <c r="DR19" t="s">
+        <v>1072</v>
+      </c>
+      <c r="DS19" t="s">
+        <v>1073</v>
+      </c>
+      <c r="DT19" t="s">
+        <v>876</v>
+      </c>
+      <c r="DU19" t="s">
+        <v>1074</v>
+      </c>
+      <c r="DV19" t="s">
+        <v>1075</v>
+      </c>
+      <c r="DW19" t="s">
+        <v>1049</v>
+      </c>
+      <c r="DX19" t="s">
+        <v>1076</v>
+      </c>
+      <c r="DY19" t="s">
+        <v>1077</v>
+      </c>
+      <c r="DZ19" t="s">
+        <v>1049</v>
+      </c>
+      <c r="EA19" t="s">
+        <v>1078</v>
+      </c>
+      <c r="EB19" t="s">
+        <v>1079</v>
+      </c>
+      <c r="EC19" t="s">
+        <v>886</v>
+      </c>
+      <c r="ED19" t="s">
+        <v>1080</v>
+      </c>
+      <c r="EE19" t="s">
+        <v>1081</v>
+      </c>
+      <c r="EF19" t="s">
+        <v>886</v>
+      </c>
+      <c r="EG19" t="s">
+        <v>1082</v>
+      </c>
+      <c r="EI19">
         <v>0</v>
       </c>
       <c r="EJ19" s="4">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
+      <c r="EL19">
+        <v>0</v>
+      </c>
       <c r="EM19" s="4">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
+      <c r="EO19">
+        <v>0</v>
+      </c>
       <c r="EP19" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
+      </c>
+      <c r="EQ19" t="s">
+        <v>455</v>
       </c>
       <c r="ES19" s="4">
         <f t="shared" si="10"/>
@@ -8517,30 +10125,294 @@
         <f t="shared" si="11"/>
         <v>ORDINARIO</v>
       </c>
-    </row>
-    <row r="20" spans="1:150" x14ac:dyDescent="0.3">
+      <c r="EU19" t="s">
+        <v>1083</v>
+      </c>
+      <c r="EV19" t="s">
+        <v>1049</v>
+      </c>
+      <c r="EW19" t="s">
+        <v>1084</v>
+      </c>
+      <c r="EX19" t="s">
+        <v>1085</v>
+      </c>
+      <c r="EY19" t="s">
+        <v>876</v>
+      </c>
+      <c r="EZ19" t="s">
+        <v>1086</v>
+      </c>
+      <c r="FA19" t="s">
+        <v>1087</v>
+      </c>
+      <c r="FB19" t="s">
+        <v>870</v>
+      </c>
+      <c r="FC19" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="20" spans="1:159" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>18</v>
       </c>
+      <c r="B20" t="s">
+        <v>845</v>
+      </c>
+      <c r="C20" t="s">
+        <v>950</v>
+      </c>
+      <c r="D20" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E20" t="s">
+        <v>847</v>
+      </c>
+      <c r="G20" t="s">
+        <v>848</v>
+      </c>
+      <c r="H20" t="s">
+        <v>849</v>
+      </c>
+      <c r="I20" t="s">
+        <v>1090</v>
+      </c>
+      <c r="J20">
+        <v>201</v>
+      </c>
+      <c r="L20" t="s">
+        <v>1091</v>
+      </c>
+      <c r="M20" t="s">
+        <v>424</v>
+      </c>
+      <c r="N20" t="s">
+        <v>424</v>
+      </c>
+      <c r="P20">
+        <v>2222405840</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="X20">
+        <v>1</v>
+      </c>
+      <c r="Y20">
+        <v>1</v>
+      </c>
+      <c r="Z20">
+        <v>1</v>
+      </c>
+      <c r="AA20">
+        <v>1</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>427</v>
+      </c>
+      <c r="AE20" t="s">
+        <v>853</v>
+      </c>
+      <c r="AF20" t="s">
+        <v>1093</v>
+      </c>
+      <c r="AG20">
+        <v>9</v>
+      </c>
+      <c r="AH20">
+        <v>0</v>
+      </c>
+      <c r="AI20">
+        <v>3</v>
+      </c>
+      <c r="AJ20">
+        <v>6</v>
+      </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>1</v>
+      </c>
+      <c r="AP20" t="s">
+        <v>534</v>
+      </c>
+      <c r="AQ20" t="s">
+        <v>855</v>
+      </c>
       <c r="AR20" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="AS20">
+        <v>1</v>
+      </c>
+      <c r="AT20" t="s">
+        <v>1027</v>
+      </c>
+      <c r="AU20">
+        <v>4</v>
+      </c>
+      <c r="AV20" t="s">
+        <v>857</v>
+      </c>
+      <c r="AW20">
+        <v>3</v>
+      </c>
+      <c r="AX20">
+        <v>1</v>
+      </c>
+      <c r="BE20">
+        <v>1</v>
+      </c>
+      <c r="BF20" t="s">
+        <v>858</v>
+      </c>
+      <c r="BJ20">
+        <v>5</v>
+      </c>
+      <c r="BK20" t="s">
+        <v>860</v>
+      </c>
+      <c r="BL20">
+        <v>5</v>
+      </c>
+      <c r="BN20">
+        <v>2</v>
+      </c>
+      <c r="BQ20">
+        <v>2</v>
+      </c>
+      <c r="BR20">
+        <v>1</v>
       </c>
       <c r="BS20" s="4">
         <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="BT20">
+        <v>1</v>
+      </c>
+      <c r="BU20">
+        <v>1</v>
+      </c>
+      <c r="BW20">
+        <v>4</v>
+      </c>
+      <c r="BX20">
+        <v>1</v>
+      </c>
+      <c r="BZ20">
+        <v>4</v>
+      </c>
+      <c r="CA20" t="s">
+        <v>859</v>
+      </c>
+      <c r="CJ20">
+        <v>4</v>
+      </c>
+      <c r="CK20" t="s">
+        <v>861</v>
+      </c>
+      <c r="CN20">
+        <v>2</v>
+      </c>
+      <c r="CO20" t="s">
+        <v>862</v>
+      </c>
+      <c r="CV20">
+        <v>6</v>
+      </c>
+      <c r="CW20" t="s">
+        <v>856</v>
+      </c>
+      <c r="CX20">
+        <v>2024</v>
+      </c>
+      <c r="DE20" t="s">
+        <v>442</v>
+      </c>
+      <c r="DF20" t="s">
+        <v>443</v>
+      </c>
+      <c r="DG20" t="s">
+        <v>1094</v>
+      </c>
+      <c r="DH20" t="s">
+        <v>1095</v>
+      </c>
+      <c r="DI20" t="s">
+        <v>1096</v>
+      </c>
+      <c r="DJ20" t="s">
+        <v>1097</v>
+      </c>
+      <c r="DL20" t="s">
+        <v>1098</v>
+      </c>
+      <c r="DM20" t="s">
+        <v>1099</v>
+      </c>
+      <c r="DO20" t="s">
+        <v>1100</v>
+      </c>
+      <c r="DP20" t="s">
+        <v>1101</v>
+      </c>
+      <c r="DR20" t="s">
+        <v>1102</v>
+      </c>
+      <c r="DS20" t="s">
+        <v>1103</v>
+      </c>
+      <c r="DU20" t="s">
+        <v>1104</v>
+      </c>
+      <c r="DV20" t="s">
+        <v>1105</v>
+      </c>
+      <c r="DX20" t="s">
+        <v>1106</v>
+      </c>
+      <c r="DY20" t="s">
+        <v>1107</v>
+      </c>
+      <c r="EA20" t="s">
+        <v>1108</v>
+      </c>
+      <c r="EI20">
         <v>0</v>
       </c>
       <c r="EJ20" s="4">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
+      <c r="EL20">
+        <v>0</v>
+      </c>
       <c r="EM20" s="4">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
+      <c r="EO20">
+        <v>0</v>
+      </c>
       <c r="EP20" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
+      </c>
+      <c r="EQ20" t="s">
+        <v>455</v>
       </c>
       <c r="ES20" s="4">
         <f t="shared" si="10"/>
@@ -8551,29 +10423,314 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="21" spans="1:150" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:159" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>19</v>
       </c>
+      <c r="B21" t="s">
+        <v>845</v>
+      </c>
+      <c r="C21" t="s">
+        <v>950</v>
+      </c>
+      <c r="D21" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E21" t="s">
+        <v>847</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1110</v>
+      </c>
+      <c r="H21" t="s">
+        <v>849</v>
+      </c>
+      <c r="I21" t="s">
+        <v>1111</v>
+      </c>
+      <c r="J21">
+        <v>3401</v>
+      </c>
+      <c r="K21" t="s">
+        <v>1112</v>
+      </c>
+      <c r="L21" t="s">
+        <v>422</v>
+      </c>
+      <c r="M21" t="s">
+        <v>813</v>
+      </c>
+      <c r="N21" t="s">
+        <v>424</v>
+      </c>
+      <c r="P21">
+        <v>2222289701</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>1138</v>
+      </c>
+      <c r="X21">
+        <v>1</v>
+      </c>
+      <c r="Y21">
+        <v>1</v>
+      </c>
+      <c r="Z21">
+        <v>1</v>
+      </c>
+      <c r="AA21">
+        <v>1</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>915</v>
+      </c>
+      <c r="AE21" t="s">
+        <v>853</v>
+      </c>
+      <c r="AF21" t="s">
+        <v>1113</v>
+      </c>
+      <c r="AG21">
+        <v>10</v>
+      </c>
+      <c r="AH21">
+        <v>0</v>
+      </c>
+      <c r="AI21">
+        <v>6</v>
+      </c>
+      <c r="AJ21">
+        <v>4</v>
+      </c>
+      <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>1</v>
+      </c>
+      <c r="AP21" t="s">
+        <v>534</v>
+      </c>
+      <c r="AQ21" t="s">
+        <v>855</v>
+      </c>
       <c r="AR21" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="AS21">
+        <v>1</v>
+      </c>
+      <c r="AT21" t="s">
+        <v>1027</v>
+      </c>
+      <c r="AU21">
+        <v>5</v>
+      </c>
+      <c r="AV21" t="s">
+        <v>857</v>
+      </c>
+      <c r="AW21">
+        <v>4</v>
+      </c>
+      <c r="AX21">
+        <v>1</v>
+      </c>
+      <c r="BE21">
+        <v>1</v>
+      </c>
+      <c r="BF21" t="s">
+        <v>858</v>
+      </c>
+      <c r="BH21">
+        <v>1</v>
+      </c>
+      <c r="BI21" t="s">
+        <v>859</v>
+      </c>
+      <c r="BJ21">
+        <v>9</v>
+      </c>
+      <c r="BK21" t="s">
+        <v>860</v>
+      </c>
+      <c r="BL21">
+        <v>7</v>
+      </c>
+      <c r="BN21">
+        <v>2</v>
+      </c>
+      <c r="BP21">
+        <v>1</v>
+      </c>
+      <c r="BQ21">
+        <v>3</v>
+      </c>
+      <c r="BR21">
+        <v>1</v>
       </c>
       <c r="BS21" s="4">
         <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="BT21">
+        <v>4</v>
+      </c>
+      <c r="BU21">
+        <v>1</v>
+      </c>
+      <c r="BW21">
+        <v>1</v>
+      </c>
+      <c r="BX21">
+        <v>1</v>
+      </c>
+      <c r="BZ21">
+        <v>6</v>
+      </c>
+      <c r="CA21" t="s">
+        <v>859</v>
+      </c>
+      <c r="CJ21">
+        <v>4</v>
+      </c>
+      <c r="CK21" t="s">
+        <v>861</v>
+      </c>
+      <c r="CN21">
+        <v>2</v>
+      </c>
+      <c r="CO21" t="s">
+        <v>862</v>
+      </c>
+      <c r="CV21">
+        <v>26</v>
+      </c>
+      <c r="CW21" t="s">
+        <v>856</v>
+      </c>
+      <c r="CX21">
+        <v>2024</v>
+      </c>
+      <c r="DE21" t="s">
+        <v>442</v>
+      </c>
+      <c r="DF21" t="s">
+        <v>443</v>
+      </c>
+      <c r="DG21" t="s">
+        <v>1114</v>
+      </c>
+      <c r="DH21" t="s">
+        <v>1115</v>
+      </c>
+      <c r="DI21" t="s">
+        <v>1116</v>
+      </c>
+      <c r="DJ21" t="s">
+        <v>1117</v>
+      </c>
+      <c r="DK21" t="s">
+        <v>870</v>
+      </c>
+      <c r="DL21" t="s">
+        <v>1118</v>
+      </c>
+      <c r="DM21" t="s">
+        <v>1119</v>
+      </c>
+      <c r="DN21" t="s">
+        <v>870</v>
+      </c>
+      <c r="DO21" t="s">
+        <v>1120</v>
+      </c>
+      <c r="DP21" t="s">
+        <v>1121</v>
+      </c>
+      <c r="DQ21" t="s">
+        <v>886</v>
+      </c>
+      <c r="DR21" t="s">
+        <v>1122</v>
+      </c>
+      <c r="DS21" t="s">
+        <v>1123</v>
+      </c>
+      <c r="DT21" t="s">
+        <v>876</v>
+      </c>
+      <c r="DU21" t="s">
+        <v>1124</v>
+      </c>
+      <c r="DV21" t="s">
+        <v>1125</v>
+      </c>
+      <c r="DW21" t="s">
+        <v>873</v>
+      </c>
+      <c r="DX21" t="s">
+        <v>1126</v>
+      </c>
+      <c r="DY21" t="s">
+        <v>1127</v>
+      </c>
+      <c r="DZ21" t="s">
+        <v>876</v>
+      </c>
+      <c r="EA21" t="s">
+        <v>1128</v>
+      </c>
+      <c r="EB21" t="s">
+        <v>1129</v>
+      </c>
+      <c r="EC21" t="s">
+        <v>873</v>
+      </c>
+      <c r="ED21" t="s">
+        <v>1130</v>
+      </c>
+      <c r="EE21" t="s">
+        <v>1131</v>
+      </c>
+      <c r="EF21" t="s">
+        <v>876</v>
+      </c>
+      <c r="EG21" t="s">
+        <v>1132</v>
+      </c>
+      <c r="EI21">
         <v>0</v>
       </c>
       <c r="EJ21" s="4">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
+      <c r="EL21">
+        <v>0</v>
+      </c>
       <c r="EM21" s="4">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
+      <c r="EO21">
+        <v>0</v>
+      </c>
       <c r="EP21" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
+      </c>
+      <c r="EQ21" t="s">
+        <v>455</v>
       </c>
       <c r="ES21" s="4">
         <f t="shared" si="10"/>
@@ -8584,29 +10741,314 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="22" spans="1:150" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:159" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>20</v>
       </c>
+      <c r="B22" t="s">
+        <v>845</v>
+      </c>
+      <c r="C22" t="s">
+        <v>950</v>
+      </c>
+      <c r="D22" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E22" t="s">
+        <v>847</v>
+      </c>
+      <c r="G22" t="s">
+        <v>848</v>
+      </c>
+      <c r="H22" t="s">
+        <v>849</v>
+      </c>
+      <c r="I22" t="s">
+        <v>1134</v>
+      </c>
+      <c r="J22">
+        <v>3156</v>
+      </c>
+      <c r="K22" t="s">
+        <v>1135</v>
+      </c>
+      <c r="L22" t="s">
+        <v>1136</v>
+      </c>
+      <c r="M22" t="s">
+        <v>424</v>
+      </c>
+      <c r="N22" t="s">
+        <v>424</v>
+      </c>
+      <c r="P22">
+        <v>2222313245</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>1137</v>
+      </c>
+      <c r="X22">
+        <v>1</v>
+      </c>
+      <c r="Y22">
+        <v>1</v>
+      </c>
+      <c r="Z22">
+        <v>1</v>
+      </c>
+      <c r="AA22">
+        <v>1</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="s">
+        <v>915</v>
+      </c>
+      <c r="AE22" t="s">
+        <v>853</v>
+      </c>
+      <c r="AF22" t="s">
+        <v>1139</v>
+      </c>
+      <c r="AG22">
+        <v>8</v>
+      </c>
+      <c r="AH22">
+        <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>3</v>
+      </c>
+      <c r="AJ22">
+        <v>5</v>
+      </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>1</v>
+      </c>
+      <c r="AP22" t="s">
+        <v>534</v>
+      </c>
+      <c r="AQ22" t="s">
+        <v>855</v>
+      </c>
       <c r="AR22" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>28</v>
+      </c>
+      <c r="AS22">
+        <v>1</v>
+      </c>
+      <c r="AT22" t="s">
+        <v>1027</v>
+      </c>
+      <c r="AU22">
+        <v>8</v>
+      </c>
+      <c r="AV22" t="s">
+        <v>857</v>
+      </c>
+      <c r="AW22">
+        <v>7</v>
+      </c>
+      <c r="AX22">
+        <v>1</v>
+      </c>
+      <c r="BE22">
+        <v>2</v>
+      </c>
+      <c r="BF22" t="s">
+        <v>858</v>
+      </c>
+      <c r="BH22">
+        <v>2</v>
+      </c>
+      <c r="BI22" t="s">
+        <v>859</v>
+      </c>
+      <c r="BJ22">
+        <v>12</v>
+      </c>
+      <c r="BK22" t="s">
+        <v>860</v>
+      </c>
+      <c r="BL22">
+        <v>12</v>
+      </c>
+      <c r="BN22">
+        <v>1</v>
+      </c>
+      <c r="BP22">
+        <v>1</v>
+      </c>
+      <c r="BQ22">
+        <v>3</v>
+      </c>
+      <c r="BR22">
+        <v>2</v>
       </c>
       <c r="BS22" s="4">
         <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="BT22">
+        <v>4</v>
+      </c>
+      <c r="BU22">
+        <v>1</v>
+      </c>
+      <c r="BW22">
+        <v>1</v>
+      </c>
+      <c r="BX22">
+        <v>1</v>
+      </c>
+      <c r="BZ22">
+        <v>4</v>
+      </c>
+      <c r="CA22" t="s">
+        <v>859</v>
+      </c>
+      <c r="CJ22">
+        <v>4</v>
+      </c>
+      <c r="CK22" t="s">
+        <v>861</v>
+      </c>
+      <c r="CN22">
+        <v>2</v>
+      </c>
+      <c r="CO22" t="s">
+        <v>862</v>
+      </c>
+      <c r="CV22">
+        <v>20</v>
+      </c>
+      <c r="CW22" t="s">
+        <v>856</v>
+      </c>
+      <c r="CX22">
+        <v>2024</v>
+      </c>
+      <c r="DE22" t="s">
+        <v>442</v>
+      </c>
+      <c r="DF22" t="s">
+        <v>443</v>
+      </c>
+      <c r="DG22" t="s">
+        <v>1140</v>
+      </c>
+      <c r="DH22" t="s">
+        <v>1141</v>
+      </c>
+      <c r="DI22" t="s">
+        <v>1142</v>
+      </c>
+      <c r="DJ22" t="s">
+        <v>1143</v>
+      </c>
+      <c r="DK22" t="s">
+        <v>1144</v>
+      </c>
+      <c r="DL22" t="s">
+        <v>1145</v>
+      </c>
+      <c r="DM22" t="s">
+        <v>1146</v>
+      </c>
+      <c r="DN22" t="s">
+        <v>870</v>
+      </c>
+      <c r="DO22" t="s">
+        <v>1147</v>
+      </c>
+      <c r="DP22" t="s">
+        <v>1148</v>
+      </c>
+      <c r="DQ22" t="s">
+        <v>870</v>
+      </c>
+      <c r="DR22" t="s">
+        <v>1149</v>
+      </c>
+      <c r="DS22" t="s">
+        <v>1150</v>
+      </c>
+      <c r="DT22" t="s">
+        <v>886</v>
+      </c>
+      <c r="DU22" t="s">
+        <v>1151</v>
+      </c>
+      <c r="DV22" t="s">
+        <v>1152</v>
+      </c>
+      <c r="DW22" t="s">
+        <v>876</v>
+      </c>
+      <c r="DX22" t="s">
+        <v>1153</v>
+      </c>
+      <c r="DY22" t="s">
+        <v>1148</v>
+      </c>
+      <c r="DZ22" t="s">
+        <v>870</v>
+      </c>
+      <c r="EA22" t="s">
+        <v>1149</v>
+      </c>
+      <c r="EB22" t="s">
+        <v>1143</v>
+      </c>
+      <c r="EC22" t="s">
+        <v>1144</v>
+      </c>
+      <c r="ED22" t="s">
+        <v>1145</v>
+      </c>
+      <c r="EE22" t="s">
+        <v>1146</v>
+      </c>
+      <c r="EF22" t="s">
+        <v>870</v>
+      </c>
+      <c r="EG22" t="s">
+        <v>1147</v>
+      </c>
+      <c r="EI22">
         <v>0</v>
       </c>
       <c r="EJ22" s="4">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
+      <c r="EL22">
+        <v>0</v>
+      </c>
       <c r="EM22" s="4">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
+      <c r="EO22">
+        <v>0</v>
+      </c>
       <c r="EP22" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
+      </c>
+      <c r="EQ22" t="s">
+        <v>455</v>
       </c>
       <c r="ES22" s="4">
         <f t="shared" si="10"/>
@@ -8616,30 +11058,321 @@
         <f t="shared" si="11"/>
         <v>ORDINARIO</v>
       </c>
-    </row>
-    <row r="23" spans="1:150" x14ac:dyDescent="0.3">
+      <c r="EU22" t="s">
+        <v>1154</v>
+      </c>
+      <c r="EV22" t="s">
+        <v>876</v>
+      </c>
+      <c r="EW22" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="23" spans="1:159" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>21</v>
       </c>
+      <c r="B23" t="s">
+        <v>845</v>
+      </c>
+      <c r="C23" t="s">
+        <v>950</v>
+      </c>
+      <c r="D23" t="s">
+        <v>1156</v>
+      </c>
+      <c r="E23" t="s">
+        <v>847</v>
+      </c>
+      <c r="G23" t="s">
+        <v>848</v>
+      </c>
+      <c r="H23" t="s">
+        <v>849</v>
+      </c>
+      <c r="I23" t="s">
+        <v>1157</v>
+      </c>
+      <c r="J23">
+        <v>3302</v>
+      </c>
+      <c r="K23" t="s">
+        <v>1158</v>
+      </c>
+      <c r="L23" t="s">
+        <v>1136</v>
+      </c>
+      <c r="M23" t="s">
+        <v>424</v>
+      </c>
+      <c r="N23" t="s">
+        <v>424</v>
+      </c>
+      <c r="P23">
+        <v>2222492228</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>1159</v>
+      </c>
+      <c r="X23">
+        <v>1</v>
+      </c>
+      <c r="Y23">
+        <v>1</v>
+      </c>
+      <c r="Z23">
+        <v>1</v>
+      </c>
+      <c r="AA23">
+        <v>1</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="s">
+        <v>949</v>
+      </c>
+      <c r="AE23" t="s">
+        <v>853</v>
+      </c>
+      <c r="AF23" t="s">
+        <v>1160</v>
+      </c>
+      <c r="AG23">
+        <v>12</v>
+      </c>
+      <c r="AH23">
+        <v>0</v>
+      </c>
+      <c r="AI23">
+        <v>4</v>
+      </c>
+      <c r="AJ23">
+        <v>8</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>1</v>
+      </c>
+      <c r="AP23" t="s">
+        <v>534</v>
+      </c>
+      <c r="AQ23" t="s">
+        <v>855</v>
+      </c>
       <c r="AR23" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="AS23">
+        <v>1</v>
+      </c>
+      <c r="AT23" t="s">
+        <v>1027</v>
+      </c>
+      <c r="AU23">
+        <v>7</v>
+      </c>
+      <c r="AV23" t="s">
+        <v>857</v>
+      </c>
+      <c r="AW23">
+        <v>6</v>
+      </c>
+      <c r="AX23">
+        <v>1</v>
+      </c>
+      <c r="BE23">
+        <v>2</v>
+      </c>
+      <c r="BF23" t="s">
+        <v>858</v>
+      </c>
+      <c r="BG23">
+        <v>2</v>
+      </c>
+      <c r="BI23" t="s">
+        <v>859</v>
+      </c>
+      <c r="BJ23">
+        <v>17</v>
+      </c>
+      <c r="BK23" t="s">
+        <v>860</v>
+      </c>
+      <c r="BL23">
+        <v>10</v>
+      </c>
+      <c r="BN23">
+        <v>2</v>
+      </c>
+      <c r="BQ23">
+        <v>3</v>
+      </c>
+      <c r="BR23">
+        <v>1</v>
       </c>
       <c r="BS23" s="4">
         <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="BT23">
+        <v>4</v>
+      </c>
+      <c r="BU23">
+        <v>1</v>
+      </c>
+      <c r="BW23">
+        <v>1</v>
+      </c>
+      <c r="BX23">
+        <v>1</v>
+      </c>
+      <c r="BZ23">
+        <v>6</v>
+      </c>
+      <c r="CA23" t="s">
+        <v>859</v>
+      </c>
+      <c r="CJ23">
+        <v>4</v>
+      </c>
+      <c r="CK23" t="s">
+        <v>861</v>
+      </c>
+      <c r="CN23">
+        <v>2</v>
+      </c>
+      <c r="CO23" t="s">
+        <v>862</v>
+      </c>
+      <c r="CV23">
+        <v>20</v>
+      </c>
+      <c r="CW23" t="s">
+        <v>856</v>
+      </c>
+      <c r="CX23">
+        <v>2024</v>
+      </c>
+      <c r="DE23" t="s">
+        <v>442</v>
+      </c>
+      <c r="DF23" t="s">
+        <v>443</v>
+      </c>
+      <c r="DG23" t="s">
+        <v>1161</v>
+      </c>
+      <c r="DH23" t="s">
+        <v>1162</v>
+      </c>
+      <c r="DI23" t="s">
+        <v>1163</v>
+      </c>
+      <c r="DJ23" t="s">
+        <v>1164</v>
+      </c>
+      <c r="DK23" t="s">
+        <v>870</v>
+      </c>
+      <c r="DL23" t="s">
+        <v>1165</v>
+      </c>
+      <c r="DM23" t="s">
+        <v>1166</v>
+      </c>
+      <c r="DN23" t="s">
+        <v>873</v>
+      </c>
+      <c r="DO23" t="s">
+        <v>1167</v>
+      </c>
+      <c r="DP23" t="s">
+        <v>1168</v>
+      </c>
+      <c r="DQ23" t="s">
+        <v>876</v>
+      </c>
+      <c r="DR23" t="s">
+        <v>1169</v>
+      </c>
+      <c r="DS23" t="s">
+        <v>1170</v>
+      </c>
+      <c r="DT23" t="s">
+        <v>876</v>
+      </c>
+      <c r="DU23" t="s">
+        <v>1171</v>
+      </c>
+      <c r="DV23" t="s">
+        <v>1172</v>
+      </c>
+      <c r="DW23" t="s">
+        <v>886</v>
+      </c>
+      <c r="DX23" t="s">
+        <v>1173</v>
+      </c>
+      <c r="DY23" t="s">
+        <v>1174</v>
+      </c>
+      <c r="DZ23" t="s">
+        <v>870</v>
+      </c>
+      <c r="EA23" t="s">
+        <v>1175</v>
+      </c>
+      <c r="EB23" t="s">
+        <v>1176</v>
+      </c>
+      <c r="EC23" t="s">
+        <v>870</v>
+      </c>
+      <c r="ED23" t="s">
+        <v>1177</v>
+      </c>
+      <c r="EE23" t="s">
+        <v>1178</v>
+      </c>
+      <c r="EF23" t="s">
+        <v>1179</v>
+      </c>
+      <c r="EG23" t="s">
+        <v>1180</v>
+      </c>
+      <c r="EI23">
         <v>0</v>
       </c>
       <c r="EJ23" s="4">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
+      <c r="EL23">
+        <v>0</v>
+      </c>
       <c r="EM23" s="4">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
+      <c r="EO23">
+        <v>0</v>
+      </c>
       <c r="EP23" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
+      </c>
+      <c r="EQ23" t="s">
+        <v>455</v>
       </c>
       <c r="ES23" s="4">
         <f t="shared" si="10"/>
@@ -8649,30 +11382,324 @@
         <f t="shared" si="11"/>
         <v>ORDINARIO</v>
       </c>
-    </row>
-    <row r="24" spans="1:150" x14ac:dyDescent="0.3">
+      <c r="EU23" t="s">
+        <v>1181</v>
+      </c>
+      <c r="EV23" t="s">
+        <v>879</v>
+      </c>
+      <c r="EW23" t="s">
+        <v>1182</v>
+      </c>
+      <c r="EX23" t="s">
+        <v>1183</v>
+      </c>
+      <c r="EY23" t="s">
+        <v>939</v>
+      </c>
+      <c r="EZ23" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="24" spans="1:159" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>22</v>
       </c>
+      <c r="B24" t="s">
+        <v>845</v>
+      </c>
+      <c r="C24" t="s">
+        <v>950</v>
+      </c>
+      <c r="D24" t="s">
+        <v>1185</v>
+      </c>
+      <c r="E24" t="s">
+        <v>847</v>
+      </c>
+      <c r="G24" t="s">
+        <v>1186</v>
+      </c>
+      <c r="H24" t="s">
+        <v>849</v>
+      </c>
+      <c r="I24" t="s">
+        <v>818</v>
+      </c>
+      <c r="J24">
+        <v>1009</v>
+      </c>
+      <c r="L24" t="s">
+        <v>1187</v>
+      </c>
+      <c r="M24" t="s">
+        <v>748</v>
+      </c>
+      <c r="N24" t="s">
+        <v>424</v>
+      </c>
+      <c r="R24">
+        <v>13</v>
+      </c>
+      <c r="S24" t="s">
+        <v>1188</v>
+      </c>
+      <c r="X24">
+        <v>1</v>
+      </c>
+      <c r="Y24">
+        <v>1</v>
+      </c>
+      <c r="Z24">
+        <v>1</v>
+      </c>
+      <c r="AA24">
+        <v>1</v>
+      </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="s">
+        <v>915</v>
+      </c>
+      <c r="AE24" t="s">
+        <v>853</v>
+      </c>
+      <c r="AF24" t="s">
+        <v>1189</v>
+      </c>
+      <c r="AG24">
+        <v>10</v>
+      </c>
+      <c r="AH24">
+        <v>0</v>
+      </c>
+      <c r="AI24">
+        <v>5</v>
+      </c>
+      <c r="AJ24">
+        <v>5</v>
+      </c>
+      <c r="AK24">
+        <v>0</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>1</v>
+      </c>
+      <c r="AP24" t="s">
+        <v>534</v>
+      </c>
+      <c r="AQ24" t="s">
+        <v>855</v>
+      </c>
       <c r="AR24" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="AS24">
+        <v>1</v>
+      </c>
+      <c r="AT24" t="s">
+        <v>1027</v>
+      </c>
+      <c r="AU24">
+        <v>6</v>
+      </c>
+      <c r="AV24" t="s">
+        <v>857</v>
+      </c>
+      <c r="AW24">
+        <v>5</v>
+      </c>
+      <c r="AX24">
+        <v>1</v>
+      </c>
+      <c r="BE24">
+        <v>1</v>
+      </c>
+      <c r="BF24" t="s">
+        <v>858</v>
+      </c>
+      <c r="BG24">
+        <v>1</v>
+      </c>
+      <c r="BI24" t="s">
+        <v>859</v>
+      </c>
+      <c r="BJ24">
+        <v>11</v>
+      </c>
+      <c r="BK24" t="s">
+        <v>860</v>
+      </c>
+      <c r="BL24">
+        <v>3</v>
+      </c>
+      <c r="BN24">
+        <v>2</v>
+      </c>
+      <c r="BP24">
+        <v>1</v>
+      </c>
+      <c r="BQ24">
+        <v>2</v>
+      </c>
+      <c r="BR24">
+        <v>7</v>
       </c>
       <c r="BS24" s="4">
         <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="BT24">
+        <v>4</v>
+      </c>
+      <c r="BU24">
+        <v>1</v>
+      </c>
+      <c r="BW24">
+        <v>1</v>
+      </c>
+      <c r="BX24">
+        <v>1</v>
+      </c>
+      <c r="BZ24">
+        <v>3</v>
+      </c>
+      <c r="CA24" t="s">
+        <v>859</v>
+      </c>
+      <c r="CJ24">
+        <v>4</v>
+      </c>
+      <c r="CK24" t="s">
+        <v>861</v>
+      </c>
+      <c r="CN24">
+        <v>2</v>
+      </c>
+      <c r="CO24" t="s">
+        <v>862</v>
+      </c>
+      <c r="CV24">
+        <v>26</v>
+      </c>
+      <c r="CW24" t="s">
+        <v>856</v>
+      </c>
+      <c r="CX24">
+        <v>2024</v>
+      </c>
+      <c r="DE24" t="s">
+        <v>442</v>
+      </c>
+      <c r="DF24" t="s">
+        <v>443</v>
+      </c>
+      <c r="DG24" t="s">
+        <v>1191</v>
+      </c>
+      <c r="DH24" t="s">
+        <v>1190</v>
+      </c>
+      <c r="DI24" t="s">
+        <v>1192</v>
+      </c>
+      <c r="DJ24" t="s">
+        <v>1193</v>
+      </c>
+      <c r="DK24" t="s">
+        <v>870</v>
+      </c>
+      <c r="DL24" t="s">
+        <v>1194</v>
+      </c>
+      <c r="DM24" t="s">
+        <v>1195</v>
+      </c>
+      <c r="DN24" t="s">
+        <v>876</v>
+      </c>
+      <c r="DO24" t="s">
+        <v>1196</v>
+      </c>
+      <c r="DP24" t="s">
+        <v>1197</v>
+      </c>
+      <c r="DQ24" t="s">
+        <v>876</v>
+      </c>
+      <c r="DR24" t="s">
+        <v>1198</v>
+      </c>
+      <c r="DS24" t="s">
+        <v>1199</v>
+      </c>
+      <c r="DT24" t="s">
+        <v>876</v>
+      </c>
+      <c r="DU24" t="s">
+        <v>1200</v>
+      </c>
+      <c r="DV24" t="s">
+        <v>1201</v>
+      </c>
+      <c r="DW24" t="s">
+        <v>873</v>
+      </c>
+      <c r="DX24" t="s">
+        <v>1202</v>
+      </c>
+      <c r="DY24" t="s">
+        <v>1203</v>
+      </c>
+      <c r="DZ24" t="s">
+        <v>886</v>
+      </c>
+      <c r="EA24" t="s">
+        <v>1204</v>
+      </c>
+      <c r="EB24" t="s">
+        <v>1205</v>
+      </c>
+      <c r="EE24" t="s">
+        <v>1206</v>
+      </c>
+      <c r="EF24" t="s">
+        <v>870</v>
+      </c>
+      <c r="EG24" t="s">
+        <v>1207</v>
+      </c>
+      <c r="EI24">
         <v>0</v>
       </c>
       <c r="EJ24" s="4">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
+      <c r="EL24">
+        <v>0</v>
+      </c>
       <c r="EM24" s="4">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
+      <c r="EO24">
+        <v>0</v>
+      </c>
       <c r="EP24" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
+      </c>
+      <c r="EQ24" t="s">
+        <v>455</v>
       </c>
       <c r="ES24" s="4">
         <f t="shared" si="10"/>
@@ -8683,29 +11710,311 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="25" spans="1:150" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:159" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>23</v>
       </c>
+      <c r="B25" t="s">
+        <v>845</v>
+      </c>
+      <c r="C25" t="s">
+        <v>950</v>
+      </c>
+      <c r="D25" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E25" t="s">
+        <v>847</v>
+      </c>
+      <c r="G25" t="s">
+        <v>848</v>
+      </c>
+      <c r="H25" t="s">
+        <v>849</v>
+      </c>
+      <c r="I25" t="s">
+        <v>1209</v>
+      </c>
+      <c r="J25">
+        <v>8323</v>
+      </c>
+      <c r="K25" t="s">
+        <v>1210</v>
+      </c>
+      <c r="L25" t="s">
+        <v>1211</v>
+      </c>
+      <c r="M25" t="s">
+        <v>424</v>
+      </c>
+      <c r="N25" t="s">
+        <v>424</v>
+      </c>
+      <c r="P25">
+        <v>2222450490</v>
+      </c>
+      <c r="Q25" s="3" t="s">
+        <v>1212</v>
+      </c>
+      <c r="X25">
+        <v>1</v>
+      </c>
+      <c r="Y25">
+        <v>1</v>
+      </c>
+      <c r="Z25">
+        <v>1</v>
+      </c>
+      <c r="AA25">
+        <v>1</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="s">
+        <v>915</v>
+      </c>
+      <c r="AE25" t="s">
+        <v>853</v>
+      </c>
+      <c r="AF25" t="s">
+        <v>1213</v>
+      </c>
+      <c r="AG25">
+        <v>10</v>
+      </c>
+      <c r="AH25">
+        <v>0</v>
+      </c>
+      <c r="AI25">
+        <v>6</v>
+      </c>
+      <c r="AJ25">
+        <v>4</v>
+      </c>
+      <c r="AK25">
+        <v>0</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>1</v>
+      </c>
+      <c r="AP25" t="s">
+        <v>534</v>
+      </c>
+      <c r="AQ25" t="s">
+        <v>855</v>
+      </c>
       <c r="AR25" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="AS25">
+        <v>1</v>
+      </c>
+      <c r="AT25" t="s">
+        <v>1027</v>
+      </c>
+      <c r="AU25">
+        <v>7</v>
+      </c>
+      <c r="AV25" t="s">
+        <v>857</v>
+      </c>
+      <c r="AW25">
+        <v>6</v>
+      </c>
+      <c r="AX25">
+        <v>1</v>
+      </c>
+      <c r="BE25">
+        <v>2</v>
+      </c>
+      <c r="BF25" t="s">
+        <v>858</v>
+      </c>
+      <c r="BH25">
+        <v>2</v>
+      </c>
+      <c r="BI25" t="s">
+        <v>859</v>
+      </c>
+      <c r="BJ25">
+        <v>14</v>
+      </c>
+      <c r="BK25" t="s">
+        <v>860</v>
+      </c>
+      <c r="BL25">
+        <v>7</v>
+      </c>
+      <c r="BN25">
+        <v>1</v>
+      </c>
+      <c r="BP25">
+        <v>1</v>
+      </c>
+      <c r="BQ25">
+        <v>3</v>
+      </c>
+      <c r="BR25">
+        <v>1</v>
       </c>
       <c r="BS25" s="4">
         <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="BT25">
+        <v>4</v>
+      </c>
+      <c r="BU25">
+        <v>1</v>
+      </c>
+      <c r="BW25">
+        <v>1</v>
+      </c>
+      <c r="BX25">
+        <v>2</v>
+      </c>
+      <c r="BZ25">
+        <v>5</v>
+      </c>
+      <c r="CA25" t="s">
+        <v>859</v>
+      </c>
+      <c r="CJ25">
+        <v>4</v>
+      </c>
+      <c r="CK25" t="s">
+        <v>861</v>
+      </c>
+      <c r="CN25">
+        <v>2</v>
+      </c>
+      <c r="CO25" t="s">
+        <v>862</v>
+      </c>
+      <c r="CV25">
+        <v>16</v>
+      </c>
+      <c r="CW25" t="s">
+        <v>856</v>
+      </c>
+      <c r="CX25">
+        <v>2024</v>
+      </c>
+      <c r="DE25" t="s">
+        <v>442</v>
+      </c>
+      <c r="DF25" t="s">
+        <v>443</v>
+      </c>
+      <c r="DG25" t="s">
+        <v>1215</v>
+      </c>
+      <c r="DH25" s="1" t="s">
+        <v>1216</v>
+      </c>
+      <c r="DI25" t="s">
+        <v>1217</v>
+      </c>
+      <c r="DJ25" t="s">
+        <v>1218</v>
+      </c>
+      <c r="DK25" t="s">
+        <v>1049</v>
+      </c>
+      <c r="DL25" t="s">
+        <v>1219</v>
+      </c>
+      <c r="DM25" t="s">
+        <v>1220</v>
+      </c>
+      <c r="DN25" t="s">
+        <v>876</v>
+      </c>
+      <c r="DO25" t="s">
+        <v>1221</v>
+      </c>
+      <c r="DP25" t="s">
+        <v>1222</v>
+      </c>
+      <c r="DQ25" t="s">
+        <v>870</v>
+      </c>
+      <c r="DR25" t="s">
+        <v>1223</v>
+      </c>
+      <c r="DS25" t="s">
+        <v>1224</v>
+      </c>
+      <c r="DT25" t="s">
+        <v>870</v>
+      </c>
+      <c r="DU25" t="s">
+        <v>1225</v>
+      </c>
+      <c r="DV25" t="s">
+        <v>1226</v>
+      </c>
+      <c r="DW25" t="s">
+        <v>876</v>
+      </c>
+      <c r="DX25" t="s">
+        <v>1227</v>
+      </c>
+      <c r="DY25" t="s">
+        <v>1228</v>
+      </c>
+      <c r="DZ25" t="s">
+        <v>876</v>
+      </c>
+      <c r="EA25" t="s">
+        <v>1229</v>
+      </c>
+      <c r="EB25" t="s">
+        <v>1230</v>
+      </c>
+      <c r="EC25" t="s">
+        <v>879</v>
+      </c>
+      <c r="EE25" t="s">
+        <v>1231</v>
+      </c>
+      <c r="EF25" t="s">
+        <v>1232</v>
+      </c>
+      <c r="EG25" t="s">
+        <v>1233</v>
+      </c>
+      <c r="EI25">
         <v>0</v>
       </c>
       <c r="EJ25" s="4">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
+      <c r="EL25">
+        <v>0</v>
+      </c>
       <c r="EM25" s="4">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
+      <c r="EO25">
+        <v>0</v>
+      </c>
       <c r="EP25" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
+      </c>
+      <c r="EQ25" t="s">
+        <v>455</v>
       </c>
       <c r="ES25" s="4">
         <f t="shared" si="10"/>
@@ -8716,29 +12025,173 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="26" spans="1:150" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:159" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>24</v>
       </c>
+      <c r="B26" t="s">
+        <v>845</v>
+      </c>
+      <c r="C26" t="s">
+        <v>950</v>
+      </c>
+      <c r="D26" t="s">
+        <v>1234</v>
+      </c>
+      <c r="E26" t="s">
+        <v>847</v>
+      </c>
+      <c r="G26" t="s">
+        <v>1235</v>
+      </c>
+      <c r="H26" t="s">
+        <v>849</v>
+      </c>
+      <c r="J26">
+        <v>7</v>
+      </c>
+      <c r="K26" t="s">
+        <v>1237</v>
+      </c>
+      <c r="L26" t="s">
+        <v>422</v>
+      </c>
+      <c r="M26" t="s">
+        <v>1236</v>
+      </c>
+      <c r="N26" t="s">
+        <v>424</v>
+      </c>
+      <c r="X26">
+        <v>1</v>
+      </c>
+      <c r="Y26">
+        <v>1</v>
+      </c>
+      <c r="Z26">
+        <v>1</v>
+      </c>
+      <c r="AA26">
+        <v>1</v>
+      </c>
+      <c r="AB26">
+        <v>2</v>
+      </c>
+      <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="s">
+        <v>1238</v>
+      </c>
+      <c r="AE26" t="s">
+        <v>853</v>
+      </c>
+      <c r="AF26" t="s">
+        <v>1239</v>
+      </c>
+      <c r="AG26">
+        <v>9</v>
+      </c>
+      <c r="AH26">
+        <v>0</v>
+      </c>
+      <c r="AI26">
+        <v>3</v>
+      </c>
+      <c r="AJ26">
+        <v>6</v>
+      </c>
+      <c r="AK26">
+        <v>0</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>1</v>
+      </c>
+      <c r="AP26" t="s">
+        <v>534</v>
+      </c>
+      <c r="AQ26" t="s">
+        <v>855</v>
+      </c>
       <c r="AR26" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="AT26" t="s">
+        <v>1027</v>
+      </c>
+      <c r="AV26" t="s">
+        <v>857</v>
+      </c>
+      <c r="BF26" t="s">
+        <v>858</v>
+      </c>
+      <c r="BI26" t="s">
+        <v>859</v>
+      </c>
+      <c r="BK26" t="s">
+        <v>860</v>
+      </c>
       <c r="BS26" s="4">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
+      <c r="CA26" t="s">
+        <v>859</v>
+      </c>
+      <c r="CJ26">
+        <v>4</v>
+      </c>
+      <c r="CK26" t="s">
+        <v>861</v>
+      </c>
+      <c r="CN26">
+        <v>2</v>
+      </c>
+      <c r="CO26" t="s">
+        <v>862</v>
+      </c>
+      <c r="CV26">
+        <v>2</v>
+      </c>
+      <c r="CW26" t="s">
+        <v>856</v>
+      </c>
+      <c r="CX26">
+        <v>2024</v>
+      </c>
+      <c r="DE26" t="s">
+        <v>442</v>
+      </c>
+      <c r="DF26" t="s">
+        <v>443</v>
+      </c>
+      <c r="EI26">
+        <v>0</v>
+      </c>
       <c r="EJ26" s="4">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
+      <c r="EL26">
+        <v>0</v>
+      </c>
       <c r="EM26" s="4">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
+      <c r="EO26">
+        <v>0</v>
+      </c>
       <c r="EP26" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
+      </c>
+      <c r="EQ26" t="s">
+        <v>455</v>
       </c>
       <c r="ES26" s="4">
         <f t="shared" si="10"/>
@@ -8749,29 +12202,125 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="27" spans="1:150" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:159" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>25</v>
       </c>
+      <c r="B27" t="s">
+        <v>845</v>
+      </c>
+      <c r="C27" t="s">
+        <v>950</v>
+      </c>
+      <c r="E27" t="s">
+        <v>847</v>
+      </c>
+      <c r="N27" t="s">
+        <v>424</v>
+      </c>
+      <c r="X27">
+        <v>1</v>
+      </c>
+      <c r="Y27">
+        <v>1</v>
+      </c>
+      <c r="Z27">
+        <v>1</v>
+      </c>
+      <c r="AA27">
+        <v>1</v>
+      </c>
+      <c r="AE27" t="s">
+        <v>853</v>
+      </c>
+      <c r="AH27">
+        <v>0</v>
+      </c>
+      <c r="AK27">
+        <v>0</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>1</v>
+      </c>
+      <c r="AP27" t="s">
+        <v>534</v>
+      </c>
+      <c r="AQ27" t="s">
+        <v>855</v>
+      </c>
       <c r="AR27" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="AT27" t="s">
+        <v>1027</v>
+      </c>
+      <c r="AV27" t="s">
+        <v>857</v>
+      </c>
+      <c r="BF27" t="s">
+        <v>858</v>
+      </c>
+      <c r="BI27" t="s">
+        <v>859</v>
+      </c>
+      <c r="BK27" t="s">
+        <v>860</v>
+      </c>
       <c r="BS27" s="4">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
+      <c r="CA27" t="s">
+        <v>859</v>
+      </c>
+      <c r="CJ27">
+        <v>4</v>
+      </c>
+      <c r="CK27" t="s">
+        <v>861</v>
+      </c>
+      <c r="CN27">
+        <v>2</v>
+      </c>
+      <c r="CO27" t="s">
+        <v>862</v>
+      </c>
+      <c r="CX27">
+        <v>2024</v>
+      </c>
+      <c r="DE27" t="s">
+        <v>442</v>
+      </c>
+      <c r="DF27" t="s">
+        <v>443</v>
+      </c>
+      <c r="EI27">
+        <v>0</v>
+      </c>
       <c r="EJ27" s="4">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
+      <c r="EL27">
+        <v>0</v>
+      </c>
       <c r="EM27" s="4">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
+      <c r="EO27">
+        <v>0</v>
+      </c>
       <c r="EP27" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
+      </c>
+      <c r="EQ27" t="s">
+        <v>455</v>
       </c>
       <c r="ES27" s="4">
         <f t="shared" si="10"/>
@@ -8782,29 +12331,122 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="28" spans="1:150" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:159" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26</v>
       </c>
+      <c r="B28" t="s">
+        <v>845</v>
+      </c>
+      <c r="C28" t="s">
+        <v>950</v>
+      </c>
+      <c r="E28" t="s">
+        <v>847</v>
+      </c>
+      <c r="X28">
+        <v>1</v>
+      </c>
+      <c r="Y28">
+        <v>1</v>
+      </c>
+      <c r="Z28">
+        <v>1</v>
+      </c>
+      <c r="AA28">
+        <v>1</v>
+      </c>
+      <c r="AE28" t="s">
+        <v>853</v>
+      </c>
+      <c r="AH28">
+        <v>0</v>
+      </c>
+      <c r="AK28">
+        <v>0</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>1</v>
+      </c>
+      <c r="AP28" t="s">
+        <v>534</v>
+      </c>
+      <c r="AQ28" t="s">
+        <v>855</v>
+      </c>
       <c r="AR28" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="AT28" t="s">
+        <v>1027</v>
+      </c>
+      <c r="AV28" t="s">
+        <v>857</v>
+      </c>
+      <c r="BF28" t="s">
+        <v>858</v>
+      </c>
+      <c r="BI28" t="s">
+        <v>859</v>
+      </c>
+      <c r="BK28" t="s">
+        <v>860</v>
+      </c>
       <c r="BS28" s="4">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
+      <c r="CA28" t="s">
+        <v>859</v>
+      </c>
+      <c r="CJ28">
+        <v>4</v>
+      </c>
+      <c r="CK28" t="s">
+        <v>861</v>
+      </c>
+      <c r="CN28">
+        <v>2</v>
+      </c>
+      <c r="CO28" t="s">
+        <v>862</v>
+      </c>
+      <c r="CX28">
+        <v>2024</v>
+      </c>
+      <c r="DE28" t="s">
+        <v>442</v>
+      </c>
+      <c r="DF28" t="s">
+        <v>443</v>
+      </c>
+      <c r="EI28">
+        <v>0</v>
+      </c>
       <c r="EJ28" s="4">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
+      <c r="EL28">
+        <v>0</v>
+      </c>
       <c r="EM28" s="4">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
+      <c r="EO28">
+        <v>0</v>
+      </c>
       <c r="EP28" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
+      </c>
+      <c r="EQ28" t="s">
+        <v>455</v>
       </c>
       <c r="ES28" s="4">
         <f t="shared" si="10"/>
@@ -8815,29 +12457,122 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="29" spans="1:150" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:159" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>27</v>
       </c>
+      <c r="B29" t="s">
+        <v>845</v>
+      </c>
+      <c r="C29" t="s">
+        <v>950</v>
+      </c>
+      <c r="E29" t="s">
+        <v>847</v>
+      </c>
+      <c r="X29">
+        <v>1</v>
+      </c>
+      <c r="Y29">
+        <v>1</v>
+      </c>
+      <c r="Z29">
+        <v>1</v>
+      </c>
+      <c r="AA29">
+        <v>1</v>
+      </c>
+      <c r="AE29" t="s">
+        <v>853</v>
+      </c>
+      <c r="AH29">
+        <v>0</v>
+      </c>
+      <c r="AK29">
+        <v>0</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>1</v>
+      </c>
+      <c r="AP29" t="s">
+        <v>534</v>
+      </c>
+      <c r="AQ29" t="s">
+        <v>855</v>
+      </c>
       <c r="AR29" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="AT29" t="s">
+        <v>1027</v>
+      </c>
+      <c r="AV29" t="s">
+        <v>857</v>
+      </c>
+      <c r="BF29" t="s">
+        <v>858</v>
+      </c>
+      <c r="BI29" t="s">
+        <v>859</v>
+      </c>
+      <c r="BK29" t="s">
+        <v>860</v>
+      </c>
       <c r="BS29" s="4">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
+      <c r="CA29" t="s">
+        <v>859</v>
+      </c>
+      <c r="CJ29">
+        <v>4</v>
+      </c>
+      <c r="CK29" t="s">
+        <v>861</v>
+      </c>
+      <c r="CN29">
+        <v>2</v>
+      </c>
+      <c r="CO29" t="s">
+        <v>862</v>
+      </c>
+      <c r="CX29">
+        <v>2024</v>
+      </c>
+      <c r="DE29" t="s">
+        <v>442</v>
+      </c>
+      <c r="DF29" t="s">
+        <v>443</v>
+      </c>
+      <c r="EI29">
+        <v>0</v>
+      </c>
       <c r="EJ29" s="4">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
+      <c r="EL29">
+        <v>0</v>
+      </c>
       <c r="EM29" s="4">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
+      <c r="EO29">
+        <v>0</v>
+      </c>
       <c r="EP29" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
+      </c>
+      <c r="EQ29" t="s">
+        <v>455</v>
       </c>
       <c r="ES29" s="4">
         <f t="shared" si="10"/>
@@ -8848,29 +12583,122 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="30" spans="1:150" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:159" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>28</v>
       </c>
+      <c r="B30" t="s">
+        <v>845</v>
+      </c>
+      <c r="C30" t="s">
+        <v>950</v>
+      </c>
+      <c r="E30" t="s">
+        <v>847</v>
+      </c>
+      <c r="X30">
+        <v>1</v>
+      </c>
+      <c r="Y30">
+        <v>1</v>
+      </c>
+      <c r="Z30">
+        <v>1</v>
+      </c>
+      <c r="AA30">
+        <v>1</v>
+      </c>
+      <c r="AE30" t="s">
+        <v>853</v>
+      </c>
+      <c r="AH30">
+        <v>0</v>
+      </c>
+      <c r="AK30">
+        <v>0</v>
+      </c>
+      <c r="AL30">
+        <v>0</v>
+      </c>
+      <c r="AM30">
+        <v>1</v>
+      </c>
+      <c r="AP30" t="s">
+        <v>534</v>
+      </c>
+      <c r="AQ30" t="s">
+        <v>855</v>
+      </c>
       <c r="AR30" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="AT30" t="s">
+        <v>1027</v>
+      </c>
+      <c r="AV30" t="s">
+        <v>857</v>
+      </c>
+      <c r="BF30" t="s">
+        <v>858</v>
+      </c>
+      <c r="BI30" t="s">
+        <v>859</v>
+      </c>
+      <c r="BK30" t="s">
+        <v>860</v>
+      </c>
       <c r="BS30" s="4">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
+      <c r="CA30" t="s">
+        <v>859</v>
+      </c>
+      <c r="CJ30">
+        <v>4</v>
+      </c>
+      <c r="CK30" t="s">
+        <v>861</v>
+      </c>
+      <c r="CN30">
+        <v>2</v>
+      </c>
+      <c r="CO30" t="s">
+        <v>862</v>
+      </c>
+      <c r="CX30">
+        <v>2024</v>
+      </c>
+      <c r="DE30" t="s">
+        <v>442</v>
+      </c>
+      <c r="DF30" t="s">
+        <v>443</v>
+      </c>
+      <c r="EI30">
+        <v>0</v>
+      </c>
       <c r="EJ30" s="4">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
+      <c r="EL30">
+        <v>0</v>
+      </c>
       <c r="EM30" s="4">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
+      <c r="EO30">
+        <v>0</v>
+      </c>
       <c r="EP30" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
+      </c>
+      <c r="EQ30" t="s">
+        <v>455</v>
       </c>
       <c r="ES30" s="4">
         <f t="shared" si="10"/>
@@ -8881,29 +12709,122 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="31" spans="1:150" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:159" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>29</v>
       </c>
+      <c r="B31" t="s">
+        <v>845</v>
+      </c>
+      <c r="C31" t="s">
+        <v>950</v>
+      </c>
+      <c r="E31" t="s">
+        <v>847</v>
+      </c>
+      <c r="X31">
+        <v>1</v>
+      </c>
+      <c r="Y31">
+        <v>1</v>
+      </c>
+      <c r="Z31">
+        <v>1</v>
+      </c>
+      <c r="AA31">
+        <v>1</v>
+      </c>
+      <c r="AE31" t="s">
+        <v>853</v>
+      </c>
+      <c r="AH31">
+        <v>0</v>
+      </c>
+      <c r="AK31">
+        <v>0</v>
+      </c>
+      <c r="AL31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>1</v>
+      </c>
+      <c r="AP31" t="s">
+        <v>534</v>
+      </c>
+      <c r="AQ31" t="s">
+        <v>855</v>
+      </c>
       <c r="AR31" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="AT31" t="s">
+        <v>1027</v>
+      </c>
+      <c r="AV31" t="s">
+        <v>857</v>
+      </c>
+      <c r="BF31" t="s">
+        <v>858</v>
+      </c>
+      <c r="BI31" t="s">
+        <v>859</v>
+      </c>
+      <c r="BK31" t="s">
+        <v>860</v>
+      </c>
       <c r="BS31" s="4">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
+      <c r="CA31" t="s">
+        <v>859</v>
+      </c>
+      <c r="CJ31">
+        <v>4</v>
+      </c>
+      <c r="CK31" t="s">
+        <v>861</v>
+      </c>
+      <c r="CN31">
+        <v>2</v>
+      </c>
+      <c r="CO31" t="s">
+        <v>862</v>
+      </c>
+      <c r="CX31">
+        <v>2024</v>
+      </c>
+      <c r="DE31" t="s">
+        <v>442</v>
+      </c>
+      <c r="DF31" t="s">
+        <v>443</v>
+      </c>
+      <c r="EI31">
+        <v>0</v>
+      </c>
       <c r="EJ31" s="4">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
+      <c r="EL31">
+        <v>0</v>
+      </c>
       <c r="EM31" s="4">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
+      <c r="EO31">
+        <v>0</v>
+      </c>
       <c r="EP31" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
+      </c>
+      <c r="EQ31" t="s">
+        <v>455</v>
       </c>
       <c r="ES31" s="4">
         <f t="shared" si="10"/>
@@ -8914,7 +12835,7 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="32" spans="1:150" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:159" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>30</v>
       </c>
@@ -14414,39 +18335,39 @@
       <formula>$A3=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="H13">
+    <cfRule type="expression" dxfId="6" priority="1">
+      <formula>$A13=$A$1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AW2:AX2">
-    <cfRule type="expression" dxfId="6" priority="6">
+    <cfRule type="expression" dxfId="5" priority="6">
       <formula>$A2=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BG2:BH2">
-    <cfRule type="expression" dxfId="5" priority="5">
+    <cfRule type="expression" dxfId="4" priority="5">
       <formula>$A2=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DD2">
-    <cfRule type="expression" dxfId="4" priority="4">
+    <cfRule type="expression" dxfId="3" priority="4">
       <formula>$A2=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DG2">
-    <cfRule type="expression" dxfId="3" priority="3">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>$A2=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DI2">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>$A2=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EU2:EZ2">
-    <cfRule type="expression" dxfId="1" priority="11">
+    <cfRule type="expression" dxfId="0" priority="11">
       <formula>#REF!=$A$1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H13">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$A13=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -14465,16 +18386,24 @@
     <hyperlink ref="Q10" r:id="rId8" xr:uid="{91878B54-61A9-411B-B68E-0E041A2904C3}"/>
     <hyperlink ref="Q11" r:id="rId9" xr:uid="{9F2CF0DE-DA06-4334-BDEB-FFE06D8179C7}"/>
     <hyperlink ref="Q12" r:id="rId10" xr:uid="{B273690A-C54D-473E-8E7B-D7B9AC83DFAD}"/>
+    <hyperlink ref="Q17" r:id="rId11" xr:uid="{73E06077-7F11-4B0F-ACA2-422A47C71700}"/>
+    <hyperlink ref="Q18" r:id="rId12" xr:uid="{7D5BC455-F102-4DF5-8F66-AAB3B80A57A9}"/>
+    <hyperlink ref="Q19" r:id="rId13" xr:uid="{8B585EED-4FB2-47D7-9D2B-AA5AE3B22B52}"/>
+    <hyperlink ref="Q20" r:id="rId14" xr:uid="{4E4BB7BD-99B7-4CA8-B2CA-7604F3EDE0D2}"/>
+    <hyperlink ref="Q21" r:id="rId15" xr:uid="{B4CA590F-5879-4279-BD3D-C463EFDC3509}"/>
+    <hyperlink ref="Q22" r:id="rId16" xr:uid="{25CFBA39-03C8-4081-A0C4-1277A6DE75F7}"/>
+    <hyperlink ref="Q23" r:id="rId17" xr:uid="{44B582C3-3169-4287-9F09-3EE5AE51FE29}"/>
+    <hyperlink ref="Q25" r:id="rId18" xr:uid="{BD402CD4-FECC-4968-9741-F72B106BBEF2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId11"/>
-  <legacyDrawing r:id="rId12"/>
+  <drawing r:id="rId19"/>
+  <legacyDrawing r:id="rId20"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x14">
       <controls>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1025" r:id="rId13" name="Spinner 1">
+            <control shapeId="1025" r:id="rId21" name="Spinner 1">
               <controlPr defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
@@ -15204,10 +19133,10 @@
         <v>715</v>
       </c>
       <c r="HY1" t="s">
+        <v>830</v>
+      </c>
+      <c r="HZ1" t="s">
         <v>831</v>
-      </c>
-      <c r="HZ1" t="s">
-        <v>832</v>
       </c>
       <c r="IA1" t="s">
         <v>716</v>
@@ -15249,7 +19178,7 @@
         <v>725</v>
       </c>
       <c r="IN1" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
     </row>
     <row r="2" spans="1:248" x14ac:dyDescent="0.3">
@@ -15375,7 +19304,7 @@
       </c>
       <c r="AF2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$209,32, FALSE)</f>
-        <v>CARLOR GONZALEZ ROMERO</v>
+        <v>CARLOS GONZALEZ ROMERO</v>
       </c>
       <c r="AG2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$209,33, FALSE)</f>
@@ -15883,7 +19812,7 @@
         <v>83</v>
       </c>
       <c r="FD2" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="FE2" t="s">
         <v>397</v>
@@ -15910,22 +19839,22 @@
         <v>406</v>
       </c>
       <c r="FM2" t="s">
+        <v>834</v>
+      </c>
+      <c r="FN2" t="s">
         <v>835</v>
       </c>
-      <c r="FN2" t="s">
+      <c r="FO2" t="s">
         <v>836</v>
       </c>
-      <c r="FO2" t="s">
+      <c r="FP2" t="s">
         <v>837</v>
       </c>
-      <c r="FP2" t="s">
+      <c r="FQ2" t="s">
         <v>838</v>
       </c>
-      <c r="FQ2" t="s">
-        <v>839</v>
-      </c>
       <c r="FR2" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="FS2" t="s">
         <v>88</v>
@@ -16093,19 +20022,19 @@
         <v>711</v>
       </c>
       <c r="HV2" t="s">
+        <v>839</v>
+      </c>
+      <c r="HW2" t="s">
         <v>840</v>
-      </c>
-      <c r="HW2" t="s">
-        <v>841</v>
       </c>
       <c r="HX2" t="s">
         <v>729</v>
       </c>
       <c r="HY2" t="s">
+        <v>841</v>
+      </c>
+      <c r="HZ2" t="s">
         <v>842</v>
-      </c>
-      <c r="HZ2" t="s">
-        <v>843</v>
       </c>
       <c r="IA2" t="s">
         <v>730</v>
@@ -16147,7 +20076,7 @@
         <v>742</v>
       </c>
       <c r="IN2" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
     </row>
   </sheetData>
@@ -16164,7 +20093,7 @@
   <sheetData>
     <row r="1" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D1" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>25</v>
@@ -16232,7 +20161,7 @@
     </row>
     <row r="2" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D2" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E2" t="s">
         <v>26</v>
@@ -16300,7 +20229,7 @@
     </row>
     <row r="3" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E3" t="s">
         <v>24</v>
@@ -16368,13 +20297,13 @@
     </row>
     <row r="4" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D4" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E4" t="s">
         <v>27</v>
       </c>
       <c r="F4" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="G4" t="s">
         <v>343</v>
@@ -16436,7 +20365,7 @@
     </row>
     <row r="5" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D5" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E5" t="s">
         <v>396</v>
@@ -16504,7 +20433,7 @@
     </row>
     <row r="6" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E6" t="s">
         <v>28</v>
@@ -16572,7 +20501,7 @@
     </row>
     <row r="7" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E7" t="s">
         <v>29</v>
@@ -16640,7 +20569,7 @@
     </row>
     <row r="8" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E8" t="s">
         <v>181</v>
@@ -16708,7 +20637,7 @@
     </row>
     <row r="9" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D9" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E9" t="s">
         <v>403</v>
@@ -16776,7 +20705,7 @@
     </row>
     <row r="10" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E10" t="s">
         <v>30</v>
@@ -16844,7 +20773,7 @@
     </row>
     <row r="11" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D11" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E11" t="s">
         <v>31</v>
@@ -16912,7 +20841,7 @@
     </row>
     <row r="12" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E12" t="s">
         <v>405</v>
@@ -16980,13 +20909,13 @@
     </row>
     <row r="13" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D13" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E13" t="s">
         <v>32</v>
       </c>
       <c r="F13" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="G13" t="s">
         <v>348</v>
@@ -17048,13 +20977,13 @@
     </row>
     <row r="14" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D14" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E14" t="s">
         <v>33</v>
       </c>
       <c r="F14" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="G14" t="s">
         <v>349</v>
@@ -17116,13 +21045,13 @@
     </row>
     <row r="15" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D15" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E15" t="s">
         <v>34</v>
       </c>
       <c r="F15" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="G15" t="s">
         <v>350</v>
@@ -17184,13 +21113,13 @@
     </row>
     <row r="16" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D16" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E16" t="s">
         <v>35</v>
       </c>
       <c r="F16" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="G16" t="s">
         <v>351</v>
@@ -17252,13 +21181,13 @@
     </row>
     <row r="17" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D17" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E17" t="s">
         <v>36</v>
       </c>
       <c r="F17" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="G17" t="s">
         <v>352</v>
@@ -17320,13 +21249,13 @@
     </row>
     <row r="18" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D18" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E18" t="s">
         <v>37</v>
       </c>
       <c r="F18" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="G18" t="s">
         <v>353</v>
@@ -17388,7 +21317,7 @@
     </row>
     <row r="19" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D19" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E19" t="s">
         <v>38</v>
@@ -17456,7 +21385,7 @@
     </row>
     <row r="20" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E20" t="s">
         <v>39</v>
@@ -17524,7 +21453,7 @@
     </row>
     <row r="21" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D21" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E21" t="s">
         <v>40</v>
@@ -17592,7 +21521,7 @@
     </row>
     <row r="22" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D22" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E22" t="s">
         <v>41</v>
@@ -17660,7 +21589,7 @@
     </row>
     <row r="23" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D23" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E23" t="s">
         <v>42</v>
@@ -17728,7 +21657,7 @@
     </row>
     <row r="24" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D24" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E24" t="s">
         <v>43</v>
@@ -17796,7 +21725,7 @@
     </row>
     <row r="25" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D25" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E25" t="s">
         <v>44</v>
@@ -17864,7 +21793,7 @@
     </row>
     <row r="26" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D26" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E26" t="s">
         <v>339</v>
@@ -17932,7 +21861,7 @@
     </row>
     <row r="27" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D27" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E27" t="s">
         <v>45</v>
@@ -18000,7 +21929,7 @@
     </row>
     <row r="28" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D28" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E28" t="s">
         <v>46</v>
@@ -18068,7 +21997,7 @@
     </row>
     <row r="29" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D29" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E29" t="s">
         <v>47</v>
@@ -18136,7 +22065,7 @@
     </row>
     <row r="30" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D30" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E30" t="s">
         <v>48</v>
@@ -18204,7 +22133,7 @@
     </row>
     <row r="31" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D31" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E31" t="s">
         <v>49</v>
@@ -18272,7 +22201,7 @@
     </row>
     <row r="32" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D32" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E32" t="s">
         <v>50</v>
@@ -18340,7 +22269,7 @@
     </row>
     <row r="33" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D33" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E33" t="s">
         <v>51</v>
@@ -18408,7 +22337,7 @@
     </row>
     <row r="34" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D34" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E34" t="s">
         <v>52</v>
@@ -18476,7 +22405,7 @@
     </row>
     <row r="35" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D35" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E35" t="s">
         <v>53</v>
@@ -18544,7 +22473,7 @@
     </row>
     <row r="36" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D36" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E36" t="s">
         <v>54</v>
@@ -18612,7 +22541,7 @@
     </row>
     <row r="37" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D37" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E37" t="s">
         <v>55</v>
@@ -18680,7 +22609,7 @@
     </row>
     <row r="38" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D38" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E38" t="s">
         <v>56</v>
@@ -18748,7 +22677,7 @@
     </row>
     <row r="39" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D39" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E39" t="s">
         <v>57</v>
@@ -18816,7 +22745,7 @@
     </row>
     <row r="40" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D40" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E40" t="s">
         <v>58</v>
@@ -18884,7 +22813,7 @@
     </row>
     <row r="41" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D41" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E41" t="s">
         <v>59</v>
@@ -18952,7 +22881,7 @@
     </row>
     <row r="42" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D42" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E42" t="s">
         <v>60</v>
@@ -19020,7 +22949,7 @@
     </row>
     <row r="43" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D43" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E43" t="s">
         <v>61</v>
@@ -19088,7 +23017,7 @@
     </row>
     <row r="44" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D44" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E44" t="s">
         <v>62</v>
@@ -19156,7 +23085,7 @@
     </row>
     <row r="45" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D45" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E45" t="s">
         <v>63</v>
@@ -19224,7 +23153,7 @@
     </row>
     <row r="46" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D46" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E46" t="s">
         <v>64</v>
@@ -19292,7 +23221,7 @@
     </row>
     <row r="47" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D47" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E47" t="s">
         <v>65</v>
@@ -19360,7 +23289,7 @@
     </row>
     <row r="48" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D48" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E48" t="s">
         <v>66</v>
@@ -19428,7 +23357,7 @@
     </row>
     <row r="49" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D49" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E49" t="s">
         <v>67</v>
@@ -19496,7 +23425,7 @@
     </row>
     <row r="50" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D50" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E50" t="s">
         <v>68</v>
@@ -19564,7 +23493,7 @@
     </row>
     <row r="51" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D51" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E51" t="s">
         <v>69</v>
@@ -19632,7 +23561,7 @@
     </row>
     <row r="52" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D52" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E52" t="s">
         <v>70</v>
@@ -19700,7 +23629,7 @@
     </row>
     <row r="53" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D53" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E53" t="s">
         <v>71</v>
@@ -19898,7 +23827,7 @@
     </row>
     <row r="56" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D56" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E56" t="s">
         <v>14</v>
@@ -19966,7 +23895,7 @@
     </row>
     <row r="57" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D57" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E57" t="s">
         <v>74</v>
@@ -20034,7 +23963,7 @@
     </row>
     <row r="58" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D58" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E58" t="s">
         <v>75</v>
@@ -20102,7 +24031,7 @@
     </row>
     <row r="59" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D59" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E59" t="s">
         <v>76</v>
@@ -20170,7 +24099,7 @@
     </row>
     <row r="60" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D60" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E60" t="s">
         <v>77</v>
@@ -20238,7 +24167,7 @@
     </row>
     <row r="61" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D61" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E61" t="s">
         <v>78</v>
@@ -20306,7 +24235,7 @@
     </row>
     <row r="62" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D62" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E62" t="s">
         <v>79</v>
@@ -20374,7 +24303,7 @@
     </row>
     <row r="63" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D63" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E63" t="s">
         <v>80</v>
@@ -20962,7 +24891,7 @@
     </row>
     <row r="72" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D72" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E72" t="s">
         <v>705</v>
@@ -21095,7 +25024,7 @@
     </row>
     <row r="74" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D74" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E74" t="s">
         <v>713</v>
@@ -21165,7 +25094,7 @@
     </row>
     <row r="75" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D75" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E75" t="s">
         <v>714</v>
@@ -21235,7 +25164,7 @@
     </row>
     <row r="76" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D76" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E76" t="s">
         <v>715</v>
@@ -21305,10 +25234,10 @@
     </row>
     <row r="77" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D77" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E77" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="F77" t="str">
         <f t="shared" si="21"/>
@@ -21375,10 +25304,10 @@
     </row>
     <row r="78" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D78" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E78" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F78" t="str">
         <f t="shared" si="21"/>
@@ -21445,7 +25374,7 @@
     </row>
     <row r="79" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D79" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E79" t="s">
         <v>716</v>
@@ -21515,7 +25444,7 @@
     </row>
     <row r="80" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D80" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E80" t="s">
         <v>717</v>
@@ -21585,7 +25514,7 @@
     </row>
     <row r="81" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D81" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E81" t="s">
         <v>718</v>
@@ -21655,7 +25584,7 @@
     </row>
     <row r="82" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D82" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E82" t="s">
         <v>719</v>
@@ -21725,7 +25654,7 @@
     </row>
     <row r="83" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D83" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E83" t="s">
         <v>720</v>
@@ -21795,7 +25724,7 @@
     </row>
     <row r="84" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D84" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E84" t="s">
         <v>721</v>
@@ -21865,7 +25794,7 @@
     </row>
     <row r="85" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D85" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E85" t="s">
         <v>722</v>
@@ -21935,7 +25864,7 @@
     </row>
     <row r="86" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D86" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E86" t="s">
         <v>726</v>
@@ -22005,7 +25934,7 @@
     </row>
     <row r="87" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D87" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E87" t="s">
         <v>727</v>
@@ -22075,7 +26004,7 @@
     </row>
     <row r="88" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D88" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E88" t="s">
         <v>728</v>
@@ -22145,7 +26074,7 @@
     </row>
     <row r="89" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D89" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E89" t="s">
         <v>723</v>
@@ -22215,7 +26144,7 @@
     </row>
     <row r="90" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D90" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E90" t="s">
         <v>724</v>
@@ -22285,7 +26214,7 @@
     </row>
     <row r="91" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D91" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E91" t="s">
         <v>725</v>
@@ -22351,16 +26280,16 @@
     </row>
     <row r="92" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D92" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E92" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
       <c r="F92" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
       <c r="G92" t="s">
-        <v>958</v>
+        <v>953</v>
       </c>
       <c r="I92" t="s">
         <v>572</v>

--- a/Inputs/BD.xlsx
+++ b/Inputs/BD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/078e1a455e5c02ce/Documentos/GitHub/Proyecto_PIPC/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2097" documentId="13_ncr:1_{7D3A426E-EC5E-453A-8CC7-F83B71F24F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D11FA5CC-0D81-47A0-ADC8-AC915EA1CB9D}"/>
+  <xr:revisionPtr revIDLastSave="2113" documentId="13_ncr:1_{7D3A426E-EC5E-453A-8CC7-F83B71F24F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B393A461-F338-4306-9288-2FEA4679A352}"/>
   <bookViews>
-    <workbookView xWindow="9972" yWindow="0" windowWidth="13056" windowHeight="8880" xr2:uid="{3F095A75-F066-4695-8672-8D4315F1EF23}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3F095A75-F066-4695-8672-8D4315F1EF23}"/>
   </bookViews>
   <sheets>
     <sheet name="BD" sheetId="1" r:id="rId1"/>
@@ -5668,9 +5668,6 @@
     <t>LAURA LILIANA CASTELLANOS MEDINA</t>
   </si>
   <si>
-    <t>CR 5020 PUEBLA SAN MANUEL</t>
-  </si>
-  <si>
     <t>CR 1521 PLAZA ARCANGELES</t>
   </si>
   <si>
@@ -5729,6 +5726,9 @@
   </si>
   <si>
     <t>FRENTE A TELEVISORA “IMAGEN TELEVISIÓN”</t>
+  </si>
+  <si>
+    <t>CR 520 PUEBLA SAN MANUEL</t>
   </si>
 </sst>
 </file>
@@ -6382,7 +6382,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="26" fmlaLink="$A$1" max="30000" min="1" page="10" val="13"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="26" fmlaLink="$A$1" max="30000" min="1" page="10" val="28"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6766,7 +6766,7 @@
   <sheetData>
     <row r="1" spans="1:281" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:281" x14ac:dyDescent="0.3">
@@ -7587,31 +7587,31 @@
         <v>646</v>
       </c>
       <c r="JM2" t="s">
+        <v>1715</v>
+      </c>
+      <c r="JN2" t="s">
         <v>1716</v>
       </c>
-      <c r="JN2" t="s">
+      <c r="JO2" t="s">
         <v>1717</v>
       </c>
-      <c r="JO2" t="s">
+      <c r="JP2" t="s">
         <v>1718</v>
       </c>
-      <c r="JP2" t="s">
+      <c r="JQ2" t="s">
         <v>1719</v>
       </c>
-      <c r="JQ2" t="s">
+      <c r="JR2" t="s">
         <v>1720</v>
       </c>
-      <c r="JR2" t="s">
+      <c r="JS2" t="s">
         <v>1721</v>
       </c>
-      <c r="JS2" t="s">
+      <c r="JT2" t="s">
         <v>1722</v>
       </c>
-      <c r="JT2" t="s">
+      <c r="JU2" t="s">
         <v>1723</v>
-      </c>
-      <c r="JU2" t="s">
-        <v>1724</v>
       </c>
     </row>
     <row r="3" spans="1:281" x14ac:dyDescent="0.3">
@@ -11438,7 +11438,7 @@
         <v>72000</v>
       </c>
       <c r="P15" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="V15">
         <v>832.26</v>
@@ -11605,19 +11605,19 @@
         <v>1343</v>
       </c>
       <c r="CZ15" t="s">
+        <v>1725</v>
+      </c>
+      <c r="DA15" t="s">
         <v>1726</v>
       </c>
-      <c r="DA15" t="s">
+      <c r="DB15" t="s">
         <v>1727</v>
-      </c>
-      <c r="DB15" t="s">
-        <v>1728</v>
       </c>
       <c r="DC15" t="s">
         <v>440</v>
       </c>
       <c r="DD15" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="DE15" t="s">
         <v>442</v>
@@ -18972,7 +18972,7 @@
         <v>948</v>
       </c>
       <c r="D30" t="s">
-        <v>1709</v>
+        <v>1729</v>
       </c>
       <c r="E30" t="s">
         <v>845</v>
@@ -24475,7 +24475,7 @@
         <v>948</v>
       </c>
       <c r="D41" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="E41" t="s">
         <v>845</v>
@@ -24487,13 +24487,13 @@
         <v>847</v>
       </c>
       <c r="I41" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="J41">
         <v>6510</v>
       </c>
       <c r="L41" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="M41" t="s">
         <v>1495</v>
@@ -24666,7 +24666,7 @@
         <v>2024</v>
       </c>
       <c r="CY41" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="DE41" t="s">
         <v>442</v>
@@ -24985,7 +24985,7 @@
         <v>847</v>
       </c>
       <c r="I42" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="J42">
         <v>101</v>
@@ -25104,7 +25104,7 @@
         <v>2024</v>
       </c>
       <c r="CY42" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="DE42" t="s">
         <v>442</v>
@@ -30910,7 +30910,7 @@
     <row r="1" spans="1:248" x14ac:dyDescent="0.3">
       <c r="A1">
         <f>+BD!A1</f>
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s">
         <v>134</v>
@@ -31665,7 +31665,7 @@
       </c>
       <c r="D2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,4, FALSE)</f>
-        <v>CR 511 PUEBLA JUAREZ</v>
+        <v>CR 520 PUEBLA SAN MANUEL</v>
       </c>
       <c r="E2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,5, FALSE)</f>
@@ -31685,19 +31685,19 @@
       </c>
       <c r="I2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,9, FALSE)</f>
-        <v xml:space="preserve"> AV. JUAREZ</v>
+        <v>DIAGONAL ZARAGOZA</v>
       </c>
       <c r="J2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,10, FALSE)</f>
-        <v>1506</v>
-      </c>
-      <c r="K2">
+        <v>5128</v>
+      </c>
+      <c r="K2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,11, FALSE)</f>
-        <v>0</v>
+        <v>A</v>
       </c>
       <c r="L2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,12, FALSE)</f>
-        <v>CENTRO</v>
+        <v>JARDINES DE SAN MANUEL</v>
       </c>
       <c r="M2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,13, FALSE)</f>
@@ -31709,15 +31709,15 @@
       </c>
       <c r="O2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,15, FALSE)</f>
-        <v>72000</v>
-      </c>
-      <c r="P2" t="str">
+        <v>72570</v>
+      </c>
+      <c r="P2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,16, FALSE)</f>
-        <v>222 232 08 09</v>
-      </c>
-      <c r="Q2">
+        <v>2216671314</v>
+      </c>
+      <c r="Q2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,17, FALSE)</f>
-        <v>0</v>
+        <v>josecasiano.garcia@bbva.xom</v>
       </c>
       <c r="R2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,18, FALSE)</f>
@@ -31737,11 +31737,11 @@
       </c>
       <c r="V2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,22, FALSE)</f>
-        <v>832.26</v>
+        <v>0</v>
       </c>
       <c r="W2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,23, FALSE)</f>
-        <v>832.26</v>
+        <v>0</v>
       </c>
       <c r="X2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,24, FALSE)</f>
@@ -31769,7 +31769,7 @@
       </c>
       <c r="AD2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,30, FALSE)</f>
-        <v>10 CAJONES</v>
+        <v>5 CAJONES</v>
       </c>
       <c r="AE2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,31, FALSE)</f>
@@ -31777,11 +31777,11 @@
       </c>
       <c r="AF2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,32, FALSE)</f>
-        <v>MARIO ROJAS JURADO</v>
+        <v>NATALIA E. MARTINEZ ROJAS</v>
       </c>
       <c r="AG2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,33, FALSE)</f>
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AH2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,34, FALSE)</f>
@@ -31789,11 +31789,11 @@
       </c>
       <c r="AI2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,35, FALSE)</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AJ2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,36, FALSE)</f>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AK2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,37, FALSE)</f>
@@ -31809,11 +31809,11 @@
       </c>
       <c r="AN2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,40, FALSE)</f>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AO2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,41, FALSE)</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AP2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,42, FALSE)</f>
@@ -31825,11 +31825,11 @@
       </c>
       <c r="AR2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,44, FALSE)</f>
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AS2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,45, FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,46, FALSE)</f>
@@ -31837,7 +31837,7 @@
       </c>
       <c r="AU2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,47, FALSE)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,48, FALSE)</f>
@@ -31849,7 +31849,7 @@
       </c>
       <c r="AX2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,50, FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,51, FALSE)</f>
@@ -31877,7 +31877,7 @@
       </c>
       <c r="BE2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,57, FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BF2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,58, FALSE)</f>
@@ -31889,7 +31889,7 @@
       </c>
       <c r="BH2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,60, FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BI2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,61, FALSE)</f>
@@ -31897,7 +31897,7 @@
       </c>
       <c r="BJ2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,62, FALSE)</f>
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="BK2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,63, FALSE)</f>
@@ -31905,7 +31905,7 @@
       </c>
       <c r="BL2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,64, FALSE)</f>
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="BM2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,65, FALSE)</f>
@@ -31921,11 +31921,11 @@
       </c>
       <c r="BP2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,68, FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,69, FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BR2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,70, FALSE)</f>
@@ -31933,11 +31933,11 @@
       </c>
       <c r="BS2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,71, FALSE)</f>
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="BT2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,72, FALSE)</f>
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="BU2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,73, FALSE)</f>
@@ -31961,7 +31961,7 @@
       </c>
       <c r="BZ2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,78, FALSE)</f>
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="CA2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,79, FALSE)</f>
@@ -32049,7 +32049,7 @@
       </c>
       <c r="CV2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,100, FALSE)</f>
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="CW2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,101, FALSE)</f>
@@ -32061,27 +32061,27 @@
       </c>
       <c r="CY2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,103, FALSE)</f>
-        <v>19.047920704202305, -98.21059731923174</v>
-      </c>
-      <c r="CZ2" t="str">
+        <v>19.01635199500545, -98.19894850064507</v>
+      </c>
+      <c r="CZ2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,104, FALSE)</f>
-        <v>AVENIDA 5 PONIENTE</v>
-      </c>
-      <c r="DA2" t="str">
+        <v>0</v>
+      </c>
+      <c r="DA2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,105, FALSE)</f>
-        <v>AVENIDA JUÁREZ</v>
-      </c>
-      <c r="DB2" t="str">
+        <v>0</v>
+      </c>
+      <c r="DB2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,106, FALSE)</f>
-        <v>CALE 15 SUR</v>
-      </c>
-      <c r="DC2" t="str">
+        <v>0</v>
+      </c>
+      <c r="DC2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,107, FALSE)</f>
-        <v>LOCALES COMERCIALES</v>
-      </c>
-      <c r="DD2" t="str">
+        <v>0</v>
+      </c>
+      <c r="DD2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,108, FALSE)</f>
-        <v>FRENTE A TELEVISORA “IMAGEN TELEVISIÓN”</v>
+        <v>0</v>
       </c>
       <c r="DE2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,109, FALSE)</f>
@@ -32091,113 +32091,113 @@
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,110, FALSE)</f>
         <v>Reglamento de la Ley del Sistema Estatal de Protección Civil para el Estado Libre y Soberano de Puebla, publicado el 1 de julio de 1998.</v>
       </c>
-      <c r="DG2" t="str">
+      <c r="DG2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,111, FALSE)</f>
-        <v>MB09216</v>
+        <v>0</v>
       </c>
       <c r="DH2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,112, FALSE)</f>
-        <v>ROSARIO GONZALEZ VALLARTE</v>
+        <v>JOSE CACIANO GARCIA SANTIAGO</v>
       </c>
       <c r="DI2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,113, FALSE)</f>
-        <v>MI5545</v>
+        <v>MB77651</v>
       </c>
       <c r="DJ2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,114, FALSE)</f>
-        <v>DIEGO HERNANDEZ CARMONA</v>
+        <v>MIRIAM CORAL ZAYAGO MOJICA</v>
       </c>
       <c r="DK2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,115, FALSE)</f>
-        <v>ASESOR DIGITAL</v>
+        <v>BANQUERO POOL</v>
       </c>
       <c r="DL2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,116, FALSE)</f>
-        <v>MI28409</v>
+        <v>MB77868</v>
       </c>
       <c r="DM2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,117, FALSE)</f>
-        <v>PAOLA CUAUTLE AGUILAR</v>
+        <v>VICTORIA ALEJANDRA HERNANDEZ SOLIS</v>
       </c>
       <c r="DN2" s="5" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,118, FALSE)</f>
-        <v>CAJERO UNIVERSAL B</v>
+        <v>ASESOR DIGITAL</v>
       </c>
       <c r="DO2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,119, FALSE)</f>
-        <v>MB87913</v>
+        <v>MI22403</v>
       </c>
       <c r="DP2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,120, FALSE)</f>
-        <v>FERNANDO HERNANDEZ MARTINEZ</v>
+        <v>EDUARDO ARTURO ORTEGA QUINTERO</v>
       </c>
       <c r="DQ2" s="5" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,121, FALSE)</f>
-        <v>CAJERO UNIVERSAL B</v>
+        <v>ASESOR DIGITAL</v>
       </c>
       <c r="DR2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,122, FALSE)</f>
-        <v>M903801</v>
+        <v>MI23928</v>
       </c>
       <c r="DS2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,123, FALSE)</f>
-        <v>RAFAEL UGARTE OLIVER</v>
+        <v>MIGUEL ANGEL FONSECA GUTIERREZ</v>
       </c>
       <c r="DT2" s="5" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,124, FALSE)</f>
-        <v>CAJERO UNIVERSAL B</v>
+        <v>BANQUERO POOL</v>
       </c>
       <c r="DU2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,125, FALSE)</f>
-        <v>MB54486</v>
+        <v>MI10709</v>
       </c>
       <c r="DV2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,126, FALSE)</f>
-        <v>MARIA ANGELICA BALCAZAR ROMERO</v>
+        <v>GLADYS PEREZ SALAZAR</v>
       </c>
       <c r="DW2" s="5" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,127, FALSE)</f>
-        <v>BANQUERO JR</v>
+        <v>JEFE DE CAJA</v>
       </c>
       <c r="DX2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,128, FALSE)</f>
-        <v>MB44681</v>
+        <v>M821641</v>
       </c>
       <c r="DY2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,129, FALSE)</f>
-        <v>MARIA DE LOS ANGELES LARA MORALES</v>
+        <v>ANA LAURA FLORES SERRANO</v>
       </c>
       <c r="DZ2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,130, FALSE)</f>
-        <v>BANQUERO</v>
+        <v>CAJERO UNIVERSAL B</v>
       </c>
       <c r="EA2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,131, FALSE)</f>
-        <v>MB90635</v>
+        <v>M841691</v>
       </c>
       <c r="EB2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,132, FALSE)</f>
-        <v>JUDITH CHICO SARTILLO</v>
+        <v>VICTOR CONCEPCION SUAREZ FLORES</v>
       </c>
       <c r="EC2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,133, FALSE)</f>
-        <v>ASESOR DIGITAL</v>
+        <v>CAJERO UNIVERSAL B</v>
       </c>
       <c r="ED2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,134, FALSE)</f>
-        <v>MI17688</v>
-      </c>
-      <c r="EE2" t="str">
+        <v>MB95251</v>
+      </c>
+      <c r="EE2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,135, FALSE)</f>
-        <v>HECTOR ELIAS COYOTL SANCHEZ</v>
-      </c>
-      <c r="EF2" t="str">
+        <v>0</v>
+      </c>
+      <c r="EF2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,136, FALSE)</f>
-        <v>ASESOR DIGITAL</v>
-      </c>
-      <c r="EG2" t="str">
+        <v>0</v>
+      </c>
+      <c r="EG2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,137, FALSE)</f>
-        <v>MI21700</v>
+        <v>0</v>
       </c>
       <c r="EH2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,138, FALSE)</f>
@@ -32241,39 +32241,39 @@
       </c>
       <c r="ER2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,148, FALSE)</f>
-        <v>960</v>
+        <v>0</v>
       </c>
       <c r="ES2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,149, FALSE)</f>
-        <v>6.4000000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="ET2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,150, FALSE)</f>
         <v>ORDINARIO</v>
       </c>
-      <c r="EU2" t="str">
+      <c r="EU2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,151, FALSE)</f>
-        <v>MARTHA PATRICIA SALGADO FLORES</v>
-      </c>
-      <c r="EV2" t="str">
+        <v>0</v>
+      </c>
+      <c r="EV2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,152, FALSE)</f>
-        <v>CAJERO UNIVERSAL B</v>
-      </c>
-      <c r="EW2" t="str">
+        <v>0</v>
+      </c>
+      <c r="EW2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,153, FALSE)</f>
-        <v>MB97571</v>
-      </c>
-      <c r="EX2" t="str">
+        <v>0</v>
+      </c>
+      <c r="EX2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,154, FALSE)</f>
-        <v>MONICA VIDAL HERANANDEZ</v>
-      </c>
-      <c r="EY2" t="str">
+        <v>0</v>
+      </c>
+      <c r="EY2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,155, FALSE)</f>
-        <v>CAJERO UNIVERSAL</v>
-      </c>
-      <c r="EZ2" t="str">
+        <v>0</v>
+      </c>
+      <c r="EZ2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,156, FALSE)</f>
-        <v>MB47232</v>
+        <v>0</v>
       </c>
       <c r="FA2" t="s">
         <v>81</v>

--- a/Inputs/BD.xlsx
+++ b/Inputs/BD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/078e1a455e5c02ce/Documentos/GitHub/Proyecto_PIPC/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2113" documentId="13_ncr:1_{7D3A426E-EC5E-453A-8CC7-F83B71F24F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B393A461-F338-4306-9288-2FEA4679A352}"/>
+  <xr:revisionPtr revIDLastSave="2647" documentId="13_ncr:1_{7D3A426E-EC5E-453A-8CC7-F83B71F24F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49319CD6-1B47-4B95-9381-CCE56D53938A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3F095A75-F066-4695-8672-8D4315F1EF23}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{3F095A75-F066-4695-8672-8D4315F1EF23}"/>
   </bookViews>
   <sheets>
     <sheet name="BD" sheetId="1" r:id="rId1"/>
@@ -539,7 +539,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5519" uniqueCount="1730">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5524" uniqueCount="1735">
   <si>
     <t>dia</t>
   </si>
@@ -5729,6 +5729,21 @@
   </si>
   <si>
     <t>CR 520 PUEBLA SAN MANUEL</t>
+  </si>
+  <si>
+    <t>registro_perito</t>
+  </si>
+  <si>
+    <t>no_registro</t>
+  </si>
+  <si>
+    <t>NÚMERO DE REGISTRO</t>
+  </si>
+  <si>
+    <t>DMPC/018/2024</t>
+  </si>
+  <si>
+    <t>28 DE SEPTIEMBRE DE 2021</t>
   </si>
 </sst>
 </file>
@@ -6382,7 +6397,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="26" fmlaLink="$A$1" max="30000" min="1" page="10" val="28"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="26" fmlaLink="$A$1" max="30000" min="1" page="10" val="38"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6766,7 +6781,7 @@
   <sheetData>
     <row r="1" spans="1:281" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:281" x14ac:dyDescent="0.3">
@@ -6828,10 +6843,10 @@
         <v>151</v>
       </c>
       <c r="T2" t="s">
-        <v>152</v>
+        <v>1730</v>
       </c>
       <c r="U2" t="s">
-        <v>153</v>
+        <v>1731</v>
       </c>
       <c r="V2" t="s">
         <v>154</v>
@@ -24009,6 +24024,24 @@
       </c>
       <c r="Q40" s="3" t="s">
         <v>1586</v>
+      </c>
+      <c r="R40">
+        <v>3</v>
+      </c>
+      <c r="S40" t="s">
+        <v>1734</v>
+      </c>
+      <c r="T40" t="s">
+        <v>1732</v>
+      </c>
+      <c r="U40" t="s">
+        <v>1733</v>
+      </c>
+      <c r="V40">
+        <v>300</v>
+      </c>
+      <c r="W40">
+        <v>300</v>
       </c>
       <c r="X40">
         <v>1</v>
@@ -30910,7 +30943,7 @@
     <row r="1" spans="1:248" x14ac:dyDescent="0.3">
       <c r="A1">
         <f>+BD!A1</f>
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s">
         <v>134</v>
@@ -30967,10 +31000,10 @@
         <v>151</v>
       </c>
       <c r="T1" t="s">
-        <v>152</v>
+        <v>1730</v>
       </c>
       <c r="U1" t="s">
-        <v>153</v>
+        <v>1731</v>
       </c>
       <c r="V1" t="s">
         <v>154</v>
@@ -31665,7 +31698,7 @@
       </c>
       <c r="D2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,4, FALSE)</f>
-        <v>CR 520 PUEBLA SAN MANUEL</v>
+        <v>CR 1888 PLAZA KENTRO SAN ANDRES CHOLULA</v>
       </c>
       <c r="E2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,5, FALSE)</f>
@@ -31685,23 +31718,23 @@
       </c>
       <c r="I2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,9, FALSE)</f>
-        <v>DIAGONAL ZARAGOZA</v>
+        <v>BOULEVARD ATLIXCAYOTL</v>
       </c>
       <c r="J2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,10, FALSE)</f>
-        <v>5128</v>
+        <v>3432</v>
       </c>
       <c r="K2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,11, FALSE)</f>
-        <v>A</v>
+        <v>LOCAL 18, 19, 20, 21</v>
       </c>
       <c r="L2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,12, FALSE)</f>
-        <v>JARDINES DE SAN MANUEL</v>
+        <v>RESERVA TERRITORIAL ATLIXCAYOTL</v>
       </c>
       <c r="M2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,13, FALSE)</f>
-        <v>PUEBLA</v>
+        <v>SAN ANDRES CHOLULA</v>
       </c>
       <c r="N2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,14, FALSE)</f>
@@ -31709,39 +31742,39 @@
       </c>
       <c r="O2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,15, FALSE)</f>
-        <v>72570</v>
+        <v>72825</v>
       </c>
       <c r="P2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,16, FALSE)</f>
-        <v>2216671314</v>
+        <v>2226894860</v>
       </c>
       <c r="Q2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,17, FALSE)</f>
-        <v>josecasiano.garcia@bbva.xom</v>
+        <v>mariamercedes.ramirez@bbva.com</v>
       </c>
       <c r="R2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,18, FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="S2">
+        <v>3</v>
+      </c>
+      <c r="S2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,19, FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="T2">
+        <v>28 DE SEPTIEMBRE DE 2021</v>
+      </c>
+      <c r="T2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,20, FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="U2">
+        <v>NÚMERO DE REGISTRO</v>
+      </c>
+      <c r="U2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,21, FALSE)</f>
-        <v>0</v>
+        <v>DMPC/018/2024</v>
       </c>
       <c r="V2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,22, FALSE)</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="W2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,23, FALSE)</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="X2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,24, FALSE)</f>
@@ -31769,7 +31802,7 @@
       </c>
       <c r="AD2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,30, FALSE)</f>
-        <v>5 CAJONES</v>
+        <v>10 CAJONES</v>
       </c>
       <c r="AE2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,31, FALSE)</f>
@@ -31777,7 +31810,7 @@
       </c>
       <c r="AF2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,32, FALSE)</f>
-        <v>NATALIA E. MARTINEZ ROJAS</v>
+        <v>NANCY KAREN CASCO GONZALEZ</v>
       </c>
       <c r="AG2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,33, FALSE)</f>
@@ -31789,11 +31822,11 @@
       </c>
       <c r="AI2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,35, FALSE)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AJ2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,36, FALSE)</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AK2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,37, FALSE)</f>
@@ -31825,11 +31858,11 @@
       </c>
       <c r="AR2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,44, FALSE)</f>
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AS2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,45, FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AT2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,46, FALSE)</f>
@@ -31837,7 +31870,7 @@
       </c>
       <c r="AU2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,47, FALSE)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,48, FALSE)</f>
@@ -31849,7 +31882,7 @@
       </c>
       <c r="AX2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,50, FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,51, FALSE)</f>
@@ -31877,7 +31910,7 @@
       </c>
       <c r="BE2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,57, FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BF2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,58, FALSE)</f>
@@ -31889,7 +31922,7 @@
       </c>
       <c r="BH2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,60, FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BI2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,61, FALSE)</f>
@@ -31897,7 +31930,7 @@
       </c>
       <c r="BJ2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,62, FALSE)</f>
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="BK2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,63, FALSE)</f>
@@ -31905,7 +31938,7 @@
       </c>
       <c r="BL2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,64, FALSE)</f>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BM2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,65, FALSE)</f>
@@ -31913,11 +31946,11 @@
       </c>
       <c r="BN2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,66, FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BO2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,67, FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,68, FALSE)</f>
@@ -31925,11 +31958,11 @@
       </c>
       <c r="BQ2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,69, FALSE)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BR2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,70, FALSE)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BS2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,71, FALSE)</f>
@@ -31961,7 +31994,7 @@
       </c>
       <c r="BZ2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,78, FALSE)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="CA2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,79, FALSE)</f>
@@ -32049,7 +32082,7 @@
       </c>
       <c r="CV2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,100, FALSE)</f>
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="CW2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,101, FALSE)</f>
@@ -32061,7 +32094,7 @@
       </c>
       <c r="CY2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,103, FALSE)</f>
-        <v>19.01635199500545, -98.19894850064507</v>
+        <v>19.016349983466032, -98.25408282595988</v>
       </c>
       <c r="CZ2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,104, FALSE)</f>
@@ -32091,113 +32124,113 @@
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,110, FALSE)</f>
         <v>Reglamento de la Ley del Sistema Estatal de Protección Civil para el Estado Libre y Soberano de Puebla, publicado el 1 de julio de 1998.</v>
       </c>
-      <c r="DG2">
+      <c r="DG2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,111, FALSE)</f>
-        <v>0</v>
+        <v>MB67587</v>
       </c>
       <c r="DH2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,112, FALSE)</f>
-        <v>JOSE CACIANO GARCIA SANTIAGO</v>
+        <v>MARIA MERCEDES RAMIREZ H</v>
       </c>
       <c r="DI2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,113, FALSE)</f>
-        <v>MB77651</v>
+        <v>MB56662</v>
       </c>
       <c r="DJ2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,114, FALSE)</f>
-        <v>MIRIAM CORAL ZAYAGO MOJICA</v>
+        <v>JAZMIN VALENCIA DE LA CRUZ</v>
       </c>
       <c r="DK2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,115, FALSE)</f>
-        <v>BANQUERO POOL</v>
+        <v>ASESOR DIGITAL</v>
       </c>
       <c r="DL2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,116, FALSE)</f>
-        <v>MB77868</v>
+        <v>MI20213</v>
       </c>
       <c r="DM2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,117, FALSE)</f>
-        <v>VICTORIA ALEJANDRA HERNANDEZ SOLIS</v>
+        <v>JULIO GABRIEL CORTES CABRERA</v>
       </c>
       <c r="DN2" s="5" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,118, FALSE)</f>
-        <v>ASESOR DIGITAL</v>
+        <v>BANQUERO JR</v>
       </c>
       <c r="DO2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,119, FALSE)</f>
-        <v>MI22403</v>
+        <v>MI05034</v>
       </c>
       <c r="DP2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,120, FALSE)</f>
-        <v>EDUARDO ARTURO ORTEGA QUINTERO</v>
+        <v>YUNIS FLORES ANGON</v>
       </c>
       <c r="DQ2" s="5" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,121, FALSE)</f>
-        <v>ASESOR DIGITAL</v>
+        <v>CAJERO UNIVERSAL B</v>
       </c>
       <c r="DR2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,122, FALSE)</f>
-        <v>MI23928</v>
+        <v>MB88363</v>
       </c>
       <c r="DS2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,123, FALSE)</f>
-        <v>MIGUEL ANGEL FONSECA GUTIERREZ</v>
+        <v>ABIGAIL VICTORIANO HERNANDEZ</v>
       </c>
       <c r="DT2" s="5" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,124, FALSE)</f>
-        <v>BANQUERO POOL</v>
+        <v>CAJERO UNIVERSAL B</v>
       </c>
       <c r="DU2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,125, FALSE)</f>
-        <v>MI10709</v>
+        <v>MB86803</v>
       </c>
       <c r="DV2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,126, FALSE)</f>
-        <v>GLADYS PEREZ SALAZAR</v>
+        <v>KATIA XIMENA CANO RODRIGUEZ</v>
       </c>
       <c r="DW2" s="5" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,127, FALSE)</f>
-        <v>JEFE DE CAJA</v>
+        <v>ASESOR DIGITAL</v>
       </c>
       <c r="DX2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,128, FALSE)</f>
-        <v>M821641</v>
+        <v>MI22288</v>
       </c>
       <c r="DY2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,129, FALSE)</f>
-        <v>ANA LAURA FLORES SERRANO</v>
+        <v>KATIA XIMENA CANO RODRIGUEZ</v>
       </c>
       <c r="DZ2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,130, FALSE)</f>
-        <v>CAJERO UNIVERSAL B</v>
+        <v>ASESOR DIGITAL</v>
       </c>
       <c r="EA2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,131, FALSE)</f>
-        <v>M841691</v>
+        <v>MI22288</v>
       </c>
       <c r="EB2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,132, FALSE)</f>
-        <v>VICTOR CONCEPCION SUAREZ FLORES</v>
+        <v>MARIA LETICIA GONZALEZ SANCHEZ</v>
       </c>
       <c r="EC2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,133, FALSE)</f>
-        <v>CAJERO UNIVERSAL B</v>
+        <v>CAJERO UNIVERSAL A</v>
       </c>
       <c r="ED2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,134, FALSE)</f>
-        <v>MB95251</v>
-      </c>
-      <c r="EE2">
+        <v>M813725</v>
+      </c>
+      <c r="EE2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,135, FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="EF2">
+        <v>DAMAYANTI RODRIGUEZ CORDOBA</v>
+      </c>
+      <c r="EF2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,136, FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="EG2">
+        <v>BANQUERO JR</v>
+      </c>
+      <c r="EG2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,137, FALSE)</f>
-        <v>0</v>
+        <v>MI22132</v>
       </c>
       <c r="EH2">
         <f>VLOOKUP($A$1,BD!$A$3:$HC$210,138, FALSE)</f>
@@ -32561,7 +32594,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4A8EE80-4440-4B18-8DA6-6D8F054BB32D}">
-  <dimension ref="C1:V179"/>
+  <dimension ref="C1:V181"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="3:22" x14ac:dyDescent="0.3">
@@ -39605,7 +39638,7 @@
         <v>332</v>
       </c>
       <c r="K143" t="str">
-        <f t="shared" ref="K143:K179" si="34">+_xlfn.CONCAT("'",I143,"' : r_val['",I143,"'],")</f>
+        <f t="shared" ref="K143:K181" si="34">+_xlfn.CONCAT("'",I143,"' : r_val['",I143,"'],")</f>
         <v>'descrip_lc' : r_val['descrip_lc'],</v>
       </c>
     </row>
@@ -40039,6 +40072,32 @@
       <c r="K179" t="str">
         <f t="shared" si="34"/>
         <v>'m10' : r_val['m10'],</v>
+      </c>
+    </row>
+    <row r="180" spans="9:11" x14ac:dyDescent="0.3">
+      <c r="I180" t="s">
+        <v>1730</v>
+      </c>
+      <c r="J180" t="str">
+        <f>+_xlfn.CONCAT("{{ ",I180," }}")</f>
+        <v>{{ registro_perito }}</v>
+      </c>
+      <c r="K180" t="str">
+        <f t="shared" si="34"/>
+        <v>'registro_perito' : r_val['registro_perito'],</v>
+      </c>
+    </row>
+    <row r="181" spans="9:11" x14ac:dyDescent="0.3">
+      <c r="I181" t="s">
+        <v>1731</v>
+      </c>
+      <c r="J181" t="str">
+        <f>+_xlfn.CONCAT("{{ ",I181," }}")</f>
+        <v>{{ no_registro }}</v>
+      </c>
+      <c r="K181" t="str">
+        <f t="shared" si="34"/>
+        <v>'no_registro' : r_val['no_registro'],</v>
       </c>
     </row>
   </sheetData>

--- a/Inputs/BD.xlsx
+++ b/Inputs/BD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/078e1a455e5c02ce/Documentos/GitHub/Proyecto_PIPC/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2746" documentId="13_ncr:1_{7D3A426E-EC5E-453A-8CC7-F83B71F24F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BFAA754-2C84-4DBC-B423-618D14D2972C}"/>
+  <xr:revisionPtr revIDLastSave="2861" documentId="13_ncr:1_{7D3A426E-EC5E-453A-8CC7-F83B71F24F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBE3CA1D-ADA2-4AD1-BDDC-5B0B8442EB46}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{3F095A75-F066-4695-8672-8D4315F1EF23}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{3F095A75-F066-4695-8672-8D4315F1EF23}"/>
   </bookViews>
   <sheets>
     <sheet name="BD" sheetId="1" r:id="rId1"/>
@@ -539,7 +539,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5576" uniqueCount="1759">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5674" uniqueCount="1761">
   <si>
     <t>dia</t>
   </si>
@@ -5812,21 +5812,16 @@
     <t>GRANIZADAS</t>
   </si>
   <si>
-    <t>•	Riesgo Geológico:
-De acuerdo con el tipo de fenómenos o agentes perturbadores. En el establecimiento comercial denominado BBVA CR 1888 PLAZA KENTRO, en algunos establecimientos estamos expuestos a los efectos de los sismos, por lo que se han definido como las zonas de menor riesgo interno los elementos de mayor   resistentes de la estructura, como muros de carga, columnas, trabes, estanterías siempre y cuando estén ancladas al piso y mostrador (TRIANGULO DE VIDA) y evitar la cercanía con elementos no estructurales como los vitrales y ventanas, que son objetos que no se encuentran fijos y son susceptibles a romperse. Sin embargo, la política es salir del inmueble durante un sismo, replegando a todas las personas en las zonas de seguridad.</t>
-  </si>
-  <si>
-    <t>•	Riesgo Hidrometeorológico:
-	Trabajos de desazolve y limpieza de ductos y cañerías.
-	Revisión del estado de tapas y registros de cisternas y de líneas hidráulicas, así como el estado en que se encuentran los tanques de almacenamiento de agua potable (tinacos, cisternas).
-•	Medidas Preventivas en caso de Agente Hidrometeorológico
-	Todo el personal deberá de realizar un simulacro cuando menos dos veces al año.
-	Contar con un plano de las principales líneas hidráulicas.
-	Verificar y mantener en buenas condiciones de funcionabilidad: llaves, válvulas, coladeras, alcantarillas y líneas de drenaje, así como, mantener despejada la azotea.
-	Designar zonas de seguridad en sitios seguros.
-	Revisar y mantener completo el material de primeros auxilios.
-	Seguir las indicaciones de las autoridades y prepararse para evacuar en caso necesario.
-	Cortar toda fuente de corriente eléctrica.</t>
+    <t>plano.png</t>
+  </si>
+  <si>
+    <t>width</t>
+  </si>
+  <si>
+    <t>height</t>
+  </si>
+  <si>
+    <t>layout.png</t>
   </si>
 </sst>
 </file>
@@ -5836,7 +5831,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5898,6 +5893,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -5938,7 +5940,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -5949,6 +5951,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -24498,12 +24501,6 @@
       <c r="DB40" t="s">
         <v>1756</v>
       </c>
-      <c r="DC40" t="s">
-        <v>1757</v>
-      </c>
-      <c r="DD40" t="s">
-        <v>1758</v>
-      </c>
       <c r="DG40">
         <v>28</v>
       </c>
@@ -33122,24 +33119,13 @@
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,106, FALSE)</f>
         <v>GRANIZADAS</v>
       </c>
-      <c r="DC2" t="str">
+      <c r="DC2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,107, FALSE)</f>
-        <v>•	Riesgo Geológico:
-De acuerdo con el tipo de fenómenos o agentes perturbadores. En el establecimiento comercial denominado BBVA CR 1888 PLAZA KENTRO, en algunos establecimientos estamos expuestos a los efectos de los sismos, por lo que se han definido como las zonas de menor riesgo interno los elementos de mayor   resistentes de la estructura, como muros de carga, columnas, trabes, estanterías siempre y cuando estén ancladas al piso y mostrador (TRIANGULO DE VIDA) y evitar la cercanía con elementos no estructurales como los vitrales y ventanas, que son objetos que no se encuentran fijos y son susceptibles a romperse. Sin embargo, la política es salir del inmueble durante un sismo, replegando a todas las personas en las zonas de seguridad.</v>
-      </c>
-      <c r="DD2" t="str">
+        <v>0</v>
+      </c>
+      <c r="DD2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,108, FALSE)</f>
-        <v>•	Riesgo Hidrometeorológico:
-	Trabajos de desazolve y limpieza de ductos y cañerías.
-	Revisión del estado de tapas y registros de cisternas y de líneas hidráulicas, así como el estado en que se encuentran los tanques de almacenamiento de agua potable (tinacos, cisternas).
-•	Medidas Preventivas en caso de Agente Hidrometeorológico
-	Todo el personal deberá de realizar un simulacro cuando menos dos veces al año.
-	Contar con un plano de las principales líneas hidráulicas.
-	Verificar y mantener en buenas condiciones de funcionabilidad: llaves, válvulas, coladeras, alcantarillas y líneas de drenaje, así como, mantener despejada la azotea.
-	Designar zonas de seguridad en sitios seguros.
-	Revisar y mantener completo el material de primeros auxilios.
-	Seguir las indicaciones de las autoridades y prepararse para evacuar en caso necesario.
-	Cortar toda fuente de corriente eléctrica.</v>
+        <v>0</v>
       </c>
       <c r="DE2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,109, FALSE)</f>
@@ -33482,7 +33468,7 @@
         <v>101</v>
       </c>
       <c r="GT2" t="s">
-        <v>102</v>
+        <v>1760</v>
       </c>
       <c r="GU2" t="s">
         <v>103</v>
@@ -33584,7 +33570,7 @@
         <v>601</v>
       </c>
       <c r="IB2" t="s">
-        <v>603</v>
+        <v>1757</v>
       </c>
       <c r="IC2" t="s">
         <v>606</v>
@@ -33671,10 +33657,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4A8EE80-4440-4B18-8DA6-6D8F054BB32D}">
-  <dimension ref="C1:V194"/>
+  <dimension ref="C1:W194"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="1" spans="3:23" x14ac:dyDescent="0.3">
       <c r="D1" t="s">
         <v>832</v>
       </c>
@@ -33690,59 +33676,59 @@
       <c r="H1">
         <v>145</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>135</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>224</v>
       </c>
-      <c r="K1" t="str">
-        <f t="shared" ref="K1:K46" si="0">+_xlfn.CONCAT("'",I1,"' : r_val['",I1,"'],")</f>
+      <c r="L1" t="str">
+        <f t="shared" ref="L1:L46" si="0">+_xlfn.CONCAT("'",J1,"' : r_val['",J1,"'],")</f>
         <v>'razon_social' : r_val['razon_social'],</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <f>+_xlfn.CONCAT("'",E1,"': ",E1,",")</f>
         <v>'logo1': logo1,</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>558</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <f>+_xlfn.CONCAT("img_path_",E1," = os.path.join(IMAGES_PATH, r_val['",E1,"'])")</f>
         <v>img_path_logo1 = os.path.join(IMAGES_PATH, r_val['logo1'])</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <f>+_xlfn.CONCAT("if os.path.exists(img_path_",E1,"):")</f>
         <v>if os.path.exists(img_path_logo1):</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <f>+_xlfn.CONCAT(E1," = InlineImage(docx_tpl, img_path_",E1,", height=Mm(",H1,"))")</f>
         <v>logo1 = InlineImage(docx_tpl, img_path_logo1, height=Mm(145))</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>560</v>
       </c>
-      <c r="R1" t="str">
+      <c r="S1" t="str">
         <f>+_xlfn.CONCAT("print(f'Advertencia: No se encontró la imagen {r_val['",E1,"']}')")</f>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['logo1']}')</v>
       </c>
-      <c r="S1" t="str">
+      <c r="T1" t="str">
         <f>+_xlfn.CONCAT(E1," = ''")</f>
         <v>logo1 = ''</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>559</v>
       </c>
-      <c r="U1" t="str">
+      <c r="V1" t="str">
         <f>+_xlfn.CONCAT("print(f'Advertencia: No se pudo cargar la imagen {r_val['",E1,"']}: {e}')")</f>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['logo1']}: {e}')</v>
       </c>
-      <c r="V1" t="str">
+      <c r="W1" t="str">
         <f>+_xlfn.CONCAT(E1," = ''")</f>
         <v>logo1 = ''</v>
       </c>
     </row>
-    <row r="2" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:23" x14ac:dyDescent="0.3">
       <c r="D2" t="s">
         <v>832</v>
       </c>
@@ -33758,59 +33744,59 @@
       <c r="H2">
         <v>15</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>136</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>225</v>
       </c>
-      <c r="K2" t="str">
+      <c r="L2" t="str">
         <f t="shared" si="0"/>
         <v>'nombre_comercial' : r_val['nombre_comercial'],</v>
       </c>
-      <c r="L2" t="str">
-        <f t="shared" ref="L2:L66" si="1">+_xlfn.CONCAT("'",E2,"': ",E2,",")</f>
+      <c r="M2" t="str">
+        <f t="shared" ref="M2:M66" si="1">+_xlfn.CONCAT("'",E2,"': ",E2,",")</f>
         <v>'logo2': logo2,</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>558</v>
       </c>
-      <c r="N2" t="str">
-        <f t="shared" ref="N2:N65" si="2">+_xlfn.CONCAT("img_path_",E2," = os.path.join(IMAGES_PATH, r_val['",E2,"'])")</f>
+      <c r="O2" t="str">
+        <f t="shared" ref="O2:O65" si="2">+_xlfn.CONCAT("img_path_",E2," = os.path.join(IMAGES_PATH, r_val['",E2,"'])")</f>
         <v>img_path_logo2 = os.path.join(IMAGES_PATH, r_val['logo2'])</v>
       </c>
-      <c r="O2" t="str">
-        <f t="shared" ref="O2:O65" si="3">+_xlfn.CONCAT("if os.path.exists(img_path_",E2,"):")</f>
+      <c r="P2" t="str">
+        <f t="shared" ref="P2:P65" si="3">+_xlfn.CONCAT("if os.path.exists(img_path_",E2,"):")</f>
         <v>if os.path.exists(img_path_logo2):</v>
       </c>
-      <c r="P2" t="str">
-        <f t="shared" ref="P2:P65" si="4">+_xlfn.CONCAT(E2," = InlineImage(docx_tpl, img_path_",E2,", height=Mm(",H2,"))")</f>
+      <c r="Q2" t="str">
+        <f t="shared" ref="Q2:Q65" si="4">+_xlfn.CONCAT(E2," = InlineImage(docx_tpl, img_path_",E2,", height=Mm(",H2,"))")</f>
         <v>logo2 = InlineImage(docx_tpl, img_path_logo2, height=Mm(15))</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>560</v>
       </c>
-      <c r="R2" t="str">
-        <f t="shared" ref="R2:R65" si="5">+_xlfn.CONCAT("print(f'Advertencia: No se encontró la imagen {r_val['",E2,"']}')")</f>
+      <c r="S2" t="str">
+        <f t="shared" ref="S2:S65" si="5">+_xlfn.CONCAT("print(f'Advertencia: No se encontró la imagen {r_val['",E2,"']}')")</f>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['logo2']}')</v>
       </c>
-      <c r="S2" t="str">
-        <f t="shared" ref="S2:S65" si="6">+_xlfn.CONCAT(E2," = ''")</f>
+      <c r="T2" t="str">
+        <f t="shared" ref="T2:T65" si="6">+_xlfn.CONCAT(E2," = ''")</f>
         <v>logo2 = ''</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>559</v>
       </c>
-      <c r="U2" t="str">
-        <f t="shared" ref="U2:U65" si="7">+_xlfn.CONCAT("print(f'Advertencia: No se pudo cargar la imagen {r_val['",E2,"']}: {e}')")</f>
+      <c r="V2" t="str">
+        <f t="shared" ref="V2:V65" si="7">+_xlfn.CONCAT("print(f'Advertencia: No se pudo cargar la imagen {r_val['",E2,"']}: {e}')")</f>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['logo2']}: {e}')</v>
       </c>
-      <c r="V2" t="str">
-        <f t="shared" ref="V2:V65" si="8">+_xlfn.CONCAT(E2," = ''")</f>
+      <c r="W2" t="str">
+        <f t="shared" ref="W2:W65" si="8">+_xlfn.CONCAT(E2," = ''")</f>
         <v>logo2 = ''</v>
       </c>
     </row>
-    <row r="3" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
         <v>843</v>
       </c>
@@ -33827,61 +33813,64 @@
         <v>342</v>
       </c>
       <c r="H3">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="I3" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J3" t="s">
         <v>137</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>226</v>
       </c>
-      <c r="K3" t="str">
+      <c r="L3" t="str">
         <f t="shared" si="0"/>
         <v>'rfc' : r_val['rfc'],</v>
       </c>
-      <c r="L3" t="str">
+      <c r="M3" t="str">
         <f t="shared" si="1"/>
         <v>'fachada': fachada,</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>558</v>
       </c>
-      <c r="N3" t="str">
+      <c r="O3" t="str">
         <f t="shared" si="2"/>
         <v>img_path_fachada = os.path.join(IMAGES_PATH, r_val['fachada'])</v>
       </c>
-      <c r="O3" t="str">
+      <c r="P3" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_fachada):</v>
       </c>
-      <c r="P3" t="str">
+      <c r="Q3" t="str">
         <f t="shared" si="4"/>
-        <v>fachada = InlineImage(docx_tpl, img_path_fachada, height=Mm(105))</v>
-      </c>
-      <c r="Q3" t="s">
+        <v>fachada = InlineImage(docx_tpl, img_path_fachada, height=Mm(90))</v>
+      </c>
+      <c r="R3" t="s">
         <v>560</v>
       </c>
-      <c r="R3" t="str">
+      <c r="S3" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['fachada']}')</v>
       </c>
-      <c r="S3" t="str">
+      <c r="T3" t="str">
         <f t="shared" si="6"/>
         <v>fachada = ''</v>
       </c>
-      <c r="T3" t="s">
+      <c r="U3" t="s">
         <v>559</v>
       </c>
-      <c r="U3" t="str">
+      <c r="V3" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['fachada']}: {e}')</v>
       </c>
-      <c r="V3" t="str">
+      <c r="W3" t="str">
         <f t="shared" si="8"/>
         <v>fachada = ''</v>
       </c>
     </row>
-    <row r="4" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
         <v>843</v>
       </c>
@@ -33898,61 +33887,67 @@
         <v>343</v>
       </c>
       <c r="H4">
-        <v>95</v>
+        <v>155</v>
       </c>
       <c r="I4" t="s">
+        <v>1758</v>
+      </c>
+      <c r="J4" t="s">
         <v>138</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>227</v>
       </c>
-      <c r="K4" t="str">
+      <c r="L4" t="str">
         <f t="shared" si="0"/>
         <v>'codigo_gasolinera' : r_val['codigo_gasolinera'],</v>
       </c>
-      <c r="L4" t="str">
+      <c r="M4" t="str">
         <f t="shared" si="1"/>
         <v>'mapa': mapa,</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>558</v>
       </c>
-      <c r="N4" t="str">
+      <c r="O4" t="str">
         <f t="shared" si="2"/>
         <v>img_path_mapa = os.path.join(IMAGES_PATH, r_val['mapa'])</v>
       </c>
-      <c r="O4" t="str">
+      <c r="P4" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_mapa):</v>
       </c>
-      <c r="P4" t="str">
+      <c r="Q4" t="str">
         <f t="shared" si="4"/>
-        <v>mapa = InlineImage(docx_tpl, img_path_mapa, height=Mm(95))</v>
-      </c>
-      <c r="Q4" t="s">
+        <v>mapa = InlineImage(docx_tpl, img_path_mapa, height=Mm(155))</v>
+      </c>
+      <c r="R4" t="s">
         <v>560</v>
       </c>
-      <c r="R4" t="str">
+      <c r="S4" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['mapa']}')</v>
       </c>
-      <c r="S4" t="str">
+      <c r="T4" t="str">
         <f t="shared" si="6"/>
         <v>mapa = ''</v>
       </c>
-      <c r="T4" t="s">
+      <c r="U4" t="s">
         <v>559</v>
       </c>
-      <c r="U4" t="str">
+      <c r="V4" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['mapa']}: {e}')</v>
       </c>
-      <c r="V4" t="str">
+      <c r="W4" t="str">
         <f t="shared" si="8"/>
         <v>mapa = ''</v>
       </c>
     </row>
-    <row r="5" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="C5" s="8" t="s">
+        <v>843</v>
+      </c>
       <c r="D5" t="s">
         <v>832</v>
       </c>
@@ -33966,61 +33961,64 @@
         <v>398</v>
       </c>
       <c r="H5">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I5" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J5" t="s">
         <v>139</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>228</v>
       </c>
-      <c r="K5" t="str">
+      <c r="L5" t="str">
         <f t="shared" si="0"/>
         <v>'giro_comercial' : r_val['giro_comercial'],</v>
       </c>
-      <c r="L5" t="str">
+      <c r="M5" t="str">
         <f t="shared" si="1"/>
         <v>'esc_emer': esc_emer,</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
         <v>558</v>
       </c>
-      <c r="N5" t="str">
+      <c r="O5" t="str">
         <f t="shared" si="2"/>
         <v>img_path_esc_emer = os.path.join(IMAGES_PATH, r_val['esc_emer'])</v>
       </c>
-      <c r="O5" t="str">
+      <c r="P5" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_esc_emer):</v>
       </c>
-      <c r="P5" t="str">
+      <c r="Q5" t="str">
         <f t="shared" si="4"/>
-        <v>esc_emer = InlineImage(docx_tpl, img_path_esc_emer, height=Mm(60))</v>
-      </c>
-      <c r="Q5" t="s">
+        <v>esc_emer = InlineImage(docx_tpl, img_path_esc_emer, height=Mm(50))</v>
+      </c>
+      <c r="R5" t="s">
         <v>560</v>
       </c>
-      <c r="R5" t="str">
+      <c r="S5" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['esc_emer']}')</v>
       </c>
-      <c r="S5" t="str">
+      <c r="T5" t="str">
         <f t="shared" si="6"/>
         <v>esc_emer = ''</v>
       </c>
-      <c r="T5" t="s">
+      <c r="U5" t="s">
         <v>559</v>
       </c>
-      <c r="U5" t="str">
+      <c r="V5" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['esc_emer']}: {e}')</v>
       </c>
-      <c r="V5" t="str">
+      <c r="W5" t="str">
         <f t="shared" si="8"/>
         <v>esc_emer = ''</v>
       </c>
     </row>
-    <row r="6" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
         <v>843</v>
       </c>
@@ -34037,61 +34035,64 @@
         <v>344</v>
       </c>
       <c r="H6">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I6" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J6" t="s">
         <v>140</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>229</v>
       </c>
-      <c r="K6" t="str">
+      <c r="L6" t="str">
         <f t="shared" si="0"/>
         <v>'descripcion_actividades' : r_val['descripcion_actividades'],</v>
       </c>
-      <c r="L6" t="str">
+      <c r="M6" t="str">
         <f t="shared" si="1"/>
         <v>'mueble1': mueble1,</v>
       </c>
-      <c r="M6" t="s">
+      <c r="N6" t="s">
         <v>558</v>
       </c>
-      <c r="N6" t="str">
+      <c r="O6" t="str">
         <f t="shared" si="2"/>
         <v>img_path_mueble1 = os.path.join(IMAGES_PATH, r_val['mueble1'])</v>
       </c>
-      <c r="O6" t="str">
+      <c r="P6" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_mueble1):</v>
       </c>
-      <c r="P6" t="str">
+      <c r="Q6" t="str">
         <f t="shared" si="4"/>
-        <v>mueble1 = InlineImage(docx_tpl, img_path_mueble1, height=Mm(60))</v>
-      </c>
-      <c r="Q6" t="s">
+        <v>mueble1 = InlineImage(docx_tpl, img_path_mueble1, height=Mm(50))</v>
+      </c>
+      <c r="R6" t="s">
         <v>560</v>
       </c>
-      <c r="R6" t="str">
+      <c r="S6" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['mueble1']}')</v>
       </c>
-      <c r="S6" t="str">
+      <c r="T6" t="str">
         <f t="shared" si="6"/>
         <v>mueble1 = ''</v>
       </c>
-      <c r="T6" t="s">
+      <c r="U6" t="s">
         <v>559</v>
       </c>
-      <c r="U6" t="str">
+      <c r="V6" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['mueble1']}: {e}')</v>
       </c>
-      <c r="V6" t="str">
+      <c r="W6" t="str">
         <f t="shared" si="8"/>
         <v>mueble1 = ''</v>
       </c>
     </row>
-    <row r="7" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
         <v>843</v>
       </c>
@@ -34108,61 +34109,64 @@
         <v>345</v>
       </c>
       <c r="H7">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I7" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J7" t="s">
         <v>141</v>
       </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
         <v>230</v>
       </c>
-      <c r="K7" t="str">
+      <c r="L7" t="str">
         <f t="shared" si="0"/>
         <v>'calle' : r_val['calle'],</v>
       </c>
-      <c r="L7" t="str">
+      <c r="M7" t="str">
         <f t="shared" si="1"/>
         <v>'mueble2': mueble2,</v>
       </c>
-      <c r="M7" t="s">
+      <c r="N7" t="s">
         <v>558</v>
       </c>
-      <c r="N7" t="str">
+      <c r="O7" t="str">
         <f t="shared" si="2"/>
         <v>img_path_mueble2 = os.path.join(IMAGES_PATH, r_val['mueble2'])</v>
       </c>
-      <c r="O7" t="str">
+      <c r="P7" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_mueble2):</v>
       </c>
-      <c r="P7" t="str">
+      <c r="Q7" t="str">
         <f t="shared" si="4"/>
-        <v>mueble2 = InlineImage(docx_tpl, img_path_mueble2, height=Mm(60))</v>
-      </c>
-      <c r="Q7" t="s">
+        <v>mueble2 = InlineImage(docx_tpl, img_path_mueble2, height=Mm(50))</v>
+      </c>
+      <c r="R7" t="s">
         <v>560</v>
       </c>
-      <c r="R7" t="str">
+      <c r="S7" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['mueble2']}')</v>
       </c>
-      <c r="S7" t="str">
+      <c r="T7" t="str">
         <f t="shared" si="6"/>
         <v>mueble2 = ''</v>
       </c>
-      <c r="T7" t="s">
+      <c r="U7" t="s">
         <v>559</v>
       </c>
-      <c r="U7" t="str">
+      <c r="V7" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['mueble2']}: {e}')</v>
       </c>
-      <c r="V7" t="str">
+      <c r="W7" t="str">
         <f t="shared" si="8"/>
         <v>mueble2 = ''</v>
       </c>
     </row>
-    <row r="8" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:23" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
         <v>832</v>
       </c>
@@ -34176,61 +34180,64 @@
         <v>272</v>
       </c>
       <c r="H8">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I8" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J8" t="s">
         <v>142</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>231</v>
       </c>
-      <c r="K8" t="str">
+      <c r="L8" t="str">
         <f t="shared" si="0"/>
         <v>'no_exterior' : r_val['no_exterior'],</v>
       </c>
-      <c r="L8" t="str">
+      <c r="M8" t="str">
         <f t="shared" si="1"/>
         <v>'venteo': venteo,</v>
       </c>
-      <c r="M8" t="s">
+      <c r="N8" t="s">
         <v>558</v>
       </c>
-      <c r="N8" t="str">
+      <c r="O8" t="str">
         <f t="shared" si="2"/>
         <v>img_path_venteo = os.path.join(IMAGES_PATH, r_val['venteo'])</v>
       </c>
-      <c r="O8" t="str">
+      <c r="P8" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_venteo):</v>
       </c>
-      <c r="P8" t="str">
+      <c r="Q8" t="str">
         <f t="shared" si="4"/>
-        <v>venteo = InlineImage(docx_tpl, img_path_venteo, height=Mm(60))</v>
-      </c>
-      <c r="Q8" t="s">
+        <v>venteo = InlineImage(docx_tpl, img_path_venteo, height=Mm(50))</v>
+      </c>
+      <c r="R8" t="s">
         <v>560</v>
       </c>
-      <c r="R8" t="str">
+      <c r="S8" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['venteo']}')</v>
       </c>
-      <c r="S8" t="str">
+      <c r="T8" t="str">
         <f t="shared" si="6"/>
         <v>venteo = ''</v>
       </c>
-      <c r="T8" t="s">
+      <c r="U8" t="s">
         <v>559</v>
       </c>
-      <c r="U8" t="str">
+      <c r="V8" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['venteo']}: {e}')</v>
       </c>
-      <c r="V8" t="str">
+      <c r="W8" t="str">
         <f t="shared" si="8"/>
         <v>venteo = ''</v>
       </c>
     </row>
-    <row r="9" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="9" spans="3:23" x14ac:dyDescent="0.3">
       <c r="D9" t="s">
         <v>832</v>
       </c>
@@ -34244,61 +34251,64 @@
         <v>402</v>
       </c>
       <c r="H9">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I9" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J9" t="s">
         <v>143</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>232</v>
       </c>
-      <c r="K9" t="str">
+      <c r="L9" t="str">
         <f t="shared" si="0"/>
         <v>'no_interior' : r_val['no_interior'],</v>
       </c>
-      <c r="L9" t="str">
+      <c r="M9" t="str">
         <f t="shared" si="1"/>
         <v>'manguera': manguera,</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>558</v>
       </c>
-      <c r="N9" t="str">
+      <c r="O9" t="str">
         <f t="shared" si="2"/>
         <v>img_path_manguera = os.path.join(IMAGES_PATH, r_val['manguera'])</v>
       </c>
-      <c r="O9" t="str">
+      <c r="P9" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_manguera):</v>
       </c>
-      <c r="P9" t="str">
+      <c r="Q9" t="str">
         <f t="shared" si="4"/>
-        <v>manguera = InlineImage(docx_tpl, img_path_manguera, height=Mm(60))</v>
-      </c>
-      <c r="Q9" t="s">
+        <v>manguera = InlineImage(docx_tpl, img_path_manguera, height=Mm(50))</v>
+      </c>
+      <c r="R9" t="s">
         <v>560</v>
       </c>
-      <c r="R9" t="str">
+      <c r="S9" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['manguera']}')</v>
       </c>
-      <c r="S9" t="str">
+      <c r="T9" t="str">
         <f t="shared" si="6"/>
         <v>manguera = ''</v>
       </c>
-      <c r="T9" t="s">
+      <c r="U9" t="s">
         <v>559</v>
       </c>
-      <c r="U9" t="str">
+      <c r="V9" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['manguera']}: {e}')</v>
       </c>
-      <c r="V9" t="str">
+      <c r="W9" t="str">
         <f t="shared" si="8"/>
         <v>manguera = ''</v>
       </c>
     </row>
-    <row r="10" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
         <v>843</v>
       </c>
@@ -34315,61 +34325,64 @@
         <v>346</v>
       </c>
       <c r="H10">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I10" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J10" t="s">
         <v>144</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
         <v>233</v>
       </c>
-      <c r="K10" t="str">
+      <c r="L10" t="str">
         <f t="shared" si="0"/>
         <v>'colonia_barrio' : r_val['colonia_barrio'],</v>
       </c>
-      <c r="L10" t="str">
+      <c r="M10" t="str">
         <f t="shared" si="1"/>
         <v>'electrico': electrico,</v>
       </c>
-      <c r="M10" t="s">
+      <c r="N10" t="s">
         <v>558</v>
       </c>
-      <c r="N10" t="str">
+      <c r="O10" t="str">
         <f t="shared" si="2"/>
         <v>img_path_electrico = os.path.join(IMAGES_PATH, r_val['electrico'])</v>
       </c>
-      <c r="O10" t="str">
+      <c r="P10" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_electrico):</v>
       </c>
-      <c r="P10" t="str">
+      <c r="Q10" t="str">
         <f t="shared" si="4"/>
-        <v>electrico = InlineImage(docx_tpl, img_path_electrico, height=Mm(60))</v>
-      </c>
-      <c r="Q10" t="s">
+        <v>electrico = InlineImage(docx_tpl, img_path_electrico, height=Mm(50))</v>
+      </c>
+      <c r="R10" t="s">
         <v>560</v>
       </c>
-      <c r="R10" t="str">
+      <c r="S10" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['electrico']}')</v>
       </c>
-      <c r="S10" t="str">
+      <c r="T10" t="str">
         <f t="shared" si="6"/>
         <v>electrico = ''</v>
       </c>
-      <c r="T10" t="s">
+      <c r="U10" t="s">
         <v>559</v>
       </c>
-      <c r="U10" t="str">
+      <c r="V10" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['electrico']}: {e}')</v>
       </c>
-      <c r="V10" t="str">
+      <c r="W10" t="str">
         <f t="shared" si="8"/>
         <v>electrico = ''</v>
       </c>
     </row>
-    <row r="11" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
         <v>843</v>
       </c>
@@ -34386,61 +34399,64 @@
         <v>347</v>
       </c>
       <c r="H11">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I11" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J11" t="s">
         <v>145</v>
       </c>
-      <c r="J11" t="s">
+      <c r="K11" t="s">
         <v>234</v>
       </c>
-      <c r="K11" t="str">
+      <c r="L11" t="str">
         <f t="shared" si="0"/>
         <v>'municipio' : r_val['municipio'],</v>
       </c>
-      <c r="L11" t="str">
+      <c r="M11" t="str">
         <f t="shared" si="1"/>
         <v>'banio': banio,</v>
       </c>
-      <c r="M11" t="s">
+      <c r="N11" t="s">
         <v>558</v>
       </c>
-      <c r="N11" t="str">
+      <c r="O11" t="str">
         <f t="shared" si="2"/>
         <v>img_path_banio = os.path.join(IMAGES_PATH, r_val['banio'])</v>
       </c>
-      <c r="O11" t="str">
+      <c r="P11" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_banio):</v>
       </c>
-      <c r="P11" t="str">
+      <c r="Q11" t="str">
         <f t="shared" si="4"/>
-        <v>banio = InlineImage(docx_tpl, img_path_banio, height=Mm(60))</v>
-      </c>
-      <c r="Q11" t="s">
+        <v>banio = InlineImage(docx_tpl, img_path_banio, height=Mm(50))</v>
+      </c>
+      <c r="R11" t="s">
         <v>560</v>
       </c>
-      <c r="R11" t="str">
+      <c r="S11" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['banio']}')</v>
       </c>
-      <c r="S11" t="str">
+      <c r="T11" t="str">
         <f t="shared" si="6"/>
         <v>banio = ''</v>
       </c>
-      <c r="T11" t="s">
+      <c r="U11" t="s">
         <v>559</v>
       </c>
-      <c r="U11" t="str">
+      <c r="V11" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['banio']}: {e}')</v>
       </c>
-      <c r="V11" t="str">
+      <c r="W11" t="str">
         <f t="shared" si="8"/>
         <v>banio = ''</v>
       </c>
     </row>
-    <row r="12" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:23" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
         <v>832</v>
       </c>
@@ -34454,61 +34470,67 @@
         <v>407</v>
       </c>
       <c r="H12">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I12" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J12" t="s">
         <v>146</v>
       </c>
-      <c r="J12" t="s">
+      <c r="K12" t="s">
         <v>235</v>
       </c>
-      <c r="K12" t="str">
+      <c r="L12" t="str">
         <f t="shared" si="0"/>
         <v>'estado' : r_val['estado'],</v>
       </c>
-      <c r="L12" t="str">
+      <c r="M12" t="str">
         <f t="shared" si="1"/>
         <v>'cisterna': cisterna,</v>
       </c>
-      <c r="M12" t="s">
+      <c r="N12" t="s">
         <v>558</v>
       </c>
-      <c r="N12" t="str">
+      <c r="O12" t="str">
         <f t="shared" si="2"/>
         <v>img_path_cisterna = os.path.join(IMAGES_PATH, r_val['cisterna'])</v>
       </c>
-      <c r="O12" t="str">
+      <c r="P12" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_cisterna):</v>
       </c>
-      <c r="P12" t="str">
+      <c r="Q12" t="str">
         <f t="shared" si="4"/>
-        <v>cisterna = InlineImage(docx_tpl, img_path_cisterna, height=Mm(60))</v>
-      </c>
-      <c r="Q12" t="s">
+        <v>cisterna = InlineImage(docx_tpl, img_path_cisterna, height=Mm(50))</v>
+      </c>
+      <c r="R12" t="s">
         <v>560</v>
       </c>
-      <c r="R12" t="str">
+      <c r="S12" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['cisterna']}')</v>
       </c>
-      <c r="S12" t="str">
+      <c r="T12" t="str">
         <f t="shared" si="6"/>
         <v>cisterna = ''</v>
       </c>
-      <c r="T12" t="s">
+      <c r="U12" t="s">
         <v>559</v>
       </c>
-      <c r="U12" t="str">
+      <c r="V12" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['cisterna']}: {e}')</v>
       </c>
-      <c r="V12" t="str">
+      <c r="W12" t="str">
         <f t="shared" si="8"/>
         <v>cisterna = ''</v>
       </c>
     </row>
-    <row r="13" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="13" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="C13" t="s">
+        <v>843</v>
+      </c>
       <c r="D13" t="s">
         <v>832</v>
       </c>
@@ -34522,61 +34544,67 @@
         <v>348</v>
       </c>
       <c r="H13">
-        <v>70</v>
+        <v>155</v>
       </c>
       <c r="I13" t="s">
+        <v>1758</v>
+      </c>
+      <c r="J13" t="s">
         <v>147</v>
       </c>
-      <c r="J13" t="s">
+      <c r="K13" t="s">
         <v>236</v>
       </c>
-      <c r="K13" t="str">
+      <c r="L13" t="str">
         <f t="shared" si="0"/>
         <v>'codigo_postal' : r_val['codigo_postal'],</v>
       </c>
-      <c r="L13" t="str">
+      <c r="M13" t="str">
         <f t="shared" si="1"/>
         <v>'sismo': sismo,</v>
       </c>
-      <c r="M13" t="s">
+      <c r="N13" t="s">
         <v>558</v>
       </c>
-      <c r="N13" t="str">
+      <c r="O13" t="str">
         <f t="shared" si="2"/>
         <v>img_path_sismo = os.path.join(IMAGES_PATH, r_val['sismo'])</v>
       </c>
-      <c r="O13" t="str">
+      <c r="P13" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_sismo):</v>
       </c>
-      <c r="P13" t="str">
+      <c r="Q13" t="str">
         <f t="shared" si="4"/>
-        <v>sismo = InlineImage(docx_tpl, img_path_sismo, height=Mm(70))</v>
-      </c>
-      <c r="Q13" t="s">
+        <v>sismo = InlineImage(docx_tpl, img_path_sismo, height=Mm(155))</v>
+      </c>
+      <c r="R13" t="s">
         <v>560</v>
       </c>
-      <c r="R13" t="str">
+      <c r="S13" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['sismo']}')</v>
       </c>
-      <c r="S13" t="str">
+      <c r="T13" t="str">
         <f t="shared" si="6"/>
         <v>sismo = ''</v>
       </c>
-      <c r="T13" t="s">
+      <c r="U13" t="s">
         <v>559</v>
       </c>
-      <c r="U13" t="str">
+      <c r="V13" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['sismo']}: {e}')</v>
       </c>
-      <c r="V13" t="str">
+      <c r="W13" t="str">
         <f t="shared" si="8"/>
         <v>sismo = ''</v>
       </c>
     </row>
-    <row r="14" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="C14" t="s">
+        <v>843</v>
+      </c>
       <c r="D14" t="s">
         <v>832</v>
       </c>
@@ -34590,61 +34618,64 @@
         <v>349</v>
       </c>
       <c r="H14">
-        <v>70</v>
+        <v>155</v>
       </c>
       <c r="I14" t="s">
+        <v>1758</v>
+      </c>
+      <c r="J14" t="s">
         <v>148</v>
       </c>
-      <c r="J14" t="s">
+      <c r="K14" t="s">
         <v>237</v>
       </c>
-      <c r="K14" t="str">
+      <c r="L14" t="str">
         <f t="shared" si="0"/>
         <v>'telefono' : r_val['telefono'],</v>
       </c>
-      <c r="L14" t="str">
+      <c r="M14" t="str">
         <f t="shared" si="1"/>
         <v>'inundacion': inundacion,</v>
       </c>
-      <c r="M14" t="s">
+      <c r="N14" t="s">
         <v>558</v>
       </c>
-      <c r="N14" t="str">
+      <c r="O14" t="str">
         <f t="shared" si="2"/>
         <v>img_path_inundacion = os.path.join(IMAGES_PATH, r_val['inundacion'])</v>
       </c>
-      <c r="O14" t="str">
+      <c r="P14" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_inundacion):</v>
       </c>
-      <c r="P14" t="str">
+      <c r="Q14" t="str">
         <f t="shared" si="4"/>
-        <v>inundacion = InlineImage(docx_tpl, img_path_inundacion, height=Mm(70))</v>
-      </c>
-      <c r="Q14" t="s">
+        <v>inundacion = InlineImage(docx_tpl, img_path_inundacion, height=Mm(155))</v>
+      </c>
+      <c r="R14" t="s">
         <v>560</v>
       </c>
-      <c r="R14" t="str">
+      <c r="S14" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['inundacion']}')</v>
       </c>
-      <c r="S14" t="str">
+      <c r="T14" t="str">
         <f t="shared" si="6"/>
         <v>inundacion = ''</v>
       </c>
-      <c r="T14" t="s">
+      <c r="U14" t="s">
         <v>559</v>
       </c>
-      <c r="U14" t="str">
+      <c r="V14" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['inundacion']}: {e}')</v>
       </c>
-      <c r="V14" t="str">
+      <c r="W14" t="str">
         <f t="shared" si="8"/>
         <v>inundacion = ''</v>
       </c>
     </row>
-    <row r="15" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="15" spans="3:23" x14ac:dyDescent="0.3">
       <c r="D15" t="s">
         <v>832</v>
       </c>
@@ -34658,61 +34689,67 @@
         <v>350</v>
       </c>
       <c r="H15">
-        <v>70</v>
+        <v>155</v>
       </c>
       <c r="I15" t="s">
+        <v>1758</v>
+      </c>
+      <c r="J15" t="s">
         <v>149</v>
       </c>
-      <c r="J15" t="s">
+      <c r="K15" t="s">
         <v>238</v>
       </c>
-      <c r="K15" t="str">
+      <c r="L15" t="str">
         <f t="shared" si="0"/>
         <v>'email' : r_val['email'],</v>
       </c>
-      <c r="L15" t="str">
+      <c r="M15" t="str">
         <f t="shared" si="1"/>
         <v>'torm_elect': torm_elect,</v>
       </c>
-      <c r="M15" t="s">
+      <c r="N15" t="s">
         <v>558</v>
       </c>
-      <c r="N15" t="str">
+      <c r="O15" t="str">
         <f t="shared" si="2"/>
         <v>img_path_torm_elect = os.path.join(IMAGES_PATH, r_val['torm_elect'])</v>
       </c>
-      <c r="O15" t="str">
+      <c r="P15" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_torm_elect):</v>
       </c>
-      <c r="P15" t="str">
+      <c r="Q15" t="str">
         <f t="shared" si="4"/>
-        <v>torm_elect = InlineImage(docx_tpl, img_path_torm_elect, height=Mm(70))</v>
-      </c>
-      <c r="Q15" t="s">
+        <v>torm_elect = InlineImage(docx_tpl, img_path_torm_elect, height=Mm(155))</v>
+      </c>
+      <c r="R15" t="s">
         <v>560</v>
       </c>
-      <c r="R15" t="str">
+      <c r="S15" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['torm_elect']}')</v>
       </c>
-      <c r="S15" t="str">
+      <c r="T15" t="str">
         <f t="shared" si="6"/>
         <v>torm_elect = ''</v>
       </c>
-      <c r="T15" t="s">
+      <c r="U15" t="s">
         <v>559</v>
       </c>
-      <c r="U15" t="str">
+      <c r="V15" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['torm_elect']}: {e}')</v>
       </c>
-      <c r="V15" t="str">
+      <c r="W15" t="str">
         <f t="shared" si="8"/>
         <v>torm_elect = ''</v>
       </c>
     </row>
-    <row r="16" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="C16" t="s">
+        <v>843</v>
+      </c>
       <c r="D16" t="s">
         <v>832</v>
       </c>
@@ -34726,61 +34763,67 @@
         <v>351</v>
       </c>
       <c r="H16">
-        <v>70</v>
+        <v>155</v>
       </c>
       <c r="I16" t="s">
+        <v>1758</v>
+      </c>
+      <c r="J16" t="s">
         <v>150</v>
       </c>
-      <c r="J16" t="s">
+      <c r="K16" t="s">
         <v>239</v>
       </c>
-      <c r="K16" t="str">
+      <c r="L16" t="str">
         <f t="shared" si="0"/>
         <v>'antiguedad_inmueble' : r_val['antiguedad_inmueble'],</v>
       </c>
-      <c r="L16" t="str">
+      <c r="M16" t="str">
         <f t="shared" si="1"/>
         <v>'incendio': incendio,</v>
       </c>
-      <c r="M16" t="s">
+      <c r="N16" t="s">
         <v>558</v>
       </c>
-      <c r="N16" t="str">
+      <c r="O16" t="str">
         <f t="shared" si="2"/>
         <v>img_path_incendio = os.path.join(IMAGES_PATH, r_val['incendio'])</v>
       </c>
-      <c r="O16" t="str">
+      <c r="P16" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_incendio):</v>
       </c>
-      <c r="P16" t="str">
+      <c r="Q16" t="str">
         <f t="shared" si="4"/>
-        <v>incendio = InlineImage(docx_tpl, img_path_incendio, height=Mm(70))</v>
-      </c>
-      <c r="Q16" t="s">
+        <v>incendio = InlineImage(docx_tpl, img_path_incendio, height=Mm(155))</v>
+      </c>
+      <c r="R16" t="s">
         <v>560</v>
       </c>
-      <c r="R16" t="str">
+      <c r="S16" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['incendio']}')</v>
       </c>
-      <c r="S16" t="str">
+      <c r="T16" t="str">
         <f t="shared" si="6"/>
         <v>incendio = ''</v>
       </c>
-      <c r="T16" t="s">
+      <c r="U16" t="s">
         <v>559</v>
       </c>
-      <c r="U16" t="str">
+      <c r="V16" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['incendio']}: {e}')</v>
       </c>
-      <c r="V16" t="str">
+      <c r="W16" t="str">
         <f t="shared" si="8"/>
         <v>incendio = ''</v>
       </c>
     </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="C17" t="s">
+        <v>843</v>
+      </c>
       <c r="D17" t="s">
         <v>832</v>
       </c>
@@ -34794,61 +34837,64 @@
         <v>352</v>
       </c>
       <c r="H17">
-        <v>70</v>
+        <v>155</v>
       </c>
       <c r="I17" t="s">
+        <v>1758</v>
+      </c>
+      <c r="J17" t="s">
         <v>151</v>
       </c>
-      <c r="J17" t="s">
+      <c r="K17" t="s">
         <v>240</v>
       </c>
-      <c r="K17" t="str">
+      <c r="L17" t="str">
         <f t="shared" si="0"/>
         <v>'inicio_operaciones' : r_val['inicio_operaciones'],</v>
       </c>
-      <c r="L17" t="str">
+      <c r="M17" t="str">
         <f t="shared" si="1"/>
         <v>'influenza': influenza,</v>
       </c>
-      <c r="M17" t="s">
+      <c r="N17" t="s">
         <v>558</v>
       </c>
-      <c r="N17" t="str">
+      <c r="O17" t="str">
         <f t="shared" si="2"/>
         <v>img_path_influenza = os.path.join(IMAGES_PATH, r_val['influenza'])</v>
       </c>
-      <c r="O17" t="str">
+      <c r="P17" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_influenza):</v>
       </c>
-      <c r="P17" t="str">
+      <c r="Q17" t="str">
         <f t="shared" si="4"/>
-        <v>influenza = InlineImage(docx_tpl, img_path_influenza, height=Mm(70))</v>
-      </c>
-      <c r="Q17" t="s">
+        <v>influenza = InlineImage(docx_tpl, img_path_influenza, height=Mm(155))</v>
+      </c>
+      <c r="R17" t="s">
         <v>560</v>
       </c>
-      <c r="R17" t="str">
+      <c r="S17" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['influenza']}')</v>
       </c>
-      <c r="S17" t="str">
+      <c r="T17" t="str">
         <f t="shared" si="6"/>
         <v>influenza = ''</v>
       </c>
-      <c r="T17" t="s">
+      <c r="U17" t="s">
         <v>559</v>
       </c>
-      <c r="U17" t="str">
+      <c r="V17" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['influenza']}: {e}')</v>
       </c>
-      <c r="V17" t="str">
+      <c r="W17" t="str">
         <f t="shared" si="8"/>
         <v>influenza = ''</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.3">
       <c r="D18" t="s">
         <v>832</v>
       </c>
@@ -34862,61 +34908,64 @@
         <v>353</v>
       </c>
       <c r="H18">
-        <v>70</v>
+        <v>155</v>
       </c>
       <c r="I18" t="s">
+        <v>1758</v>
+      </c>
+      <c r="J18" t="s">
         <v>152</v>
       </c>
-      <c r="J18" t="s">
+      <c r="K18" t="s">
         <v>241</v>
       </c>
-      <c r="K18" t="str">
+      <c r="L18" t="str">
         <f t="shared" si="0"/>
         <v>'mod_estructurales' : r_val['mod_estructurales'],</v>
       </c>
-      <c r="L18" t="str">
+      <c r="M18" t="str">
         <f t="shared" si="1"/>
         <v>'radiacion': radiacion,</v>
       </c>
-      <c r="M18" t="s">
+      <c r="N18" t="s">
         <v>558</v>
       </c>
-      <c r="N18" t="str">
+      <c r="O18" t="str">
         <f t="shared" si="2"/>
         <v>img_path_radiacion = os.path.join(IMAGES_PATH, r_val['radiacion'])</v>
       </c>
-      <c r="O18" t="str">
+      <c r="P18" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_radiacion):</v>
       </c>
-      <c r="P18" t="str">
+      <c r="Q18" t="str">
         <f t="shared" si="4"/>
-        <v>radiacion = InlineImage(docx_tpl, img_path_radiacion, height=Mm(70))</v>
-      </c>
-      <c r="Q18" t="s">
+        <v>radiacion = InlineImage(docx_tpl, img_path_radiacion, height=Mm(155))</v>
+      </c>
+      <c r="R18" t="s">
         <v>560</v>
       </c>
-      <c r="R18" t="str">
+      <c r="S18" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['radiacion']}')</v>
       </c>
-      <c r="S18" t="str">
+      <c r="T18" t="str">
         <f t="shared" si="6"/>
         <v>radiacion = ''</v>
       </c>
-      <c r="T18" t="s">
+      <c r="U18" t="s">
         <v>559</v>
       </c>
-      <c r="U18" t="str">
+      <c r="V18" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['radiacion']}: {e}')</v>
       </c>
-      <c r="V18" t="str">
+      <c r="W18" t="str">
         <f t="shared" si="8"/>
         <v>radiacion = ''</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C19" t="s">
         <v>843</v>
       </c>
@@ -34933,61 +34982,64 @@
         <v>354</v>
       </c>
       <c r="H19">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I19" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J19" t="s">
         <v>153</v>
       </c>
-      <c r="J19" t="s">
+      <c r="K19" t="s">
         <v>242</v>
       </c>
-      <c r="K19" t="str">
+      <c r="L19" t="str">
         <f t="shared" si="0"/>
         <v>'mod_arquitect' : r_val['mod_arquitect'],</v>
       </c>
-      <c r="L19" t="str">
+      <c r="M19" t="str">
         <f t="shared" si="1"/>
         <v>'ext1': ext1,</v>
       </c>
-      <c r="M19" t="s">
+      <c r="N19" t="s">
         <v>558</v>
       </c>
-      <c r="N19" t="str">
+      <c r="O19" t="str">
         <f t="shared" si="2"/>
         <v>img_path_ext1 = os.path.join(IMAGES_PATH, r_val['ext1'])</v>
       </c>
-      <c r="O19" t="str">
+      <c r="P19" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_ext1):</v>
       </c>
-      <c r="P19" t="str">
+      <c r="Q19" t="str">
         <f t="shared" si="4"/>
-        <v>ext1 = InlineImage(docx_tpl, img_path_ext1, height=Mm(60))</v>
-      </c>
-      <c r="Q19" t="s">
+        <v>ext1 = InlineImage(docx_tpl, img_path_ext1, height=Mm(50))</v>
+      </c>
+      <c r="R19" t="s">
         <v>560</v>
       </c>
-      <c r="R19" t="str">
+      <c r="S19" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['ext1']}')</v>
       </c>
-      <c r="S19" t="str">
+      <c r="T19" t="str">
         <f t="shared" si="6"/>
         <v>ext1 = ''</v>
       </c>
-      <c r="T19" t="s">
+      <c r="U19" t="s">
         <v>559</v>
       </c>
-      <c r="U19" t="str">
+      <c r="V19" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['ext1']}: {e}')</v>
       </c>
-      <c r="V19" t="str">
+      <c r="W19" t="str">
         <f t="shared" si="8"/>
         <v>ext1 = ''</v>
       </c>
     </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:23" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
         <v>832</v>
       </c>
@@ -35001,61 +35053,64 @@
         <v>355</v>
       </c>
       <c r="H20">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I20" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J20" t="s">
         <v>154</v>
       </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
         <v>243</v>
       </c>
-      <c r="K20" t="str">
+      <c r="L20" t="str">
         <f t="shared" si="0"/>
         <v>'terreno_m2' : r_val['terreno_m2'],</v>
       </c>
-      <c r="L20" t="str">
+      <c r="M20" t="str">
         <f t="shared" si="1"/>
         <v>'ext2': ext2,</v>
       </c>
-      <c r="M20" t="s">
+      <c r="N20" t="s">
         <v>558</v>
       </c>
-      <c r="N20" t="str">
+      <c r="O20" t="str">
         <f t="shared" si="2"/>
         <v>img_path_ext2 = os.path.join(IMAGES_PATH, r_val['ext2'])</v>
       </c>
-      <c r="O20" t="str">
+      <c r="P20" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_ext2):</v>
       </c>
-      <c r="P20" t="str">
+      <c r="Q20" t="str">
         <f t="shared" si="4"/>
-        <v>ext2 = InlineImage(docx_tpl, img_path_ext2, height=Mm(60))</v>
-      </c>
-      <c r="Q20" t="s">
+        <v>ext2 = InlineImage(docx_tpl, img_path_ext2, height=Mm(50))</v>
+      </c>
+      <c r="R20" t="s">
         <v>560</v>
       </c>
-      <c r="R20" t="str">
+      <c r="S20" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['ext2']}')</v>
       </c>
-      <c r="S20" t="str">
+      <c r="T20" t="str">
         <f t="shared" si="6"/>
         <v>ext2 = ''</v>
       </c>
-      <c r="T20" t="s">
+      <c r="U20" t="s">
         <v>559</v>
       </c>
-      <c r="U20" t="str">
+      <c r="V20" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['ext2']}: {e}')</v>
       </c>
-      <c r="V20" t="str">
+      <c r="W20" t="str">
         <f t="shared" si="8"/>
         <v>ext2 = ''</v>
       </c>
     </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:23" x14ac:dyDescent="0.3">
       <c r="D21" t="s">
         <v>832</v>
       </c>
@@ -35069,61 +35124,64 @@
         <v>356</v>
       </c>
       <c r="H21">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I21" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J21" t="s">
         <v>155</v>
       </c>
-      <c r="J21" t="s">
+      <c r="K21" t="s">
         <v>244</v>
       </c>
-      <c r="K21" t="str">
+      <c r="L21" t="str">
         <f t="shared" si="0"/>
         <v>'construccion_m2' : r_val['construccion_m2'],</v>
       </c>
-      <c r="L21" t="str">
+      <c r="M21" t="str">
         <f t="shared" si="1"/>
         <v>'ext3': ext3,</v>
       </c>
-      <c r="M21" t="s">
+      <c r="N21" t="s">
         <v>558</v>
       </c>
-      <c r="N21" t="str">
+      <c r="O21" t="str">
         <f t="shared" si="2"/>
         <v>img_path_ext3 = os.path.join(IMAGES_PATH, r_val['ext3'])</v>
       </c>
-      <c r="O21" t="str">
+      <c r="P21" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_ext3):</v>
       </c>
-      <c r="P21" t="str">
+      <c r="Q21" t="str">
         <f t="shared" si="4"/>
-        <v>ext3 = InlineImage(docx_tpl, img_path_ext3, height=Mm(60))</v>
-      </c>
-      <c r="Q21" t="s">
+        <v>ext3 = InlineImage(docx_tpl, img_path_ext3, height=Mm(50))</v>
+      </c>
+      <c r="R21" t="s">
         <v>560</v>
       </c>
-      <c r="R21" t="str">
+      <c r="S21" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['ext3']}')</v>
       </c>
-      <c r="S21" t="str">
+      <c r="T21" t="str">
         <f t="shared" si="6"/>
         <v>ext3 = ''</v>
       </c>
-      <c r="T21" t="s">
+      <c r="U21" t="s">
         <v>559</v>
       </c>
-      <c r="U21" t="str">
+      <c r="V21" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['ext3']}: {e}')</v>
       </c>
-      <c r="V21" t="str">
+      <c r="W21" t="str">
         <f t="shared" si="8"/>
         <v>ext3 = ''</v>
       </c>
     </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:23" x14ac:dyDescent="0.3">
       <c r="D22" t="s">
         <v>832</v>
       </c>
@@ -35137,61 +35195,64 @@
         <v>357</v>
       </c>
       <c r="H22">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I22" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J22" t="s">
         <v>156</v>
       </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
         <v>245</v>
       </c>
-      <c r="K22" t="str">
+      <c r="L22" t="str">
         <f t="shared" si="0"/>
         <v>'edificios' : r_val['edificios'],</v>
       </c>
-      <c r="L22" t="str">
+      <c r="M22" t="str">
         <f t="shared" si="1"/>
         <v>'ext4': ext4,</v>
       </c>
-      <c r="M22" t="s">
+      <c r="N22" t="s">
         <v>558</v>
       </c>
-      <c r="N22" t="str">
+      <c r="O22" t="str">
         <f t="shared" si="2"/>
         <v>img_path_ext4 = os.path.join(IMAGES_PATH, r_val['ext4'])</v>
       </c>
-      <c r="O22" t="str">
+      <c r="P22" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_ext4):</v>
       </c>
-      <c r="P22" t="str">
+      <c r="Q22" t="str">
         <f t="shared" si="4"/>
-        <v>ext4 = InlineImage(docx_tpl, img_path_ext4, height=Mm(60))</v>
-      </c>
-      <c r="Q22" t="s">
+        <v>ext4 = InlineImage(docx_tpl, img_path_ext4, height=Mm(50))</v>
+      </c>
+      <c r="R22" t="s">
         <v>560</v>
       </c>
-      <c r="R22" t="str">
+      <c r="S22" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['ext4']}')</v>
       </c>
-      <c r="S22" t="str">
+      <c r="T22" t="str">
         <f t="shared" si="6"/>
         <v>ext4 = ''</v>
       </c>
-      <c r="T22" t="s">
+      <c r="U22" t="s">
         <v>559</v>
       </c>
-      <c r="U22" t="str">
+      <c r="V22" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['ext4']}: {e}')</v>
       </c>
-      <c r="V22" t="str">
+      <c r="W22" t="str">
         <f t="shared" si="8"/>
         <v>ext4 = ''</v>
       </c>
     </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C23" t="s">
         <v>843</v>
       </c>
@@ -35208,61 +35269,64 @@
         <v>266</v>
       </c>
       <c r="H23">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I23" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J23" t="s">
         <v>157</v>
       </c>
-      <c r="J23" t="s">
+      <c r="K23" t="s">
         <v>246</v>
       </c>
-      <c r="K23" t="str">
+      <c r="L23" t="str">
         <f t="shared" si="0"/>
         <v>'niveles' : r_val['niveles'],</v>
       </c>
-      <c r="L23" t="str">
+      <c r="M23" t="str">
         <f t="shared" si="1"/>
         <v>'botiquin': botiquin,</v>
       </c>
-      <c r="M23" t="s">
+      <c r="N23" t="s">
         <v>558</v>
       </c>
-      <c r="N23" t="str">
+      <c r="O23" t="str">
         <f t="shared" si="2"/>
         <v>img_path_botiquin = os.path.join(IMAGES_PATH, r_val['botiquin'])</v>
       </c>
-      <c r="O23" t="str">
+      <c r="P23" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_botiquin):</v>
       </c>
-      <c r="P23" t="str">
+      <c r="Q23" t="str">
         <f t="shared" si="4"/>
-        <v>botiquin = InlineImage(docx_tpl, img_path_botiquin, height=Mm(60))</v>
-      </c>
-      <c r="Q23" t="s">
+        <v>botiquin = InlineImage(docx_tpl, img_path_botiquin, height=Mm(50))</v>
+      </c>
+      <c r="R23" t="s">
         <v>560</v>
       </c>
-      <c r="R23" t="str">
+      <c r="S23" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['botiquin']}')</v>
       </c>
-      <c r="S23" t="str">
+      <c r="T23" t="str">
         <f t="shared" si="6"/>
         <v>botiquin = ''</v>
       </c>
-      <c r="T23" t="s">
+      <c r="U23" t="s">
         <v>559</v>
       </c>
-      <c r="U23" t="str">
+      <c r="V23" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['botiquin']}: {e}')</v>
       </c>
-      <c r="V23" t="str">
+      <c r="W23" t="str">
         <f t="shared" si="8"/>
         <v>botiquin = ''</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C24" t="s">
         <v>843</v>
       </c>
@@ -35282,58 +35346,61 @@
         <v>50</v>
       </c>
       <c r="I24" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J24" t="s">
         <v>158</v>
       </c>
-      <c r="J24" t="s">
+      <c r="K24" t="s">
         <v>247</v>
       </c>
-      <c r="K24" t="str">
+      <c r="L24" t="str">
         <f t="shared" si="0"/>
         <v>'accesos' : r_val['accesos'],</v>
       </c>
-      <c r="L24" t="str">
+      <c r="M24" t="str">
         <f t="shared" si="1"/>
         <v>'ruta1': ruta1,</v>
       </c>
-      <c r="M24" t="s">
+      <c r="N24" t="s">
         <v>558</v>
       </c>
-      <c r="N24" t="str">
+      <c r="O24" t="str">
         <f t="shared" si="2"/>
         <v>img_path_ruta1 = os.path.join(IMAGES_PATH, r_val['ruta1'])</v>
       </c>
-      <c r="O24" t="str">
+      <c r="P24" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_ruta1):</v>
       </c>
-      <c r="P24" t="str">
+      <c r="Q24" t="str">
         <f t="shared" si="4"/>
         <v>ruta1 = InlineImage(docx_tpl, img_path_ruta1, height=Mm(50))</v>
       </c>
-      <c r="Q24" t="s">
+      <c r="R24" t="s">
         <v>560</v>
       </c>
-      <c r="R24" t="str">
+      <c r="S24" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['ruta1']}')</v>
       </c>
-      <c r="S24" t="str">
+      <c r="T24" t="str">
         <f t="shared" si="6"/>
         <v>ruta1 = ''</v>
       </c>
-      <c r="T24" t="s">
+      <c r="U24" t="s">
         <v>559</v>
       </c>
-      <c r="U24" t="str">
+      <c r="V24" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['ruta1']}: {e}')</v>
       </c>
-      <c r="V24" t="str">
+      <c r="W24" t="str">
         <f t="shared" si="8"/>
         <v>ruta1 = ''</v>
       </c>
     </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C25" t="s">
         <v>843</v>
       </c>
@@ -35353,58 +35420,61 @@
         <v>50</v>
       </c>
       <c r="I25" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J25" t="s">
         <v>159</v>
       </c>
-      <c r="J25" t="s">
+      <c r="K25" t="s">
         <v>248</v>
       </c>
-      <c r="K25" t="str">
+      <c r="L25" t="str">
         <f t="shared" si="0"/>
         <v>'salidas_emergencia' : r_val['salidas_emergencia'],</v>
       </c>
-      <c r="L25" t="str">
+      <c r="M25" t="str">
         <f t="shared" si="1"/>
         <v>'ruta2': ruta2,</v>
       </c>
-      <c r="M25" t="s">
+      <c r="N25" t="s">
         <v>558</v>
       </c>
-      <c r="N25" t="str">
+      <c r="O25" t="str">
         <f t="shared" si="2"/>
         <v>img_path_ruta2 = os.path.join(IMAGES_PATH, r_val['ruta2'])</v>
       </c>
-      <c r="O25" t="str">
+      <c r="P25" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_ruta2):</v>
       </c>
-      <c r="P25" t="str">
+      <c r="Q25" t="str">
         <f t="shared" si="4"/>
         <v>ruta2 = InlineImage(docx_tpl, img_path_ruta2, height=Mm(50))</v>
       </c>
-      <c r="Q25" t="s">
+      <c r="R25" t="s">
         <v>560</v>
       </c>
-      <c r="R25" t="str">
+      <c r="S25" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['ruta2']}')</v>
       </c>
-      <c r="S25" t="str">
+      <c r="T25" t="str">
         <f t="shared" si="6"/>
         <v>ruta2 = ''</v>
       </c>
-      <c r="T25" t="s">
+      <c r="U25" t="s">
         <v>559</v>
       </c>
-      <c r="U25" t="str">
+      <c r="V25" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['ruta2']}: {e}')</v>
       </c>
-      <c r="V25" t="str">
+      <c r="W25" t="str">
         <f t="shared" si="8"/>
         <v>ruta2 = ''</v>
       </c>
     </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:23" x14ac:dyDescent="0.3">
       <c r="D26" t="s">
         <v>832</v>
       </c>
@@ -35421,58 +35491,61 @@
         <v>50</v>
       </c>
       <c r="I26" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J26" t="s">
         <v>5</v>
       </c>
-      <c r="J26" t="s">
+      <c r="K26" t="s">
         <v>249</v>
       </c>
-      <c r="K26" t="str">
+      <c r="L26" t="str">
         <f t="shared" si="0"/>
         <v>'escaleras' : r_val['escaleras'],</v>
       </c>
-      <c r="L26" t="str">
+      <c r="M26" t="str">
         <f t="shared" si="1"/>
         <v>'ruta3': ruta3,</v>
       </c>
-      <c r="M26" t="s">
+      <c r="N26" t="s">
         <v>558</v>
       </c>
-      <c r="N26" t="str">
+      <c r="O26" t="str">
         <f t="shared" si="2"/>
         <v>img_path_ruta3 = os.path.join(IMAGES_PATH, r_val['ruta3'])</v>
       </c>
-      <c r="O26" t="str">
+      <c r="P26" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_ruta3):</v>
       </c>
-      <c r="P26" t="str">
+      <c r="Q26" t="str">
         <f t="shared" si="4"/>
         <v>ruta3 = InlineImage(docx_tpl, img_path_ruta3, height=Mm(50))</v>
       </c>
-      <c r="Q26" t="s">
+      <c r="R26" t="s">
         <v>560</v>
       </c>
-      <c r="R26" t="str">
+      <c r="S26" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['ruta3']}')</v>
       </c>
-      <c r="S26" t="str">
+      <c r="T26" t="str">
         <f t="shared" si="6"/>
         <v>ruta3 = ''</v>
       </c>
-      <c r="T26" t="s">
+      <c r="U26" t="s">
         <v>559</v>
       </c>
-      <c r="U26" t="str">
+      <c r="V26" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['ruta3']}: {e}')</v>
       </c>
-      <c r="V26" t="str">
+      <c r="W26" t="str">
         <f t="shared" si="8"/>
         <v>ruta3 = ''</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.3">
       <c r="D27" t="s">
         <v>832</v>
       </c>
@@ -35489,58 +35562,61 @@
         <v>50</v>
       </c>
       <c r="I27" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J27" t="s">
         <v>160</v>
       </c>
-      <c r="J27" t="s">
+      <c r="K27" t="s">
         <v>250</v>
       </c>
-      <c r="K27" t="str">
+      <c r="L27" t="str">
         <f t="shared" si="0"/>
         <v>'escaleras_emergencia' : r_val['escaleras_emergencia'],</v>
       </c>
-      <c r="L27" t="str">
+      <c r="M27" t="str">
         <f t="shared" si="1"/>
         <v>'salida': salida,</v>
       </c>
-      <c r="M27" t="s">
+      <c r="N27" t="s">
         <v>558</v>
       </c>
-      <c r="N27" t="str">
+      <c r="O27" t="str">
         <f t="shared" si="2"/>
         <v>img_path_salida = os.path.join(IMAGES_PATH, r_val['salida'])</v>
       </c>
-      <c r="O27" t="str">
+      <c r="P27" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_salida):</v>
       </c>
-      <c r="P27" t="str">
+      <c r="Q27" t="str">
         <f t="shared" si="4"/>
         <v>salida = InlineImage(docx_tpl, img_path_salida, height=Mm(50))</v>
       </c>
-      <c r="Q27" t="s">
+      <c r="R27" t="s">
         <v>560</v>
       </c>
-      <c r="R27" t="str">
+      <c r="S27" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['salida']}')</v>
       </c>
-      <c r="S27" t="str">
+      <c r="T27" t="str">
         <f t="shared" si="6"/>
         <v>salida = ''</v>
       </c>
-      <c r="T27" t="s">
+      <c r="U27" t="s">
         <v>559</v>
       </c>
-      <c r="U27" t="str">
+      <c r="V27" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['salida']}: {e}')</v>
       </c>
-      <c r="V27" t="str">
+      <c r="W27" t="str">
         <f t="shared" si="8"/>
         <v>salida = ''</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
         <v>843</v>
       </c>
@@ -35557,61 +35633,64 @@
         <v>276</v>
       </c>
       <c r="H28">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I28" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J28" t="s">
         <v>161</v>
       </c>
-      <c r="J28" t="s">
+      <c r="K28" t="s">
         <v>251</v>
       </c>
-      <c r="K28" t="str">
+      <c r="L28" t="str">
         <f t="shared" si="0"/>
         <v>'estacionamiento' : r_val['estacionamiento'],</v>
       </c>
-      <c r="L28" t="str">
+      <c r="M28" t="str">
         <f t="shared" si="1"/>
         <v>'alarma': alarma,</v>
       </c>
-      <c r="M28" t="s">
+      <c r="N28" t="s">
         <v>558</v>
       </c>
-      <c r="N28" t="str">
+      <c r="O28" t="str">
         <f t="shared" si="2"/>
         <v>img_path_alarma = os.path.join(IMAGES_PATH, r_val['alarma'])</v>
       </c>
-      <c r="O28" t="str">
+      <c r="P28" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_alarma):</v>
       </c>
-      <c r="P28" t="str">
+      <c r="Q28" t="str">
         <f t="shared" si="4"/>
-        <v>alarma = InlineImage(docx_tpl, img_path_alarma, height=Mm(60))</v>
-      </c>
-      <c r="Q28" t="s">
+        <v>alarma = InlineImage(docx_tpl, img_path_alarma, height=Mm(50))</v>
+      </c>
+      <c r="R28" t="s">
         <v>560</v>
       </c>
-      <c r="R28" t="str">
+      <c r="S28" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['alarma']}')</v>
       </c>
-      <c r="S28" t="str">
+      <c r="T28" t="str">
         <f t="shared" si="6"/>
         <v>alarma = ''</v>
       </c>
-      <c r="T28" t="s">
+      <c r="U28" t="s">
         <v>559</v>
       </c>
-      <c r="U28" t="str">
+      <c r="V28" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['alarma']}: {e}')</v>
       </c>
-      <c r="V28" t="str">
+      <c r="W28" t="str">
         <f t="shared" si="8"/>
         <v>alarma = ''</v>
       </c>
     </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:23" x14ac:dyDescent="0.3">
       <c r="D29" t="s">
         <v>832</v>
       </c>
@@ -35628,58 +35707,61 @@
         <v>50</v>
       </c>
       <c r="I29" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J29" t="s">
         <v>162</v>
       </c>
-      <c r="J29" t="s">
+      <c r="K29" t="s">
         <v>252</v>
       </c>
-      <c r="K29" t="str">
+      <c r="L29" t="str">
         <f t="shared" si="0"/>
         <v>'representante_legal' : r_val['representante_legal'],</v>
       </c>
-      <c r="L29" t="str">
+      <c r="M29" t="str">
         <f t="shared" si="1"/>
         <v>'prohib1': prohib1,</v>
       </c>
-      <c r="M29" t="s">
+      <c r="N29" t="s">
         <v>558</v>
       </c>
-      <c r="N29" t="str">
+      <c r="O29" t="str">
         <f t="shared" si="2"/>
         <v>img_path_prohib1 = os.path.join(IMAGES_PATH, r_val['prohib1'])</v>
       </c>
-      <c r="O29" t="str">
+      <c r="P29" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_prohib1):</v>
       </c>
-      <c r="P29" t="str">
+      <c r="Q29" t="str">
         <f t="shared" si="4"/>
         <v>prohib1 = InlineImage(docx_tpl, img_path_prohib1, height=Mm(50))</v>
       </c>
-      <c r="Q29" t="s">
+      <c r="R29" t="s">
         <v>560</v>
       </c>
-      <c r="R29" t="str">
+      <c r="S29" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['prohib1']}')</v>
       </c>
-      <c r="S29" t="str">
+      <c r="T29" t="str">
         <f t="shared" si="6"/>
         <v>prohib1 = ''</v>
       </c>
-      <c r="T29" t="s">
+      <c r="U29" t="s">
         <v>559</v>
       </c>
-      <c r="U29" t="str">
+      <c r="V29" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['prohib1']}: {e}')</v>
       </c>
-      <c r="V29" t="str">
+      <c r="W29" t="str">
         <f t="shared" si="8"/>
         <v>prohib1 = ''</v>
       </c>
     </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:23" x14ac:dyDescent="0.3">
       <c r="D30" t="s">
         <v>832</v>
       </c>
@@ -35696,58 +35778,61 @@
         <v>50</v>
       </c>
       <c r="I30" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J30" t="s">
         <v>163</v>
       </c>
-      <c r="J30" t="s">
+      <c r="K30" t="s">
         <v>253</v>
       </c>
-      <c r="K30" t="str">
+      <c r="L30" t="str">
         <f t="shared" si="0"/>
         <v>'responsable_pipc' : r_val['responsable_pipc'],</v>
       </c>
-      <c r="L30" t="str">
+      <c r="M30" t="str">
         <f t="shared" si="1"/>
         <v>'prohib2': prohib2,</v>
       </c>
-      <c r="M30" t="s">
+      <c r="N30" t="s">
         <v>558</v>
       </c>
-      <c r="N30" t="str">
+      <c r="O30" t="str">
         <f t="shared" si="2"/>
         <v>img_path_prohib2 = os.path.join(IMAGES_PATH, r_val['prohib2'])</v>
       </c>
-      <c r="O30" t="str">
+      <c r="P30" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_prohib2):</v>
       </c>
-      <c r="P30" t="str">
+      <c r="Q30" t="str">
         <f t="shared" si="4"/>
         <v>prohib2 = InlineImage(docx_tpl, img_path_prohib2, height=Mm(50))</v>
       </c>
-      <c r="Q30" t="s">
+      <c r="R30" t="s">
         <v>560</v>
       </c>
-      <c r="R30" t="str">
+      <c r="S30" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['prohib2']}')</v>
       </c>
-      <c r="S30" t="str">
+      <c r="T30" t="str">
         <f t="shared" si="6"/>
         <v>prohib2 = ''</v>
       </c>
-      <c r="T30" t="s">
+      <c r="U30" t="s">
         <v>559</v>
       </c>
-      <c r="U30" t="str">
+      <c r="V30" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['prohib2']}: {e}')</v>
       </c>
-      <c r="V30" t="str">
+      <c r="W30" t="str">
         <f t="shared" si="8"/>
         <v>prohib2 = ''</v>
       </c>
     </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:23" x14ac:dyDescent="0.3">
       <c r="D31" t="s">
         <v>832</v>
       </c>
@@ -35764,58 +35849,61 @@
         <v>50</v>
       </c>
       <c r="I31" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J31" t="s">
         <v>164</v>
       </c>
-      <c r="J31" t="s">
+      <c r="K31" t="s">
         <v>254</v>
       </c>
-      <c r="K31" t="str">
+      <c r="L31" t="str">
         <f t="shared" si="0"/>
         <v>'trabajadores' : r_val['trabajadores'],</v>
       </c>
-      <c r="L31" t="str">
+      <c r="M31" t="str">
         <f t="shared" si="1"/>
         <v>'prohib3': prohib3,</v>
       </c>
-      <c r="M31" t="s">
+      <c r="N31" t="s">
         <v>558</v>
       </c>
-      <c r="N31" t="str">
+      <c r="O31" t="str">
         <f t="shared" si="2"/>
         <v>img_path_prohib3 = os.path.join(IMAGES_PATH, r_val['prohib3'])</v>
       </c>
-      <c r="O31" t="str">
+      <c r="P31" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_prohib3):</v>
       </c>
-      <c r="P31" t="str">
+      <c r="Q31" t="str">
         <f t="shared" si="4"/>
         <v>prohib3 = InlineImage(docx_tpl, img_path_prohib3, height=Mm(50))</v>
       </c>
-      <c r="Q31" t="s">
+      <c r="R31" t="s">
         <v>560</v>
       </c>
-      <c r="R31" t="str">
+      <c r="S31" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['prohib3']}')</v>
       </c>
-      <c r="S31" t="str">
+      <c r="T31" t="str">
         <f t="shared" si="6"/>
         <v>prohib3 = ''</v>
       </c>
-      <c r="T31" t="s">
+      <c r="U31" t="s">
         <v>559</v>
       </c>
-      <c r="U31" t="str">
+      <c r="V31" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['prohib3']}: {e}')</v>
       </c>
-      <c r="V31" t="str">
+      <c r="W31" t="str">
         <f t="shared" si="8"/>
         <v>prohib3 = ''</v>
       </c>
     </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:23" x14ac:dyDescent="0.3">
       <c r="D32" t="s">
         <v>832</v>
       </c>
@@ -35832,58 +35920,61 @@
         <v>50</v>
       </c>
       <c r="I32" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J32" t="s">
         <v>165</v>
       </c>
-      <c r="J32" t="s">
+      <c r="K32" t="s">
         <v>255</v>
       </c>
-      <c r="K32" t="str">
+      <c r="L32" t="str">
         <f t="shared" si="0"/>
         <v>'poblacion_discapacidad' : r_val['poblacion_discapacidad'],</v>
       </c>
-      <c r="L32" t="str">
+      <c r="M32" t="str">
         <f t="shared" si="1"/>
         <v>'prohib4': prohib4,</v>
       </c>
-      <c r="M32" t="s">
+      <c r="N32" t="s">
         <v>558</v>
       </c>
-      <c r="N32" t="str">
+      <c r="O32" t="str">
         <f t="shared" si="2"/>
         <v>img_path_prohib4 = os.path.join(IMAGES_PATH, r_val['prohib4'])</v>
       </c>
-      <c r="O32" t="str">
+      <c r="P32" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_prohib4):</v>
       </c>
-      <c r="P32" t="str">
+      <c r="Q32" t="str">
         <f t="shared" si="4"/>
         <v>prohib4 = InlineImage(docx_tpl, img_path_prohib4, height=Mm(50))</v>
       </c>
-      <c r="Q32" t="s">
+      <c r="R32" t="s">
         <v>560</v>
       </c>
-      <c r="R32" t="str">
+      <c r="S32" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['prohib4']}')</v>
       </c>
-      <c r="S32" t="str">
+      <c r="T32" t="str">
         <f t="shared" si="6"/>
         <v>prohib4 = ''</v>
       </c>
-      <c r="T32" t="s">
+      <c r="U32" t="s">
         <v>559</v>
       </c>
-      <c r="U32" t="str">
+      <c r="V32" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['prohib4']}: {e}')</v>
       </c>
-      <c r="V32" t="str">
+      <c r="W32" t="str">
         <f t="shared" si="8"/>
         <v>prohib4 = ''</v>
       </c>
     </row>
-    <row r="33" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C33" t="s">
         <v>843</v>
       </c>
@@ -35900,61 +35991,64 @@
         <v>366</v>
       </c>
       <c r="H33">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="I33" t="s">
+        <v>1758</v>
+      </c>
+      <c r="J33" t="s">
         <v>166</v>
       </c>
-      <c r="J33" t="s">
+      <c r="K33" t="s">
         <v>256</v>
       </c>
-      <c r="K33" t="str">
+      <c r="L33" t="str">
         <f t="shared" si="0"/>
         <v>'hombres' : r_val['hombres'],</v>
       </c>
-      <c r="L33" t="str">
+      <c r="M33" t="str">
         <f t="shared" si="1"/>
         <v>'layout': layout,</v>
       </c>
-      <c r="M33" t="s">
+      <c r="N33" t="s">
         <v>558</v>
       </c>
-      <c r="N33" t="str">
+      <c r="O33" t="str">
         <f t="shared" si="2"/>
         <v>img_path_layout = os.path.join(IMAGES_PATH, r_val['layout'])</v>
       </c>
-      <c r="O33" t="str">
+      <c r="P33" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_layout):</v>
       </c>
-      <c r="P33" t="str">
+      <c r="Q33" t="str">
         <f t="shared" si="4"/>
-        <v>layout = InlineImage(docx_tpl, img_path_layout, height=Mm(160))</v>
-      </c>
-      <c r="Q33" t="s">
+        <v>layout = InlineImage(docx_tpl, img_path_layout, height=Mm(155))</v>
+      </c>
+      <c r="R33" t="s">
         <v>560</v>
       </c>
-      <c r="R33" t="str">
+      <c r="S33" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['layout']}')</v>
       </c>
-      <c r="S33" t="str">
+      <c r="T33" t="str">
         <f t="shared" si="6"/>
         <v>layout = ''</v>
       </c>
-      <c r="T33" t="s">
+      <c r="U33" t="s">
         <v>559</v>
       </c>
-      <c r="U33" t="str">
+      <c r="V33" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['layout']}: {e}')</v>
       </c>
-      <c r="V33" t="str">
+      <c r="W33" t="str">
         <f t="shared" si="8"/>
         <v>layout = ''</v>
       </c>
     </row>
-    <row r="34" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C34" t="s">
         <v>843</v>
       </c>
@@ -35974,58 +36068,61 @@
         <v>60</v>
       </c>
       <c r="I34" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J34" t="s">
         <v>167</v>
       </c>
-      <c r="J34" t="s">
+      <c r="K34" t="s">
         <v>257</v>
       </c>
-      <c r="K34" t="str">
+      <c r="L34" t="str">
         <f t="shared" si="0"/>
         <v>'mujeres' : r_val['mujeres'],</v>
       </c>
-      <c r="L34" t="str">
+      <c r="M34" t="str">
         <f t="shared" si="1"/>
         <v>'cap1': cap1,</v>
       </c>
-      <c r="M34" t="s">
+      <c r="N34" t="s">
         <v>558</v>
       </c>
-      <c r="N34" t="str">
+      <c r="O34" t="str">
         <f t="shared" si="2"/>
         <v>img_path_cap1 = os.path.join(IMAGES_PATH, r_val['cap1'])</v>
       </c>
-      <c r="O34" t="str">
+      <c r="P34" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_cap1):</v>
       </c>
-      <c r="P34" t="str">
+      <c r="Q34" t="str">
         <f t="shared" si="4"/>
         <v>cap1 = InlineImage(docx_tpl, img_path_cap1, height=Mm(60))</v>
       </c>
-      <c r="Q34" t="s">
+      <c r="R34" t="s">
         <v>560</v>
       </c>
-      <c r="R34" t="str">
+      <c r="S34" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['cap1']}')</v>
       </c>
-      <c r="S34" t="str">
+      <c r="T34" t="str">
         <f t="shared" si="6"/>
         <v>cap1 = ''</v>
       </c>
-      <c r="T34" t="s">
+      <c r="U34" t="s">
         <v>559</v>
       </c>
-      <c r="U34" t="str">
+      <c r="V34" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['cap1']}: {e}')</v>
       </c>
-      <c r="V34" t="str">
+      <c r="W34" t="str">
         <f t="shared" si="8"/>
         <v>cap1 = ''</v>
       </c>
     </row>
-    <row r="35" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C35" t="s">
         <v>843</v>
       </c>
@@ -36045,58 +36142,61 @@
         <v>60</v>
       </c>
       <c r="I35" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J35" t="s">
         <v>168</v>
       </c>
-      <c r="J35" t="s">
+      <c r="K35" t="s">
         <v>258</v>
       </c>
-      <c r="K35" t="str">
+      <c r="L35" t="str">
         <f t="shared" si="0"/>
         <v>'hombre_dicapacidad' : r_val['hombre_dicapacidad'],</v>
       </c>
-      <c r="L35" t="str">
+      <c r="M35" t="str">
         <f t="shared" si="1"/>
         <v>'cap2': cap2,</v>
       </c>
-      <c r="M35" t="s">
+      <c r="N35" t="s">
         <v>558</v>
       </c>
-      <c r="N35" t="str">
+      <c r="O35" t="str">
         <f t="shared" si="2"/>
         <v>img_path_cap2 = os.path.join(IMAGES_PATH, r_val['cap2'])</v>
       </c>
-      <c r="O35" t="str">
+      <c r="P35" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_cap2):</v>
       </c>
-      <c r="P35" t="str">
+      <c r="Q35" t="str">
         <f t="shared" si="4"/>
         <v>cap2 = InlineImage(docx_tpl, img_path_cap2, height=Mm(60))</v>
       </c>
-      <c r="Q35" t="s">
+      <c r="R35" t="s">
         <v>560</v>
       </c>
-      <c r="R35" t="str">
+      <c r="S35" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['cap2']}')</v>
       </c>
-      <c r="S35" t="str">
+      <c r="T35" t="str">
         <f t="shared" si="6"/>
         <v>cap2 = ''</v>
       </c>
-      <c r="T35" t="s">
+      <c r="U35" t="s">
         <v>559</v>
       </c>
-      <c r="U35" t="str">
+      <c r="V35" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['cap2']}: {e}')</v>
       </c>
-      <c r="V35" t="str">
+      <c r="W35" t="str">
         <f t="shared" si="8"/>
         <v>cap2 = ''</v>
       </c>
     </row>
-    <row r="36" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C36" t="s">
         <v>843</v>
       </c>
@@ -36116,58 +36216,61 @@
         <v>60</v>
       </c>
       <c r="I36" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J36" t="s">
         <v>169</v>
       </c>
-      <c r="J36" t="s">
+      <c r="K36" t="s">
         <v>259</v>
       </c>
-      <c r="K36" t="str">
+      <c r="L36" t="str">
         <f t="shared" si="0"/>
         <v>'mujeres_discapacidad' : r_val['mujeres_discapacidad'],</v>
       </c>
-      <c r="L36" t="str">
+      <c r="M36" t="str">
         <f t="shared" si="1"/>
         <v>'cap3': cap3,</v>
       </c>
-      <c r="M36" t="s">
+      <c r="N36" t="s">
         <v>558</v>
       </c>
-      <c r="N36" t="str">
+      <c r="O36" t="str">
         <f t="shared" si="2"/>
         <v>img_path_cap3 = os.path.join(IMAGES_PATH, r_val['cap3'])</v>
       </c>
-      <c r="O36" t="str">
+      <c r="P36" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_cap3):</v>
       </c>
-      <c r="P36" t="str">
+      <c r="Q36" t="str">
         <f t="shared" si="4"/>
         <v>cap3 = InlineImage(docx_tpl, img_path_cap3, height=Mm(60))</v>
       </c>
-      <c r="Q36" t="s">
+      <c r="R36" t="s">
         <v>560</v>
       </c>
-      <c r="R36" t="str">
+      <c r="S36" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['cap3']}')</v>
       </c>
-      <c r="S36" t="str">
+      <c r="T36" t="str">
         <f t="shared" si="6"/>
         <v>cap3 = ''</v>
       </c>
-      <c r="T36" t="s">
+      <c r="U36" t="s">
         <v>559</v>
       </c>
-      <c r="U36" t="str">
+      <c r="V36" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['cap3']}: {e}')</v>
       </c>
-      <c r="V36" t="str">
+      <c r="W36" t="str">
         <f t="shared" si="8"/>
         <v>cap3 = ''</v>
       </c>
     </row>
-    <row r="37" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C37" t="s">
         <v>843</v>
       </c>
@@ -36187,58 +36290,61 @@
         <v>60</v>
       </c>
       <c r="I37" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J37" t="s">
         <v>170</v>
       </c>
-      <c r="J37" t="s">
+      <c r="K37" t="s">
         <v>260</v>
       </c>
-      <c r="K37" t="str">
+      <c r="L37" t="str">
         <f t="shared" si="0"/>
         <v>'turnos' : r_val['turnos'],</v>
       </c>
-      <c r="L37" t="str">
+      <c r="M37" t="str">
         <f t="shared" si="1"/>
         <v>'cap4': cap4,</v>
       </c>
-      <c r="M37" t="s">
+      <c r="N37" t="s">
         <v>558</v>
       </c>
-      <c r="N37" t="str">
+      <c r="O37" t="str">
         <f t="shared" si="2"/>
         <v>img_path_cap4 = os.path.join(IMAGES_PATH, r_val['cap4'])</v>
       </c>
-      <c r="O37" t="str">
+      <c r="P37" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_cap4):</v>
       </c>
-      <c r="P37" t="str">
+      <c r="Q37" t="str">
         <f t="shared" si="4"/>
         <v>cap4 = InlineImage(docx_tpl, img_path_cap4, height=Mm(60))</v>
       </c>
-      <c r="Q37" t="s">
+      <c r="R37" t="s">
         <v>560</v>
       </c>
-      <c r="R37" t="str">
+      <c r="S37" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['cap4']}')</v>
       </c>
-      <c r="S37" t="str">
+      <c r="T37" t="str">
         <f t="shared" si="6"/>
         <v>cap4 = ''</v>
       </c>
-      <c r="T37" t="s">
+      <c r="U37" t="s">
         <v>559</v>
       </c>
-      <c r="U37" t="str">
+      <c r="V37" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['cap4']}: {e}')</v>
       </c>
-      <c r="V37" t="str">
+      <c r="W37" t="str">
         <f t="shared" si="8"/>
         <v>cap4 = ''</v>
       </c>
     </row>
-    <row r="38" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C38" t="s">
         <v>843</v>
       </c>
@@ -36258,58 +36364,61 @@
         <v>60</v>
       </c>
       <c r="I38" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J38" t="s">
         <v>171</v>
       </c>
-      <c r="J38" t="s">
+      <c r="K38" t="s">
         <v>261</v>
       </c>
-      <c r="K38" t="str">
+      <c r="L38" t="str">
         <f t="shared" si="0"/>
         <v>'visitantes' : r_val['visitantes'],</v>
       </c>
-      <c r="L38" t="str">
+      <c r="M38" t="str">
         <f t="shared" si="1"/>
         <v>'cap5': cap5,</v>
       </c>
-      <c r="M38" t="s">
+      <c r="N38" t="s">
         <v>558</v>
       </c>
-      <c r="N38" t="str">
+      <c r="O38" t="str">
         <f t="shared" si="2"/>
         <v>img_path_cap5 = os.path.join(IMAGES_PATH, r_val['cap5'])</v>
       </c>
-      <c r="O38" t="str">
+      <c r="P38" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_cap5):</v>
       </c>
-      <c r="P38" t="str">
+      <c r="Q38" t="str">
         <f t="shared" si="4"/>
         <v>cap5 = InlineImage(docx_tpl, img_path_cap5, height=Mm(60))</v>
       </c>
-      <c r="Q38" t="s">
+      <c r="R38" t="s">
         <v>560</v>
       </c>
-      <c r="R38" t="str">
+      <c r="S38" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['cap5']}')</v>
       </c>
-      <c r="S38" t="str">
+      <c r="T38" t="str">
         <f t="shared" si="6"/>
         <v>cap5 = ''</v>
       </c>
-      <c r="T38" t="s">
+      <c r="U38" t="s">
         <v>559</v>
       </c>
-      <c r="U38" t="str">
+      <c r="V38" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['cap5']}: {e}')</v>
       </c>
-      <c r="V38" t="str">
+      <c r="W38" t="str">
         <f t="shared" si="8"/>
         <v>cap5 = ''</v>
       </c>
     </row>
-    <row r="39" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C39" t="s">
         <v>843</v>
       </c>
@@ -36329,58 +36438,61 @@
         <v>60</v>
       </c>
       <c r="I39" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J39" t="s">
         <v>172</v>
       </c>
-      <c r="J39" t="s">
+      <c r="K39" t="s">
         <v>262</v>
       </c>
-      <c r="K39" t="str">
+      <c r="L39" t="str">
         <f t="shared" si="0"/>
         <v>'proveedores' : r_val['proveedores'],</v>
       </c>
-      <c r="L39" t="str">
+      <c r="M39" t="str">
         <f t="shared" si="1"/>
         <v>'cap6': cap6,</v>
       </c>
-      <c r="M39" t="s">
+      <c r="N39" t="s">
         <v>558</v>
       </c>
-      <c r="N39" t="str">
+      <c r="O39" t="str">
         <f t="shared" si="2"/>
         <v>img_path_cap6 = os.path.join(IMAGES_PATH, r_val['cap6'])</v>
       </c>
-      <c r="O39" t="str">
+      <c r="P39" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_cap6):</v>
       </c>
-      <c r="P39" t="str">
+      <c r="Q39" t="str">
         <f t="shared" si="4"/>
         <v>cap6 = InlineImage(docx_tpl, img_path_cap6, height=Mm(60))</v>
       </c>
-      <c r="Q39" t="s">
+      <c r="R39" t="s">
         <v>560</v>
       </c>
-      <c r="R39" t="str">
+      <c r="S39" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['cap6']}')</v>
       </c>
-      <c r="S39" t="str">
+      <c r="T39" t="str">
         <f t="shared" si="6"/>
         <v>cap6 = ''</v>
       </c>
-      <c r="T39" t="s">
+      <c r="U39" t="s">
         <v>559</v>
       </c>
-      <c r="U39" t="str">
+      <c r="V39" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['cap6']}: {e}')</v>
       </c>
-      <c r="V39" t="str">
+      <c r="W39" t="str">
         <f t="shared" si="8"/>
         <v>cap6 = ''</v>
       </c>
     </row>
-    <row r="40" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C40" t="s">
         <v>843</v>
       </c>
@@ -36400,58 +36512,61 @@
         <v>60</v>
       </c>
       <c r="I40" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J40" t="s">
         <v>173</v>
       </c>
-      <c r="J40" t="s">
+      <c r="K40" t="s">
         <v>263</v>
       </c>
-      <c r="K40" t="str">
+      <c r="L40" t="str">
         <f t="shared" si="0"/>
         <v>'dias' : r_val['dias'],</v>
       </c>
-      <c r="L40" t="str">
+      <c r="M40" t="str">
         <f t="shared" si="1"/>
         <v>'cap7': cap7,</v>
       </c>
-      <c r="M40" t="s">
+      <c r="N40" t="s">
         <v>558</v>
       </c>
-      <c r="N40" t="str">
+      <c r="O40" t="str">
         <f t="shared" si="2"/>
         <v>img_path_cap7 = os.path.join(IMAGES_PATH, r_val['cap7'])</v>
       </c>
-      <c r="O40" t="str">
+      <c r="P40" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_cap7):</v>
       </c>
-      <c r="P40" t="str">
+      <c r="Q40" t="str">
         <f t="shared" si="4"/>
         <v>cap7 = InlineImage(docx_tpl, img_path_cap7, height=Mm(60))</v>
       </c>
-      <c r="Q40" t="s">
+      <c r="R40" t="s">
         <v>560</v>
       </c>
-      <c r="R40" t="str">
+      <c r="S40" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['cap7']}')</v>
       </c>
-      <c r="S40" t="str">
+      <c r="T40" t="str">
         <f t="shared" si="6"/>
         <v>cap7 = ''</v>
       </c>
-      <c r="T40" t="s">
+      <c r="U40" t="s">
         <v>559</v>
       </c>
-      <c r="U40" t="str">
+      <c r="V40" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['cap7']}: {e}')</v>
       </c>
-      <c r="V40" t="str">
+      <c r="W40" t="str">
         <f t="shared" si="8"/>
         <v>cap7 = ''</v>
       </c>
     </row>
-    <row r="41" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C41" t="s">
         <v>843</v>
       </c>
@@ -36471,58 +36586,61 @@
         <v>60</v>
       </c>
       <c r="I41" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J41" t="s">
         <v>174</v>
       </c>
-      <c r="J41" t="s">
+      <c r="K41" t="s">
         <v>264</v>
       </c>
-      <c r="K41" t="str">
+      <c r="L41" t="str">
         <f t="shared" si="0"/>
         <v>'horario' : r_val['horario'],</v>
       </c>
-      <c r="L41" t="str">
+      <c r="M41" t="str">
         <f t="shared" si="1"/>
         <v>'cap8': cap8,</v>
       </c>
-      <c r="M41" t="s">
+      <c r="N41" t="s">
         <v>558</v>
       </c>
-      <c r="N41" t="str">
+      <c r="O41" t="str">
         <f t="shared" si="2"/>
         <v>img_path_cap8 = os.path.join(IMAGES_PATH, r_val['cap8'])</v>
       </c>
-      <c r="O41" t="str">
+      <c r="P41" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_cap8):</v>
       </c>
-      <c r="P41" t="str">
+      <c r="Q41" t="str">
         <f t="shared" si="4"/>
         <v>cap8 = InlineImage(docx_tpl, img_path_cap8, height=Mm(60))</v>
       </c>
-      <c r="Q41" t="s">
+      <c r="R41" t="s">
         <v>560</v>
       </c>
-      <c r="R41" t="str">
+      <c r="S41" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['cap8']}')</v>
       </c>
-      <c r="S41" t="str">
+      <c r="T41" t="str">
         <f t="shared" si="6"/>
         <v>cap8 = ''</v>
       </c>
-      <c r="T41" t="s">
+      <c r="U41" t="s">
         <v>559</v>
       </c>
-      <c r="U41" t="str">
+      <c r="V41" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['cap8']}: {e}')</v>
       </c>
-      <c r="V41" t="str">
+      <c r="W41" t="str">
         <f t="shared" si="8"/>
         <v>cap8 = ''</v>
       </c>
     </row>
-    <row r="42" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C42" t="s">
         <v>843</v>
       </c>
@@ -36542,58 +36660,61 @@
         <v>60</v>
       </c>
       <c r="I42" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J42" t="s">
         <v>175</v>
       </c>
-      <c r="J42" t="s">
+      <c r="K42" t="s">
         <v>265</v>
       </c>
-      <c r="K42" t="str">
+      <c r="L42" t="str">
         <f t="shared" si="0"/>
         <v>'senial_informacion' : r_val['senial_informacion'],</v>
       </c>
-      <c r="L42" t="str">
+      <c r="M42" t="str">
         <f t="shared" si="1"/>
         <v>'cap9': cap9,</v>
       </c>
-      <c r="M42" t="s">
+      <c r="N42" t="s">
         <v>558</v>
       </c>
-      <c r="N42" t="str">
+      <c r="O42" t="str">
         <f t="shared" si="2"/>
         <v>img_path_cap9 = os.path.join(IMAGES_PATH, r_val['cap9'])</v>
       </c>
-      <c r="O42" t="str">
+      <c r="P42" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_cap9):</v>
       </c>
-      <c r="P42" t="str">
+      <c r="Q42" t="str">
         <f t="shared" si="4"/>
         <v>cap9 = InlineImage(docx_tpl, img_path_cap9, height=Mm(60))</v>
       </c>
-      <c r="Q42" t="s">
+      <c r="R42" t="s">
         <v>560</v>
       </c>
-      <c r="R42" t="str">
+      <c r="S42" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['cap9']}')</v>
       </c>
-      <c r="S42" t="str">
+      <c r="T42" t="str">
         <f t="shared" si="6"/>
         <v>cap9 = ''</v>
       </c>
-      <c r="T42" t="s">
+      <c r="U42" t="s">
         <v>559</v>
       </c>
-      <c r="U42" t="str">
+      <c r="V42" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['cap9']}: {e}')</v>
       </c>
-      <c r="V42" t="str">
+      <c r="W42" t="str">
         <f t="shared" si="8"/>
         <v>cap9 = ''</v>
       </c>
     </row>
-    <row r="43" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C43" t="s">
         <v>843</v>
       </c>
@@ -36613,58 +36734,61 @@
         <v>60</v>
       </c>
       <c r="I43" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J43" t="s">
         <v>410</v>
       </c>
-      <c r="J43" t="s">
+      <c r="K43" t="s">
         <v>266</v>
       </c>
-      <c r="K43" t="str">
+      <c r="L43" t="str">
         <f t="shared" si="0"/>
         <v>'botiquin_emer' : r_val['botiquin_emer'],</v>
       </c>
-      <c r="L43" t="str">
+      <c r="M43" t="str">
         <f t="shared" si="1"/>
         <v>'cap10': cap10,</v>
       </c>
-      <c r="M43" t="s">
+      <c r="N43" t="s">
         <v>558</v>
       </c>
-      <c r="N43" t="str">
+      <c r="O43" t="str">
         <f t="shared" si="2"/>
         <v>img_path_cap10 = os.path.join(IMAGES_PATH, r_val['cap10'])</v>
       </c>
-      <c r="O43" t="str">
+      <c r="P43" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_cap10):</v>
       </c>
-      <c r="P43" t="str">
+      <c r="Q43" t="str">
         <f t="shared" si="4"/>
         <v>cap10 = InlineImage(docx_tpl, img_path_cap10, height=Mm(60))</v>
       </c>
-      <c r="Q43" t="s">
+      <c r="R43" t="s">
         <v>560</v>
       </c>
-      <c r="R43" t="str">
+      <c r="S43" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['cap10']}')</v>
       </c>
-      <c r="S43" t="str">
+      <c r="T43" t="str">
         <f t="shared" si="6"/>
         <v>cap10 = ''</v>
       </c>
-      <c r="T43" t="s">
+      <c r="U43" t="s">
         <v>559</v>
       </c>
-      <c r="U43" t="str">
+      <c r="V43" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['cap10']}: {e}')</v>
       </c>
-      <c r="V43" t="str">
+      <c r="W43" t="str">
         <f t="shared" si="8"/>
         <v>cap10 = ''</v>
       </c>
     </row>
-    <row r="44" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C44" t="s">
         <v>843</v>
       </c>
@@ -36684,58 +36808,61 @@
         <v>60</v>
       </c>
       <c r="I44" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J44" t="s">
         <v>176</v>
       </c>
-      <c r="J44" t="s">
+      <c r="K44" t="s">
         <v>267</v>
       </c>
-      <c r="K44" t="str">
+      <c r="L44" t="str">
         <f t="shared" si="0"/>
         <v>'ubicación_bot' : r_val['ubicación_bot'],</v>
       </c>
-      <c r="L44" t="str">
+      <c r="M44" t="str">
         <f t="shared" si="1"/>
         <v>'cap11': cap11,</v>
       </c>
-      <c r="M44" t="s">
+      <c r="N44" t="s">
         <v>558</v>
       </c>
-      <c r="N44" t="str">
+      <c r="O44" t="str">
         <f t="shared" si="2"/>
         <v>img_path_cap11 = os.path.join(IMAGES_PATH, r_val['cap11'])</v>
       </c>
-      <c r="O44" t="str">
+      <c r="P44" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_cap11):</v>
       </c>
-      <c r="P44" t="str">
+      <c r="Q44" t="str">
         <f t="shared" si="4"/>
         <v>cap11 = InlineImage(docx_tpl, img_path_cap11, height=Mm(60))</v>
       </c>
-      <c r="Q44" t="s">
+      <c r="R44" t="s">
         <v>560</v>
       </c>
-      <c r="R44" t="str">
+      <c r="S44" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['cap11']}')</v>
       </c>
-      <c r="S44" t="str">
+      <c r="T44" t="str">
         <f t="shared" si="6"/>
         <v>cap11 = ''</v>
       </c>
-      <c r="T44" t="s">
+      <c r="U44" t="s">
         <v>559</v>
       </c>
-      <c r="U44" t="str">
+      <c r="V44" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['cap11']}: {e}')</v>
       </c>
-      <c r="V44" t="str">
+      <c r="W44" t="str">
         <f t="shared" si="8"/>
         <v>cap11 = ''</v>
       </c>
     </row>
-    <row r="45" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C45" t="s">
         <v>843</v>
       </c>
@@ -36755,58 +36882,61 @@
         <v>60</v>
       </c>
       <c r="I45" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J45" t="s">
         <v>177</v>
       </c>
-      <c r="J45" t="s">
+      <c r="K45" t="s">
         <v>268</v>
       </c>
-      <c r="K45" t="str">
+      <c r="L45" t="str">
         <f t="shared" si="0"/>
         <v>'extintor' : r_val['extintor'],</v>
       </c>
-      <c r="L45" t="str">
+      <c r="M45" t="str">
         <f t="shared" si="1"/>
         <v>'cap12': cap12,</v>
       </c>
-      <c r="M45" t="s">
+      <c r="N45" t="s">
         <v>558</v>
       </c>
-      <c r="N45" t="str">
+      <c r="O45" t="str">
         <f t="shared" si="2"/>
         <v>img_path_cap12 = os.path.join(IMAGES_PATH, r_val['cap12'])</v>
       </c>
-      <c r="O45" t="str">
+      <c r="P45" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_cap12):</v>
       </c>
-      <c r="P45" t="str">
+      <c r="Q45" t="str">
         <f t="shared" si="4"/>
         <v>cap12 = InlineImage(docx_tpl, img_path_cap12, height=Mm(60))</v>
       </c>
-      <c r="Q45" t="s">
+      <c r="R45" t="s">
         <v>560</v>
       </c>
-      <c r="R45" t="str">
+      <c r="S45" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['cap12']}')</v>
       </c>
-      <c r="S45" t="str">
+      <c r="T45" t="str">
         <f t="shared" si="6"/>
         <v>cap12 = ''</v>
       </c>
-      <c r="T45" t="s">
+      <c r="U45" t="s">
         <v>559</v>
       </c>
-      <c r="U45" t="str">
+      <c r="V45" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['cap12']}: {e}')</v>
       </c>
-      <c r="V45" t="str">
+      <c r="W45" t="str">
         <f t="shared" si="8"/>
         <v>cap12 = ''</v>
       </c>
     </row>
-    <row r="46" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C46" t="s">
         <v>843</v>
       </c>
@@ -36826,58 +36956,61 @@
         <v>60</v>
       </c>
       <c r="I46" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J46" t="s">
         <v>178</v>
       </c>
-      <c r="J46" t="s">
+      <c r="K46" t="s">
         <v>269</v>
       </c>
-      <c r="K46" t="str">
+      <c r="L46" t="str">
         <f t="shared" si="0"/>
         <v>'ubicación_ext' : r_val['ubicación_ext'],</v>
       </c>
-      <c r="L46" t="str">
+      <c r="M46" t="str">
         <f t="shared" si="1"/>
         <v>'sim1': sim1,</v>
       </c>
-      <c r="M46" t="s">
+      <c r="N46" t="s">
         <v>558</v>
       </c>
-      <c r="N46" t="str">
+      <c r="O46" t="str">
         <f t="shared" si="2"/>
         <v>img_path_sim1 = os.path.join(IMAGES_PATH, r_val['sim1'])</v>
       </c>
-      <c r="O46" t="str">
+      <c r="P46" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_sim1):</v>
       </c>
-      <c r="P46" t="str">
+      <c r="Q46" t="str">
         <f t="shared" si="4"/>
         <v>sim1 = InlineImage(docx_tpl, img_path_sim1, height=Mm(60))</v>
       </c>
-      <c r="Q46" t="s">
+      <c r="R46" t="s">
         <v>560</v>
       </c>
-      <c r="R46" t="str">
+      <c r="S46" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['sim1']}')</v>
       </c>
-      <c r="S46" t="str">
+      <c r="T46" t="str">
         <f t="shared" si="6"/>
         <v>sim1 = ''</v>
       </c>
-      <c r="T46" t="s">
+      <c r="U46" t="s">
         <v>559</v>
       </c>
-      <c r="U46" t="str">
+      <c r="V46" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['sim1']}: {e}')</v>
       </c>
-      <c r="V46" t="str">
+      <c r="W46" t="str">
         <f t="shared" si="8"/>
         <v>sim1 = ''</v>
       </c>
     </row>
-    <row r="47" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C47" t="s">
         <v>843</v>
       </c>
@@ -36897,58 +37030,61 @@
         <v>60</v>
       </c>
       <c r="I47" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J47" t="s">
         <v>697</v>
       </c>
-      <c r="J47" t="s">
+      <c r="K47" t="s">
         <v>699</v>
       </c>
-      <c r="K47" t="str">
-        <f t="shared" ref="K47:K78" si="9">+_xlfn.CONCAT("'",I47,"' : r_val['",I47,"'],")</f>
+      <c r="L47" t="str">
+        <f t="shared" ref="L47:L78" si="9">+_xlfn.CONCAT("'",J47,"' : r_val['",J47,"'],")</f>
         <v>'ext_pqs' : r_val['ext_pqs'],</v>
       </c>
-      <c r="L47" t="str">
+      <c r="M47" t="str">
         <f t="shared" si="1"/>
         <v>'sim2': sim2,</v>
       </c>
-      <c r="M47" t="s">
+      <c r="N47" t="s">
         <v>558</v>
       </c>
-      <c r="N47" t="str">
+      <c r="O47" t="str">
         <f t="shared" si="2"/>
         <v>img_path_sim2 = os.path.join(IMAGES_PATH, r_val['sim2'])</v>
       </c>
-      <c r="O47" t="str">
+      <c r="P47" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_sim2):</v>
       </c>
-      <c r="P47" t="str">
+      <c r="Q47" t="str">
         <f t="shared" si="4"/>
         <v>sim2 = InlineImage(docx_tpl, img_path_sim2, height=Mm(60))</v>
       </c>
-      <c r="Q47" t="s">
+      <c r="R47" t="s">
         <v>560</v>
       </c>
-      <c r="R47" t="str">
+      <c r="S47" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['sim2']}')</v>
       </c>
-      <c r="S47" t="str">
+      <c r="T47" t="str">
         <f t="shared" si="6"/>
         <v>sim2 = ''</v>
       </c>
-      <c r="T47" t="s">
+      <c r="U47" t="s">
         <v>559</v>
       </c>
-      <c r="U47" t="str">
+      <c r="V47" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['sim2']}: {e}')</v>
       </c>
-      <c r="V47" t="str">
+      <c r="W47" t="str">
         <f t="shared" si="8"/>
         <v>sim2 = ''</v>
       </c>
     </row>
-    <row r="48" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C48" t="s">
         <v>843</v>
       </c>
@@ -36968,58 +37104,61 @@
         <v>60</v>
       </c>
       <c r="I48" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J48" t="s">
         <v>698</v>
       </c>
-      <c r="J48" t="s">
+      <c r="K48" t="s">
         <v>700</v>
       </c>
-      <c r="K48" t="str">
+      <c r="L48" t="str">
         <f t="shared" si="9"/>
         <v>'ext_co2' : r_val['ext_co2'],</v>
       </c>
-      <c r="L48" t="str">
+      <c r="M48" t="str">
         <f t="shared" si="1"/>
         <v>'sim3': sim3,</v>
       </c>
-      <c r="M48" t="s">
+      <c r="N48" t="s">
         <v>558</v>
       </c>
-      <c r="N48" t="str">
+      <c r="O48" t="str">
         <f t="shared" si="2"/>
         <v>img_path_sim3 = os.path.join(IMAGES_PATH, r_val['sim3'])</v>
       </c>
-      <c r="O48" t="str">
+      <c r="P48" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_sim3):</v>
       </c>
-      <c r="P48" t="str">
+      <c r="Q48" t="str">
         <f t="shared" si="4"/>
         <v>sim3 = InlineImage(docx_tpl, img_path_sim3, height=Mm(60))</v>
       </c>
-      <c r="Q48" t="s">
+      <c r="R48" t="s">
         <v>560</v>
       </c>
-      <c r="R48" t="str">
+      <c r="S48" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['sim3']}')</v>
       </c>
-      <c r="S48" t="str">
+      <c r="T48" t="str">
         <f t="shared" si="6"/>
         <v>sim3 = ''</v>
       </c>
-      <c r="T48" t="s">
+      <c r="U48" t="s">
         <v>559</v>
       </c>
-      <c r="U48" t="str">
+      <c r="V48" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['sim3']}: {e}')</v>
       </c>
-      <c r="V48" t="str">
+      <c r="W48" t="str">
         <f t="shared" si="8"/>
         <v>sim3 = ''</v>
       </c>
     </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C49" t="s">
         <v>843</v>
       </c>
@@ -37039,58 +37178,61 @@
         <v>60</v>
       </c>
       <c r="I49" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J49" t="s">
         <v>179</v>
       </c>
-      <c r="J49" t="s">
+      <c r="K49" t="s">
         <v>270</v>
       </c>
-      <c r="K49" t="str">
+      <c r="L49" t="str">
         <f t="shared" si="9"/>
         <v>'paros_emergencia' : r_val['paros_emergencia'],</v>
       </c>
-      <c r="L49" t="str">
+      <c r="M49" t="str">
         <f t="shared" si="1"/>
         <v>'sim4': sim4,</v>
       </c>
-      <c r="M49" t="s">
+      <c r="N49" t="s">
         <v>558</v>
       </c>
-      <c r="N49" t="str">
+      <c r="O49" t="str">
         <f t="shared" si="2"/>
         <v>img_path_sim4 = os.path.join(IMAGES_PATH, r_val['sim4'])</v>
       </c>
-      <c r="O49" t="str">
+      <c r="P49" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_sim4):</v>
       </c>
-      <c r="P49" t="str">
+      <c r="Q49" t="str">
         <f t="shared" si="4"/>
         <v>sim4 = InlineImage(docx_tpl, img_path_sim4, height=Mm(60))</v>
       </c>
-      <c r="Q49" t="s">
+      <c r="R49" t="s">
         <v>560</v>
       </c>
-      <c r="R49" t="str">
+      <c r="S49" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['sim4']}')</v>
       </c>
-      <c r="S49" t="str">
+      <c r="T49" t="str">
         <f t="shared" si="6"/>
         <v>sim4 = ''</v>
       </c>
-      <c r="T49" t="s">
+      <c r="U49" t="s">
         <v>559</v>
       </c>
-      <c r="U49" t="str">
+      <c r="V49" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['sim4']}: {e}')</v>
       </c>
-      <c r="V49" t="str">
+      <c r="W49" t="str">
         <f t="shared" si="8"/>
         <v>sim4 = ''</v>
       </c>
     </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C50" t="s">
         <v>843</v>
       </c>
@@ -37110,58 +37252,61 @@
         <v>60</v>
       </c>
       <c r="I50" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J50" t="s">
         <v>180</v>
       </c>
-      <c r="J50" t="s">
+      <c r="K50" t="s">
         <v>271</v>
       </c>
-      <c r="K50" t="str">
+      <c r="L50" t="str">
         <f t="shared" si="9"/>
         <v>'ubicación_pe' : r_val['ubicación_pe'],</v>
       </c>
-      <c r="L50" t="str">
+      <c r="M50" t="str">
         <f t="shared" si="1"/>
         <v>'sim5': sim5,</v>
       </c>
-      <c r="M50" t="s">
+      <c r="N50" t="s">
         <v>558</v>
       </c>
-      <c r="N50" t="str">
+      <c r="O50" t="str">
         <f t="shared" si="2"/>
         <v>img_path_sim5 = os.path.join(IMAGES_PATH, r_val['sim5'])</v>
       </c>
-      <c r="O50" t="str">
+      <c r="P50" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_sim5):</v>
       </c>
-      <c r="P50" t="str">
+      <c r="Q50" t="str">
         <f t="shared" si="4"/>
         <v>sim5 = InlineImage(docx_tpl, img_path_sim5, height=Mm(60))</v>
       </c>
-      <c r="Q50" t="s">
+      <c r="R50" t="s">
         <v>560</v>
       </c>
-      <c r="R50" t="str">
+      <c r="S50" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['sim5']}')</v>
       </c>
-      <c r="S50" t="str">
+      <c r="T50" t="str">
         <f t="shared" si="6"/>
         <v>sim5 = ''</v>
       </c>
-      <c r="T50" t="s">
+      <c r="U50" t="s">
         <v>559</v>
       </c>
-      <c r="U50" t="str">
+      <c r="V50" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['sim5']}: {e}')</v>
       </c>
-      <c r="V50" t="str">
+      <c r="W50" t="str">
         <f t="shared" si="8"/>
         <v>sim5 = ''</v>
       </c>
     </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C51" t="s">
         <v>843</v>
       </c>
@@ -37181,58 +37326,61 @@
         <v>60</v>
       </c>
       <c r="I51" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J51" t="s">
         <v>399</v>
       </c>
-      <c r="J51" t="s">
+      <c r="K51" t="s">
         <v>400</v>
       </c>
-      <c r="K51" t="str">
+      <c r="L51" t="str">
         <f t="shared" si="9"/>
         <v>'venteo_sist' : r_val['venteo_sist'],</v>
       </c>
-      <c r="L51" t="str">
+      <c r="M51" t="str">
         <f>+_xlfn.CONCAT("'",E51,"': ",E51,",")</f>
         <v>'sim6': sim6,</v>
       </c>
-      <c r="M51" t="s">
+      <c r="N51" t="s">
         <v>558</v>
       </c>
-      <c r="N51" t="str">
+      <c r="O51" t="str">
         <f t="shared" si="2"/>
         <v>img_path_sim6 = os.path.join(IMAGES_PATH, r_val['sim6'])</v>
       </c>
-      <c r="O51" t="str">
+      <c r="P51" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_sim6):</v>
       </c>
-      <c r="P51" t="str">
+      <c r="Q51" t="str">
         <f t="shared" si="4"/>
         <v>sim6 = InlineImage(docx_tpl, img_path_sim6, height=Mm(60))</v>
       </c>
-      <c r="Q51" t="s">
+      <c r="R51" t="s">
         <v>560</v>
       </c>
-      <c r="R51" t="str">
+      <c r="S51" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['sim6']}')</v>
       </c>
-      <c r="S51" t="str">
+      <c r="T51" t="str">
         <f t="shared" si="6"/>
         <v>sim6 = ''</v>
       </c>
-      <c r="T51" t="s">
+      <c r="U51" t="s">
         <v>559</v>
       </c>
-      <c r="U51" t="str">
+      <c r="V51" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['sim6']}: {e}')</v>
       </c>
-      <c r="V51" t="str">
+      <c r="W51" t="str">
         <f t="shared" si="8"/>
         <v>sim6 = ''</v>
       </c>
     </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C52" t="s">
         <v>843</v>
       </c>
@@ -37252,58 +37400,61 @@
         <v>60</v>
       </c>
       <c r="I52" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J52" t="s">
         <v>182</v>
       </c>
-      <c r="J52" t="s">
+      <c r="K52" t="s">
         <v>273</v>
       </c>
-      <c r="K52" t="str">
+      <c r="L52" t="str">
         <f t="shared" si="9"/>
         <v>'ubicación_vent' : r_val['ubicación_vent'],</v>
       </c>
-      <c r="L52" t="str">
+      <c r="M52" t="str">
         <f t="shared" si="1"/>
         <v>'techo': techo,</v>
       </c>
-      <c r="M52" t="s">
+      <c r="N52" t="s">
         <v>558</v>
       </c>
-      <c r="N52" t="str">
+      <c r="O52" t="str">
         <f t="shared" si="2"/>
         <v>img_path_techo = os.path.join(IMAGES_PATH, r_val['techo'])</v>
       </c>
-      <c r="O52" t="str">
+      <c r="P52" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_techo):</v>
       </c>
-      <c r="P52" t="str">
+      <c r="Q52" t="str">
         <f t="shared" si="4"/>
         <v>techo = InlineImage(docx_tpl, img_path_techo, height=Mm(60))</v>
       </c>
-      <c r="Q52" t="s">
+      <c r="R52" t="s">
         <v>560</v>
       </c>
-      <c r="R52" t="str">
+      <c r="S52" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['techo']}')</v>
       </c>
-      <c r="S52" t="str">
+      <c r="T52" t="str">
         <f t="shared" si="6"/>
         <v>techo = ''</v>
       </c>
-      <c r="T52" t="s">
+      <c r="U52" t="s">
         <v>559</v>
       </c>
-      <c r="U52" t="str">
+      <c r="V52" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['techo']}: {e}')</v>
       </c>
-      <c r="V52" t="str">
+      <c r="W52" t="str">
         <f t="shared" si="8"/>
         <v>techo = ''</v>
       </c>
     </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C53" t="s">
         <v>843</v>
       </c>
@@ -37320,61 +37471,64 @@
         <v>386</v>
       </c>
       <c r="H53">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I53" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J53" t="s">
         <v>411</v>
       </c>
-      <c r="J53" t="s">
+      <c r="K53" t="s">
         <v>412</v>
       </c>
-      <c r="K53" t="str">
+      <c r="L53" t="str">
         <f t="shared" si="9"/>
         <v>'planta_emer' : r_val['planta_emer'],</v>
       </c>
-      <c r="L53" t="str">
+      <c r="M53" t="str">
         <f t="shared" si="1"/>
         <v>'pisos': pisos,</v>
       </c>
-      <c r="M53" t="s">
+      <c r="N53" t="s">
         <v>558</v>
       </c>
-      <c r="N53" t="str">
+      <c r="O53" t="str">
         <f t="shared" si="2"/>
         <v>img_path_pisos = os.path.join(IMAGES_PATH, r_val['pisos'])</v>
       </c>
-      <c r="O53" t="str">
+      <c r="P53" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_pisos):</v>
       </c>
-      <c r="P53" t="str">
+      <c r="Q53" t="str">
         <f t="shared" si="4"/>
-        <v>pisos = InlineImage(docx_tpl, img_path_pisos, height=Mm(60))</v>
-      </c>
-      <c r="Q53" t="s">
+        <v>pisos = InlineImage(docx_tpl, img_path_pisos, height=Mm(50))</v>
+      </c>
+      <c r="R53" t="s">
         <v>560</v>
       </c>
-      <c r="R53" t="str">
+      <c r="S53" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['pisos']}')</v>
       </c>
-      <c r="S53" t="str">
+      <c r="T53" t="str">
         <f t="shared" si="6"/>
         <v>pisos = ''</v>
       </c>
-      <c r="T53" t="s">
+      <c r="U53" t="s">
         <v>559</v>
       </c>
-      <c r="U53" t="str">
+      <c r="V53" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['pisos']}: {e}')</v>
       </c>
-      <c r="V53" t="str">
+      <c r="W53" t="str">
         <f t="shared" si="8"/>
         <v>pisos = ''</v>
       </c>
     </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C54" t="s">
         <v>843</v>
       </c>
@@ -37388,61 +37542,64 @@
         <v>387</v>
       </c>
       <c r="H54">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I54" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J54" t="s">
         <v>183</v>
       </c>
-      <c r="J54" t="s">
+      <c r="K54" t="s">
         <v>275</v>
       </c>
-      <c r="K54" t="str">
+      <c r="L54" t="str">
         <f t="shared" si="9"/>
         <v>'ubicación_plant' : r_val['ubicación_plant'],</v>
       </c>
-      <c r="L54" t="str">
+      <c r="M54" t="str">
         <f t="shared" si="1"/>
         <v>'puerta': puerta,</v>
       </c>
-      <c r="M54" t="s">
+      <c r="N54" t="s">
         <v>558</v>
       </c>
-      <c r="N54" t="str">
+      <c r="O54" t="str">
         <f t="shared" si="2"/>
         <v>img_path_puerta = os.path.join(IMAGES_PATH, r_val['puerta'])</v>
       </c>
-      <c r="O54" t="str">
+      <c r="P54" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_puerta):</v>
       </c>
-      <c r="P54" t="str">
+      <c r="Q54" t="str">
         <f t="shared" si="4"/>
-        <v>puerta = InlineImage(docx_tpl, img_path_puerta, height=Mm(60))</v>
-      </c>
-      <c r="Q54" t="s">
+        <v>puerta = InlineImage(docx_tpl, img_path_puerta, height=Mm(50))</v>
+      </c>
+      <c r="R54" t="s">
         <v>560</v>
       </c>
-      <c r="R54" t="str">
+      <c r="S54" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['puerta']}')</v>
       </c>
-      <c r="S54" t="str">
+      <c r="T54" t="str">
         <f t="shared" si="6"/>
         <v>puerta = ''</v>
       </c>
-      <c r="T54" t="s">
+      <c r="U54" t="s">
         <v>559</v>
       </c>
-      <c r="U54" t="str">
+      <c r="V54" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['puerta']}: {e}')</v>
       </c>
-      <c r="V54" t="str">
+      <c r="W54" t="str">
         <f t="shared" si="8"/>
         <v>puerta = ''</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C55" t="s">
         <v>843</v>
       </c>
@@ -37456,61 +37613,64 @@
         <v>388</v>
       </c>
       <c r="H55">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I55" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J55" t="s">
         <v>408</v>
       </c>
-      <c r="J55" t="s">
+      <c r="K55" t="s">
         <v>409</v>
       </c>
-      <c r="K55" t="str">
+      <c r="L55" t="str">
         <f t="shared" si="9"/>
         <v>'met_alarma' : r_val['met_alarma'],</v>
       </c>
-      <c r="L55" t="str">
+      <c r="M55" t="str">
         <f t="shared" si="1"/>
         <v>'estantes': estantes,</v>
       </c>
-      <c r="M55" t="s">
+      <c r="N55" t="s">
         <v>558</v>
       </c>
-      <c r="N55" t="str">
+      <c r="O55" t="str">
         <f t="shared" si="2"/>
         <v>img_path_estantes = os.path.join(IMAGES_PATH, r_val['estantes'])</v>
       </c>
-      <c r="O55" t="str">
+      <c r="P55" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_estantes):</v>
       </c>
-      <c r="P55" t="str">
+      <c r="Q55" t="str">
         <f t="shared" si="4"/>
-        <v>estantes = InlineImage(docx_tpl, img_path_estantes, height=Mm(60))</v>
-      </c>
-      <c r="Q55" t="s">
+        <v>estantes = InlineImage(docx_tpl, img_path_estantes, height=Mm(50))</v>
+      </c>
+      <c r="R55" t="s">
         <v>560</v>
       </c>
-      <c r="R55" t="str">
+      <c r="S55" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['estantes']}')</v>
       </c>
-      <c r="S55" t="str">
+      <c r="T55" t="str">
         <f t="shared" si="6"/>
         <v>estantes = ''</v>
       </c>
-      <c r="T55" t="s">
+      <c r="U55" t="s">
         <v>559</v>
       </c>
-      <c r="U55" t="str">
+      <c r="V55" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['estantes']}: {e}')</v>
       </c>
-      <c r="V55" t="str">
+      <c r="W55" t="str">
         <f t="shared" si="8"/>
         <v>estantes = ''</v>
       </c>
     </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C56" t="s">
         <v>843</v>
       </c>
@@ -37527,61 +37687,64 @@
         <v>294</v>
       </c>
       <c r="H56">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I56" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J56" t="s">
         <v>7</v>
       </c>
-      <c r="J56" t="s">
+      <c r="K56" t="s">
         <v>277</v>
       </c>
-      <c r="K56" t="str">
+      <c r="L56" t="str">
         <f t="shared" si="9"/>
         <v>'tipo_alarma' : r_val['tipo_alarma'],</v>
       </c>
-      <c r="L56" t="str">
+      <c r="M56" t="str">
         <f t="shared" si="1"/>
         <v>'site': site,</v>
       </c>
-      <c r="M56" t="s">
+      <c r="N56" t="s">
         <v>558</v>
       </c>
-      <c r="N56" t="str">
+      <c r="O56" t="str">
         <f t="shared" si="2"/>
         <v>img_path_site = os.path.join(IMAGES_PATH, r_val['site'])</v>
       </c>
-      <c r="O56" t="str">
+      <c r="P56" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_site):</v>
       </c>
-      <c r="P56" t="str">
+      <c r="Q56" t="str">
         <f t="shared" si="4"/>
-        <v>site = InlineImage(docx_tpl, img_path_site, height=Mm(60))</v>
-      </c>
-      <c r="Q56" t="s">
+        <v>site = InlineImage(docx_tpl, img_path_site, height=Mm(50))</v>
+      </c>
+      <c r="R56" t="s">
         <v>560</v>
       </c>
-      <c r="R56" t="str">
+      <c r="S56" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['site']}')</v>
       </c>
-      <c r="S56" t="str">
+      <c r="T56" t="str">
         <f t="shared" si="6"/>
         <v>site = ''</v>
       </c>
-      <c r="T56" t="s">
+      <c r="U56" t="s">
         <v>559</v>
       </c>
-      <c r="U56" t="str">
+      <c r="V56" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['site']}: {e}')</v>
       </c>
-      <c r="V56" t="str">
+      <c r="W56" t="str">
         <f t="shared" si="8"/>
         <v>site = ''</v>
       </c>
     </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C57" t="s">
         <v>843</v>
       </c>
@@ -37598,61 +37761,64 @@
         <v>389</v>
       </c>
       <c r="H57">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I57" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J57" t="s">
         <v>701</v>
       </c>
-      <c r="J57" t="s">
+      <c r="K57" t="s">
         <v>702</v>
       </c>
-      <c r="K57" t="str">
+      <c r="L57" t="str">
         <f t="shared" si="9"/>
         <v>'silbato' : r_val['silbato'],</v>
       </c>
-      <c r="L57" t="str">
+      <c r="M57" t="str">
         <f t="shared" si="1"/>
         <v>'dh': dh,</v>
       </c>
-      <c r="M57" t="s">
+      <c r="N57" t="s">
         <v>558</v>
       </c>
-      <c r="N57" t="str">
+      <c r="O57" t="str">
         <f t="shared" si="2"/>
         <v>img_path_dh = os.path.join(IMAGES_PATH, r_val['dh'])</v>
       </c>
-      <c r="O57" t="str">
+      <c r="P57" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_dh):</v>
       </c>
-      <c r="P57" t="str">
+      <c r="Q57" t="str">
         <f t="shared" si="4"/>
-        <v>dh = InlineImage(docx_tpl, img_path_dh, height=Mm(60))</v>
-      </c>
-      <c r="Q57" t="s">
+        <v>dh = InlineImage(docx_tpl, img_path_dh, height=Mm(50))</v>
+      </c>
+      <c r="R57" t="s">
         <v>560</v>
       </c>
-      <c r="R57" t="str">
+      <c r="S57" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['dh']}')</v>
       </c>
-      <c r="S57" t="str">
+      <c r="T57" t="str">
         <f t="shared" si="6"/>
         <v>dh = ''</v>
       </c>
-      <c r="T57" t="s">
+      <c r="U57" t="s">
         <v>559</v>
       </c>
-      <c r="U57" t="str">
+      <c r="V57" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['dh']}: {e}')</v>
       </c>
-      <c r="V57" t="str">
+      <c r="W57" t="str">
         <f t="shared" si="8"/>
         <v>dh = ''</v>
       </c>
     </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C58" t="s">
         <v>843</v>
       </c>
@@ -37669,61 +37835,64 @@
         <v>390</v>
       </c>
       <c r="H58">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I58" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J58" t="s">
         <v>703</v>
       </c>
-      <c r="J58" t="s">
+      <c r="K58" t="s">
         <v>704</v>
       </c>
-      <c r="K58" t="str">
+      <c r="L58" t="str">
         <f t="shared" si="9"/>
         <v>'estrobo' : r_val['estrobo'],</v>
       </c>
-      <c r="L58" t="str">
+      <c r="M58" t="str">
         <f t="shared" si="1"/>
         <v>'ventanas': ventanas,</v>
       </c>
-      <c r="M58" t="s">
+      <c r="N58" t="s">
         <v>558</v>
       </c>
-      <c r="N58" t="str">
+      <c r="O58" t="str">
         <f t="shared" si="2"/>
         <v>img_path_ventanas = os.path.join(IMAGES_PATH, r_val['ventanas'])</v>
       </c>
-      <c r="O58" t="str">
+      <c r="P58" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_ventanas):</v>
       </c>
-      <c r="P58" t="str">
+      <c r="Q58" t="str">
         <f t="shared" si="4"/>
-        <v>ventanas = InlineImage(docx_tpl, img_path_ventanas, height=Mm(60))</v>
-      </c>
-      <c r="Q58" t="s">
+        <v>ventanas = InlineImage(docx_tpl, img_path_ventanas, height=Mm(50))</v>
+      </c>
+      <c r="R58" t="s">
         <v>560</v>
       </c>
-      <c r="R58" t="str">
+      <c r="S58" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['ventanas']}')</v>
       </c>
-      <c r="S58" t="str">
+      <c r="T58" t="str">
         <f t="shared" si="6"/>
         <v>ventanas = ''</v>
       </c>
-      <c r="T58" t="s">
+      <c r="U58" t="s">
         <v>559</v>
       </c>
-      <c r="U58" t="str">
+      <c r="V58" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['ventanas']}: {e}')</v>
       </c>
-      <c r="V58" t="str">
+      <c r="W58" t="str">
         <f t="shared" si="8"/>
         <v>ventanas = ''</v>
       </c>
     </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:23" x14ac:dyDescent="0.3">
       <c r="D59" t="s">
         <v>832</v>
       </c>
@@ -37737,61 +37906,64 @@
         <v>391</v>
       </c>
       <c r="H59">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I59" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J59" t="s">
         <v>8</v>
       </c>
-      <c r="J59" t="s">
+      <c r="K59" t="s">
         <v>278</v>
       </c>
-      <c r="K59" t="str">
+      <c r="L59" t="str">
         <f t="shared" si="9"/>
         <v>'ubicacion_alarma' : r_val['ubicacion_alarma'],</v>
       </c>
-      <c r="L59" t="str">
+      <c r="M59" t="str">
         <f t="shared" si="1"/>
         <v>'compresor': compresor,</v>
       </c>
-      <c r="M59" t="s">
+      <c r="N59" t="s">
         <v>558</v>
       </c>
-      <c r="N59" t="str">
+      <c r="O59" t="str">
         <f t="shared" si="2"/>
         <v>img_path_compresor = os.path.join(IMAGES_PATH, r_val['compresor'])</v>
       </c>
-      <c r="O59" t="str">
+      <c r="P59" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_compresor):</v>
       </c>
-      <c r="P59" t="str">
+      <c r="Q59" t="str">
         <f t="shared" si="4"/>
-        <v>compresor = InlineImage(docx_tpl, img_path_compresor, height=Mm(60))</v>
-      </c>
-      <c r="Q59" t="s">
+        <v>compresor = InlineImage(docx_tpl, img_path_compresor, height=Mm(50))</v>
+      </c>
+      <c r="R59" t="s">
         <v>560</v>
       </c>
-      <c r="R59" t="str">
+      <c r="S59" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['compresor']}')</v>
       </c>
-      <c r="S59" t="str">
+      <c r="T59" t="str">
         <f t="shared" si="6"/>
         <v>compresor = ''</v>
       </c>
-      <c r="T59" t="s">
+      <c r="U59" t="s">
         <v>559</v>
       </c>
-      <c r="U59" t="str">
+      <c r="V59" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['compresor']}: {e}')</v>
       </c>
-      <c r="V59" t="str">
+      <c r="W59" t="str">
         <f t="shared" si="8"/>
         <v>compresor = ''</v>
       </c>
     </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:23" x14ac:dyDescent="0.3">
       <c r="D60" t="s">
         <v>832</v>
       </c>
@@ -37805,61 +37977,64 @@
         <v>392</v>
       </c>
       <c r="H60">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I60" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J60" t="s">
         <v>3</v>
       </c>
-      <c r="J60" t="s">
+      <c r="K60" t="s">
         <v>279</v>
       </c>
-      <c r="K60" t="str">
+      <c r="L60" t="str">
         <f t="shared" si="9"/>
         <v>'detectores_humo' : r_val['detectores_humo'],</v>
       </c>
-      <c r="L60" t="str">
+      <c r="M60" t="str">
         <f t="shared" si="1"/>
         <v>'quimicos': quimicos,</v>
       </c>
-      <c r="M60" t="s">
+      <c r="N60" t="s">
         <v>558</v>
       </c>
-      <c r="N60" t="str">
+      <c r="O60" t="str">
         <f t="shared" si="2"/>
         <v>img_path_quimicos = os.path.join(IMAGES_PATH, r_val['quimicos'])</v>
       </c>
-      <c r="O60" t="str">
+      <c r="P60" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_quimicos):</v>
       </c>
-      <c r="P60" t="str">
+      <c r="Q60" t="str">
         <f t="shared" si="4"/>
-        <v>quimicos = InlineImage(docx_tpl, img_path_quimicos, height=Mm(60))</v>
-      </c>
-      <c r="Q60" t="s">
+        <v>quimicos = InlineImage(docx_tpl, img_path_quimicos, height=Mm(50))</v>
+      </c>
+      <c r="R60" t="s">
         <v>560</v>
       </c>
-      <c r="R60" t="str">
+      <c r="S60" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['quimicos']}')</v>
       </c>
-      <c r="S60" t="str">
+      <c r="T60" t="str">
         <f t="shared" si="6"/>
         <v>quimicos = ''</v>
       </c>
-      <c r="T60" t="s">
+      <c r="U60" t="s">
         <v>559</v>
       </c>
-      <c r="U60" t="str">
+      <c r="V60" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['quimicos']}: {e}')</v>
       </c>
-      <c r="V60" t="str">
+      <c r="W60" t="str">
         <f t="shared" si="8"/>
         <v>quimicos = ''</v>
       </c>
     </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:23" x14ac:dyDescent="0.3">
       <c r="D61" t="s">
         <v>832</v>
       </c>
@@ -37873,61 +38048,64 @@
         <v>393</v>
       </c>
       <c r="H61">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I61" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J61" t="s">
         <v>4</v>
       </c>
-      <c r="J61" t="s">
+      <c r="K61" t="s">
         <v>280</v>
       </c>
-      <c r="K61" t="str">
+      <c r="L61" t="str">
         <f t="shared" si="9"/>
         <v>'ubicación_dh' : r_val['ubicación_dh'],</v>
       </c>
-      <c r="L61" t="str">
+      <c r="M61" t="str">
         <f t="shared" si="1"/>
         <v>'tanques_gaso': tanques_gaso,</v>
       </c>
-      <c r="M61" t="s">
+      <c r="N61" t="s">
         <v>558</v>
       </c>
-      <c r="N61" t="str">
+      <c r="O61" t="str">
         <f t="shared" si="2"/>
         <v>img_path_tanques_gaso = os.path.join(IMAGES_PATH, r_val['tanques_gaso'])</v>
       </c>
-      <c r="O61" t="str">
+      <c r="P61" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_tanques_gaso):</v>
       </c>
-      <c r="P61" t="str">
+      <c r="Q61" t="str">
         <f t="shared" si="4"/>
-        <v>tanques_gaso = InlineImage(docx_tpl, img_path_tanques_gaso, height=Mm(60))</v>
-      </c>
-      <c r="Q61" t="s">
+        <v>tanques_gaso = InlineImage(docx_tpl, img_path_tanques_gaso, height=Mm(50))</v>
+      </c>
+      <c r="R61" t="s">
         <v>560</v>
       </c>
-      <c r="R61" t="str">
+      <c r="S61" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['tanques_gaso']}')</v>
       </c>
-      <c r="S61" t="str">
+      <c r="T61" t="str">
         <f t="shared" si="6"/>
         <v>tanques_gaso = ''</v>
       </c>
-      <c r="T61" t="s">
+      <c r="U61" t="s">
         <v>559</v>
       </c>
-      <c r="U61" t="str">
+      <c r="V61" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['tanques_gaso']}: {e}')</v>
       </c>
-      <c r="V61" t="str">
+      <c r="W61" t="str">
         <f t="shared" si="8"/>
         <v>tanques_gaso = ''</v>
       </c>
     </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:23" x14ac:dyDescent="0.3">
       <c r="D62" t="s">
         <v>832</v>
       </c>
@@ -37941,61 +38119,64 @@
         <v>394</v>
       </c>
       <c r="H62">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I62" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J62" t="s">
         <v>184</v>
       </c>
-      <c r="J62" t="s">
+      <c r="K62" t="s">
         <v>281</v>
       </c>
-      <c r="K62" t="str">
+      <c r="L62" t="str">
         <f t="shared" si="9"/>
         <v>'ruta_evac' : r_val['ruta_evac'],</v>
       </c>
-      <c r="L62" t="str">
+      <c r="M62" t="str">
         <f t="shared" si="1"/>
         <v>'paro': paro,</v>
       </c>
-      <c r="M62" t="s">
+      <c r="N62" t="s">
         <v>558</v>
       </c>
-      <c r="N62" t="str">
+      <c r="O62" t="str">
         <f t="shared" si="2"/>
         <v>img_path_paro = os.path.join(IMAGES_PATH, r_val['paro'])</v>
       </c>
-      <c r="O62" t="str">
+      <c r="P62" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_paro):</v>
       </c>
-      <c r="P62" t="str">
+      <c r="Q62" t="str">
         <f t="shared" si="4"/>
-        <v>paro = InlineImage(docx_tpl, img_path_paro, height=Mm(60))</v>
-      </c>
-      <c r="Q62" t="s">
+        <v>paro = InlineImage(docx_tpl, img_path_paro, height=Mm(50))</v>
+      </c>
+      <c r="R62" t="s">
         <v>560</v>
       </c>
-      <c r="R62" t="str">
+      <c r="S62" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['paro']}')</v>
       </c>
-      <c r="S62" t="str">
+      <c r="T62" t="str">
         <f t="shared" si="6"/>
         <v>paro = ''</v>
       </c>
-      <c r="T62" t="s">
+      <c r="U62" t="s">
         <v>559</v>
       </c>
-      <c r="U62" t="str">
+      <c r="V62" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['paro']}: {e}')</v>
       </c>
-      <c r="V62" t="str">
+      <c r="W62" t="str">
         <f t="shared" si="8"/>
         <v>paro = ''</v>
       </c>
     </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:23" x14ac:dyDescent="0.3">
       <c r="D63" t="s">
         <v>832</v>
       </c>
@@ -38009,61 +38190,64 @@
         <v>395</v>
       </c>
       <c r="H63">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I63" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J63" t="s">
         <v>5</v>
       </c>
-      <c r="J63" t="s">
+      <c r="K63" t="s">
         <v>249</v>
       </c>
-      <c r="K63" t="str">
+      <c r="L63" t="str">
         <f t="shared" si="9"/>
         <v>'escaleras' : r_val['escaleras'],</v>
       </c>
-      <c r="L63" t="str">
+      <c r="M63" t="str">
         <f t="shared" si="1"/>
         <v>'trampa_grasa': trampa_grasa,</v>
       </c>
-      <c r="M63" t="s">
+      <c r="N63" t="s">
         <v>558</v>
       </c>
-      <c r="N63" t="str">
+      <c r="O63" t="str">
         <f t="shared" si="2"/>
         <v>img_path_trampa_grasa = os.path.join(IMAGES_PATH, r_val['trampa_grasa'])</v>
       </c>
-      <c r="O63" t="str">
+      <c r="P63" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_trampa_grasa):</v>
       </c>
-      <c r="P63" t="str">
+      <c r="Q63" t="str">
         <f t="shared" si="4"/>
-        <v>trampa_grasa = InlineImage(docx_tpl, img_path_trampa_grasa, height=Mm(60))</v>
-      </c>
-      <c r="Q63" t="s">
+        <v>trampa_grasa = InlineImage(docx_tpl, img_path_trampa_grasa, height=Mm(50))</v>
+      </c>
+      <c r="R63" t="s">
         <v>560</v>
       </c>
-      <c r="R63" t="str">
+      <c r="S63" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['trampa_grasa']}')</v>
       </c>
-      <c r="S63" t="str">
+      <c r="T63" t="str">
         <f t="shared" si="6"/>
         <v>trampa_grasa = ''</v>
       </c>
-      <c r="T63" t="s">
+      <c r="U63" t="s">
         <v>559</v>
       </c>
-      <c r="U63" t="str">
+      <c r="V63" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['trampa_grasa']}: {e}')</v>
       </c>
-      <c r="V63" t="str">
+      <c r="W63" t="str">
         <f t="shared" si="8"/>
         <v>trampa_grasa = ''</v>
       </c>
     </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="64" spans="3:23" x14ac:dyDescent="0.3">
       <c r="E64" t="s">
         <v>21</v>
       </c>
@@ -38074,61 +38258,64 @@
         <v>274</v>
       </c>
       <c r="H64">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I64" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J64" t="s">
         <v>185</v>
       </c>
-      <c r="J64" t="s">
+      <c r="K64" t="s">
         <v>282</v>
       </c>
-      <c r="K64" t="str">
+      <c r="L64" t="str">
         <f t="shared" si="9"/>
         <v>'salida_emerg' : r_val['salida_emerg'],</v>
       </c>
-      <c r="L64" t="str">
+      <c r="M64" t="str">
         <f t="shared" si="1"/>
         <v>'planta': planta,</v>
       </c>
-      <c r="M64" t="s">
+      <c r="N64" t="s">
         <v>558</v>
       </c>
-      <c r="N64" t="str">
+      <c r="O64" t="str">
         <f t="shared" si="2"/>
         <v>img_path_planta = os.path.join(IMAGES_PATH, r_val['planta'])</v>
       </c>
-      <c r="O64" t="str">
+      <c r="P64" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_planta):</v>
       </c>
-      <c r="P64" t="str">
+      <c r="Q64" t="str">
         <f t="shared" si="4"/>
-        <v>planta = InlineImage(docx_tpl, img_path_planta, height=Mm(60))</v>
-      </c>
-      <c r="Q64" t="s">
+        <v>planta = InlineImage(docx_tpl, img_path_planta, height=Mm(50))</v>
+      </c>
+      <c r="R64" t="s">
         <v>560</v>
       </c>
-      <c r="R64" t="str">
+      <c r="S64" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['planta']}')</v>
       </c>
-      <c r="S64" t="str">
+      <c r="T64" t="str">
         <f t="shared" si="6"/>
         <v>planta = ''</v>
       </c>
-      <c r="T64" t="s">
+      <c r="U64" t="s">
         <v>559</v>
       </c>
-      <c r="U64" t="str">
+      <c r="V64" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['planta']}: {e}')</v>
       </c>
-      <c r="V64" t="str">
+      <c r="W64" t="str">
         <f t="shared" si="8"/>
         <v>planta = ''</v>
       </c>
     </row>
-    <row r="65" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="65" spans="3:23" x14ac:dyDescent="0.3">
       <c r="E65" t="s">
         <v>414</v>
       </c>
@@ -38139,61 +38326,64 @@
         <v>416</v>
       </c>
       <c r="H65">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I65" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J65" t="s">
         <v>186</v>
       </c>
-      <c r="J65" t="s">
+      <c r="K65" t="s">
         <v>283</v>
       </c>
-      <c r="K65" t="str">
+      <c r="L65" t="str">
         <f t="shared" si="9"/>
         <v>'zona_menor_rg' : r_val['zona_menor_rg'],</v>
       </c>
-      <c r="L65" t="str">
+      <c r="M65" t="str">
         <f t="shared" si="1"/>
         <v>'deposito': deposito,</v>
       </c>
-      <c r="M65" t="s">
+      <c r="N65" t="s">
         <v>558</v>
       </c>
-      <c r="N65" t="str">
+      <c r="O65" t="str">
         <f t="shared" si="2"/>
         <v>img_path_deposito = os.path.join(IMAGES_PATH, r_val['deposito'])</v>
       </c>
-      <c r="O65" t="str">
+      <c r="P65" t="str">
         <f t="shared" si="3"/>
         <v>if os.path.exists(img_path_deposito):</v>
       </c>
-      <c r="P65" t="str">
+      <c r="Q65" t="str">
         <f t="shared" si="4"/>
-        <v>deposito = InlineImage(docx_tpl, img_path_deposito, height=Mm(60))</v>
-      </c>
-      <c r="Q65" t="s">
+        <v>deposito = InlineImage(docx_tpl, img_path_deposito, height=Mm(50))</v>
+      </c>
+      <c r="R65" t="s">
         <v>560</v>
       </c>
-      <c r="R65" t="str">
+      <c r="S65" t="str">
         <f t="shared" si="5"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val['deposito']}')</v>
       </c>
-      <c r="S65" t="str">
+      <c r="T65" t="str">
         <f t="shared" si="6"/>
         <v>deposito = ''</v>
       </c>
-      <c r="T65" t="s">
+      <c r="U65" t="s">
         <v>559</v>
       </c>
-      <c r="U65" t="str">
+      <c r="V65" t="str">
         <f t="shared" si="7"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val['deposito']}: {e}')</v>
       </c>
-      <c r="V65" t="str">
+      <c r="W65" t="str">
         <f t="shared" si="8"/>
         <v>deposito = ''</v>
       </c>
     </row>
-    <row r="66" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="66" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C66" t="s">
         <v>843</v>
       </c>
@@ -38207,61 +38397,64 @@
         <v>599</v>
       </c>
       <c r="H66">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="I66" t="s">
+        <v>1758</v>
+      </c>
+      <c r="J66" t="s">
         <v>187</v>
       </c>
-      <c r="J66" t="s">
+      <c r="K66" t="s">
         <v>284</v>
       </c>
-      <c r="K66" t="str">
+      <c r="L66" t="str">
         <f t="shared" si="9"/>
         <v>'punto_reunion' : r_val['punto_reunion'],</v>
       </c>
-      <c r="L66" t="str">
+      <c r="M66" t="str">
         <f t="shared" si="1"/>
         <v>'mapa_satel': mapa_satel,</v>
       </c>
-      <c r="M66" t="s">
+      <c r="N66" t="s">
         <v>558</v>
       </c>
-      <c r="N66" t="str">
+      <c r="O66" t="str">
         <f>+_xlfn.CONCAT("img_path_",E66," = os.path.join(IMAGES_PATH, r_val[""",E66,"""])")</f>
         <v>img_path_mapa_satel = os.path.join(IMAGES_PATH, r_val["mapa_satel"])</v>
       </c>
-      <c r="O66" t="str">
-        <f t="shared" ref="O66" si="10">+_xlfn.CONCAT("if os.path.exists(img_path_",E66,"):")</f>
+      <c r="P66" t="str">
+        <f t="shared" ref="P66" si="10">+_xlfn.CONCAT("if os.path.exists(img_path_",E66,"):")</f>
         <v>if os.path.exists(img_path_mapa_satel):</v>
       </c>
-      <c r="P66" t="str">
+      <c r="Q66" t="str">
         <f>+_xlfn.CONCAT(E66," = InlineImage(docx_tpl, img_path_",E66,", width=Mm(",H66,"))")</f>
-        <v>mapa_satel = InlineImage(docx_tpl, img_path_mapa_satel, width=Mm(140))</v>
-      </c>
-      <c r="Q66" t="s">
+        <v>mapa_satel = InlineImage(docx_tpl, img_path_mapa_satel, width=Mm(155))</v>
+      </c>
+      <c r="R66" t="s">
         <v>560</v>
       </c>
-      <c r="R66" t="str">
+      <c r="S66" t="str">
         <f>+_xlfn.CONCAT("print(f'Advertencia: No se encontró la imagen {r_val[""",E66,"""]}')")</f>
         <v>print(f'Advertencia: No se encontró la imagen {r_val["mapa_satel"]}')</v>
       </c>
-      <c r="S66" t="str">
-        <f t="shared" ref="S66" si="11">+_xlfn.CONCAT(E66," = ''")</f>
+      <c r="T66" t="str">
+        <f t="shared" ref="T66" si="11">+_xlfn.CONCAT(E66," = ''")</f>
         <v>mapa_satel = ''</v>
       </c>
-      <c r="T66" t="s">
+      <c r="U66" t="s">
         <v>559</v>
       </c>
-      <c r="U66" t="str">
+      <c r="V66" t="str">
         <f>+_xlfn.CONCAT("print(f'Advertencia: No se pudo cargar la imagen {r_val[""",E66,"""]}: {e}')")</f>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["mapa_satel"]}: {e}')</v>
       </c>
-      <c r="V66" t="str">
-        <f t="shared" ref="V66" si="12">+_xlfn.CONCAT(E66," = ''")</f>
+      <c r="W66" t="str">
+        <f t="shared" ref="W66" si="12">+_xlfn.CONCAT(E66," = ''")</f>
         <v>mapa_satel = ''</v>
       </c>
     </row>
-    <row r="67" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="67" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C67" t="s">
         <v>843</v>
       </c>
@@ -38275,61 +38468,64 @@
         <v>604</v>
       </c>
       <c r="H67">
-        <v>200</v>
+        <v>155</v>
       </c>
       <c r="I67" t="s">
+        <v>1758</v>
+      </c>
+      <c r="J67" t="s">
         <v>6</v>
       </c>
-      <c r="J67" t="s">
+      <c r="K67" t="s">
         <v>285</v>
       </c>
-      <c r="K67" t="str">
+      <c r="L67" t="str">
         <f t="shared" si="9"/>
         <v>'sismo_incendio' : r_val['sismo_incendio'],</v>
       </c>
-      <c r="L67" t="str">
-        <f t="shared" ref="L67:L92" si="13">+_xlfn.CONCAT("'",E67,"': ",E67,",")</f>
+      <c r="M67" t="str">
+        <f t="shared" ref="M67:M92" si="13">+_xlfn.CONCAT("'",E67,"': ",E67,",")</f>
         <v>'plano': plano,</v>
       </c>
-      <c r="M67" t="s">
+      <c r="N67" t="s">
         <v>558</v>
       </c>
-      <c r="N67" t="str">
-        <f t="shared" ref="N67:N90" si="14">+_xlfn.CONCAT("img_path_",E67," = os.path.join(IMAGES_PATH, r_val[""",E67,"""])")</f>
+      <c r="O67" t="str">
+        <f t="shared" ref="O67:O90" si="14">+_xlfn.CONCAT("img_path_",E67," = os.path.join(IMAGES_PATH, r_val[""",E67,"""])")</f>
         <v>img_path_plano = os.path.join(IMAGES_PATH, r_val["plano"])</v>
       </c>
-      <c r="O67" t="str">
-        <f t="shared" ref="O67:O90" si="15">+_xlfn.CONCAT("if os.path.exists(img_path_",E67,"):")</f>
+      <c r="P67" t="str">
+        <f t="shared" ref="P67:P90" si="15">+_xlfn.CONCAT("if os.path.exists(img_path_",E67,"):")</f>
         <v>if os.path.exists(img_path_plano):</v>
       </c>
-      <c r="P67" t="str">
-        <f t="shared" ref="P67:P90" si="16">+_xlfn.CONCAT(E67," = InlineImage(docx_tpl, img_path_",E67,", height=Mm(",H67,"))")</f>
-        <v>plano = InlineImage(docx_tpl, img_path_plano, height=Mm(200))</v>
-      </c>
-      <c r="Q67" t="s">
+      <c r="Q67" t="str">
+        <f t="shared" ref="Q67:Q90" si="16">+_xlfn.CONCAT(E67," = InlineImage(docx_tpl, img_path_",E67,", height=Mm(",H67,"))")</f>
+        <v>plano = InlineImage(docx_tpl, img_path_plano, height=Mm(155))</v>
+      </c>
+      <c r="R67" t="s">
         <v>560</v>
       </c>
-      <c r="R67" t="str">
-        <f t="shared" ref="R67:R90" si="17">+_xlfn.CONCAT("print(f'Advertencia: No se encontró la imagen {r_val[""",E67,"""]}')")</f>
+      <c r="S67" t="str">
+        <f t="shared" ref="S67:S90" si="17">+_xlfn.CONCAT("print(f'Advertencia: No se encontró la imagen {r_val[""",E67,"""]}')")</f>
         <v>print(f'Advertencia: No se encontró la imagen {r_val["plano"]}')</v>
       </c>
-      <c r="S67" t="str">
-        <f t="shared" ref="S67:S90" si="18">+_xlfn.CONCAT(E67," = ''")</f>
+      <c r="T67" t="str">
+        <f t="shared" ref="T67:T90" si="18">+_xlfn.CONCAT(E67," = ''")</f>
         <v>plano = ''</v>
       </c>
-      <c r="T67" t="s">
+      <c r="U67" t="s">
         <v>559</v>
       </c>
-      <c r="U67" t="str">
-        <f t="shared" ref="U67:U90" si="19">+_xlfn.CONCAT("print(f'Advertencia: No se pudo cargar la imagen {r_val[""",E67,"""]}: {e}')")</f>
+      <c r="V67" t="str">
+        <f t="shared" ref="V67:V90" si="19">+_xlfn.CONCAT("print(f'Advertencia: No se pudo cargar la imagen {r_val[""",E67,"""]}: {e}')")</f>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["plano"]}: {e}')</v>
       </c>
-      <c r="V67" t="str">
-        <f t="shared" ref="V67:V90" si="20">+_xlfn.CONCAT(E67," = ''")</f>
+      <c r="W67" t="str">
+        <f t="shared" ref="W67:W90" si="20">+_xlfn.CONCAT(E67," = ''")</f>
         <v>plano = ''</v>
       </c>
     </row>
-    <row r="68" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="68" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C68" t="s">
         <v>843</v>
       </c>
@@ -38343,61 +38539,64 @@
         <v>607</v>
       </c>
       <c r="H68">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I68" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J68" t="s">
         <v>188</v>
       </c>
-      <c r="J68" t="s">
+      <c r="K68" t="s">
         <v>286</v>
       </c>
-      <c r="K68" t="str">
+      <c r="L68" t="str">
         <f t="shared" si="9"/>
         <v>'riesgo_electrico' : r_val['riesgo_electrico'],</v>
       </c>
-      <c r="L68" t="str">
+      <c r="M68" t="str">
         <f t="shared" si="13"/>
         <v>'inmueble1': inmueble1,</v>
       </c>
-      <c r="M68" t="s">
+      <c r="N68" t="s">
         <v>558</v>
       </c>
-      <c r="N68" t="str">
+      <c r="O68" t="str">
         <f t="shared" si="14"/>
         <v>img_path_inmueble1 = os.path.join(IMAGES_PATH, r_val["inmueble1"])</v>
       </c>
-      <c r="O68" t="str">
+      <c r="P68" t="str">
         <f t="shared" si="15"/>
         <v>if os.path.exists(img_path_inmueble1):</v>
       </c>
-      <c r="P68" t="str">
+      <c r="Q68" t="str">
         <f t="shared" si="16"/>
-        <v>inmueble1 = InlineImage(docx_tpl, img_path_inmueble1, height=Mm(60))</v>
-      </c>
-      <c r="Q68" t="s">
+        <v>inmueble1 = InlineImage(docx_tpl, img_path_inmueble1, height=Mm(50))</v>
+      </c>
+      <c r="R68" t="s">
         <v>560</v>
       </c>
-      <c r="R68" t="str">
+      <c r="S68" t="str">
         <f t="shared" si="17"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val["inmueble1"]}')</v>
       </c>
-      <c r="S68" t="str">
+      <c r="T68" t="str">
         <f t="shared" si="18"/>
         <v>inmueble1 = ''</v>
       </c>
-      <c r="T68" t="s">
+      <c r="U68" t="s">
         <v>559</v>
       </c>
-      <c r="U68" t="str">
+      <c r="V68" t="str">
         <f t="shared" si="19"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["inmueble1"]}: {e}')</v>
       </c>
-      <c r="V68" t="str">
+      <c r="W68" t="str">
         <f t="shared" si="20"/>
         <v>inmueble1 = ''</v>
       </c>
     </row>
-    <row r="69" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="69" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C69" t="s">
         <v>843</v>
       </c>
@@ -38411,61 +38610,64 @@
         <v>610</v>
       </c>
       <c r="H69">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I69" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J69" t="s">
         <v>189</v>
       </c>
-      <c r="J69" t="s">
+      <c r="K69" t="s">
         <v>287</v>
       </c>
-      <c r="K69" t="str">
+      <c r="L69" t="str">
         <f t="shared" si="9"/>
         <v>'senial_prohibicion' : r_val['senial_prohibicion'],</v>
       </c>
-      <c r="L69" t="str">
+      <c r="M69" t="str">
         <f t="shared" si="13"/>
         <v>'inmueble2': inmueble2,</v>
       </c>
-      <c r="M69" t="s">
+      <c r="N69" t="s">
         <v>558</v>
       </c>
-      <c r="N69" t="str">
+      <c r="O69" t="str">
         <f t="shared" si="14"/>
         <v>img_path_inmueble2 = os.path.join(IMAGES_PATH, r_val["inmueble2"])</v>
       </c>
-      <c r="O69" t="str">
+      <c r="P69" t="str">
         <f t="shared" si="15"/>
         <v>if os.path.exists(img_path_inmueble2):</v>
       </c>
-      <c r="P69" t="str">
+      <c r="Q69" t="str">
         <f t="shared" si="16"/>
-        <v>inmueble2 = InlineImage(docx_tpl, img_path_inmueble2, height=Mm(60))</v>
-      </c>
-      <c r="Q69" t="s">
+        <v>inmueble2 = InlineImage(docx_tpl, img_path_inmueble2, height=Mm(50))</v>
+      </c>
+      <c r="R69" t="s">
         <v>560</v>
       </c>
-      <c r="R69" t="str">
+      <c r="S69" t="str">
         <f t="shared" si="17"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val["inmueble2"]}')</v>
       </c>
-      <c r="S69" t="str">
+      <c r="T69" t="str">
         <f t="shared" si="18"/>
         <v>inmueble2 = ''</v>
       </c>
-      <c r="T69" t="s">
+      <c r="U69" t="s">
         <v>559</v>
       </c>
-      <c r="U69" t="str">
+      <c r="V69" t="str">
         <f t="shared" si="19"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["inmueble2"]}: {e}')</v>
       </c>
-      <c r="V69" t="str">
+      <c r="W69" t="str">
         <f t="shared" si="20"/>
         <v>inmueble2 = ''</v>
       </c>
     </row>
-    <row r="70" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="70" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C70" t="s">
         <v>843</v>
       </c>
@@ -38479,61 +38681,64 @@
         <v>613</v>
       </c>
       <c r="H70">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I70" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J70" t="s">
         <v>190</v>
       </c>
-      <c r="J70" t="s">
+      <c r="K70" t="s">
         <v>288</v>
       </c>
-      <c r="K70" t="str">
+      <c r="L70" t="str">
         <f t="shared" si="9"/>
         <v>'no_fumar' : r_val['no_fumar'],</v>
       </c>
-      <c r="L70" t="str">
+      <c r="M70" t="str">
         <f t="shared" si="13"/>
         <v>'banio1': banio1,</v>
       </c>
-      <c r="M70" t="s">
+      <c r="N70" t="s">
         <v>558</v>
       </c>
-      <c r="N70" t="str">
+      <c r="O70" t="str">
         <f t="shared" si="14"/>
         <v>img_path_banio1 = os.path.join(IMAGES_PATH, r_val["banio1"])</v>
       </c>
-      <c r="O70" t="str">
+      <c r="P70" t="str">
         <f t="shared" si="15"/>
         <v>if os.path.exists(img_path_banio1):</v>
       </c>
-      <c r="P70" t="str">
+      <c r="Q70" t="str">
         <f t="shared" si="16"/>
-        <v>banio1 = InlineImage(docx_tpl, img_path_banio1, height=Mm(60))</v>
-      </c>
-      <c r="Q70" t="s">
+        <v>banio1 = InlineImage(docx_tpl, img_path_banio1, height=Mm(50))</v>
+      </c>
+      <c r="R70" t="s">
         <v>560</v>
       </c>
-      <c r="R70" t="str">
+      <c r="S70" t="str">
         <f t="shared" si="17"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val["banio1"]}')</v>
       </c>
-      <c r="S70" t="str">
+      <c r="T70" t="str">
         <f t="shared" si="18"/>
         <v>banio1 = ''</v>
       </c>
-      <c r="T70" t="s">
+      <c r="U70" t="s">
         <v>559</v>
       </c>
-      <c r="U70" t="str">
+      <c r="V70" t="str">
         <f t="shared" si="19"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["banio1"]}: {e}')</v>
       </c>
-      <c r="V70" t="str">
+      <c r="W70" t="str">
         <f t="shared" si="20"/>
         <v>banio1 = ''</v>
       </c>
     </row>
-    <row r="71" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="71" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C71" t="s">
         <v>843</v>
       </c>
@@ -38547,61 +38752,64 @@
         <v>616</v>
       </c>
       <c r="H71">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I71" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J71" t="s">
         <v>540</v>
       </c>
-      <c r="J71" t="s">
+      <c r="K71" t="s">
         <v>541</v>
       </c>
-      <c r="K71" t="str">
+      <c r="L71" t="str">
         <f t="shared" si="9"/>
         <v>'area_restrig ' : r_val['area_restrig '],</v>
       </c>
-      <c r="L71" t="str">
+      <c r="M71" t="str">
         <f t="shared" si="13"/>
         <v>'electrico1': electrico1,</v>
       </c>
-      <c r="M71" t="s">
+      <c r="N71" t="s">
         <v>558</v>
       </c>
-      <c r="N71" t="str">
+      <c r="O71" t="str">
         <f t="shared" si="14"/>
         <v>img_path_electrico1 = os.path.join(IMAGES_PATH, r_val["electrico1"])</v>
       </c>
-      <c r="O71" t="str">
+      <c r="P71" t="str">
         <f t="shared" si="15"/>
         <v>if os.path.exists(img_path_electrico1):</v>
       </c>
-      <c r="P71" t="str">
+      <c r="Q71" t="str">
         <f t="shared" si="16"/>
-        <v>electrico1 = InlineImage(docx_tpl, img_path_electrico1, height=Mm(60))</v>
-      </c>
-      <c r="Q71" t="s">
+        <v>electrico1 = InlineImage(docx_tpl, img_path_electrico1, height=Mm(50))</v>
+      </c>
+      <c r="R71" t="s">
         <v>560</v>
       </c>
-      <c r="R71" t="str">
+      <c r="S71" t="str">
         <f t="shared" si="17"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val["electrico1"]}')</v>
       </c>
-      <c r="S71" t="str">
+      <c r="T71" t="str">
         <f t="shared" si="18"/>
         <v>electrico1 = ''</v>
       </c>
-      <c r="T71" t="s">
+      <c r="U71" t="s">
         <v>559</v>
       </c>
-      <c r="U71" t="str">
+      <c r="V71" t="str">
         <f t="shared" si="19"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["electrico1"]}: {e}')</v>
       </c>
-      <c r="V71" t="str">
+      <c r="W71" t="str">
         <f t="shared" si="20"/>
         <v>electrico1 = ''</v>
       </c>
     </row>
-    <row r="72" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="72" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C72" t="s">
         <v>843</v>
       </c>
@@ -38618,61 +38826,64 @@
         <v>707</v>
       </c>
       <c r="H72">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I72" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J72" t="s">
         <v>9</v>
       </c>
-      <c r="J72" t="s">
+      <c r="K72" t="s">
         <v>289</v>
       </c>
-      <c r="K72" t="str">
+      <c r="L72" t="str">
         <f t="shared" si="9"/>
         <v>'apague_motor' : r_val['apague_motor'],</v>
       </c>
-      <c r="L72" t="str">
+      <c r="M72" t="str">
         <f t="shared" si="13"/>
         <v>'fachada1': fachada1,</v>
       </c>
-      <c r="M72" t="s">
+      <c r="N72" t="s">
         <v>558</v>
       </c>
-      <c r="N72" t="str">
+      <c r="O72" t="str">
         <f t="shared" si="14"/>
         <v>img_path_fachada1 = os.path.join(IMAGES_PATH, r_val["fachada1"])</v>
       </c>
-      <c r="O72" t="str">
+      <c r="P72" t="str">
         <f t="shared" si="15"/>
         <v>if os.path.exists(img_path_fachada1):</v>
       </c>
-      <c r="P72" t="str">
+      <c r="Q72" t="str">
         <f t="shared" si="16"/>
-        <v>fachada1 = InlineImage(docx_tpl, img_path_fachada1, height=Mm(60))</v>
-      </c>
-      <c r="Q72" t="s">
+        <v>fachada1 = InlineImage(docx_tpl, img_path_fachada1, height=Mm(50))</v>
+      </c>
+      <c r="R72" t="s">
         <v>560</v>
       </c>
-      <c r="R72" t="str">
+      <c r="S72" t="str">
         <f t="shared" si="17"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val["fachada1"]}')</v>
       </c>
-      <c r="S72" t="str">
+      <c r="T72" t="str">
         <f t="shared" si="18"/>
         <v>fachada1 = ''</v>
       </c>
-      <c r="T72" t="s">
+      <c r="U72" t="s">
         <v>559</v>
       </c>
-      <c r="U72" t="str">
+      <c r="V72" t="str">
         <f t="shared" si="19"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["fachada1"]}: {e}')</v>
       </c>
-      <c r="V72" t="str">
+      <c r="W72" t="str">
         <f t="shared" si="20"/>
         <v>fachada1 = ''</v>
       </c>
     </row>
-    <row r="73" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="73" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C73" t="s">
         <v>843</v>
       </c>
@@ -38686,61 +38897,64 @@
         <v>712</v>
       </c>
       <c r="H73">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I73" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J73" t="s">
         <v>10</v>
       </c>
-      <c r="J73" t="s">
+      <c r="K73" t="s">
         <v>290</v>
       </c>
-      <c r="K73" t="str">
+      <c r="L73" t="str">
         <f t="shared" si="9"/>
         <v>'no_celular' : r_val['no_celular'],</v>
       </c>
-      <c r="L73" t="str">
+      <c r="M73" t="str">
         <f t="shared" si="13"/>
         <v>'bateria': bateria,</v>
       </c>
-      <c r="M73" t="s">
+      <c r="N73" t="s">
         <v>558</v>
       </c>
-      <c r="N73" t="str">
+      <c r="O73" t="str">
         <f t="shared" si="14"/>
         <v>img_path_bateria = os.path.join(IMAGES_PATH, r_val["bateria"])</v>
       </c>
-      <c r="O73" t="str">
+      <c r="P73" t="str">
         <f t="shared" si="15"/>
         <v>if os.path.exists(img_path_bateria):</v>
       </c>
-      <c r="P73" t="str">
+      <c r="Q73" t="str">
         <f t="shared" si="16"/>
-        <v>bateria = InlineImage(docx_tpl, img_path_bateria, height=Mm(60))</v>
-      </c>
-      <c r="Q73" t="s">
+        <v>bateria = InlineImage(docx_tpl, img_path_bateria, height=Mm(50))</v>
+      </c>
+      <c r="R73" t="s">
         <v>560</v>
       </c>
-      <c r="R73" t="str">
+      <c r="S73" t="str">
         <f t="shared" si="17"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val["bateria"]}')</v>
       </c>
-      <c r="S73" t="str">
+      <c r="T73" t="str">
         <f t="shared" si="18"/>
         <v>bateria = ''</v>
       </c>
-      <c r="T73" t="s">
+      <c r="U73" t="s">
         <v>559</v>
       </c>
-      <c r="U73" t="str">
+      <c r="V73" t="str">
         <f t="shared" si="19"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["bateria"]}: {e}')</v>
       </c>
-      <c r="V73" t="str">
+      <c r="W73" t="str">
         <f t="shared" si="20"/>
         <v>bateria = ''</v>
       </c>
     </row>
-    <row r="74" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="74" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C74" t="s">
         <v>843</v>
       </c>
@@ -38759,61 +38973,64 @@
         <v>{{ acta1 }}</v>
       </c>
       <c r="H74">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="I74" t="s">
+        <v>1758</v>
+      </c>
+      <c r="J74" t="s">
         <v>11</v>
       </c>
-      <c r="J74" t="s">
+      <c r="K74" t="s">
         <v>291</v>
       </c>
-      <c r="K74" t="str">
+      <c r="L74" t="str">
         <f t="shared" si="9"/>
         <v>'no_gorra_lentes' : r_val['no_gorra_lentes'],</v>
       </c>
-      <c r="L74" t="str">
+      <c r="M74" t="str">
         <f t="shared" si="13"/>
         <v>'acta1': acta1,</v>
       </c>
-      <c r="M74" t="s">
+      <c r="N74" t="s">
         <v>558</v>
       </c>
-      <c r="N74" t="str">
+      <c r="O74" t="str">
         <f t="shared" si="14"/>
         <v>img_path_acta1 = os.path.join(IMAGES_PATH, r_val["acta1"])</v>
       </c>
-      <c r="O74" t="str">
+      <c r="P74" t="str">
         <f t="shared" si="15"/>
         <v>if os.path.exists(img_path_acta1):</v>
       </c>
-      <c r="P74" t="str">
+      <c r="Q74" t="str">
         <f t="shared" si="16"/>
-        <v>acta1 = InlineImage(docx_tpl, img_path_acta1, height=Mm(190))</v>
-      </c>
-      <c r="Q74" t="s">
+        <v>acta1 = InlineImage(docx_tpl, img_path_acta1, height=Mm(155))</v>
+      </c>
+      <c r="R74" t="s">
         <v>560</v>
       </c>
-      <c r="R74" t="str">
+      <c r="S74" t="str">
         <f t="shared" si="17"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val["acta1"]}')</v>
       </c>
-      <c r="S74" t="str">
+      <c r="T74" t="str">
         <f t="shared" si="18"/>
         <v>acta1 = ''</v>
       </c>
-      <c r="T74" t="s">
+      <c r="U74" t="s">
         <v>559</v>
       </c>
-      <c r="U74" t="str">
+      <c r="V74" t="str">
         <f t="shared" si="19"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["acta1"]}: {e}')</v>
       </c>
-      <c r="V74" t="str">
+      <c r="W74" t="str">
         <f t="shared" si="20"/>
         <v>acta1 = ''</v>
       </c>
     </row>
-    <row r="75" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="75" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C75" t="s">
         <v>843</v>
       </c>
@@ -38832,61 +39049,64 @@
         <v>{{ acta2 }}</v>
       </c>
       <c r="H75">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="I75" t="s">
+        <v>1758</v>
+      </c>
+      <c r="J75" t="s">
         <v>12</v>
       </c>
-      <c r="J75" t="s">
+      <c r="K75" t="s">
         <v>292</v>
       </c>
-      <c r="K75" t="str">
+      <c r="L75" t="str">
         <f t="shared" si="9"/>
         <v>'uso_epp' : r_val['uso_epp'],</v>
       </c>
-      <c r="L75" t="str">
+      <c r="M75" t="str">
         <f t="shared" si="13"/>
         <v>'acta2': acta2,</v>
       </c>
-      <c r="M75" t="s">
+      <c r="N75" t="s">
         <v>558</v>
       </c>
-      <c r="N75" t="str">
+      <c r="O75" t="str">
         <f t="shared" si="14"/>
         <v>img_path_acta2 = os.path.join(IMAGES_PATH, r_val["acta2"])</v>
       </c>
-      <c r="O75" t="str">
+      <c r="P75" t="str">
         <f t="shared" si="15"/>
         <v>if os.path.exists(img_path_acta2):</v>
       </c>
-      <c r="P75" t="str">
+      <c r="Q75" t="str">
         <f t="shared" si="16"/>
-        <v>acta2 = InlineImage(docx_tpl, img_path_acta2, height=Mm(190))</v>
-      </c>
-      <c r="Q75" t="s">
+        <v>acta2 = InlineImage(docx_tpl, img_path_acta2, height=Mm(155))</v>
+      </c>
+      <c r="R75" t="s">
         <v>560</v>
       </c>
-      <c r="R75" t="str">
+      <c r="S75" t="str">
         <f t="shared" si="17"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val["acta2"]}')</v>
       </c>
-      <c r="S75" t="str">
+      <c r="T75" t="str">
         <f t="shared" si="18"/>
         <v>acta2 = ''</v>
       </c>
-      <c r="T75" t="s">
+      <c r="U75" t="s">
         <v>559</v>
       </c>
-      <c r="U75" t="str">
+      <c r="V75" t="str">
         <f t="shared" si="19"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["acta2"]}: {e}')</v>
       </c>
-      <c r="V75" t="str">
+      <c r="W75" t="str">
         <f t="shared" si="20"/>
         <v>acta2 = ''</v>
       </c>
     </row>
-    <row r="76" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="76" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C76" t="s">
         <v>843</v>
       </c>
@@ -38905,61 +39125,64 @@
         <v>{{ crono_anual }}</v>
       </c>
       <c r="H76">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="I76" t="s">
+        <v>1758</v>
+      </c>
+      <c r="J76" t="s">
         <v>13</v>
       </c>
-      <c r="J76" t="s">
+      <c r="K76" t="s">
         <v>293</v>
       </c>
-      <c r="K76" t="str">
+      <c r="L76" t="str">
         <f t="shared" si="9"/>
         <v>'detectores_mov' : r_val['detectores_mov'],</v>
       </c>
-      <c r="L76" t="str">
+      <c r="M76" t="str">
         <f t="shared" si="13"/>
         <v>'crono_anual': crono_anual,</v>
       </c>
-      <c r="M76" t="s">
+      <c r="N76" t="s">
         <v>558</v>
       </c>
-      <c r="N76" t="str">
+      <c r="O76" t="str">
         <f t="shared" si="14"/>
         <v>img_path_crono_anual = os.path.join(IMAGES_PATH, r_val["crono_anual"])</v>
       </c>
-      <c r="O76" t="str">
+      <c r="P76" t="str">
         <f t="shared" si="15"/>
         <v>if os.path.exists(img_path_crono_anual):</v>
       </c>
-      <c r="P76" t="str">
+      <c r="Q76" t="str">
         <f t="shared" si="16"/>
-        <v>crono_anual = InlineImage(docx_tpl, img_path_crono_anual, height=Mm(190))</v>
-      </c>
-      <c r="Q76" t="s">
+        <v>crono_anual = InlineImage(docx_tpl, img_path_crono_anual, height=Mm(155))</v>
+      </c>
+      <c r="R76" t="s">
         <v>560</v>
       </c>
-      <c r="R76" t="str">
+      <c r="S76" t="str">
         <f t="shared" si="17"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val["crono_anual"]}')</v>
       </c>
-      <c r="S76" t="str">
+      <c r="T76" t="str">
         <f t="shared" si="18"/>
         <v>crono_anual = ''</v>
       </c>
-      <c r="T76" t="s">
+      <c r="U76" t="s">
         <v>559</v>
       </c>
-      <c r="U76" t="str">
+      <c r="V76" t="str">
         <f t="shared" si="19"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["crono_anual"]}: {e}')</v>
       </c>
-      <c r="V76" t="str">
+      <c r="W76" t="str">
         <f t="shared" si="20"/>
         <v>crono_anual = ''</v>
       </c>
     </row>
-    <row r="77" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="77" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C77" t="s">
         <v>843</v>
       </c>
@@ -38978,61 +39201,64 @@
         <v>{{ mantto1 }}</v>
       </c>
       <c r="H77">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="I77" t="s">
+        <v>1758</v>
+      </c>
+      <c r="J77" t="s">
         <v>568</v>
       </c>
-      <c r="J77" t="s">
+      <c r="K77" t="s">
         <v>567</v>
       </c>
-      <c r="K77" t="str">
+      <c r="L77" t="str">
         <f t="shared" si="9"/>
         <v>'ubicación_mov' : r_val['ubicación_mov'],</v>
       </c>
-      <c r="L77" t="str">
+      <c r="M77" t="str">
         <f t="shared" si="13"/>
         <v>'mantto1': mantto1,</v>
       </c>
-      <c r="M77" t="s">
+      <c r="N77" t="s">
         <v>558</v>
       </c>
-      <c r="N77" t="str">
+      <c r="O77" t="str">
         <f t="shared" si="14"/>
         <v>img_path_mantto1 = os.path.join(IMAGES_PATH, r_val["mantto1"])</v>
       </c>
-      <c r="O77" t="str">
+      <c r="P77" t="str">
         <f t="shared" si="15"/>
         <v>if os.path.exists(img_path_mantto1):</v>
       </c>
-      <c r="P77" t="str">
+      <c r="Q77" t="str">
         <f t="shared" si="16"/>
-        <v>mantto1 = InlineImage(docx_tpl, img_path_mantto1, height=Mm(190))</v>
-      </c>
-      <c r="Q77" t="s">
+        <v>mantto1 = InlineImage(docx_tpl, img_path_mantto1, height=Mm(155))</v>
+      </c>
+      <c r="R77" t="s">
         <v>560</v>
       </c>
-      <c r="R77" t="str">
+      <c r="S77" t="str">
         <f t="shared" si="17"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val["mantto1"]}')</v>
       </c>
-      <c r="S77" t="str">
+      <c r="T77" t="str">
         <f t="shared" si="18"/>
         <v>mantto1 = ''</v>
       </c>
-      <c r="T77" t="s">
+      <c r="U77" t="s">
         <v>559</v>
       </c>
-      <c r="U77" t="str">
+      <c r="V77" t="str">
         <f t="shared" si="19"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["mantto1"]}: {e}')</v>
       </c>
-      <c r="V77" t="str">
+      <c r="W77" t="str">
         <f t="shared" si="20"/>
         <v>mantto1 = ''</v>
       </c>
     </row>
-    <row r="78" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="78" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C78" t="s">
         <v>843</v>
       </c>
@@ -39051,61 +39277,64 @@
         <v>{{ mantto2 }}</v>
       </c>
       <c r="H78">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="I78" t="s">
+        <v>1758</v>
+      </c>
+      <c r="J78" t="s">
         <v>575</v>
       </c>
-      <c r="J78" t="s">
+      <c r="K78" t="s">
         <v>576</v>
       </c>
-      <c r="K78" t="str">
+      <c r="L78" t="str">
         <f t="shared" si="9"/>
         <v>'site_emer' : r_val['site_emer'],</v>
       </c>
-      <c r="L78" t="str">
+      <c r="M78" t="str">
         <f t="shared" si="13"/>
         <v>'mantto2': mantto2,</v>
       </c>
-      <c r="M78" t="s">
+      <c r="N78" t="s">
         <v>558</v>
       </c>
-      <c r="N78" t="str">
+      <c r="O78" t="str">
         <f t="shared" si="14"/>
         <v>img_path_mantto2 = os.path.join(IMAGES_PATH, r_val["mantto2"])</v>
       </c>
-      <c r="O78" t="str">
+      <c r="P78" t="str">
         <f t="shared" si="15"/>
         <v>if os.path.exists(img_path_mantto2):</v>
       </c>
-      <c r="P78" t="str">
+      <c r="Q78" t="str">
         <f t="shared" si="16"/>
-        <v>mantto2 = InlineImage(docx_tpl, img_path_mantto2, height=Mm(190))</v>
-      </c>
-      <c r="Q78" t="s">
+        <v>mantto2 = InlineImage(docx_tpl, img_path_mantto2, height=Mm(155))</v>
+      </c>
+      <c r="R78" t="s">
         <v>560</v>
       </c>
-      <c r="R78" t="str">
+      <c r="S78" t="str">
         <f t="shared" si="17"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val["mantto2"]}')</v>
       </c>
-      <c r="S78" t="str">
+      <c r="T78" t="str">
         <f t="shared" si="18"/>
         <v>mantto2 = ''</v>
       </c>
-      <c r="T78" t="s">
+      <c r="U78" t="s">
         <v>559</v>
       </c>
-      <c r="U78" t="str">
+      <c r="V78" t="str">
         <f t="shared" si="19"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["mantto2"]}: {e}')</v>
       </c>
-      <c r="V78" t="str">
+      <c r="W78" t="str">
         <f t="shared" si="20"/>
         <v>mantto2 = ''</v>
       </c>
     </row>
-    <row r="79" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="79" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C79" t="s">
         <v>843</v>
       </c>
@@ -39124,61 +39353,64 @@
         <v>{{ simulacro }}</v>
       </c>
       <c r="H79">
-        <v>95</v>
+        <v>155</v>
       </c>
       <c r="I79" t="s">
+        <v>1758</v>
+      </c>
+      <c r="J79" t="s">
         <v>574</v>
       </c>
-      <c r="J79" t="s">
+      <c r="K79" t="s">
         <v>573</v>
       </c>
-      <c r="K79" t="str">
-        <f t="shared" ref="K79:K110" si="25">+_xlfn.CONCAT("'",I79,"' : r_val['",I79,"'],")</f>
+      <c r="L79" t="str">
+        <f t="shared" ref="L79:L110" si="25">+_xlfn.CONCAT("'",J79,"' : r_val['",J79,"'],")</f>
         <v>'ubicacion_site' : r_val['ubicacion_site'],</v>
       </c>
-      <c r="L79" t="str">
+      <c r="M79" t="str">
         <f t="shared" si="13"/>
         <v>'simulacro': simulacro,</v>
       </c>
-      <c r="M79" t="s">
+      <c r="N79" t="s">
         <v>558</v>
       </c>
-      <c r="N79" t="str">
+      <c r="O79" t="str">
         <f t="shared" si="14"/>
         <v>img_path_simulacro = os.path.join(IMAGES_PATH, r_val["simulacro"])</v>
       </c>
-      <c r="O79" t="str">
+      <c r="P79" t="str">
         <f t="shared" si="15"/>
         <v>if os.path.exists(img_path_simulacro):</v>
       </c>
-      <c r="P79" t="str">
+      <c r="Q79" t="str">
         <f t="shared" si="16"/>
-        <v>simulacro = InlineImage(docx_tpl, img_path_simulacro, height=Mm(95))</v>
-      </c>
-      <c r="Q79" t="s">
+        <v>simulacro = InlineImage(docx_tpl, img_path_simulacro, height=Mm(155))</v>
+      </c>
+      <c r="R79" t="s">
         <v>560</v>
       </c>
-      <c r="R79" t="str">
+      <c r="S79" t="str">
         <f t="shared" si="17"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val["simulacro"]}')</v>
       </c>
-      <c r="S79" t="str">
+      <c r="T79" t="str">
         <f t="shared" si="18"/>
         <v>simulacro = ''</v>
       </c>
-      <c r="T79" t="s">
+      <c r="U79" t="s">
         <v>559</v>
       </c>
-      <c r="U79" t="str">
+      <c r="V79" t="str">
         <f t="shared" si="19"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["simulacro"]}: {e}')</v>
       </c>
-      <c r="V79" t="str">
+      <c r="W79" t="str">
         <f t="shared" si="20"/>
         <v>simulacro = ''</v>
       </c>
     </row>
-    <row r="80" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="80" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C80" t="s">
         <v>843</v>
       </c>
@@ -39197,61 +39429,67 @@
         <v>{{ capacitacion }}</v>
       </c>
       <c r="H80">
-        <v>95</v>
+        <v>155</v>
       </c>
       <c r="I80" t="s">
+        <v>1758</v>
+      </c>
+      <c r="J80" t="s">
         <v>15</v>
       </c>
-      <c r="J80" t="s">
+      <c r="K80" t="s">
         <v>295</v>
       </c>
-      <c r="K80" t="str">
+      <c r="L80" t="str">
         <f t="shared" si="25"/>
         <v>'hidrantes' : r_val['hidrantes'],</v>
       </c>
-      <c r="L80" t="str">
+      <c r="M80" t="str">
         <f t="shared" si="13"/>
         <v>'capacitacion': capacitacion,</v>
       </c>
-      <c r="M80" t="s">
+      <c r="N80" t="s">
         <v>558</v>
       </c>
-      <c r="N80" t="str">
+      <c r="O80" t="str">
         <f t="shared" si="14"/>
         <v>img_path_capacitacion = os.path.join(IMAGES_PATH, r_val["capacitacion"])</v>
       </c>
-      <c r="O80" t="str">
+      <c r="P80" t="str">
         <f t="shared" si="15"/>
         <v>if os.path.exists(img_path_capacitacion):</v>
       </c>
-      <c r="P80" t="str">
+      <c r="Q80" t="str">
         <f t="shared" si="16"/>
-        <v>capacitacion = InlineImage(docx_tpl, img_path_capacitacion, height=Mm(95))</v>
-      </c>
-      <c r="Q80" t="s">
+        <v>capacitacion = InlineImage(docx_tpl, img_path_capacitacion, height=Mm(155))</v>
+      </c>
+      <c r="R80" t="s">
         <v>560</v>
       </c>
-      <c r="R80" t="str">
+      <c r="S80" t="str">
         <f t="shared" si="17"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val["capacitacion"]}')</v>
       </c>
-      <c r="S80" t="str">
+      <c r="T80" t="str">
         <f t="shared" si="18"/>
         <v>capacitacion = ''</v>
       </c>
-      <c r="T80" t="s">
+      <c r="U80" t="s">
         <v>559</v>
       </c>
-      <c r="U80" t="str">
+      <c r="V80" t="str">
         <f t="shared" si="19"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["capacitacion"]}: {e}')</v>
       </c>
-      <c r="V80" t="str">
+      <c r="W80" t="str">
         <f t="shared" si="20"/>
         <v>capacitacion = ''</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="C81" t="s">
+        <v>843</v>
+      </c>
       <c r="D81" t="s">
         <v>832</v>
       </c>
@@ -39267,61 +39505,67 @@
         <v>{{ inv_quim }}</v>
       </c>
       <c r="H81">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="I81" t="s">
+        <v>1758</v>
+      </c>
+      <c r="J81" t="s">
         <v>16</v>
       </c>
-      <c r="J81" t="s">
+      <c r="K81" t="s">
         <v>296</v>
       </c>
-      <c r="K81" t="str">
+      <c r="L81" t="str">
         <f t="shared" si="25"/>
         <v>'aspersores' : r_val['aspersores'],</v>
       </c>
-      <c r="L81" t="str">
+      <c r="M81" t="str">
         <f t="shared" si="13"/>
         <v>'inv_quim': inv_quim,</v>
       </c>
-      <c r="M81" t="s">
+      <c r="N81" t="s">
         <v>558</v>
       </c>
-      <c r="N81" t="str">
+      <c r="O81" t="str">
         <f t="shared" si="14"/>
         <v>img_path_inv_quim = os.path.join(IMAGES_PATH, r_val["inv_quim"])</v>
       </c>
-      <c r="O81" t="str">
+      <c r="P81" t="str">
         <f t="shared" si="15"/>
         <v>if os.path.exists(img_path_inv_quim):</v>
       </c>
-      <c r="P81" t="str">
+      <c r="Q81" t="str">
         <f t="shared" si="16"/>
-        <v>inv_quim = InlineImage(docx_tpl, img_path_inv_quim, height=Mm(190))</v>
-      </c>
-      <c r="Q81" t="s">
+        <v>inv_quim = InlineImage(docx_tpl, img_path_inv_quim, height=Mm(155))</v>
+      </c>
+      <c r="R81" t="s">
         <v>560</v>
       </c>
-      <c r="R81" t="str">
+      <c r="S81" t="str">
         <f t="shared" si="17"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val["inv_quim"]}')</v>
       </c>
-      <c r="S81" t="str">
+      <c r="T81" t="str">
         <f t="shared" si="18"/>
         <v>inv_quim = ''</v>
       </c>
-      <c r="T81" t="s">
+      <c r="U81" t="s">
         <v>559</v>
       </c>
-      <c r="U81" t="str">
+      <c r="V81" t="str">
         <f t="shared" si="19"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["inv_quim"]}: {e}')</v>
       </c>
-      <c r="V81" t="str">
+      <c r="W81" t="str">
         <f t="shared" si="20"/>
         <v>inv_quim = ''</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="C82" t="s">
+        <v>843</v>
+      </c>
       <c r="D82" t="s">
         <v>832</v>
       </c>
@@ -39337,61 +39581,67 @@
         <v>{{ inv_emer }}</v>
       </c>
       <c r="H82">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="I82" t="s">
+        <v>1758</v>
+      </c>
+      <c r="J82" t="s">
         <v>17</v>
       </c>
-      <c r="J82" t="s">
+      <c r="K82" t="s">
         <v>297</v>
       </c>
-      <c r="K82" t="str">
+      <c r="L82" t="str">
         <f t="shared" si="25"/>
         <v>'bomberos' : r_val['bomberos'],</v>
       </c>
-      <c r="L82" t="str">
+      <c r="M82" t="str">
         <f t="shared" si="13"/>
         <v>'inv_emer': inv_emer,</v>
       </c>
-      <c r="M82" t="s">
+      <c r="N82" t="s">
         <v>558</v>
       </c>
-      <c r="N82" t="str">
+      <c r="O82" t="str">
         <f t="shared" si="14"/>
         <v>img_path_inv_emer = os.path.join(IMAGES_PATH, r_val["inv_emer"])</v>
       </c>
-      <c r="O82" t="str">
+      <c r="P82" t="str">
         <f t="shared" si="15"/>
         <v>if os.path.exists(img_path_inv_emer):</v>
       </c>
-      <c r="P82" t="str">
+      <c r="Q82" t="str">
         <f t="shared" si="16"/>
-        <v>inv_emer = InlineImage(docx_tpl, img_path_inv_emer, height=Mm(190))</v>
-      </c>
-      <c r="Q82" t="s">
+        <v>inv_emer = InlineImage(docx_tpl, img_path_inv_emer, height=Mm(155))</v>
+      </c>
+      <c r="R82" t="s">
         <v>560</v>
       </c>
-      <c r="R82" t="str">
+      <c r="S82" t="str">
         <f t="shared" si="17"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val["inv_emer"]}')</v>
       </c>
-      <c r="S82" t="str">
+      <c r="T82" t="str">
         <f t="shared" si="18"/>
         <v>inv_emer = ''</v>
       </c>
-      <c r="T82" t="s">
+      <c r="U82" t="s">
         <v>559</v>
       </c>
-      <c r="U82" t="str">
+      <c r="V82" t="str">
         <f t="shared" si="19"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["inv_emer"]}: {e}')</v>
       </c>
-      <c r="V82" t="str">
+      <c r="W82" t="str">
         <f t="shared" si="20"/>
         <v>inv_emer = ''</v>
       </c>
     </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="83" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="C83" t="s">
+        <v>843</v>
+      </c>
       <c r="D83" t="s">
         <v>832</v>
       </c>
@@ -39407,61 +39657,64 @@
         <v>{{ bit_emer }}</v>
       </c>
       <c r="H83">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="I83" t="s">
+        <v>1758</v>
+      </c>
+      <c r="J83" t="s">
         <v>566</v>
       </c>
-      <c r="J83" t="s">
+      <c r="K83" t="s">
         <v>565</v>
       </c>
-      <c r="K83" t="str">
+      <c r="L83" t="str">
         <f t="shared" si="25"/>
         <v>'ubicacion_bombero' : r_val['ubicacion_bombero'],</v>
       </c>
-      <c r="L83" t="str">
+      <c r="M83" t="str">
         <f t="shared" si="13"/>
         <v>'bit_emer': bit_emer,</v>
       </c>
-      <c r="M83" t="s">
+      <c r="N83" t="s">
         <v>558</v>
       </c>
-      <c r="N83" t="str">
+      <c r="O83" t="str">
         <f t="shared" si="14"/>
         <v>img_path_bit_emer = os.path.join(IMAGES_PATH, r_val["bit_emer"])</v>
       </c>
-      <c r="O83" t="str">
+      <c r="P83" t="str">
         <f t="shared" si="15"/>
         <v>if os.path.exists(img_path_bit_emer):</v>
       </c>
-      <c r="P83" t="str">
+      <c r="Q83" t="str">
         <f t="shared" si="16"/>
-        <v>bit_emer = InlineImage(docx_tpl, img_path_bit_emer, height=Mm(190))</v>
-      </c>
-      <c r="Q83" t="s">
+        <v>bit_emer = InlineImage(docx_tpl, img_path_bit_emer, height=Mm(155))</v>
+      </c>
+      <c r="R83" t="s">
         <v>560</v>
       </c>
-      <c r="R83" t="str">
+      <c r="S83" t="str">
         <f t="shared" si="17"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val["bit_emer"]}')</v>
       </c>
-      <c r="S83" t="str">
+      <c r="T83" t="str">
         <f t="shared" si="18"/>
         <v>bit_emer = ''</v>
       </c>
-      <c r="T83" t="s">
+      <c r="U83" t="s">
         <v>559</v>
       </c>
-      <c r="U83" t="str">
+      <c r="V83" t="str">
         <f t="shared" si="19"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["bit_emer"]}: {e}')</v>
       </c>
-      <c r="V83" t="str">
+      <c r="W83" t="str">
         <f t="shared" si="20"/>
         <v>bit_emer = ''</v>
       </c>
     </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="84" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C84" t="s">
         <v>843</v>
       </c>
@@ -39480,61 +39733,64 @@
         <v>{{ insp_bot }}</v>
       </c>
       <c r="H84">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="I84" t="s">
+        <v>1758</v>
+      </c>
+      <c r="J84" t="s">
         <v>18</v>
       </c>
-      <c r="J84" t="s">
+      <c r="K84" t="s">
         <v>298</v>
       </c>
-      <c r="K84" t="str">
+      <c r="L84" t="str">
         <f t="shared" si="25"/>
         <v>'detector_gas' : r_val['detector_gas'],</v>
       </c>
-      <c r="L84" t="str">
+      <c r="M84" t="str">
         <f t="shared" si="13"/>
         <v>'insp_bot': insp_bot,</v>
       </c>
-      <c r="M84" t="s">
+      <c r="N84" t="s">
         <v>558</v>
       </c>
-      <c r="N84" t="str">
+      <c r="O84" t="str">
         <f t="shared" si="14"/>
         <v>img_path_insp_bot = os.path.join(IMAGES_PATH, r_val["insp_bot"])</v>
       </c>
-      <c r="O84" t="str">
+      <c r="P84" t="str">
         <f t="shared" si="15"/>
         <v>if os.path.exists(img_path_insp_bot):</v>
       </c>
-      <c r="P84" t="str">
+      <c r="Q84" t="str">
         <f t="shared" si="16"/>
-        <v>insp_bot = InlineImage(docx_tpl, img_path_insp_bot, height=Mm(190))</v>
-      </c>
-      <c r="Q84" t="s">
+        <v>insp_bot = InlineImage(docx_tpl, img_path_insp_bot, height=Mm(155))</v>
+      </c>
+      <c r="R84" t="s">
         <v>560</v>
       </c>
-      <c r="R84" t="str">
+      <c r="S84" t="str">
         <f t="shared" si="17"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val["insp_bot"]}')</v>
       </c>
-      <c r="S84" t="str">
+      <c r="T84" t="str">
         <f t="shared" si="18"/>
         <v>insp_bot = ''</v>
       </c>
-      <c r="T84" t="s">
+      <c r="U84" t="s">
         <v>559</v>
       </c>
-      <c r="U84" t="str">
+      <c r="V84" t="str">
         <f t="shared" si="19"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["insp_bot"]}: {e}')</v>
       </c>
-      <c r="V84" t="str">
+      <c r="W84" t="str">
         <f t="shared" si="20"/>
         <v>insp_bot = ''</v>
       </c>
     </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="85" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C85" t="s">
         <v>843</v>
       </c>
@@ -39553,61 +39809,67 @@
         <v>{{ insp_ext }}</v>
       </c>
       <c r="H85">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="I85" t="s">
+        <v>1758</v>
+      </c>
+      <c r="J85" t="s">
         <v>570</v>
       </c>
-      <c r="J85" t="s">
+      <c r="K85" t="s">
         <v>569</v>
       </c>
-      <c r="K85" t="str">
+      <c r="L85" t="str">
         <f t="shared" si="25"/>
         <v>'ubicación_gas' : r_val['ubicación_gas'],</v>
       </c>
-      <c r="L85" t="str">
+      <c r="M85" t="str">
         <f t="shared" si="13"/>
         <v>'insp_ext': insp_ext,</v>
       </c>
-      <c r="M85" t="s">
+      <c r="N85" t="s">
         <v>558</v>
       </c>
-      <c r="N85" t="str">
+      <c r="O85" t="str">
         <f t="shared" si="14"/>
         <v>img_path_insp_ext = os.path.join(IMAGES_PATH, r_val["insp_ext"])</v>
       </c>
-      <c r="O85" t="str">
+      <c r="P85" t="str">
         <f t="shared" si="15"/>
         <v>if os.path.exists(img_path_insp_ext):</v>
       </c>
-      <c r="P85" t="str">
+      <c r="Q85" t="str">
         <f t="shared" si="16"/>
-        <v>insp_ext = InlineImage(docx_tpl, img_path_insp_ext, height=Mm(190))</v>
-      </c>
-      <c r="Q85" t="s">
+        <v>insp_ext = InlineImage(docx_tpl, img_path_insp_ext, height=Mm(149))</v>
+      </c>
+      <c r="R85" t="s">
         <v>560</v>
       </c>
-      <c r="R85" t="str">
+      <c r="S85" t="str">
         <f t="shared" si="17"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val["insp_ext"]}')</v>
       </c>
-      <c r="S85" t="str">
+      <c r="T85" t="str">
         <f t="shared" si="18"/>
         <v>insp_ext = ''</v>
       </c>
-      <c r="T85" t="s">
+      <c r="U85" t="s">
         <v>559</v>
       </c>
-      <c r="U85" t="str">
+      <c r="V85" t="str">
         <f t="shared" si="19"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["insp_ext"]}: {e}')</v>
       </c>
-      <c r="V85" t="str">
+      <c r="W85" t="str">
         <f t="shared" si="20"/>
         <v>insp_ext = ''</v>
       </c>
     </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="86" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="C86" t="s">
+        <v>843</v>
+      </c>
       <c r="D86" t="s">
         <v>832</v>
       </c>
@@ -39623,61 +39885,64 @@
         <v>{{ insp_dh }}</v>
       </c>
       <c r="H86">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="I86" t="s">
+        <v>1758</v>
+      </c>
+      <c r="J86" t="s">
         <v>19</v>
       </c>
-      <c r="J86" t="s">
+      <c r="K86" t="s">
         <v>299</v>
       </c>
-      <c r="K86" t="str">
+      <c r="L86" t="str">
         <f t="shared" si="25"/>
         <v>'equipo_brigada' : r_val['equipo_brigada'],</v>
       </c>
-      <c r="L86" t="str">
+      <c r="M86" t="str">
         <f t="shared" si="13"/>
         <v>'insp_dh': insp_dh,</v>
       </c>
-      <c r="M86" t="s">
+      <c r="N86" t="s">
         <v>558</v>
       </c>
-      <c r="N86" t="str">
+      <c r="O86" t="str">
         <f t="shared" si="14"/>
         <v>img_path_insp_dh = os.path.join(IMAGES_PATH, r_val["insp_dh"])</v>
       </c>
-      <c r="O86" t="str">
+      <c r="P86" t="str">
         <f t="shared" si="15"/>
         <v>if os.path.exists(img_path_insp_dh):</v>
       </c>
-      <c r="P86" t="str">
+      <c r="Q86" t="str">
         <f t="shared" si="16"/>
-        <v>insp_dh = InlineImage(docx_tpl, img_path_insp_dh, height=Mm(190))</v>
-      </c>
-      <c r="Q86" t="s">
+        <v>insp_dh = InlineImage(docx_tpl, img_path_insp_dh, height=Mm(155))</v>
+      </c>
+      <c r="R86" t="s">
         <v>560</v>
       </c>
-      <c r="R86" t="str">
+      <c r="S86" t="str">
         <f t="shared" si="17"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val["insp_dh"]}')</v>
       </c>
-      <c r="S86" t="str">
+      <c r="T86" t="str">
         <f t="shared" si="18"/>
         <v>insp_dh = ''</v>
       </c>
-      <c r="T86" t="s">
+      <c r="U86" t="s">
         <v>559</v>
       </c>
-      <c r="U86" t="str">
+      <c r="V86" t="str">
         <f t="shared" si="19"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["insp_dh"]}: {e}')</v>
       </c>
-      <c r="V86" t="str">
+      <c r="W86" t="str">
         <f t="shared" si="20"/>
         <v>insp_dh = ''</v>
       </c>
     </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="87" spans="3:23" x14ac:dyDescent="0.3">
       <c r="D87" t="s">
         <v>832</v>
       </c>
@@ -39693,61 +39958,64 @@
         <v>{{ insp_lamp }}</v>
       </c>
       <c r="H87">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="I87" t="s">
+        <v>1758</v>
+      </c>
+      <c r="J87" t="s">
         <v>578</v>
       </c>
-      <c r="J87" t="s">
+      <c r="K87" t="s">
         <v>577</v>
       </c>
-      <c r="K87" t="str">
+      <c r="L87" t="str">
         <f t="shared" si="25"/>
         <v>'ubicacion_brigada' : r_val['ubicacion_brigada'],</v>
       </c>
-      <c r="L87" t="str">
+      <c r="M87" t="str">
         <f t="shared" si="13"/>
         <v>'insp_lamp': insp_lamp,</v>
       </c>
-      <c r="M87" t="s">
+      <c r="N87" t="s">
         <v>558</v>
       </c>
-      <c r="N87" t="str">
+      <c r="O87" t="str">
         <f t="shared" si="14"/>
         <v>img_path_insp_lamp = os.path.join(IMAGES_PATH, r_val["insp_lamp"])</v>
       </c>
-      <c r="O87" t="str">
+      <c r="P87" t="str">
         <f t="shared" si="15"/>
         <v>if os.path.exists(img_path_insp_lamp):</v>
       </c>
-      <c r="P87" t="str">
+      <c r="Q87" t="str">
         <f t="shared" si="16"/>
-        <v>insp_lamp = InlineImage(docx_tpl, img_path_insp_lamp, height=Mm(190))</v>
-      </c>
-      <c r="Q87" t="s">
+        <v>insp_lamp = InlineImage(docx_tpl, img_path_insp_lamp, height=Mm(155))</v>
+      </c>
+      <c r="R87" t="s">
         <v>560</v>
       </c>
-      <c r="R87" t="str">
+      <c r="S87" t="str">
         <f t="shared" si="17"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val["insp_lamp"]}')</v>
       </c>
-      <c r="S87" t="str">
+      <c r="T87" t="str">
         <f t="shared" si="18"/>
         <v>insp_lamp = ''</v>
       </c>
-      <c r="T87" t="s">
+      <c r="U87" t="s">
         <v>559</v>
       </c>
-      <c r="U87" t="str">
+      <c r="V87" t="str">
         <f t="shared" si="19"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["insp_lamp"]}: {e}')</v>
       </c>
-      <c r="V87" t="str">
+      <c r="W87" t="str">
         <f t="shared" si="20"/>
         <v>insp_lamp = ''</v>
       </c>
     </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="88" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C88" t="s">
         <v>843</v>
       </c>
@@ -39766,61 +40034,64 @@
         <v>{{ insp_alarm }}</v>
       </c>
       <c r="H88">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="I88" t="s">
+        <v>1758</v>
+      </c>
+      <c r="J88" t="s">
         <v>708</v>
       </c>
-      <c r="J88" t="s">
+      <c r="K88" t="s">
         <v>709</v>
       </c>
-      <c r="K88" t="str">
+      <c r="L88" t="str">
         <f t="shared" si="25"/>
         <v>'ubiacion_brigadas' : r_val['ubiacion_brigadas'],</v>
       </c>
-      <c r="L88" t="str">
+      <c r="M88" t="str">
         <f t="shared" si="13"/>
         <v>'insp_alarm': insp_alarm,</v>
       </c>
-      <c r="M88" t="s">
+      <c r="N88" t="s">
         <v>558</v>
       </c>
-      <c r="N88" t="str">
+      <c r="O88" t="str">
         <f t="shared" si="14"/>
         <v>img_path_insp_alarm = os.path.join(IMAGES_PATH, r_val["insp_alarm"])</v>
       </c>
-      <c r="O88" t="str">
+      <c r="P88" t="str">
         <f t="shared" si="15"/>
         <v>if os.path.exists(img_path_insp_alarm):</v>
       </c>
-      <c r="P88" t="str">
+      <c r="Q88" t="str">
         <f t="shared" si="16"/>
-        <v>insp_alarm = InlineImage(docx_tpl, img_path_insp_alarm, height=Mm(190))</v>
-      </c>
-      <c r="Q88" t="s">
+        <v>insp_alarm = InlineImage(docx_tpl, img_path_insp_alarm, height=Mm(155))</v>
+      </c>
+      <c r="R88" t="s">
         <v>560</v>
       </c>
-      <c r="R88" t="str">
+      <c r="S88" t="str">
         <f t="shared" si="17"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val["insp_alarm"]}')</v>
       </c>
-      <c r="S88" t="str">
+      <c r="T88" t="str">
         <f t="shared" si="18"/>
         <v>insp_alarm = ''</v>
       </c>
-      <c r="T88" t="s">
+      <c r="U88" t="s">
         <v>559</v>
       </c>
-      <c r="U88" t="str">
+      <c r="V88" t="str">
         <f t="shared" si="19"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["insp_alarm"]}: {e}')</v>
       </c>
-      <c r="V88" t="str">
+      <c r="W88" t="str">
         <f t="shared" si="20"/>
         <v>insp_alarm = ''</v>
       </c>
     </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="89" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C89" t="s">
         <v>843</v>
       </c>
@@ -39839,61 +40110,64 @@
         <v>{{ ev_sim1 }}</v>
       </c>
       <c r="H89">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="I89" t="s">
+        <v>1758</v>
+      </c>
+      <c r="J89" t="s">
         <v>20</v>
       </c>
-      <c r="J89" t="s">
+      <c r="K89" t="s">
         <v>300</v>
       </c>
-      <c r="K89" t="str">
+      <c r="L89" t="str">
         <f t="shared" si="25"/>
         <v>'lampara' : r_val['lampara'],</v>
       </c>
-      <c r="L89" t="str">
+      <c r="M89" t="str">
         <f t="shared" si="13"/>
         <v>'ev_sim1': ev_sim1,</v>
       </c>
-      <c r="M89" t="s">
+      <c r="N89" t="s">
         <v>558</v>
       </c>
-      <c r="N89" t="str">
+      <c r="O89" t="str">
         <f t="shared" si="14"/>
         <v>img_path_ev_sim1 = os.path.join(IMAGES_PATH, r_val["ev_sim1"])</v>
       </c>
-      <c r="O89" t="str">
+      <c r="P89" t="str">
         <f t="shared" si="15"/>
         <v>if os.path.exists(img_path_ev_sim1):</v>
       </c>
-      <c r="P89" t="str">
+      <c r="Q89" t="str">
         <f t="shared" si="16"/>
-        <v>ev_sim1 = InlineImage(docx_tpl, img_path_ev_sim1, height=Mm(190))</v>
-      </c>
-      <c r="Q89" t="s">
+        <v>ev_sim1 = InlineImage(docx_tpl, img_path_ev_sim1, height=Mm(155))</v>
+      </c>
+      <c r="R89" t="s">
         <v>560</v>
       </c>
-      <c r="R89" t="str">
+      <c r="S89" t="str">
         <f t="shared" si="17"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val["ev_sim1"]}')</v>
       </c>
-      <c r="S89" t="str">
+      <c r="T89" t="str">
         <f t="shared" si="18"/>
         <v>ev_sim1 = ''</v>
       </c>
-      <c r="T89" t="s">
+      <c r="U89" t="s">
         <v>559</v>
       </c>
-      <c r="U89" t="str">
+      <c r="V89" t="str">
         <f t="shared" si="19"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["ev_sim1"]}: {e}')</v>
       </c>
-      <c r="V89" t="str">
+      <c r="W89" t="str">
         <f t="shared" si="20"/>
         <v>ev_sim1 = ''</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C90" t="s">
         <v>843</v>
       </c>
@@ -39912,61 +40186,67 @@
         <v>{{ ev_sim2 }}</v>
       </c>
       <c r="H90">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="I90" t="s">
+        <v>1758</v>
+      </c>
+      <c r="J90" t="s">
         <v>562</v>
       </c>
-      <c r="J90" t="s">
+      <c r="K90" t="s">
         <v>561</v>
       </c>
-      <c r="K90" t="str">
+      <c r="L90" t="str">
         <f t="shared" si="25"/>
         <v>'ubicacion_lampara' : r_val['ubicacion_lampara'],</v>
       </c>
-      <c r="L90" t="str">
+      <c r="M90" t="str">
         <f t="shared" si="13"/>
         <v>'ev_sim2': ev_sim2,</v>
       </c>
-      <c r="M90" t="s">
+      <c r="N90" t="s">
         <v>558</v>
       </c>
-      <c r="N90" t="str">
+      <c r="O90" t="str">
         <f t="shared" si="14"/>
         <v>img_path_ev_sim2 = os.path.join(IMAGES_PATH, r_val["ev_sim2"])</v>
       </c>
-      <c r="O90" t="str">
+      <c r="P90" t="str">
         <f t="shared" si="15"/>
         <v>if os.path.exists(img_path_ev_sim2):</v>
       </c>
-      <c r="P90" t="str">
+      <c r="Q90" t="str">
         <f t="shared" si="16"/>
-        <v>ev_sim2 = InlineImage(docx_tpl, img_path_ev_sim2, height=Mm(190))</v>
-      </c>
-      <c r="Q90" t="s">
+        <v>ev_sim2 = InlineImage(docx_tpl, img_path_ev_sim2, height=Mm(155))</v>
+      </c>
+      <c r="R90" t="s">
         <v>560</v>
       </c>
-      <c r="R90" t="str">
+      <c r="S90" t="str">
         <f t="shared" si="17"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val["ev_sim2"]}')</v>
       </c>
-      <c r="S90" t="str">
+      <c r="T90" t="str">
         <f t="shared" si="18"/>
         <v>ev_sim2 = ''</v>
       </c>
-      <c r="T90" t="s">
+      <c r="U90" t="s">
         <v>559</v>
       </c>
-      <c r="U90" t="str">
+      <c r="V90" t="str">
         <f t="shared" si="19"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["ev_sim2"]}: {e}')</v>
       </c>
-      <c r="V90" t="str">
+      <c r="W90" t="str">
         <f t="shared" si="20"/>
         <v>ev_sim2 = ''</v>
       </c>
     </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="91" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="C91" t="s">
+        <v>843</v>
+      </c>
       <c r="D91" t="s">
         <v>832</v>
       </c>
@@ -39982,61 +40262,64 @@
         <v>{{ visitas }}</v>
       </c>
       <c r="H91">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="I91" t="s">
+        <v>1758</v>
+      </c>
+      <c r="J91" t="s">
         <v>22</v>
       </c>
-      <c r="J91" t="s">
+      <c r="K91" t="s">
         <v>301</v>
       </c>
-      <c r="K91" t="str">
+      <c r="L91" t="str">
         <f t="shared" si="25"/>
         <v>'baterias' : r_val['baterias'],</v>
       </c>
-      <c r="L91" t="str">
+      <c r="M91" t="str">
         <f t="shared" si="13"/>
         <v>'visitas': visitas,</v>
       </c>
-      <c r="M91" t="s">
+      <c r="N91" t="s">
         <v>558</v>
       </c>
-      <c r="N91" t="str">
-        <f t="shared" ref="N91:N92" si="26">+_xlfn.CONCAT("img_path_",E91," = os.path.join(IMAGES_PATH, r_val[""",E91,"""])")</f>
+      <c r="O91" t="str">
+        <f t="shared" ref="O91:O92" si="26">+_xlfn.CONCAT("img_path_",E91," = os.path.join(IMAGES_PATH, r_val[""",E91,"""])")</f>
         <v>img_path_visitas = os.path.join(IMAGES_PATH, r_val["visitas"])</v>
       </c>
-      <c r="O91" t="str">
-        <f t="shared" ref="O91:O92" si="27">+_xlfn.CONCAT("if os.path.exists(img_path_",E91,"):")</f>
+      <c r="P91" t="str">
+        <f t="shared" ref="P91:P92" si="27">+_xlfn.CONCAT("if os.path.exists(img_path_",E91,"):")</f>
         <v>if os.path.exists(img_path_visitas):</v>
       </c>
-      <c r="P91" t="str">
-        <f t="shared" ref="P91:P92" si="28">+_xlfn.CONCAT(E91," = InlineImage(docx_tpl, img_path_",E91,", height=Mm(",H91,"))")</f>
-        <v>visitas = InlineImage(docx_tpl, img_path_visitas, height=Mm(190))</v>
-      </c>
-      <c r="Q91" t="s">
+      <c r="Q91" t="str">
+        <f t="shared" ref="Q91:Q92" si="28">+_xlfn.CONCAT(E91," = InlineImage(docx_tpl, img_path_",E91,", height=Mm(",H91,"))")</f>
+        <v>visitas = InlineImage(docx_tpl, img_path_visitas, height=Mm(155))</v>
+      </c>
+      <c r="R91" t="s">
         <v>560</v>
       </c>
-      <c r="R91" t="str">
-        <f t="shared" ref="R91:R92" si="29">+_xlfn.CONCAT("print(f'Advertencia: No se encontró la imagen {r_val[""",E91,"""]}')")</f>
+      <c r="S91" t="str">
+        <f t="shared" ref="S91:S92" si="29">+_xlfn.CONCAT("print(f'Advertencia: No se encontró la imagen {r_val[""",E91,"""]}')")</f>
         <v>print(f'Advertencia: No se encontró la imagen {r_val["visitas"]}')</v>
       </c>
-      <c r="S91" t="str">
-        <f t="shared" ref="S91:S92" si="30">+_xlfn.CONCAT(E91," = ''")</f>
+      <c r="T91" t="str">
+        <f t="shared" ref="T91:T92" si="30">+_xlfn.CONCAT(E91," = ''")</f>
         <v>visitas = ''</v>
       </c>
-      <c r="T91" t="s">
+      <c r="U91" t="s">
         <v>559</v>
       </c>
-      <c r="U91" t="str">
-        <f t="shared" ref="U91:U92" si="31">+_xlfn.CONCAT("print(f'Advertencia: No se pudo cargar la imagen {r_val[""",E91,"""]}: {e}')")</f>
+      <c r="V91" t="str">
+        <f t="shared" ref="V91:V92" si="31">+_xlfn.CONCAT("print(f'Advertencia: No se pudo cargar la imagen {r_val[""",E91,"""]}: {e}')")</f>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["visitas"]}: {e}')</v>
       </c>
-      <c r="V91" t="str">
-        <f t="shared" ref="V91:V92" si="32">+_xlfn.CONCAT(E91," = ''")</f>
+      <c r="W91" t="str">
+        <f t="shared" ref="W91:W92" si="32">+_xlfn.CONCAT(E91," = ''")</f>
         <v>visitas = ''</v>
       </c>
     </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="92" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C92" t="s">
         <v>843</v>
       </c>
@@ -40053,1295 +40336,1298 @@
         <v>951</v>
       </c>
       <c r="H92">
-        <v>60</v>
+        <v>155</v>
       </c>
       <c r="I92" t="s">
+        <v>1758</v>
+      </c>
+      <c r="J92" t="s">
         <v>572</v>
       </c>
-      <c r="J92" t="s">
+      <c r="K92" t="s">
         <v>571</v>
       </c>
-      <c r="K92" t="str">
+      <c r="L92" t="str">
         <f t="shared" si="25"/>
         <v>'ubiacion_baterias' : r_val['ubiacion_baterias'],</v>
       </c>
-      <c r="L92" t="str">
+      <c r="M92" t="str">
         <f t="shared" si="13"/>
         <v>'dir_emer': dir_emer,</v>
       </c>
-      <c r="M92" t="s">
+      <c r="N92" t="s">
         <v>558</v>
       </c>
-      <c r="N92" t="str">
+      <c r="O92" t="str">
         <f t="shared" si="26"/>
         <v>img_path_dir_emer = os.path.join(IMAGES_PATH, r_val["dir_emer"])</v>
       </c>
-      <c r="O92" t="str">
+      <c r="P92" t="str">
         <f t="shared" si="27"/>
         <v>if os.path.exists(img_path_dir_emer):</v>
       </c>
-      <c r="P92" t="str">
+      <c r="Q92" t="str">
         <f t="shared" si="28"/>
-        <v>dir_emer = InlineImage(docx_tpl, img_path_dir_emer, height=Mm(60))</v>
-      </c>
-      <c r="Q92" t="s">
+        <v>dir_emer = InlineImage(docx_tpl, img_path_dir_emer, height=Mm(155))</v>
+      </c>
+      <c r="R92" t="s">
         <v>560</v>
       </c>
-      <c r="R92" t="str">
+      <c r="S92" t="str">
         <f t="shared" si="29"/>
         <v>print(f'Advertencia: No se encontró la imagen {r_val["dir_emer"]}')</v>
       </c>
-      <c r="S92" t="str">
+      <c r="T92" t="str">
         <f t="shared" si="30"/>
         <v>dir_emer = ''</v>
       </c>
-      <c r="T92" t="s">
+      <c r="U92" t="s">
         <v>559</v>
       </c>
-      <c r="U92" t="str">
+      <c r="V92" t="str">
         <f t="shared" si="31"/>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["dir_emer"]}: {e}')</v>
       </c>
-      <c r="V92" t="str">
+      <c r="W92" t="str">
         <f t="shared" si="32"/>
         <v>dir_emer = ''</v>
       </c>
     </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.3">
-      <c r="I93" t="s">
+    <row r="93" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="J93" t="s">
         <v>23</v>
       </c>
-      <c r="J93" t="s">
+      <c r="K93" t="s">
         <v>302</v>
       </c>
-      <c r="K93" t="str">
+      <c r="L93" t="str">
         <f t="shared" si="25"/>
         <v>'tambo_arena' : r_val['tambo_arena'],</v>
       </c>
     </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.3">
-      <c r="I94" t="s">
+    <row r="94" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="J94" t="s">
         <v>564</v>
       </c>
-      <c r="J94" t="s">
+      <c r="K94" t="s">
         <v>563</v>
       </c>
-      <c r="K94" t="str">
+      <c r="L94" t="str">
         <f t="shared" si="25"/>
         <v>'ubicacion_tambo' : r_val['ubicacion_tambo'],</v>
       </c>
     </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.3">
-      <c r="I95" t="s">
+    <row r="95" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="J95" t="s">
         <v>191</v>
       </c>
-      <c r="J95" t="s">
+      <c r="K95" t="s">
         <v>303</v>
       </c>
-      <c r="K95" t="str">
+      <c r="L95" t="str">
         <f t="shared" si="25"/>
         <v>'tanques' : r_val['tanques'],</v>
       </c>
     </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.3">
-      <c r="I96" t="s">
+    <row r="96" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="J96" t="s">
         <v>192</v>
       </c>
-      <c r="J96" t="s">
+      <c r="K96" t="s">
         <v>304</v>
       </c>
-      <c r="K96" t="str">
+      <c r="L96" t="str">
         <f t="shared" si="25"/>
         <v>'tanque_1' : r_val['tanque_1'],</v>
       </c>
     </row>
-    <row r="97" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I97" t="s">
+    <row r="97" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J97" t="s">
         <v>193</v>
       </c>
-      <c r="J97" t="s">
+      <c r="K97" t="s">
         <v>305</v>
       </c>
-      <c r="K97" t="str">
+      <c r="L97" t="str">
         <f t="shared" si="25"/>
         <v>'tanque_2' : r_val['tanque_2'],</v>
       </c>
     </row>
-    <row r="98" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I98" t="s">
+    <row r="98" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J98" t="s">
         <v>194</v>
       </c>
-      <c r="J98" t="s">
+      <c r="K98" t="s">
         <v>306</v>
       </c>
-      <c r="K98" t="str">
+      <c r="L98" t="str">
         <f t="shared" si="25"/>
         <v>'tanque_3' : r_val['tanque_3'],</v>
       </c>
     </row>
-    <row r="99" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I99" t="s">
-        <v>0</v>
-      </c>
+    <row r="99" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J99" t="s">
+        <v>0</v>
+      </c>
+      <c r="K99" t="s">
         <v>307</v>
       </c>
-      <c r="K99" t="str">
+      <c r="L99" t="str">
         <f t="shared" si="25"/>
         <v>'dia' : r_val['dia'],</v>
       </c>
     </row>
-    <row r="100" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I100" t="s">
-        <v>1</v>
-      </c>
+    <row r="100" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J100" t="s">
+        <v>1</v>
+      </c>
+      <c r="K100" t="s">
         <v>308</v>
       </c>
-      <c r="K100" t="str">
+      <c r="L100" t="str">
         <f t="shared" si="25"/>
         <v>'mes' : r_val['mes'],</v>
       </c>
     </row>
-    <row r="101" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I101" t="s">
+    <row r="101" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J101" t="s">
         <v>2</v>
       </c>
-      <c r="J101" t="s">
+      <c r="K101" t="s">
         <v>309</v>
       </c>
-      <c r="K101" t="str">
+      <c r="L101" t="str">
         <f t="shared" si="25"/>
         <v>'anio' : r_val['anio'],</v>
       </c>
     </row>
-    <row r="102" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I102" t="s">
+    <row r="102" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J102" t="s">
         <v>195</v>
       </c>
-      <c r="J102" t="s">
+      <c r="K102" t="s">
         <v>310</v>
       </c>
-      <c r="K102" t="str">
+      <c r="L102" t="str">
         <f t="shared" si="25"/>
         <v>'coordenadas' : r_val['coordenadas'],</v>
       </c>
     </row>
-    <row r="103" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I103" t="s">
+    <row r="103" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J103" t="s">
         <v>196</v>
       </c>
-      <c r="J103" t="s">
+      <c r="K103" t="s">
         <v>311</v>
       </c>
-      <c r="K103" t="str">
+      <c r="L103" t="str">
         <f t="shared" si="25"/>
         <v>'norte' : r_val['norte'],</v>
       </c>
     </row>
-    <row r="104" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I104" t="s">
+    <row r="104" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J104" t="s">
         <v>197</v>
       </c>
-      <c r="J104" t="s">
+      <c r="K104" t="s">
         <v>312</v>
       </c>
-      <c r="K104" t="str">
+      <c r="L104" t="str">
         <f t="shared" si="25"/>
         <v>'sur' : r_val['sur'],</v>
       </c>
     </row>
-    <row r="105" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I105" t="s">
+    <row r="105" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J105" t="s">
         <v>198</v>
       </c>
-      <c r="J105" t="s">
+      <c r="K105" t="s">
         <v>313</v>
       </c>
-      <c r="K105" t="str">
+      <c r="L105" t="str">
         <f t="shared" si="25"/>
         <v>'este' : r_val['este'],</v>
       </c>
     </row>
-    <row r="106" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I106" t="s">
+    <row r="106" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J106" t="s">
         <v>199</v>
       </c>
-      <c r="J106" t="s">
+      <c r="K106" t="s">
         <v>314</v>
       </c>
-      <c r="K106" t="str">
+      <c r="L106" t="str">
         <f t="shared" si="25"/>
         <v>'oeste' : r_val['oeste'],</v>
       </c>
     </row>
-    <row r="107" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I107" t="s">
+    <row r="107" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J107" t="s">
         <v>597</v>
       </c>
-      <c r="J107" t="s">
+      <c r="K107" t="s">
         <v>598</v>
       </c>
-      <c r="K107" t="str">
+      <c r="L107" t="str">
         <f t="shared" si="25"/>
         <v>'ref_llegar' : r_val['ref_llegar'],</v>
       </c>
     </row>
-    <row r="108" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I108" t="s">
+    <row r="108" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J108" t="s">
         <v>200</v>
       </c>
-      <c r="J108" t="s">
+      <c r="K108" t="s">
         <v>315</v>
       </c>
-      <c r="K108" t="str">
+      <c r="L108" t="str">
         <f t="shared" si="25"/>
         <v>'ley' : r_val['ley'],</v>
       </c>
     </row>
-    <row r="109" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I109" t="s">
+    <row r="109" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J109" t="s">
         <v>201</v>
       </c>
-      <c r="J109" t="s">
+      <c r="K109" t="s">
         <v>316</v>
       </c>
-      <c r="K109" t="str">
+      <c r="L109" t="str">
         <f t="shared" si="25"/>
         <v>'reglamento' : r_val['reglamento'],</v>
       </c>
     </row>
-    <row r="110" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I110" t="s">
+    <row r="110" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J110" t="s">
         <v>647</v>
       </c>
-      <c r="J110" t="s">
+      <c r="K110" t="s">
         <v>687</v>
       </c>
-      <c r="K110" t="str">
+      <c r="L110" t="str">
         <f t="shared" si="25"/>
         <v>'m_dir' : r_val['m_dir'],</v>
       </c>
     </row>
-    <row r="111" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I111" t="s">
+    <row r="111" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J111" t="s">
         <v>202</v>
       </c>
-      <c r="J111" t="s">
+      <c r="K111" t="s">
         <v>317</v>
       </c>
-      <c r="K111" t="str">
-        <f t="shared" ref="K111:K142" si="33">+_xlfn.CONCAT("'",I111,"' : r_val['",I111,"'],")</f>
+      <c r="L111" t="str">
+        <f t="shared" ref="L111:L142" si="33">+_xlfn.CONCAT("'",J111,"' : r_val['",J111,"'],")</f>
         <v>'coord_suplente' : r_val['coord_suplente'],</v>
       </c>
     </row>
-    <row r="112" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I112" t="s">
+    <row r="112" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J112" t="s">
         <v>648</v>
       </c>
-      <c r="J112" t="s">
+      <c r="K112" t="s">
         <v>688</v>
       </c>
-      <c r="K112" t="str">
+      <c r="L112" t="str">
         <f t="shared" si="33"/>
         <v>'m_jef_caj' : r_val['m_jef_caj'],</v>
       </c>
     </row>
-    <row r="113" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I113" t="s">
+    <row r="113" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J113" t="s">
         <v>203</v>
       </c>
-      <c r="J113" t="s">
+      <c r="K113" t="s">
         <v>318</v>
       </c>
-      <c r="K113" t="str">
+      <c r="L113" t="str">
         <f t="shared" si="33"/>
         <v>'evacuacion' : r_val['evacuacion'],</v>
       </c>
     </row>
-    <row r="114" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I114" t="s">
+    <row r="114" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J114" t="s">
         <v>581</v>
       </c>
-      <c r="J114" t="s">
+      <c r="K114" t="s">
         <v>589</v>
       </c>
-      <c r="K114" t="str">
+      <c r="L114" t="str">
         <f t="shared" si="33"/>
         <v>'evac_puesto' : r_val['evac_puesto'],</v>
       </c>
     </row>
-    <row r="115" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I115" t="s">
+    <row r="115" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J115" t="s">
         <v>649</v>
       </c>
-      <c r="J115" t="s">
+      <c r="K115" t="s">
         <v>689</v>
       </c>
-      <c r="K115" t="str">
+      <c r="L115" t="str">
         <f t="shared" si="33"/>
         <v>'m_evac' : r_val['m_evac'],</v>
       </c>
     </row>
-    <row r="116" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I116" t="s">
+    <row r="116" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J116" t="s">
         <v>204</v>
       </c>
-      <c r="J116" t="s">
+      <c r="K116" t="s">
         <v>319</v>
       </c>
-      <c r="K116" t="str">
+      <c r="L116" t="str">
         <f t="shared" si="33"/>
         <v>'evac_suplente' : r_val['evac_suplente'],</v>
       </c>
     </row>
-    <row r="117" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I117" t="s">
+    <row r="117" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J117" t="s">
         <v>582</v>
       </c>
-      <c r="J117" t="s">
+      <c r="K117" t="s">
         <v>590</v>
       </c>
-      <c r="K117" t="str">
+      <c r="L117" t="str">
         <f t="shared" si="33"/>
         <v>'supl_evac_pue' : r_val['supl_evac_pue'],</v>
       </c>
     </row>
-    <row r="118" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I118" t="s">
+    <row r="118" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J118" t="s">
         <v>650</v>
       </c>
-      <c r="J118" t="s">
+      <c r="K118" t="s">
         <v>690</v>
       </c>
-      <c r="K118" t="str">
+      <c r="L118" t="str">
         <f t="shared" si="33"/>
         <v>'m_supl_evac' : r_val['m_supl_evac'],</v>
       </c>
     </row>
-    <row r="119" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I119" t="s">
+    <row r="119" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J119" t="s">
         <v>205</v>
       </c>
-      <c r="J119" t="s">
+      <c r="K119" t="s">
         <v>320</v>
       </c>
-      <c r="K119" t="str">
+      <c r="L119" t="str">
         <f t="shared" si="33"/>
         <v>'incendios' : r_val['incendios'],</v>
       </c>
     </row>
-    <row r="120" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I120" t="s">
+    <row r="120" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J120" t="s">
         <v>583</v>
       </c>
-      <c r="J120" t="s">
+      <c r="K120" t="s">
         <v>591</v>
       </c>
-      <c r="K120" t="str">
+      <c r="L120" t="str">
         <f t="shared" si="33"/>
         <v>'incen_puesto' : r_val['incen_puesto'],</v>
       </c>
     </row>
-    <row r="121" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I121" t="s">
+    <row r="121" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J121" t="s">
         <v>651</v>
       </c>
-      <c r="J121" t="s">
+      <c r="K121" t="s">
         <v>691</v>
       </c>
-      <c r="K121" t="str">
+      <c r="L121" t="str">
         <f t="shared" si="33"/>
         <v>'m_inc' : r_val['m_inc'],</v>
       </c>
     </row>
-    <row r="122" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I122" t="s">
+    <row r="122" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J122" t="s">
         <v>206</v>
       </c>
-      <c r="J122" t="s">
+      <c r="K122" t="s">
         <v>321</v>
       </c>
-      <c r="K122" t="str">
+      <c r="L122" t="str">
         <f t="shared" si="33"/>
         <v>'inc_suplente' : r_val['inc_suplente'],</v>
       </c>
     </row>
-    <row r="123" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I123" t="s">
+    <row r="123" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J123" t="s">
         <v>584</v>
       </c>
-      <c r="J123" t="s">
+      <c r="K123" t="s">
         <v>592</v>
       </c>
-      <c r="K123" t="str">
+      <c r="L123" t="str">
         <f t="shared" si="33"/>
         <v>'supl_inc_puesto' : r_val['supl_inc_puesto'],</v>
       </c>
     </row>
-    <row r="124" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I124" t="s">
+    <row r="124" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J124" t="s">
         <v>652</v>
       </c>
-      <c r="J124" t="s">
+      <c r="K124" t="s">
         <v>692</v>
       </c>
-      <c r="K124" t="str">
+      <c r="L124" t="str">
         <f t="shared" si="33"/>
         <v>'m_supl_inc' : r_val['m_supl_inc'],</v>
       </c>
     </row>
-    <row r="125" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I125" t="s">
+    <row r="125" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J125" t="s">
         <v>207</v>
       </c>
-      <c r="J125" t="s">
+      <c r="K125" t="s">
         <v>322</v>
       </c>
-      <c r="K125" t="str">
+      <c r="L125" t="str">
         <f t="shared" si="33"/>
         <v>'primeros_auxilios' : r_val['primeros_auxilios'],</v>
       </c>
     </row>
-    <row r="126" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I126" t="s">
+    <row r="126" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J126" t="s">
         <v>585</v>
       </c>
-      <c r="J126" t="s">
+      <c r="K126" t="s">
         <v>593</v>
       </c>
-      <c r="K126" t="str">
+      <c r="L126" t="str">
         <f t="shared" si="33"/>
         <v>'prim_aux_puesto' : r_val['prim_aux_puesto'],</v>
       </c>
     </row>
-    <row r="127" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I127" t="s">
+    <row r="127" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J127" t="s">
         <v>653</v>
       </c>
-      <c r="J127" t="s">
+      <c r="K127" t="s">
         <v>693</v>
       </c>
-      <c r="K127" t="str">
+      <c r="L127" t="str">
         <f t="shared" si="33"/>
         <v>'m_prim_aux' : r_val['m_prim_aux'],</v>
       </c>
     </row>
-    <row r="128" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I128" t="s">
+    <row r="128" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J128" t="s">
         <v>208</v>
       </c>
-      <c r="J128" t="s">
+      <c r="K128" t="s">
         <v>323</v>
       </c>
-      <c r="K128" t="str">
+      <c r="L128" t="str">
         <f t="shared" si="33"/>
         <v>'aux_suplente' : r_val['aux_suplente'],</v>
       </c>
     </row>
-    <row r="129" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I129" t="s">
+    <row r="129" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J129" t="s">
         <v>586</v>
       </c>
-      <c r="J129" t="s">
+      <c r="K129" t="s">
         <v>594</v>
       </c>
-      <c r="K129" t="str">
+      <c r="L129" t="str">
         <f t="shared" si="33"/>
         <v>'supl_prim_aux_puesto' : r_val['supl_prim_aux_puesto'],</v>
       </c>
     </row>
-    <row r="130" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I130" t="s">
+    <row r="130" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J130" t="s">
         <v>654</v>
       </c>
-      <c r="J130" t="s">
+      <c r="K130" t="s">
         <v>694</v>
       </c>
-      <c r="K130" t="str">
+      <c r="L130" t="str">
         <f t="shared" si="33"/>
         <v>'m_supl_paux' : r_val['m_supl_paux'],</v>
       </c>
     </row>
-    <row r="131" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I131" t="s">
+    <row r="131" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J131" t="s">
         <v>209</v>
       </c>
-      <c r="J131" t="s">
+      <c r="K131" t="s">
         <v>324</v>
       </c>
-      <c r="K131" t="str">
+      <c r="L131" t="str">
         <f t="shared" si="33"/>
         <v>'busqueda' : r_val['busqueda'],</v>
       </c>
     </row>
-    <row r="132" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I132" t="s">
+    <row r="132" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J132" t="s">
         <v>587</v>
       </c>
-      <c r="J132" t="s">
+      <c r="K132" t="s">
         <v>595</v>
       </c>
-      <c r="K132" t="str">
+      <c r="L132" t="str">
         <f t="shared" si="33"/>
         <v>'busq_puesto' : r_val['busq_puesto'],</v>
       </c>
     </row>
-    <row r="133" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I133" t="s">
+    <row r="133" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J133" t="s">
         <v>655</v>
       </c>
-      <c r="J133" t="s">
+      <c r="K133" t="s">
         <v>695</v>
       </c>
-      <c r="K133" t="str">
+      <c r="L133" t="str">
         <f t="shared" si="33"/>
         <v>'m_busq' : r_val['m_busq'],</v>
       </c>
     </row>
-    <row r="134" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I134" t="s">
+    <row r="134" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J134" t="s">
         <v>210</v>
       </c>
-      <c r="J134" t="s">
+      <c r="K134" t="s">
         <v>325</v>
       </c>
-      <c r="K134" t="str">
+      <c r="L134" t="str">
         <f t="shared" si="33"/>
         <v>'busq_suplente' : r_val['busq_suplente'],</v>
       </c>
     </row>
-    <row r="135" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I135" t="s">
+    <row r="135" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J135" t="s">
         <v>588</v>
       </c>
-      <c r="J135" t="s">
+      <c r="K135" t="s">
         <v>596</v>
       </c>
-      <c r="K135" t="str">
+      <c r="L135" t="str">
         <f t="shared" si="33"/>
         <v>'supl_busq_puesto' : r_val['supl_busq_puesto'],</v>
       </c>
     </row>
-    <row r="136" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I136" t="s">
+    <row r="136" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J136" t="s">
         <v>656</v>
       </c>
-      <c r="J136" t="s">
+      <c r="K136" t="s">
         <v>696</v>
       </c>
-      <c r="K136" t="str">
+      <c r="L136" t="str">
         <f t="shared" si="33"/>
         <v>'m_supl_busq' : r_val['m_supl_busq'],</v>
       </c>
     </row>
-    <row r="137" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I137" t="s">
+    <row r="137" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J137" t="s">
         <v>211</v>
       </c>
-      <c r="J137" t="s">
+      <c r="K137" t="s">
         <v>326</v>
       </c>
-      <c r="K137" t="str">
+      <c r="L137" t="str">
         <f t="shared" si="33"/>
         <v>'descrip_gi' : r_val['descrip_gi'],</v>
       </c>
     </row>
-    <row r="138" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I138" t="s">
+    <row r="138" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J138" t="s">
         <v>212</v>
       </c>
-      <c r="J138" t="s">
+      <c r="K138" t="s">
         <v>327</v>
       </c>
-      <c r="K138" t="str">
+      <c r="L138" t="str">
         <f t="shared" si="33"/>
         <v>'gas_inflamable' : r_val['gas_inflamable'],</v>
       </c>
     </row>
-    <row r="139" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I139" t="s">
+    <row r="139" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J139" t="s">
         <v>213</v>
       </c>
-      <c r="J139" t="s">
+      <c r="K139" t="s">
         <v>328</v>
       </c>
-      <c r="K139" t="str">
+      <c r="L139" t="str">
         <f t="shared" si="33"/>
         <v>'valor_gi' : r_val['valor_gi'],</v>
       </c>
     </row>
-    <row r="140" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I140" t="s">
+    <row r="140" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J140" t="s">
         <v>214</v>
       </c>
-      <c r="J140" t="s">
+      <c r="K140" t="s">
         <v>329</v>
       </c>
-      <c r="K140" t="str">
+      <c r="L140" t="str">
         <f t="shared" si="33"/>
         <v>'descrp_li' : r_val['descrp_li'],</v>
       </c>
     </row>
-    <row r="141" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I141" t="s">
+    <row r="141" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J141" t="s">
         <v>215</v>
       </c>
-      <c r="J141" t="s">
+      <c r="K141" t="s">
         <v>330</v>
       </c>
-      <c r="K141" t="str">
+      <c r="L141" t="str">
         <f t="shared" si="33"/>
         <v>'liquido_inflamable' : r_val['liquido_inflamable'],</v>
       </c>
     </row>
-    <row r="142" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I142" t="s">
+    <row r="142" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J142" t="s">
         <v>216</v>
       </c>
-      <c r="J142" t="s">
+      <c r="K142" t="s">
         <v>331</v>
       </c>
-      <c r="K142" t="str">
+      <c r="L142" t="str">
         <f t="shared" si="33"/>
         <v>'valor_li' : r_val['valor_li'],</v>
       </c>
     </row>
-    <row r="143" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I143" t="s">
+    <row r="143" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J143" t="s">
         <v>217</v>
       </c>
-      <c r="J143" t="s">
+      <c r="K143" t="s">
         <v>332</v>
       </c>
-      <c r="K143" t="str">
-        <f t="shared" ref="K143:K181" si="34">+_xlfn.CONCAT("'",I143,"' : r_val['",I143,"'],")</f>
+      <c r="L143" t="str">
+        <f t="shared" ref="L143:L181" si="34">+_xlfn.CONCAT("'",J143,"' : r_val['",J143,"'],")</f>
         <v>'descrip_lc' : r_val['descrip_lc'],</v>
       </c>
     </row>
-    <row r="144" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I144" t="s">
+    <row r="144" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J144" t="s">
         <v>218</v>
       </c>
-      <c r="J144" t="s">
+      <c r="K144" t="s">
         <v>333</v>
       </c>
-      <c r="K144" t="str">
+      <c r="L144" t="str">
         <f t="shared" si="34"/>
         <v>'liquido_combustible' : r_val['liquido_combustible'],</v>
       </c>
     </row>
-    <row r="145" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I145" t="s">
+    <row r="145" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J145" t="s">
         <v>219</v>
       </c>
-      <c r="J145" t="s">
+      <c r="K145" t="s">
         <v>334</v>
       </c>
-      <c r="K145" t="str">
+      <c r="L145" t="str">
         <f t="shared" si="34"/>
         <v>'valor_lc' : r_val['valor_lc'],</v>
       </c>
     </row>
-    <row r="146" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I146" t="s">
+    <row r="146" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J146" t="s">
         <v>220</v>
       </c>
-      <c r="J146" t="s">
+      <c r="K146" t="s">
         <v>335</v>
       </c>
-      <c r="K146" t="str">
+      <c r="L146" t="str">
         <f t="shared" si="34"/>
         <v>'descrip_sc' : r_val['descrip_sc'],</v>
       </c>
     </row>
-    <row r="147" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I147" t="s">
+    <row r="147" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J147" t="s">
         <v>221</v>
       </c>
-      <c r="J147" t="s">
+      <c r="K147" t="s">
         <v>336</v>
       </c>
-      <c r="K147" t="str">
+      <c r="L147" t="str">
         <f t="shared" si="34"/>
         <v>'solido_combusible' : r_val['solido_combusible'],</v>
       </c>
     </row>
-    <row r="148" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I148" t="s">
+    <row r="148" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J148" t="s">
         <v>222</v>
       </c>
-      <c r="J148" t="s">
+      <c r="K148" t="s">
         <v>337</v>
       </c>
-      <c r="K148" t="str">
+      <c r="L148" t="str">
         <f t="shared" si="34"/>
         <v>'valor_sc' : r_val['valor_sc'],</v>
       </c>
     </row>
-    <row r="149" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I149" t="s">
+    <row r="149" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J149" t="s">
         <v>223</v>
       </c>
-      <c r="J149" t="s">
+      <c r="K149" t="s">
         <v>338</v>
       </c>
-      <c r="K149" t="str">
+      <c r="L149" t="str">
         <f t="shared" si="34"/>
         <v>'tipo_riesgo' : r_val['tipo_riesgo'],</v>
       </c>
     </row>
-    <row r="150" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I150" t="s">
+    <row r="150" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J150" t="s">
         <v>617</v>
       </c>
-      <c r="J150" t="s">
+      <c r="K150" t="s">
         <v>657</v>
       </c>
-      <c r="K150" t="str">
+      <c r="L150" t="str">
         <f t="shared" si="34"/>
         <v>'nombre1' : r_val['nombre1'],</v>
       </c>
     </row>
-    <row r="151" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I151" t="s">
+    <row r="151" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J151" t="s">
         <v>619</v>
       </c>
-      <c r="J151" t="s">
+      <c r="K151" t="s">
         <v>658</v>
       </c>
-      <c r="K151" t="str">
+      <c r="L151" t="str">
         <f t="shared" si="34"/>
         <v>'puesto1' : r_val['puesto1'],</v>
       </c>
     </row>
-    <row r="152" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I152" t="s">
+    <row r="152" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J152" t="s">
         <v>637</v>
       </c>
-      <c r="J152" t="s">
+      <c r="K152" t="s">
         <v>659</v>
       </c>
-      <c r="K152" t="str">
+      <c r="L152" t="str">
         <f t="shared" si="34"/>
         <v>'m1' : r_val['m1'],</v>
       </c>
     </row>
-    <row r="153" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I153" t="s">
+    <row r="153" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J153" t="s">
         <v>618</v>
       </c>
-      <c r="J153" t="s">
+      <c r="K153" t="s">
         <v>660</v>
       </c>
-      <c r="K153" t="str">
+      <c r="L153" t="str">
         <f t="shared" si="34"/>
         <v>'nombre2' : r_val['nombre2'],</v>
       </c>
     </row>
-    <row r="154" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I154" t="s">
+    <row r="154" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J154" t="s">
         <v>620</v>
       </c>
-      <c r="J154" t="s">
+      <c r="K154" t="s">
         <v>661</v>
       </c>
-      <c r="K154" t="str">
+      <c r="L154" t="str">
         <f t="shared" si="34"/>
         <v>'puesto2' : r_val['puesto2'],</v>
       </c>
     </row>
-    <row r="155" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I155" t="s">
+    <row r="155" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J155" t="s">
         <v>638</v>
       </c>
-      <c r="J155" t="s">
+      <c r="K155" t="s">
         <v>662</v>
       </c>
-      <c r="K155" t="str">
+      <c r="L155" t="str">
         <f t="shared" si="34"/>
         <v>'m2' : r_val['m2'],</v>
       </c>
     </row>
-    <row r="156" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I156" t="s">
+    <row r="156" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J156" t="s">
         <v>621</v>
       </c>
-      <c r="J156" t="s">
+      <c r="K156" t="s">
         <v>663</v>
       </c>
-      <c r="K156" t="str">
+      <c r="L156" t="str">
         <f t="shared" si="34"/>
         <v>'nombre3' : r_val['nombre3'],</v>
       </c>
     </row>
-    <row r="157" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I157" t="s">
+    <row r="157" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J157" t="s">
         <v>622</v>
       </c>
-      <c r="J157" t="s">
+      <c r="K157" t="s">
         <v>664</v>
       </c>
-      <c r="K157" t="str">
+      <c r="L157" t="str">
         <f t="shared" si="34"/>
         <v>'puesto3' : r_val['puesto3'],</v>
       </c>
     </row>
-    <row r="158" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I158" t="s">
+    <row r="158" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J158" t="s">
         <v>639</v>
       </c>
-      <c r="J158" t="s">
+      <c r="K158" t="s">
         <v>665</v>
       </c>
-      <c r="K158" t="str">
+      <c r="L158" t="str">
         <f t="shared" si="34"/>
         <v>'m3' : r_val['m3'],</v>
       </c>
     </row>
-    <row r="159" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I159" t="s">
+    <row r="159" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J159" t="s">
         <v>623</v>
       </c>
-      <c r="J159" t="s">
+      <c r="K159" t="s">
         <v>666</v>
       </c>
-      <c r="K159" t="str">
+      <c r="L159" t="str">
         <f t="shared" si="34"/>
         <v>'nombre4' : r_val['nombre4'],</v>
       </c>
     </row>
-    <row r="160" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I160" t="s">
+    <row r="160" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J160" t="s">
         <v>624</v>
       </c>
-      <c r="J160" t="s">
+      <c r="K160" t="s">
         <v>667</v>
       </c>
-      <c r="K160" t="str">
+      <c r="L160" t="str">
         <f t="shared" si="34"/>
         <v>'puesto4' : r_val['puesto4'],</v>
       </c>
     </row>
-    <row r="161" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I161" t="s">
+    <row r="161" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J161" t="s">
         <v>640</v>
       </c>
-      <c r="J161" t="s">
+      <c r="K161" t="s">
         <v>668</v>
       </c>
-      <c r="K161" t="str">
+      <c r="L161" t="str">
         <f t="shared" si="34"/>
         <v>'m4' : r_val['m4'],</v>
       </c>
     </row>
-    <row r="162" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I162" t="s">
+    <row r="162" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J162" t="s">
         <v>625</v>
       </c>
-      <c r="J162" t="s">
+      <c r="K162" t="s">
         <v>669</v>
       </c>
-      <c r="K162" t="str">
+      <c r="L162" t="str">
         <f t="shared" si="34"/>
         <v>'nombre5' : r_val['nombre5'],</v>
       </c>
     </row>
-    <row r="163" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I163" t="s">
+    <row r="163" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J163" t="s">
         <v>626</v>
       </c>
-      <c r="J163" t="s">
+      <c r="K163" t="s">
         <v>670</v>
       </c>
-      <c r="K163" t="str">
+      <c r="L163" t="str">
         <f t="shared" si="34"/>
         <v>'puesto5' : r_val['puesto5'],</v>
       </c>
     </row>
-    <row r="164" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I164" t="s">
+    <row r="164" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J164" t="s">
         <v>641</v>
       </c>
-      <c r="J164" t="s">
+      <c r="K164" t="s">
         <v>671</v>
       </c>
-      <c r="K164" t="str">
+      <c r="L164" t="str">
         <f t="shared" si="34"/>
         <v>'m5' : r_val['m5'],</v>
       </c>
     </row>
-    <row r="165" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I165" t="s">
+    <row r="165" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J165" t="s">
         <v>627</v>
       </c>
-      <c r="J165" t="s">
+      <c r="K165" t="s">
         <v>672</v>
       </c>
-      <c r="K165" t="str">
+      <c r="L165" t="str">
         <f t="shared" si="34"/>
         <v>'nombre6' : r_val['nombre6'],</v>
       </c>
     </row>
-    <row r="166" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I166" t="s">
+    <row r="166" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J166" t="s">
         <v>628</v>
       </c>
-      <c r="J166" t="s">
+      <c r="K166" t="s">
         <v>673</v>
       </c>
-      <c r="K166" t="str">
+      <c r="L166" t="str">
         <f t="shared" si="34"/>
         <v>'puesto6' : r_val['puesto6'],</v>
       </c>
     </row>
-    <row r="167" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I167" t="s">
+    <row r="167" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J167" t="s">
         <v>642</v>
       </c>
-      <c r="J167" t="s">
+      <c r="K167" t="s">
         <v>674</v>
       </c>
-      <c r="K167" t="str">
+      <c r="L167" t="str">
         <f t="shared" si="34"/>
         <v>'m6' : r_val['m6'],</v>
       </c>
     </row>
-    <row r="168" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I168" t="s">
+    <row r="168" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J168" t="s">
         <v>629</v>
       </c>
-      <c r="J168" t="s">
+      <c r="K168" t="s">
         <v>675</v>
       </c>
-      <c r="K168" t="str">
+      <c r="L168" t="str">
         <f t="shared" si="34"/>
         <v>'nombre7' : r_val['nombre7'],</v>
       </c>
     </row>
-    <row r="169" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I169" t="s">
+    <row r="169" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J169" t="s">
         <v>630</v>
       </c>
-      <c r="J169" t="s">
+      <c r="K169" t="s">
         <v>676</v>
       </c>
-      <c r="K169" t="str">
+      <c r="L169" t="str">
         <f t="shared" si="34"/>
         <v>'puesto7' : r_val['puesto7'],</v>
       </c>
     </row>
-    <row r="170" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I170" t="s">
+    <row r="170" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J170" t="s">
         <v>643</v>
       </c>
-      <c r="J170" t="s">
+      <c r="K170" t="s">
         <v>677</v>
       </c>
-      <c r="K170" t="str">
+      <c r="L170" t="str">
         <f t="shared" si="34"/>
         <v>'m7' : r_val['m7'],</v>
       </c>
     </row>
-    <row r="171" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I171" t="s">
+    <row r="171" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J171" t="s">
         <v>631</v>
       </c>
-      <c r="J171" t="s">
+      <c r="K171" t="s">
         <v>678</v>
       </c>
-      <c r="K171" t="str">
+      <c r="L171" t="str">
         <f t="shared" si="34"/>
         <v>'nombre8' : r_val['nombre8'],</v>
       </c>
     </row>
-    <row r="172" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I172" t="s">
+    <row r="172" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J172" t="s">
         <v>632</v>
       </c>
-      <c r="J172" t="s">
+      <c r="K172" t="s">
         <v>679</v>
       </c>
-      <c r="K172" t="str">
+      <c r="L172" t="str">
         <f t="shared" si="34"/>
         <v>'puesto8' : r_val['puesto8'],</v>
       </c>
     </row>
-    <row r="173" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I173" t="s">
+    <row r="173" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J173" t="s">
         <v>644</v>
       </c>
-      <c r="J173" t="s">
+      <c r="K173" t="s">
         <v>680</v>
       </c>
-      <c r="K173" t="str">
+      <c r="L173" t="str">
         <f t="shared" si="34"/>
         <v>'m8' : r_val['m8'],</v>
       </c>
     </row>
-    <row r="174" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I174" t="s">
+    <row r="174" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J174" t="s">
         <v>633</v>
       </c>
-      <c r="J174" t="s">
+      <c r="K174" t="s">
         <v>681</v>
       </c>
-      <c r="K174" t="str">
+      <c r="L174" t="str">
         <f t="shared" si="34"/>
         <v>'nombre9' : r_val['nombre9'],</v>
       </c>
     </row>
-    <row r="175" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I175" t="s">
+    <row r="175" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J175" t="s">
         <v>634</v>
       </c>
-      <c r="J175" t="s">
+      <c r="K175" t="s">
         <v>682</v>
       </c>
-      <c r="K175" t="str">
+      <c r="L175" t="str">
         <f t="shared" si="34"/>
         <v>'puesto9' : r_val['puesto9'],</v>
       </c>
     </row>
-    <row r="176" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I176" t="s">
+    <row r="176" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J176" t="s">
         <v>645</v>
       </c>
-      <c r="J176" t="s">
+      <c r="K176" t="s">
         <v>683</v>
       </c>
-      <c r="K176" t="str">
+      <c r="L176" t="str">
         <f t="shared" si="34"/>
         <v>'m9' : r_val['m9'],</v>
       </c>
     </row>
-    <row r="177" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I177" t="s">
+    <row r="177" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J177" t="s">
         <v>635</v>
       </c>
-      <c r="J177" t="s">
+      <c r="K177" t="s">
         <v>684</v>
       </c>
-      <c r="K177" t="str">
+      <c r="L177" t="str">
         <f t="shared" si="34"/>
         <v>'nombre10' : r_val['nombre10'],</v>
       </c>
     </row>
-    <row r="178" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I178" t="s">
+    <row r="178" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J178" t="s">
         <v>636</v>
       </c>
-      <c r="J178" t="s">
+      <c r="K178" t="s">
         <v>685</v>
       </c>
-      <c r="K178" t="str">
+      <c r="L178" t="str">
         <f t="shared" si="34"/>
         <v>'puesto10' : r_val['puesto10'],</v>
       </c>
     </row>
-    <row r="179" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I179" t="s">
+    <row r="179" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J179" t="s">
         <v>646</v>
       </c>
-      <c r="J179" t="s">
+      <c r="K179" t="s">
         <v>686</v>
       </c>
-      <c r="K179" t="str">
+      <c r="L179" t="str">
         <f t="shared" si="34"/>
         <v>'m10' : r_val['m10'],</v>
       </c>
     </row>
-    <row r="180" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I180" t="s">
+    <row r="180" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J180" t="s">
         <v>1730</v>
       </c>
-      <c r="J180" t="str">
-        <f>+_xlfn.CONCAT("{{ ",I180," }}")</f>
+      <c r="K180" t="str">
+        <f>+_xlfn.CONCAT("{{ ",J180," }}")</f>
         <v>{{ registro_perito }}</v>
       </c>
-      <c r="K180" t="str">
+      <c r="L180" t="str">
         <f t="shared" si="34"/>
         <v>'registro_perito' : r_val['registro_perito'],</v>
       </c>
     </row>
-    <row r="181" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I181" t="s">
+    <row r="181" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J181" t="s">
         <v>1731</v>
       </c>
-      <c r="J181" t="str">
-        <f>+_xlfn.CONCAT("{{ ",I181," }}")</f>
+      <c r="K181" t="str">
+        <f>+_xlfn.CONCAT("{{ ",J181," }}")</f>
         <v>{{ no_registro }}</v>
       </c>
-      <c r="K181" t="str">
+      <c r="L181" t="str">
         <f t="shared" si="34"/>
         <v>'no_registro' : r_val['no_registro'],</v>
       </c>
     </row>
-    <row r="182" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I182" t="s">
+    <row r="182" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J182" t="s">
         <v>1735</v>
       </c>
-      <c r="J182" t="str">
-        <f t="shared" ref="J182:J183" si="35">+_xlfn.CONCAT("{{ ",I182," }}")</f>
+      <c r="K182" t="str">
+        <f t="shared" ref="K182:K183" si="35">+_xlfn.CONCAT("{{ ",J182," }}")</f>
         <v>{{ dh_int }}</v>
       </c>
-      <c r="K182" t="str">
-        <f t="shared" ref="K182:K183" si="36">+_xlfn.CONCAT("'",I182,"' : r_val['",I182,"'],")</f>
+      <c r="L182" t="str">
+        <f t="shared" ref="L182:L183" si="36">+_xlfn.CONCAT("'",J182,"' : r_val['",J182,"'],")</f>
         <v>'dh_int' : r_val['dh_int'],</v>
       </c>
     </row>
-    <row r="183" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I183" t="s">
+    <row r="183" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J183" t="s">
         <v>1736</v>
       </c>
-      <c r="J183" t="str">
+      <c r="K183" t="str">
         <f t="shared" si="35"/>
         <v>{{ dh_ext }}</v>
       </c>
-      <c r="K183" t="str">
+      <c r="L183" t="str">
         <f t="shared" si="36"/>
         <v>'dh_ext' : r_val['dh_ext'],</v>
       </c>
     </row>
-    <row r="184" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I184" t="s">
+    <row r="184" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J184" t="s">
         <v>1737</v>
       </c>
-      <c r="J184" t="str">
-        <f t="shared" ref="J184" si="37">+_xlfn.CONCAT("{{ ",I184," }}")</f>
+      <c r="K184" t="str">
+        <f t="shared" ref="K184" si="37">+_xlfn.CONCAT("{{ ",J184," }}")</f>
         <v>{{ detectores_ext }}</v>
       </c>
-      <c r="K184" t="str">
-        <f t="shared" ref="K184" si="38">+_xlfn.CONCAT("'",I184,"' : r_val['",I184,"'],")</f>
+      <c r="L184" t="str">
+        <f t="shared" ref="L184" si="38">+_xlfn.CONCAT("'",J184,"' : r_val['",J184,"'],")</f>
         <v>'detectores_ext' : r_val['detectores_ext'],</v>
       </c>
     </row>
-    <row r="185" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I185" t="s">
+    <row r="185" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J185" t="s">
         <v>1738</v>
       </c>
-      <c r="J185" t="str">
-        <f t="shared" ref="J185" si="39">+_xlfn.CONCAT("{{ ",I185," }}")</f>
+      <c r="K185" t="str">
+        <f t="shared" ref="K185" si="39">+_xlfn.CONCAT("{{ ",J185," }}")</f>
         <v>{{ coord_sup_puesto }}</v>
       </c>
-      <c r="K185" t="str">
-        <f t="shared" ref="K185" si="40">+_xlfn.CONCAT("'",I185,"' : r_val['",I185,"'],")</f>
+      <c r="L185" t="str">
+        <f t="shared" ref="L185" si="40">+_xlfn.CONCAT("'",J185,"' : r_val['",J185,"'],")</f>
         <v>'coord_sup_puesto' : r_val['coord_sup_puesto'],</v>
       </c>
     </row>
-    <row r="186" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I186" t="s">
+    <row r="186" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J186" t="s">
         <v>1744</v>
       </c>
-      <c r="J186" t="str">
-        <f t="shared" ref="J186:J189" si="41">+_xlfn.CONCAT("{{ ",I186," }}")</f>
+      <c r="K186" t="str">
+        <f t="shared" ref="K186:K189" si="41">+_xlfn.CONCAT("{{ ",J186," }}")</f>
         <v>{{ riesgo1 }}</v>
       </c>
-      <c r="K186" t="str">
-        <f t="shared" ref="K186:K189" si="42">+_xlfn.CONCAT("'",I186,"' : r_val['",I186,"'],")</f>
+      <c r="L186" t="str">
+        <f t="shared" ref="L186:L189" si="42">+_xlfn.CONCAT("'",J186,"' : r_val['",J186,"'],")</f>
         <v>'riesgo1' : r_val['riesgo1'],</v>
       </c>
     </row>
-    <row r="187" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I187" t="s">
+    <row r="187" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J187" t="s">
         <v>1745</v>
       </c>
-      <c r="J187" t="str">
+      <c r="K187" t="str">
         <f t="shared" si="41"/>
         <v>{{ riesgo2 }}</v>
       </c>
-      <c r="K187" t="str">
+      <c r="L187" t="str">
         <f t="shared" si="42"/>
         <v>'riesgo2' : r_val['riesgo2'],</v>
       </c>
     </row>
-    <row r="188" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I188" t="s">
+    <row r="188" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J188" t="s">
         <v>1746</v>
       </c>
-      <c r="J188" t="str">
+      <c r="K188" t="str">
         <f t="shared" si="41"/>
         <v>{{ riesgo3 }}</v>
       </c>
-      <c r="K188" t="str">
+      <c r="L188" t="str">
         <f t="shared" si="42"/>
         <v>'riesgo3' : r_val['riesgo3'],</v>
       </c>
     </row>
-    <row r="189" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I189" t="s">
+    <row r="189" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J189" t="s">
         <v>1747</v>
       </c>
-      <c r="J189" t="str">
+      <c r="K189" t="str">
         <f t="shared" si="41"/>
         <v>{{ riesgo4 }}</v>
       </c>
-      <c r="K189" t="str">
+      <c r="L189" t="str">
         <f t="shared" si="42"/>
         <v>'riesgo4' : r_val['riesgo4'],</v>
       </c>
     </row>
-    <row r="190" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I190" t="s">
+    <row r="190" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J190" t="s">
         <v>1751</v>
       </c>
-      <c r="J190" t="str">
-        <f t="shared" ref="J190" si="43">+_xlfn.CONCAT("{{ ",I190," }}")</f>
+      <c r="K190" t="str">
+        <f t="shared" ref="K190" si="43">+_xlfn.CONCAT("{{ ",J190," }}")</f>
         <v>{{ valor_gri }}</v>
       </c>
-      <c r="K190" t="str">
-        <f t="shared" ref="K190" si="44">+_xlfn.CONCAT("'",I190,"' : r_val['",I190,"'],")</f>
+      <c r="L190" t="str">
+        <f t="shared" ref="L190" si="44">+_xlfn.CONCAT("'",J190,"' : r_val['",J190,"'],")</f>
         <v>'valor_gri' : r_val['valor_gri'],</v>
       </c>
     </row>
-    <row r="191" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I191" t="s">
+    <row r="191" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J191" t="s">
         <v>1752</v>
       </c>
-      <c r="J191" t="str">
-        <f t="shared" ref="J191:J194" si="45">+_xlfn.CONCAT("{{ ",I191," }}")</f>
+      <c r="K191" t="str">
+        <f t="shared" ref="K191:K194" si="45">+_xlfn.CONCAT("{{ ",J191," }}")</f>
         <v>{{ medidas_ries1 }}</v>
       </c>
-      <c r="K191" t="str">
-        <f t="shared" ref="K191:K194" si="46">+_xlfn.CONCAT("'",I191,"' : r_val['",I191,"'],")</f>
+      <c r="L191" t="str">
+        <f t="shared" ref="L191:L194" si="46">+_xlfn.CONCAT("'",J191,"' : r_val['",J191,"'],")</f>
         <v>'medidas_ries1' : r_val['medidas_ries1'],</v>
       </c>
     </row>
-    <row r="192" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I192" t="s">
+    <row r="192" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J192" t="s">
         <v>1753</v>
       </c>
-      <c r="J192" t="str">
+      <c r="K192" t="str">
         <f t="shared" si="45"/>
         <v>{{ medidas_ries2 }}</v>
       </c>
-      <c r="K192" t="str">
+      <c r="L192" t="str">
         <f t="shared" si="46"/>
         <v>'medidas_ries2' : r_val['medidas_ries2'],</v>
       </c>
     </row>
-    <row r="193" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I193" t="s">
+    <row r="193" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J193" t="s">
         <v>1754</v>
       </c>
-      <c r="J193" t="str">
+      <c r="K193" t="str">
         <f t="shared" si="45"/>
         <v>{{ medidas_ries3 }}</v>
       </c>
-      <c r="K193" t="str">
+      <c r="L193" t="str">
         <f t="shared" si="46"/>
         <v>'medidas_ries3' : r_val['medidas_ries3'],</v>
       </c>
     </row>
-    <row r="194" spans="9:11" x14ac:dyDescent="0.3">
-      <c r="I194" t="s">
+    <row r="194" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J194" t="s">
         <v>1755</v>
       </c>
-      <c r="J194" t="str">
+      <c r="K194" t="str">
         <f t="shared" si="45"/>
         <v>{{ medidas_ries4 }}</v>
       </c>
-      <c r="K194" t="str">
+      <c r="L194" t="str">
         <f t="shared" si="46"/>
         <v>'medidas_ries4' : r_val['medidas_ries4'],</v>
       </c>

--- a/Inputs/BD.xlsx
+++ b/Inputs/BD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/078e1a455e5c02ce/Documentos/GitHub/Proyecto_PIPC/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2861" documentId="13_ncr:1_{7D3A426E-EC5E-453A-8CC7-F83B71F24F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBE3CA1D-ADA2-4AD1-BDDC-5B0B8442EB46}"/>
+  <xr:revisionPtr revIDLastSave="2872" documentId="13_ncr:1_{7D3A426E-EC5E-453A-8CC7-F83B71F24F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13ABC23B-9C10-4F43-BB9C-F9DD185C515F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{3F095A75-F066-4695-8672-8D4315F1EF23}"/>
   </bookViews>
@@ -539,7 +539,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5674" uniqueCount="1761">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5680" uniqueCount="1762">
   <si>
     <t>dia</t>
   </si>
@@ -5822,6 +5822,9 @@
   </si>
   <si>
     <t>layout.png</t>
+  </si>
+  <si>
+    <t>corresp1</t>
   </si>
 </sst>
 </file>
@@ -31909,10 +31912,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76893F01-97EA-43A4-9AE2-ED099B9448DD}">
-  <dimension ref="A1:JA2"/>
+  <dimension ref="A1:JB2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:261" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:262" x14ac:dyDescent="0.3">
       <c r="A1">
         <f>+BD!A1</f>
         <v>38</v>
@@ -32697,8 +32700,11 @@
       <c r="JA1" t="s">
         <v>949</v>
       </c>
+      <c r="JB1" t="s">
+        <v>1761</v>
+      </c>
     </row>
-    <row r="2" spans="1:261" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:262" x14ac:dyDescent="0.3">
       <c r="B2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,2, FALSE)</f>
         <v>BBVA</v>
@@ -33646,6 +33652,10 @@
       </c>
       <c r="JA2" t="s">
         <v>950</v>
+      </c>
+      <c r="JB2" t="str">
+        <f>+_xlfn.CONCAT(JB1,".png")</f>
+        <v>corresp1.png</v>
       </c>
     </row>
   </sheetData>
@@ -38484,7 +38494,7 @@
         <v>'sismo_incendio' : r_val['sismo_incendio'],</v>
       </c>
       <c r="M67" t="str">
-        <f t="shared" ref="M67:M92" si="13">+_xlfn.CONCAT("'",E67,"': ",E67,",")</f>
+        <f t="shared" ref="M67:M93" si="13">+_xlfn.CONCAT("'",E67,"': ",E67,",")</f>
         <v>'plano': plano,</v>
       </c>
       <c r="N67" t="s">
@@ -40285,37 +40295,37 @@
         <v>558</v>
       </c>
       <c r="O91" t="str">
-        <f t="shared" ref="O91:O92" si="26">+_xlfn.CONCAT("img_path_",E91," = os.path.join(IMAGES_PATH, r_val[""",E91,"""])")</f>
+        <f t="shared" ref="O91:O93" si="26">+_xlfn.CONCAT("img_path_",E91," = os.path.join(IMAGES_PATH, r_val[""",E91,"""])")</f>
         <v>img_path_visitas = os.path.join(IMAGES_PATH, r_val["visitas"])</v>
       </c>
       <c r="P91" t="str">
-        <f t="shared" ref="P91:P92" si="27">+_xlfn.CONCAT("if os.path.exists(img_path_",E91,"):")</f>
+        <f t="shared" ref="P91:P93" si="27">+_xlfn.CONCAT("if os.path.exists(img_path_",E91,"):")</f>
         <v>if os.path.exists(img_path_visitas):</v>
       </c>
       <c r="Q91" t="str">
-        <f t="shared" ref="Q91:Q92" si="28">+_xlfn.CONCAT(E91," = InlineImage(docx_tpl, img_path_",E91,", height=Mm(",H91,"))")</f>
+        <f t="shared" ref="Q91:Q93" si="28">+_xlfn.CONCAT(E91," = InlineImage(docx_tpl, img_path_",E91,", height=Mm(",H91,"))")</f>
         <v>visitas = InlineImage(docx_tpl, img_path_visitas, height=Mm(155))</v>
       </c>
       <c r="R91" t="s">
         <v>560</v>
       </c>
       <c r="S91" t="str">
-        <f t="shared" ref="S91:S92" si="29">+_xlfn.CONCAT("print(f'Advertencia: No se encontró la imagen {r_val[""",E91,"""]}')")</f>
+        <f t="shared" ref="S91:S93" si="29">+_xlfn.CONCAT("print(f'Advertencia: No se encontró la imagen {r_val[""",E91,"""]}')")</f>
         <v>print(f'Advertencia: No se encontró la imagen {r_val["visitas"]}')</v>
       </c>
       <c r="T91" t="str">
-        <f t="shared" ref="T91:T92" si="30">+_xlfn.CONCAT(E91," = ''")</f>
+        <f t="shared" ref="T91:T93" si="30">+_xlfn.CONCAT(E91," = ''")</f>
         <v>visitas = ''</v>
       </c>
       <c r="U91" t="s">
         <v>559</v>
       </c>
       <c r="V91" t="str">
-        <f t="shared" ref="V91:V92" si="31">+_xlfn.CONCAT("print(f'Advertencia: No se pudo cargar la imagen {r_val[""",E91,"""]}: {e}')")</f>
+        <f t="shared" ref="V91:V93" si="31">+_xlfn.CONCAT("print(f'Advertencia: No se pudo cargar la imagen {r_val[""",E91,"""]}: {e}')")</f>
         <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["visitas"]}: {e}')</v>
       </c>
       <c r="W91" t="str">
-        <f t="shared" ref="W91:W92" si="32">+_xlfn.CONCAT(E91," = ''")</f>
+        <f t="shared" ref="W91:W93" si="32">+_xlfn.CONCAT(E91," = ''")</f>
         <v>visitas = ''</v>
       </c>
     </row>
@@ -40394,6 +40404,23 @@
       </c>
     </row>
     <row r="93" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="E93" t="s">
+        <v>1761</v>
+      </c>
+      <c r="F93" t="str">
+        <f>+_xlfn.CONCAT(E93,".png")</f>
+        <v>corresp1.png</v>
+      </c>
+      <c r="G93" t="str">
+        <f>+_xlfn.CONCAT("{{ ",E93," }}")</f>
+        <v>{{ corresp1 }}</v>
+      </c>
+      <c r="H93">
+        <v>155</v>
+      </c>
+      <c r="I93" t="s">
+        <v>1758</v>
+      </c>
       <c r="J93" t="s">
         <v>23</v>
       </c>
@@ -40403,6 +40430,47 @@
       <c r="L93" t="str">
         <f t="shared" si="25"/>
         <v>'tambo_arena' : r_val['tambo_arena'],</v>
+      </c>
+      <c r="M93" t="str">
+        <f t="shared" si="13"/>
+        <v>'corresp1': corresp1,</v>
+      </c>
+      <c r="N93" t="s">
+        <v>558</v>
+      </c>
+      <c r="O93" t="str">
+        <f t="shared" si="26"/>
+        <v>img_path_corresp1 = os.path.join(IMAGES_PATH, r_val["corresp1"])</v>
+      </c>
+      <c r="P93" t="str">
+        <f t="shared" si="27"/>
+        <v>if os.path.exists(img_path_corresp1):</v>
+      </c>
+      <c r="Q93" s="1" t="str">
+        <f>+_xlfn.CONCAT(E93," = InlineImage(docx_tpl, img_path_",E93,", ",I93,"=Mm(",H93,"))")</f>
+        <v>corresp1 = InlineImage(docx_tpl, img_path_corresp1, width=Mm(155))</v>
+      </c>
+      <c r="R93" t="s">
+        <v>560</v>
+      </c>
+      <c r="S93" t="str">
+        <f t="shared" si="29"/>
+        <v>print(f'Advertencia: No se encontró la imagen {r_val["corresp1"]}')</v>
+      </c>
+      <c r="T93" t="str">
+        <f t="shared" si="30"/>
+        <v>corresp1 = ''</v>
+      </c>
+      <c r="U93" t="s">
+        <v>559</v>
+      </c>
+      <c r="V93" t="str">
+        <f t="shared" si="31"/>
+        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["corresp1"]}: {e}')</v>
+      </c>
+      <c r="W93" t="str">
+        <f t="shared" si="32"/>
+        <v>corresp1 = ''</v>
       </c>
     </row>
     <row r="94" spans="3:23" x14ac:dyDescent="0.3">

--- a/Inputs/BD.xlsx
+++ b/Inputs/BD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/078e1a455e5c02ce/Documentos/GitHub/Proyecto_PIPC/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2872" documentId="13_ncr:1_{7D3A426E-EC5E-453A-8CC7-F83B71F24F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13ABC23B-9C10-4F43-BB9C-F9DD185C515F}"/>
+  <xr:revisionPtr revIDLastSave="2913" documentId="13_ncr:1_{7D3A426E-EC5E-453A-8CC7-F83B71F24F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13B4B3A0-B833-4C48-85B8-DDDF8DA6B11D}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{3F095A75-F066-4695-8672-8D4315F1EF23}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3F095A75-F066-4695-8672-8D4315F1EF23}"/>
   </bookViews>
   <sheets>
     <sheet name="BD" sheetId="1" r:id="rId1"/>
@@ -539,7 +539,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5680" uniqueCount="1762">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5783" uniqueCount="1785">
   <si>
     <t>dia</t>
   </si>
@@ -5825,6 +5825,75 @@
   </si>
   <si>
     <t>corresp1</t>
+  </si>
+  <si>
+    <t>corresp2</t>
+  </si>
+  <si>
+    <t>corresp3</t>
+  </si>
+  <si>
+    <t>carta_respon</t>
+  </si>
+  <si>
+    <t>registro1</t>
+  </si>
+  <si>
+    <t>registro2</t>
+  </si>
+  <si>
+    <t>ries_circ</t>
+  </si>
+  <si>
+    <t>mapa_ext</t>
+  </si>
+  <si>
+    <t>rec_ext</t>
+  </si>
+  <si>
+    <t>mayor_ries</t>
+  </si>
+  <si>
+    <t>menor_ries</t>
+  </si>
+  <si>
+    <t>zona_evac</t>
+  </si>
+  <si>
+    <t>corresp1.png</t>
+  </si>
+  <si>
+    <t>corresp2.png</t>
+  </si>
+  <si>
+    <t>corresp3.png</t>
+  </si>
+  <si>
+    <t>carta_respon.png</t>
+  </si>
+  <si>
+    <t>registro1.png</t>
+  </si>
+  <si>
+    <t>registro2.png</t>
+  </si>
+  <si>
+    <t>ries_circ.png</t>
+  </si>
+  <si>
+    <t>mapa_ext.png</t>
+  </si>
+  <si>
+    <t>rec_ext.png</t>
+  </si>
+  <si>
+    <t>mayor_ries.png</t>
+  </si>
+  <si>
+    <t>menor_ries.png</t>
+  </si>
+  <si>
+    <t>zona_evac.png</t>
   </si>
 </sst>
 </file>
@@ -6865,15 +6934,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE6A0106-4EDF-4D58-B8A9-1C9CC54D9FE0}">
-  <dimension ref="A1:KH201"/>
+  <dimension ref="A1:KT201"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:294" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:306" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:294" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:306" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>133</v>
       </c>
@@ -7658,106 +7727,142 @@
         <v>949</v>
       </c>
       <c r="JB2" t="s">
+        <v>1761</v>
+      </c>
+      <c r="JC2" t="s">
+        <v>1762</v>
+      </c>
+      <c r="JD2" t="s">
+        <v>1763</v>
+      </c>
+      <c r="JE2" t="s">
+        <v>1764</v>
+      </c>
+      <c r="JF2" t="s">
+        <v>1765</v>
+      </c>
+      <c r="JG2" t="s">
+        <v>1766</v>
+      </c>
+      <c r="JH2" t="s">
+        <v>1767</v>
+      </c>
+      <c r="JI2" t="s">
+        <v>1768</v>
+      </c>
+      <c r="JJ2" t="s">
+        <v>1769</v>
+      </c>
+      <c r="JK2" t="s">
+        <v>1770</v>
+      </c>
+      <c r="JL2" t="s">
+        <v>1771</v>
+      </c>
+      <c r="JM2" t="s">
+        <v>1772</v>
+      </c>
+      <c r="JN2" t="s">
         <v>621</v>
       </c>
-      <c r="JC2" t="s">
+      <c r="JO2" t="s">
         <v>622</v>
       </c>
-      <c r="JD2" t="s">
+      <c r="JP2" t="s">
         <v>639</v>
       </c>
-      <c r="JE2" t="s">
+      <c r="JQ2" t="s">
         <v>623</v>
       </c>
-      <c r="JF2" t="s">
+      <c r="JR2" t="s">
         <v>624</v>
       </c>
-      <c r="JG2" t="s">
+      <c r="JS2" t="s">
         <v>640</v>
       </c>
-      <c r="JH2" t="s">
+      <c r="JT2" t="s">
         <v>625</v>
       </c>
-      <c r="JI2" t="s">
+      <c r="JU2" t="s">
         <v>626</v>
       </c>
-      <c r="JJ2" t="s">
+      <c r="JV2" t="s">
         <v>641</v>
       </c>
-      <c r="JK2" t="s">
+      <c r="JW2" t="s">
         <v>627</v>
       </c>
-      <c r="JL2" t="s">
+      <c r="JX2" t="s">
         <v>628</v>
       </c>
-      <c r="JM2" t="s">
+      <c r="JY2" t="s">
         <v>642</v>
       </c>
-      <c r="JN2" t="s">
+      <c r="JZ2" t="s">
         <v>629</v>
       </c>
-      <c r="JO2" t="s">
+      <c r="KA2" t="s">
         <v>630</v>
       </c>
-      <c r="JP2" t="s">
+      <c r="KB2" t="s">
         <v>643</v>
       </c>
-      <c r="JQ2" t="s">
+      <c r="KC2" t="s">
         <v>631</v>
       </c>
-      <c r="JR2" t="s">
+      <c r="KD2" t="s">
         <v>632</v>
       </c>
-      <c r="JS2" t="s">
+      <c r="KE2" t="s">
         <v>644</v>
       </c>
-      <c r="JT2" t="s">
+      <c r="KF2" t="s">
         <v>633</v>
       </c>
-      <c r="JU2" t="s">
+      <c r="KG2" t="s">
         <v>634</v>
       </c>
-      <c r="JV2" t="s">
+      <c r="KH2" t="s">
         <v>645</v>
       </c>
-      <c r="JW2" t="s">
+      <c r="KI2" t="s">
         <v>635</v>
       </c>
-      <c r="JX2" t="s">
+      <c r="KJ2" t="s">
         <v>636</v>
       </c>
-      <c r="JY2" t="s">
+      <c r="KK2" t="s">
         <v>646</v>
       </c>
-      <c r="JZ2" t="s">
+      <c r="KL2" t="s">
         <v>1715</v>
       </c>
-      <c r="KA2" t="s">
+      <c r="KM2" t="s">
         <v>1716</v>
       </c>
-      <c r="KB2" t="s">
+      <c r="KN2" t="s">
         <v>1717</v>
       </c>
-      <c r="KC2" t="s">
+      <c r="KO2" t="s">
         <v>1718</v>
       </c>
-      <c r="KD2" t="s">
+      <c r="KP2" t="s">
         <v>1719</v>
       </c>
-      <c r="KE2" t="s">
+      <c r="KQ2" t="s">
         <v>1720</v>
       </c>
-      <c r="KF2" t="s">
+      <c r="KR2" t="s">
         <v>1721</v>
       </c>
-      <c r="KG2" t="s">
+      <c r="KS2" t="s">
         <v>1722</v>
       </c>
-      <c r="KH2" t="s">
+      <c r="KT2" t="s">
         <v>1723</v>
       </c>
     </row>
-    <row r="3" spans="1:294" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:306" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -8040,7 +8145,7 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="4" spans="1:294" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:306" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -8317,7 +8422,7 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="5" spans="1:294" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:306" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -8600,7 +8705,7 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="6" spans="1:294" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:306" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -8877,7 +8982,7 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="7" spans="1:294" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:306" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -9151,7 +9256,7 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="8" spans="1:294" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:306" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -9461,7 +9566,7 @@
         <v>ALTO</v>
       </c>
     </row>
-    <row r="9" spans="1:294" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:306" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -9744,7 +9849,7 @@
         <v>ALTO</v>
       </c>
     </row>
-    <row r="10" spans="1:294" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:306" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -10057,7 +10162,7 @@
         <v>ALTO</v>
       </c>
     </row>
-    <row r="11" spans="1:294" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:306" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -10379,7 +10484,7 @@
         <v>ALTO</v>
       </c>
     </row>
-    <row r="12" spans="1:294" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:306" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
@@ -10680,7 +10785,7 @@
         <v>ALTO</v>
       </c>
     </row>
-    <row r="13" spans="1:294" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:306" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
@@ -10978,7 +11083,7 @@
         <v>ALTO</v>
       </c>
     </row>
-    <row r="14" spans="1:294" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:306" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12</v>
       </c>
@@ -11491,107 +11596,107 @@
       <c r="JA14" t="s">
         <v>843</v>
       </c>
-      <c r="JB14" t="s">
+      <c r="JN14" t="s">
         <v>890</v>
       </c>
-      <c r="JC14" t="s">
+      <c r="JO14" t="s">
         <v>877</v>
       </c>
-      <c r="JD14" t="s">
+      <c r="JP14" t="s">
         <v>891</v>
       </c>
-      <c r="JE14" t="s">
+      <c r="JQ14" t="s">
         <v>892</v>
       </c>
-      <c r="JF14" t="s">
+      <c r="JR14" t="s">
         <v>877</v>
       </c>
-      <c r="JG14" t="s">
+      <c r="JS14" t="s">
         <v>893</v>
       </c>
-      <c r="JH14" t="s">
+      <c r="JT14" t="s">
         <v>894</v>
       </c>
-      <c r="JI14" t="s">
+      <c r="JU14" t="s">
         <v>865</v>
       </c>
-      <c r="JJ14" t="s">
+      <c r="JV14" t="s">
         <v>895</v>
       </c>
-      <c r="JK14" t="s">
+      <c r="JW14" t="s">
         <v>896</v>
-      </c>
-      <c r="JL14" t="s">
-        <v>868</v>
-      </c>
-      <c r="JM14" t="s">
-        <v>897</v>
-      </c>
-      <c r="JN14" t="s">
-        <v>898</v>
-      </c>
-      <c r="JO14" t="s">
-        <v>868</v>
-      </c>
-      <c r="JP14" t="s">
-        <v>899</v>
-      </c>
-      <c r="JQ14" t="s">
-        <v>900</v>
-      </c>
-      <c r="JR14" t="s">
-        <v>868</v>
-      </c>
-      <c r="JS14" t="s">
-        <v>901</v>
-      </c>
-      <c r="JT14" t="s">
-        <v>902</v>
-      </c>
-      <c r="JU14" t="s">
-        <v>868</v>
-      </c>
-      <c r="JV14" t="s">
-        <v>903</v>
-      </c>
-      <c r="JW14" t="s">
-        <v>904</v>
       </c>
       <c r="JX14" t="s">
         <v>868</v>
       </c>
       <c r="JY14" t="s">
-        <v>905</v>
+        <v>897</v>
       </c>
       <c r="JZ14" t="s">
-        <v>906</v>
+        <v>898</v>
       </c>
       <c r="KA14" t="s">
         <v>868</v>
       </c>
       <c r="KB14" t="s">
+        <v>899</v>
+      </c>
+      <c r="KC14" t="s">
+        <v>900</v>
+      </c>
+      <c r="KD14" t="s">
+        <v>868</v>
+      </c>
+      <c r="KE14" t="s">
+        <v>901</v>
+      </c>
+      <c r="KF14" t="s">
+        <v>902</v>
+      </c>
+      <c r="KG14" t="s">
+        <v>868</v>
+      </c>
+      <c r="KH14" t="s">
+        <v>903</v>
+      </c>
+      <c r="KI14" t="s">
+        <v>904</v>
+      </c>
+      <c r="KJ14" t="s">
+        <v>868</v>
+      </c>
+      <c r="KK14" t="s">
+        <v>905</v>
+      </c>
+      <c r="KL14" t="s">
+        <v>906</v>
+      </c>
+      <c r="KM14" t="s">
+        <v>868</v>
+      </c>
+      <c r="KN14" t="s">
         <v>907</v>
       </c>
-      <c r="KC14" t="s">
+      <c r="KO14" t="s">
         <v>908</v>
       </c>
-      <c r="KD14" t="s">
+      <c r="KP14" t="s">
         <v>874</v>
       </c>
-      <c r="KE14" t="s">
+      <c r="KQ14" t="s">
         <v>909</v>
       </c>
-      <c r="KF14" t="s">
+      <c r="KR14" t="s">
         <v>910</v>
       </c>
-      <c r="KG14" t="s">
+      <c r="KS14" t="s">
         <v>874</v>
       </c>
-      <c r="KH14" t="s">
+      <c r="KT14" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="15" spans="1:294" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:306" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13</v>
       </c>
@@ -12136,35 +12241,35 @@
       <c r="JA15" t="s">
         <v>843</v>
       </c>
-      <c r="JB15" t="s">
+      <c r="JN15" t="s">
         <v>939</v>
       </c>
-      <c r="JC15" t="s">
+      <c r="JO15" t="s">
         <v>868</v>
       </c>
-      <c r="JD15" t="s">
+      <c r="JP15" t="s">
         <v>940</v>
       </c>
-      <c r="JE15" t="s">
+      <c r="JQ15" t="s">
         <v>941</v>
       </c>
-      <c r="JF15" t="s">
+      <c r="JR15" t="s">
         <v>868</v>
       </c>
-      <c r="JG15" t="s">
+      <c r="JS15" t="s">
         <v>942</v>
       </c>
-      <c r="JH15" t="s">
+      <c r="JT15" t="s">
         <v>943</v>
       </c>
-      <c r="JI15" t="s">
+      <c r="JU15" t="s">
         <v>871</v>
       </c>
-      <c r="JJ15" t="s">
+      <c r="JV15" t="s">
         <v>944</v>
       </c>
     </row>
-    <row r="16" spans="1:294" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:306" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
@@ -12650,7 +12755,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="17" spans="1:267" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:279" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>15</v>
       </c>
@@ -13141,7 +13246,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="18" spans="1:267" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:279" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>16</v>
       </c>
@@ -13640,7 +13745,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="19" spans="1:267" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:279" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>17</v>
       </c>
@@ -14157,7 +14262,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="20" spans="1:267" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:279" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>18</v>
       </c>
@@ -14672,17 +14777,17 @@
       <c r="JA20" t="s">
         <v>843</v>
       </c>
-      <c r="JB20" t="s">
+      <c r="JN20" t="s">
         <v>1085</v>
       </c>
-      <c r="JC20" t="s">
+      <c r="JO20" t="s">
         <v>868</v>
       </c>
-      <c r="JD20" t="s">
+      <c r="JP20" t="s">
         <v>1086</v>
       </c>
     </row>
-    <row r="21" spans="1:267" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:279" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>19</v>
       </c>
@@ -15144,7 +15249,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="22" spans="1:267" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:279" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>20</v>
       </c>
@@ -15646,7 +15751,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="23" spans="1:267" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:279" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>21</v>
       </c>
@@ -16162,7 +16267,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="24" spans="1:267" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:279" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>22</v>
       </c>
@@ -16684,7 +16789,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="25" spans="1:267" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:279" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>23</v>
       </c>
@@ -17177,7 +17282,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="26" spans="1:267" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:279" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>24</v>
       </c>
@@ -17677,7 +17782,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="27" spans="1:267" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:279" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>25</v>
       </c>
@@ -18167,7 +18272,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="28" spans="1:267" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:279" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26</v>
       </c>
@@ -18679,7 +18784,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="29" spans="1:267" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:279" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>27</v>
       </c>
@@ -19202,23 +19307,23 @@
       <c r="JA29" t="s">
         <v>843</v>
       </c>
-      <c r="JB29" t="s">
+      <c r="JN29" t="s">
         <v>1309</v>
       </c>
-      <c r="JC29" t="s">
+      <c r="JO29" t="s">
         <v>874</v>
       </c>
-      <c r="JE29" t="s">
+      <c r="JQ29" t="s">
         <v>1310</v>
       </c>
-      <c r="JF29" t="s">
+      <c r="JR29" t="s">
         <v>874</v>
       </c>
-      <c r="JG29" t="s">
+      <c r="JS29" t="s">
         <v>1311</v>
       </c>
     </row>
-    <row r="30" spans="1:267" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:279" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>28</v>
       </c>
@@ -19709,7 +19814,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="31" spans="1:267" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:279" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>29</v>
       </c>
@@ -20212,7 +20317,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="32" spans="1:267" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:279" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>30</v>
       </c>
@@ -20715,7 +20820,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="33" spans="1:279" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:291" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>31</v>
       </c>
@@ -21196,7 +21301,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="34" spans="1:279" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:291" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>32</v>
       </c>
@@ -21685,7 +21790,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="35" spans="1:279" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:291" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>33</v>
       </c>
@@ -22188,7 +22293,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="36" spans="1:279" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:291" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>34</v>
       </c>
@@ -22692,7 +22797,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="37" spans="1:279" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:291" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>35</v>
       </c>
@@ -23189,7 +23294,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="38" spans="1:279" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:291" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>36</v>
       </c>
@@ -23685,7 +23790,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="39" spans="1:279" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:291" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>37</v>
       </c>
@@ -24208,62 +24313,62 @@
       <c r="JA39" t="s">
         <v>843</v>
       </c>
-      <c r="JB39" t="s">
+      <c r="JN39" t="s">
         <v>1572</v>
       </c>
-      <c r="JC39" t="s">
+      <c r="JO39" t="s">
         <v>868</v>
       </c>
-      <c r="JD39" t="s">
+      <c r="JP39" t="s">
         <v>1573</v>
       </c>
-      <c r="JE39" t="s">
+      <c r="JQ39" t="s">
         <v>1574</v>
-      </c>
-      <c r="JF39" t="s">
-        <v>868</v>
-      </c>
-      <c r="JG39" t="s">
-        <v>1575</v>
-      </c>
-      <c r="JH39" t="s">
-        <v>1576</v>
-      </c>
-      <c r="JI39" t="s">
-        <v>884</v>
-      </c>
-      <c r="JJ39" t="s">
-        <v>1577</v>
-      </c>
-      <c r="JK39" t="s">
-        <v>1578</v>
-      </c>
-      <c r="JL39" t="s">
-        <v>868</v>
-      </c>
-      <c r="JM39" t="s">
-        <v>1579</v>
-      </c>
-      <c r="JN39" t="s">
-        <v>1580</v>
-      </c>
-      <c r="JO39" t="s">
-        <v>1230</v>
-      </c>
-      <c r="JP39" t="s">
-        <v>1581</v>
-      </c>
-      <c r="JQ39" t="s">
-        <v>1582</v>
       </c>
       <c r="JR39" t="s">
         <v>868</v>
       </c>
       <c r="JS39" t="s">
+        <v>1575</v>
+      </c>
+      <c r="JT39" t="s">
+        <v>1576</v>
+      </c>
+      <c r="JU39" t="s">
+        <v>884</v>
+      </c>
+      <c r="JV39" t="s">
+        <v>1577</v>
+      </c>
+      <c r="JW39" t="s">
+        <v>1578</v>
+      </c>
+      <c r="JX39" t="s">
+        <v>868</v>
+      </c>
+      <c r="JY39" t="s">
+        <v>1579</v>
+      </c>
+      <c r="JZ39" t="s">
+        <v>1580</v>
+      </c>
+      <c r="KA39" t="s">
+        <v>1230</v>
+      </c>
+      <c r="KB39" t="s">
+        <v>1581</v>
+      </c>
+      <c r="KC39" t="s">
+        <v>1582</v>
+      </c>
+      <c r="KD39" t="s">
+        <v>868</v>
+      </c>
+      <c r="KE39" t="s">
         <v>1583</v>
       </c>
     </row>
-    <row r="40" spans="1:279" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:291" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>38</v>
       </c>
@@ -24840,7 +24945,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="41" spans="1:279" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:291" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>39</v>
       </c>
@@ -25345,7 +25450,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="42" spans="1:279" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:291" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>40</v>
       </c>
@@ -25801,26 +25906,26 @@
       <c r="JA42" t="s">
         <v>843</v>
       </c>
-      <c r="JB42" t="s">
+      <c r="JN42" t="s">
         <v>1650</v>
       </c>
-      <c r="JC42" t="s">
+      <c r="JO42" t="s">
         <v>1321</v>
       </c>
-      <c r="JD42" t="s">
+      <c r="JP42" t="s">
         <v>1651</v>
       </c>
-      <c r="JE42" t="s">
+      <c r="JQ42" t="s">
         <v>1652</v>
       </c>
-      <c r="JF42" t="s">
+      <c r="JR42" t="s">
         <v>874</v>
       </c>
-      <c r="JG42" t="s">
+      <c r="JS42" t="s">
         <v>1653</v>
       </c>
     </row>
-    <row r="43" spans="1:279" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:291" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>41</v>
       </c>
@@ -25857,7 +25962,7 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="44" spans="1:279" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:291" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>42</v>
       </c>
@@ -25894,7 +25999,7 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="45" spans="1:279" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:291" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>43</v>
       </c>
@@ -25931,7 +26036,7 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="46" spans="1:279" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:291" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>44</v>
       </c>
@@ -25968,7 +26073,7 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="47" spans="1:279" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:291" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>45</v>
       </c>
@@ -26005,7 +26110,7 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="48" spans="1:279" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:291" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>46</v>
       </c>
@@ -31829,12 +31934,12 @@
       <formula>$A40=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="JB2:KH2">
+  <conditionalFormatting sqref="JN2:KT2">
     <cfRule type="expression" dxfId="1" priority="151">
       <formula>#REF!=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="JB14:KH42">
+  <conditionalFormatting sqref="JN14:KT42">
     <cfRule type="expression" dxfId="0" priority="152">
       <formula>$A14=$A$1</formula>
     </cfRule>
@@ -31912,10 +32017,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76893F01-97EA-43A4-9AE2-ED099B9448DD}">
-  <dimension ref="A1:JB2"/>
+  <dimension ref="A1:JM2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:262" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:273" x14ac:dyDescent="0.3">
       <c r="A1">
         <f>+BD!A1</f>
         <v>38</v>
@@ -32703,8 +32808,41 @@
       <c r="JB1" t="s">
         <v>1761</v>
       </c>
+      <c r="JC1" t="s">
+        <v>1762</v>
+      </c>
+      <c r="JD1" t="s">
+        <v>1763</v>
+      </c>
+      <c r="JE1" t="s">
+        <v>1764</v>
+      </c>
+      <c r="JF1" t="s">
+        <v>1765</v>
+      </c>
+      <c r="JG1" t="s">
+        <v>1766</v>
+      </c>
+      <c r="JH1" t="s">
+        <v>1767</v>
+      </c>
+      <c r="JI1" t="s">
+        <v>1768</v>
+      </c>
+      <c r="JJ1" t="s">
+        <v>1769</v>
+      </c>
+      <c r="JK1" t="s">
+        <v>1770</v>
+      </c>
+      <c r="JL1" t="s">
+        <v>1771</v>
+      </c>
+      <c r="JM1" t="s">
+        <v>1772</v>
+      </c>
     </row>
-    <row r="2" spans="1:262" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:273" x14ac:dyDescent="0.3">
       <c r="B2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,2, FALSE)</f>
         <v>BBVA</v>
@@ -33653,9 +33791,41 @@
       <c r="JA2" t="s">
         <v>950</v>
       </c>
-      <c r="JB2" t="str">
-        <f>+_xlfn.CONCAT(JB1,".png")</f>
-        <v>corresp1.png</v>
+      <c r="JB2" t="s">
+        <v>1773</v>
+      </c>
+      <c r="JC2" t="s">
+        <v>1774</v>
+      </c>
+      <c r="JD2" t="s">
+        <v>1775</v>
+      </c>
+      <c r="JE2" t="s">
+        <v>1776</v>
+      </c>
+      <c r="JF2" t="s">
+        <v>1777</v>
+      </c>
+      <c r="JG2" t="s">
+        <v>1778</v>
+      </c>
+      <c r="JH2" t="s">
+        <v>1779</v>
+      </c>
+      <c r="JI2" t="s">
+        <v>1780</v>
+      </c>
+      <c r="JJ2" t="s">
+        <v>1781</v>
+      </c>
+      <c r="JK2" t="s">
+        <v>1782</v>
+      </c>
+      <c r="JL2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="JM2" t="s">
+        <v>1784</v>
       </c>
     </row>
   </sheetData>
@@ -38494,7 +38664,7 @@
         <v>'sismo_incendio' : r_val['sismo_incendio'],</v>
       </c>
       <c r="M67" t="str">
-        <f t="shared" ref="M67:M93" si="13">+_xlfn.CONCAT("'",E67,"': ",E67,",")</f>
+        <f t="shared" ref="M67:M104" si="13">+_xlfn.CONCAT("'",E67,"': ",E67,",")</f>
         <v>'plano': plano,</v>
       </c>
       <c r="N67" t="s">
@@ -40303,7 +40473,7 @@
         <v>if os.path.exists(img_path_visitas):</v>
       </c>
       <c r="Q91" t="str">
-        <f t="shared" ref="Q91:Q93" si="28">+_xlfn.CONCAT(E91," = InlineImage(docx_tpl, img_path_",E91,", height=Mm(",H91,"))")</f>
+        <f t="shared" ref="Q91:Q92" si="28">+_xlfn.CONCAT(E91," = InlineImage(docx_tpl, img_path_",E91,", height=Mm(",H91,"))")</f>
         <v>visitas = InlineImage(docx_tpl, img_path_visitas, height=Mm(155))</v>
       </c>
       <c r="R91" t="s">
@@ -40404,6 +40574,9 @@
       </c>
     </row>
     <row r="93" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="C93" t="s">
+        <v>843</v>
+      </c>
       <c r="E93" t="s">
         <v>1761</v>
       </c>
@@ -40474,6 +40647,26 @@
       </c>
     </row>
     <row r="94" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="C94" t="s">
+        <v>843</v>
+      </c>
+      <c r="E94" t="s">
+        <v>1762</v>
+      </c>
+      <c r="F94" t="str">
+        <f t="shared" ref="F94:F104" si="33">+_xlfn.CONCAT(E94,".png")</f>
+        <v>corresp2.png</v>
+      </c>
+      <c r="G94" t="str">
+        <f t="shared" ref="G94:G104" si="34">+_xlfn.CONCAT("{{ ",E94," }}")</f>
+        <v>{{ corresp2 }}</v>
+      </c>
+      <c r="H94">
+        <v>155</v>
+      </c>
+      <c r="I94" t="s">
+        <v>1758</v>
+      </c>
       <c r="J94" t="s">
         <v>564</v>
       </c>
@@ -40484,8 +40677,69 @@
         <f t="shared" si="25"/>
         <v>'ubicacion_tambo' : r_val['ubicacion_tambo'],</v>
       </c>
+      <c r="M94" t="str">
+        <f t="shared" si="13"/>
+        <v>'corresp2': corresp2,</v>
+      </c>
+      <c r="N94" t="s">
+        <v>558</v>
+      </c>
+      <c r="O94" t="str">
+        <f t="shared" ref="O94:O104" si="35">+_xlfn.CONCAT("img_path_",E94," = os.path.join(IMAGES_PATH, r_val[""",E94,"""])")</f>
+        <v>img_path_corresp2 = os.path.join(IMAGES_PATH, r_val["corresp2"])</v>
+      </c>
+      <c r="P94" t="str">
+        <f t="shared" ref="P94:P104" si="36">+_xlfn.CONCAT("if os.path.exists(img_path_",E94,"):")</f>
+        <v>if os.path.exists(img_path_corresp2):</v>
+      </c>
+      <c r="Q94" t="str">
+        <f t="shared" ref="Q94:Q104" si="37">+_xlfn.CONCAT(E94," = InlineImage(docx_tpl, img_path_",E94,", ",I94,"=Mm(",H94,"))")</f>
+        <v>corresp2 = InlineImage(docx_tpl, img_path_corresp2, width=Mm(155))</v>
+      </c>
+      <c r="R94" t="s">
+        <v>560</v>
+      </c>
+      <c r="S94" t="str">
+        <f t="shared" ref="S94:S104" si="38">+_xlfn.CONCAT("print(f'Advertencia: No se encontró la imagen {r_val[""",E94,"""]}')")</f>
+        <v>print(f'Advertencia: No se encontró la imagen {r_val["corresp2"]}')</v>
+      </c>
+      <c r="T94" t="str">
+        <f t="shared" ref="T94:T104" si="39">+_xlfn.CONCAT(E94," = ''")</f>
+        <v>corresp2 = ''</v>
+      </c>
+      <c r="U94" t="s">
+        <v>559</v>
+      </c>
+      <c r="V94" t="str">
+        <f t="shared" ref="V94:V104" si="40">+_xlfn.CONCAT("print(f'Advertencia: No se pudo cargar la imagen {r_val[""",E94,"""]}: {e}')")</f>
+        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["corresp2"]}: {e}')</v>
+      </c>
+      <c r="W94" t="str">
+        <f t="shared" ref="W94:W104" si="41">+_xlfn.CONCAT(E94," = ''")</f>
+        <v>corresp2 = ''</v>
+      </c>
     </row>
     <row r="95" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="C95" t="s">
+        <v>843</v>
+      </c>
+      <c r="E95" t="s">
+        <v>1763</v>
+      </c>
+      <c r="F95" t="str">
+        <f t="shared" si="33"/>
+        <v>corresp3.png</v>
+      </c>
+      <c r="G95" t="str">
+        <f t="shared" si="34"/>
+        <v>{{ corresp3 }}</v>
+      </c>
+      <c r="H95">
+        <v>155</v>
+      </c>
+      <c r="I95" t="s">
+        <v>1758</v>
+      </c>
       <c r="J95" t="s">
         <v>191</v>
       </c>
@@ -40496,8 +40750,69 @@
         <f t="shared" si="25"/>
         <v>'tanques' : r_val['tanques'],</v>
       </c>
+      <c r="M95" t="str">
+        <f t="shared" si="13"/>
+        <v>'corresp3': corresp3,</v>
+      </c>
+      <c r="N95" t="s">
+        <v>558</v>
+      </c>
+      <c r="O95" t="str">
+        <f t="shared" si="35"/>
+        <v>img_path_corresp3 = os.path.join(IMAGES_PATH, r_val["corresp3"])</v>
+      </c>
+      <c r="P95" t="str">
+        <f t="shared" si="36"/>
+        <v>if os.path.exists(img_path_corresp3):</v>
+      </c>
+      <c r="Q95" t="str">
+        <f t="shared" si="37"/>
+        <v>corresp3 = InlineImage(docx_tpl, img_path_corresp3, width=Mm(155))</v>
+      </c>
+      <c r="R95" t="s">
+        <v>560</v>
+      </c>
+      <c r="S95" t="str">
+        <f t="shared" si="38"/>
+        <v>print(f'Advertencia: No se encontró la imagen {r_val["corresp3"]}')</v>
+      </c>
+      <c r="T95" t="str">
+        <f t="shared" si="39"/>
+        <v>corresp3 = ''</v>
+      </c>
+      <c r="U95" t="s">
+        <v>559</v>
+      </c>
+      <c r="V95" t="str">
+        <f t="shared" si="40"/>
+        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["corresp3"]}: {e}')</v>
+      </c>
+      <c r="W95" t="str">
+        <f t="shared" si="41"/>
+        <v>corresp3 = ''</v>
+      </c>
     </row>
     <row r="96" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="C96" t="s">
+        <v>843</v>
+      </c>
+      <c r="E96" t="s">
+        <v>1764</v>
+      </c>
+      <c r="F96" t="str">
+        <f t="shared" si="33"/>
+        <v>carta_respon.png</v>
+      </c>
+      <c r="G96" t="str">
+        <f t="shared" si="34"/>
+        <v>{{ carta_respon }}</v>
+      </c>
+      <c r="H96">
+        <v>155</v>
+      </c>
+      <c r="I96" t="s">
+        <v>1758</v>
+      </c>
       <c r="J96" t="s">
         <v>192</v>
       </c>
@@ -40508,8 +40823,69 @@
         <f t="shared" si="25"/>
         <v>'tanque_1' : r_val['tanque_1'],</v>
       </c>
+      <c r="M96" t="str">
+        <f t="shared" si="13"/>
+        <v>'carta_respon': carta_respon,</v>
+      </c>
+      <c r="N96" t="s">
+        <v>558</v>
+      </c>
+      <c r="O96" t="str">
+        <f t="shared" si="35"/>
+        <v>img_path_carta_respon = os.path.join(IMAGES_PATH, r_val["carta_respon"])</v>
+      </c>
+      <c r="P96" t="str">
+        <f t="shared" si="36"/>
+        <v>if os.path.exists(img_path_carta_respon):</v>
+      </c>
+      <c r="Q96" t="str">
+        <f t="shared" si="37"/>
+        <v>carta_respon = InlineImage(docx_tpl, img_path_carta_respon, width=Mm(155))</v>
+      </c>
+      <c r="R96" t="s">
+        <v>560</v>
+      </c>
+      <c r="S96" t="str">
+        <f t="shared" si="38"/>
+        <v>print(f'Advertencia: No se encontró la imagen {r_val["carta_respon"]}')</v>
+      </c>
+      <c r="T96" t="str">
+        <f t="shared" si="39"/>
+        <v>carta_respon = ''</v>
+      </c>
+      <c r="U96" t="s">
+        <v>559</v>
+      </c>
+      <c r="V96" t="str">
+        <f t="shared" si="40"/>
+        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["carta_respon"]}: {e}')</v>
+      </c>
+      <c r="W96" t="str">
+        <f t="shared" si="41"/>
+        <v>carta_respon = ''</v>
+      </c>
     </row>
-    <row r="97" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="97" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="C97" t="s">
+        <v>843</v>
+      </c>
+      <c r="E97" t="s">
+        <v>1765</v>
+      </c>
+      <c r="F97" t="str">
+        <f t="shared" si="33"/>
+        <v>registro1.png</v>
+      </c>
+      <c r="G97" t="str">
+        <f t="shared" si="34"/>
+        <v>{{ registro1 }}</v>
+      </c>
+      <c r="H97">
+        <v>155</v>
+      </c>
+      <c r="I97" t="s">
+        <v>1758</v>
+      </c>
       <c r="J97" t="s">
         <v>193</v>
       </c>
@@ -40520,8 +40896,69 @@
         <f t="shared" si="25"/>
         <v>'tanque_2' : r_val['tanque_2'],</v>
       </c>
+      <c r="M97" t="str">
+        <f t="shared" si="13"/>
+        <v>'registro1': registro1,</v>
+      </c>
+      <c r="N97" t="s">
+        <v>558</v>
+      </c>
+      <c r="O97" t="str">
+        <f t="shared" si="35"/>
+        <v>img_path_registro1 = os.path.join(IMAGES_PATH, r_val["registro1"])</v>
+      </c>
+      <c r="P97" t="str">
+        <f t="shared" si="36"/>
+        <v>if os.path.exists(img_path_registro1):</v>
+      </c>
+      <c r="Q97" t="str">
+        <f t="shared" si="37"/>
+        <v>registro1 = InlineImage(docx_tpl, img_path_registro1, width=Mm(155))</v>
+      </c>
+      <c r="R97" t="s">
+        <v>560</v>
+      </c>
+      <c r="S97" t="str">
+        <f t="shared" si="38"/>
+        <v>print(f'Advertencia: No se encontró la imagen {r_val["registro1"]}')</v>
+      </c>
+      <c r="T97" t="str">
+        <f t="shared" si="39"/>
+        <v>registro1 = ''</v>
+      </c>
+      <c r="U97" t="s">
+        <v>559</v>
+      </c>
+      <c r="V97" t="str">
+        <f t="shared" si="40"/>
+        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["registro1"]}: {e}')</v>
+      </c>
+      <c r="W97" t="str">
+        <f t="shared" si="41"/>
+        <v>registro1 = ''</v>
+      </c>
     </row>
-    <row r="98" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="98" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="C98" t="s">
+        <v>843</v>
+      </c>
+      <c r="E98" t="s">
+        <v>1766</v>
+      </c>
+      <c r="F98" t="str">
+        <f t="shared" si="33"/>
+        <v>registro2.png</v>
+      </c>
+      <c r="G98" t="str">
+        <f t="shared" si="34"/>
+        <v>{{ registro2 }}</v>
+      </c>
+      <c r="H98">
+        <v>155</v>
+      </c>
+      <c r="I98" t="s">
+        <v>1758</v>
+      </c>
       <c r="J98" t="s">
         <v>194</v>
       </c>
@@ -40532,8 +40969,69 @@
         <f t="shared" si="25"/>
         <v>'tanque_3' : r_val['tanque_3'],</v>
       </c>
+      <c r="M98" t="str">
+        <f t="shared" si="13"/>
+        <v>'registro2': registro2,</v>
+      </c>
+      <c r="N98" t="s">
+        <v>558</v>
+      </c>
+      <c r="O98" t="str">
+        <f t="shared" si="35"/>
+        <v>img_path_registro2 = os.path.join(IMAGES_PATH, r_val["registro2"])</v>
+      </c>
+      <c r="P98" t="str">
+        <f t="shared" si="36"/>
+        <v>if os.path.exists(img_path_registro2):</v>
+      </c>
+      <c r="Q98" t="str">
+        <f t="shared" si="37"/>
+        <v>registro2 = InlineImage(docx_tpl, img_path_registro2, width=Mm(155))</v>
+      </c>
+      <c r="R98" t="s">
+        <v>560</v>
+      </c>
+      <c r="S98" t="str">
+        <f t="shared" si="38"/>
+        <v>print(f'Advertencia: No se encontró la imagen {r_val["registro2"]}')</v>
+      </c>
+      <c r="T98" t="str">
+        <f t="shared" si="39"/>
+        <v>registro2 = ''</v>
+      </c>
+      <c r="U98" t="s">
+        <v>559</v>
+      </c>
+      <c r="V98" t="str">
+        <f t="shared" si="40"/>
+        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["registro2"]}: {e}')</v>
+      </c>
+      <c r="W98" t="str">
+        <f t="shared" si="41"/>
+        <v>registro2 = ''</v>
+      </c>
     </row>
-    <row r="99" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="99" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="C99" t="s">
+        <v>843</v>
+      </c>
+      <c r="E99" t="s">
+        <v>1767</v>
+      </c>
+      <c r="F99" t="str">
+        <f t="shared" si="33"/>
+        <v>ries_circ.png</v>
+      </c>
+      <c r="G99" t="str">
+        <f t="shared" si="34"/>
+        <v>{{ ries_circ }}</v>
+      </c>
+      <c r="H99">
+        <v>155</v>
+      </c>
+      <c r="I99" t="s">
+        <v>1758</v>
+      </c>
       <c r="J99" t="s">
         <v>0</v>
       </c>
@@ -40544,8 +41042,69 @@
         <f t="shared" si="25"/>
         <v>'dia' : r_val['dia'],</v>
       </c>
+      <c r="M99" t="str">
+        <f t="shared" si="13"/>
+        <v>'ries_circ': ries_circ,</v>
+      </c>
+      <c r="N99" t="s">
+        <v>558</v>
+      </c>
+      <c r="O99" t="str">
+        <f t="shared" si="35"/>
+        <v>img_path_ries_circ = os.path.join(IMAGES_PATH, r_val["ries_circ"])</v>
+      </c>
+      <c r="P99" t="str">
+        <f t="shared" si="36"/>
+        <v>if os.path.exists(img_path_ries_circ):</v>
+      </c>
+      <c r="Q99" t="str">
+        <f t="shared" si="37"/>
+        <v>ries_circ = InlineImage(docx_tpl, img_path_ries_circ, width=Mm(155))</v>
+      </c>
+      <c r="R99" t="s">
+        <v>560</v>
+      </c>
+      <c r="S99" t="str">
+        <f t="shared" si="38"/>
+        <v>print(f'Advertencia: No se encontró la imagen {r_val["ries_circ"]}')</v>
+      </c>
+      <c r="T99" t="str">
+        <f t="shared" si="39"/>
+        <v>ries_circ = ''</v>
+      </c>
+      <c r="U99" t="s">
+        <v>559</v>
+      </c>
+      <c r="V99" t="str">
+        <f t="shared" si="40"/>
+        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["ries_circ"]}: {e}')</v>
+      </c>
+      <c r="W99" t="str">
+        <f t="shared" si="41"/>
+        <v>ries_circ = ''</v>
+      </c>
     </row>
-    <row r="100" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="100" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="C100" t="s">
+        <v>843</v>
+      </c>
+      <c r="E100" t="s">
+        <v>1768</v>
+      </c>
+      <c r="F100" t="str">
+        <f t="shared" si="33"/>
+        <v>mapa_ext.png</v>
+      </c>
+      <c r="G100" t="str">
+        <f t="shared" si="34"/>
+        <v>{{ mapa_ext }}</v>
+      </c>
+      <c r="H100">
+        <v>155</v>
+      </c>
+      <c r="I100" t="s">
+        <v>1758</v>
+      </c>
       <c r="J100" t="s">
         <v>1</v>
       </c>
@@ -40556,8 +41115,69 @@
         <f t="shared" si="25"/>
         <v>'mes' : r_val['mes'],</v>
       </c>
+      <c r="M100" t="str">
+        <f t="shared" si="13"/>
+        <v>'mapa_ext': mapa_ext,</v>
+      </c>
+      <c r="N100" t="s">
+        <v>558</v>
+      </c>
+      <c r="O100" t="str">
+        <f t="shared" si="35"/>
+        <v>img_path_mapa_ext = os.path.join(IMAGES_PATH, r_val["mapa_ext"])</v>
+      </c>
+      <c r="P100" t="str">
+        <f t="shared" si="36"/>
+        <v>if os.path.exists(img_path_mapa_ext):</v>
+      </c>
+      <c r="Q100" t="str">
+        <f t="shared" si="37"/>
+        <v>mapa_ext = InlineImage(docx_tpl, img_path_mapa_ext, width=Mm(155))</v>
+      </c>
+      <c r="R100" t="s">
+        <v>560</v>
+      </c>
+      <c r="S100" t="str">
+        <f t="shared" si="38"/>
+        <v>print(f'Advertencia: No se encontró la imagen {r_val["mapa_ext"]}')</v>
+      </c>
+      <c r="T100" t="str">
+        <f t="shared" si="39"/>
+        <v>mapa_ext = ''</v>
+      </c>
+      <c r="U100" t="s">
+        <v>559</v>
+      </c>
+      <c r="V100" t="str">
+        <f t="shared" si="40"/>
+        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["mapa_ext"]}: {e}')</v>
+      </c>
+      <c r="W100" t="str">
+        <f t="shared" si="41"/>
+        <v>mapa_ext = ''</v>
+      </c>
     </row>
-    <row r="101" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="101" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="C101" t="s">
+        <v>843</v>
+      </c>
+      <c r="E101" t="s">
+        <v>1769</v>
+      </c>
+      <c r="F101" t="str">
+        <f t="shared" si="33"/>
+        <v>rec_ext.png</v>
+      </c>
+      <c r="G101" t="str">
+        <f t="shared" si="34"/>
+        <v>{{ rec_ext }}</v>
+      </c>
+      <c r="H101">
+        <v>155</v>
+      </c>
+      <c r="I101" t="s">
+        <v>1758</v>
+      </c>
       <c r="J101" t="s">
         <v>2</v>
       </c>
@@ -40568,8 +41188,69 @@
         <f t="shared" si="25"/>
         <v>'anio' : r_val['anio'],</v>
       </c>
+      <c r="M101" t="str">
+        <f t="shared" si="13"/>
+        <v>'rec_ext': rec_ext,</v>
+      </c>
+      <c r="N101" t="s">
+        <v>558</v>
+      </c>
+      <c r="O101" t="str">
+        <f t="shared" si="35"/>
+        <v>img_path_rec_ext = os.path.join(IMAGES_PATH, r_val["rec_ext"])</v>
+      </c>
+      <c r="P101" t="str">
+        <f t="shared" si="36"/>
+        <v>if os.path.exists(img_path_rec_ext):</v>
+      </c>
+      <c r="Q101" t="str">
+        <f t="shared" si="37"/>
+        <v>rec_ext = InlineImage(docx_tpl, img_path_rec_ext, width=Mm(155))</v>
+      </c>
+      <c r="R101" t="s">
+        <v>560</v>
+      </c>
+      <c r="S101" t="str">
+        <f t="shared" si="38"/>
+        <v>print(f'Advertencia: No se encontró la imagen {r_val["rec_ext"]}')</v>
+      </c>
+      <c r="T101" t="str">
+        <f t="shared" si="39"/>
+        <v>rec_ext = ''</v>
+      </c>
+      <c r="U101" t="s">
+        <v>559</v>
+      </c>
+      <c r="V101" t="str">
+        <f t="shared" si="40"/>
+        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["rec_ext"]}: {e}')</v>
+      </c>
+      <c r="W101" t="str">
+        <f t="shared" si="41"/>
+        <v>rec_ext = ''</v>
+      </c>
     </row>
-    <row r="102" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="102" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="C102" t="s">
+        <v>843</v>
+      </c>
+      <c r="E102" t="s">
+        <v>1770</v>
+      </c>
+      <c r="F102" t="str">
+        <f t="shared" si="33"/>
+        <v>mayor_ries.png</v>
+      </c>
+      <c r="G102" t="str">
+        <f t="shared" si="34"/>
+        <v>{{ mayor_ries }}</v>
+      </c>
+      <c r="H102">
+        <v>155</v>
+      </c>
+      <c r="I102" t="s">
+        <v>1758</v>
+      </c>
       <c r="J102" t="s">
         <v>195</v>
       </c>
@@ -40580,8 +41261,69 @@
         <f t="shared" si="25"/>
         <v>'coordenadas' : r_val['coordenadas'],</v>
       </c>
+      <c r="M102" t="str">
+        <f t="shared" si="13"/>
+        <v>'mayor_ries': mayor_ries,</v>
+      </c>
+      <c r="N102" t="s">
+        <v>558</v>
+      </c>
+      <c r="O102" t="str">
+        <f t="shared" si="35"/>
+        <v>img_path_mayor_ries = os.path.join(IMAGES_PATH, r_val["mayor_ries"])</v>
+      </c>
+      <c r="P102" t="str">
+        <f t="shared" si="36"/>
+        <v>if os.path.exists(img_path_mayor_ries):</v>
+      </c>
+      <c r="Q102" t="str">
+        <f t="shared" si="37"/>
+        <v>mayor_ries = InlineImage(docx_tpl, img_path_mayor_ries, width=Mm(155))</v>
+      </c>
+      <c r="R102" t="s">
+        <v>560</v>
+      </c>
+      <c r="S102" t="str">
+        <f t="shared" si="38"/>
+        <v>print(f'Advertencia: No se encontró la imagen {r_val["mayor_ries"]}')</v>
+      </c>
+      <c r="T102" t="str">
+        <f t="shared" si="39"/>
+        <v>mayor_ries = ''</v>
+      </c>
+      <c r="U102" t="s">
+        <v>559</v>
+      </c>
+      <c r="V102" t="str">
+        <f t="shared" si="40"/>
+        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["mayor_ries"]}: {e}')</v>
+      </c>
+      <c r="W102" t="str">
+        <f t="shared" si="41"/>
+        <v>mayor_ries = ''</v>
+      </c>
     </row>
-    <row r="103" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="103" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="C103" t="s">
+        <v>843</v>
+      </c>
+      <c r="E103" t="s">
+        <v>1771</v>
+      </c>
+      <c r="F103" t="str">
+        <f t="shared" si="33"/>
+        <v>menor_ries.png</v>
+      </c>
+      <c r="G103" t="str">
+        <f t="shared" si="34"/>
+        <v>{{ menor_ries }}</v>
+      </c>
+      <c r="H103">
+        <v>155</v>
+      </c>
+      <c r="I103" t="s">
+        <v>1758</v>
+      </c>
       <c r="J103" t="s">
         <v>196</v>
       </c>
@@ -40592,8 +41334,69 @@
         <f t="shared" si="25"/>
         <v>'norte' : r_val['norte'],</v>
       </c>
+      <c r="M103" t="str">
+        <f t="shared" si="13"/>
+        <v>'menor_ries': menor_ries,</v>
+      </c>
+      <c r="N103" t="s">
+        <v>558</v>
+      </c>
+      <c r="O103" t="str">
+        <f t="shared" si="35"/>
+        <v>img_path_menor_ries = os.path.join(IMAGES_PATH, r_val["menor_ries"])</v>
+      </c>
+      <c r="P103" t="str">
+        <f t="shared" si="36"/>
+        <v>if os.path.exists(img_path_menor_ries):</v>
+      </c>
+      <c r="Q103" t="str">
+        <f t="shared" si="37"/>
+        <v>menor_ries = InlineImage(docx_tpl, img_path_menor_ries, width=Mm(155))</v>
+      </c>
+      <c r="R103" t="s">
+        <v>560</v>
+      </c>
+      <c r="S103" t="str">
+        <f t="shared" si="38"/>
+        <v>print(f'Advertencia: No se encontró la imagen {r_val["menor_ries"]}')</v>
+      </c>
+      <c r="T103" t="str">
+        <f t="shared" si="39"/>
+        <v>menor_ries = ''</v>
+      </c>
+      <c r="U103" t="s">
+        <v>559</v>
+      </c>
+      <c r="V103" t="str">
+        <f t="shared" si="40"/>
+        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["menor_ries"]}: {e}')</v>
+      </c>
+      <c r="W103" t="str">
+        <f t="shared" si="41"/>
+        <v>menor_ries = ''</v>
+      </c>
     </row>
-    <row r="104" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="104" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="C104" t="s">
+        <v>843</v>
+      </c>
+      <c r="E104" t="s">
+        <v>1772</v>
+      </c>
+      <c r="F104" t="str">
+        <f t="shared" si="33"/>
+        <v>zona_evac.png</v>
+      </c>
+      <c r="G104" t="str">
+        <f t="shared" si="34"/>
+        <v>{{ zona_evac }}</v>
+      </c>
+      <c r="H104">
+        <v>155</v>
+      </c>
+      <c r="I104" t="s">
+        <v>1758</v>
+      </c>
       <c r="J104" t="s">
         <v>197</v>
       </c>
@@ -40604,8 +41407,52 @@
         <f t="shared" si="25"/>
         <v>'sur' : r_val['sur'],</v>
       </c>
+      <c r="M104" t="str">
+        <f t="shared" si="13"/>
+        <v>'zona_evac': zona_evac,</v>
+      </c>
+      <c r="N104" t="s">
+        <v>558</v>
+      </c>
+      <c r="O104" t="str">
+        <f t="shared" si="35"/>
+        <v>img_path_zona_evac = os.path.join(IMAGES_PATH, r_val["zona_evac"])</v>
+      </c>
+      <c r="P104" t="str">
+        <f t="shared" si="36"/>
+        <v>if os.path.exists(img_path_zona_evac):</v>
+      </c>
+      <c r="Q104" t="str">
+        <f t="shared" si="37"/>
+        <v>zona_evac = InlineImage(docx_tpl, img_path_zona_evac, width=Mm(155))</v>
+      </c>
+      <c r="R104" t="s">
+        <v>560</v>
+      </c>
+      <c r="S104" t="str">
+        <f t="shared" si="38"/>
+        <v>print(f'Advertencia: No se encontró la imagen {r_val["zona_evac"]}')</v>
+      </c>
+      <c r="T104" t="str">
+        <f t="shared" si="39"/>
+        <v>zona_evac = ''</v>
+      </c>
+      <c r="U104" t="s">
+        <v>559</v>
+      </c>
+      <c r="V104" t="str">
+        <f t="shared" si="40"/>
+        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["zona_evac"]}: {e}')</v>
+      </c>
+      <c r="W104" t="str">
+        <f t="shared" si="41"/>
+        <v>zona_evac = ''</v>
+      </c>
     </row>
-    <row r="105" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="105" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="C105" t="s">
+        <v>843</v>
+      </c>
       <c r="J105" t="s">
         <v>198</v>
       </c>
@@ -40617,7 +41464,7 @@
         <v>'este' : r_val['este'],</v>
       </c>
     </row>
-    <row r="106" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="106" spans="3:23" x14ac:dyDescent="0.3">
       <c r="J106" t="s">
         <v>199</v>
       </c>
@@ -40629,7 +41476,7 @@
         <v>'oeste' : r_val['oeste'],</v>
       </c>
     </row>
-    <row r="107" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="107" spans="3:23" x14ac:dyDescent="0.3">
       <c r="J107" t="s">
         <v>597</v>
       </c>
@@ -40641,7 +41488,7 @@
         <v>'ref_llegar' : r_val['ref_llegar'],</v>
       </c>
     </row>
-    <row r="108" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="108" spans="3:23" x14ac:dyDescent="0.3">
       <c r="J108" t="s">
         <v>200</v>
       </c>
@@ -40653,7 +41500,7 @@
         <v>'ley' : r_val['ley'],</v>
       </c>
     </row>
-    <row r="109" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="109" spans="3:23" x14ac:dyDescent="0.3">
       <c r="J109" t="s">
         <v>201</v>
       </c>
@@ -40665,7 +41512,7 @@
         <v>'reglamento' : r_val['reglamento'],</v>
       </c>
     </row>
-    <row r="110" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="110" spans="3:23" x14ac:dyDescent="0.3">
       <c r="J110" t="s">
         <v>647</v>
       </c>
@@ -40677,7 +41524,7 @@
         <v>'m_dir' : r_val['m_dir'],</v>
       </c>
     </row>
-    <row r="111" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="111" spans="3:23" x14ac:dyDescent="0.3">
       <c r="J111" t="s">
         <v>202</v>
       </c>
@@ -40685,11 +41532,11 @@
         <v>317</v>
       </c>
       <c r="L111" t="str">
-        <f t="shared" ref="L111:L142" si="33">+_xlfn.CONCAT("'",J111,"' : r_val['",J111,"'],")</f>
+        <f t="shared" ref="L111:L142" si="42">+_xlfn.CONCAT("'",J111,"' : r_val['",J111,"'],")</f>
         <v>'coord_suplente' : r_val['coord_suplente'],</v>
       </c>
     </row>
-    <row r="112" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="112" spans="3:23" x14ac:dyDescent="0.3">
       <c r="J112" t="s">
         <v>648</v>
       </c>
@@ -40697,7 +41544,7 @@
         <v>688</v>
       </c>
       <c r="L112" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="42"/>
         <v>'m_jef_caj' : r_val['m_jef_caj'],</v>
       </c>
     </row>
@@ -40709,7 +41556,7 @@
         <v>318</v>
       </c>
       <c r="L113" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="42"/>
         <v>'evacuacion' : r_val['evacuacion'],</v>
       </c>
     </row>
@@ -40721,7 +41568,7 @@
         <v>589</v>
       </c>
       <c r="L114" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="42"/>
         <v>'evac_puesto' : r_val['evac_puesto'],</v>
       </c>
     </row>
@@ -40733,7 +41580,7 @@
         <v>689</v>
       </c>
       <c r="L115" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="42"/>
         <v>'m_evac' : r_val['m_evac'],</v>
       </c>
     </row>
@@ -40745,7 +41592,7 @@
         <v>319</v>
       </c>
       <c r="L116" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="42"/>
         <v>'evac_suplente' : r_val['evac_suplente'],</v>
       </c>
     </row>
@@ -40757,7 +41604,7 @@
         <v>590</v>
       </c>
       <c r="L117" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="42"/>
         <v>'supl_evac_pue' : r_val['supl_evac_pue'],</v>
       </c>
     </row>
@@ -40769,7 +41616,7 @@
         <v>690</v>
       </c>
       <c r="L118" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="42"/>
         <v>'m_supl_evac' : r_val['m_supl_evac'],</v>
       </c>
     </row>
@@ -40781,7 +41628,7 @@
         <v>320</v>
       </c>
       <c r="L119" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="42"/>
         <v>'incendios' : r_val['incendios'],</v>
       </c>
     </row>
@@ -40793,7 +41640,7 @@
         <v>591</v>
       </c>
       <c r="L120" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="42"/>
         <v>'incen_puesto' : r_val['incen_puesto'],</v>
       </c>
     </row>
@@ -40805,7 +41652,7 @@
         <v>691</v>
       </c>
       <c r="L121" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="42"/>
         <v>'m_inc' : r_val['m_inc'],</v>
       </c>
     </row>
@@ -40817,7 +41664,7 @@
         <v>321</v>
       </c>
       <c r="L122" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="42"/>
         <v>'inc_suplente' : r_val['inc_suplente'],</v>
       </c>
     </row>
@@ -40829,7 +41676,7 @@
         <v>592</v>
       </c>
       <c r="L123" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="42"/>
         <v>'supl_inc_puesto' : r_val['supl_inc_puesto'],</v>
       </c>
     </row>
@@ -40841,7 +41688,7 @@
         <v>692</v>
       </c>
       <c r="L124" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="42"/>
         <v>'m_supl_inc' : r_val['m_supl_inc'],</v>
       </c>
     </row>
@@ -40853,7 +41700,7 @@
         <v>322</v>
       </c>
       <c r="L125" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="42"/>
         <v>'primeros_auxilios' : r_val['primeros_auxilios'],</v>
       </c>
     </row>
@@ -40865,7 +41712,7 @@
         <v>593</v>
       </c>
       <c r="L126" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="42"/>
         <v>'prim_aux_puesto' : r_val['prim_aux_puesto'],</v>
       </c>
     </row>
@@ -40877,7 +41724,7 @@
         <v>693</v>
       </c>
       <c r="L127" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="42"/>
         <v>'m_prim_aux' : r_val['m_prim_aux'],</v>
       </c>
     </row>
@@ -40889,7 +41736,7 @@
         <v>323</v>
       </c>
       <c r="L128" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="42"/>
         <v>'aux_suplente' : r_val['aux_suplente'],</v>
       </c>
     </row>
@@ -40901,7 +41748,7 @@
         <v>594</v>
       </c>
       <c r="L129" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="42"/>
         <v>'supl_prim_aux_puesto' : r_val['supl_prim_aux_puesto'],</v>
       </c>
     </row>
@@ -40913,7 +41760,7 @@
         <v>694</v>
       </c>
       <c r="L130" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="42"/>
         <v>'m_supl_paux' : r_val['m_supl_paux'],</v>
       </c>
     </row>
@@ -40925,7 +41772,7 @@
         <v>324</v>
       </c>
       <c r="L131" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="42"/>
         <v>'busqueda' : r_val['busqueda'],</v>
       </c>
     </row>
@@ -40937,7 +41784,7 @@
         <v>595</v>
       </c>
       <c r="L132" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="42"/>
         <v>'busq_puesto' : r_val['busq_puesto'],</v>
       </c>
     </row>
@@ -40949,7 +41796,7 @@
         <v>695</v>
       </c>
       <c r="L133" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="42"/>
         <v>'m_busq' : r_val['m_busq'],</v>
       </c>
     </row>
@@ -40961,7 +41808,7 @@
         <v>325</v>
       </c>
       <c r="L134" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="42"/>
         <v>'busq_suplente' : r_val['busq_suplente'],</v>
       </c>
     </row>
@@ -40973,7 +41820,7 @@
         <v>596</v>
       </c>
       <c r="L135" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="42"/>
         <v>'supl_busq_puesto' : r_val['supl_busq_puesto'],</v>
       </c>
     </row>
@@ -40985,7 +41832,7 @@
         <v>696</v>
       </c>
       <c r="L136" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="42"/>
         <v>'m_supl_busq' : r_val['m_supl_busq'],</v>
       </c>
     </row>
@@ -40997,7 +41844,7 @@
         <v>326</v>
       </c>
       <c r="L137" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="42"/>
         <v>'descrip_gi' : r_val['descrip_gi'],</v>
       </c>
     </row>
@@ -41009,7 +41856,7 @@
         <v>327</v>
       </c>
       <c r="L138" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="42"/>
         <v>'gas_inflamable' : r_val['gas_inflamable'],</v>
       </c>
     </row>
@@ -41021,7 +41868,7 @@
         <v>328</v>
       </c>
       <c r="L139" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="42"/>
         <v>'valor_gi' : r_val['valor_gi'],</v>
       </c>
     </row>
@@ -41033,7 +41880,7 @@
         <v>329</v>
       </c>
       <c r="L140" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="42"/>
         <v>'descrp_li' : r_val['descrp_li'],</v>
       </c>
     </row>
@@ -41045,7 +41892,7 @@
         <v>330</v>
       </c>
       <c r="L141" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="42"/>
         <v>'liquido_inflamable' : r_val['liquido_inflamable'],</v>
       </c>
     </row>
@@ -41057,7 +41904,7 @@
         <v>331</v>
       </c>
       <c r="L142" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="42"/>
         <v>'valor_li' : r_val['valor_li'],</v>
       </c>
     </row>
@@ -41069,7 +41916,7 @@
         <v>332</v>
       </c>
       <c r="L143" t="str">
-        <f t="shared" ref="L143:L181" si="34">+_xlfn.CONCAT("'",J143,"' : r_val['",J143,"'],")</f>
+        <f t="shared" ref="L143:L181" si="43">+_xlfn.CONCAT("'",J143,"' : r_val['",J143,"'],")</f>
         <v>'descrip_lc' : r_val['descrip_lc'],</v>
       </c>
     </row>
@@ -41081,7 +41928,7 @@
         <v>333</v>
       </c>
       <c r="L144" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>'liquido_combustible' : r_val['liquido_combustible'],</v>
       </c>
     </row>
@@ -41093,7 +41940,7 @@
         <v>334</v>
       </c>
       <c r="L145" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>'valor_lc' : r_val['valor_lc'],</v>
       </c>
     </row>
@@ -41105,7 +41952,7 @@
         <v>335</v>
       </c>
       <c r="L146" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>'descrip_sc' : r_val['descrip_sc'],</v>
       </c>
     </row>
@@ -41117,7 +41964,7 @@
         <v>336</v>
       </c>
       <c r="L147" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>'solido_combusible' : r_val['solido_combusible'],</v>
       </c>
     </row>
@@ -41129,7 +41976,7 @@
         <v>337</v>
       </c>
       <c r="L148" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>'valor_sc' : r_val['valor_sc'],</v>
       </c>
     </row>
@@ -41141,7 +41988,7 @@
         <v>338</v>
       </c>
       <c r="L149" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>'tipo_riesgo' : r_val['tipo_riesgo'],</v>
       </c>
     </row>
@@ -41153,7 +42000,7 @@
         <v>657</v>
       </c>
       <c r="L150" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>'nombre1' : r_val['nombre1'],</v>
       </c>
     </row>
@@ -41165,7 +42012,7 @@
         <v>658</v>
       </c>
       <c r="L151" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>'puesto1' : r_val['puesto1'],</v>
       </c>
     </row>
@@ -41177,7 +42024,7 @@
         <v>659</v>
       </c>
       <c r="L152" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>'m1' : r_val['m1'],</v>
       </c>
     </row>
@@ -41189,7 +42036,7 @@
         <v>660</v>
       </c>
       <c r="L153" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>'nombre2' : r_val['nombre2'],</v>
       </c>
     </row>
@@ -41201,7 +42048,7 @@
         <v>661</v>
       </c>
       <c r="L154" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>'puesto2' : r_val['puesto2'],</v>
       </c>
     </row>
@@ -41213,7 +42060,7 @@
         <v>662</v>
       </c>
       <c r="L155" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>'m2' : r_val['m2'],</v>
       </c>
     </row>
@@ -41225,7 +42072,7 @@
         <v>663</v>
       </c>
       <c r="L156" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>'nombre3' : r_val['nombre3'],</v>
       </c>
     </row>
@@ -41237,7 +42084,7 @@
         <v>664</v>
       </c>
       <c r="L157" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>'puesto3' : r_val['puesto3'],</v>
       </c>
     </row>
@@ -41249,7 +42096,7 @@
         <v>665</v>
       </c>
       <c r="L158" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>'m3' : r_val['m3'],</v>
       </c>
     </row>
@@ -41261,7 +42108,7 @@
         <v>666</v>
       </c>
       <c r="L159" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>'nombre4' : r_val['nombre4'],</v>
       </c>
     </row>
@@ -41273,7 +42120,7 @@
         <v>667</v>
       </c>
       <c r="L160" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>'puesto4' : r_val['puesto4'],</v>
       </c>
     </row>
@@ -41285,7 +42132,7 @@
         <v>668</v>
       </c>
       <c r="L161" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>'m4' : r_val['m4'],</v>
       </c>
     </row>
@@ -41297,7 +42144,7 @@
         <v>669</v>
       </c>
       <c r="L162" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>'nombre5' : r_val['nombre5'],</v>
       </c>
     </row>
@@ -41309,7 +42156,7 @@
         <v>670</v>
       </c>
       <c r="L163" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>'puesto5' : r_val['puesto5'],</v>
       </c>
     </row>
@@ -41321,7 +42168,7 @@
         <v>671</v>
       </c>
       <c r="L164" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>'m5' : r_val['m5'],</v>
       </c>
     </row>
@@ -41333,7 +42180,7 @@
         <v>672</v>
       </c>
       <c r="L165" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>'nombre6' : r_val['nombre6'],</v>
       </c>
     </row>
@@ -41345,7 +42192,7 @@
         <v>673</v>
       </c>
       <c r="L166" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>'puesto6' : r_val['puesto6'],</v>
       </c>
     </row>
@@ -41357,7 +42204,7 @@
         <v>674</v>
       </c>
       <c r="L167" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>'m6' : r_val['m6'],</v>
       </c>
     </row>
@@ -41369,7 +42216,7 @@
         <v>675</v>
       </c>
       <c r="L168" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>'nombre7' : r_val['nombre7'],</v>
       </c>
     </row>
@@ -41381,7 +42228,7 @@
         <v>676</v>
       </c>
       <c r="L169" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>'puesto7' : r_val['puesto7'],</v>
       </c>
     </row>
@@ -41393,7 +42240,7 @@
         <v>677</v>
       </c>
       <c r="L170" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>'m7' : r_val['m7'],</v>
       </c>
     </row>
@@ -41405,7 +42252,7 @@
         <v>678</v>
       </c>
       <c r="L171" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>'nombre8' : r_val['nombre8'],</v>
       </c>
     </row>
@@ -41417,7 +42264,7 @@
         <v>679</v>
       </c>
       <c r="L172" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>'puesto8' : r_val['puesto8'],</v>
       </c>
     </row>
@@ -41429,7 +42276,7 @@
         <v>680</v>
       </c>
       <c r="L173" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>'m8' : r_val['m8'],</v>
       </c>
     </row>
@@ -41441,7 +42288,7 @@
         <v>681</v>
       </c>
       <c r="L174" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>'nombre9' : r_val['nombre9'],</v>
       </c>
     </row>
@@ -41453,7 +42300,7 @@
         <v>682</v>
       </c>
       <c r="L175" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>'puesto9' : r_val['puesto9'],</v>
       </c>
     </row>
@@ -41465,7 +42312,7 @@
         <v>683</v>
       </c>
       <c r="L176" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>'m9' : r_val['m9'],</v>
       </c>
     </row>
@@ -41477,7 +42324,7 @@
         <v>684</v>
       </c>
       <c r="L177" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>'nombre10' : r_val['nombre10'],</v>
       </c>
     </row>
@@ -41489,7 +42336,7 @@
         <v>685</v>
       </c>
       <c r="L178" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>'puesto10' : r_val['puesto10'],</v>
       </c>
     </row>
@@ -41501,7 +42348,7 @@
         <v>686</v>
       </c>
       <c r="L179" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>'m10' : r_val['m10'],</v>
       </c>
     </row>
@@ -41514,7 +42361,7 @@
         <v>{{ registro_perito }}</v>
       </c>
       <c r="L180" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>'registro_perito' : r_val['registro_perito'],</v>
       </c>
     </row>
@@ -41527,7 +42374,7 @@
         <v>{{ no_registro }}</v>
       </c>
       <c r="L181" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>'no_registro' : r_val['no_registro'],</v>
       </c>
     </row>
@@ -41536,11 +42383,11 @@
         <v>1735</v>
       </c>
       <c r="K182" t="str">
-        <f t="shared" ref="K182:K183" si="35">+_xlfn.CONCAT("{{ ",J182," }}")</f>
+        <f t="shared" ref="K182:K183" si="44">+_xlfn.CONCAT("{{ ",J182," }}")</f>
         <v>{{ dh_int }}</v>
       </c>
       <c r="L182" t="str">
-        <f t="shared" ref="L182:L183" si="36">+_xlfn.CONCAT("'",J182,"' : r_val['",J182,"'],")</f>
+        <f t="shared" ref="L182:L183" si="45">+_xlfn.CONCAT("'",J182,"' : r_val['",J182,"'],")</f>
         <v>'dh_int' : r_val['dh_int'],</v>
       </c>
     </row>
@@ -41549,11 +42396,11 @@
         <v>1736</v>
       </c>
       <c r="K183" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="44"/>
         <v>{{ dh_ext }}</v>
       </c>
       <c r="L183" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="45"/>
         <v>'dh_ext' : r_val['dh_ext'],</v>
       </c>
     </row>
@@ -41562,11 +42409,11 @@
         <v>1737</v>
       </c>
       <c r="K184" t="str">
-        <f t="shared" ref="K184" si="37">+_xlfn.CONCAT("{{ ",J184," }}")</f>
+        <f t="shared" ref="K184" si="46">+_xlfn.CONCAT("{{ ",J184," }}")</f>
         <v>{{ detectores_ext }}</v>
       </c>
       <c r="L184" t="str">
-        <f t="shared" ref="L184" si="38">+_xlfn.CONCAT("'",J184,"' : r_val['",J184,"'],")</f>
+        <f t="shared" ref="L184" si="47">+_xlfn.CONCAT("'",J184,"' : r_val['",J184,"'],")</f>
         <v>'detectores_ext' : r_val['detectores_ext'],</v>
       </c>
     </row>
@@ -41575,11 +42422,11 @@
         <v>1738</v>
       </c>
       <c r="K185" t="str">
-        <f t="shared" ref="K185" si="39">+_xlfn.CONCAT("{{ ",J185," }}")</f>
+        <f t="shared" ref="K185" si="48">+_xlfn.CONCAT("{{ ",J185," }}")</f>
         <v>{{ coord_sup_puesto }}</v>
       </c>
       <c r="L185" t="str">
-        <f t="shared" ref="L185" si="40">+_xlfn.CONCAT("'",J185,"' : r_val['",J185,"'],")</f>
+        <f t="shared" ref="L185" si="49">+_xlfn.CONCAT("'",J185,"' : r_val['",J185,"'],")</f>
         <v>'coord_sup_puesto' : r_val['coord_sup_puesto'],</v>
       </c>
     </row>
@@ -41588,11 +42435,11 @@
         <v>1744</v>
       </c>
       <c r="K186" t="str">
-        <f t="shared" ref="K186:K189" si="41">+_xlfn.CONCAT("{{ ",J186," }}")</f>
+        <f t="shared" ref="K186:K189" si="50">+_xlfn.CONCAT("{{ ",J186," }}")</f>
         <v>{{ riesgo1 }}</v>
       </c>
       <c r="L186" t="str">
-        <f t="shared" ref="L186:L189" si="42">+_xlfn.CONCAT("'",J186,"' : r_val['",J186,"'],")</f>
+        <f t="shared" ref="L186:L189" si="51">+_xlfn.CONCAT("'",J186,"' : r_val['",J186,"'],")</f>
         <v>'riesgo1' : r_val['riesgo1'],</v>
       </c>
     </row>
@@ -41601,11 +42448,11 @@
         <v>1745</v>
       </c>
       <c r="K187" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="50"/>
         <v>{{ riesgo2 }}</v>
       </c>
       <c r="L187" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="51"/>
         <v>'riesgo2' : r_val['riesgo2'],</v>
       </c>
     </row>
@@ -41614,11 +42461,11 @@
         <v>1746</v>
       </c>
       <c r="K188" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="50"/>
         <v>{{ riesgo3 }}</v>
       </c>
       <c r="L188" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="51"/>
         <v>'riesgo3' : r_val['riesgo3'],</v>
       </c>
     </row>
@@ -41627,11 +42474,11 @@
         <v>1747</v>
       </c>
       <c r="K189" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="50"/>
         <v>{{ riesgo4 }}</v>
       </c>
       <c r="L189" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="51"/>
         <v>'riesgo4' : r_val['riesgo4'],</v>
       </c>
     </row>
@@ -41640,11 +42487,11 @@
         <v>1751</v>
       </c>
       <c r="K190" t="str">
-        <f t="shared" ref="K190" si="43">+_xlfn.CONCAT("{{ ",J190," }}")</f>
+        <f t="shared" ref="K190" si="52">+_xlfn.CONCAT("{{ ",J190," }}")</f>
         <v>{{ valor_gri }}</v>
       </c>
       <c r="L190" t="str">
-        <f t="shared" ref="L190" si="44">+_xlfn.CONCAT("'",J190,"' : r_val['",J190,"'],")</f>
+        <f t="shared" ref="L190" si="53">+_xlfn.CONCAT("'",J190,"' : r_val['",J190,"'],")</f>
         <v>'valor_gri' : r_val['valor_gri'],</v>
       </c>
     </row>
@@ -41653,11 +42500,11 @@
         <v>1752</v>
       </c>
       <c r="K191" t="str">
-        <f t="shared" ref="K191:K194" si="45">+_xlfn.CONCAT("{{ ",J191," }}")</f>
+        <f t="shared" ref="K191:K194" si="54">+_xlfn.CONCAT("{{ ",J191," }}")</f>
         <v>{{ medidas_ries1 }}</v>
       </c>
       <c r="L191" t="str">
-        <f t="shared" ref="L191:L194" si="46">+_xlfn.CONCAT("'",J191,"' : r_val['",J191,"'],")</f>
+        <f t="shared" ref="L191:L194" si="55">+_xlfn.CONCAT("'",J191,"' : r_val['",J191,"'],")</f>
         <v>'medidas_ries1' : r_val['medidas_ries1'],</v>
       </c>
     </row>
@@ -41666,11 +42513,11 @@
         <v>1753</v>
       </c>
       <c r="K192" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="54"/>
         <v>{{ medidas_ries2 }}</v>
       </c>
       <c r="L192" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="55"/>
         <v>'medidas_ries2' : r_val['medidas_ries2'],</v>
       </c>
     </row>
@@ -41679,11 +42526,11 @@
         <v>1754</v>
       </c>
       <c r="K193" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="54"/>
         <v>{{ medidas_ries3 }}</v>
       </c>
       <c r="L193" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="55"/>
         <v>'medidas_ries3' : r_val['medidas_ries3'],</v>
       </c>
     </row>
@@ -41692,11 +42539,11 @@
         <v>1755</v>
       </c>
       <c r="K194" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="54"/>
         <v>{{ medidas_ries4 }}</v>
       </c>
       <c r="L194" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="55"/>
         <v>'medidas_ries4' : r_val['medidas_ries4'],</v>
       </c>
     </row>

--- a/Inputs/BD.xlsx
+++ b/Inputs/BD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/078e1a455e5c02ce/Documentos/GitHub/Proyecto_PIPC/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4828" documentId="13_ncr:1_{7D3A426E-EC5E-453A-8CC7-F83B71F24F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B66DF82-9828-4BF5-9291-7D324BBD001A}"/>
+  <xr:revisionPtr revIDLastSave="5297" documentId="13_ncr:1_{7D3A426E-EC5E-453A-8CC7-F83B71F24F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4454FD2-C819-4AC3-96D0-A118F591D333}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3F095A75-F066-4695-8672-8D4315F1EF23}"/>
   </bookViews>
@@ -563,7 +563,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6291" uniqueCount="1899">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6523" uniqueCount="2000">
   <si>
     <t>dia</t>
   </si>
@@ -6260,6 +6260,309 @@
   </si>
   <si>
     <t>AL INTERIOR DE CORPORATIVO ZAVALETA, PISO</t>
+  </si>
+  <si>
+    <t>General</t>
+  </si>
+  <si>
+    <t>ROSTICERIA BASE POLLO Y MAS</t>
+  </si>
+  <si>
+    <t>ROHA8501212G1</t>
+  </si>
+  <si>
+    <t>POLLERIA, ROSTICERIA Y AHUMADOS</t>
+  </si>
+  <si>
+    <t>PREPARACIÓN DE POLLO MEDIANTE UN MÉTODO DE COCCIÓN TRADICIONAL UTILIZANDO LEÑA COMO COMBUSTIBLE</t>
+  </si>
+  <si>
+    <t>BULEVAR MUNICIPIO LIBRE</t>
+  </si>
+  <si>
+    <t>UNIVERSIDAD</t>
+  </si>
+  <si>
+    <t>222 193 3374</t>
+  </si>
+  <si>
+    <t>anabel_ronquilloh@gmail.com</t>
+  </si>
+  <si>
+    <t>27 DE FEBRERO DE 2024</t>
+  </si>
+  <si>
+    <t>7 CAJONES</t>
+  </si>
+  <si>
+    <t>LUNES - SABADO</t>
+  </si>
+  <si>
+    <t>10:00 A 18:00 HORAS</t>
+  </si>
+  <si>
+    <t>COCINA</t>
+  </si>
+  <si>
+    <t>COCINA Y COMEDOR</t>
+  </si>
+  <si>
+    <t>SILBATO</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <t>18°59'41.8"N 98°11'55.6"W</t>
+  </si>
+  <si>
+    <t>MUEBLERA</t>
+  </si>
+  <si>
+    <t>LUIS ALBERTO MARUH OJEDA</t>
+  </si>
+  <si>
+    <t>ELIONAI VELAZQUEZ MARTINEZ</t>
+  </si>
+  <si>
+    <t>CARLOS ALBERTO RONQUILLO HERRERA</t>
+  </si>
+  <si>
+    <t>MA. DE LOURDES HERRERA REYES</t>
+  </si>
+  <si>
+    <t>MOBILIARIO Y LEÑA</t>
+  </si>
+  <si>
+    <t>ANABEL GUADALUPE RONQUILLO HERRERA</t>
+  </si>
+  <si>
+    <t>HIDRO TRATAMIENTOS DE TEPEACA SA DE CV</t>
+  </si>
+  <si>
+    <t>COPO DE HIELO</t>
+  </si>
+  <si>
+    <t>HTT950327UN8</t>
+  </si>
+  <si>
+    <t>FRABRICACION Y VENTA DE HIELO</t>
+  </si>
+  <si>
+    <t>PRODUCIR, ALMACENAR Y DISTRIBUIR HIELO EN DIFERENTES PRESENTACIONES, ASEGURANDO LA CALIDAD DEL AGUA, EL PROCESO DE CONGELACIÓN Y EL CUMPLIMIENTO DE NORMATIVAS SANITARIAS Y DE DISTRIBUCIÓN.</t>
+  </si>
+  <si>
+    <t>3 ORIENTE</t>
+  </si>
+  <si>
+    <t>TEHUACAN</t>
+  </si>
+  <si>
+    <t>hidrotepeacafacturas@hotmail.com</t>
+  </si>
+  <si>
+    <t>27 DE MARZO DE 1979</t>
+  </si>
+  <si>
+    <t>8 CAJONES</t>
+  </si>
+  <si>
+    <t>LUCINA ORTIZ ROSAINTS</t>
+  </si>
+  <si>
+    <t>7:00 A 17:00 HORAS</t>
+  </si>
+  <si>
+    <t>OFICINA Y PRODUCCION</t>
+  </si>
+  <si>
+    <t>18.963423523409002, -97.90123975508969</t>
+  </si>
+  <si>
+    <t>MARIA EUGENIA ROSSAINZ TORRES</t>
+  </si>
+  <si>
+    <t>MOISES ARRAYALA JUAREZ</t>
+  </si>
+  <si>
+    <t>LEONARDO HUERTA CASTILLO</t>
+  </si>
+  <si>
+    <t>JUAN APOLINAR RAMIREZ CARREON</t>
+  </si>
+  <si>
+    <t>ABEL RAMIREZ CARREON</t>
+  </si>
+  <si>
+    <t>AMONIACO</t>
+  </si>
+  <si>
+    <t>SUPRACARE SA DE CV</t>
+  </si>
+  <si>
+    <t>FRAICHE</t>
+  </si>
+  <si>
+    <t>SUP200818IP0</t>
+  </si>
+  <si>
+    <t>VENTA AL POR MENOR DE PERFUMES, ESENCIAS Y ARTICULOS DE HIGIENE</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>pitavallejacarrera0205@gmail.com</t>
+  </si>
+  <si>
+    <t>11 DE ENERO DE 1995</t>
+  </si>
+  <si>
+    <t>VERONICA ANDRADE GARCIA</t>
+  </si>
+  <si>
+    <t>GUADALUPE VALLEJO CARRERA</t>
+  </si>
+  <si>
+    <t>CAJA Y BODEGA</t>
+  </si>
+  <si>
+    <t>BODEGA</t>
+  </si>
+  <si>
+    <t>BODEGA Y CLIENTES</t>
+  </si>
+  <si>
+    <t>18.46083231100189, -97.3917459340405</t>
+  </si>
+  <si>
+    <t>MERCERIA Y PAPELERIA</t>
+  </si>
+  <si>
+    <t>EDIFICIO GAUDALUPE</t>
+  </si>
+  <si>
+    <t>FERRETERIA</t>
+  </si>
+  <si>
+    <t>MAYRA LIZBETH ANGEL PEREZ</t>
+  </si>
+  <si>
+    <t>MARIA DEL SOCORRO CRUZ HERNANDEZ</t>
+  </si>
+  <si>
+    <t>PALMIRA BERENICEESPORRAGOZA CORTES</t>
+  </si>
+  <si>
+    <t>ERIBERTO ANSELMO SANCHEZ</t>
+  </si>
+  <si>
+    <t>JACQUELINES MONTIEL SALAZAR</t>
+  </si>
+  <si>
+    <t>SERGIO MENDOZA CID</t>
+  </si>
+  <si>
+    <t>MONICA LOPEZ HERRARA</t>
+  </si>
+  <si>
+    <t>PERFUMON Y FIJADOR</t>
+  </si>
+  <si>
+    <t>SE OFRECE UNA AMPLIA VARIEDAD DE FRAGANCIAS Y PRODUCTOS, COMO COSMÉTICOS Y PRODUCTOS PARA EL CUIDADO PERSONAL, BRINDANDO ASESORAMIENTO, PROMOCIONES, Y SERVICIOS DE PRUEBA Y PERSONALIZACIÓN DE FRAGANCIAS</t>
+  </si>
+  <si>
+    <t>10:30 A 19:30 HORAS</t>
+  </si>
+  <si>
+    <t>colindancias</t>
+  </si>
+  <si>
+    <t>BANCO COMPARTAMOS S.A INSTITUCION DE BANCA MULTIPLE</t>
+  </si>
+  <si>
+    <t>SUCURSAL SALINA CRUZ</t>
+  </si>
+  <si>
+    <t>BCI001030ECA</t>
+  </si>
+  <si>
+    <t>SERVICIOS FINANCIEROS</t>
+  </si>
+  <si>
+    <t>AV. TAMPICO</t>
+  </si>
+  <si>
+    <t>SALINA CRUZ</t>
+  </si>
+  <si>
+    <t>OAXACA</t>
+  </si>
+  <si>
+    <t>971 720 2793</t>
+  </si>
+  <si>
+    <t>CONCEPCION GUERRERO GARCIA</t>
+  </si>
+  <si>
+    <t>JUAN CARLOS MARTINEZ OROZCO</t>
+  </si>
+  <si>
+    <t>08:00 A 17:00 HORAS</t>
+  </si>
+  <si>
+    <t>CALLE MANZANILLO, CALLE PROGRESO, AV. MANUAL AVILA CAMACHO, AV. TAMPICO</t>
+  </si>
+  <si>
+    <t>16.179683242805982, -95.19539195628619</t>
+  </si>
+  <si>
+    <t>HOTEL, RESTAURANTE DINASTIA, FARMACIA SIMILAR</t>
+  </si>
+  <si>
+    <t>INSTITUTO DE EDUCACION NAUTICO, RESTAURANTE CANTON.</t>
+  </si>
+  <si>
+    <t>MISCELANEA YOYIS, LAS DELICIAS CREPAS, RASPADOS RASS.</t>
+  </si>
+  <si>
+    <t>TERMINAL ALTAMAR, LABORATORIO, MODELO PLUS, INBURSA</t>
+  </si>
+  <si>
+    <t>CONTRA ESQUINA DE LA FARMACIA SIMILARES.</t>
+  </si>
+  <si>
+    <t>SUCURSAL TEHUANTEPEC</t>
+  </si>
+  <si>
+    <t>CALLE CRISTOBAL COLON</t>
+  </si>
+  <si>
+    <t>BARRIO SAN JERONIMO</t>
+  </si>
+  <si>
+    <t>SANTO DOMINGO TEHUANTEPEC</t>
+  </si>
+  <si>
+    <t>SUCURSAL JUCHITAN DE ZARAGOZA</t>
+  </si>
+  <si>
+    <t>CALLE 2 DE ABRIL</t>
+  </si>
+  <si>
+    <t>3 SECCION</t>
+  </si>
+  <si>
+    <t>JUCHITAN DE ZARAGOZA</t>
+  </si>
+  <si>
+    <t>SUCURSAL MATIAS ROMERO CEMENTERA</t>
+  </si>
+  <si>
+    <t>CORREGIDORA SUR</t>
+  </si>
+  <si>
+    <t>MATIAS ROMERO AVEDAÑO</t>
   </si>
 </sst>
 </file>
@@ -6345,7 +6648,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6370,6 +6673,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -6384,7 +6693,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -6397,6 +6706,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -6873,7 +7185,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="26" fmlaLink="$A$1" max="30000" min="1" page="10" val="23"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="26" fmlaLink="$A$1" max="30000" min="1" page="10" val="48"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6929,10 +7241,6 @@
     <mc:Fallback/>
   </mc:AlternateContent>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7254,10 +7562,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE6A0106-4EDF-4D58-B8A9-1C9CC54D9FE0}">
   <dimension ref="A1:KT201"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="123" max="123" width="11.5546875" style="11"/>
+    <col min="126" max="126" width="11.5546875" style="11"/>
+    <col min="129" max="129" width="11.5546875" style="11"/>
+    <col min="132" max="132" width="11.5546875" style="11"/>
+    <col min="135" max="135" width="11.5546875" style="11"/>
+    <col min="138" max="138" width="11.5546875" style="11"/>
+    <col min="141" max="141" width="11.5546875" style="11"/>
+    <col min="144" max="144" width="11.5546875" style="11"/>
+    <col min="147" max="147" width="11.5546875" style="11"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:306" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2">
-        <v>23</v>
+        <v>48</v>
+      </c>
+      <c r="DC1" t="s">
+        <v>1970</v>
       </c>
     </row>
     <row r="2" spans="1:306" x14ac:dyDescent="0.3">
@@ -7627,7 +7949,7 @@
       <c r="DR2" t="s">
         <v>647</v>
       </c>
-      <c r="DS2" t="s">
+      <c r="DS2" s="11" t="s">
         <v>202</v>
       </c>
       <c r="DT2" t="s">
@@ -7636,7 +7958,7 @@
       <c r="DU2" t="s">
         <v>648</v>
       </c>
-      <c r="DV2" t="s">
+      <c r="DV2" s="11" t="s">
         <v>203</v>
       </c>
       <c r="DW2" t="s">
@@ -7645,7 +7967,7 @@
       <c r="DX2" t="s">
         <v>649</v>
       </c>
-      <c r="DY2" t="s">
+      <c r="DY2" s="11" t="s">
         <v>204</v>
       </c>
       <c r="DZ2" t="s">
@@ -7654,7 +7976,7 @@
       <c r="EA2" t="s">
         <v>650</v>
       </c>
-      <c r="EB2" t="s">
+      <c r="EB2" s="11" t="s">
         <v>205</v>
       </c>
       <c r="EC2" t="s">
@@ -7663,7 +7985,7 @@
       <c r="ED2" t="s">
         <v>651</v>
       </c>
-      <c r="EE2" t="s">
+      <c r="EE2" s="11" t="s">
         <v>206</v>
       </c>
       <c r="EF2" t="s">
@@ -7672,7 +7994,7 @@
       <c r="EG2" t="s">
         <v>652</v>
       </c>
-      <c r="EH2" t="s">
+      <c r="EH2" s="11" t="s">
         <v>207</v>
       </c>
       <c r="EI2" t="s">
@@ -7681,7 +8003,7 @@
       <c r="EJ2" t="s">
         <v>653</v>
       </c>
-      <c r="EK2" t="s">
+      <c r="EK2" s="11" t="s">
         <v>208</v>
       </c>
       <c r="EL2" t="s">
@@ -7690,7 +8012,7 @@
       <c r="EM2" t="s">
         <v>654</v>
       </c>
-      <c r="EN2" t="s">
+      <c r="EN2" s="11" t="s">
         <v>209</v>
       </c>
       <c r="EO2" t="s">
@@ -7699,7 +8021,7 @@
       <c r="EP2" t="s">
         <v>655</v>
       </c>
-      <c r="EQ2" t="s">
+      <c r="EQ2" s="11" t="s">
         <v>210</v>
       </c>
       <c r="ER2" t="s">
@@ -8390,31 +8712,31 @@
       <c r="DQ3" t="s">
         <v>443</v>
       </c>
-      <c r="DS3" t="s">
+      <c r="DS3" s="11" t="s">
         <v>444</v>
       </c>
-      <c r="DV3" t="s">
+      <c r="DV3" s="11" t="s">
         <v>445</v>
       </c>
-      <c r="DY3" t="s">
+      <c r="DY3" s="11" t="s">
         <v>446</v>
       </c>
-      <c r="EB3" t="s">
+      <c r="EB3" s="11" t="s">
         <v>447</v>
       </c>
-      <c r="EE3" t="s">
+      <c r="EE3" s="11" t="s">
         <v>448</v>
       </c>
-      <c r="EH3" t="s">
+      <c r="EH3" s="11" t="s">
         <v>449</v>
       </c>
-      <c r="EK3" t="s">
+      <c r="EK3" s="11" t="s">
         <v>450</v>
       </c>
-      <c r="EN3" t="s">
+      <c r="EN3" s="11" t="s">
         <v>451</v>
       </c>
-      <c r="EQ3" t="s">
+      <c r="EQ3" s="11" t="s">
         <v>452</v>
       </c>
       <c r="EU3">
@@ -8673,31 +8995,31 @@
       <c r="DQ4" t="s">
         <v>443</v>
       </c>
-      <c r="DS4" t="s">
+      <c r="DS4" s="11" t="s">
         <v>472</v>
       </c>
-      <c r="DV4" t="s">
+      <c r="DV4" s="11" t="s">
         <v>473</v>
       </c>
-      <c r="DY4" t="s">
+      <c r="DY4" s="11" t="s">
         <v>474</v>
       </c>
-      <c r="EB4" t="s">
+      <c r="EB4" s="11" t="s">
         <v>475</v>
       </c>
-      <c r="EE4" t="s">
+      <c r="EE4" s="11" t="s">
         <v>476</v>
       </c>
-      <c r="EH4" t="s">
+      <c r="EH4" s="11" t="s">
         <v>477</v>
       </c>
-      <c r="EK4" t="s">
+      <c r="EK4" s="11" t="s">
         <v>478</v>
       </c>
-      <c r="EN4" t="s">
+      <c r="EN4" s="11" t="s">
         <v>479</v>
       </c>
-      <c r="EQ4" t="s">
+      <c r="EQ4" s="11" t="s">
         <v>480</v>
       </c>
       <c r="EU4">
@@ -8950,31 +9272,31 @@
       <c r="DQ5" t="s">
         <v>443</v>
       </c>
-      <c r="DS5" t="s">
+      <c r="DS5" s="11" t="s">
         <v>489</v>
       </c>
-      <c r="DV5" t="s">
+      <c r="DV5" s="11" t="s">
         <v>490</v>
       </c>
-      <c r="DY5" t="s">
+      <c r="DY5" s="11" t="s">
         <v>491</v>
       </c>
-      <c r="EB5" t="s">
+      <c r="EB5" s="11" t="s">
         <v>492</v>
       </c>
-      <c r="EE5" t="s">
+      <c r="EE5" s="11" t="s">
         <v>493</v>
       </c>
-      <c r="EH5" t="s">
+      <c r="EH5" s="11" t="s">
         <v>494</v>
       </c>
-      <c r="EK5" t="s">
+      <c r="EK5" s="11" t="s">
         <v>495</v>
       </c>
-      <c r="EN5" t="s">
+      <c r="EN5" s="11" t="s">
         <v>496</v>
       </c>
-      <c r="EQ5" t="s">
+      <c r="EQ5" s="11" t="s">
         <v>497</v>
       </c>
       <c r="EU5">
@@ -9233,31 +9555,31 @@
       <c r="DQ6" t="s">
         <v>443</v>
       </c>
-      <c r="DS6" t="s">
+      <c r="DS6" s="11" t="s">
         <v>513</v>
       </c>
-      <c r="DV6" t="s">
+      <c r="DV6" s="11" t="s">
         <v>514</v>
       </c>
-      <c r="DY6" t="s">
+      <c r="DY6" s="11" t="s">
         <v>515</v>
       </c>
-      <c r="EB6" t="s">
+      <c r="EB6" s="11" t="s">
         <v>516</v>
       </c>
-      <c r="EE6" t="s">
+      <c r="EE6" s="11" t="s">
         <v>517</v>
       </c>
-      <c r="EH6" t="s">
+      <c r="EH6" s="11" t="s">
         <v>518</v>
       </c>
-      <c r="EK6" t="s">
+      <c r="EK6" s="11" t="s">
         <v>519</v>
       </c>
-      <c r="EN6" t="s">
+      <c r="EN6" s="11" t="s">
         <v>520</v>
       </c>
-      <c r="EQ6" t="s">
+      <c r="EQ6" s="11" t="s">
         <v>521</v>
       </c>
       <c r="EU6">
@@ -9507,31 +9829,31 @@
       <c r="DQ7" t="s">
         <v>443</v>
       </c>
-      <c r="DS7" t="s">
+      <c r="DS7" s="11" t="s">
         <v>543</v>
       </c>
-      <c r="DV7" t="s">
+      <c r="DV7" s="11" t="s">
         <v>544</v>
       </c>
-      <c r="DY7" t="s">
+      <c r="DY7" s="11" t="s">
         <v>545</v>
       </c>
-      <c r="EB7" t="s">
+      <c r="EB7" s="11" t="s">
         <v>546</v>
       </c>
-      <c r="EE7" t="s">
+      <c r="EE7" s="11" t="s">
         <v>547</v>
       </c>
-      <c r="EH7" t="s">
+      <c r="EH7" s="11" t="s">
         <v>548</v>
       </c>
-      <c r="EK7" t="s">
+      <c r="EK7" s="11" t="s">
         <v>549</v>
       </c>
-      <c r="EN7" t="s">
+      <c r="EN7" s="11" t="s">
         <v>550</v>
       </c>
-      <c r="EQ7" t="s">
+      <c r="EQ7" s="11" t="s">
         <v>551</v>
       </c>
       <c r="EU7">
@@ -9823,19 +10145,19 @@
       <c r="DQ8" t="s">
         <v>443</v>
       </c>
-      <c r="DS8" t="s">
+      <c r="DS8" s="11" t="s">
         <v>1653</v>
       </c>
-      <c r="DV8" t="s">
+      <c r="DV8" s="11" t="s">
         <v>1654</v>
       </c>
-      <c r="EB8" t="s">
+      <c r="EB8" s="11" t="s">
         <v>1655</v>
       </c>
-      <c r="EH8" t="s">
+      <c r="EH8" s="11" t="s">
         <v>1656</v>
       </c>
-      <c r="EN8" t="s">
+      <c r="EN8" s="11" t="s">
         <v>1657</v>
       </c>
       <c r="EU8">
@@ -10115,10 +10437,10 @@
       <c r="DQ9" t="s">
         <v>443</v>
       </c>
-      <c r="DS9" t="s">
+      <c r="DS9" s="11" t="s">
         <v>782</v>
       </c>
-      <c r="EH9" t="s">
+      <c r="EH9" s="11" t="s">
         <v>783</v>
       </c>
       <c r="EU9">
@@ -10410,28 +10732,28 @@
       <c r="DQ10" t="s">
         <v>443</v>
       </c>
-      <c r="DS10" t="s">
+      <c r="DS10" s="11" t="s">
         <v>798</v>
       </c>
-      <c r="DV10" t="s">
+      <c r="DV10" s="11" t="s">
         <v>799</v>
       </c>
-      <c r="DY10" t="s">
+      <c r="DY10" s="11" t="s">
         <v>800</v>
       </c>
-      <c r="EB10" t="s">
+      <c r="EB10" s="11" t="s">
         <v>801</v>
       </c>
-      <c r="EE10" t="s">
+      <c r="EE10" s="11" t="s">
         <v>802</v>
       </c>
-      <c r="EH10" t="s">
+      <c r="EH10" s="11" t="s">
         <v>803</v>
       </c>
-      <c r="EK10" t="s">
+      <c r="EK10" s="11" t="s">
         <v>804</v>
       </c>
-      <c r="EN10" t="s">
+      <c r="EN10" s="11" t="s">
         <v>841</v>
       </c>
       <c r="EU10">
@@ -10726,31 +11048,31 @@
       <c r="DQ11" t="s">
         <v>443</v>
       </c>
-      <c r="DS11" t="s">
+      <c r="DS11" s="11" t="s">
         <v>1664</v>
       </c>
-      <c r="DV11" t="s">
+      <c r="DV11" s="11" t="s">
         <v>1665</v>
       </c>
-      <c r="DY11" t="s">
+      <c r="DY11" s="11" t="s">
         <v>1666</v>
       </c>
-      <c r="EB11" t="s">
+      <c r="EB11" s="11" t="s">
         <v>1667</v>
       </c>
-      <c r="EE11" t="s">
+      <c r="EE11" s="11" t="s">
         <v>1668</v>
       </c>
-      <c r="EH11" t="s">
+      <c r="EH11" s="11" t="s">
         <v>1669</v>
       </c>
-      <c r="EK11" t="s">
+      <c r="EK11" s="11" t="s">
         <v>1670</v>
       </c>
-      <c r="EN11" t="s">
+      <c r="EN11" s="11" t="s">
         <v>1671</v>
       </c>
-      <c r="EQ11" t="s">
+      <c r="EQ11" s="11" t="s">
         <v>1672</v>
       </c>
       <c r="ET11" t="s">
@@ -11042,19 +11364,19 @@
       <c r="DQ12" t="s">
         <v>443</v>
       </c>
-      <c r="DS12" t="s">
+      <c r="DS12" s="11" t="s">
         <v>1702</v>
       </c>
-      <c r="DV12" t="s">
+      <c r="DV12" s="11" t="s">
         <v>1703</v>
       </c>
-      <c r="EB12" t="s">
+      <c r="EB12" s="11" t="s">
         <v>1704</v>
       </c>
-      <c r="EH12" t="s">
+      <c r="EH12" s="11" t="s">
         <v>1705</v>
       </c>
-      <c r="EN12" t="s">
+      <c r="EN12" s="11" t="s">
         <v>1706</v>
       </c>
       <c r="EU12">
@@ -11328,31 +11650,31 @@
       <c r="DQ13" t="s">
         <v>443</v>
       </c>
-      <c r="DS13" t="s">
+      <c r="DS13" s="11" t="s">
         <v>1684</v>
       </c>
-      <c r="DV13" t="s">
+      <c r="DV13" s="11" t="s">
         <v>1685</v>
       </c>
-      <c r="DY13" t="s">
+      <c r="DY13" s="11" t="s">
         <v>1686</v>
       </c>
-      <c r="EB13" t="s">
+      <c r="EB13" s="11" t="s">
         <v>1687</v>
       </c>
-      <c r="EE13" t="s">
+      <c r="EE13" s="11" t="s">
         <v>1688</v>
       </c>
-      <c r="EH13" t="s">
+      <c r="EH13" s="11" t="s">
         <v>1689</v>
       </c>
-      <c r="EK13" t="s">
+      <c r="EK13" s="11" t="s">
         <v>1690</v>
       </c>
-      <c r="EN13" t="s">
+      <c r="EN13" s="11" t="s">
         <v>1691</v>
       </c>
-      <c r="EQ13" t="s">
+      <c r="EQ13" s="11" t="s">
         <v>1692</v>
       </c>
       <c r="EU13">
@@ -11608,7 +11930,7 @@
       <c r="DR14" t="s">
         <v>1092</v>
       </c>
-      <c r="DS14" t="s">
+      <c r="DS14" s="11" t="s">
         <v>1093</v>
       </c>
       <c r="DT14" t="s">
@@ -11617,37 +11939,37 @@
       <c r="DU14" t="s">
         <v>1094</v>
       </c>
-      <c r="DV14" t="s">
+      <c r="DV14" s="11" t="s">
         <v>1095</v>
       </c>
       <c r="DX14" t="s">
         <v>1096</v>
       </c>
-      <c r="DY14" t="s">
+      <c r="DY14" s="11" t="s">
         <v>1097</v>
       </c>
       <c r="EA14" t="s">
         <v>1098</v>
       </c>
-      <c r="EB14" t="s">
+      <c r="EB14" s="11" t="s">
         <v>1099</v>
       </c>
       <c r="ED14" t="s">
         <v>1100</v>
       </c>
-      <c r="EE14" t="s">
+      <c r="EE14" s="11" t="s">
         <v>1101</v>
       </c>
       <c r="EG14" t="s">
         <v>1102</v>
       </c>
-      <c r="EH14" t="s">
+      <c r="EH14" s="11" t="s">
         <v>1103</v>
       </c>
       <c r="EJ14" t="s">
         <v>1104</v>
       </c>
-      <c r="EK14" t="s">
+      <c r="EK14" s="11" t="s">
         <v>1105</v>
       </c>
       <c r="EM14" t="s">
@@ -12094,7 +12416,7 @@
       <c r="DR15" t="s">
         <v>914</v>
       </c>
-      <c r="DS15" t="s">
+      <c r="DS15" s="11" t="s">
         <v>915</v>
       </c>
       <c r="DT15" t="s">
@@ -12103,7 +12425,7 @@
       <c r="DU15" t="s">
         <v>916</v>
       </c>
-      <c r="DV15" t="s">
+      <c r="DV15" s="11" t="s">
         <v>917</v>
       </c>
       <c r="DW15" t="s">
@@ -12112,7 +12434,7 @@
       <c r="DX15" t="s">
         <v>918</v>
       </c>
-      <c r="DY15" t="s">
+      <c r="DY15" s="11" t="s">
         <v>919</v>
       </c>
       <c r="DZ15" t="s">
@@ -12121,7 +12443,7 @@
       <c r="EA15" t="s">
         <v>920</v>
       </c>
-      <c r="EB15" t="s">
+      <c r="EB15" s="11" t="s">
         <v>921</v>
       </c>
       <c r="EC15" t="s">
@@ -12130,7 +12452,7 @@
       <c r="ED15" t="s">
         <v>922</v>
       </c>
-      <c r="EE15" t="s">
+      <c r="EE15" s="11" t="s">
         <v>923</v>
       </c>
       <c r="EF15" t="s">
@@ -12139,7 +12461,7 @@
       <c r="EG15" t="s">
         <v>924</v>
       </c>
-      <c r="EH15" t="s">
+      <c r="EH15" s="11" t="s">
         <v>925</v>
       </c>
       <c r="EI15" t="s">
@@ -12148,7 +12470,7 @@
       <c r="EJ15" t="s">
         <v>927</v>
       </c>
-      <c r="EK15" t="s">
+      <c r="EK15" s="11" t="s">
         <v>928</v>
       </c>
       <c r="EL15" t="s">
@@ -12157,7 +12479,7 @@
       <c r="EM15" t="s">
         <v>929</v>
       </c>
-      <c r="EN15" t="s">
+      <c r="EN15" s="11" t="s">
         <v>930</v>
       </c>
       <c r="EO15" t="s">
@@ -12166,7 +12488,7 @@
       <c r="EP15" t="s">
         <v>931</v>
       </c>
-      <c r="EQ15" t="s">
+      <c r="EQ15" s="11" t="s">
         <v>932</v>
       </c>
       <c r="ER15" t="s">
@@ -12646,14 +12968,14 @@
       <c r="DQ16" t="s">
         <v>443</v>
       </c>
-      <c r="DS16" s="1" t="s">
+      <c r="DS16" s="11" t="s">
         <v>1316</v>
       </c>
       <c r="DT16" s="1"/>
       <c r="DU16" t="s">
         <v>1317</v>
       </c>
-      <c r="DV16" t="s">
+      <c r="DV16" s="11" t="s">
         <v>1318</v>
       </c>
       <c r="DW16" t="s">
@@ -12662,7 +12984,7 @@
       <c r="DX16" t="s">
         <v>1320</v>
       </c>
-      <c r="DY16" t="s">
+      <c r="DY16" s="11" t="s">
         <v>1321</v>
       </c>
       <c r="DZ16" t="s">
@@ -12671,7 +12993,7 @@
       <c r="EA16" t="s">
         <v>1322</v>
       </c>
-      <c r="EB16" t="s">
+      <c r="EB16" s="11" t="s">
         <v>1323</v>
       </c>
       <c r="EC16" t="s">
@@ -12680,7 +13002,7 @@
       <c r="ED16" t="s">
         <v>1324</v>
       </c>
-      <c r="EE16" t="s">
+      <c r="EE16" s="11" t="s">
         <v>1325</v>
       </c>
       <c r="EF16" t="s">
@@ -12689,7 +13011,7 @@
       <c r="EG16" t="s">
         <v>1326</v>
       </c>
-      <c r="EH16" t="s">
+      <c r="EH16" s="11" t="s">
         <v>1327</v>
       </c>
       <c r="EI16" t="s">
@@ -12698,7 +13020,7 @@
       <c r="EJ16" t="s">
         <v>1328</v>
       </c>
-      <c r="EK16" t="s">
+      <c r="EK16" s="11" t="s">
         <v>1329</v>
       </c>
       <c r="EL16" t="s">
@@ -12707,7 +13029,7 @@
       <c r="EM16" t="s">
         <v>1330</v>
       </c>
-      <c r="EN16" t="s">
+      <c r="EN16" s="11" t="s">
         <v>1331</v>
       </c>
       <c r="EO16" t="s">
@@ -13128,7 +13450,7 @@
       <c r="DR17" t="s">
         <v>1425</v>
       </c>
-      <c r="DS17" t="s">
+      <c r="DS17" s="11" t="s">
         <v>1426</v>
       </c>
       <c r="DT17" t="s">
@@ -13137,7 +13459,7 @@
       <c r="DU17" t="s">
         <v>1427</v>
       </c>
-      <c r="DV17" t="s">
+      <c r="DV17" s="11" t="s">
         <v>1428</v>
       </c>
       <c r="DW17" t="s">
@@ -13146,7 +13468,7 @@
       <c r="DX17" t="s">
         <v>1429</v>
       </c>
-      <c r="DY17" t="s">
+      <c r="DY17" s="11" t="s">
         <v>1430</v>
       </c>
       <c r="DZ17" t="s">
@@ -13155,7 +13477,7 @@
       <c r="EA17" t="s">
         <v>1431</v>
       </c>
-      <c r="EB17" t="s">
+      <c r="EB17" s="11" t="s">
         <v>1432</v>
       </c>
       <c r="EC17" t="s">
@@ -13164,7 +13486,7 @@
       <c r="ED17" t="s">
         <v>1433</v>
       </c>
-      <c r="EE17" t="s">
+      <c r="EE17" s="11" t="s">
         <v>1434</v>
       </c>
       <c r="EF17" t="s">
@@ -13173,7 +13495,7 @@
       <c r="EG17" t="s">
         <v>1435</v>
       </c>
-      <c r="EH17" t="s">
+      <c r="EH17" s="11" t="s">
         <v>1436</v>
       </c>
       <c r="EI17" t="s">
@@ -13182,7 +13504,7 @@
       <c r="EJ17" t="s">
         <v>1437</v>
       </c>
-      <c r="EK17" t="s">
+      <c r="EK17" s="11" t="s">
         <v>1438</v>
       </c>
       <c r="EL17" t="s">
@@ -13191,7 +13513,7 @@
       <c r="EM17" t="s">
         <v>1439</v>
       </c>
-      <c r="EN17" t="s">
+      <c r="EN17" s="11" t="s">
         <v>1440</v>
       </c>
       <c r="EO17" t="s">
@@ -13626,7 +13948,7 @@
       <c r="DR18" t="s">
         <v>1138</v>
       </c>
-      <c r="DS18" t="s">
+      <c r="DS18" s="11" t="s">
         <v>1139</v>
       </c>
       <c r="DT18" t="s">
@@ -13635,7 +13957,7 @@
       <c r="DU18" t="s">
         <v>1140</v>
       </c>
-      <c r="DV18" t="s">
+      <c r="DV18" s="11" t="s">
         <v>1141</v>
       </c>
       <c r="DW18" t="s">
@@ -13644,7 +13966,7 @@
       <c r="DX18" t="s">
         <v>1143</v>
       </c>
-      <c r="DY18" t="s">
+      <c r="DY18" s="11" t="s">
         <v>1144</v>
       </c>
       <c r="DZ18" t="s">
@@ -13653,7 +13975,7 @@
       <c r="EA18" t="s">
         <v>1145</v>
       </c>
-      <c r="EB18" t="s">
+      <c r="EB18" s="11" t="s">
         <v>1146</v>
       </c>
       <c r="EC18" t="s">
@@ -13662,7 +13984,7 @@
       <c r="ED18" t="s">
         <v>1147</v>
       </c>
-      <c r="EE18" t="s">
+      <c r="EE18" s="11" t="s">
         <v>1148</v>
       </c>
       <c r="EF18" t="s">
@@ -13671,7 +13993,7 @@
       <c r="EG18" t="s">
         <v>1149</v>
       </c>
-      <c r="EH18" t="s">
+      <c r="EH18" s="11" t="s">
         <v>1150</v>
       </c>
       <c r="EI18" t="s">
@@ -13680,7 +14002,7 @@
       <c r="EJ18" t="s">
         <v>1151</v>
       </c>
-      <c r="EK18" t="s">
+      <c r="EK18" s="11" t="s">
         <v>1146</v>
       </c>
       <c r="EL18" t="s">
@@ -13689,7 +14011,7 @@
       <c r="EM18" t="s">
         <v>1147</v>
       </c>
-      <c r="EN18" t="s">
+      <c r="EN18" s="11" t="s">
         <v>1141</v>
       </c>
       <c r="EO18" t="s">
@@ -13698,7 +14020,7 @@
       <c r="EP18" t="s">
         <v>1143</v>
       </c>
-      <c r="EQ18" t="s">
+      <c r="EQ18" s="11" t="s">
         <v>1144</v>
       </c>
       <c r="ER18" t="s">
@@ -14133,7 +14455,7 @@
       <c r="DR19" t="s">
         <v>1238</v>
       </c>
-      <c r="DS19" t="s">
+      <c r="DS19" s="11" t="s">
         <v>1239</v>
       </c>
       <c r="DT19" t="s">
@@ -14142,7 +14464,7 @@
       <c r="DU19" t="s">
         <v>1240</v>
       </c>
-      <c r="DV19" t="s">
+      <c r="DV19" s="11" t="s">
         <v>1241</v>
       </c>
       <c r="DW19" t="s">
@@ -14151,7 +14473,7 @@
       <c r="DX19" t="s">
         <v>1242</v>
       </c>
-      <c r="EB19" t="s">
+      <c r="EB19" s="11" t="s">
         <v>1243</v>
       </c>
       <c r="EC19" t="s">
@@ -14160,7 +14482,7 @@
       <c r="ED19" t="s">
         <v>1244</v>
       </c>
-      <c r="EE19" t="s">
+      <c r="EE19" s="11" t="s">
         <v>1245</v>
       </c>
       <c r="EF19" t="s">
@@ -14169,7 +14491,7 @@
       <c r="EG19" t="s">
         <v>1246</v>
       </c>
-      <c r="EH19" t="s">
+      <c r="EH19" s="11" t="s">
         <v>1247</v>
       </c>
       <c r="EI19" t="s">
@@ -14178,7 +14500,7 @@
       <c r="EJ19" t="s">
         <v>1248</v>
       </c>
-      <c r="EK19" t="s">
+      <c r="EK19" s="11" t="s">
         <v>1249</v>
       </c>
       <c r="EL19" t="s">
@@ -14187,7 +14509,7 @@
       <c r="EM19" t="s">
         <v>1250</v>
       </c>
-      <c r="EN19" t="s">
+      <c r="EN19" s="11" t="s">
         <v>1251</v>
       </c>
       <c r="EO19" t="s">
@@ -14196,7 +14518,7 @@
       <c r="EP19" t="s">
         <v>1252</v>
       </c>
-      <c r="EQ19" t="s">
+      <c r="EQ19" s="11" t="s">
         <v>1253</v>
       </c>
       <c r="ER19" t="s">
@@ -14569,7 +14891,7 @@
       <c r="DR20" t="s">
         <v>1282</v>
       </c>
-      <c r="DS20" t="s">
+      <c r="DS20" s="11" t="s">
         <v>1626</v>
       </c>
       <c r="DT20" t="s">
@@ -14578,7 +14900,7 @@
       <c r="DU20" t="s">
         <v>1627</v>
       </c>
-      <c r="DV20" t="s">
+      <c r="DV20" s="11" t="s">
         <v>1628</v>
       </c>
       <c r="DW20" t="s">
@@ -14587,7 +14909,7 @@
       <c r="DX20" t="s">
         <v>1629</v>
       </c>
-      <c r="DY20" t="s">
+      <c r="DY20" s="11" t="s">
         <v>1630</v>
       </c>
       <c r="DZ20" t="s">
@@ -14596,7 +14918,7 @@
       <c r="EA20" t="s">
         <v>1631</v>
       </c>
-      <c r="EB20" t="s">
+      <c r="EB20" s="11" t="s">
         <v>1632</v>
       </c>
       <c r="EC20" t="s">
@@ -14605,7 +14927,7 @@
       <c r="ED20" t="s">
         <v>1633</v>
       </c>
-      <c r="EE20" t="s">
+      <c r="EE20" s="11" t="s">
         <v>1634</v>
       </c>
       <c r="EF20" t="s">
@@ -14614,7 +14936,7 @@
       <c r="EG20" t="s">
         <v>1635</v>
       </c>
-      <c r="EH20" t="s">
+      <c r="EH20" s="11" t="s">
         <v>1636</v>
       </c>
       <c r="EI20" t="s">
@@ -14623,7 +14945,7 @@
       <c r="EJ20" t="s">
         <v>1637</v>
       </c>
-      <c r="EK20" t="s">
+      <c r="EK20" s="11" t="s">
         <v>1638</v>
       </c>
       <c r="EL20" t="s">
@@ -14632,7 +14954,7 @@
       <c r="EM20" t="s">
         <v>1639</v>
       </c>
-      <c r="EN20" t="s">
+      <c r="EN20" s="11" t="s">
         <v>1640</v>
       </c>
       <c r="EO20" t="s">
@@ -14641,7 +14963,7 @@
       <c r="EP20" t="s">
         <v>1641</v>
       </c>
-      <c r="EQ20" t="s">
+      <c r="EQ20" s="11" t="s">
         <v>1642</v>
       </c>
       <c r="ER20" t="s">
@@ -15101,13 +15423,13 @@
       <c r="DR21" t="s">
         <v>954</v>
       </c>
-      <c r="DS21" t="s">
+      <c r="DS21" s="11" t="s">
         <v>955</v>
       </c>
       <c r="DT21" t="s">
         <v>1230</v>
       </c>
-      <c r="DV21" t="s">
+      <c r="DV21" s="11" t="s">
         <v>956</v>
       </c>
       <c r="DW21" t="s">
@@ -15116,7 +15438,7 @@
       <c r="DX21" t="s">
         <v>957</v>
       </c>
-      <c r="DY21" t="s">
+      <c r="DY21" s="11" t="s">
         <v>958</v>
       </c>
       <c r="DZ21" t="s">
@@ -15125,7 +15447,7 @@
       <c r="EA21" t="s">
         <v>959</v>
       </c>
-      <c r="EB21" t="s">
+      <c r="EB21" s="11" t="s">
         <v>960</v>
       </c>
       <c r="EC21" t="s">
@@ -15134,7 +15456,7 @@
       <c r="ED21" t="s">
         <v>961</v>
       </c>
-      <c r="EE21" t="s">
+      <c r="EE21" s="11" t="s">
         <v>962</v>
       </c>
       <c r="EF21" t="s">
@@ -15143,7 +15465,7 @@
       <c r="EG21" t="s">
         <v>963</v>
       </c>
-      <c r="EH21" t="s">
+      <c r="EH21" s="11" t="s">
         <v>964</v>
       </c>
       <c r="EI21" t="s">
@@ -15152,7 +15474,7 @@
       <c r="EJ21" t="s">
         <v>965</v>
       </c>
-      <c r="EK21" t="s">
+      <c r="EK21" s="11" t="s">
         <v>966</v>
       </c>
       <c r="EL21" t="s">
@@ -15161,7 +15483,7 @@
       <c r="EM21" t="s">
         <v>967</v>
       </c>
-      <c r="EN21" t="s">
+      <c r="EN21" s="11" t="s">
         <v>968</v>
       </c>
       <c r="EO21" t="s">
@@ -15590,7 +15912,7 @@
       <c r="DR22" t="s">
         <v>1473</v>
       </c>
-      <c r="DS22" t="s">
+      <c r="DS22" s="11" t="s">
         <v>1474</v>
       </c>
       <c r="DT22" t="s">
@@ -15599,7 +15921,7 @@
       <c r="DU22" t="s">
         <v>1475</v>
       </c>
-      <c r="DV22" t="s">
+      <c r="DV22" s="11" t="s">
         <v>1476</v>
       </c>
       <c r="DW22" t="s">
@@ -15608,7 +15930,7 @@
       <c r="DX22" t="s">
         <v>1477</v>
       </c>
-      <c r="DY22" t="s">
+      <c r="DY22" s="11" t="s">
         <v>1478</v>
       </c>
       <c r="DZ22" t="s">
@@ -15617,7 +15939,7 @@
       <c r="EA22" t="s">
         <v>1479</v>
       </c>
-      <c r="EB22" t="s">
+      <c r="EB22" s="11" t="s">
         <v>1480</v>
       </c>
       <c r="EC22" t="s">
@@ -15626,7 +15948,7 @@
       <c r="ED22" t="s">
         <v>1481</v>
       </c>
-      <c r="EE22" t="s">
+      <c r="EE22" s="11" t="s">
         <v>1482</v>
       </c>
       <c r="EF22" t="s">
@@ -15635,7 +15957,7 @@
       <c r="EG22" t="s">
         <v>1483</v>
       </c>
-      <c r="EH22" t="s">
+      <c r="EH22" s="11" t="s">
         <v>1463</v>
       </c>
       <c r="EI22" t="s">
@@ -15644,7 +15966,7 @@
       <c r="EJ22" t="s">
         <v>1464</v>
       </c>
-      <c r="EK22" t="s">
+      <c r="EK22" s="11" t="s">
         <v>1484</v>
       </c>
       <c r="EL22" t="s">
@@ -15653,7 +15975,7 @@
       <c r="EM22" t="s">
         <v>1485</v>
       </c>
-      <c r="EN22" t="s">
+      <c r="EN22" s="11" t="s">
         <v>1486</v>
       </c>
       <c r="EO22" t="s">
@@ -15662,7 +15984,7 @@
       <c r="EP22" t="s">
         <v>1487</v>
       </c>
-      <c r="EQ22" t="s">
+      <c r="EQ22" s="11" t="s">
         <v>1488</v>
       </c>
       <c r="ER22" t="s">
@@ -16154,7 +16476,7 @@
       <c r="DR23" t="s">
         <v>1606</v>
       </c>
-      <c r="DS23" t="s">
+      <c r="DS23" s="11" t="s">
         <v>1607</v>
       </c>
       <c r="DT23" t="s">
@@ -16163,7 +16485,7 @@
       <c r="DU23" t="s">
         <v>1608</v>
       </c>
-      <c r="DV23" t="s">
+      <c r="DV23" s="11" t="s">
         <v>1609</v>
       </c>
       <c r="DW23" t="s">
@@ -16172,7 +16494,7 @@
       <c r="DX23" t="s">
         <v>1610</v>
       </c>
-      <c r="DY23" t="s">
+      <c r="DY23" s="11" t="s">
         <v>1611</v>
       </c>
       <c r="DZ23" t="s">
@@ -16181,7 +16503,7 @@
       <c r="EA23" t="s">
         <v>1612</v>
       </c>
-      <c r="EB23" t="s">
+      <c r="EB23" s="11" t="s">
         <v>1613</v>
       </c>
       <c r="EC23" t="s">
@@ -16190,7 +16512,7 @@
       <c r="ED23" t="s">
         <v>1614</v>
       </c>
-      <c r="EE23" t="s">
+      <c r="EE23" s="11" t="s">
         <v>1615</v>
       </c>
       <c r="EF23" t="s">
@@ -16199,7 +16521,7 @@
       <c r="EG23" t="s">
         <v>1616</v>
       </c>
-      <c r="EH23" t="s">
+      <c r="EH23" s="11" t="s">
         <v>1617</v>
       </c>
       <c r="EI23" t="s">
@@ -16208,7 +16530,7 @@
       <c r="EJ23" t="s">
         <v>1618</v>
       </c>
-      <c r="EK23" t="s">
+      <c r="EK23" s="11" t="s">
         <v>1619</v>
       </c>
       <c r="EL23" t="s">
@@ -16217,7 +16539,7 @@
       <c r="EM23" t="s">
         <v>1620</v>
       </c>
-      <c r="EN23" t="s">
+      <c r="EN23" s="11" t="s">
         <v>1621</v>
       </c>
       <c r="EO23" t="s">
@@ -16226,7 +16548,7 @@
       <c r="EP23" t="s">
         <v>1622</v>
       </c>
-      <c r="EQ23" t="s">
+      <c r="EQ23" s="11" t="s">
         <v>1623</v>
       </c>
       <c r="ER23" t="s">
@@ -16750,7 +17072,7 @@
       <c r="DR24" t="s">
         <v>1587</v>
       </c>
-      <c r="DS24" t="s">
+      <c r="DS24" s="11" t="s">
         <v>1588</v>
       </c>
       <c r="DT24" t="s">
@@ -16759,7 +17081,7 @@
       <c r="DU24" t="s">
         <v>1589</v>
       </c>
-      <c r="DV24" t="s">
+      <c r="DV24" s="11" t="s">
         <v>1590</v>
       </c>
       <c r="DW24" t="s">
@@ -16768,7 +17090,7 @@
       <c r="DX24" t="s">
         <v>1591</v>
       </c>
-      <c r="DY24" t="s">
+      <c r="DY24" s="11" t="s">
         <v>1592</v>
       </c>
       <c r="DZ24" t="s">
@@ -16777,7 +17099,7 @@
       <c r="EA24" t="s">
         <v>1593</v>
       </c>
-      <c r="EB24" t="s">
+      <c r="EB24" s="11" t="s">
         <v>1594</v>
       </c>
       <c r="EC24" t="s">
@@ -16786,7 +17108,7 @@
       <c r="ED24" t="s">
         <v>1595</v>
       </c>
-      <c r="EE24" t="s">
+      <c r="EE24" s="11" t="s">
         <v>1596</v>
       </c>
       <c r="EF24" t="s">
@@ -16795,7 +17117,7 @@
       <c r="EG24" t="s">
         <v>1597</v>
       </c>
-      <c r="EH24" t="s">
+      <c r="EH24" s="11" t="s">
         <v>1598</v>
       </c>
       <c r="EI24" t="s">
@@ -16804,7 +17126,7 @@
       <c r="EJ24" t="s">
         <v>1599</v>
       </c>
-      <c r="EK24" t="s">
+      <c r="EK24" s="11" t="s">
         <v>1598</v>
       </c>
       <c r="EL24" t="s">
@@ -16813,7 +17135,7 @@
       <c r="EM24" t="s">
         <v>1599</v>
       </c>
-      <c r="EN24" t="s">
+      <c r="EN24" s="11" t="s">
         <v>1600</v>
       </c>
       <c r="EO24" t="s">
@@ -16822,7 +17144,7 @@
       <c r="EP24" t="s">
         <v>1601</v>
       </c>
-      <c r="EQ24" t="s">
+      <c r="EQ24" s="11" t="s">
         <v>1602</v>
       </c>
       <c r="ER24" t="s">
@@ -17082,7 +17404,7 @@
       <c r="C25" t="s">
         <v>948</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="1" t="s">
         <v>1888</v>
       </c>
       <c r="E25" t="s">
@@ -17336,7 +17658,7 @@
       <c r="DR25" t="s">
         <v>972</v>
       </c>
-      <c r="DS25" t="s">
+      <c r="DS25" s="11" t="s">
         <v>1876</v>
       </c>
       <c r="DT25" t="s">
@@ -17345,7 +17667,7 @@
       <c r="DU25" t="s">
         <v>1877</v>
       </c>
-      <c r="DV25" t="s">
+      <c r="DV25" s="11" t="s">
         <v>1878</v>
       </c>
       <c r="DW25" t="s">
@@ -17354,7 +17676,7 @@
       <c r="DX25" t="s">
         <v>1879</v>
       </c>
-      <c r="DY25" t="s">
+      <c r="DY25" s="11" t="s">
         <v>1880</v>
       </c>
       <c r="DZ25" t="s">
@@ -17363,7 +17685,7 @@
       <c r="EA25" t="s">
         <v>1881</v>
       </c>
-      <c r="EB25" t="s">
+      <c r="EB25" s="11" t="s">
         <v>1882</v>
       </c>
       <c r="EC25" t="s">
@@ -17372,7 +17694,7 @@
       <c r="ED25" t="s">
         <v>1883</v>
       </c>
-      <c r="EE25" t="s">
+      <c r="EE25" s="11" t="s">
         <v>1884</v>
       </c>
       <c r="EF25" t="s">
@@ -17381,7 +17703,7 @@
       <c r="EG25" t="s">
         <v>1885</v>
       </c>
-      <c r="EH25" t="s">
+      <c r="EH25" s="11" t="s">
         <v>1886</v>
       </c>
       <c r="EI25" t="s">
@@ -17632,7 +17954,7 @@
       <c r="C26" t="s">
         <v>948</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="1" t="s">
         <v>1057</v>
       </c>
       <c r="E26" t="s">
@@ -17886,7 +18208,7 @@
       <c r="DR26" t="s">
         <v>972</v>
       </c>
-      <c r="DS26" s="1" t="s">
+      <c r="DS26" s="11" t="s">
         <v>973</v>
       </c>
       <c r="DT26" s="1" t="s">
@@ -17895,7 +18217,7 @@
       <c r="DU26" t="s">
         <v>975</v>
       </c>
-      <c r="DV26" t="s">
+      <c r="DV26" s="11" t="s">
         <v>976</v>
       </c>
       <c r="DW26" t="s">
@@ -17904,7 +18226,7 @@
       <c r="DX26" t="s">
         <v>978</v>
       </c>
-      <c r="DY26" t="s">
+      <c r="DY26" s="11" t="s">
         <v>979</v>
       </c>
       <c r="DZ26" t="s">
@@ -17913,7 +18235,7 @@
       <c r="EA26" t="s">
         <v>980</v>
       </c>
-      <c r="EB26" t="s">
+      <c r="EB26" s="11" t="s">
         <v>981</v>
       </c>
       <c r="EC26" t="s">
@@ -17922,7 +18244,7 @@
       <c r="ED26" t="s">
         <v>982</v>
       </c>
-      <c r="EE26" t="s">
+      <c r="EE26" s="11" t="s">
         <v>983</v>
       </c>
       <c r="EF26" t="s">
@@ -17931,7 +18253,7 @@
       <c r="EG26" t="s">
         <v>984</v>
       </c>
-      <c r="EK26" t="s">
+      <c r="EK26" s="11" t="s">
         <v>985</v>
       </c>
       <c r="EL26" t="s">
@@ -17940,7 +18262,7 @@
       <c r="EM26" t="s">
         <v>986</v>
       </c>
-      <c r="EN26" t="s">
+      <c r="EN26" s="11" t="s">
         <v>987</v>
       </c>
       <c r="EO26" t="s">
@@ -17949,7 +18271,7 @@
       <c r="EP26" t="s">
         <v>988</v>
       </c>
-      <c r="EQ26" t="s">
+      <c r="EQ26" s="11" t="s">
         <v>989</v>
       </c>
       <c r="ER26" t="s">
@@ -18466,7 +18788,7 @@
       <c r="DR27" t="s">
         <v>1062</v>
       </c>
-      <c r="DS27" t="s">
+      <c r="DS27" s="11" t="s">
         <v>1063</v>
       </c>
       <c r="DT27" t="s">
@@ -18475,7 +18797,7 @@
       <c r="DU27" t="s">
         <v>1064</v>
       </c>
-      <c r="DV27" t="s">
+      <c r="DV27" s="11" t="s">
         <v>1065</v>
       </c>
       <c r="DW27" t="s">
@@ -18484,7 +18806,7 @@
       <c r="DX27" t="s">
         <v>1066</v>
       </c>
-      <c r="DY27" t="s">
+      <c r="DY27" s="11" t="s">
         <v>1067</v>
       </c>
       <c r="DZ27" t="s">
@@ -18493,7 +18815,7 @@
       <c r="EA27" t="s">
         <v>1068</v>
       </c>
-      <c r="EB27" t="s">
+      <c r="EB27" s="11" t="s">
         <v>1069</v>
       </c>
       <c r="EC27" t="s">
@@ -18502,7 +18824,7 @@
       <c r="ED27" t="s">
         <v>1070</v>
       </c>
-      <c r="EE27" t="s">
+      <c r="EE27" s="11" t="s">
         <v>1071</v>
       </c>
       <c r="EF27" t="s">
@@ -18511,7 +18833,7 @@
       <c r="EG27" t="s">
         <v>1072</v>
       </c>
-      <c r="EH27" t="s">
+      <c r="EH27" s="11" t="s">
         <v>1073</v>
       </c>
       <c r="EI27" t="s">
@@ -18520,7 +18842,7 @@
       <c r="EJ27" t="s">
         <v>1074</v>
       </c>
-      <c r="EK27" t="s">
+      <c r="EK27" s="11" t="s">
         <v>1075</v>
       </c>
       <c r="EL27" t="s">
@@ -18529,7 +18851,7 @@
       <c r="EM27" t="s">
         <v>1076</v>
       </c>
-      <c r="EN27" t="s">
+      <c r="EN27" s="11" t="s">
         <v>1077</v>
       </c>
       <c r="EO27" t="s">
@@ -18538,7 +18860,7 @@
       <c r="EP27" t="s">
         <v>1078</v>
       </c>
-      <c r="EQ27" t="s">
+      <c r="EQ27" s="11" t="s">
         <v>1079</v>
       </c>
       <c r="ER27" t="s">
@@ -19064,7 +19386,7 @@
       <c r="DR28" t="s">
         <v>1447</v>
       </c>
-      <c r="DS28" t="s">
+      <c r="DS28" s="11" t="s">
         <v>1448</v>
       </c>
       <c r="DT28" t="s">
@@ -19073,10 +19395,10 @@
       <c r="DU28" t="s">
         <v>1449</v>
       </c>
-      <c r="DV28" t="s">
+      <c r="DV28" s="11" t="s">
         <v>1450</v>
       </c>
-      <c r="DY28" t="s">
+      <c r="DY28" s="11" t="s">
         <v>1451</v>
       </c>
       <c r="DZ28" t="s">
@@ -19085,7 +19407,7 @@
       <c r="EA28" t="s">
         <v>1452</v>
       </c>
-      <c r="EB28" t="s">
+      <c r="EB28" s="11" t="s">
         <v>1453</v>
       </c>
       <c r="EC28" t="s">
@@ -19094,7 +19416,7 @@
       <c r="ED28" t="s">
         <v>1454</v>
       </c>
-      <c r="EE28" t="s">
+      <c r="EE28" s="11" t="s">
         <v>1455</v>
       </c>
       <c r="EF28" t="s">
@@ -19103,7 +19425,7 @@
       <c r="EG28" t="s">
         <v>1456</v>
       </c>
-      <c r="EH28" t="s">
+      <c r="EH28" s="11" t="s">
         <v>1457</v>
       </c>
       <c r="EI28" t="s">
@@ -19112,7 +19434,7 @@
       <c r="EJ28" t="s">
         <v>1458</v>
       </c>
-      <c r="EK28" t="s">
+      <c r="EK28" s="11" t="s">
         <v>1459</v>
       </c>
       <c r="EL28" t="s">
@@ -19121,7 +19443,7 @@
       <c r="EM28" t="s">
         <v>1460</v>
       </c>
-      <c r="EN28" t="s">
+      <c r="EN28" s="11" t="s">
         <v>1461</v>
       </c>
       <c r="EO28" t="s">
@@ -19130,7 +19452,7 @@
       <c r="EP28" t="s">
         <v>1462</v>
       </c>
-      <c r="EQ28" t="s">
+      <c r="EQ28" s="11" t="s">
         <v>1463</v>
       </c>
       <c r="ER28" t="s">
@@ -19653,7 +19975,7 @@
       <c r="DR29" t="s">
         <v>1159</v>
       </c>
-      <c r="DS29" t="s">
+      <c r="DS29" s="11" t="s">
         <v>1160</v>
       </c>
       <c r="DT29" t="s">
@@ -19662,7 +19984,7 @@
       <c r="DU29" t="s">
         <v>1161</v>
       </c>
-      <c r="DV29" t="s">
+      <c r="DV29" s="11" t="s">
         <v>1162</v>
       </c>
       <c r="DW29" t="s">
@@ -19671,7 +19993,7 @@
       <c r="DX29" t="s">
         <v>1163</v>
       </c>
-      <c r="DY29" t="s">
+      <c r="DY29" s="11" t="s">
         <v>1164</v>
       </c>
       <c r="DZ29" t="s">
@@ -19680,7 +20002,7 @@
       <c r="EA29" t="s">
         <v>1165</v>
       </c>
-      <c r="EB29" t="s">
+      <c r="EB29" s="11" t="s">
         <v>1166</v>
       </c>
       <c r="EC29" t="s">
@@ -19689,7 +20011,7 @@
       <c r="ED29" t="s">
         <v>1167</v>
       </c>
-      <c r="EE29" t="s">
+      <c r="EE29" s="11" t="s">
         <v>1168</v>
       </c>
       <c r="EF29" t="s">
@@ -19698,7 +20020,7 @@
       <c r="EG29" t="s">
         <v>1169</v>
       </c>
-      <c r="EH29" t="s">
+      <c r="EH29" s="11" t="s">
         <v>1170</v>
       </c>
       <c r="EI29" t="s">
@@ -19707,7 +20029,7 @@
       <c r="EJ29" t="s">
         <v>1171</v>
       </c>
-      <c r="EK29" t="s">
+      <c r="EK29" s="11" t="s">
         <v>1172</v>
       </c>
       <c r="EL29" t="s">
@@ -19716,7 +20038,7 @@
       <c r="EM29" t="s">
         <v>1173</v>
       </c>
-      <c r="EN29" t="s">
+      <c r="EN29" s="11" t="s">
         <v>1174</v>
       </c>
       <c r="EO29" t="s">
@@ -19725,7 +20047,7 @@
       <c r="EP29" t="s">
         <v>1175</v>
       </c>
-      <c r="EQ29" t="s">
+      <c r="EQ29" s="11" t="s">
         <v>1176</v>
       </c>
       <c r="ER29" t="s">
@@ -20266,7 +20588,7 @@
       <c r="DR30" t="s">
         <v>1283</v>
       </c>
-      <c r="DS30" s="1" t="s">
+      <c r="DS30" s="11" t="s">
         <v>1259</v>
       </c>
       <c r="DT30" s="1" t="s">
@@ -20275,7 +20597,7 @@
       <c r="DU30" t="s">
         <v>1260</v>
       </c>
-      <c r="DV30" t="s">
+      <c r="DV30" s="11" t="s">
         <v>1261</v>
       </c>
       <c r="DW30" t="s">
@@ -20284,7 +20606,7 @@
       <c r="DX30" t="s">
         <v>1262</v>
       </c>
-      <c r="DY30" t="s">
+      <c r="DY30" s="11" t="s">
         <v>1263</v>
       </c>
       <c r="DZ30" t="s">
@@ -20293,7 +20615,7 @@
       <c r="EA30" t="s">
         <v>1264</v>
       </c>
-      <c r="EB30" t="s">
+      <c r="EB30" s="11" t="s">
         <v>1265</v>
       </c>
       <c r="EC30" t="s">
@@ -20302,7 +20624,7 @@
       <c r="ED30" t="s">
         <v>1266</v>
       </c>
-      <c r="EE30" t="s">
+      <c r="EE30" s="11" t="s">
         <v>1267</v>
       </c>
       <c r="EF30" t="s">
@@ -20311,7 +20633,7 @@
       <c r="EG30" t="s">
         <v>1268</v>
       </c>
-      <c r="EH30" t="s">
+      <c r="EH30" s="11" t="s">
         <v>1269</v>
       </c>
       <c r="EI30" t="s">
@@ -20320,7 +20642,7 @@
       <c r="EJ30" t="s">
         <v>1271</v>
       </c>
-      <c r="EK30" t="s">
+      <c r="EK30" s="11" t="s">
         <v>1272</v>
       </c>
       <c r="EL30" t="s">
@@ -20329,7 +20651,7 @@
       <c r="EM30" t="s">
         <v>1273</v>
       </c>
-      <c r="EN30" t="s">
+      <c r="EN30" s="11" t="s">
         <v>1274</v>
       </c>
       <c r="EO30" t="s">
@@ -20338,7 +20660,7 @@
       <c r="EP30" t="s">
         <v>1275</v>
       </c>
-      <c r="EQ30" t="s">
+      <c r="EQ30" s="11" t="s">
         <v>1276</v>
       </c>
       <c r="ER30" t="s">
@@ -20855,7 +21177,7 @@
       <c r="DR31" t="s">
         <v>1375</v>
       </c>
-      <c r="DS31" s="1" t="s">
+      <c r="DS31" s="11" t="s">
         <v>1376</v>
       </c>
       <c r="DT31" s="1" t="s">
@@ -20864,7 +21186,7 @@
       <c r="DU31" t="s">
         <v>1377</v>
       </c>
-      <c r="DV31" t="s">
+      <c r="DV31" s="11" t="s">
         <v>1378</v>
       </c>
       <c r="DW31" t="s">
@@ -20873,7 +21195,7 @@
       <c r="DX31" t="s">
         <v>1379</v>
       </c>
-      <c r="DY31" t="s">
+      <c r="DY31" s="11" t="s">
         <v>1380</v>
       </c>
       <c r="DZ31" t="s">
@@ -20882,7 +21204,7 @@
       <c r="EA31" t="s">
         <v>1381</v>
       </c>
-      <c r="EB31" t="s">
+      <c r="EB31" s="11" t="s">
         <v>1382</v>
       </c>
       <c r="EC31" t="s">
@@ -20891,7 +21213,7 @@
       <c r="ED31" t="s">
         <v>1383</v>
       </c>
-      <c r="EE31" t="s">
+      <c r="EE31" s="11" t="s">
         <v>1384</v>
       </c>
       <c r="EF31" t="s">
@@ -20900,7 +21222,7 @@
       <c r="EG31" t="s">
         <v>1385</v>
       </c>
-      <c r="EH31" t="s">
+      <c r="EH31" s="11" t="s">
         <v>1386</v>
       </c>
       <c r="EI31" t="s">
@@ -20909,7 +21231,7 @@
       <c r="EJ31" t="s">
         <v>1387</v>
       </c>
-      <c r="EK31" t="s">
+      <c r="EK31" s="11" t="s">
         <v>1388</v>
       </c>
       <c r="EL31" t="s">
@@ -20918,7 +21240,7 @@
       <c r="EM31" t="s">
         <v>1389</v>
       </c>
-      <c r="EN31" t="s">
+      <c r="EN31" s="11" t="s">
         <v>1390</v>
       </c>
       <c r="EO31" t="s">
@@ -20927,7 +21249,7 @@
       <c r="EP31" t="s">
         <v>1391</v>
       </c>
-      <c r="EQ31" t="s">
+      <c r="EQ31" s="11" t="s">
         <v>1376</v>
       </c>
       <c r="ER31" t="s">
@@ -21438,7 +21760,7 @@
       <c r="DR32" t="s">
         <v>1027</v>
       </c>
-      <c r="DS32" t="s">
+      <c r="DS32" s="11" t="s">
         <v>1028</v>
       </c>
       <c r="DT32" t="s">
@@ -21447,7 +21769,7 @@
       <c r="DU32" t="s">
         <v>1029</v>
       </c>
-      <c r="DV32" t="s">
+      <c r="DV32" s="11" t="s">
         <v>1030</v>
       </c>
       <c r="DW32" t="s">
@@ -21456,7 +21778,7 @@
       <c r="DX32" t="s">
         <v>1031</v>
       </c>
-      <c r="DY32" t="s">
+      <c r="DY32" s="11" t="s">
         <v>1032</v>
       </c>
       <c r="DZ32" t="s">
@@ -21465,7 +21787,7 @@
       <c r="EA32" t="s">
         <v>1033</v>
       </c>
-      <c r="EB32" t="s">
+      <c r="EB32" s="11" t="s">
         <v>1034</v>
       </c>
       <c r="EC32" t="s">
@@ -21474,7 +21796,7 @@
       <c r="ED32" t="s">
         <v>1035</v>
       </c>
-      <c r="EE32" t="s">
+      <c r="EE32" s="11" t="s">
         <v>1036</v>
       </c>
       <c r="EF32" t="s">
@@ -21483,7 +21805,7 @@
       <c r="EG32" t="s">
         <v>1037</v>
       </c>
-      <c r="EH32" t="s">
+      <c r="EH32" s="11" t="s">
         <v>1038</v>
       </c>
       <c r="EI32" t="s">
@@ -21492,7 +21814,7 @@
       <c r="EJ32" t="s">
         <v>1039</v>
       </c>
-      <c r="EK32" t="s">
+      <c r="EK32" s="11" t="s">
         <v>1040</v>
       </c>
       <c r="EL32" t="s">
@@ -21501,7 +21823,7 @@
       <c r="EM32" t="s">
         <v>1041</v>
       </c>
-      <c r="EN32" t="s">
+      <c r="EN32" s="11" t="s">
         <v>1042</v>
       </c>
       <c r="EO32" t="s">
@@ -21510,7 +21832,7 @@
       <c r="EP32" t="s">
         <v>1043</v>
       </c>
-      <c r="EQ32" t="s">
+      <c r="EQ32" s="11" t="s">
         <v>1044</v>
       </c>
       <c r="ER32" t="s">
@@ -22039,7 +22361,7 @@
       <c r="DR33" t="s">
         <v>1344</v>
       </c>
-      <c r="DS33" s="1" t="s">
+      <c r="DS33" s="11" t="s">
         <v>1345</v>
       </c>
       <c r="DT33" s="1" t="s">
@@ -22048,7 +22370,7 @@
       <c r="DU33" t="s">
         <v>1346</v>
       </c>
-      <c r="DV33" t="s">
+      <c r="DV33" s="11" t="s">
         <v>1347</v>
       </c>
       <c r="DW33" t="s">
@@ -22057,7 +22379,7 @@
       <c r="DX33" t="s">
         <v>1348</v>
       </c>
-      <c r="DY33" t="s">
+      <c r="DY33" s="11" t="s">
         <v>1349</v>
       </c>
       <c r="DZ33" t="s">
@@ -22066,7 +22388,7 @@
       <c r="EA33" t="s">
         <v>1350</v>
       </c>
-      <c r="EB33" t="s">
+      <c r="EB33" s="11" t="s">
         <v>1351</v>
       </c>
       <c r="EC33" t="s">
@@ -22075,7 +22397,7 @@
       <c r="ED33" t="s">
         <v>1353</v>
       </c>
-      <c r="EE33" t="s">
+      <c r="EE33" s="11" t="s">
         <v>1352</v>
       </c>
       <c r="EF33" t="s">
@@ -22084,7 +22406,7 @@
       <c r="EG33" t="s">
         <v>1354</v>
       </c>
-      <c r="EH33" t="s">
+      <c r="EH33" s="11" t="s">
         <v>1355</v>
       </c>
       <c r="EI33" t="s">
@@ -22093,7 +22415,7 @@
       <c r="EJ33" t="s">
         <v>1356</v>
       </c>
-      <c r="EK33" t="s">
+      <c r="EK33" s="11" t="s">
         <v>1357</v>
       </c>
       <c r="EL33" t="s">
@@ -22102,7 +22424,7 @@
       <c r="EM33" t="s">
         <v>1350</v>
       </c>
-      <c r="EN33" t="s">
+      <c r="EN33" s="11" t="s">
         <v>1358</v>
       </c>
       <c r="EO33" t="s">
@@ -22111,7 +22433,7 @@
       <c r="EP33" t="s">
         <v>1359</v>
       </c>
-      <c r="EQ33" t="s">
+      <c r="EQ33" s="11" t="s">
         <v>1360</v>
       </c>
       <c r="ER33" t="s">
@@ -22619,7 +22941,7 @@
       <c r="DR34" t="s">
         <v>861</v>
       </c>
-      <c r="DS34" t="s">
+      <c r="DS34" s="11" t="s">
         <v>862</v>
       </c>
       <c r="DT34" t="s">
@@ -22628,7 +22950,7 @@
       <c r="DU34" t="s">
         <v>863</v>
       </c>
-      <c r="DV34" t="s">
+      <c r="DV34" s="11" t="s">
         <v>864</v>
       </c>
       <c r="DW34" t="s">
@@ -22637,7 +22959,7 @@
       <c r="DX34" t="s">
         <v>866</v>
       </c>
-      <c r="DY34" t="s">
+      <c r="DY34" s="11" t="s">
         <v>867</v>
       </c>
       <c r="DZ34" t="s">
@@ -22646,7 +22968,7 @@
       <c r="EA34" t="s">
         <v>869</v>
       </c>
-      <c r="EB34" t="s">
+      <c r="EB34" s="11" t="s">
         <v>870</v>
       </c>
       <c r="EC34" t="s">
@@ -22655,7 +22977,7 @@
       <c r="ED34" t="s">
         <v>872</v>
       </c>
-      <c r="EE34" t="s">
+      <c r="EE34" s="11" t="s">
         <v>873</v>
       </c>
       <c r="EF34" t="s">
@@ -22664,7 +22986,7 @@
       <c r="EG34" t="s">
         <v>875</v>
       </c>
-      <c r="EH34" t="s">
+      <c r="EH34" s="11" t="s">
         <v>876</v>
       </c>
       <c r="EI34" t="s">
@@ -22673,7 +22995,7 @@
       <c r="EJ34" t="s">
         <v>878</v>
       </c>
-      <c r="EK34" t="s">
+      <c r="EK34" s="11" t="s">
         <v>879</v>
       </c>
       <c r="EL34" t="s">
@@ -22682,7 +23004,7 @@
       <c r="EM34" t="s">
         <v>880</v>
       </c>
-      <c r="EN34" t="s">
+      <c r="EN34" s="11" t="s">
         <v>881</v>
       </c>
       <c r="EO34" t="s">
@@ -22691,7 +23013,7 @@
       <c r="EP34" t="s">
         <v>882</v>
       </c>
-      <c r="EQ34" t="s">
+      <c r="EQ34" s="11" t="s">
         <v>883</v>
       </c>
       <c r="ER34" t="s">
@@ -23328,7 +23650,7 @@
       <c r="DR35" t="s">
         <v>1547</v>
       </c>
-      <c r="DS35" s="1" t="s">
+      <c r="DS35" s="11" t="s">
         <v>1548</v>
       </c>
       <c r="DT35" s="1" t="s">
@@ -23337,7 +23659,7 @@
       <c r="DU35" t="s">
         <v>1549</v>
       </c>
-      <c r="DV35" t="s">
+      <c r="DV35" s="11" t="s">
         <v>1550</v>
       </c>
       <c r="DW35" t="s">
@@ -23346,7 +23668,7 @@
       <c r="DX35" t="s">
         <v>1551</v>
       </c>
-      <c r="DY35" t="s">
+      <c r="DY35" s="11" t="s">
         <v>1552</v>
       </c>
       <c r="DZ35" t="s">
@@ -23355,7 +23677,7 @@
       <c r="EA35" t="s">
         <v>1553</v>
       </c>
-      <c r="EB35" t="s">
+      <c r="EB35" s="11" t="s">
         <v>1560</v>
       </c>
       <c r="EC35" t="s">
@@ -23364,7 +23686,7 @@
       <c r="ED35" t="s">
         <v>1561</v>
       </c>
-      <c r="EE35" t="s">
+      <c r="EE35" s="11" t="s">
         <v>1554</v>
       </c>
       <c r="EF35" t="s">
@@ -23373,7 +23695,7 @@
       <c r="EG35" t="s">
         <v>1555</v>
       </c>
-      <c r="EH35" t="s">
+      <c r="EH35" s="11" t="s">
         <v>1556</v>
       </c>
       <c r="EI35" t="s">
@@ -23382,7 +23704,7 @@
       <c r="EJ35" t="s">
         <v>1557</v>
       </c>
-      <c r="EK35" t="s">
+      <c r="EK35" s="11" t="s">
         <v>1558</v>
       </c>
       <c r="EL35" t="s">
@@ -23391,7 +23713,7 @@
       <c r="EM35" t="s">
         <v>1559</v>
       </c>
-      <c r="EN35" t="s">
+      <c r="EN35" s="11" t="s">
         <v>1562</v>
       </c>
       <c r="EO35" t="s">
@@ -23400,7 +23722,7 @@
       <c r="EP35" t="s">
         <v>1563</v>
       </c>
-      <c r="EQ35" t="s">
+      <c r="EQ35" s="11" t="s">
         <v>1564</v>
       </c>
       <c r="ER35" t="s">
@@ -23986,7 +24308,7 @@
       <c r="DR36" t="s">
         <v>1112</v>
       </c>
-      <c r="DS36" t="s">
+      <c r="DS36" s="11" t="s">
         <v>1113</v>
       </c>
       <c r="DT36" t="s">
@@ -23995,7 +24317,7 @@
       <c r="DU36" t="s">
         <v>1114</v>
       </c>
-      <c r="DV36" t="s">
+      <c r="DV36" s="11" t="s">
         <v>1115</v>
       </c>
       <c r="DW36" t="s">
@@ -24004,7 +24326,7 @@
       <c r="DX36" t="s">
         <v>1116</v>
       </c>
-      <c r="DY36" t="s">
+      <c r="DY36" s="11" t="s">
         <v>1117</v>
       </c>
       <c r="DZ36" t="s">
@@ -24013,7 +24335,7 @@
       <c r="EA36" t="s">
         <v>1118</v>
       </c>
-      <c r="EB36" t="s">
+      <c r="EB36" s="11" t="s">
         <v>1119</v>
       </c>
       <c r="EC36" t="s">
@@ -24022,7 +24344,7 @@
       <c r="ED36" t="s">
         <v>1120</v>
       </c>
-      <c r="EE36" t="s">
+      <c r="EE36" s="11" t="s">
         <v>1121</v>
       </c>
       <c r="EF36" t="s">
@@ -24031,7 +24353,7 @@
       <c r="EG36" t="s">
         <v>1122</v>
       </c>
-      <c r="EH36" t="s">
+      <c r="EH36" s="11" t="s">
         <v>1123</v>
       </c>
       <c r="EI36" t="s">
@@ -24040,7 +24362,7 @@
       <c r="EJ36" t="s">
         <v>1124</v>
       </c>
-      <c r="EK36" t="s">
+      <c r="EK36" s="11" t="s">
         <v>1125</v>
       </c>
       <c r="EL36" t="s">
@@ -24049,7 +24371,7 @@
       <c r="EM36" t="s">
         <v>1126</v>
       </c>
-      <c r="EN36" t="s">
+      <c r="EN36" s="11" t="s">
         <v>1127</v>
       </c>
       <c r="EO36" t="s">
@@ -24058,7 +24380,7 @@
       <c r="EP36" t="s">
         <v>1128</v>
       </c>
-      <c r="EQ36" t="s">
+      <c r="EQ36" s="11" t="s">
         <v>1129</v>
       </c>
       <c r="ER36" t="s">
@@ -24569,7 +24891,7 @@
       <c r="DR37" t="s">
         <v>1001</v>
       </c>
-      <c r="DS37" t="s">
+      <c r="DS37" s="11" t="s">
         <v>1002</v>
       </c>
       <c r="DT37" t="s">
@@ -24578,7 +24900,7 @@
       <c r="DU37" t="s">
         <v>1003</v>
       </c>
-      <c r="DV37" t="s">
+      <c r="DV37" s="11" t="s">
         <v>1004</v>
       </c>
       <c r="DW37" t="s">
@@ -24587,7 +24909,7 @@
       <c r="DX37" t="s">
         <v>1005</v>
       </c>
-      <c r="DY37" t="s">
+      <c r="DY37" s="11" t="s">
         <v>1006</v>
       </c>
       <c r="DZ37" t="s">
@@ -24596,7 +24918,7 @@
       <c r="EA37" t="s">
         <v>1007</v>
       </c>
-      <c r="EB37" t="s">
+      <c r="EB37" s="11" t="s">
         <v>1008</v>
       </c>
       <c r="EC37" t="s">
@@ -24605,7 +24927,7 @@
       <c r="ED37" t="s">
         <v>1009</v>
       </c>
-      <c r="EE37" t="s">
+      <c r="EE37" s="11" t="s">
         <v>1010</v>
       </c>
       <c r="EF37" t="s">
@@ -24614,7 +24936,7 @@
       <c r="EG37" t="s">
         <v>1011</v>
       </c>
-      <c r="EH37" t="s">
+      <c r="EH37" s="11" t="s">
         <v>1012</v>
       </c>
       <c r="EI37" t="s">
@@ -24623,7 +24945,7 @@
       <c r="EJ37" t="s">
         <v>1013</v>
       </c>
-      <c r="EK37" t="s">
+      <c r="EK37" s="11" t="s">
         <v>1014</v>
       </c>
       <c r="EL37" t="s">
@@ -24632,7 +24954,7 @@
       <c r="EM37" t="s">
         <v>1015</v>
       </c>
-      <c r="EN37" t="s">
+      <c r="EN37" s="11" t="s">
         <v>1016</v>
       </c>
       <c r="EO37" t="s">
@@ -24641,7 +24963,7 @@
       <c r="EP37" t="s">
         <v>1017</v>
       </c>
-      <c r="EQ37" t="s">
+      <c r="EQ37" s="11" t="s">
         <v>1018</v>
       </c>
       <c r="ER37" t="s">
@@ -25149,7 +25471,7 @@
       <c r="DR38" t="s">
         <v>1522</v>
       </c>
-      <c r="DS38" t="s">
+      <c r="DS38" s="11" t="s">
         <v>1523</v>
       </c>
       <c r="DT38" t="s">
@@ -25158,7 +25480,7 @@
       <c r="DU38" t="s">
         <v>1524</v>
       </c>
-      <c r="DV38" t="s">
+      <c r="DV38" s="11" t="s">
         <v>1525</v>
       </c>
       <c r="DW38" t="s">
@@ -25167,7 +25489,7 @@
       <c r="DX38" t="s">
         <v>1526</v>
       </c>
-      <c r="DY38" t="s">
+      <c r="DY38" s="11" t="s">
         <v>1527</v>
       </c>
       <c r="DZ38" t="s">
@@ -25176,7 +25498,7 @@
       <c r="EA38" t="s">
         <v>1528</v>
       </c>
-      <c r="EB38" t="s">
+      <c r="EB38" s="11" t="s">
         <v>1529</v>
       </c>
       <c r="EC38" t="s">
@@ -25185,7 +25507,7 @@
       <c r="ED38" t="s">
         <v>1530</v>
       </c>
-      <c r="EE38" t="s">
+      <c r="EE38" s="11" t="s">
         <v>1531</v>
       </c>
       <c r="EF38" t="s">
@@ -25194,7 +25516,7 @@
       <c r="EG38" t="s">
         <v>1532</v>
       </c>
-      <c r="EH38" t="s">
+      <c r="EH38" s="11" t="s">
         <v>1533</v>
       </c>
       <c r="EI38" t="s">
@@ -25203,7 +25525,7 @@
       <c r="EJ38" t="s">
         <v>1534</v>
       </c>
-      <c r="EK38" t="s">
+      <c r="EK38" s="11" t="s">
         <v>1535</v>
       </c>
       <c r="EL38" t="s">
@@ -25212,7 +25534,7 @@
       <c r="EM38" t="s">
         <v>1536</v>
       </c>
-      <c r="EN38" t="s">
+      <c r="EN38" s="11" t="s">
         <v>1537</v>
       </c>
       <c r="EO38" t="s">
@@ -25729,7 +26051,7 @@
       <c r="DR39" t="s">
         <v>1213</v>
       </c>
-      <c r="DS39" s="1" t="s">
+      <c r="DS39" s="11" t="s">
         <v>1214</v>
       </c>
       <c r="DT39" s="1" t="s">
@@ -25738,7 +26060,7 @@
       <c r="DU39" t="s">
         <v>1215</v>
       </c>
-      <c r="DV39" t="s">
+      <c r="DV39" s="11" t="s">
         <v>1216</v>
       </c>
       <c r="DW39" t="s">
@@ -25747,7 +26069,7 @@
       <c r="DX39" t="s">
         <v>1217</v>
       </c>
-      <c r="DY39" t="s">
+      <c r="DY39" s="11" t="s">
         <v>1218</v>
       </c>
       <c r="DZ39" t="s">
@@ -25756,7 +26078,7 @@
       <c r="EA39" t="s">
         <v>1219</v>
       </c>
-      <c r="EB39" t="s">
+      <c r="EB39" s="11" t="s">
         <v>1220</v>
       </c>
       <c r="EC39" t="s">
@@ -25765,7 +26087,7 @@
       <c r="ED39" t="s">
         <v>1221</v>
       </c>
-      <c r="EE39" t="s">
+      <c r="EE39" s="11" t="s">
         <v>1222</v>
       </c>
       <c r="EF39" t="s">
@@ -25774,7 +26096,7 @@
       <c r="EG39" t="s">
         <v>1223</v>
       </c>
-      <c r="EH39" t="s">
+      <c r="EH39" s="11" t="s">
         <v>1224</v>
       </c>
       <c r="EI39" t="s">
@@ -25783,7 +26105,7 @@
       <c r="EJ39" t="s">
         <v>1225</v>
       </c>
-      <c r="EK39" t="s">
+      <c r="EK39" s="11" t="s">
         <v>1226</v>
       </c>
       <c r="EL39" t="s">
@@ -25792,13 +26114,13 @@
       <c r="EM39" t="s">
         <v>1227</v>
       </c>
-      <c r="EN39" t="s">
+      <c r="EN39" s="11" t="s">
         <v>1228</v>
       </c>
       <c r="EO39" t="s">
         <v>877</v>
       </c>
-      <c r="EQ39" t="s">
+      <c r="EQ39" s="11" t="s">
         <v>1229</v>
       </c>
       <c r="ER39" t="s">
@@ -26306,7 +26628,7 @@
       <c r="DR40" t="s">
         <v>1189</v>
       </c>
-      <c r="DS40" t="s">
+      <c r="DS40" s="11" t="s">
         <v>1188</v>
       </c>
       <c r="DT40" t="s">
@@ -26315,7 +26637,7 @@
       <c r="DU40" t="s">
         <v>1190</v>
       </c>
-      <c r="DV40" t="s">
+      <c r="DV40" s="11" t="s">
         <v>1191</v>
       </c>
       <c r="DW40" t="s">
@@ -26324,7 +26646,7 @@
       <c r="DX40" t="s">
         <v>1192</v>
       </c>
-      <c r="DY40" t="s">
+      <c r="DY40" s="11" t="s">
         <v>1193</v>
       </c>
       <c r="DZ40" t="s">
@@ -26333,7 +26655,7 @@
       <c r="EA40" t="s">
         <v>1194</v>
       </c>
-      <c r="EB40" t="s">
+      <c r="EB40" s="11" t="s">
         <v>1195</v>
       </c>
       <c r="EC40" t="s">
@@ -26342,7 +26664,7 @@
       <c r="ED40" t="s">
         <v>1196</v>
       </c>
-      <c r="EE40" t="s">
+      <c r="EE40" s="11" t="s">
         <v>1197</v>
       </c>
       <c r="EF40" t="s">
@@ -26351,7 +26673,7 @@
       <c r="EG40" t="s">
         <v>1198</v>
       </c>
-      <c r="EH40" t="s">
+      <c r="EH40" s="11" t="s">
         <v>1199</v>
       </c>
       <c r="EI40" t="s">
@@ -26360,7 +26682,7 @@
       <c r="EJ40" t="s">
         <v>1200</v>
       </c>
-      <c r="EK40" t="s">
+      <c r="EK40" s="11" t="s">
         <v>1201</v>
       </c>
       <c r="EL40" t="s">
@@ -26369,10 +26691,10 @@
       <c r="EM40" t="s">
         <v>1202</v>
       </c>
-      <c r="EN40" t="s">
+      <c r="EN40" s="11" t="s">
         <v>1203</v>
       </c>
-      <c r="EQ40" t="s">
+      <c r="EQ40" s="11" t="s">
         <v>1204</v>
       </c>
       <c r="ER40" t="s">
@@ -26620,7 +26942,7 @@
       <c r="C41" t="s">
         <v>948</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" s="1" t="s">
         <v>1398</v>
       </c>
       <c r="E41" t="s">
@@ -26877,7 +27199,7 @@
       <c r="DR41" t="s">
         <v>1405</v>
       </c>
-      <c r="DS41" t="s">
+      <c r="DS41" s="11" t="s">
         <v>1406</v>
       </c>
       <c r="DT41" t="s">
@@ -26886,7 +27208,7 @@
       <c r="DU41" t="s">
         <v>1407</v>
       </c>
-      <c r="DV41" t="s">
+      <c r="DV41" s="11" t="s">
         <v>1408</v>
       </c>
       <c r="DW41" t="s">
@@ -26895,7 +27217,7 @@
       <c r="DX41" t="s">
         <v>1409</v>
       </c>
-      <c r="DY41" t="s">
+      <c r="DY41" s="11" t="s">
         <v>1410</v>
       </c>
       <c r="DZ41" t="s">
@@ -26904,7 +27226,7 @@
       <c r="EA41" t="s">
         <v>1411</v>
       </c>
-      <c r="EB41" t="s">
+      <c r="EB41" s="11" t="s">
         <v>1412</v>
       </c>
       <c r="EC41" t="s">
@@ -26913,7 +27235,7 @@
       <c r="ED41" t="s">
         <v>1413</v>
       </c>
-      <c r="EE41" t="s">
+      <c r="EE41" s="11" t="s">
         <v>1414</v>
       </c>
       <c r="EF41" t="s">
@@ -26922,7 +27244,7 @@
       <c r="EG41" t="s">
         <v>1415</v>
       </c>
-      <c r="EH41" t="s">
+      <c r="EH41" s="11" t="s">
         <v>1416</v>
       </c>
       <c r="EI41" t="s">
@@ -26931,7 +27253,7 @@
       <c r="EJ41" t="s">
         <v>1417</v>
       </c>
-      <c r="EK41" t="s">
+      <c r="EK41" s="11" t="s">
         <v>1418</v>
       </c>
       <c r="EL41" t="s">
@@ -27185,7 +27507,7 @@
       <c r="C42" t="s">
         <v>948</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="1" t="s">
         <v>1490</v>
       </c>
       <c r="E42" t="s">
@@ -27442,7 +27764,7 @@
       <c r="DR42" t="s">
         <v>1497</v>
       </c>
-      <c r="DS42" s="1" t="s">
+      <c r="DS42" s="11" t="s">
         <v>1498</v>
       </c>
       <c r="DT42" s="1" t="s">
@@ -27451,7 +27773,7 @@
       <c r="DU42" t="s">
         <v>1499</v>
       </c>
-      <c r="DV42" t="s">
+      <c r="DV42" s="11" t="s">
         <v>1500</v>
       </c>
       <c r="DW42" t="s">
@@ -27460,7 +27782,7 @@
       <c r="DX42" t="s">
         <v>1501</v>
       </c>
-      <c r="DY42" t="s">
+      <c r="DY42" s="11" t="s">
         <v>1502</v>
       </c>
       <c r="DZ42" t="s">
@@ -27469,7 +27791,7 @@
       <c r="EA42" t="s">
         <v>1504</v>
       </c>
-      <c r="EB42" t="s">
+      <c r="EB42" s="11" t="s">
         <v>1512</v>
       </c>
       <c r="EC42" t="s">
@@ -27478,7 +27800,7 @@
       <c r="ED42" t="s">
         <v>1513</v>
       </c>
-      <c r="EE42" t="s">
+      <c r="EE42" s="11" t="s">
         <v>1505</v>
       </c>
       <c r="EF42" t="s">
@@ -27487,7 +27809,7 @@
       <c r="EG42" t="s">
         <v>1506</v>
       </c>
-      <c r="EH42" t="s">
+      <c r="EH42" s="11" t="s">
         <v>1507</v>
       </c>
       <c r="EI42" t="s">
@@ -27496,7 +27818,7 @@
       <c r="EJ42" t="s">
         <v>1508</v>
       </c>
-      <c r="EK42" t="s">
+      <c r="EK42" s="11" t="s">
         <v>1509</v>
       </c>
       <c r="EL42" t="s">
@@ -27505,10 +27827,10 @@
       <c r="EM42" t="s">
         <v>1510</v>
       </c>
-      <c r="EN42" t="s">
+      <c r="EN42" s="11" t="s">
         <v>1511</v>
       </c>
-      <c r="EQ42" t="s">
+      <c r="EQ42" s="11" t="s">
         <v>1514</v>
       </c>
       <c r="ER42" t="s">
@@ -27759,7 +28081,7 @@
       <c r="C43" t="s">
         <v>948</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" s="1" t="s">
         <v>1278</v>
       </c>
       <c r="E43" t="s">
@@ -28019,7 +28341,7 @@
       <c r="DR43" t="s">
         <v>1282</v>
       </c>
-      <c r="DS43" t="s">
+      <c r="DS43" s="11" t="s">
         <v>1284</v>
       </c>
       <c r="DT43" t="s">
@@ -28028,7 +28350,7 @@
       <c r="DU43" t="s">
         <v>1285</v>
       </c>
-      <c r="DV43" t="s">
+      <c r="DV43" s="11" t="s">
         <v>1286</v>
       </c>
       <c r="DW43" t="s">
@@ -28037,7 +28359,7 @@
       <c r="DX43" t="s">
         <v>1287</v>
       </c>
-      <c r="DY43" t="s">
+      <c r="DY43" s="11" t="s">
         <v>1288</v>
       </c>
       <c r="DZ43" t="s">
@@ -28046,7 +28368,7 @@
       <c r="EA43" t="s">
         <v>1289</v>
       </c>
-      <c r="EB43" t="s">
+      <c r="EB43" s="11" t="s">
         <v>1290</v>
       </c>
       <c r="EC43" t="s">
@@ -28055,7 +28377,7 @@
       <c r="ED43" t="s">
         <v>1291</v>
       </c>
-      <c r="EE43" t="s">
+      <c r="EE43" s="11" t="s">
         <v>1292</v>
       </c>
       <c r="EF43" t="s">
@@ -28064,7 +28386,7 @@
       <c r="EG43" t="s">
         <v>1293</v>
       </c>
-      <c r="EH43" t="s">
+      <c r="EH43" s="11" t="s">
         <v>1294</v>
       </c>
       <c r="EI43" t="s">
@@ -28073,7 +28395,7 @@
       <c r="EJ43" t="s">
         <v>1295</v>
       </c>
-      <c r="EK43" t="s">
+      <c r="EK43" s="11" t="s">
         <v>1296</v>
       </c>
       <c r="EL43" t="s">
@@ -28082,7 +28404,7 @@
       <c r="EM43" t="s">
         <v>1297</v>
       </c>
-      <c r="EN43" t="s">
+      <c r="EN43" s="11" t="s">
         <v>1298</v>
       </c>
       <c r="EO43" t="s">
@@ -28091,7 +28413,7 @@
       <c r="EP43" t="s">
         <v>1299</v>
       </c>
-      <c r="EQ43" t="s">
+      <c r="EQ43" s="11" t="s">
         <v>1300</v>
       </c>
       <c r="ER43" t="s">
@@ -28369,33 +28691,252 @@
       <c r="A44">
         <v>42</v>
       </c>
+      <c r="B44" t="s">
+        <v>552</v>
+      </c>
+      <c r="C44" t="s">
+        <v>1923</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>1900</v>
+      </c>
+      <c r="E44" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G44" t="s">
+        <v>1902</v>
+      </c>
+      <c r="H44" t="s">
+        <v>1903</v>
+      </c>
+      <c r="I44" t="s">
+        <v>1904</v>
+      </c>
+      <c r="J44">
+        <v>2028</v>
+      </c>
+      <c r="K44" t="s">
+        <v>996</v>
+      </c>
+      <c r="L44" t="s">
+        <v>1905</v>
+      </c>
+      <c r="M44" t="s">
+        <v>424</v>
+      </c>
+      <c r="N44" t="s">
+        <v>424</v>
+      </c>
+      <c r="O44">
+        <v>72590</v>
+      </c>
+      <c r="P44" t="s">
+        <v>1906</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>1907</v>
+      </c>
+      <c r="R44">
+        <v>10</v>
+      </c>
+      <c r="S44" t="s">
+        <v>1908</v>
+      </c>
+      <c r="V44">
+        <v>259</v>
+      </c>
+      <c r="W44">
+        <v>259</v>
+      </c>
+      <c r="X44">
+        <v>1</v>
+      </c>
+      <c r="Y44">
+        <v>1</v>
+      </c>
+      <c r="Z44">
+        <v>1</v>
+      </c>
+      <c r="AA44">
+        <v>1</v>
+      </c>
+      <c r="AB44">
+        <v>0</v>
+      </c>
+      <c r="AC44">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="s">
+        <v>1909</v>
+      </c>
+      <c r="AE44" t="s">
+        <v>1923</v>
+      </c>
+      <c r="AF44" t="s">
+        <v>1923</v>
+      </c>
+      <c r="AG44">
+        <v>5</v>
+      </c>
+      <c r="AH44">
+        <v>0</v>
+      </c>
+      <c r="AI44">
+        <v>3</v>
+      </c>
+      <c r="AJ44">
+        <v>2</v>
+      </c>
+      <c r="AK44">
+        <v>0</v>
+      </c>
+      <c r="AL44">
+        <v>0</v>
+      </c>
+      <c r="AM44">
+        <v>1</v>
+      </c>
+      <c r="AN44">
+        <v>7</v>
+      </c>
+      <c r="AO44">
+        <v>4</v>
+      </c>
+      <c r="AP44" t="s">
+        <v>1910</v>
+      </c>
+      <c r="AQ44" t="s">
+        <v>1911</v>
+      </c>
       <c r="AR44" s="4">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="AS44">
+        <v>1</v>
+      </c>
+      <c r="AT44" t="s">
+        <v>1912</v>
+      </c>
+      <c r="AU44">
+        <v>2</v>
+      </c>
+      <c r="AV44" t="s">
+        <v>1913</v>
+      </c>
+      <c r="AW44">
+        <v>2</v>
+      </c>
+      <c r="BE44">
+        <v>1</v>
+      </c>
+      <c r="BF44" t="s">
+        <v>1914</v>
+      </c>
+      <c r="BG44">
+        <v>1</v>
+      </c>
+      <c r="BI44" t="s">
+        <v>1912</v>
+      </c>
+      <c r="BN44">
+        <v>3</v>
+      </c>
+      <c r="BP44">
+        <v>1</v>
+      </c>
+      <c r="BR44">
+        <v>1</v>
+      </c>
+      <c r="BS44">
+        <v>1</v>
+      </c>
+      <c r="BT44">
+        <v>1</v>
       </c>
       <c r="BU44" s="4">
         <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="BV44">
+        <v>1</v>
+      </c>
+      <c r="DG44">
+        <v>10</v>
+      </c>
+      <c r="DH44" t="s">
+        <v>1915</v>
+      </c>
+      <c r="DI44">
+        <v>2024</v>
+      </c>
+      <c r="DJ44" t="s">
+        <v>1916</v>
+      </c>
+      <c r="DK44" t="s">
+        <v>438</v>
+      </c>
+      <c r="DL44" t="s">
+        <v>1904</v>
+      </c>
+      <c r="DM44" t="s">
+        <v>1917</v>
+      </c>
+      <c r="DN44" t="s">
+        <v>555</v>
+      </c>
+      <c r="DP44" t="s">
+        <v>442</v>
+      </c>
+      <c r="DQ44" t="s">
+        <v>443</v>
+      </c>
+      <c r="DS44" s="11" t="s">
+        <v>1918</v>
+      </c>
+      <c r="DV44" s="11" t="s">
+        <v>1919</v>
+      </c>
+      <c r="EB44" s="11" t="s">
+        <v>1920</v>
+      </c>
+      <c r="EH44" s="11" t="s">
+        <v>1921</v>
+      </c>
+      <c r="EU44">
         <v>0</v>
       </c>
       <c r="EV44" s="4">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
+      <c r="EX44">
+        <v>0</v>
+      </c>
       <c r="EY44" s="4">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
+      <c r="FA44">
+        <v>0</v>
+      </c>
       <c r="FB44" s="4">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
+      <c r="FC44" t="s">
+        <v>1922</v>
+      </c>
+      <c r="FD44">
+        <v>1000</v>
+      </c>
       <c r="FE44" s="4">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="FF44" s="4">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="FG44" s="4" t="str">
         <f t="shared" si="20"/>
@@ -28406,33 +28947,247 @@
       <c r="A45">
         <v>43</v>
       </c>
+      <c r="B45" t="s">
+        <v>552</v>
+      </c>
+      <c r="C45" t="s">
+        <v>1924</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>1925</v>
+      </c>
+      <c r="E45" t="s">
+        <v>1926</v>
+      </c>
+      <c r="G45" t="s">
+        <v>1927</v>
+      </c>
+      <c r="H45" t="s">
+        <v>1928</v>
+      </c>
+      <c r="I45" t="s">
+        <v>1929</v>
+      </c>
+      <c r="J45">
+        <v>206</v>
+      </c>
+      <c r="K45" s="10"/>
+      <c r="L45" t="s">
+        <v>422</v>
+      </c>
+      <c r="M45" t="s">
+        <v>1930</v>
+      </c>
+      <c r="N45" t="s">
+        <v>424</v>
+      </c>
+      <c r="O45">
+        <v>75200</v>
+      </c>
+      <c r="P45">
+        <v>2231080462</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>1931</v>
+      </c>
+      <c r="R45">
+        <v>45</v>
+      </c>
+      <c r="S45" t="s">
+        <v>1932</v>
+      </c>
+      <c r="V45">
+        <v>933</v>
+      </c>
+      <c r="W45">
+        <v>933</v>
+      </c>
+      <c r="X45">
+        <v>2</v>
+      </c>
+      <c r="Y45">
+        <v>2</v>
+      </c>
+      <c r="Z45">
+        <v>1</v>
+      </c>
+      <c r="AA45">
+        <v>1</v>
+      </c>
+      <c r="AB45">
+        <v>3</v>
+      </c>
+      <c r="AC45">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="s">
+        <v>1933</v>
+      </c>
+      <c r="AE45" t="s">
+        <v>1934</v>
+      </c>
+      <c r="AF45" t="s">
+        <v>1934</v>
+      </c>
+      <c r="AG45">
+        <v>6</v>
+      </c>
+      <c r="AH45">
+        <v>0</v>
+      </c>
+      <c r="AI45">
+        <v>4</v>
+      </c>
+      <c r="AJ45">
+        <v>2</v>
+      </c>
+      <c r="AK45">
+        <v>0</v>
+      </c>
+      <c r="AL45">
+        <v>0</v>
+      </c>
+      <c r="AM45">
+        <v>1</v>
+      </c>
+      <c r="AN45">
+        <v>20</v>
+      </c>
+      <c r="AO45">
+        <v>3</v>
+      </c>
+      <c r="AP45" t="s">
+        <v>1910</v>
+      </c>
+      <c r="AQ45" t="s">
+        <v>1935</v>
+      </c>
       <c r="AR45" s="4">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="AU45">
+        <v>4</v>
+      </c>
+      <c r="AV45" t="s">
+        <v>1936</v>
+      </c>
+      <c r="AW45">
+        <v>4</v>
+      </c>
+      <c r="BE45">
+        <v>1</v>
+      </c>
+      <c r="BF45" t="s">
+        <v>754</v>
+      </c>
+      <c r="BI45" t="s">
+        <v>755</v>
+      </c>
+      <c r="BN45">
+        <v>10</v>
+      </c>
+      <c r="BP45">
+        <v>1</v>
+      </c>
+      <c r="BR45">
+        <v>1</v>
+      </c>
+      <c r="BS45">
+        <v>1</v>
+      </c>
+      <c r="BT45">
+        <v>3</v>
       </c>
       <c r="BU45" s="4">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BV45">
+        <v>1</v>
+      </c>
+      <c r="DG45">
+        <v>8</v>
+      </c>
+      <c r="DH45" t="s">
+        <v>1915</v>
+      </c>
+      <c r="DI45">
+        <v>2024</v>
+      </c>
+      <c r="DJ45" t="s">
+        <v>1937</v>
+      </c>
+      <c r="DK45" t="s">
+        <v>438</v>
+      </c>
+      <c r="DL45" t="s">
+        <v>1929</v>
+      </c>
+      <c r="DM45" t="s">
+        <v>820</v>
+      </c>
+      <c r="DN45" t="s">
+        <v>820</v>
+      </c>
+      <c r="DP45" t="s">
+        <v>442</v>
+      </c>
+      <c r="DQ45" t="s">
+        <v>443</v>
+      </c>
+      <c r="DS45" s="11" t="s">
+        <v>1938</v>
+      </c>
+      <c r="DV45" s="11" t="s">
+        <v>1940</v>
+      </c>
+      <c r="EB45" s="11" t="s">
+        <v>1941</v>
+      </c>
+      <c r="EH45" s="11" t="s">
+        <v>1939</v>
+      </c>
+      <c r="EN45" s="11" t="s">
+        <v>1942</v>
+      </c>
+      <c r="ET45" t="s">
+        <v>1943</v>
+      </c>
+      <c r="EU45">
+        <v>30</v>
       </c>
       <c r="EV45" s="4">
         <f t="shared" si="15"/>
+        <v>0.01</v>
+      </c>
+      <c r="EX45">
         <v>0</v>
       </c>
       <c r="EY45" s="4">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
+      <c r="FA45">
+        <v>0</v>
+      </c>
       <c r="FB45" s="4">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
+      <c r="FC45" t="s">
+        <v>455</v>
+      </c>
+      <c r="FD45">
+        <v>7000</v>
+      </c>
       <c r="FE45" s="4">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>0.46666666666666667</v>
       </c>
       <c r="FF45" s="4">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>0.47666666666666668</v>
       </c>
       <c r="FG45" s="4" t="str">
         <f t="shared" si="20"/>
@@ -28443,33 +29198,258 @@
       <c r="A46">
         <v>44</v>
       </c>
+      <c r="B46" t="s">
+        <v>552</v>
+      </c>
+      <c r="C46" t="s">
+        <v>1944</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>1945</v>
+      </c>
+      <c r="E46" t="s">
+        <v>1946</v>
+      </c>
+      <c r="G46" t="s">
+        <v>1947</v>
+      </c>
+      <c r="H46" t="s">
+        <v>1968</v>
+      </c>
+      <c r="I46" t="s">
+        <v>1929</v>
+      </c>
+      <c r="J46">
+        <v>150</v>
+      </c>
+      <c r="K46" t="s">
+        <v>1948</v>
+      </c>
+      <c r="L46" t="s">
+        <v>422</v>
+      </c>
+      <c r="M46" t="s">
+        <v>1930</v>
+      </c>
+      <c r="N46" t="s">
+        <v>424</v>
+      </c>
+      <c r="O46">
+        <v>75700</v>
+      </c>
+      <c r="P46">
+        <v>2223718725</v>
+      </c>
+      <c r="Q46" s="3" t="s">
+        <v>1949</v>
+      </c>
+      <c r="R46">
+        <v>31</v>
+      </c>
+      <c r="S46" t="s">
+        <v>1950</v>
+      </c>
+      <c r="V46">
+        <v>231.96</v>
+      </c>
+      <c r="W46">
+        <v>231.96</v>
+      </c>
+      <c r="X46">
+        <v>1</v>
+      </c>
+      <c r="Y46">
+        <v>2</v>
+      </c>
+      <c r="Z46">
+        <v>1</v>
+      </c>
+      <c r="AA46">
+        <v>1</v>
+      </c>
+      <c r="AB46">
+        <v>1</v>
+      </c>
+      <c r="AC46">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="s">
+        <v>850</v>
+      </c>
+      <c r="AE46" t="s">
+        <v>1951</v>
+      </c>
+      <c r="AF46" t="s">
+        <v>1952</v>
+      </c>
+      <c r="AG46">
+        <v>8</v>
+      </c>
+      <c r="AH46">
+        <v>0</v>
+      </c>
+      <c r="AI46">
+        <v>2</v>
+      </c>
+      <c r="AJ46">
+        <v>6</v>
+      </c>
+      <c r="AK46">
+        <v>0</v>
+      </c>
+      <c r="AL46">
+        <v>0</v>
+      </c>
+      <c r="AM46">
+        <v>2</v>
+      </c>
+      <c r="AN46">
+        <v>200</v>
+      </c>
+      <c r="AO46">
+        <v>4</v>
+      </c>
+      <c r="AP46" t="s">
+        <v>430</v>
+      </c>
+      <c r="AQ46" t="s">
+        <v>1969</v>
+      </c>
       <c r="AR46" s="4">
         <f t="shared" ref="AR46:AR77" si="21">+AS46+AU46+BE46+BN46+BO46+BP46+BQ46+BR46+BS46+CG46</f>
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="AS46">
+        <v>1</v>
+      </c>
+      <c r="AT46" t="s">
+        <v>1954</v>
+      </c>
+      <c r="AU46">
+        <v>2</v>
+      </c>
+      <c r="AV46" t="s">
+        <v>1953</v>
+      </c>
+      <c r="AW46">
+        <v>2</v>
+      </c>
+      <c r="BL46">
+        <v>5</v>
+      </c>
+      <c r="BM46" t="s">
+        <v>1955</v>
+      </c>
+      <c r="BN46">
+        <v>6</v>
+      </c>
+      <c r="BP46">
+        <v>1</v>
+      </c>
+      <c r="BQ46">
+        <v>1</v>
+      </c>
+      <c r="BS46">
+        <v>2</v>
+      </c>
+      <c r="BT46">
+        <v>1</v>
       </c>
       <c r="BU46" s="4">
         <f t="shared" ref="BU46:BU77" si="22">+BV46+BX46+BY46+BZ46+CA46</f>
+        <v>2</v>
+      </c>
+      <c r="BV46">
+        <v>2</v>
+      </c>
+      <c r="DG46">
+        <v>21</v>
+      </c>
+      <c r="DH46" t="s">
+        <v>542</v>
+      </c>
+      <c r="DI46">
+        <v>2024</v>
+      </c>
+      <c r="DJ46" t="s">
+        <v>1956</v>
+      </c>
+      <c r="DK46" t="s">
+        <v>1929</v>
+      </c>
+      <c r="DL46" t="s">
+        <v>1957</v>
+      </c>
+      <c r="DM46" t="s">
+        <v>1958</v>
+      </c>
+      <c r="DN46" t="s">
+        <v>1959</v>
+      </c>
+      <c r="DP46" t="s">
+        <v>442</v>
+      </c>
+      <c r="DQ46" t="s">
+        <v>443</v>
+      </c>
+      <c r="DS46" s="11" t="s">
+        <v>1960</v>
+      </c>
+      <c r="DV46" s="11" t="s">
+        <v>1961</v>
+      </c>
+      <c r="DY46" s="11" t="s">
+        <v>1962</v>
+      </c>
+      <c r="EB46" s="11" t="s">
+        <v>1963</v>
+      </c>
+      <c r="EE46" t="s">
+        <v>1964</v>
+      </c>
+      <c r="EH46" t="s">
+        <v>1965</v>
+      </c>
+      <c r="EK46" t="s">
+        <v>1966</v>
+      </c>
+      <c r="EU46">
         <v>0</v>
       </c>
       <c r="EV46" s="4">
         <f t="shared" ref="EV46:EV77" si="23">+EU46/3000</f>
         <v>0</v>
       </c>
+      <c r="EW46" t="s">
+        <v>1967</v>
+      </c>
+      <c r="EX46">
+        <v>272</v>
+      </c>
       <c r="EY46" s="4">
         <f t="shared" ref="EY46:EY77" si="24">+EX46/1400</f>
+        <v>0.19428571428571428</v>
+      </c>
+      <c r="FA46">
         <v>0</v>
       </c>
       <c r="FB46" s="4">
         <f t="shared" ref="FB46:FB77" si="25">+FA46/2000</f>
         <v>0</v>
       </c>
+      <c r="FC46" t="s">
+        <v>455</v>
+      </c>
+      <c r="FD46">
+        <v>500</v>
+      </c>
       <c r="FE46" s="4">
         <f t="shared" ref="FE46:FE77" si="26">+FD46/15000</f>
-        <v>0</v>
+        <v>3.3333333333333333E-2</v>
       </c>
       <c r="FF46" s="4">
         <f t="shared" ref="FF46:FF77" si="27">+EV46+EY46+FB46+FE46</f>
-        <v>0</v>
+        <v>0.22761904761904761</v>
       </c>
       <c r="FG46" s="4" t="str">
         <f t="shared" ref="FG46:FG77" si="28">+IF((EV46+EY46+FB46+FE46)&gt;=1,"ALTO","ORDINARIO")</f>
@@ -28480,6 +29460,72 @@
       <c r="A47">
         <v>45</v>
       </c>
+      <c r="B47" t="s">
+        <v>1891</v>
+      </c>
+      <c r="C47" t="s">
+        <v>1971</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>1972</v>
+      </c>
+      <c r="E47" t="s">
+        <v>1973</v>
+      </c>
+      <c r="G47" t="s">
+        <v>1974</v>
+      </c>
+      <c r="I47" t="s">
+        <v>1975</v>
+      </c>
+      <c r="J47">
+        <v>22</v>
+      </c>
+      <c r="L47" t="s">
+        <v>422</v>
+      </c>
+      <c r="M47" t="s">
+        <v>1976</v>
+      </c>
+      <c r="N47" t="s">
+        <v>1977</v>
+      </c>
+      <c r="O47">
+        <v>70600</v>
+      </c>
+      <c r="P47" t="s">
+        <v>1978</v>
+      </c>
+      <c r="R47">
+        <v>33</v>
+      </c>
+      <c r="S47" s="12">
+        <v>39264</v>
+      </c>
+      <c r="V47">
+        <v>612.16999999999996</v>
+      </c>
+      <c r="W47">
+        <v>194.03</v>
+      </c>
+      <c r="Y47">
+        <v>2</v>
+      </c>
+      <c r="AE47" t="s">
+        <v>1979</v>
+      </c>
+      <c r="AF47" t="s">
+        <v>1980</v>
+      </c>
+      <c r="AG47">
+        <v>28</v>
+      </c>
+      <c r="AN47">
+        <v>20</v>
+      </c>
+      <c r="AQ47" t="s">
+        <v>1981</v>
+      </c>
       <c r="AR47" s="4">
         <f t="shared" si="21"/>
         <v>0</v>
@@ -28487,6 +29533,36 @@
       <c r="BU47" s="4">
         <f t="shared" si="22"/>
         <v>0</v>
+      </c>
+      <c r="DC47" t="s">
+        <v>1982</v>
+      </c>
+      <c r="DG47">
+        <v>19</v>
+      </c>
+      <c r="DH47" t="s">
+        <v>1915</v>
+      </c>
+      <c r="DI47">
+        <v>2024</v>
+      </c>
+      <c r="DJ47" t="s">
+        <v>1983</v>
+      </c>
+      <c r="DK47" t="s">
+        <v>1984</v>
+      </c>
+      <c r="DL47" t="s">
+        <v>1985</v>
+      </c>
+      <c r="DM47" t="s">
+        <v>1986</v>
+      </c>
+      <c r="DN47" t="s">
+        <v>1987</v>
+      </c>
+      <c r="DO47" t="s">
+        <v>1988</v>
       </c>
       <c r="EV47" s="4">
         <f t="shared" si="23"/>
@@ -28517,6 +29593,48 @@
       <c r="A48">
         <v>46</v>
       </c>
+      <c r="B48" t="s">
+        <v>1891</v>
+      </c>
+      <c r="C48" t="s">
+        <v>1971</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>1989</v>
+      </c>
+      <c r="E48" t="s">
+        <v>1973</v>
+      </c>
+      <c r="G48" t="s">
+        <v>1974</v>
+      </c>
+      <c r="I48" t="s">
+        <v>1990</v>
+      </c>
+      <c r="J48">
+        <v>35</v>
+      </c>
+      <c r="K48" t="s">
+        <v>849</v>
+      </c>
+      <c r="L48" t="s">
+        <v>1991</v>
+      </c>
+      <c r="M48" t="s">
+        <v>1992</v>
+      </c>
+      <c r="N48" t="s">
+        <v>1977</v>
+      </c>
+      <c r="O48">
+        <v>70760</v>
+      </c>
+      <c r="AG48">
+        <v>25</v>
+      </c>
+      <c r="AN48">
+        <v>15</v>
+      </c>
       <c r="AR48" s="4">
         <f t="shared" si="21"/>
         <v>0</v>
@@ -28524,6 +29642,15 @@
       <c r="BU48" s="4">
         <f t="shared" si="22"/>
         <v>0</v>
+      </c>
+      <c r="DG48">
+        <v>18</v>
+      </c>
+      <c r="DH48" t="s">
+        <v>1915</v>
+      </c>
+      <c r="DI48">
+        <v>2024</v>
       </c>
       <c r="EV48" s="4">
         <f t="shared" si="23"/>
@@ -28554,6 +29681,45 @@
       <c r="A49">
         <v>47</v>
       </c>
+      <c r="B49" t="s">
+        <v>1891</v>
+      </c>
+      <c r="C49" t="s">
+        <v>1971</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>1993</v>
+      </c>
+      <c r="E49" t="s">
+        <v>1973</v>
+      </c>
+      <c r="G49" t="s">
+        <v>1974</v>
+      </c>
+      <c r="I49" t="s">
+        <v>1994</v>
+      </c>
+      <c r="J49">
+        <v>75</v>
+      </c>
+      <c r="L49" t="s">
+        <v>1995</v>
+      </c>
+      <c r="M49" t="s">
+        <v>1996</v>
+      </c>
+      <c r="N49" t="s">
+        <v>1977</v>
+      </c>
+      <c r="O49">
+        <v>70000</v>
+      </c>
+      <c r="AG49">
+        <v>27</v>
+      </c>
+      <c r="AN49">
+        <v>100</v>
+      </c>
       <c r="AR49" s="4">
         <f t="shared" si="21"/>
         <v>0</v>
@@ -28561,6 +29727,15 @@
       <c r="BU49" s="4">
         <f t="shared" si="22"/>
         <v>0</v>
+      </c>
+      <c r="DG49">
+        <v>17</v>
+      </c>
+      <c r="DH49" t="s">
+        <v>1915</v>
+      </c>
+      <c r="DI49">
+        <v>2024</v>
       </c>
       <c r="EV49" s="4">
         <f t="shared" si="23"/>
@@ -28591,6 +29766,45 @@
       <c r="A50">
         <v>48</v>
       </c>
+      <c r="B50" t="s">
+        <v>1891</v>
+      </c>
+      <c r="C50" t="s">
+        <v>1971</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>1997</v>
+      </c>
+      <c r="E50" t="s">
+        <v>1973</v>
+      </c>
+      <c r="G50" t="s">
+        <v>1974</v>
+      </c>
+      <c r="I50" t="s">
+        <v>1998</v>
+      </c>
+      <c r="J50">
+        <v>302</v>
+      </c>
+      <c r="L50" t="s">
+        <v>422</v>
+      </c>
+      <c r="M50" t="s">
+        <v>1999</v>
+      </c>
+      <c r="N50" t="s">
+        <v>1977</v>
+      </c>
+      <c r="O50">
+        <v>70300</v>
+      </c>
+      <c r="AG50">
+        <v>31</v>
+      </c>
+      <c r="AN50">
+        <v>10</v>
+      </c>
       <c r="AR50" s="4">
         <f t="shared" si="21"/>
         <v>0</v>
@@ -28598,6 +29812,15 @@
       <c r="BU50" s="4">
         <f t="shared" si="22"/>
         <v>0</v>
+      </c>
+      <c r="DG50">
+        <v>16</v>
+      </c>
+      <c r="DH50" t="s">
+        <v>1915</v>
+      </c>
+      <c r="DI50">
+        <v>2024</v>
       </c>
       <c r="EV50" s="4">
         <f t="shared" si="23"/>
@@ -34322,9 +35545,9 @@
       <formula>#REF!=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B201" xr:uid="{41C0D522-5D90-43F5-9DB3-E0F81FDE0774}">
-      <formula1>"BANCO, BBVA, GASOLINERA, GENERAL, GDL"</formula1>
+      <formula1>"BANCO, BBVA, COMPARTAMOS, GASOLINERA, GENERAL, GDL"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -34358,16 +35581,19 @@
     <hyperlink ref="Q24" r:id="rId28" xr:uid="{5F9561E0-F04E-4138-9F17-72093CC7A3C0}"/>
     <hyperlink ref="Q23" r:id="rId29" xr:uid="{451E82E8-3F55-4F80-A080-6E168E11EF8A}"/>
     <hyperlink ref="Q13" r:id="rId30" xr:uid="{2032BBE1-31DA-46EE-AC48-65C122EE0282}"/>
+    <hyperlink ref="Q44" r:id="rId31" xr:uid="{A2BBFE7A-BA9E-492E-AF1D-D4A45C7C4B60}"/>
+    <hyperlink ref="Q45" r:id="rId32" xr:uid="{2BE003B8-9D85-4724-A606-402C9915F18E}"/>
+    <hyperlink ref="Q46" r:id="rId33" xr:uid="{2B09FFA2-5189-4D4D-A65B-4B15422C7C5B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId31"/>
-  <legacyDrawing r:id="rId32"/>
+  <drawing r:id="rId34"/>
+  <legacyDrawing r:id="rId35"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x14">
       <controls>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1025" r:id="rId33" name="Spinner 1">
+            <control shapeId="1025" r:id="rId36" name="Spinner 1">
               <controlPr defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
@@ -34401,7 +35627,7 @@
     <row r="1" spans="1:273" x14ac:dyDescent="0.3">
       <c r="A1">
         <f>+BD!A1</f>
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="B1" t="s">
         <v>134</v>
@@ -35223,19 +36449,19 @@
     <row r="2" spans="1:273" x14ac:dyDescent="0.3">
       <c r="B2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,2, FALSE)</f>
-        <v>BBVA</v>
+        <v>COMPARTAMOS</v>
       </c>
       <c r="C2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,3, FALSE)</f>
-        <v>BBVA MEXICO S.A. INSTITUCION DE BANCA MULTIPLE GRUPO FINANCIERO BBVA MEXICO</v>
+        <v>BANCO COMPARTAMOS S.A INSTITUCION DE BANCA MULTIPLE</v>
       </c>
       <c r="D2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,4, FALSE)</f>
-        <v>CR 2256 HIPOTECARIA NORTE PUEBLA</v>
+        <v>SUCURSAL MATIAS ROMERO CEMENTERA</v>
       </c>
       <c r="E2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,5, FALSE)</f>
-        <v>BBA 830831 LJ2</v>
+        <v>BCI001030ECA</v>
       </c>
       <c r="F2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,6, FALSE)</f>
@@ -35243,43 +36469,43 @@
       </c>
       <c r="G2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,7, FALSE)</f>
-        <v>BANCO</v>
-      </c>
-      <c r="H2" t="str">
+        <v>SERVICIOS FINANCIEROS</v>
+      </c>
+      <c r="H2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,8, FALSE)</f>
-        <v>INTERMEDIACIÓN FINANCIERA, GESTIÓN DE CUENTAS Y TRANSACCIONES, PRÉSTAMOS Y CRÉDITOS, SERVICIOS DE INVERSIÓN, ASESORAMIENTO FINANCIERO Y CUMPLIMIENTO DE REGULACIONES BANCARIAS</v>
+        <v>0</v>
       </c>
       <c r="I2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,9, FALSE)</f>
-        <v>CALZADA ZAVALETA</v>
+        <v>CORREGIDORA SUR</v>
       </c>
       <c r="J2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,10, FALSE)</f>
-        <v>3920</v>
+        <v>302</v>
       </c>
       <c r="K2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,11, FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,12, FALSE)</f>
-        <v>SANTA CRUZ BUENA VISTA</v>
+        <v>CENTRO</v>
       </c>
       <c r="M2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,13, FALSE)</f>
-        <v>PUEBLA</v>
+        <v>MATIAS ROMERO AVEDAÑO</v>
       </c>
       <c r="N2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,14, FALSE)</f>
-        <v>PUEBLA</v>
+        <v>OAXACA</v>
       </c>
       <c r="O2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,15, FALSE)</f>
-        <v>72150</v>
+        <v>70300</v>
       </c>
       <c r="P2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,16, FALSE)</f>
-        <v>2222231030</v>
+        <v>0</v>
       </c>
       <c r="Q2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,17, FALSE)</f>
@@ -35287,67 +36513,67 @@
       </c>
       <c r="R2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,18, FALSE)</f>
-        <v>8</v>
-      </c>
-      <c r="S2" t="str">
+        <v>0</v>
+      </c>
+      <c r="S2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,19, FALSE)</f>
-        <v>29 DE JULIO DE 2016</v>
-      </c>
-      <c r="T2" t="str">
+        <v>0</v>
+      </c>
+      <c r="T2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,20, FALSE)</f>
-        <v>REG. PROTECCION CIVIL TERCER ACREDITADO</v>
-      </c>
-      <c r="U2" t="str">
+        <v>0</v>
+      </c>
+      <c r="U2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,21, FALSE)</f>
-        <v>SGyDU-DGRPC-PREGIR-8/2024</v>
+        <v>0</v>
       </c>
       <c r="V2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,22, FALSE)</f>
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="W2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,23, FALSE)</f>
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="X2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,24, FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="Y2" t="str">
+        <v>0</v>
+      </c>
+      <c r="Y2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,25, FALSE)</f>
-        <v>PRIMER PISO</v>
+        <v>0</v>
       </c>
       <c r="Z2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,26, FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,27, FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,28, FALSE)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,29, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AD2" t="str">
+      <c r="AD2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,30, FALSE)</f>
-        <v>5 CAJONES</v>
-      </c>
-      <c r="AE2" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,31, FALSE)</f>
-        <v>EDUARDO NAVA DEVEAUX</v>
-      </c>
-      <c r="AF2" t="str">
+        <v>0</v>
+      </c>
+      <c r="AF2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,32, FALSE)</f>
-        <v>GABRIELA GUADARRAMA ISLAS</v>
+        <v>0</v>
       </c>
       <c r="AG2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,33, FALSE)</f>
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="AH2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,34, FALSE)</f>
@@ -35355,11 +36581,11 @@
       </c>
       <c r="AI2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,35, FALSE)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,36, FALSE)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AK2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,37, FALSE)</f>
@@ -35371,51 +36597,51 @@
       </c>
       <c r="AM2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,39, FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,40, FALSE)</f>
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AO2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,41, FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="AP2" t="str">
+        <v>0</v>
+      </c>
+      <c r="AP2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,42, FALSE)</f>
-        <v>LUNES - VIERNES</v>
-      </c>
-      <c r="AQ2" t="str">
+        <v>0</v>
+      </c>
+      <c r="AQ2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,43, FALSE)</f>
-        <v>08:30 A 16:00 HORAS</v>
+        <v>0</v>
       </c>
       <c r="AR2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,44, FALSE)</f>
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AS2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,45, FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="AT2" t="str">
+        <v>0</v>
+      </c>
+      <c r="AT2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,46, FALSE)</f>
-        <v>ESCRITORIOS Y AREA INTERNA</v>
+        <v>0</v>
       </c>
       <c r="AU2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,47, FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="AV2" t="str">
+        <v>0</v>
+      </c>
+      <c r="AV2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,48, FALSE)</f>
-        <v>ON LINE, AREA COMUN, AREA INTERNA</v>
+        <v>0</v>
       </c>
       <c r="AW2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,49, FALSE)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AX2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,50, FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,51, FALSE)</f>
@@ -35443,11 +36669,11 @@
       </c>
       <c r="BE2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,57, FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="BF2" t="str">
+        <v>0</v>
+      </c>
+      <c r="BF2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,58, FALSE)</f>
-        <v>BOTONERA Y ESTROBO</v>
+        <v>0</v>
       </c>
       <c r="BG2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,59, FALSE)</f>
@@ -35455,31 +36681,31 @@
       </c>
       <c r="BH2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,60, FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="BI2" t="str">
+        <v>0</v>
+      </c>
+      <c r="BI2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,61, FALSE)</f>
-        <v>AREA INTERNA Y AREA EXTERNA</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,62, FALSE)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BK2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,63, FALSE)</f>
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BL2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,64, FALSE)</f>
-        <v>23</v>
-      </c>
-      <c r="BM2" t="str">
+        <v>0</v>
+      </c>
+      <c r="BM2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,65, FALSE)</f>
-        <v>TODA LA OFICINA</v>
+        <v>0</v>
       </c>
       <c r="BN2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,66, FALSE)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BO2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,67, FALSE)</f>
@@ -35487,31 +36713,31 @@
       </c>
       <c r="BP2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,68, FALSE)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,69, FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,70, FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,71, FALSE)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BT2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,72, FALSE)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BU2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,73, FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BV2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,74, FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BW2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,75, FALSE)</f>
@@ -35535,15 +36761,15 @@
       </c>
       <c r="CB2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,80, FALSE)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CC2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,81, FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="CD2" t="str">
+        <v>0</v>
+      </c>
+      <c r="CD2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,82, FALSE)</f>
-        <v>EN TODA LA OFICINA</v>
+        <v>0</v>
       </c>
       <c r="CE2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,83, FALSE)</f>
@@ -35579,11 +36805,11 @@
       </c>
       <c r="CM2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,91, FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="CN2" t="str">
+        <v>0</v>
+      </c>
+      <c r="CN2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,92, FALSE)</f>
-        <v>ESCRITORIOS</v>
+        <v>0</v>
       </c>
       <c r="CO2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,93, FALSE)</f>
@@ -35595,11 +36821,11 @@
       </c>
       <c r="CQ2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,95, FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="CR2" t="str">
+        <v>0</v>
+      </c>
+      <c r="CR2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,96, FALSE)</f>
-        <v>ON LINE</v>
+        <v>0</v>
       </c>
       <c r="CS2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,97, FALSE)</f>
@@ -35625,21 +36851,21 @@
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,102, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="CY2" t="str">
+      <c r="CY2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,103, FALSE)</f>
-        <v>SISMO</v>
-      </c>
-      <c r="CZ2" t="str">
+        <v>0</v>
+      </c>
+      <c r="CZ2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,104, FALSE)</f>
-        <v>VOLCANES</v>
-      </c>
-      <c r="DA2" t="str">
+        <v>0</v>
+      </c>
+      <c r="DA2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,105, FALSE)</f>
-        <v>INUNDACION</v>
-      </c>
-      <c r="DB2" t="str">
+        <v>0</v>
+      </c>
+      <c r="DB2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,106, FALSE)</f>
-        <v>GRANIZADAS</v>
+        <v>0</v>
       </c>
       <c r="DC2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,107, FALSE)</f>
@@ -35659,123 +36885,123 @@
       </c>
       <c r="DG2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,111, FALSE)</f>
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="DH2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,112, FALSE)</f>
-        <v>FEBRERO</v>
+        <v>ABRIL</v>
       </c>
       <c r="DI2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,113, FALSE)</f>
         <v>2024</v>
       </c>
-      <c r="DJ2" t="str">
+      <c r="DJ2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,114, FALSE)</f>
-        <v>19.048579939224606, -98.24851718219394</v>
-      </c>
-      <c r="DK2" t="str">
+        <v>0</v>
+      </c>
+      <c r="DK2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,115, FALSE)</f>
-        <v xml:space="preserve">INBURSA ZAVALETA  </v>
-      </c>
-      <c r="DL2" t="str">
+        <v>0</v>
+      </c>
+      <c r="DL2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,116, FALSE)</f>
-        <v>CALLE PALMAS</v>
-      </c>
-      <c r="DM2" t="str">
+        <v>0</v>
+      </c>
+      <c r="DM2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,117, FALSE)</f>
-        <v>SALÓN DE FIESTAS</v>
-      </c>
-      <c r="DN2" s="5" t="str">
+        <v>0</v>
+      </c>
+      <c r="DN2" s="5">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,118, FALSE)</f>
-        <v>CALZADA ZAVALETA</v>
-      </c>
-      <c r="DO2" t="str">
+        <v>0</v>
+      </c>
+      <c r="DO2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,119, FALSE)</f>
-        <v>AL INTERIOR DE CORPORATIVO ZAVALETA, PISO</v>
-      </c>
-      <c r="DP2" t="str">
+        <v>0</v>
+      </c>
+      <c r="DP2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,120, FALSE)</f>
-        <v>Ley del Sistema Estatal de Protección Civil del Estado de Puebla última reforma publicada en el periódico oficial el 08 de abril de 2022.</v>
-      </c>
-      <c r="DQ2" s="5" t="str">
+        <v>0</v>
+      </c>
+      <c r="DQ2" s="5">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,121, FALSE)</f>
-        <v>Reglamento de la Ley del Sistema Estatal de Protección Civil para el Estado Libre y Soberano de Puebla, publicado el 1 de julio de 1998.</v>
-      </c>
-      <c r="DR2" t="str">
+        <v>0</v>
+      </c>
+      <c r="DR2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,122, FALSE)</f>
-        <v>M101461</v>
-      </c>
-      <c r="DS2" t="str">
+        <v>0</v>
+      </c>
+      <c r="DS2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,123, FALSE)</f>
-        <v>ANGELES AIDE MENDEZ REYES</v>
-      </c>
-      <c r="DT2" s="5" t="str">
+        <v>0</v>
+      </c>
+      <c r="DT2" s="5">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,124, FALSE)</f>
-        <v>EJECUTIVO DE ORIGINACION</v>
-      </c>
-      <c r="DU2" t="str">
+        <v>0</v>
+      </c>
+      <c r="DU2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,125, FALSE)</f>
-        <v>MI18046</v>
-      </c>
-      <c r="DV2" t="str">
+        <v>0</v>
+      </c>
+      <c r="DV2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,126, FALSE)</f>
-        <v>NORBERTO AMAURY LUNA URBINA</v>
-      </c>
-      <c r="DW2" s="5" t="str">
+        <v>0</v>
+      </c>
+      <c r="DW2" s="5">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,127, FALSE)</f>
-        <v>EJECUTIVO DE ORIGINACION</v>
-      </c>
-      <c r="DX2" t="str">
+        <v>0</v>
+      </c>
+      <c r="DX2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,128, FALSE)</f>
-        <v>MI04765</v>
-      </c>
-      <c r="DY2" t="str">
+        <v>0</v>
+      </c>
+      <c r="DY2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,129, FALSE)</f>
-        <v>SUSANA ANDREA SIGUENZA BARROSO</v>
-      </c>
-      <c r="DZ2" t="str">
+        <v>0</v>
+      </c>
+      <c r="DZ2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,130, FALSE)</f>
-        <v>EJECUTIVO DE ORIGINACION</v>
-      </c>
-      <c r="EA2" t="str">
+        <v>0</v>
+      </c>
+      <c r="EA2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,131, FALSE)</f>
-        <v>MI18737</v>
-      </c>
-      <c r="EB2" t="str">
+        <v>0</v>
+      </c>
+      <c r="EB2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,132, FALSE)</f>
-        <v>JULIAN CASTO TLACOMULCO</v>
-      </c>
-      <c r="EC2" t="str">
+        <v>0</v>
+      </c>
+      <c r="EC2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,133, FALSE)</f>
-        <v>EJECUTIVO DE ORIGINACION</v>
-      </c>
-      <c r="ED2" t="str">
+        <v>0</v>
+      </c>
+      <c r="ED2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,134, FALSE)</f>
-        <v>MI24098</v>
-      </c>
-      <c r="EE2" t="str">
+        <v>0</v>
+      </c>
+      <c r="EE2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,135, FALSE)</f>
-        <v>ANAHI GARCIA SANCHEZ</v>
-      </c>
-      <c r="EF2" t="str">
+        <v>0</v>
+      </c>
+      <c r="EF2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,136, FALSE)</f>
-        <v>EJECUTIVO DE ORIGINACION</v>
-      </c>
-      <c r="EG2" t="str">
+        <v>0</v>
+      </c>
+      <c r="EG2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,137, FALSE)</f>
-        <v>MI16361</v>
-      </c>
-      <c r="EH2" t="str">
+        <v>0</v>
+      </c>
+      <c r="EH2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,138, FALSE)</f>
-        <v>LUIS ALBERTO TORRES LECHUGA</v>
-      </c>
-      <c r="EI2" t="str">
+        <v>0</v>
+      </c>
+      <c r="EI2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,139, FALSE)</f>
-        <v>EJECUTIVO DE ORIGINACION</v>
-      </c>
-      <c r="EJ2" t="str">
+        <v>0</v>
+      </c>
+      <c r="EJ2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,140, FALSE)</f>
-        <v>MI17743</v>
+        <v>0</v>
       </c>
       <c r="EK2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,141, FALSE)</f>
@@ -35849,21 +37075,21 @@
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,158, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="FC2" t="str">
+      <c r="FC2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,159, FALSE)</f>
-        <v>MOBILIARIO</v>
+        <v>0</v>
       </c>
       <c r="FD2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,160, FALSE)</f>
-        <v>660</v>
+        <v>0</v>
       </c>
       <c r="FE2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,161, FALSE)</f>
-        <v>4.3999999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="FF2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,162, FALSE)</f>
-        <v>4.3999999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="FG2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,163, FALSE)</f>
@@ -36215,10 +37441,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4A8EE80-4440-4B18-8DA6-6D8F054BB32D}">
-  <dimension ref="C1:W194"/>
+  <dimension ref="B1:W194"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B1" t="s">
+        <v>1899</v>
+      </c>
       <c r="D1" t="s">
         <v>832</v>
       </c>
@@ -36286,7 +37515,10 @@
         <v>logo1 = ''</v>
       </c>
     </row>
-    <row r="2" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>1899</v>
+      </c>
       <c r="D2" t="s">
         <v>832</v>
       </c>
@@ -36354,7 +37586,10 @@
         <v>logo2 = ''</v>
       </c>
     </row>
-    <row r="3" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>1899</v>
+      </c>
       <c r="C3" t="s">
         <v>843</v>
       </c>
@@ -36428,7 +37663,10 @@
         <v>fachada = ''</v>
       </c>
     </row>
-    <row r="4" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>1899</v>
+      </c>
       <c r="C4" t="s">
         <v>843</v>
       </c>
@@ -36502,7 +37740,10 @@
         <v>mapa = ''</v>
       </c>
     </row>
-    <row r="5" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>1899</v>
+      </c>
       <c r="C5" s="8" t="s">
         <v>843</v>
       </c>
@@ -36576,7 +37817,10 @@
         <v>esc_emer = ''</v>
       </c>
     </row>
-    <row r="6" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>1899</v>
+      </c>
       <c r="C6" t="s">
         <v>843</v>
       </c>
@@ -36650,7 +37894,10 @@
         <v>mueble1 = ''</v>
       </c>
     </row>
-    <row r="7" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>1899</v>
+      </c>
       <c r="C7" t="s">
         <v>843</v>
       </c>
@@ -36724,7 +37971,7 @@
         <v>mueble2 = ''</v>
       </c>
     </row>
-    <row r="8" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:23" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
         <v>832</v>
       </c>
@@ -36795,7 +38042,7 @@
         <v>venteo = ''</v>
       </c>
     </row>
-    <row r="9" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:23" x14ac:dyDescent="0.3">
       <c r="D9" t="s">
         <v>832</v>
       </c>
@@ -36866,7 +38113,10 @@
         <v>manguera = ''</v>
       </c>
     </row>
-    <row r="10" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>1899</v>
+      </c>
       <c r="C10" t="s">
         <v>843</v>
       </c>
@@ -36940,7 +38190,10 @@
         <v>electrico = ''</v>
       </c>
     </row>
-    <row r="11" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>1899</v>
+      </c>
       <c r="C11" t="s">
         <v>843</v>
       </c>
@@ -37014,7 +38267,7 @@
         <v>banio = ''</v>
       </c>
     </row>
-    <row r="12" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:23" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
         <v>832</v>
       </c>
@@ -37085,7 +38338,10 @@
         <v>cisterna = ''</v>
       </c>
     </row>
-    <row r="13" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>1899</v>
+      </c>
       <c r="C13" t="s">
         <v>843</v>
       </c>
@@ -37159,7 +38415,10 @@
         <v>sismo = ''</v>
       </c>
     </row>
-    <row r="14" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>1899</v>
+      </c>
       <c r="C14" t="s">
         <v>843</v>
       </c>
@@ -37233,7 +38492,10 @@
         <v>inundacion = ''</v>
       </c>
     </row>
-    <row r="15" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>1899</v>
+      </c>
       <c r="D15" t="s">
         <v>832</v>
       </c>
@@ -37304,7 +38566,10 @@
         <v>torm_elect = ''</v>
       </c>
     </row>
-    <row r="16" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>1899</v>
+      </c>
       <c r="C16" t="s">
         <v>843</v>
       </c>
@@ -37378,7 +38643,10 @@
         <v>incendio = ''</v>
       </c>
     </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>1899</v>
+      </c>
       <c r="C17" t="s">
         <v>843</v>
       </c>
@@ -37452,7 +38720,10 @@
         <v>influenza = ''</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>1899</v>
+      </c>
       <c r="D18" t="s">
         <v>832</v>
       </c>
@@ -37523,7 +38794,10 @@
         <v>radiacion = ''</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>1899</v>
+      </c>
       <c r="C19" t="s">
         <v>843</v>
       </c>
@@ -37597,7 +38871,10 @@
         <v>ext1 = ''</v>
       </c>
     </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>1899</v>
+      </c>
       <c r="D20" t="s">
         <v>832</v>
       </c>
@@ -37668,7 +38945,10 @@
         <v>ext2 = ''</v>
       </c>
     </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>1899</v>
+      </c>
       <c r="D21" t="s">
         <v>832</v>
       </c>
@@ -37739,7 +39019,10 @@
         <v>ext3 = ''</v>
       </c>
     </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>1899</v>
+      </c>
       <c r="D22" t="s">
         <v>832</v>
       </c>
@@ -37810,7 +39093,10 @@
         <v>ext4 = ''</v>
       </c>
     </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>1899</v>
+      </c>
       <c r="C23" t="s">
         <v>843</v>
       </c>
@@ -37884,7 +39170,10 @@
         <v>botiquin = ''</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>1899</v>
+      </c>
       <c r="C24" t="s">
         <v>843</v>
       </c>
@@ -37958,7 +39247,10 @@
         <v>ruta1 = ''</v>
       </c>
     </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
+        <v>1899</v>
+      </c>
       <c r="C25" t="s">
         <v>843</v>
       </c>
@@ -38032,7 +39324,10 @@
         <v>ruta2 = ''</v>
       </c>
     </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>1899</v>
+      </c>
       <c r="D26" t="s">
         <v>832</v>
       </c>
@@ -38103,7 +39398,10 @@
         <v>ruta3 = ''</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
+        <v>1899</v>
+      </c>
       <c r="D27" t="s">
         <v>832</v>
       </c>
@@ -38174,7 +39472,10 @@
         <v>salida = ''</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
+        <v>1899</v>
+      </c>
       <c r="C28" t="s">
         <v>843</v>
       </c>
@@ -38248,7 +39549,10 @@
         <v>alarma = ''</v>
       </c>
     </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
+        <v>1899</v>
+      </c>
       <c r="D29" t="s">
         <v>832</v>
       </c>
@@ -38319,7 +39623,10 @@
         <v>prohib1 = ''</v>
       </c>
     </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
+        <v>1899</v>
+      </c>
       <c r="D30" t="s">
         <v>832</v>
       </c>
@@ -38390,7 +39697,10 @@
         <v>prohib2 = ''</v>
       </c>
     </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
+        <v>1899</v>
+      </c>
       <c r="D31" t="s">
         <v>832</v>
       </c>
@@ -38461,7 +39771,10 @@
         <v>prohib3 = ''</v>
       </c>
     </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B32" t="s">
+        <v>1899</v>
+      </c>
       <c r="D32" t="s">
         <v>832</v>
       </c>
@@ -38532,7 +39845,10 @@
         <v>prohib4 = ''</v>
       </c>
     </row>
-    <row r="33" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B33" t="s">
+        <v>1899</v>
+      </c>
       <c r="C33" t="s">
         <v>843</v>
       </c>
@@ -38606,7 +39922,10 @@
         <v>layout = ''</v>
       </c>
     </row>
-    <row r="34" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B34" t="s">
+        <v>1899</v>
+      </c>
       <c r="C34" t="s">
         <v>843</v>
       </c>
@@ -38680,7 +39999,10 @@
         <v>cap1 = ''</v>
       </c>
     </row>
-    <row r="35" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B35" t="s">
+        <v>1899</v>
+      </c>
       <c r="C35" t="s">
         <v>843</v>
       </c>
@@ -38754,7 +40076,10 @@
         <v>cap2 = ''</v>
       </c>
     </row>
-    <row r="36" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B36" t="s">
+        <v>1899</v>
+      </c>
       <c r="C36" t="s">
         <v>843</v>
       </c>
@@ -38828,7 +40153,10 @@
         <v>cap3 = ''</v>
       </c>
     </row>
-    <row r="37" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B37" t="s">
+        <v>1899</v>
+      </c>
       <c r="C37" t="s">
         <v>843</v>
       </c>
@@ -38902,7 +40230,10 @@
         <v>cap4 = ''</v>
       </c>
     </row>
-    <row r="38" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B38" t="s">
+        <v>1899</v>
+      </c>
       <c r="C38" t="s">
         <v>843</v>
       </c>
@@ -38976,7 +40307,10 @@
         <v>cap5 = ''</v>
       </c>
     </row>
-    <row r="39" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B39" t="s">
+        <v>1899</v>
+      </c>
       <c r="C39" t="s">
         <v>843</v>
       </c>
@@ -39050,7 +40384,10 @@
         <v>cap6 = ''</v>
       </c>
     </row>
-    <row r="40" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B40" t="s">
+        <v>1899</v>
+      </c>
       <c r="C40" t="s">
         <v>843</v>
       </c>
@@ -39124,7 +40461,10 @@
         <v>cap7 = ''</v>
       </c>
     </row>
-    <row r="41" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B41" t="s">
+        <v>1899</v>
+      </c>
       <c r="C41" t="s">
         <v>843</v>
       </c>
@@ -39198,7 +40538,10 @@
         <v>cap8 = ''</v>
       </c>
     </row>
-    <row r="42" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B42" t="s">
+        <v>1899</v>
+      </c>
       <c r="C42" t="s">
         <v>843</v>
       </c>
@@ -39272,7 +40615,10 @@
         <v>cap9 = ''</v>
       </c>
     </row>
-    <row r="43" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B43" t="s">
+        <v>1899</v>
+      </c>
       <c r="C43" t="s">
         <v>843</v>
       </c>
@@ -39346,7 +40692,10 @@
         <v>cap10 = ''</v>
       </c>
     </row>
-    <row r="44" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B44" t="s">
+        <v>1899</v>
+      </c>
       <c r="C44" t="s">
         <v>843</v>
       </c>
@@ -39420,7 +40769,10 @@
         <v>cap11 = ''</v>
       </c>
     </row>
-    <row r="45" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B45" t="s">
+        <v>1899</v>
+      </c>
       <c r="C45" t="s">
         <v>843</v>
       </c>
@@ -39494,7 +40846,10 @@
         <v>cap12 = ''</v>
       </c>
     </row>
-    <row r="46" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B46" t="s">
+        <v>1899</v>
+      </c>
       <c r="C46" t="s">
         <v>843</v>
       </c>
@@ -39568,7 +40923,10 @@
         <v>sim1 = ''</v>
       </c>
     </row>
-    <row r="47" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B47" t="s">
+        <v>1899</v>
+      </c>
       <c r="C47" t="s">
         <v>843</v>
       </c>
@@ -39642,7 +41000,10 @@
         <v>sim2 = ''</v>
       </c>
     </row>
-    <row r="48" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B48" t="s">
+        <v>1899</v>
+      </c>
       <c r="C48" t="s">
         <v>843</v>
       </c>
@@ -39716,7 +41077,10 @@
         <v>sim3 = ''</v>
       </c>
     </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B49" t="s">
+        <v>1899</v>
+      </c>
       <c r="C49" t="s">
         <v>843</v>
       </c>
@@ -39790,7 +41154,10 @@
         <v>sim4 = ''</v>
       </c>
     </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B50" t="s">
+        <v>1899</v>
+      </c>
       <c r="C50" t="s">
         <v>843</v>
       </c>
@@ -39864,7 +41231,10 @@
         <v>sim5 = ''</v>
       </c>
     </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B51" t="s">
+        <v>1899</v>
+      </c>
       <c r="C51" t="s">
         <v>843</v>
       </c>
@@ -39938,7 +41308,10 @@
         <v>sim6 = ''</v>
       </c>
     </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B52" t="s">
+        <v>1899</v>
+      </c>
       <c r="C52" t="s">
         <v>843</v>
       </c>
@@ -40012,7 +41385,10 @@
         <v>techo = ''</v>
       </c>
     </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B53" t="s">
+        <v>1899</v>
+      </c>
       <c r="C53" t="s">
         <v>843</v>
       </c>
@@ -40086,7 +41462,10 @@
         <v>pisos = ''</v>
       </c>
     </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B54" t="s">
+        <v>1899</v>
+      </c>
       <c r="C54" t="s">
         <v>843</v>
       </c>
@@ -40157,7 +41536,7 @@
         <v>puerta = ''</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C55" t="s">
         <v>843</v>
       </c>
@@ -40228,7 +41607,7 @@
         <v>estantes = ''</v>
       </c>
     </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C56" t="s">
         <v>843</v>
       </c>
@@ -40302,7 +41681,10 @@
         <v>site = ''</v>
       </c>
     </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B57" t="s">
+        <v>1899</v>
+      </c>
       <c r="C57" t="s">
         <v>843</v>
       </c>
@@ -40376,7 +41758,7 @@
         <v>dh = ''</v>
       </c>
     </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C58" t="s">
         <v>843</v>
       </c>
@@ -40450,7 +41832,7 @@
         <v>ventanas = ''</v>
       </c>
     </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:23" x14ac:dyDescent="0.3">
       <c r="D59" t="s">
         <v>832</v>
       </c>
@@ -40521,7 +41903,7 @@
         <v>compresor = ''</v>
       </c>
     </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:23" x14ac:dyDescent="0.3">
       <c r="D60" t="s">
         <v>832</v>
       </c>
@@ -40592,7 +41974,7 @@
         <v>quimicos = ''</v>
       </c>
     </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:23" x14ac:dyDescent="0.3">
       <c r="D61" t="s">
         <v>832</v>
       </c>
@@ -40663,7 +42045,7 @@
         <v>tanques_gaso = ''</v>
       </c>
     </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:23" x14ac:dyDescent="0.3">
       <c r="D62" t="s">
         <v>832</v>
       </c>
@@ -40734,7 +42116,7 @@
         <v>paro = ''</v>
       </c>
     </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:23" x14ac:dyDescent="0.3">
       <c r="D63" t="s">
         <v>832</v>
       </c>
@@ -40805,7 +42187,7 @@
         <v>trampa_grasa = ''</v>
       </c>
     </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:23" x14ac:dyDescent="0.3">
       <c r="E64" t="s">
         <v>21</v>
       </c>
@@ -40873,7 +42255,7 @@
         <v>planta = ''</v>
       </c>
     </row>
-    <row r="65" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:23" x14ac:dyDescent="0.3">
       <c r="E65" t="s">
         <v>414</v>
       </c>
@@ -40941,7 +42323,7 @@
         <v>deposito = ''</v>
       </c>
     </row>
-    <row r="66" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C66" t="s">
         <v>843</v>
       </c>
@@ -41012,7 +42394,7 @@
         <v>mapa_satel = ''</v>
       </c>
     </row>
-    <row r="67" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C67" t="s">
         <v>843</v>
       </c>
@@ -41083,7 +42465,7 @@
         <v>plano = ''</v>
       </c>
     </row>
-    <row r="68" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C68" t="s">
         <v>843</v>
       </c>
@@ -41154,7 +42536,7 @@
         <v>inmueble1 = ''</v>
       </c>
     </row>
-    <row r="69" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C69" t="s">
         <v>843</v>
       </c>
@@ -41225,7 +42607,7 @@
         <v>inmueble2 = ''</v>
       </c>
     </row>
-    <row r="70" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C70" t="s">
         <v>843</v>
       </c>
@@ -41296,7 +42678,7 @@
         <v>banio1 = ''</v>
       </c>
     </row>
-    <row r="71" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C71" t="s">
         <v>843</v>
       </c>
@@ -41367,7 +42749,7 @@
         <v>electrico1 = ''</v>
       </c>
     </row>
-    <row r="72" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C72" t="s">
         <v>843</v>
       </c>
@@ -41441,7 +42823,7 @@
         <v>fachada1 = ''</v>
       </c>
     </row>
-    <row r="73" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C73" t="s">
         <v>843</v>
       </c>
@@ -41512,7 +42894,10 @@
         <v>bateria = ''</v>
       </c>
     </row>
-    <row r="74" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B74" t="s">
+        <v>1899</v>
+      </c>
       <c r="C74" t="s">
         <v>843</v>
       </c>
@@ -41588,7 +42973,10 @@
         <v>acta1 = ''</v>
       </c>
     </row>
-    <row r="75" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B75" t="s">
+        <v>1899</v>
+      </c>
       <c r="C75" t="s">
         <v>843</v>
       </c>
@@ -41664,7 +43052,10 @@
         <v>acta2 = ''</v>
       </c>
     </row>
-    <row r="76" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B76" t="s">
+        <v>1899</v>
+      </c>
       <c r="C76" t="s">
         <v>843</v>
       </c>
@@ -41740,7 +43131,10 @@
         <v>crono_anual = ''</v>
       </c>
     </row>
-    <row r="77" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B77" t="s">
+        <v>1899</v>
+      </c>
       <c r="C77" t="s">
         <v>843</v>
       </c>
@@ -41816,7 +43210,7 @@
         <v>mantto1 = ''</v>
       </c>
     </row>
-    <row r="78" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C78" t="s">
         <v>843</v>
       </c>
@@ -41892,7 +43286,10 @@
         <v>mantto2 = ''</v>
       </c>
     </row>
-    <row r="79" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B79" t="s">
+        <v>1899</v>
+      </c>
       <c r="C79" t="s">
         <v>843</v>
       </c>
@@ -41968,7 +43365,10 @@
         <v>simulacro = ''</v>
       </c>
     </row>
-    <row r="80" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B80" t="s">
+        <v>1899</v>
+      </c>
       <c r="C80" t="s">
         <v>843</v>
       </c>
@@ -42044,7 +43444,10 @@
         <v>capacitacion = ''</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B81" t="s">
+        <v>1899</v>
+      </c>
       <c r="C81" t="s">
         <v>843</v>
       </c>
@@ -42120,7 +43523,10 @@
         <v>inv_quim = ''</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B82" t="s">
+        <v>1899</v>
+      </c>
       <c r="C82" t="s">
         <v>843</v>
       </c>
@@ -42196,7 +43602,10 @@
         <v>inv_emer = ''</v>
       </c>
     </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B83" t="s">
+        <v>1899</v>
+      </c>
       <c r="C83" t="s">
         <v>843</v>
       </c>
@@ -42272,7 +43681,10 @@
         <v>bit_emer = ''</v>
       </c>
     </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B84" t="s">
+        <v>1899</v>
+      </c>
       <c r="C84" t="s">
         <v>843</v>
       </c>
@@ -42348,7 +43760,10 @@
         <v>insp_bot = ''</v>
       </c>
     </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B85" t="s">
+        <v>1899</v>
+      </c>
       <c r="C85" t="s">
         <v>843</v>
       </c>
@@ -42424,7 +43839,10 @@
         <v>insp_ext = ''</v>
       </c>
     </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B86" t="s">
+        <v>1899</v>
+      </c>
       <c r="C86" t="s">
         <v>843</v>
       </c>
@@ -42500,7 +43918,10 @@
         <v>insp_dh = ''</v>
       </c>
     </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B87" t="s">
+        <v>1899</v>
+      </c>
       <c r="D87" t="s">
         <v>832</v>
       </c>
@@ -42573,7 +43994,10 @@
         <v>insp_lamp = ''</v>
       </c>
     </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B88" t="s">
+        <v>1899</v>
+      </c>
       <c r="C88" t="s">
         <v>843</v>
       </c>
@@ -42649,7 +44073,10 @@
         <v>insp_alarm = ''</v>
       </c>
     </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B89" t="s">
+        <v>1899</v>
+      </c>
       <c r="C89" t="s">
         <v>843</v>
       </c>
@@ -42725,7 +44152,10 @@
         <v>ev_sim1 = ''</v>
       </c>
     </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B90" t="s">
+        <v>1899</v>
+      </c>
       <c r="C90" t="s">
         <v>843</v>
       </c>
@@ -42801,7 +44231,10 @@
         <v>ev_sim2 = ''</v>
       </c>
     </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B91" t="s">
+        <v>1899</v>
+      </c>
       <c r="C91" t="s">
         <v>843</v>
       </c>
@@ -42877,7 +44310,10 @@
         <v>visitas = ''</v>
       </c>
     </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B92" t="s">
+        <v>1899</v>
+      </c>
       <c r="C92" t="s">
         <v>843</v>
       </c>
@@ -42951,7 +44387,7 @@
         <v>dir_emer = ''</v>
       </c>
     </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C93" t="s">
         <v>843</v>
       </c>
@@ -43024,7 +44460,7 @@
         <v>corresp1 = ''</v>
       </c>
     </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C94" t="s">
         <v>843</v>
       </c>
@@ -43097,7 +44533,7 @@
         <v>corresp2 = ''</v>
       </c>
     </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C95" t="s">
         <v>843</v>
       </c>
@@ -43170,7 +44606,7 @@
         <v>corresp3 = ''</v>
       </c>
     </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C96" t="s">
         <v>843</v>
       </c>

--- a/Inputs/BD.xlsx
+++ b/Inputs/BD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/078e1a455e5c02ce/Documentos/GitHub/Proyecto_PIPC/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5297" documentId="13_ncr:1_{7D3A426E-EC5E-453A-8CC7-F83B71F24F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4454FD2-C819-4AC3-96D0-A118F591D333}"/>
+  <xr:revisionPtr revIDLastSave="5548" documentId="13_ncr:1_{7D3A426E-EC5E-453A-8CC7-F83B71F24F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38AA905A-7F4F-441B-B4B5-9AD0AB5C2E30}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3F095A75-F066-4695-8672-8D4315F1EF23}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10400" xr2:uid="{3F095A75-F066-4695-8672-8D4315F1EF23}"/>
   </bookViews>
   <sheets>
     <sheet name="BD" sheetId="1" r:id="rId1"/>
@@ -563,7 +563,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6523" uniqueCount="2000">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6710" uniqueCount="2065">
   <si>
     <t>dia</t>
   </si>
@@ -6563,6 +6563,201 @@
   </si>
   <si>
     <t>MATIAS ROMERO AVEDAÑO</t>
+  </si>
+  <si>
+    <t>SERVICIOS SAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>PL/2764/EXP/2015</t>
+  </si>
+  <si>
+    <t>ALMACENAMIENTO Y VENTA DE HIDROCARBUROS</t>
+  </si>
+  <si>
+    <t>CALLE PINOLACO Y PROLONGACION MIGUEL ALVARADO</t>
+  </si>
+  <si>
+    <t>CIUDAD DE CUETZALAN</t>
+  </si>
+  <si>
+    <t>CUETZALAN DEL PROGRESO</t>
+  </si>
+  <si>
+    <t>estacioncuetzalan2@gmail.com</t>
+  </si>
+  <si>
+    <t>18 DE DICIEMRBE DE 1995</t>
+  </si>
+  <si>
+    <t>FELICITAS ROBLES DIEGO</t>
+  </si>
+  <si>
+    <t>DESPACHADORES</t>
+  </si>
+  <si>
+    <t>20.023620628641062, -97.52844270318204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MINI SUPER EL CERRITO </t>
+  </si>
+  <si>
+    <t>MATERIALES TORAL</t>
+  </si>
+  <si>
+    <t>MIGUEL ALVARADO</t>
+  </si>
+  <si>
+    <t>PINOLACO</t>
+  </si>
+  <si>
+    <t>ANADEIRA AMETA GONZALEZ</t>
+  </si>
+  <si>
+    <t>AUXILIAR ADMINISTRATIVO</t>
+  </si>
+  <si>
+    <t>GENARO HERNANDEZ ARROYO</t>
+  </si>
+  <si>
+    <t>LIMPIEZA</t>
+  </si>
+  <si>
+    <t>ANDREA GALICIA MOLINA</t>
+  </si>
+  <si>
+    <t>DESPACHADOR</t>
+  </si>
+  <si>
+    <t>LUIS ADRIAN RUPERTO FUENTES</t>
+  </si>
+  <si>
+    <t>MARCO ANTONIO MADERO</t>
+  </si>
+  <si>
+    <t>YAMIL OMAR DIB MORA</t>
+  </si>
+  <si>
+    <t>OLIVA BAUTISTA MANCILLA</t>
+  </si>
+  <si>
+    <t>EDGAR CHICO VAZQUEZ</t>
+  </si>
+  <si>
+    <t>JUNTO OFICINA</t>
+  </si>
+  <si>
+    <t>SUCURSAL TUXTEPEC PAPALOAPAN</t>
+  </si>
+  <si>
+    <t>AVENIDA 16 DE SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>OAXAQUEÑOS ILUSTRES</t>
+  </si>
+  <si>
+    <t>SUCURSAL TUXTEPEC LOMA BONITA</t>
+  </si>
+  <si>
+    <t>TUXTEPEC LOMA BONITA</t>
+  </si>
+  <si>
+    <t>BANCO FORJADORES, S.A. INSTITUCION DE BANCA MULTIPLE</t>
+  </si>
+  <si>
+    <t>TUXTEPEC LA PIRAGUA</t>
+  </si>
+  <si>
+    <t>FNE050520EE6</t>
+  </si>
+  <si>
+    <t>AV. INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>LA PIRAGUA</t>
+  </si>
+  <si>
+    <t>TUXTEPEC</t>
+  </si>
+  <si>
+    <t>UNIVERSIDAD DEL VALLE DE PUEBLA SC</t>
+  </si>
+  <si>
+    <t>IMPARTICIÓN DE PROGRAMAS ACADÉMICOS, DESDE LICENCIATURAS HASTA POSGRADOS. ADEMÁS, PROMUEVE LA FORMACIÓN CONTINUA Y RECURSOS DE APRENDIZAJE. LOS ESTUDIANTES TAMBIÉN PUEDEN PARTICIPAR EN CLUBES Y ORGANIZACIONES ESTUDIANTILES PARA ENRIQUECER SU EXPERIENCIA ACADÉMICA Y SOCIAL.</t>
+  </si>
+  <si>
+    <t>AZTLAN</t>
+  </si>
+  <si>
+    <t>CALMECAC</t>
+  </si>
+  <si>
+    <t>CUETLAXCOAPAN</t>
+  </si>
+  <si>
+    <t>KUKULCAN</t>
+  </si>
+  <si>
+    <t>MIXCOATL</t>
+  </si>
+  <si>
+    <t>QUETZALCOATL</t>
+  </si>
+  <si>
+    <t>TEOCALLI</t>
+  </si>
+  <si>
+    <t>TLALOC</t>
+  </si>
+  <si>
+    <t>UVP810305C25</t>
+  </si>
+  <si>
+    <t>UVP810305C26</t>
+  </si>
+  <si>
+    <t>UVP810305C27</t>
+  </si>
+  <si>
+    <t>UVP810305C28</t>
+  </si>
+  <si>
+    <t>UVP810305C29</t>
+  </si>
+  <si>
+    <t>UVP810305C30</t>
+  </si>
+  <si>
+    <t>UVP810305C31</t>
+  </si>
+  <si>
+    <t>UVP810305C32</t>
+  </si>
+  <si>
+    <t>ESCUELA DE EDUCACION MEDIA Y SUPERIOR</t>
+  </si>
+  <si>
+    <t>5 SUR</t>
+  </si>
+  <si>
+    <t>EL CERRITO</t>
+  </si>
+  <si>
+    <t>PRISCILIANO GERARDO ILLESCAS LOZANO</t>
+  </si>
+  <si>
+    <t>3 SUR</t>
+  </si>
+  <si>
+    <t>PRIVADA JACARANDAS</t>
+  </si>
+  <si>
+    <t>PRIVADA 3 A SUR</t>
+  </si>
+  <si>
+    <t>TAMAULIPAS</t>
+  </si>
+  <si>
+    <t>MAYO</t>
   </si>
 </sst>
 </file>
@@ -7185,7 +7380,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="26" fmlaLink="$A$1" max="30000" min="1" page="10" val="48"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="26" fmlaLink="$A$1" max="30000" min="1" page="10" val="54"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7195,15 +7390,15 @@
       <xdr:twoCellAnchor>
         <xdr:from>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>297180</xdr:colOff>
+          <xdr:colOff>298450</xdr:colOff>
           <xdr:row>0</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>617220</xdr:colOff>
+          <xdr:colOff>615950</xdr:colOff>
           <xdr:row>0</xdr:row>
-          <xdr:rowOff>350520</xdr:rowOff>
+          <xdr:rowOff>349250</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -7561,28 +7756,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE6A0106-4EDF-4D58-B8A9-1C9CC54D9FE0}">
   <dimension ref="A1:KT201"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="123" max="123" width="11.5546875" style="11"/>
-    <col min="126" max="126" width="11.5546875" style="11"/>
-    <col min="129" max="129" width="11.5546875" style="11"/>
-    <col min="132" max="132" width="11.5546875" style="11"/>
-    <col min="135" max="135" width="11.5546875" style="11"/>
-    <col min="138" max="138" width="11.5546875" style="11"/>
-    <col min="141" max="141" width="11.5546875" style="11"/>
-    <col min="144" max="144" width="11.5546875" style="11"/>
-    <col min="147" max="147" width="11.5546875" style="11"/>
+    <col min="123" max="123" width="11.54296875" style="11"/>
+    <col min="126" max="126" width="11.54296875" style="11"/>
+    <col min="129" max="129" width="11.54296875" style="11"/>
+    <col min="132" max="132" width="11.54296875" style="11"/>
+    <col min="135" max="135" width="11.54296875" style="11"/>
+    <col min="138" max="138" width="11.54296875" style="11"/>
+    <col min="141" max="141" width="11.54296875" style="11"/>
+    <col min="144" max="144" width="11.54296875" style="11"/>
+    <col min="147" max="147" width="11.54296875" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:306" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:306" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="DC1" t="s">
         <v>1970</v>
       </c>
     </row>
-    <row r="2" spans="1:306" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:306" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>133</v>
       </c>
@@ -8502,7 +8697,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="3" spans="1:306" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:306" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -8785,7 +8980,7 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="4" spans="1:306" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:306" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -9062,7 +9257,7 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="5" spans="1:306" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:306" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3</v>
       </c>
@@ -9345,7 +9540,7 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="6" spans="1:306" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:306" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>4</v>
       </c>
@@ -9622,7 +9817,7 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="7" spans="1:306" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:306" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>5</v>
       </c>
@@ -9896,7 +10091,7 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="8" spans="1:306" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:306" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>6</v>
       </c>
@@ -10206,7 +10401,7 @@
         <v>ALTO</v>
       </c>
     </row>
-    <row r="9" spans="1:306" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:306" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>7</v>
       </c>
@@ -10489,7 +10684,7 @@
         <v>ALTO</v>
       </c>
     </row>
-    <row r="10" spans="1:306" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:306" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>8</v>
       </c>
@@ -10802,7 +10997,7 @@
         <v>ALTO</v>
       </c>
     </row>
-    <row r="11" spans="1:306" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:306" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>9</v>
       </c>
@@ -11124,7 +11319,7 @@
         <v>ALTO</v>
       </c>
     </row>
-    <row r="12" spans="1:306" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:306" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>10</v>
       </c>
@@ -11425,7 +11620,7 @@
         <v>ALTO</v>
       </c>
     </row>
-    <row r="13" spans="1:306" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:306" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>11</v>
       </c>
@@ -11723,7 +11918,7 @@
         <v>ALTO</v>
       </c>
     </row>
-    <row r="14" spans="1:306" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:306" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>12</v>
       </c>
@@ -12185,7 +12380,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="15" spans="1:306" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:306" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>13</v>
       </c>
@@ -12758,7 +12953,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="16" spans="1:306" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:306" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>14</v>
       </c>
@@ -13246,7 +13441,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="17" spans="1:279" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:279" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>15</v>
       </c>
@@ -13735,7 +13930,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="18" spans="1:279" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:279" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>16</v>
       </c>
@@ -14251,7 +14446,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="19" spans="1:279" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:279" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>17</v>
       </c>
@@ -14741,7 +14936,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="20" spans="1:279" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:279" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>18</v>
       </c>
@@ -15216,7 +15411,7 @@
         <v>1651</v>
       </c>
     </row>
-    <row r="21" spans="1:279" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:279" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>19</v>
       </c>
@@ -15702,7 +15897,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="22" spans="1:279" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:279" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>20</v>
       </c>
@@ -16206,7 +16401,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="23" spans="1:279" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:279" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>21</v>
       </c>
@@ -16795,7 +16990,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="24" spans="1:279" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:279" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>22</v>
       </c>
@@ -17394,7 +17589,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="25" spans="1:279" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:279" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>23</v>
       </c>
@@ -17944,7 +18139,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="26" spans="1:279" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:279" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>24</v>
       </c>
@@ -18521,7 +18716,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="27" spans="1:279" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:279" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>25</v>
       </c>
@@ -19125,7 +19320,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="28" spans="1:279" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:279" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>26</v>
       </c>
@@ -19702,7 +19897,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="29" spans="1:279" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:279" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>27</v>
       </c>
@@ -20312,7 +20507,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="30" spans="1:279" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:279" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>28</v>
       </c>
@@ -20904,7 +21099,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="31" spans="1:279" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:279" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>29</v>
       </c>
@@ -21490,7 +21685,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="32" spans="1:279" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:279" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>30</v>
       </c>
@@ -22088,7 +22283,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="33" spans="1:306" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:306" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>31</v>
       </c>
@@ -22674,7 +22869,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="34" spans="1:306" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:306" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>32</v>
       </c>
@@ -23374,7 +23569,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="35" spans="1:306" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:306" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>33</v>
       </c>
@@ -24038,7 +24233,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="36" spans="1:306" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:306" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>34</v>
       </c>
@@ -24621,7 +24816,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="37" spans="1:306" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:306" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>35</v>
       </c>
@@ -25201,7 +25396,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="38" spans="1:306" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:306" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>36</v>
       </c>
@@ -25778,7 +25973,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="39" spans="1:306" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:306" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>37</v>
       </c>
@@ -26361,7 +26556,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="40" spans="1:306" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:306" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>38</v>
       </c>
@@ -26932,7 +27127,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="41" spans="1:306" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:306" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>39</v>
       </c>
@@ -27497,7 +27692,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="42" spans="1:306" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:306" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>40</v>
       </c>
@@ -28071,7 +28266,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="43" spans="1:306" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:306" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>41</v>
       </c>
@@ -28687,7 +28882,7 @@
         <v>1309</v>
       </c>
     </row>
-    <row r="44" spans="1:306" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:306" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>42</v>
       </c>
@@ -28943,7 +29138,7 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="45" spans="1:306" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:306" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>43</v>
       </c>
@@ -29194,7 +29389,7 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="46" spans="1:306" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:306" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>44</v>
       </c>
@@ -29456,7 +29651,7 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="47" spans="1:306" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:306" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>45</v>
       </c>
@@ -29589,7 +29784,7 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="48" spans="1:306" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:306" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>46</v>
       </c>
@@ -29677,7 +29872,7 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="49" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>47</v>
       </c>
@@ -29762,7 +29957,7 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="50" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>48</v>
       </c>
@@ -29847,47 +30042,380 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="51" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>49</v>
       </c>
+      <c r="B51" t="s">
+        <v>579</v>
+      </c>
+      <c r="C51" t="s">
+        <v>805</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>2000</v>
+      </c>
+      <c r="E51" t="s">
+        <v>808</v>
+      </c>
+      <c r="F51" t="s">
+        <v>2001</v>
+      </c>
+      <c r="G51" t="s">
+        <v>579</v>
+      </c>
+      <c r="H51" t="s">
+        <v>2002</v>
+      </c>
+      <c r="I51" t="s">
+        <v>2003</v>
+      </c>
+      <c r="J51">
+        <v>134</v>
+      </c>
+      <c r="L51" t="s">
+        <v>2004</v>
+      </c>
+      <c r="M51" t="s">
+        <v>2005</v>
+      </c>
+      <c r="N51" t="s">
+        <v>424</v>
+      </c>
+      <c r="O51">
+        <v>73560</v>
+      </c>
+      <c r="P51">
+        <v>2333310437</v>
+      </c>
+      <c r="Q51" s="3" t="s">
+        <v>2006</v>
+      </c>
+      <c r="R51">
+        <v>29</v>
+      </c>
+      <c r="S51" t="s">
+        <v>2007</v>
+      </c>
+      <c r="V51">
+        <v>968.74</v>
+      </c>
+      <c r="W51">
+        <v>968.74</v>
+      </c>
+      <c r="X51">
+        <v>1</v>
+      </c>
+      <c r="Y51">
+        <v>1</v>
+      </c>
+      <c r="Z51">
+        <v>2</v>
+      </c>
+      <c r="AA51">
+        <v>2</v>
+      </c>
+      <c r="AB51">
+        <v>0</v>
+      </c>
+      <c r="AC51">
+        <v>0</v>
+      </c>
+      <c r="AD51" t="s">
+        <v>1236</v>
+      </c>
+      <c r="AE51" t="s">
+        <v>752</v>
+      </c>
+      <c r="AF51" t="s">
+        <v>2008</v>
+      </c>
+      <c r="AG51">
+        <v>9</v>
+      </c>
+      <c r="AH51">
+        <v>0</v>
+      </c>
+      <c r="AI51">
+        <v>5</v>
+      </c>
+      <c r="AJ51">
+        <v>4</v>
+      </c>
+      <c r="AK51">
+        <v>0</v>
+      </c>
+      <c r="AL51">
+        <v>0</v>
+      </c>
+      <c r="AM51">
+        <v>3</v>
+      </c>
+      <c r="AN51">
+        <v>100</v>
+      </c>
+      <c r="AO51">
+        <v>4</v>
+      </c>
+      <c r="AP51" t="s">
+        <v>430</v>
+      </c>
+      <c r="AQ51" t="s">
+        <v>431</v>
+      </c>
       <c r="AR51" s="4">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="AS51">
+        <v>1</v>
+      </c>
+      <c r="AT51" t="s">
+        <v>755</v>
+      </c>
+      <c r="AU51">
+        <v>5</v>
+      </c>
+      <c r="AV51" t="s">
+        <v>753</v>
+      </c>
+      <c r="AW51">
+        <v>5</v>
+      </c>
+      <c r="AY51">
+        <v>3</v>
+      </c>
+      <c r="AZ51" t="s">
+        <v>793</v>
+      </c>
+      <c r="BA51">
+        <v>3</v>
+      </c>
+      <c r="BB51" t="s">
+        <v>1697</v>
+      </c>
+      <c r="BC51">
+        <v>1</v>
+      </c>
+      <c r="BD51" t="s">
+        <v>2026</v>
+      </c>
+      <c r="BE51">
+        <v>1</v>
+      </c>
+      <c r="BF51" t="s">
+        <v>1914</v>
+      </c>
+      <c r="BG51">
+        <v>1</v>
+      </c>
+      <c r="BI51" t="s">
+        <v>755</v>
+      </c>
+      <c r="BN51">
+        <v>6</v>
+      </c>
+      <c r="BT51">
+        <v>2</v>
       </c>
       <c r="BU51" s="4">
         <f t="shared" si="22"/>
+        <v>6</v>
+      </c>
+      <c r="BV51">
+        <v>2</v>
+      </c>
+      <c r="BX51">
+        <v>2</v>
+      </c>
+      <c r="BY51">
+        <v>2</v>
+      </c>
+      <c r="CS51">
+        <v>2</v>
+      </c>
+      <c r="CT51" t="s">
+        <v>2009</v>
+      </c>
+      <c r="CU51">
+        <v>3</v>
+      </c>
+      <c r="CV51">
+        <v>40000</v>
+      </c>
+      <c r="CW51">
+        <v>60000</v>
+      </c>
+      <c r="CX51">
+        <v>60000</v>
+      </c>
+      <c r="DG51">
+        <v>2</v>
+      </c>
+      <c r="DH51" t="s">
+        <v>1915</v>
+      </c>
+      <c r="DI51">
+        <v>2024</v>
+      </c>
+      <c r="DJ51" t="s">
+        <v>2010</v>
+      </c>
+      <c r="DK51" t="s">
+        <v>2011</v>
+      </c>
+      <c r="DL51" t="s">
+        <v>2012</v>
+      </c>
+      <c r="DM51" t="s">
+        <v>2013</v>
+      </c>
+      <c r="DN51" t="s">
+        <v>2014</v>
+      </c>
+      <c r="DP51" t="s">
+        <v>442</v>
+      </c>
+      <c r="DQ51" t="s">
+        <v>443</v>
+      </c>
+      <c r="DS51" s="11" t="s">
+        <v>2015</v>
+      </c>
+      <c r="DT51" t="s">
+        <v>2016</v>
+      </c>
+      <c r="DV51" s="11" t="s">
+        <v>2017</v>
+      </c>
+      <c r="DW51" t="s">
+        <v>2018</v>
+      </c>
+      <c r="DY51" s="11" t="s">
+        <v>2019</v>
+      </c>
+      <c r="DZ51" t="s">
+        <v>2020</v>
+      </c>
+      <c r="EB51" s="11" t="s">
+        <v>2021</v>
+      </c>
+      <c r="EC51" t="s">
+        <v>2020</v>
+      </c>
+      <c r="EE51" s="11" t="s">
+        <v>2022</v>
+      </c>
+      <c r="EF51" t="s">
+        <v>2020</v>
+      </c>
+      <c r="EH51" s="11" t="s">
+        <v>2023</v>
+      </c>
+      <c r="EI51" t="s">
+        <v>2020</v>
+      </c>
+      <c r="EK51" s="11" t="s">
+        <v>2024</v>
+      </c>
+      <c r="EL51" t="s">
+        <v>2020</v>
+      </c>
+      <c r="EN51" s="11" t="s">
+        <v>2025</v>
+      </c>
+      <c r="EO51" t="s">
+        <v>2020</v>
+      </c>
+      <c r="EU51">
         <v>0</v>
       </c>
       <c r="EV51" s="4">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
+      <c r="EW51" t="s">
+        <v>454</v>
+      </c>
+      <c r="EX51">
+        <v>100000</v>
+      </c>
       <c r="EY51" s="4">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>71.428571428571431</v>
+      </c>
+      <c r="EZ51" t="s">
+        <v>761</v>
+      </c>
+      <c r="FA51">
+        <v>60100</v>
       </c>
       <c r="FB51" s="4">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>30.05</v>
+      </c>
+      <c r="FC51" t="s">
+        <v>455</v>
+      </c>
+      <c r="FD51">
+        <v>540</v>
       </c>
       <c r="FE51" s="4">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="FF51" s="4">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>101.51457142857143</v>
       </c>
       <c r="FG51" s="4" t="str">
         <f t="shared" si="28"/>
-        <v>ORDINARIO</v>
+        <v>ALTO</v>
       </c>
     </row>
-    <row r="52" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>50</v>
       </c>
+      <c r="B52" t="s">
+        <v>1891</v>
+      </c>
+      <c r="C52" t="s">
+        <v>1971</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>2027</v>
+      </c>
+      <c r="E52" t="s">
+        <v>1973</v>
+      </c>
+      <c r="G52" t="s">
+        <v>1974</v>
+      </c>
+      <c r="I52" t="s">
+        <v>2028</v>
+      </c>
+      <c r="J52">
+        <v>94</v>
+      </c>
+      <c r="L52" t="s">
+        <v>2029</v>
+      </c>
+      <c r="M52" t="s">
+        <v>2031</v>
+      </c>
+      <c r="N52" t="s">
+        <v>1977</v>
+      </c>
+      <c r="O52">
+        <v>68405</v>
+      </c>
+      <c r="AG52">
+        <v>18</v>
+      </c>
+      <c r="AN52">
+        <v>133</v>
+      </c>
       <c r="AR52" s="4">
         <f t="shared" si="21"/>
         <v>0</v>
@@ -29895,6 +30423,15 @@
       <c r="BU52" s="4">
         <f t="shared" si="22"/>
         <v>0</v>
+      </c>
+      <c r="DG52">
+        <v>15</v>
+      </c>
+      <c r="DH52" t="s">
+        <v>1915</v>
+      </c>
+      <c r="DI52">
+        <v>2024</v>
       </c>
       <c r="EV52" s="4">
         <f t="shared" si="23"/>
@@ -29921,10 +30458,49 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="53" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>51</v>
       </c>
+      <c r="B53" t="s">
+        <v>1891</v>
+      </c>
+      <c r="C53" t="s">
+        <v>1971</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>2030</v>
+      </c>
+      <c r="E53" t="s">
+        <v>1973</v>
+      </c>
+      <c r="G53" t="s">
+        <v>1974</v>
+      </c>
+      <c r="I53" t="s">
+        <v>758</v>
+      </c>
+      <c r="J53">
+        <v>8</v>
+      </c>
+      <c r="L53" t="s">
+        <v>422</v>
+      </c>
+      <c r="M53" t="s">
+        <v>2031</v>
+      </c>
+      <c r="N53" t="s">
+        <v>1977</v>
+      </c>
+      <c r="O53">
+        <v>68400</v>
+      </c>
+      <c r="AG53">
+        <v>4</v>
+      </c>
+      <c r="AN53">
+        <v>100</v>
+      </c>
       <c r="AR53" s="4">
         <f t="shared" si="21"/>
         <v>0</v>
@@ -29932,6 +30508,15 @@
       <c r="BU53" s="4">
         <f t="shared" si="22"/>
         <v>0</v>
+      </c>
+      <c r="DG53">
+        <v>15</v>
+      </c>
+      <c r="DH53" t="s">
+        <v>1915</v>
+      </c>
+      <c r="DI53">
+        <v>2024</v>
       </c>
       <c r="EV53" s="4">
         <f t="shared" si="23"/>
@@ -29958,10 +30543,49 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="54" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>52</v>
       </c>
+      <c r="B54" t="s">
+        <v>1891</v>
+      </c>
+      <c r="C54" t="s">
+        <v>2032</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>2033</v>
+      </c>
+      <c r="E54" t="s">
+        <v>2034</v>
+      </c>
+      <c r="G54" t="s">
+        <v>846</v>
+      </c>
+      <c r="I54" t="s">
+        <v>2035</v>
+      </c>
+      <c r="J54">
+        <v>1011</v>
+      </c>
+      <c r="L54" t="s">
+        <v>2036</v>
+      </c>
+      <c r="M54" t="s">
+        <v>2037</v>
+      </c>
+      <c r="N54" t="s">
+        <v>1977</v>
+      </c>
+      <c r="O54">
+        <v>68310</v>
+      </c>
+      <c r="AG54">
+        <v>14</v>
+      </c>
+      <c r="AN54">
+        <v>15</v>
+      </c>
       <c r="AR54" s="4">
         <f t="shared" si="21"/>
         <v>0</v>
@@ -29969,6 +30593,15 @@
       <c r="BU54" s="4">
         <f t="shared" si="22"/>
         <v>0</v>
+      </c>
+      <c r="DG54">
+        <v>18</v>
+      </c>
+      <c r="DH54" t="s">
+        <v>1915</v>
+      </c>
+      <c r="DI54">
+        <v>2024</v>
       </c>
       <c r="EV54" s="4">
         <f t="shared" si="23"/>
@@ -29995,10 +30628,63 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="55" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>53</v>
       </c>
+      <c r="B55" t="s">
+        <v>552</v>
+      </c>
+      <c r="C55" t="s">
+        <v>2038</v>
+      </c>
+      <c r="D55" t="s">
+        <v>2038</v>
+      </c>
+      <c r="E55" t="s">
+        <v>2048</v>
+      </c>
+      <c r="F55" t="str">
+        <f>+_xlfn.CONCAT("COMPLEJO ",K55)</f>
+        <v>COMPLEJO AZTLAN</v>
+      </c>
+      <c r="G55" t="s">
+        <v>2056</v>
+      </c>
+      <c r="H55" t="s">
+        <v>2039</v>
+      </c>
+      <c r="I55" t="s">
+        <v>2057</v>
+      </c>
+      <c r="J55">
+        <v>5906</v>
+      </c>
+      <c r="K55" t="s">
+        <v>2040</v>
+      </c>
+      <c r="L55" t="s">
+        <v>2058</v>
+      </c>
+      <c r="M55" t="s">
+        <v>424</v>
+      </c>
+      <c r="N55" t="s">
+        <v>424</v>
+      </c>
+      <c r="T55" t="str">
+        <f>+IF(V55&gt;1000,"JORGE MANUEL ISLAS GOWER", "NOE MORA RAMIREZ")</f>
+        <v>JORGE MANUEL ISLAS GOWER</v>
+      </c>
+      <c r="V55">
+        <v>2485</v>
+      </c>
+      <c r="W55">
+        <v>4639.5200000000004</v>
+      </c>
+      <c r="AE55" t="s">
+        <v>2059</v>
+      </c>
       <c r="AR55" s="4">
         <f t="shared" si="21"/>
         <v>0</v>
@@ -30006,6 +30692,15 @@
       <c r="BU55" s="4">
         <f t="shared" si="22"/>
         <v>0</v>
+      </c>
+      <c r="DG55">
+        <v>9</v>
+      </c>
+      <c r="DH55" t="s">
+        <v>2064</v>
+      </c>
+      <c r="DI55">
+        <v>2024</v>
       </c>
       <c r="EV55" s="4">
         <f t="shared" si="23"/>
@@ -30032,10 +30727,63 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="56" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>54</v>
       </c>
+      <c r="B56" t="s">
+        <v>552</v>
+      </c>
+      <c r="C56" t="s">
+        <v>2038</v>
+      </c>
+      <c r="D56" t="s">
+        <v>2038</v>
+      </c>
+      <c r="E56" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F56" t="str">
+        <f t="shared" ref="F56:F62" si="29">+_xlfn.CONCAT("COMPLEJO ",K56)</f>
+        <v>COMPLEJO CALMECAC</v>
+      </c>
+      <c r="G56" t="s">
+        <v>2056</v>
+      </c>
+      <c r="H56" t="s">
+        <v>2039</v>
+      </c>
+      <c r="I56" t="s">
+        <v>2060</v>
+      </c>
+      <c r="J56">
+        <v>5758</v>
+      </c>
+      <c r="K56" t="s">
+        <v>2041</v>
+      </c>
+      <c r="L56" t="s">
+        <v>2058</v>
+      </c>
+      <c r="M56" t="s">
+        <v>424</v>
+      </c>
+      <c r="N56" t="s">
+        <v>424</v>
+      </c>
+      <c r="T56" t="str">
+        <f t="shared" ref="T56:T62" si="30">+IF(V56&gt;1000,"JORGE MANUEL ISLAS GOWER", "NOE MORA RAMIREZ")</f>
+        <v>NOE MORA RAMIREZ</v>
+      </c>
+      <c r="V56">
+        <v>608</v>
+      </c>
+      <c r="W56">
+        <v>2530.0100000000002</v>
+      </c>
+      <c r="AE56" t="s">
+        <v>2059</v>
+      </c>
       <c r="AR56" s="4">
         <f t="shared" si="21"/>
         <v>0</v>
@@ -30043,6 +30791,15 @@
       <c r="BU56" s="4">
         <f t="shared" si="22"/>
         <v>0</v>
+      </c>
+      <c r="DG56">
+        <v>9</v>
+      </c>
+      <c r="DH56" t="s">
+        <v>2064</v>
+      </c>
+      <c r="DI56">
+        <v>2024</v>
       </c>
       <c r="EV56" s="4">
         <f t="shared" si="23"/>
@@ -30069,10 +30826,63 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="57" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>55</v>
       </c>
+      <c r="B57" t="s">
+        <v>552</v>
+      </c>
+      <c r="C57" t="s">
+        <v>2038</v>
+      </c>
+      <c r="D57" t="s">
+        <v>2038</v>
+      </c>
+      <c r="E57" t="s">
+        <v>2050</v>
+      </c>
+      <c r="F57" t="str">
+        <f t="shared" si="29"/>
+        <v>COMPLEJO CUETLAXCOAPAN</v>
+      </c>
+      <c r="G57" t="s">
+        <v>2056</v>
+      </c>
+      <c r="H57" t="s">
+        <v>2039</v>
+      </c>
+      <c r="I57" t="s">
+        <v>2060</v>
+      </c>
+      <c r="J57">
+        <v>5720</v>
+      </c>
+      <c r="K57" t="s">
+        <v>2042</v>
+      </c>
+      <c r="L57" t="s">
+        <v>2058</v>
+      </c>
+      <c r="M57" t="s">
+        <v>424</v>
+      </c>
+      <c r="N57" t="s">
+        <v>424</v>
+      </c>
+      <c r="T57" t="str">
+        <f t="shared" si="30"/>
+        <v>NOE MORA RAMIREZ</v>
+      </c>
+      <c r="V57">
+        <v>585</v>
+      </c>
+      <c r="W57">
+        <v>661.53</v>
+      </c>
+      <c r="AE57" t="s">
+        <v>2059</v>
+      </c>
       <c r="AR57" s="4">
         <f t="shared" si="21"/>
         <v>0</v>
@@ -30080,6 +30890,15 @@
       <c r="BU57" s="4">
         <f t="shared" si="22"/>
         <v>0</v>
+      </c>
+      <c r="DG57">
+        <v>9</v>
+      </c>
+      <c r="DH57" t="s">
+        <v>2064</v>
+      </c>
+      <c r="DI57">
+        <v>2024</v>
       </c>
       <c r="EV57" s="4">
         <f t="shared" si="23"/>
@@ -30106,10 +30925,63 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="58" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>56</v>
       </c>
+      <c r="B58" t="s">
+        <v>552</v>
+      </c>
+      <c r="C58" t="s">
+        <v>2038</v>
+      </c>
+      <c r="D58" t="s">
+        <v>2038</v>
+      </c>
+      <c r="E58" t="s">
+        <v>2051</v>
+      </c>
+      <c r="F58" t="str">
+        <f t="shared" si="29"/>
+        <v>COMPLEJO KUKULCAN</v>
+      </c>
+      <c r="G58" t="s">
+        <v>2056</v>
+      </c>
+      <c r="H58" t="s">
+        <v>2039</v>
+      </c>
+      <c r="I58" t="s">
+        <v>2060</v>
+      </c>
+      <c r="J58">
+        <v>5759</v>
+      </c>
+      <c r="K58" t="s">
+        <v>2043</v>
+      </c>
+      <c r="L58" t="s">
+        <v>2058</v>
+      </c>
+      <c r="M58" t="s">
+        <v>424</v>
+      </c>
+      <c r="N58" t="s">
+        <v>424</v>
+      </c>
+      <c r="T58" t="str">
+        <f t="shared" si="30"/>
+        <v>JORGE MANUEL ISLAS GOWER</v>
+      </c>
+      <c r="V58">
+        <v>1272</v>
+      </c>
+      <c r="W58">
+        <v>4473.59</v>
+      </c>
+      <c r="AE58" t="s">
+        <v>2059</v>
+      </c>
       <c r="AR58" s="4">
         <f t="shared" si="21"/>
         <v>0</v>
@@ -30117,6 +30989,15 @@
       <c r="BU58" s="4">
         <f t="shared" si="22"/>
         <v>0</v>
+      </c>
+      <c r="DG58">
+        <v>9</v>
+      </c>
+      <c r="DH58" t="s">
+        <v>2064</v>
+      </c>
+      <c r="DI58">
+        <v>2024</v>
       </c>
       <c r="EV58" s="4">
         <f t="shared" si="23"/>
@@ -30143,10 +31024,63 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="59" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>57</v>
       </c>
+      <c r="B59" t="s">
+        <v>552</v>
+      </c>
+      <c r="C59" t="s">
+        <v>2038</v>
+      </c>
+      <c r="D59" t="s">
+        <v>2038</v>
+      </c>
+      <c r="E59" t="s">
+        <v>2052</v>
+      </c>
+      <c r="F59" t="str">
+        <f t="shared" si="29"/>
+        <v>COMPLEJO MIXCOATL</v>
+      </c>
+      <c r="G59" t="s">
+        <v>2056</v>
+      </c>
+      <c r="H59" t="s">
+        <v>2039</v>
+      </c>
+      <c r="I59" t="s">
+        <v>2061</v>
+      </c>
+      <c r="J59">
+        <v>327</v>
+      </c>
+      <c r="K59" t="s">
+        <v>2044</v>
+      </c>
+      <c r="L59" t="s">
+        <v>2058</v>
+      </c>
+      <c r="M59" t="s">
+        <v>424</v>
+      </c>
+      <c r="N59" t="s">
+        <v>424</v>
+      </c>
+      <c r="T59" t="str">
+        <f t="shared" si="30"/>
+        <v>NOE MORA RAMIREZ</v>
+      </c>
+      <c r="V59">
+        <v>496</v>
+      </c>
+      <c r="W59">
+        <v>298.74</v>
+      </c>
+      <c r="AE59" t="s">
+        <v>2059</v>
+      </c>
       <c r="AR59" s="4">
         <f t="shared" si="21"/>
         <v>0</v>
@@ -30154,6 +31088,15 @@
       <c r="BU59" s="4">
         <f t="shared" si="22"/>
         <v>0</v>
+      </c>
+      <c r="DG59">
+        <v>9</v>
+      </c>
+      <c r="DH59" t="s">
+        <v>2064</v>
+      </c>
+      <c r="DI59">
+        <v>2024</v>
       </c>
       <c r="EV59" s="4">
         <f t="shared" si="23"/>
@@ -30180,10 +31123,63 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="60" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>58</v>
       </c>
+      <c r="B60" t="s">
+        <v>552</v>
+      </c>
+      <c r="C60" t="s">
+        <v>2038</v>
+      </c>
+      <c r="D60" t="s">
+        <v>2038</v>
+      </c>
+      <c r="E60" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F60" t="str">
+        <f t="shared" si="29"/>
+        <v>COMPLEJO QUETZALCOATL</v>
+      </c>
+      <c r="G60" t="s">
+        <v>2056</v>
+      </c>
+      <c r="H60" t="s">
+        <v>2039</v>
+      </c>
+      <c r="I60" t="s">
+        <v>2062</v>
+      </c>
+      <c r="J60">
+        <v>5720</v>
+      </c>
+      <c r="K60" t="s">
+        <v>2045</v>
+      </c>
+      <c r="L60" t="s">
+        <v>2058</v>
+      </c>
+      <c r="M60" t="s">
+        <v>424</v>
+      </c>
+      <c r="N60" t="s">
+        <v>424</v>
+      </c>
+      <c r="T60" t="str">
+        <f t="shared" si="30"/>
+        <v>JORGE MANUEL ISLAS GOWER</v>
+      </c>
+      <c r="V60">
+        <v>2225</v>
+      </c>
+      <c r="W60">
+        <v>2206.85</v>
+      </c>
+      <c r="AE60" t="s">
+        <v>2059</v>
+      </c>
       <c r="AR60" s="4">
         <f t="shared" si="21"/>
         <v>0</v>
@@ -30191,6 +31187,15 @@
       <c r="BU60" s="4">
         <f t="shared" si="22"/>
         <v>0</v>
+      </c>
+      <c r="DG60">
+        <v>9</v>
+      </c>
+      <c r="DH60" t="s">
+        <v>2064</v>
+      </c>
+      <c r="DI60">
+        <v>2024</v>
       </c>
       <c r="EV60" s="4">
         <f t="shared" si="23"/>
@@ -30217,10 +31222,63 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="61" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>59</v>
       </c>
+      <c r="B61" t="s">
+        <v>552</v>
+      </c>
+      <c r="C61" t="s">
+        <v>2038</v>
+      </c>
+      <c r="D61" t="s">
+        <v>2038</v>
+      </c>
+      <c r="E61" t="s">
+        <v>2054</v>
+      </c>
+      <c r="F61" t="str">
+        <f t="shared" si="29"/>
+        <v>COMPLEJO TEOCALLI</v>
+      </c>
+      <c r="G61" t="s">
+        <v>2056</v>
+      </c>
+      <c r="H61" t="s">
+        <v>2039</v>
+      </c>
+      <c r="I61" t="s">
+        <v>2063</v>
+      </c>
+      <c r="J61">
+        <v>329</v>
+      </c>
+      <c r="K61" t="s">
+        <v>2046</v>
+      </c>
+      <c r="L61" t="s">
+        <v>2058</v>
+      </c>
+      <c r="M61" t="s">
+        <v>424</v>
+      </c>
+      <c r="N61" t="s">
+        <v>424</v>
+      </c>
+      <c r="T61" t="str">
+        <f t="shared" si="30"/>
+        <v>JORGE MANUEL ISLAS GOWER</v>
+      </c>
+      <c r="V61">
+        <v>1995</v>
+      </c>
+      <c r="W61">
+        <v>4052.67</v>
+      </c>
+      <c r="AE61" t="s">
+        <v>2059</v>
+      </c>
       <c r="AR61" s="4">
         <f t="shared" si="21"/>
         <v>0</v>
@@ -30228,6 +31286,15 @@
       <c r="BU61" s="4">
         <f t="shared" si="22"/>
         <v>0</v>
+      </c>
+      <c r="DG61">
+        <v>9</v>
+      </c>
+      <c r="DH61" t="s">
+        <v>2064</v>
+      </c>
+      <c r="DI61">
+        <v>2024</v>
       </c>
       <c r="EV61" s="4">
         <f t="shared" si="23"/>
@@ -30254,10 +31321,63 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="62" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>60</v>
       </c>
+      <c r="B62" t="s">
+        <v>552</v>
+      </c>
+      <c r="C62" t="s">
+        <v>2038</v>
+      </c>
+      <c r="D62" t="s">
+        <v>2038</v>
+      </c>
+      <c r="E62" t="s">
+        <v>2055</v>
+      </c>
+      <c r="F62" t="str">
+        <f t="shared" si="29"/>
+        <v>COMPLEJO TLALOC</v>
+      </c>
+      <c r="G62" t="s">
+        <v>2056</v>
+      </c>
+      <c r="H62" t="s">
+        <v>2039</v>
+      </c>
+      <c r="I62" t="s">
+        <v>2060</v>
+      </c>
+      <c r="J62">
+        <v>5904</v>
+      </c>
+      <c r="K62" t="s">
+        <v>2047</v>
+      </c>
+      <c r="L62" t="s">
+        <v>2058</v>
+      </c>
+      <c r="M62" t="s">
+        <v>424</v>
+      </c>
+      <c r="N62" t="s">
+        <v>424</v>
+      </c>
+      <c r="T62" t="str">
+        <f t="shared" si="30"/>
+        <v>NOE MORA RAMIREZ</v>
+      </c>
+      <c r="V62">
+        <v>954</v>
+      </c>
+      <c r="W62">
+        <v>858.66</v>
+      </c>
+      <c r="AE62" t="s">
+        <v>2059</v>
+      </c>
       <c r="AR62" s="4">
         <f t="shared" si="21"/>
         <v>0</v>
@@ -30265,6 +31385,15 @@
       <c r="BU62" s="4">
         <f t="shared" si="22"/>
         <v>0</v>
+      </c>
+      <c r="DG62">
+        <v>9</v>
+      </c>
+      <c r="DH62" t="s">
+        <v>2064</v>
+      </c>
+      <c r="DI62">
+        <v>2024</v>
       </c>
       <c r="EV62" s="4">
         <f t="shared" si="23"/>
@@ -30291,7 +31420,7 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="63" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>61</v>
       </c>
@@ -30328,7 +31457,7 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="64" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>62</v>
       </c>
@@ -30365,7 +31494,7 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="65" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>63</v>
       </c>
@@ -30402,7 +31531,7 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="66" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>64</v>
       </c>
@@ -30439,7 +31568,7 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="67" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>65</v>
       </c>
@@ -30476,7 +31605,7 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="68" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>66</v>
       </c>
@@ -30513,7 +31642,7 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="69" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>67</v>
       </c>
@@ -30550,7 +31679,7 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="70" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>68</v>
       </c>
@@ -30587,7 +31716,7 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="71" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>69</v>
       </c>
@@ -30624,7 +31753,7 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="72" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>70</v>
       </c>
@@ -30661,7 +31790,7 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="73" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>71</v>
       </c>
@@ -30698,7 +31827,7 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="74" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>72</v>
       </c>
@@ -30735,7 +31864,7 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="75" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>73</v>
       </c>
@@ -30772,7 +31901,7 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="76" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>74</v>
       </c>
@@ -30809,7 +31938,7 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="77" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>75</v>
       </c>
@@ -30846,4494 +31975,4494 @@
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="78" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>76</v>
       </c>
       <c r="AR78" s="4">
-        <f t="shared" ref="AR78:AR109" si="29">+AS78+AU78+BE78+BN78+BO78+BP78+BQ78+BR78+BS78+CG78</f>
+        <f t="shared" ref="AR78:AR109" si="31">+AS78+AU78+BE78+BN78+BO78+BP78+BQ78+BR78+BS78+CG78</f>
         <v>0</v>
       </c>
       <c r="BU78" s="4">
-        <f t="shared" ref="BU78:BU109" si="30">+BV78+BX78+BY78+BZ78+CA78</f>
+        <f t="shared" ref="BU78:BU109" si="32">+BV78+BX78+BY78+BZ78+CA78</f>
         <v>0</v>
       </c>
       <c r="EV78" s="4">
-        <f t="shared" ref="EV78:EV109" si="31">+EU78/3000</f>
+        <f t="shared" ref="EV78:EV109" si="33">+EU78/3000</f>
         <v>0</v>
       </c>
       <c r="EY78" s="4">
-        <f t="shared" ref="EY78:EY109" si="32">+EX78/1400</f>
+        <f t="shared" ref="EY78:EY109" si="34">+EX78/1400</f>
         <v>0</v>
       </c>
       <c r="FB78" s="4">
-        <f t="shared" ref="FB78:FB109" si="33">+FA78/2000</f>
+        <f t="shared" ref="FB78:FB109" si="35">+FA78/2000</f>
         <v>0</v>
       </c>
       <c r="FE78" s="4">
-        <f t="shared" ref="FE78:FE109" si="34">+FD78/15000</f>
+        <f t="shared" ref="FE78:FE109" si="36">+FD78/15000</f>
         <v>0</v>
       </c>
       <c r="FF78" s="4">
-        <f t="shared" ref="FF78:FF109" si="35">+EV78+EY78+FB78+FE78</f>
+        <f t="shared" ref="FF78:FF109" si="37">+EV78+EY78+FB78+FE78</f>
         <v>0</v>
       </c>
       <c r="FG78" s="4" t="str">
-        <f t="shared" ref="FG78:FG109" si="36">+IF((EV78+EY78+FB78+FE78)&gt;=1,"ALTO","ORDINARIO")</f>
+        <f t="shared" ref="FG78:FG109" si="38">+IF((EV78+EY78+FB78+FE78)&gt;=1,"ALTO","ORDINARIO")</f>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="79" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>77</v>
       </c>
       <c r="AR79" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BU79" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="EV79" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="EY79" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FB79" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FE79" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="FF79" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FG79" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="80" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>78</v>
       </c>
       <c r="AR80" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BU80" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="EV80" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="EY80" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FB80" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FE80" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="FF80" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FG80" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="81" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>79</v>
       </c>
       <c r="AR81" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BU81" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="EV81" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="EY81" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FB81" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FE81" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="FF81" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FG81" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="82" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>80</v>
       </c>
       <c r="AR82" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BU82" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="EV82" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="EY82" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FB82" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FE82" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="FF82" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FG82" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="83" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>81</v>
       </c>
       <c r="AR83" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BU83" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="EV83" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="EY83" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FB83" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FE83" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="FF83" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FG83" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="84" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>82</v>
       </c>
       <c r="AR84" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BU84" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="EV84" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="EY84" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FB84" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FE84" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="FF84" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FG84" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="85" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>83</v>
       </c>
       <c r="AR85" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BU85" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="EV85" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="EY85" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FB85" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FE85" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="FF85" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FG85" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="86" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>84</v>
       </c>
       <c r="AR86" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BU86" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="EV86" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="EY86" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FB86" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FE86" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="FF86" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FG86" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="87" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>85</v>
       </c>
       <c r="AR87" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BU87" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="EV87" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="EY87" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FB87" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FE87" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="FF87" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FG87" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="88" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>86</v>
       </c>
       <c r="AR88" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BU88" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="EV88" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="EY88" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FB88" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FE88" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="FF88" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FG88" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="89" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>87</v>
       </c>
       <c r="AR89" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BU89" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="EV89" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="EY89" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FB89" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FE89" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="FF89" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FG89" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="90" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>88</v>
       </c>
       <c r="AR90" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BU90" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="EV90" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="EY90" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FB90" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FE90" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="FF90" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FG90" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="91" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>89</v>
       </c>
       <c r="AR91" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BU91" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="EV91" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="EY91" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FB91" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FE91" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="FF91" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FG91" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="92" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>90</v>
       </c>
       <c r="AR92" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BU92" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="EV92" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="EY92" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FB92" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FE92" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="FF92" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FG92" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="93" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>91</v>
       </c>
       <c r="AR93" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BU93" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="EV93" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="EY93" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FB93" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FE93" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="FF93" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FG93" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="94" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>92</v>
       </c>
       <c r="AR94" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BU94" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="EV94" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="EY94" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FB94" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FE94" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="FF94" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FG94" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="95" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>93</v>
       </c>
       <c r="AR95" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BU95" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="EV95" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="EY95" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FB95" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FE95" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="FF95" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FG95" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="96" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>94</v>
       </c>
       <c r="AR96" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BU96" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="EV96" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="EY96" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FB96" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FE96" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="FF96" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FG96" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="97" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>95</v>
       </c>
       <c r="AR97" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BU97" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="EV97" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="EY97" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FB97" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FE97" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="FF97" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FG97" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="98" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>96</v>
       </c>
       <c r="AR98" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BU98" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="EV98" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="EY98" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FB98" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FE98" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="FF98" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FG98" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="99" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>97</v>
       </c>
       <c r="AR99" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BU99" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="EV99" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="EY99" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FB99" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FE99" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="FF99" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FG99" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="100" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>98</v>
       </c>
       <c r="AR100" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BU100" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="EV100" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="EY100" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FB100" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FE100" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="FF100" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FG100" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="101" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>99</v>
       </c>
       <c r="AR101" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BU101" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="EV101" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="EY101" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FB101" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FE101" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="FF101" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FG101" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="102" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>100</v>
       </c>
       <c r="AR102" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BU102" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="EV102" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="EY102" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FB102" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FE102" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="FF102" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FG102" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="103" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>101</v>
       </c>
       <c r="AR103" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BU103" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="EV103" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="EY103" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FB103" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FE103" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="FF103" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FG103" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="104" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>102</v>
       </c>
       <c r="AR104" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BU104" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="EV104" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="EY104" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FB104" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FE104" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="FF104" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FG104" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="105" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>103</v>
       </c>
       <c r="AR105" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BU105" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="EV105" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="EY105" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FB105" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FE105" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="FF105" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FG105" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="106" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>104</v>
       </c>
       <c r="AR106" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BU106" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="EV106" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="EY106" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FB106" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FE106" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="FF106" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FG106" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="107" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>105</v>
       </c>
       <c r="AR107" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BU107" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="EV107" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="EY107" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FB107" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FE107" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="FF107" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FG107" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="108" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>106</v>
       </c>
       <c r="AR108" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BU108" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="EV108" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="EY108" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FB108" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FE108" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="FF108" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FG108" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="109" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>107</v>
       </c>
       <c r="AR109" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BU109" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="EV109" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="EY109" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FB109" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FE109" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="FF109" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FG109" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="110" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>108</v>
       </c>
       <c r="AR110" s="4">
-        <f t="shared" ref="AR110:AR141" si="37">+AS110+AU110+BE110+BN110+BO110+BP110+BQ110+BR110+BS110+CG110</f>
+        <f t="shared" ref="AR110:AR141" si="39">+AS110+AU110+BE110+BN110+BO110+BP110+BQ110+BR110+BS110+CG110</f>
         <v>0</v>
       </c>
       <c r="BU110" s="4">
-        <f t="shared" ref="BU110:BU141" si="38">+BV110+BX110+BY110+BZ110+CA110</f>
+        <f t="shared" ref="BU110:BU141" si="40">+BV110+BX110+BY110+BZ110+CA110</f>
         <v>0</v>
       </c>
       <c r="EV110" s="4">
-        <f t="shared" ref="EV110:EV141" si="39">+EU110/3000</f>
+        <f t="shared" ref="EV110:EV141" si="41">+EU110/3000</f>
         <v>0</v>
       </c>
       <c r="EY110" s="4">
-        <f t="shared" ref="EY110:EY141" si="40">+EX110/1400</f>
+        <f t="shared" ref="EY110:EY141" si="42">+EX110/1400</f>
         <v>0</v>
       </c>
       <c r="FB110" s="4">
-        <f t="shared" ref="FB110:FB141" si="41">+FA110/2000</f>
+        <f t="shared" ref="FB110:FB141" si="43">+FA110/2000</f>
         <v>0</v>
       </c>
       <c r="FE110" s="4">
-        <f t="shared" ref="FE110:FE141" si="42">+FD110/15000</f>
+        <f t="shared" ref="FE110:FE141" si="44">+FD110/15000</f>
         <v>0</v>
       </c>
       <c r="FF110" s="4">
-        <f t="shared" ref="FF110:FF141" si="43">+EV110+EY110+FB110+FE110</f>
+        <f t="shared" ref="FF110:FF141" si="45">+EV110+EY110+FB110+FE110</f>
         <v>0</v>
       </c>
       <c r="FG110" s="4" t="str">
-        <f t="shared" ref="FG110:FG141" si="44">+IF((EV110+EY110+FB110+FE110)&gt;=1,"ALTO","ORDINARIO")</f>
+        <f t="shared" ref="FG110:FG141" si="46">+IF((EV110+EY110+FB110+FE110)&gt;=1,"ALTO","ORDINARIO")</f>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="111" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>109</v>
       </c>
       <c r="AR111" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BU111" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="EV111" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="EY111" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FB111" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FE111" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FF111" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FG111" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="112" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>110</v>
       </c>
       <c r="AR112" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BU112" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="EV112" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="EY112" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FB112" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FE112" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FF112" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FG112" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="113" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>111</v>
       </c>
       <c r="AR113" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BU113" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="EV113" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="EY113" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FB113" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FE113" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FF113" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FG113" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="114" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>112</v>
       </c>
       <c r="AR114" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BU114" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="EV114" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="EY114" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FB114" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FE114" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FF114" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FG114" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="115" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>113</v>
       </c>
       <c r="AR115" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BU115" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="EV115" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="EY115" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FB115" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FE115" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FF115" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FG115" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="116" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>114</v>
       </c>
       <c r="AR116" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BU116" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="EV116" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="EY116" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FB116" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FE116" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FF116" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FG116" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="117" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>115</v>
       </c>
       <c r="AR117" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BU117" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="EV117" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="EY117" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FB117" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FE117" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FF117" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FG117" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="118" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>116</v>
       </c>
       <c r="AR118" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BU118" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="EV118" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="EY118" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FB118" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FE118" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FF118" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FG118" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="119" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>117</v>
       </c>
       <c r="AR119" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BU119" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="EV119" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="EY119" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FB119" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FE119" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FF119" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FG119" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="120" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>118</v>
       </c>
       <c r="AR120" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BU120" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="EV120" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="EY120" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FB120" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FE120" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FF120" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FG120" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="121" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>119</v>
       </c>
       <c r="AR121" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BU121" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="EV121" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="EY121" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FB121" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FE121" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FF121" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FG121" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="122" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>120</v>
       </c>
       <c r="AR122" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BU122" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="EV122" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="EY122" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FB122" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FE122" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FF122" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FG122" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="123" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>121</v>
       </c>
       <c r="AR123" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BU123" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="EV123" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="EY123" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FB123" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FE123" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FF123" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FG123" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="124" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>122</v>
       </c>
       <c r="AR124" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BU124" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="EV124" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="EY124" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FB124" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FE124" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FF124" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FG124" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="125" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>123</v>
       </c>
       <c r="AR125" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BU125" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="EV125" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="EY125" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FB125" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FE125" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FF125" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FG125" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="126" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>124</v>
       </c>
       <c r="AR126" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BU126" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="EV126" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="EY126" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FB126" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FE126" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FF126" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FG126" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="127" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>125</v>
       </c>
       <c r="AR127" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BU127" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="EV127" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="EY127" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FB127" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FE127" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FF127" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FG127" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="128" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>126</v>
       </c>
       <c r="AR128" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BU128" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="EV128" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="EY128" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FB128" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FE128" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FF128" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FG128" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="129" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>127</v>
       </c>
       <c r="AR129" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BU129" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="EV129" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="EY129" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FB129" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FE129" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FF129" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FG129" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="130" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>128</v>
       </c>
       <c r="AR130" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BU130" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="EV130" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="EY130" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FB130" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FE130" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FF130" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FG130" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="131" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>129</v>
       </c>
       <c r="AR131" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BU131" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="EV131" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="EY131" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FB131" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FE131" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FF131" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FG131" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="132" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>130</v>
       </c>
       <c r="AR132" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BU132" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="EV132" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="EY132" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FB132" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FE132" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FF132" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FG132" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="133" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>131</v>
       </c>
       <c r="AR133" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BU133" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="EV133" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="EY133" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FB133" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FE133" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FF133" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FG133" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="134" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>132</v>
       </c>
       <c r="AR134" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BU134" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="EV134" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="EY134" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FB134" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FE134" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FF134" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FG134" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="135" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>133</v>
       </c>
       <c r="AR135" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BU135" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="EV135" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="EY135" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FB135" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FE135" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FF135" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FG135" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="136" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>134</v>
       </c>
       <c r="AR136" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BU136" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="EV136" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="EY136" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FB136" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FE136" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FF136" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FG136" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="137" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>135</v>
       </c>
       <c r="AR137" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BU137" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="EV137" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="EY137" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FB137" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FE137" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FF137" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FG137" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="138" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>136</v>
       </c>
       <c r="AR138" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BU138" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="EV138" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="EY138" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FB138" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FE138" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FF138" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FG138" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="139" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>137</v>
       </c>
       <c r="AR139" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BU139" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="EV139" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="EY139" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FB139" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FE139" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FF139" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FG139" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="140" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>138</v>
       </c>
       <c r="AR140" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BU140" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="EV140" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="EY140" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FB140" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FE140" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FF140" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FG140" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="141" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>139</v>
       </c>
       <c r="AR141" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BU141" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="EV141" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="EY141" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FB141" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FE141" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FF141" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FG141" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="142" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>140</v>
       </c>
       <c r="AR142" s="4">
-        <f t="shared" ref="AR142:AR173" si="45">+AS142+AU142+BE142+BN142+BO142+BP142+BQ142+BR142+BS142+CG142</f>
+        <f t="shared" ref="AR142:AR173" si="47">+AS142+AU142+BE142+BN142+BO142+BP142+BQ142+BR142+BS142+CG142</f>
         <v>0</v>
       </c>
       <c r="BU142" s="4">
-        <f t="shared" ref="BU142:BU173" si="46">+BV142+BX142+BY142+BZ142+CA142</f>
+        <f t="shared" ref="BU142:BU173" si="48">+BV142+BX142+BY142+BZ142+CA142</f>
         <v>0</v>
       </c>
       <c r="EV142" s="4">
-        <f t="shared" ref="EV142:EV173" si="47">+EU142/3000</f>
+        <f t="shared" ref="EV142:EV173" si="49">+EU142/3000</f>
         <v>0</v>
       </c>
       <c r="EY142" s="4">
-        <f t="shared" ref="EY142:EY173" si="48">+EX142/1400</f>
+        <f t="shared" ref="EY142:EY173" si="50">+EX142/1400</f>
         <v>0</v>
       </c>
       <c r="FB142" s="4">
-        <f t="shared" ref="FB142:FB173" si="49">+FA142/2000</f>
+        <f t="shared" ref="FB142:FB173" si="51">+FA142/2000</f>
         <v>0</v>
       </c>
       <c r="FE142" s="4">
-        <f t="shared" ref="FE142:FE173" si="50">+FD142/15000</f>
+        <f t="shared" ref="FE142:FE173" si="52">+FD142/15000</f>
         <v>0</v>
       </c>
       <c r="FF142" s="4">
-        <f t="shared" ref="FF142:FF173" si="51">+EV142+EY142+FB142+FE142</f>
+        <f t="shared" ref="FF142:FF173" si="53">+EV142+EY142+FB142+FE142</f>
         <v>0</v>
       </c>
       <c r="FG142" s="4" t="str">
-        <f t="shared" ref="FG142:FG173" si="52">+IF((EV142+EY142+FB142+FE142)&gt;=1,"ALTO","ORDINARIO")</f>
+        <f t="shared" ref="FG142:FG173" si="54">+IF((EV142+EY142+FB142+FE142)&gt;=1,"ALTO","ORDINARIO")</f>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="143" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>141</v>
       </c>
       <c r="AR143" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="BU143" s="4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="EV143" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="EY143" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="FB143" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="FE143" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FF143" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FG143" s="4" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="144" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>142</v>
       </c>
       <c r="AR144" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="BU144" s="4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="EV144" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="EY144" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="FB144" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="FE144" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FF144" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FG144" s="4" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="145" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>143</v>
       </c>
       <c r="AR145" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="BU145" s="4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="EV145" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="EY145" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="FB145" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="FE145" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FF145" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FG145" s="4" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="146" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>144</v>
       </c>
       <c r="AR146" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="BU146" s="4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="EV146" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="EY146" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="FB146" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="FE146" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FF146" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FG146" s="4" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="147" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>145</v>
       </c>
       <c r="AR147" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="BU147" s="4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="EV147" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="EY147" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="FB147" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="FE147" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FF147" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FG147" s="4" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="148" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>146</v>
       </c>
       <c r="AR148" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="BU148" s="4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="EV148" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="EY148" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="FB148" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="FE148" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FF148" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FG148" s="4" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="149" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>147</v>
       </c>
       <c r="AR149" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="BU149" s="4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="EV149" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="EY149" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="FB149" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="FE149" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FF149" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FG149" s="4" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="150" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>148</v>
       </c>
       <c r="AR150" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="BU150" s="4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="EV150" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="EY150" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="FB150" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="FE150" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FF150" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FG150" s="4" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="151" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>149</v>
       </c>
       <c r="AR151" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="BU151" s="4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="EV151" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="EY151" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="FB151" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="FE151" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FF151" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FG151" s="4" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="152" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>150</v>
       </c>
       <c r="AR152" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="BU152" s="4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="EV152" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="EY152" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="FB152" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="FE152" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FF152" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FG152" s="4" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="153" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>151</v>
       </c>
       <c r="AR153" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="BU153" s="4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="EV153" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="EY153" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="FB153" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="FE153" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FF153" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FG153" s="4" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="154" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>152</v>
       </c>
       <c r="AR154" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="BU154" s="4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="EV154" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="EY154" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="FB154" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="FE154" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FF154" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FG154" s="4" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="155" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>153</v>
       </c>
       <c r="AR155" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="BU155" s="4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="EV155" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="EY155" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="FB155" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="FE155" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FF155" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FG155" s="4" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="156" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>154</v>
       </c>
       <c r="AR156" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="BU156" s="4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="EV156" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="EY156" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="FB156" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="FE156" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FF156" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FG156" s="4" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="157" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>155</v>
       </c>
       <c r="AR157" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="BU157" s="4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="EV157" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="EY157" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="FB157" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="FE157" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FF157" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FG157" s="4" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="158" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>156</v>
       </c>
       <c r="AR158" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="BU158" s="4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="EV158" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="EY158" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="FB158" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="FE158" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FF158" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FG158" s="4" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="159" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>157</v>
       </c>
       <c r="AR159" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="BU159" s="4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="EV159" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="EY159" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="FB159" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="FE159" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FF159" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FG159" s="4" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="160" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>158</v>
       </c>
       <c r="AR160" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="BU160" s="4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="EV160" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="EY160" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="FB160" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="FE160" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FF160" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FG160" s="4" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="161" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>159</v>
       </c>
       <c r="AR161" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="BU161" s="4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="EV161" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="EY161" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="FB161" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="FE161" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FF161" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FG161" s="4" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="162" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>160</v>
       </c>
       <c r="AR162" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="BU162" s="4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="EV162" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="EY162" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="FB162" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="FE162" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FF162" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FG162" s="4" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="163" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>161</v>
       </c>
       <c r="AR163" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="BU163" s="4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="EV163" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="EY163" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="FB163" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="FE163" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FF163" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FG163" s="4" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="164" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>162</v>
       </c>
       <c r="AR164" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="BU164" s="4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="EV164" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="EY164" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="FB164" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="FE164" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FF164" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FG164" s="4" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="165" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>163</v>
       </c>
       <c r="AR165" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="BU165" s="4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="EV165" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="EY165" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="FB165" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="FE165" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FF165" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FG165" s="4" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="166" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>164</v>
       </c>
       <c r="AR166" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="BU166" s="4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="EV166" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="EY166" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="FB166" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="FE166" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FF166" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FG166" s="4" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="167" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>165</v>
       </c>
       <c r="AR167" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="BU167" s="4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="EV167" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="EY167" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="FB167" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="FE167" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FF167" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FG167" s="4" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="168" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>166</v>
       </c>
       <c r="AR168" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="BU168" s="4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="EV168" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="EY168" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="FB168" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="FE168" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FF168" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FG168" s="4" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="169" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>167</v>
       </c>
       <c r="AR169" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="BU169" s="4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="EV169" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="EY169" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="FB169" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="FE169" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FF169" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FG169" s="4" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="170" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>168</v>
       </c>
       <c r="AR170" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="BU170" s="4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="EV170" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="EY170" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="FB170" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="FE170" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FF170" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FG170" s="4" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="171" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>169</v>
       </c>
       <c r="AR171" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="BU171" s="4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="EV171" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="EY171" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="FB171" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="FE171" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FF171" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FG171" s="4" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="172" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>170</v>
       </c>
       <c r="AR172" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="BU172" s="4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="EV172" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="EY172" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="FB172" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="FE172" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FF172" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FG172" s="4" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="173" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>171</v>
       </c>
       <c r="AR173" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="BU173" s="4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="EV173" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="EY173" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="FB173" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="FE173" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FF173" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FG173" s="4" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="174" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>172</v>
       </c>
       <c r="AR174" s="4">
-        <f t="shared" ref="AR174:AR198" si="53">+AS174+AU174+BE174+BN174+BO174+BP174+BQ174+BR174+BS174+CG174</f>
+        <f t="shared" ref="AR174:AR198" si="55">+AS174+AU174+BE174+BN174+BO174+BP174+BQ174+BR174+BS174+CG174</f>
         <v>0</v>
       </c>
       <c r="BU174" s="4">
-        <f t="shared" ref="BU174:BU198" si="54">+BV174+BX174+BY174+BZ174+CA174</f>
+        <f t="shared" ref="BU174:BU198" si="56">+BV174+BX174+BY174+BZ174+CA174</f>
         <v>0</v>
       </c>
       <c r="EV174" s="4">
-        <f t="shared" ref="EV174:EV198" si="55">+EU174/3000</f>
+        <f t="shared" ref="EV174:EV198" si="57">+EU174/3000</f>
         <v>0</v>
       </c>
       <c r="EY174" s="4">
-        <f t="shared" ref="EY174:EY198" si="56">+EX174/1400</f>
+        <f t="shared" ref="EY174:EY198" si="58">+EX174/1400</f>
         <v>0</v>
       </c>
       <c r="FB174" s="4">
-        <f t="shared" ref="FB174:FB198" si="57">+FA174/2000</f>
+        <f t="shared" ref="FB174:FB198" si="59">+FA174/2000</f>
         <v>0</v>
       </c>
       <c r="FE174" s="4">
-        <f t="shared" ref="FE174:FE198" si="58">+FD174/15000</f>
+        <f t="shared" ref="FE174:FE198" si="60">+FD174/15000</f>
         <v>0</v>
       </c>
       <c r="FF174" s="4">
-        <f t="shared" ref="FF174:FF198" si="59">+EV174+EY174+FB174+FE174</f>
+        <f t="shared" ref="FF174:FF198" si="61">+EV174+EY174+FB174+FE174</f>
         <v>0</v>
       </c>
       <c r="FG174" s="4" t="str">
-        <f t="shared" ref="FG174:FG198" si="60">+IF((EV174+EY174+FB174+FE174)&gt;=1,"ALTO","ORDINARIO")</f>
+        <f t="shared" ref="FG174:FG198" si="62">+IF((EV174+EY174+FB174+FE174)&gt;=1,"ALTO","ORDINARIO")</f>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="175" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>173</v>
       </c>
       <c r="AR175" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="BU175" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="EV175" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="EY175" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FB175" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FE175" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FF175" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="FG175" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="176" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>174</v>
       </c>
       <c r="AR176" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="BU176" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="EV176" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="EY176" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FB176" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FE176" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FF176" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="FG176" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="177" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A177">
         <v>175</v>
       </c>
       <c r="AR177" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="BU177" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="EV177" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="EY177" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FB177" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FE177" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FF177" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="FG177" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="178" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>176</v>
       </c>
       <c r="AR178" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="BU178" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="EV178" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="EY178" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FB178" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FE178" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FF178" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="FG178" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="179" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A179">
         <v>177</v>
       </c>
       <c r="AR179" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="BU179" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="EV179" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="EY179" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FB179" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FE179" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FF179" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="FG179" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="180" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A180">
         <v>178</v>
       </c>
       <c r="AR180" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="BU180" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="EV180" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="EY180" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FB180" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FE180" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FF180" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="FG180" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="181" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A181">
         <v>179</v>
       </c>
       <c r="AR181" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="BU181" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="EV181" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="EY181" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FB181" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FE181" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FF181" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="FG181" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="182" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A182">
         <v>180</v>
       </c>
       <c r="AR182" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="BU182" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="EV182" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="EY182" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FB182" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FE182" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FF182" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="FG182" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="183" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A183">
         <v>181</v>
       </c>
       <c r="AR183" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="BU183" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="EV183" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="EY183" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FB183" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FE183" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FF183" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="FG183" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="184" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>182</v>
       </c>
       <c r="AR184" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="BU184" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="EV184" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="EY184" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FB184" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FE184" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FF184" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="FG184" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="185" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>183</v>
       </c>
       <c r="AR185" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="BU185" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="EV185" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="EY185" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FB185" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FE185" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FF185" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="FG185" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="186" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A186">
         <v>184</v>
       </c>
       <c r="AR186" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="BU186" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="EV186" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="EY186" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FB186" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FE186" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FF186" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="FG186" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="187" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A187">
         <v>185</v>
       </c>
       <c r="AR187" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="BU187" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="EV187" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="EY187" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FB187" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FE187" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FF187" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="FG187" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="188" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A188">
         <v>186</v>
       </c>
       <c r="AR188" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="BU188" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="EV188" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="EY188" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FB188" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FE188" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FF188" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="FG188" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="189" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A189">
         <v>187</v>
       </c>
       <c r="AR189" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="BU189" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="EV189" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="EY189" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FB189" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FE189" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FF189" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="FG189" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="190" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A190">
         <v>188</v>
       </c>
       <c r="AR190" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="BU190" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="EV190" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="EY190" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FB190" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FE190" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FF190" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="FG190" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="191" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A191">
         <v>189</v>
       </c>
       <c r="AR191" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="BU191" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="EV191" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="EY191" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FB191" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FE191" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FF191" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="FG191" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="192" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A192">
         <v>190</v>
       </c>
       <c r="AR192" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="BU192" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="EV192" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="EY192" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FB192" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FE192" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FF192" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="FG192" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="193" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A193">
         <v>191</v>
       </c>
       <c r="AR193" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="BU193" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="EV193" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="EY193" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FB193" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FE193" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FF193" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="FG193" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="194" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A194">
         <v>192</v>
       </c>
       <c r="AR194" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="BU194" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="EV194" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="EY194" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FB194" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FE194" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FF194" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="FG194" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="195" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A195">
         <v>193</v>
       </c>
       <c r="AR195" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="BU195" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="EV195" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="EY195" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FB195" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FE195" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FF195" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="FG195" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="196" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A196">
         <v>194</v>
       </c>
       <c r="AR196" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="BU196" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="EV196" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="EY196" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FB196" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FE196" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FF196" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="FG196" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="197" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A197">
         <v>195</v>
       </c>
       <c r="AR197" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="BU197" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="EV197" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="EY197" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FB197" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FE197" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FF197" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="FG197" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="198" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A198">
         <v>196</v>
       </c>
       <c r="AR198" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="BU198" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="EV198" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="EY198" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FB198" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FE198" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FF198" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="FG198" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>ORDINARIO</v>
       </c>
     </row>
-    <row r="199" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A199">
         <v>197</v>
       </c>
     </row>
-    <row r="200" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A200">
         <v>198</v>
       </c>
     </row>
-    <row r="201" spans="1:163" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:163" x14ac:dyDescent="0.35">
       <c r="A201">
         <v>199</v>
       </c>
@@ -35584,29 +36713,30 @@
     <hyperlink ref="Q44" r:id="rId31" xr:uid="{A2BBFE7A-BA9E-492E-AF1D-D4A45C7C4B60}"/>
     <hyperlink ref="Q45" r:id="rId32" xr:uid="{2BE003B8-9D85-4724-A606-402C9915F18E}"/>
     <hyperlink ref="Q46" r:id="rId33" xr:uid="{2B09FFA2-5189-4D4D-A65B-4B15422C7C5B}"/>
+    <hyperlink ref="Q51" r:id="rId34" xr:uid="{DDE804A1-A1F2-4C98-8E4E-FF4954DAAB88}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId34"/>
-  <legacyDrawing r:id="rId35"/>
+  <drawing r:id="rId35"/>
+  <legacyDrawing r:id="rId36"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x14">
       <controls>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1025" r:id="rId36" name="Spinner 1">
+            <control shapeId="1025" r:id="rId37" name="Spinner 1">
               <controlPr defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>297180</xdr:colOff>
+                    <xdr:colOff>298450</xdr:colOff>
                     <xdr:row>0</xdr:row>
-                    <xdr:rowOff>15240</xdr:rowOff>
+                    <xdr:rowOff>12700</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>617220</xdr:colOff>
+                    <xdr:colOff>615950</xdr:colOff>
                     <xdr:row>0</xdr:row>
-                    <xdr:rowOff>350520</xdr:rowOff>
+                    <xdr:rowOff>349250</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -35622,12 +36752,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76893F01-97EA-43A4-9AE2-ED099B9448DD}">
   <dimension ref="A1:JM2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:273" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:273" x14ac:dyDescent="0.35">
       <c r="A1">
         <f>+BD!A1</f>
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B1" t="s">
         <v>134</v>
@@ -36446,62 +37576,62 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="2" spans="1:273" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:273" x14ac:dyDescent="0.35">
       <c r="B2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,2, FALSE)</f>
-        <v>COMPARTAMOS</v>
+        <v>GENERAL</v>
       </c>
       <c r="C2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,3, FALSE)</f>
-        <v>BANCO COMPARTAMOS S.A INSTITUCION DE BANCA MULTIPLE</v>
+        <v>UNIVERSIDAD DEL VALLE DE PUEBLA SC</v>
       </c>
       <c r="D2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,4, FALSE)</f>
-        <v>SUCURSAL MATIAS ROMERO CEMENTERA</v>
+        <v>UNIVERSIDAD DEL VALLE DE PUEBLA SC</v>
       </c>
       <c r="E2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,5, FALSE)</f>
-        <v>BCI001030ECA</v>
-      </c>
-      <c r="F2">
+        <v>UVP810305C26</v>
+      </c>
+      <c r="F2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,6, FALSE)</f>
-        <v>0</v>
+        <v>COMPLEJO CALMECAC</v>
       </c>
       <c r="G2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,7, FALSE)</f>
-        <v>SERVICIOS FINANCIEROS</v>
-      </c>
-      <c r="H2">
+        <v>ESCUELA DE EDUCACION MEDIA Y SUPERIOR</v>
+      </c>
+      <c r="H2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,8, FALSE)</f>
-        <v>0</v>
+        <v>IMPARTICIÓN DE PROGRAMAS ACADÉMICOS, DESDE LICENCIATURAS HASTA POSGRADOS. ADEMÁS, PROMUEVE LA FORMACIÓN CONTINUA Y RECURSOS DE APRENDIZAJE. LOS ESTUDIANTES TAMBIÉN PUEDEN PARTICIPAR EN CLUBES Y ORGANIZACIONES ESTUDIANTILES PARA ENRIQUECER SU EXPERIENCIA ACADÉMICA Y SOCIAL.</v>
       </c>
       <c r="I2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,9, FALSE)</f>
-        <v>CORREGIDORA SUR</v>
+        <v>3 SUR</v>
       </c>
       <c r="J2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,10, FALSE)</f>
-        <v>302</v>
-      </c>
-      <c r="K2">
+        <v>5758</v>
+      </c>
+      <c r="K2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,11, FALSE)</f>
-        <v>0</v>
+        <v>CALMECAC</v>
       </c>
       <c r="L2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,12, FALSE)</f>
-        <v>CENTRO</v>
+        <v>EL CERRITO</v>
       </c>
       <c r="M2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,13, FALSE)</f>
-        <v>MATIAS ROMERO AVEDAÑO</v>
+        <v>PUEBLA</v>
       </c>
       <c r="N2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,14, FALSE)</f>
-        <v>OAXACA</v>
+        <v>PUEBLA</v>
       </c>
       <c r="O2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,15, FALSE)</f>
-        <v>70300</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,16, FALSE)</f>
@@ -36519,9 +37649,9 @@
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,19, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="T2">
+      <c r="T2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,20, FALSE)</f>
-        <v>0</v>
+        <v>NOE MORA RAMIREZ</v>
       </c>
       <c r="U2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,21, FALSE)</f>
@@ -36529,11 +37659,11 @@
       </c>
       <c r="V2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,22, FALSE)</f>
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="W2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,23, FALSE)</f>
-        <v>0</v>
+        <v>2530.0100000000002</v>
       </c>
       <c r="X2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,24, FALSE)</f>
@@ -36563,9 +37693,9 @@
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,30, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AE2">
+      <c r="AE2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,31, FALSE)</f>
-        <v>0</v>
+        <v>PRISCILIANO GERARDO ILLESCAS LOZANO</v>
       </c>
       <c r="AF2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,32, FALSE)</f>
@@ -36573,7 +37703,7 @@
       </c>
       <c r="AG2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,33, FALSE)</f>
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="AH2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,34, FALSE)</f>
@@ -36601,7 +37731,7 @@
       </c>
       <c r="AN2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,40, FALSE)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AO2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,41, FALSE)</f>
@@ -36885,11 +38015,11 @@
       </c>
       <c r="DG2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,111, FALSE)</f>
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="DH2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,112, FALSE)</f>
-        <v>ABRIL</v>
+        <v>MAYO</v>
       </c>
       <c r="DI2">
         <f>VLOOKUP($A$1,BD!$A$3:$HP$210,113, FALSE)</f>
@@ -37442,9 +38572,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4A8EE80-4440-4B18-8DA6-6D8F054BB32D}">
   <dimension ref="B1:W194"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>1899</v>
       </c>
@@ -37515,7 +38645,7 @@
         <v>logo1 = ''</v>
       </c>
     </row>
-    <row r="2" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>1899</v>
       </c>
@@ -37586,7 +38716,7 @@
         <v>logo2 = ''</v>
       </c>
     </row>
-    <row r="3" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>1899</v>
       </c>
@@ -37663,7 +38793,7 @@
         <v>fachada = ''</v>
       </c>
     </row>
-    <row r="4" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>1899</v>
       </c>
@@ -37740,7 +38870,7 @@
         <v>mapa = ''</v>
       </c>
     </row>
-    <row r="5" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>1899</v>
       </c>
@@ -37817,7 +38947,7 @@
         <v>esc_emer = ''</v>
       </c>
     </row>
-    <row r="6" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>1899</v>
       </c>
@@ -37894,7 +39024,7 @@
         <v>mueble1 = ''</v>
       </c>
     </row>
-    <row r="7" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>1899</v>
       </c>
@@ -37971,7 +39101,7 @@
         <v>mueble2 = ''</v>
       </c>
     </row>
-    <row r="8" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:23" x14ac:dyDescent="0.35">
       <c r="D8" t="s">
         <v>832</v>
       </c>
@@ -38042,7 +39172,7 @@
         <v>venteo = ''</v>
       </c>
     </row>
-    <row r="9" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:23" x14ac:dyDescent="0.35">
       <c r="D9" t="s">
         <v>832</v>
       </c>
@@ -38113,7 +39243,7 @@
         <v>manguera = ''</v>
       </c>
     </row>
-    <row r="10" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>1899</v>
       </c>
@@ -38190,7 +39320,7 @@
         <v>electrico = ''</v>
       </c>
     </row>
-    <row r="11" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>1899</v>
       </c>
@@ -38267,7 +39397,7 @@
         <v>banio = ''</v>
       </c>
     </row>
-    <row r="12" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:23" x14ac:dyDescent="0.35">
       <c r="D12" t="s">
         <v>832</v>
       </c>
@@ -38338,7 +39468,7 @@
         <v>cisterna = ''</v>
       </c>
     </row>
-    <row r="13" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>1899</v>
       </c>
@@ -38415,7 +39545,7 @@
         <v>sismo = ''</v>
       </c>
     </row>
-    <row r="14" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>1899</v>
       </c>
@@ -38492,7 +39622,7 @@
         <v>inundacion = ''</v>
       </c>
     </row>
-    <row r="15" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>1899</v>
       </c>
@@ -38566,7 +39696,7 @@
         <v>torm_elect = ''</v>
       </c>
     </row>
-    <row r="16" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>1899</v>
       </c>
@@ -38643,7 +39773,7 @@
         <v>incendio = ''</v>
       </c>
     </row>
-    <row r="17" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>1899</v>
       </c>
@@ -38720,7 +39850,7 @@
         <v>influenza = ''</v>
       </c>
     </row>
-    <row r="18" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>1899</v>
       </c>
@@ -38794,7 +39924,7 @@
         <v>radiacion = ''</v>
       </c>
     </row>
-    <row r="19" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>1899</v>
       </c>
@@ -38871,7 +40001,7 @@
         <v>ext1 = ''</v>
       </c>
     </row>
-    <row r="20" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>1899</v>
       </c>
@@ -38945,7 +40075,7 @@
         <v>ext2 = ''</v>
       </c>
     </row>
-    <row r="21" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>1899</v>
       </c>
@@ -39019,7 +40149,7 @@
         <v>ext3 = ''</v>
       </c>
     </row>
-    <row r="22" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>1899</v>
       </c>
@@ -39093,7 +40223,7 @@
         <v>ext4 = ''</v>
       </c>
     </row>
-    <row r="23" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>1899</v>
       </c>
@@ -39170,7 +40300,7 @@
         <v>botiquin = ''</v>
       </c>
     </row>
-    <row r="24" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>1899</v>
       </c>
@@ -39247,7 +40377,7 @@
         <v>ruta1 = ''</v>
       </c>
     </row>
-    <row r="25" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
         <v>1899</v>
       </c>
@@ -39324,7 +40454,7 @@
         <v>ruta2 = ''</v>
       </c>
     </row>
-    <row r="26" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
         <v>1899</v>
       </c>
@@ -39398,7 +40528,7 @@
         <v>ruta3 = ''</v>
       </c>
     </row>
-    <row r="27" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>1899</v>
       </c>
@@ -39472,7 +40602,7 @@
         <v>salida = ''</v>
       </c>
     </row>
-    <row r="28" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>1899</v>
       </c>
@@ -39549,7 +40679,7 @@
         <v>alarma = ''</v>
       </c>
     </row>
-    <row r="29" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>1899</v>
       </c>
@@ -39623,7 +40753,7 @@
         <v>prohib1 = ''</v>
       </c>
     </row>
-    <row r="30" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
         <v>1899</v>
       </c>
@@ -39697,7 +40827,7 @@
         <v>prohib2 = ''</v>
       </c>
     </row>
-    <row r="31" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B31" t="s">
         <v>1899</v>
       </c>
@@ -39771,7 +40901,7 @@
         <v>prohib3 = ''</v>
       </c>
     </row>
-    <row r="32" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
         <v>1899</v>
       </c>
@@ -39845,7 +40975,7 @@
         <v>prohib4 = ''</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
         <v>1899</v>
       </c>
@@ -39922,7 +41052,7 @@
         <v>layout = ''</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B34" t="s">
         <v>1899</v>
       </c>
@@ -39999,7 +41129,7 @@
         <v>cap1 = ''</v>
       </c>
     </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B35" t="s">
         <v>1899</v>
       </c>
@@ -40076,7 +41206,7 @@
         <v>cap2 = ''</v>
       </c>
     </row>
-    <row r="36" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
         <v>1899</v>
       </c>
@@ -40153,7 +41283,7 @@
         <v>cap3 = ''</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
         <v>1899</v>
       </c>
@@ -40230,7 +41360,7 @@
         <v>cap4 = ''</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
         <v>1899</v>
       </c>
@@ -40307,7 +41437,7 @@
         <v>cap5 = ''</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
         <v>1899</v>
       </c>
@@ -40384,7 +41514,7 @@
         <v>cap6 = ''</v>
       </c>
     </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
         <v>1899</v>
       </c>
@@ -40461,7 +41591,7 @@
         <v>cap7 = ''</v>
       </c>
     </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
         <v>1899</v>
       </c>
@@ -40538,7 +41668,7 @@
         <v>cap8 = ''</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B42" t="s">
         <v>1899</v>
       </c>
@@ -40615,7 +41745,7 @@
         <v>cap9 = ''</v>
       </c>
     </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B43" t="s">
         <v>1899</v>
       </c>
@@ -40692,7 +41822,7 @@
         <v>cap10 = ''</v>
       </c>
     </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B44" t="s">
         <v>1899</v>
       </c>
@@ -40769,7 +41899,7 @@
         <v>cap11 = ''</v>
       </c>
     </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B45" t="s">
         <v>1899</v>
       </c>
@@ -40846,7 +41976,7 @@
         <v>cap12 = ''</v>
       </c>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B46" t="s">
         <v>1899</v>
       </c>
@@ -40923,7 +42053,7 @@
         <v>sim1 = ''</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B47" t="s">
         <v>1899</v>
       </c>
@@ -41000,7 +42130,7 @@
         <v>sim2 = ''</v>
       </c>
     </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B48" t="s">
         <v>1899</v>
       </c>
@@ -41077,7 +42207,7 @@
         <v>sim3 = ''</v>
       </c>
     </row>
-    <row r="49" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B49" t="s">
         <v>1899</v>
       </c>
@@ -41154,7 +42284,7 @@
         <v>sim4 = ''</v>
       </c>
     </row>
-    <row r="50" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B50" t="s">
         <v>1899</v>
       </c>
@@ -41231,7 +42361,7 @@
         <v>sim5 = ''</v>
       </c>
     </row>
-    <row r="51" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B51" t="s">
         <v>1899</v>
       </c>
@@ -41308,7 +42438,7 @@
         <v>sim6 = ''</v>
       </c>
     </row>
-    <row r="52" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B52" t="s">
         <v>1899</v>
       </c>
@@ -41385,7 +42515,7 @@
         <v>techo = ''</v>
       </c>
     </row>
-    <row r="53" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B53" t="s">
         <v>1899</v>
       </c>
@@ -41462,7 +42592,7 @@
         <v>pisos = ''</v>
       </c>
     </row>
-    <row r="54" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B54" t="s">
         <v>1899</v>
       </c>
@@ -41536,7 +42666,7 @@
         <v>puerta = ''</v>
       </c>
     </row>
-    <row r="55" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:23" x14ac:dyDescent="0.35">
       <c r="C55" t="s">
         <v>843</v>
       </c>
@@ -41607,7 +42737,7 @@
         <v>estantes = ''</v>
       </c>
     </row>
-    <row r="56" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:23" x14ac:dyDescent="0.35">
       <c r="C56" t="s">
         <v>843</v>
       </c>
@@ -41681,7 +42811,7 @@
         <v>site = ''</v>
       </c>
     </row>
-    <row r="57" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B57" t="s">
         <v>1899</v>
       </c>
@@ -41758,7 +42888,7 @@
         <v>dh = ''</v>
       </c>
     </row>
-    <row r="58" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:23" x14ac:dyDescent="0.35">
       <c r="C58" t="s">
         <v>843</v>
       </c>
@@ -41832,7 +42962,7 @@
         <v>ventanas = ''</v>
       </c>
     </row>
-    <row r="59" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:23" x14ac:dyDescent="0.35">
       <c r="D59" t="s">
         <v>832</v>
       </c>
@@ -41903,7 +43033,7 @@
         <v>compresor = ''</v>
       </c>
     </row>
-    <row r="60" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:23" x14ac:dyDescent="0.35">
       <c r="D60" t="s">
         <v>832</v>
       </c>
@@ -41974,7 +43104,7 @@
         <v>quimicos = ''</v>
       </c>
     </row>
-    <row r="61" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:23" x14ac:dyDescent="0.35">
       <c r="D61" t="s">
         <v>832</v>
       </c>
@@ -42045,7 +43175,7 @@
         <v>tanques_gaso = ''</v>
       </c>
     </row>
-    <row r="62" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:23" x14ac:dyDescent="0.35">
       <c r="D62" t="s">
         <v>832</v>
       </c>
@@ -42116,7 +43246,7 @@
         <v>paro = ''</v>
       </c>
     </row>
-    <row r="63" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:23" x14ac:dyDescent="0.35">
       <c r="D63" t="s">
         <v>832</v>
       </c>
@@ -42187,7 +43317,7 @@
         <v>trampa_grasa = ''</v>
       </c>
     </row>
-    <row r="64" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:23" x14ac:dyDescent="0.35">
       <c r="E64" t="s">
         <v>21</v>
       </c>
@@ -42255,7 +43385,7 @@
         <v>planta = ''</v>
       </c>
     </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:23" x14ac:dyDescent="0.35">
       <c r="E65" t="s">
         <v>414</v>
       </c>
@@ -42323,7 +43453,7 @@
         <v>deposito = ''</v>
       </c>
     </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:23" x14ac:dyDescent="0.35">
       <c r="C66" t="s">
         <v>843</v>
       </c>
@@ -42394,7 +43524,7 @@
         <v>mapa_satel = ''</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.35">
       <c r="C67" t="s">
         <v>843</v>
       </c>
@@ -42465,7 +43595,7 @@
         <v>plano = ''</v>
       </c>
     </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:23" x14ac:dyDescent="0.35">
       <c r="C68" t="s">
         <v>843</v>
       </c>
@@ -42536,7 +43666,7 @@
         <v>inmueble1 = ''</v>
       </c>
     </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:23" x14ac:dyDescent="0.35">
       <c r="C69" t="s">
         <v>843</v>
       </c>
@@ -42607,7 +43737,7 @@
         <v>inmueble2 = ''</v>
       </c>
     </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:23" x14ac:dyDescent="0.35">
       <c r="C70" t="s">
         <v>843</v>
       </c>
@@ -42678,7 +43808,7 @@
         <v>banio1 = ''</v>
       </c>
     </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:23" x14ac:dyDescent="0.35">
       <c r="C71" t="s">
         <v>843</v>
       </c>
@@ -42749,7 +43879,7 @@
         <v>electrico1 = ''</v>
       </c>
     </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:23" x14ac:dyDescent="0.35">
       <c r="C72" t="s">
         <v>843</v>
       </c>
@@ -42823,7 +43953,7 @@
         <v>fachada1 = ''</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.35">
       <c r="C73" t="s">
         <v>843</v>
       </c>
@@ -42894,7 +44024,7 @@
         <v>bateria = ''</v>
       </c>
     </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B74" t="s">
         <v>1899</v>
       </c>
@@ -42973,7 +44103,7 @@
         <v>acta1 = ''</v>
       </c>
     </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B75" t="s">
         <v>1899</v>
       </c>
@@ -43052,7 +44182,7 @@
         <v>acta2 = ''</v>
       </c>
     </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B76" t="s">
         <v>1899</v>
       </c>
@@ -43131,7 +44261,7 @@
         <v>crono_anual = ''</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B77" t="s">
         <v>1899</v>
       </c>
@@ -43210,7 +44340,7 @@
         <v>mantto1 = ''</v>
       </c>
     </row>
-    <row r="78" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:23" x14ac:dyDescent="0.35">
       <c r="C78" t="s">
         <v>843</v>
       </c>
@@ -43286,7 +44416,7 @@
         <v>mantto2 = ''</v>
       </c>
     </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B79" t="s">
         <v>1899</v>
       </c>
@@ -43365,7 +44495,7 @@
         <v>simulacro = ''</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B80" t="s">
         <v>1899</v>
       </c>
@@ -43444,7 +44574,7 @@
         <v>capacitacion = ''</v>
       </c>
     </row>
-    <row r="81" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B81" t="s">
         <v>1899</v>
       </c>
@@ -43523,7 +44653,7 @@
         <v>inv_quim = ''</v>
       </c>
     </row>
-    <row r="82" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B82" t="s">
         <v>1899</v>
       </c>
@@ -43602,7 +44732,7 @@
         <v>inv_emer = ''</v>
       </c>
     </row>
-    <row r="83" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B83" t="s">
         <v>1899</v>
       </c>
@@ -43681,7 +44811,7 @@
         <v>bit_emer = ''</v>
       </c>
     </row>
-    <row r="84" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B84" t="s">
         <v>1899</v>
       </c>
@@ -43760,7 +44890,7 @@
         <v>insp_bot = ''</v>
       </c>
     </row>
-    <row r="85" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B85" t="s">
         <v>1899</v>
       </c>
@@ -43839,7 +44969,7 @@
         <v>insp_ext = ''</v>
       </c>
     </row>
-    <row r="86" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B86" t="s">
         <v>1899</v>
       </c>
@@ -43918,7 +45048,7 @@
         <v>insp_dh = ''</v>
       </c>
     </row>
-    <row r="87" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B87" t="s">
         <v>1899</v>
       </c>
@@ -43994,7 +45124,7 @@
         <v>insp_lamp = ''</v>
       </c>
     </row>
-    <row r="88" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B88" t="s">
         <v>1899</v>
       </c>
@@ -44073,7 +45203,7 @@
         <v>insp_alarm = ''</v>
       </c>
     </row>
-    <row r="89" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B89" t="s">
         <v>1899</v>
       </c>
@@ -44152,7 +45282,7 @@
         <v>ev_sim1 = ''</v>
       </c>
     </row>
-    <row r="90" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B90" t="s">
         <v>1899</v>
       </c>
@@ -44231,7 +45361,7 @@
         <v>ev_sim2 = ''</v>
       </c>
     </row>
-    <row r="91" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B91" t="s">
         <v>1899</v>
       </c>
@@ -44310,7 +45440,7 @@
         <v>visitas = ''</v>
       </c>
     </row>
-    <row r="92" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B92" t="s">
         <v>1899</v>
       </c>
@@ -44387,7 +45517,7 @@
         <v>dir_emer = ''</v>
       </c>
     </row>
-    <row r="93" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:23" x14ac:dyDescent="0.35">
       <c r="C93" t="s">
         <v>843</v>
       </c>
@@ -44460,7 +45590,7 @@
         <v>corresp1 = ''</v>
       </c>
     </row>
-    <row r="94" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:23" x14ac:dyDescent="0.35">
       <c r="C94" t="s">
         <v>843</v>
       </c>
@@ -44533,7 +45663,7 @@
         <v>corresp2 = ''</v>
       </c>
     </row>
-    <row r="95" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:23" x14ac:dyDescent="0.35">
       <c r="C95" t="s">
         <v>843</v>
       </c>
@@ -44606,7 +45736,7 @@
         <v>corresp3 = ''</v>
       </c>
     </row>
-    <row r="96" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:23" x14ac:dyDescent="0.35">
       <c r="C96" t="s">
         <v>843</v>
       </c>
@@ -44679,7 +45809,7 @@
         <v>carta_respon = ''</v>
       </c>
     </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="97" spans="3:23" x14ac:dyDescent="0.35">
       <c r="C97" t="s">
         <v>843</v>
       </c>
@@ -44752,7 +45882,7 @@
         <v>registro1 = ''</v>
       </c>
     </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="98" spans="3:23" x14ac:dyDescent="0.35">
       <c r="C98" t="s">
         <v>843</v>
       </c>
@@ -44825,7 +45955,7 @@
         <v>registro2 = ''</v>
       </c>
     </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="99" spans="3:23" x14ac:dyDescent="0.35">
       <c r="C99" t="s">
         <v>843</v>
       </c>
@@ -44898,7 +46028,7 @@
         <v>ries_circ = ''</v>
       </c>
     </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="100" spans="3:23" x14ac:dyDescent="0.35">
       <c r="C100" t="s">
         <v>843</v>
       </c>
@@ -44971,7 +46101,7 @@
         <v>mapa_ext = ''</v>
       </c>
     </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="101" spans="3:23" x14ac:dyDescent="0.35">
       <c r="C101" t="s">
         <v>843</v>
       </c>
@@ -45044,7 +46174,7 @@
         <v>rec_ext = ''</v>
       </c>
     </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="102" spans="3:23" x14ac:dyDescent="0.35">
       <c r="C102" t="s">
         <v>843</v>
       </c>
@@ -45117,7 +46247,7 @@
         <v>mayor_ries = ''</v>
       </c>
     </row>
-    <row r="103" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="103" spans="3:23" x14ac:dyDescent="0.35">
       <c r="C103" t="s">
         <v>843</v>
       </c>
@@ -45190,7 +46320,7 @@
         <v>menor_ries = ''</v>
       </c>
     </row>
-    <row r="104" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="104" spans="3:23" x14ac:dyDescent="0.35">
       <c r="C104" t="s">
         <v>843</v>
       </c>
@@ -45263,7 +46393,7 @@
         <v>zona_evac = ''</v>
       </c>
     </row>
-    <row r="105" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="105" spans="3:23" x14ac:dyDescent="0.35">
       <c r="C105" t="s">
         <v>843</v>
       </c>
@@ -45278,7 +46408,7 @@
         <v>'este' : r_val['este'],</v>
       </c>
     </row>
-    <row r="106" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="106" spans="3:23" x14ac:dyDescent="0.35">
       <c r="J106" t="s">
         <v>199</v>
       </c>
@@ -45290,7 +46420,7 @@
         <v>'oeste' : r_val['oeste'],</v>
       </c>
     </row>
-    <row r="107" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="107" spans="3:23" x14ac:dyDescent="0.35">
       <c r="J107" t="s">
         <v>597</v>
       </c>
@@ -45302,7 +46432,7 @@
         <v>'ref_llegar' : r_val['ref_llegar'],</v>
       </c>
     </row>
-    <row r="108" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="108" spans="3:23" x14ac:dyDescent="0.35">
       <c r="J108" t="s">
         <v>200</v>
       </c>
@@ -45314,7 +46444,7 @@
         <v>'ley' : r_val['ley'],</v>
       </c>
     </row>
-    <row r="109" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="109" spans="3:23" x14ac:dyDescent="0.35">
       <c r="J109" t="s">
         <v>201</v>
       </c>
@@ -45326,7 +46456,7 @@
         <v>'reglamento' : r_val['reglamento'],</v>
       </c>
     </row>
-    <row r="110" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="110" spans="3:23" x14ac:dyDescent="0.35">
       <c r="J110" t="s">
         <v>647</v>
       </c>
@@ -45338,7 +46468,7 @@
         <v>'m_dir' : r_val['m_dir'],</v>
       </c>
     </row>
-    <row r="111" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="111" spans="3:23" x14ac:dyDescent="0.35">
       <c r="J111" t="s">
         <v>202</v>
       </c>
@@ -45350,7 +46480,7 @@
         <v>'coord_suplente' : r_val['coord_suplente'],</v>
       </c>
     </row>
-    <row r="112" spans="3:23" x14ac:dyDescent="0.3">
+    <row r="112" spans="3:23" x14ac:dyDescent="0.35">
       <c r="J112" t="s">
         <v>648</v>
       </c>
@@ -45362,7 +46492,7 @@
         <v>'m_jef_caj' : r_val['m_jef_caj'],</v>
       </c>
     </row>
-    <row r="113" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="113" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J113" t="s">
         <v>203</v>
       </c>
@@ -45374,7 +46504,7 @@
         <v>'evacuacion' : r_val['evacuacion'],</v>
       </c>
     </row>
-    <row r="114" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="114" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J114" t="s">
         <v>581</v>
       </c>
@@ -45386,7 +46516,7 @@
         <v>'evac_puesto' : r_val['evac_puesto'],</v>
       </c>
     </row>
-    <row r="115" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="115" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J115" t="s">
         <v>649</v>
       </c>
@@ -45398,7 +46528,7 @@
         <v>'m_evac' : r_val['m_evac'],</v>
       </c>
     </row>
-    <row r="116" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="116" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J116" t="s">
         <v>204</v>
       </c>
@@ -45410,7 +46540,7 @@
         <v>'evac_suplente' : r_val['evac_suplente'],</v>
       </c>
     </row>
-    <row r="117" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="117" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J117" t="s">
         <v>582</v>
       </c>
@@ -45422,7 +46552,7 @@
         <v>'supl_evac_pue' : r_val['supl_evac_pue'],</v>
       </c>
     </row>
-    <row r="118" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="118" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J118" t="s">
         <v>650</v>
       </c>
@@ -45434,7 +46564,7 @@
         <v>'m_supl_evac' : r_val['m_supl_evac'],</v>
       </c>
     </row>
-    <row r="119" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="119" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J119" t="s">
         <v>205</v>
       </c>
@@ -45446,7 +46576,7 @@
         <v>'incendios' : r_val['incendios'],</v>
       </c>
     </row>
-    <row r="120" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="120" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J120" t="s">
         <v>583</v>
       </c>
@@ -45458,7 +46588,7 @@
         <v>'incen_puesto' : r_val['incen_puesto'],</v>
       </c>
     </row>
-    <row r="121" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="121" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J121" t="s">
         <v>651</v>
       </c>
@@ -45470,7 +46600,7 @@
         <v>'m_inc' : r_val['m_inc'],</v>
       </c>
     </row>
-    <row r="122" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="122" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J122" t="s">
         <v>206</v>
       </c>
@@ -45482,7 +46612,7 @@
         <v>'inc_suplente' : r_val['inc_suplente'],</v>
       </c>
     </row>
-    <row r="123" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="123" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J123" t="s">
         <v>584</v>
       </c>
@@ -45494,7 +46624,7 @@
         <v>'supl_inc_puesto' : r_val['supl_inc_puesto'],</v>
       </c>
     </row>
-    <row r="124" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="124" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J124" t="s">
         <v>652</v>
       </c>
@@ -45506,7 +46636,7 @@
         <v>'m_supl_inc' : r_val['m_supl_inc'],</v>
       </c>
     </row>
-    <row r="125" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="125" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J125" t="s">
         <v>207</v>
       </c>
@@ -45518,7 +46648,7 @@
         <v>'primeros_auxilios' : r_val['primeros_auxilios'],</v>
       </c>
     </row>
-    <row r="126" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="126" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J126" t="s">
         <v>585</v>
       </c>
@@ -45530,7 +46660,7 @@
         <v>'prim_aux_puesto' : r_val['prim_aux_puesto'],</v>
       </c>
     </row>
-    <row r="127" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="127" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J127" t="s">
         <v>653</v>
       </c>
@@ -45542,7 +46672,7 @@
         <v>'m_prim_aux' : r_val['m_prim_aux'],</v>
       </c>
     </row>
-    <row r="128" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="128" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J128" t="s">
         <v>208</v>
       </c>
@@ -45554,7 +46684,7 @@
         <v>'aux_suplente' : r_val['aux_suplente'],</v>
       </c>
     </row>
-    <row r="129" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="129" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J129" t="s">
         <v>586</v>
       </c>
@@ -45566,7 +46696,7 @@
         <v>'supl_prim_aux_puesto' : r_val['supl_prim_aux_puesto'],</v>
       </c>
     </row>
-    <row r="130" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="130" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J130" t="s">
         <v>654</v>
       </c>
@@ -45578,7 +46708,7 @@
         <v>'m_supl_paux' : r_val['m_supl_paux'],</v>
       </c>
     </row>
-    <row r="131" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="131" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J131" t="s">
         <v>209</v>
       </c>
@@ -45590,7 +46720,7 @@
         <v>'busqueda' : r_val['busqueda'],</v>
       </c>
     </row>
-    <row r="132" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="132" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J132" t="s">
         <v>587</v>
       </c>
@@ -45602,7 +46732,7 @@
         <v>'busq_puesto' : r_val['busq_puesto'],</v>
       </c>
     </row>
-    <row r="133" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="133" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J133" t="s">
         <v>655</v>
       </c>
@@ -45614,7 +46744,7 @@
         <v>'m_busq' : r_val['m_busq'],</v>
       </c>
     </row>
-    <row r="134" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="134" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J134" t="s">
         <v>210</v>
       </c>
@@ -45626,7 +46756,7 @@
         <v>'busq_suplente' : r_val['busq_suplente'],</v>
       </c>
     </row>
-    <row r="135" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="135" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J135" t="s">
         <v>588</v>
       </c>
@@ -45638,7 +46768,7 @@
         <v>'supl_busq_puesto' : r_val['supl_busq_puesto'],</v>
       </c>
     </row>
-    <row r="136" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="136" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J136" t="s">
         <v>656</v>
       </c>
@@ -45650,7 +46780,7 @@
         <v>'m_supl_busq' : r_val['m_supl_busq'],</v>
       </c>
     </row>
-    <row r="137" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="137" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J137" t="s">
         <v>211</v>
       </c>
@@ -45662,7 +46792,7 @@
         <v>'descrip_gi' : r_val['descrip_gi'],</v>
       </c>
     </row>
-    <row r="138" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="138" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J138" t="s">
         <v>212</v>
       </c>
@@ -45674,7 +46804,7 @@
         <v>'gas_inflamable' : r_val['gas_inflamable'],</v>
       </c>
     </row>
-    <row r="139" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="139" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J139" t="s">
         <v>213</v>
       </c>
@@ -45686,7 +46816,7 @@
         <v>'valor_gi' : r_val['valor_gi'],</v>
       </c>
     </row>
-    <row r="140" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="140" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J140" t="s">
         <v>214</v>
       </c>
@@ -45698,7 +46828,7 @@
         <v>'descrp_li' : r_val['descrp_li'],</v>
       </c>
     </row>
-    <row r="141" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="141" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J141" t="s">
         <v>215</v>
       </c>
@@ -45710,7 +46840,7 @@
         <v>'liquido_inflamable' : r_val['liquido_inflamable'],</v>
       </c>
     </row>
-    <row r="142" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="142" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J142" t="s">
         <v>216</v>
       </c>
@@ -45722,7 +46852,7 @@
         <v>'valor_li' : r_val['valor_li'],</v>
       </c>
     </row>
-    <row r="143" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="143" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J143" t="s">
         <v>217</v>
       </c>
@@ -45734,7 +46864,7 @@
         <v>'descrip_lc' : r_val['descrip_lc'],</v>
       </c>
     </row>
-    <row r="144" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="144" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J144" t="s">
         <v>218</v>
       </c>
@@ -45746,7 +46876,7 @@
         <v>'liquido_combustible' : r_val['liquido_combustible'],</v>
       </c>
     </row>
-    <row r="145" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="145" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J145" t="s">
         <v>219</v>
       </c>
@@ -45758,7 +46888,7 @@
         <v>'valor_lc' : r_val['valor_lc'],</v>
       </c>
     </row>
-    <row r="146" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="146" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J146" t="s">
         <v>220</v>
       </c>
@@ -45770,7 +46900,7 @@
         <v>'descrip_sc' : r_val['descrip_sc'],</v>
       </c>
     </row>
-    <row r="147" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="147" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J147" t="s">
         <v>221</v>
       </c>
@@ -45782,7 +46912,7 @@
         <v>'solido_combusible' : r_val['solido_combusible'],</v>
       </c>
     </row>
-    <row r="148" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="148" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J148" t="s">
         <v>222</v>
       </c>
@@ -45794,7 +46924,7 @@
         <v>'valor_sc' : r_val['valor_sc'],</v>
       </c>
     </row>
-    <row r="149" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="149" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J149" t="s">
         <v>223</v>
       </c>
@@ -45806,7 +46936,7 @@
         <v>'tipo_riesgo' : r_val['tipo_riesgo'],</v>
       </c>
     </row>
-    <row r="150" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="150" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J150" t="s">
         <v>617</v>
       </c>
@@ -45818,7 +46948,7 @@
         <v>'nombre1' : r_val['nombre1'],</v>
       </c>
     </row>
-    <row r="151" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="151" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J151" t="s">
         <v>619</v>
       </c>
@@ -45830,7 +46960,7 @@
         <v>'puesto1' : r_val['puesto1'],</v>
       </c>
     </row>
-    <row r="152" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="152" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J152" t="s">
         <v>637</v>
       </c>
@@ -45842,7 +46972,7 @@
         <v>'m1' : r_val['m1'],</v>
       </c>
     </row>
-    <row r="153" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="153" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J153" t="s">
         <v>618</v>
       </c>
@@ -45854,7 +46984,7 @@
         <v>'nombre2' : r_val['nombre2'],</v>
       </c>
     </row>
-    <row r="154" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="154" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J154" t="s">
         <v>620</v>
       </c>
@@ -45866,7 +46996,7 @@
         <v>'puesto2' : r_val['puesto2'],</v>
       </c>
     </row>
-    <row r="155" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="155" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J155" t="s">
         <v>638</v>
       </c>
@@ -45878,7 +47008,7 @@
         <v>'m2' : r_val['m2'],</v>
       </c>
     </row>
-    <row r="156" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="156" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J156" t="s">
         <v>621</v>
       </c>
@@ -45890,7 +47020,7 @@
         <v>'nombre3' : r_val['nombre3'],</v>
       </c>
     </row>
-    <row r="157" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="157" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J157" t="s">
         <v>622</v>
       </c>
@@ -45902,7 +47032,7 @@
         <v>'puesto3' : r_val['puesto3'],</v>
       </c>
     </row>
-    <row r="158" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="158" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J158" t="s">
         <v>639</v>
       </c>
@@ -45914,7 +47044,7 @@
         <v>'m3' : r_val['m3'],</v>
       </c>
     </row>
-    <row r="159" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="159" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J159" t="s">
         <v>623</v>
       </c>
@@ -45926,7 +47056,7 @@
         <v>'nombre4' : r_val['nombre4'],</v>
       </c>
     </row>
-    <row r="160" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="160" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J160" t="s">
         <v>624</v>
       </c>
@@ -45938,7 +47068,7 @@
         <v>'puesto4' : r_val['puesto4'],</v>
       </c>
     </row>
-    <row r="161" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="161" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J161" t="s">
         <v>640</v>
       </c>
@@ -45950,7 +47080,7 @@
         <v>'m4' : r_val['m4'],</v>
       </c>
     </row>
-    <row r="162" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="162" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J162" t="s">
         <v>625</v>
       </c>
@@ -45962,7 +47092,7 @@
         <v>'nombre5' : r_val['nombre5'],</v>
       </c>
     </row>
-    <row r="163" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="163" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J163" t="s">
         <v>626</v>
       </c>
@@ -45974,7 +47104,7 @@
         <v>'puesto5' : r_val['puesto5'],</v>
       </c>
     </row>
-    <row r="164" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="164" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J164" t="s">
         <v>641</v>
       </c>
@@ -45986,7 +47116,7 @@
         <v>'m5' : r_val['m5'],</v>
       </c>
     </row>
-    <row r="165" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="165" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J165" t="s">
         <v>627</v>
       </c>
@@ -45998,7 +47128,7 @@
         <v>'nombre6' : r_val['nombre6'],</v>
       </c>
     </row>
-    <row r="166" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="166" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J166" t="s">
         <v>628</v>
       </c>
@@ -46010,7 +47140,7 @@
         <v>'puesto6' : r_val['puesto6'],</v>
       </c>
     </row>
-    <row r="167" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="167" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J167" t="s">
         <v>642</v>
       </c>
@@ -46022,7 +47152,7 @@
         <v>'m6' : r_val['m6'],</v>
       </c>
     </row>
-    <row r="168" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="168" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J168" t="s">
         <v>629</v>
       </c>
@@ -46034,7 +47164,7 @@
         <v>'nombre7' : r_val['nombre7'],</v>
       </c>
     </row>
-    <row r="169" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="169" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J169" t="s">
         <v>630</v>
       </c>
@@ -46046,7 +47176,7 @@
         <v>'puesto7' : r_val['puesto7'],</v>
       </c>
     </row>
-    <row r="170" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="170" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J170" t="s">
         <v>643</v>
       </c>
@@ -46058,7 +47188,7 @@
         <v>'m7' : r_val['m7'],</v>
       </c>
     </row>
-    <row r="171" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="171" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J171" t="s">
         <v>631</v>
       </c>
@@ -46070,7 +47200,7 @@
         <v>'nombre8' : r_val['nombre8'],</v>
       </c>
     </row>
-    <row r="172" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="172" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J172" t="s">
         <v>632</v>
       </c>
@@ -46082,7 +47212,7 @@
         <v>'puesto8' : r_val['puesto8'],</v>
       </c>
     </row>
-    <row r="173" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="173" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J173" t="s">
         <v>644</v>
       </c>
@@ -46094,7 +47224,7 @@
         <v>'m8' : r_val['m8'],</v>
       </c>
     </row>
-    <row r="174" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="174" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J174" t="s">
         <v>633</v>
       </c>
@@ -46106,7 +47236,7 @@
         <v>'nombre9' : r_val['nombre9'],</v>
       </c>
     </row>
-    <row r="175" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="175" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J175" t="s">
         <v>634</v>
       </c>
@@ -46118,7 +47248,7 @@
         <v>'puesto9' : r_val['puesto9'],</v>
       </c>
     </row>
-    <row r="176" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="176" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J176" t="s">
         <v>645</v>
       </c>
@@ -46130,7 +47260,7 @@
         <v>'m9' : r_val['m9'],</v>
       </c>
     </row>
-    <row r="177" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="177" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J177" t="s">
         <v>635</v>
       </c>
@@ -46142,7 +47272,7 @@
         <v>'nombre10' : r_val['nombre10'],</v>
       </c>
     </row>
-    <row r="178" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="178" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J178" t="s">
         <v>636</v>
       </c>
@@ -46154,7 +47284,7 @@
         <v>'puesto10' : r_val['puesto10'],</v>
       </c>
     </row>
-    <row r="179" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="179" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J179" t="s">
         <v>646</v>
       </c>
@@ -46166,7 +47296,7 @@
         <v>'m10' : r_val['m10'],</v>
       </c>
     </row>
-    <row r="180" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="180" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J180" t="s">
         <v>1728</v>
       </c>
@@ -46179,7 +47309,7 @@
         <v>'registro_perito' : r_val['registro_perito'],</v>
       </c>
     </row>
-    <row r="181" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="181" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J181" t="s">
         <v>1729</v>
       </c>
@@ -46192,7 +47322,7 @@
         <v>'no_registro' : r_val['no_registro'],</v>
       </c>
     </row>
-    <row r="182" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="182" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J182" t="s">
         <v>1733</v>
       </c>
@@ -46205,7 +47335,7 @@
         <v>'dh_int' : r_val['dh_int'],</v>
       </c>
     </row>
-    <row r="183" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="183" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J183" t="s">
         <v>1734</v>
       </c>
@@ -46218,7 +47348,7 @@
         <v>'dh_ext' : r_val['dh_ext'],</v>
       </c>
     </row>
-    <row r="184" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="184" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J184" t="s">
         <v>1735</v>
       </c>
@@ -46231,7 +47361,7 @@
         <v>'detectores_ext' : r_val['detectores_ext'],</v>
       </c>
     </row>
-    <row r="185" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="185" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J185" t="s">
         <v>1736</v>
       </c>
@@ -46244,7 +47374,7 @@
         <v>'coord_sup_puesto' : r_val['coord_sup_puesto'],</v>
       </c>
     </row>
-    <row r="186" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="186" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J186" t="s">
         <v>1742</v>
       </c>
@@ -46257,7 +47387,7 @@
         <v>'riesgo1' : r_val['riesgo1'],</v>
       </c>
     </row>
-    <row r="187" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="187" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J187" t="s">
         <v>1743</v>
       </c>
@@ -46270,7 +47400,7 @@
         <v>'riesgo2' : r_val['riesgo2'],</v>
       </c>
     </row>
-    <row r="188" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="188" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J188" t="s">
         <v>1744</v>
       </c>
@@ -46283,7 +47413,7 @@
         <v>'riesgo3' : r_val['riesgo3'],</v>
       </c>
     </row>
-    <row r="189" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="189" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J189" t="s">
         <v>1745</v>
       </c>
@@ -46296,7 +47426,7 @@
         <v>'riesgo4' : r_val['riesgo4'],</v>
       </c>
     </row>
-    <row r="190" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="190" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J190" t="s">
         <v>1749</v>
       </c>
@@ -46309,7 +47439,7 @@
         <v>'valor_gri' : r_val['valor_gri'],</v>
       </c>
     </row>
-    <row r="191" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="191" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J191" t="s">
         <v>1750</v>
       </c>
@@ -46322,7 +47452,7 @@
         <v>'medidas_ries1' : r_val['medidas_ries1'],</v>
       </c>
     </row>
-    <row r="192" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="192" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J192" t="s">
         <v>1751</v>
       </c>
@@ -46335,7 +47465,7 @@
         <v>'medidas_ries2' : r_val['medidas_ries2'],</v>
       </c>
     </row>
-    <row r="193" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="193" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J193" t="s">
         <v>1752</v>
       </c>
@@ -46348,7 +47478,7 @@
         <v>'medidas_ries3' : r_val['medidas_ries3'],</v>
       </c>
     </row>
-    <row r="194" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="194" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J194" t="s">
         <v>1753</v>
       </c>

--- a/Inputs/BD.xlsx
+++ b/Inputs/BD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/078e1a455e5c02ce/Documentos/GitHub/Proyecto_PIPC/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6242" documentId="13_ncr:1_{7D3A426E-EC5E-453A-8CC7-F83B71F24F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6FA3155-E44A-4DE4-96B9-E887838E4F64}"/>
+  <xr:revisionPtr revIDLastSave="6316" documentId="13_ncr:1_{7D3A426E-EC5E-453A-8CC7-F83B71F24F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B58571F-D84D-438F-B359-A07494472925}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3F095A75-F066-4695-8672-8D4315F1EF23}"/>
   </bookViews>
@@ -563,7 +563,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7062" uniqueCount="2149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7178" uniqueCount="2175">
   <si>
     <t>dia</t>
   </si>
@@ -7010,6 +7010,84 @@
   </si>
   <si>
     <t>layout12</t>
+  </si>
+  <si>
+    <t>ev_sim (3).png</t>
+  </si>
+  <si>
+    <t>ev_sim (4).png</t>
+  </si>
+  <si>
+    <t>ev_sim (5).png</t>
+  </si>
+  <si>
+    <t>ev_sim (6).png</t>
+  </si>
+  <si>
+    <t>acta3</t>
+  </si>
+  <si>
+    <t>acta4</t>
+  </si>
+  <si>
+    <t>ev_sim3</t>
+  </si>
+  <si>
+    <t>ev_sim4</t>
+  </si>
+  <si>
+    <t>ev_sim5</t>
+  </si>
+  <si>
+    <t>ev_sim6</t>
+  </si>
+  <si>
+    <t>ev_sim7</t>
+  </si>
+  <si>
+    <t>ev_sim8</t>
+  </si>
+  <si>
+    <t>layout (1).png</t>
+  </si>
+  <si>
+    <t>layout (2).png</t>
+  </si>
+  <si>
+    <t>layout (3).png</t>
+  </si>
+  <si>
+    <t>layout (4).png</t>
+  </si>
+  <si>
+    <t>layout (5).png</t>
+  </si>
+  <si>
+    <t>layout (6).png</t>
+  </si>
+  <si>
+    <t>layout (7).png</t>
+  </si>
+  <si>
+    <t>layout (8).png</t>
+  </si>
+  <si>
+    <t>layout (9).png</t>
+  </si>
+  <si>
+    <t>layout (10).png</t>
+  </si>
+  <si>
+    <t>layout (11).png</t>
+  </si>
+  <si>
+    <t>layout (12).png</t>
+  </si>
+  <si>
+    <t>ev_sim (7).png</t>
+  </si>
+  <si>
+    <t>ev_sim (8).png</t>
   </si>
 </sst>
 </file>
@@ -7632,7 +7710,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="26" fmlaLink="$A$1" max="30000" min="1" page="10" val="57"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="26" fmlaLink="$A$1" max="30000" min="1" page="10" val="53"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8027,7 +8105,7 @@
   <sheetData>
     <row r="1" spans="1:322" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="DS1" t="s">
         <v>1969</v>
@@ -38717,13 +38795,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76893F01-97EA-43A4-9AE2-ED099B9448DD}">
-  <dimension ref="A1:KD2"/>
+  <dimension ref="A1:KX2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:290" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:310" x14ac:dyDescent="0.3">
       <c r="A1">
         <f>+BD!A1</f>
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B1" t="s">
         <v>134</v>
@@ -39592,8 +39670,68 @@
       <c r="KD1" t="s">
         <v>2135</v>
       </c>
+      <c r="KE1" t="s">
+        <v>2137</v>
+      </c>
+      <c r="KF1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="KG1" t="s">
+        <v>2139</v>
+      </c>
+      <c r="KH1" t="s">
+        <v>2140</v>
+      </c>
+      <c r="KI1" t="s">
+        <v>2141</v>
+      </c>
+      <c r="KJ1" t="s">
+        <v>2142</v>
+      </c>
+      <c r="KK1" t="s">
+        <v>2143</v>
+      </c>
+      <c r="KL1" t="s">
+        <v>2144</v>
+      </c>
+      <c r="KM1" t="s">
+        <v>2145</v>
+      </c>
+      <c r="KN1" t="s">
+        <v>2146</v>
+      </c>
+      <c r="KO1" t="s">
+        <v>2147</v>
+      </c>
+      <c r="KP1" t="s">
+        <v>2148</v>
+      </c>
+      <c r="KQ1" t="s">
+        <v>2155</v>
+      </c>
+      <c r="KR1" t="s">
+        <v>2156</v>
+      </c>
+      <c r="KS1" t="s">
+        <v>2157</v>
+      </c>
+      <c r="KT1" t="s">
+        <v>2158</v>
+      </c>
+      <c r="KU1" t="s">
+        <v>2159</v>
+      </c>
+      <c r="KV1" t="s">
+        <v>2160</v>
+      </c>
+      <c r="KW1" t="s">
+        <v>2153</v>
+      </c>
+      <c r="KX1" t="s">
+        <v>2154</v>
+      </c>
     </row>
-    <row r="2" spans="1:290" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:310" x14ac:dyDescent="0.3">
       <c r="B2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,2, FALSE)</f>
         <v>GENERAL</v>
@@ -39604,15 +39742,15 @@
       </c>
       <c r="D2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,4, FALSE)</f>
-        <v>COMPLEJO MIXCOATL</v>
+        <v>COMPLEJO AZTLAN</v>
       </c>
       <c r="E2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,5, FALSE)</f>
-        <v>UVP810305C29</v>
+        <v>UVP810305C25</v>
       </c>
       <c r="F2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,6, FALSE)</f>
-        <v>COMPLEJO MIXCOATL</v>
+        <v>COMPLEJO AZTLAN</v>
       </c>
       <c r="G2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,7, FALSE)</f>
@@ -39624,11 +39762,11 @@
       </c>
       <c r="I2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,9, FALSE)</f>
-        <v>PRIVADA JACARANDAS</v>
+        <v>5 SUR</v>
       </c>
       <c r="J2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,10, FALSE)</f>
-        <v>327</v>
+        <v>5906</v>
       </c>
       <c r="K2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,11, FALSE)</f>
@@ -39660,15 +39798,15 @@
       </c>
       <c r="R2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,18, FALSE)</f>
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="S2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,19, FALSE)</f>
-        <v>7 DE SEPTIEMBRE DE 2021</v>
+        <v>6 DE DICIEMBRE DE 2010</v>
       </c>
       <c r="T2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,20, FALSE)</f>
-        <v>NOE MORA RAMIREZ</v>
+        <v>JORGE MANUEL ISLAS GOWER</v>
       </c>
       <c r="U2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,21, FALSE)</f>
@@ -39676,31 +39814,31 @@
       </c>
       <c r="V2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,22, FALSE)</f>
-        <v>496</v>
+        <v>2485</v>
       </c>
       <c r="W2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,23, FALSE)</f>
-        <v>298.74</v>
+        <v>4639.5200000000004</v>
       </c>
       <c r="X2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,24, FALSE)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,25, FALSE)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,26, FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,27, FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,28, FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,29, FALSE)</f>
@@ -39708,7 +39846,7 @@
       </c>
       <c r="AD2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,30, FALSE)</f>
-        <v>0 CAJONES</v>
+        <v>6 CAJONES</v>
       </c>
       <c r="AE2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,31, FALSE)</f>
@@ -39716,11 +39854,11 @@
       </c>
       <c r="AF2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,32, FALSE)</f>
-        <v>ISABEL MARÍA CORTES CUELLAR</v>
+        <v>MODESTO ALFONSO HERNÁNDEZ ORTIZ</v>
       </c>
       <c r="AG2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,33, FALSE)</f>
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="AH2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,34, FALSE)</f>
@@ -39728,11 +39866,11 @@
       </c>
       <c r="AI2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,35, FALSE)</f>
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="AJ2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,36, FALSE)</f>
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="AK2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,37, FALSE)</f>
@@ -39748,11 +39886,11 @@
       </c>
       <c r="AN2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,40, FALSE)</f>
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AO2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,41, FALSE)</f>
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="AP2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,42, FALSE)</f>
@@ -39764,19 +39902,19 @@
       </c>
       <c r="AR2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,44, FALSE)</f>
-        <v>23</v>
+        <v>92</v>
       </c>
       <c r="AS2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,45, FALSE)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AT2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,46, FALSE)</f>
-        <v>PREFECTURA</v>
+        <v>RECEPCION, BIBLIOTECA, CAI, CAPS</v>
       </c>
       <c r="AU2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,47, FALSE)</f>
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="AV2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,48, FALSE)</f>
@@ -39784,11 +39922,11 @@
       </c>
       <c r="AW2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,49, FALSE)</f>
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="AX2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,50, FALSE)</f>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AY2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,51, FALSE)</f>
@@ -39824,7 +39962,7 @@
       </c>
       <c r="BG2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,59, FALSE)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BH2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,60, FALSE)</f>
@@ -39832,7 +39970,7 @@
       </c>
       <c r="BI2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,61, FALSE)</f>
-        <v>DIRECCION</v>
+        <v>COORDINACION, VIGILANCIA, CONTROL EXTERNO</v>
       </c>
       <c r="BJ2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,62, FALSE)</f>
@@ -39844,23 +39982,23 @@
       </c>
       <c r="BL2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,64, FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="BM2">
+        <v>5</v>
+      </c>
+      <c r="BM2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,65, FALSE)</f>
-        <v>0</v>
+        <v>OFICINAS</v>
       </c>
       <c r="BN2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,66, FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="BO2">
+        <v>1</v>
+      </c>
+      <c r="BO2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,67, FALSE)</f>
-        <v>0</v>
+        <v>GABINETE</v>
       </c>
       <c r="BP2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,68, FALSE)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BQ2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,69, FALSE)</f>
@@ -39868,7 +40006,7 @@
       </c>
       <c r="BR2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,70, FALSE)</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BS2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,71, FALSE)</f>
@@ -39876,11 +40014,11 @@
       </c>
       <c r="BT2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,72, FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="BU2">
+        <v>2</v>
+      </c>
+      <c r="BU2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,73, FALSE)</f>
-        <v>0</v>
+        <v>GABINETE</v>
       </c>
       <c r="BV2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,74, FALSE)</f>
@@ -39888,23 +40026,23 @@
       </c>
       <c r="BW2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,75, FALSE)</f>
-        <v>GABINETE</v>
+        <v>COORDINACION</v>
       </c>
       <c r="BX2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,76, FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="BY2" t="str">
+        <v>0</v>
+      </c>
+      <c r="BY2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,77, FALSE)</f>
-        <v>GABINETE</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,78, FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="CA2">
+        <v>1</v>
+      </c>
+      <c r="CA2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,79, FALSE)</f>
-        <v>0</v>
+        <v>GABINETE</v>
       </c>
       <c r="CB2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,80, FALSE)</f>
@@ -39916,15 +40054,15 @@
       </c>
       <c r="CD2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,82, FALSE)</f>
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="CE2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,83, FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,84, FALSE)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="CG2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,85, FALSE)</f>
@@ -39932,27 +40070,27 @@
       </c>
       <c r="CH2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,86, FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CI2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,87, FALSE)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="CJ2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,88, FALSE)</f>
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="CK2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,89, FALSE)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="CL2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,90, FALSE)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="CM2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,91, FALSE)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="CN2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,92, FALSE)</f>
@@ -39976,11 +40114,11 @@
       </c>
       <c r="CS2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,97, FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="CT2">
+        <v>9</v>
+      </c>
+      <c r="CT2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,98, FALSE)</f>
-        <v>0</v>
+        <v>AREA COMÚN</v>
       </c>
       <c r="CU2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,99, FALSE)</f>
@@ -40016,7 +40154,7 @@
       </c>
       <c r="DC2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,107, FALSE)</f>
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="DD2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,108, FALSE)</f>
@@ -40024,11 +40162,11 @@
       </c>
       <c r="DE2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,109, FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="DF2">
+        <v>11</v>
+      </c>
+      <c r="DF2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,110, FALSE)</f>
-        <v>0</v>
+        <v>AREA COMÚN</v>
       </c>
       <c r="DG2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,111, FALSE)</f>
@@ -40108,15 +40246,15 @@
       </c>
       <c r="DZ2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,130, FALSE)</f>
-        <v>19.020492484141947, -98.21580700217788</v>
+        <v>19.017749517200585, -98.2183180754988</v>
       </c>
       <c r="EA2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,131, FALSE)</f>
-        <v>CASA HABITACIÓN</v>
+        <v>TAQUERIA</v>
       </c>
       <c r="EB2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,132, FALSE)</f>
-        <v>CASAS HABITACION</v>
+        <v>UVP TEOCALLI</v>
       </c>
       <c r="EC2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,133, FALSE)</f>
@@ -40124,7 +40262,7 @@
       </c>
       <c r="ED2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,134, FALSE)</f>
-        <v>CASA HABITACION</v>
+        <v>PARQUE EL ELEFANTE</v>
       </c>
       <c r="EE2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,135, FALSE)</f>
@@ -40252,15 +40390,15 @@
       </c>
       <c r="FJ2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,166, FALSE)</f>
-        <v>GAS LP</v>
+        <v>GAS LP Y GAS NATURAL</v>
       </c>
       <c r="FK2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,167, FALSE)</f>
-        <v>20</v>
+        <v>20480</v>
       </c>
       <c r="FL2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,168, FALSE)</f>
-        <v>6.6666666666666671E-3</v>
+        <v>6.8266666666666671</v>
       </c>
       <c r="FM2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,169, FALSE)</f>
@@ -40292,19 +40430,19 @@
       </c>
       <c r="FT2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,176, FALSE)</f>
-        <v>360</v>
+        <v>4200</v>
       </c>
       <c r="FU2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,177, FALSE)</f>
-        <v>2.4E-2</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="FV2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,178, FALSE)</f>
-        <v>3.0666666666666668E-2</v>
+        <v>7.1066666666666674</v>
       </c>
       <c r="FW2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,179, FALSE)</f>
-        <v>ORDINARIO</v>
+        <v>ALTO</v>
       </c>
       <c r="FX2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,180, FALSE)</f>
@@ -40644,6 +40782,68 @@
       </c>
       <c r="KD2" t="s">
         <v>2136</v>
+      </c>
+      <c r="KE2" t="s">
+        <v>2161</v>
+      </c>
+      <c r="KF2" t="s">
+        <v>2162</v>
+      </c>
+      <c r="KG2" t="s">
+        <v>2163</v>
+      </c>
+      <c r="KH2" t="s">
+        <v>2164</v>
+      </c>
+      <c r="KI2" t="s">
+        <v>2165</v>
+      </c>
+      <c r="KJ2" t="s">
+        <v>2166</v>
+      </c>
+      <c r="KK2" t="s">
+        <v>2167</v>
+      </c>
+      <c r="KL2" t="s">
+        <v>2168</v>
+      </c>
+      <c r="KM2" t="s">
+        <v>2169</v>
+      </c>
+      <c r="KN2" t="s">
+        <v>2170</v>
+      </c>
+      <c r="KO2" t="s">
+        <v>2171</v>
+      </c>
+      <c r="KP2" t="s">
+        <v>2172</v>
+      </c>
+      <c r="KQ2" t="s">
+        <v>2149</v>
+      </c>
+      <c r="KR2" t="s">
+        <v>2150</v>
+      </c>
+      <c r="KS2" t="s">
+        <v>2151</v>
+      </c>
+      <c r="KT2" t="s">
+        <v>2152</v>
+      </c>
+      <c r="KU2" t="s">
+        <v>2173</v>
+      </c>
+      <c r="KV2" t="s">
+        <v>2174</v>
+      </c>
+      <c r="KW2" t="str">
+        <f>+_xlfn.CONCAT(KW1,".png")</f>
+        <v>acta3.png</v>
+      </c>
+      <c r="KX2" t="str">
+        <f>+_xlfn.CONCAT(KX1,".png")</f>
+        <v>acta4.png</v>
       </c>
     </row>
   </sheetData>
@@ -47685,7 +47885,7 @@
         <v>1759</v>
       </c>
       <c r="F94" t="str">
-        <f t="shared" ref="F94:F107" si="33">+_xlfn.CONCAT(E94,".png")</f>
+        <f t="shared" ref="F94:F105" si="33">+_xlfn.CONCAT(E94,".png")</f>
         <v>corresp2.png</v>
       </c>
       <c r="G94" t="str">
@@ -48557,12 +48757,14 @@
       </c>
     </row>
     <row r="106" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B106" t="s">
+        <v>1898</v>
+      </c>
       <c r="E106" t="s">
         <v>2137</v>
       </c>
-      <c r="F106" t="str">
-        <f t="shared" si="33"/>
-        <v>layout1.png</v>
+      <c r="F106" t="s">
+        <v>2161</v>
       </c>
       <c r="G106" t="str">
         <f t="shared" si="34"/>
@@ -48627,12 +48829,14 @@
       </c>
     </row>
     <row r="107" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B107" t="s">
+        <v>1898</v>
+      </c>
       <c r="E107" t="s">
         <v>2138</v>
       </c>
-      <c r="F107" t="str">
-        <f t="shared" si="33"/>
-        <v>layout2.png</v>
+      <c r="F107" t="s">
+        <v>2162</v>
       </c>
       <c r="G107" t="str">
         <f t="shared" si="34"/>
@@ -48697,15 +48901,17 @@
       </c>
     </row>
     <row r="108" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B108" t="s">
+        <v>1898</v>
+      </c>
       <c r="E108" t="s">
         <v>2139</v>
       </c>
-      <c r="F108" t="str">
-        <f t="shared" ref="F108:F117" si="57">+_xlfn.CONCAT(E108,".png")</f>
-        <v>layout3.png</v>
+      <c r="F108" t="s">
+        <v>2163</v>
       </c>
       <c r="G108" t="str">
-        <f t="shared" ref="G108:G117" si="58">+_xlfn.CONCAT("{{ ",E108," }}")</f>
+        <f t="shared" ref="G108:G118" si="57">+_xlfn.CONCAT("{{ ",E108," }}")</f>
         <v>{{ layout3 }}</v>
       </c>
       <c r="H108">
@@ -48767,15 +48973,17 @@
       </c>
     </row>
     <row r="109" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B109" t="s">
+        <v>1898</v>
+      </c>
       <c r="E109" t="s">
         <v>2140</v>
       </c>
-      <c r="F109" t="str">
+      <c r="F109" t="s">
+        <v>2164</v>
+      </c>
+      <c r="G109" t="str">
         <f t="shared" si="57"/>
-        <v>layout4.png</v>
-      </c>
-      <c r="G109" t="str">
-        <f t="shared" si="58"/>
         <v>{{ layout4 }}</v>
       </c>
       <c r="H109">
@@ -48837,15 +49045,17 @@
       </c>
     </row>
     <row r="110" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B110" t="s">
+        <v>1898</v>
+      </c>
       <c r="E110" t="s">
         <v>2141</v>
       </c>
-      <c r="F110" t="str">
+      <c r="F110" t="s">
+        <v>2165</v>
+      </c>
+      <c r="G110" t="str">
         <f t="shared" si="57"/>
-        <v>layout5.png</v>
-      </c>
-      <c r="G110" t="str">
-        <f t="shared" si="58"/>
         <v>{{ layout5 }}</v>
       </c>
       <c r="H110">
@@ -48907,15 +49117,17 @@
       </c>
     </row>
     <row r="111" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B111" t="s">
+        <v>1898</v>
+      </c>
       <c r="E111" t="s">
         <v>2142</v>
       </c>
-      <c r="F111" t="str">
+      <c r="F111" t="s">
+        <v>2166</v>
+      </c>
+      <c r="G111" t="str">
         <f t="shared" si="57"/>
-        <v>layout6.png</v>
-      </c>
-      <c r="G111" t="str">
-        <f t="shared" si="58"/>
         <v>{{ layout6 }}</v>
       </c>
       <c r="H111">
@@ -48931,7 +49143,7 @@
         <v>317</v>
       </c>
       <c r="L111" t="str">
-        <f t="shared" ref="L111:L142" si="59">+_xlfn.CONCAT("'",J111,"' : r_val['",J111,"'],")</f>
+        <f t="shared" ref="L111:L142" si="58">+_xlfn.CONCAT("'",J111,"' : r_val['",J111,"'],")</f>
         <v>'coord_suplente' : r_val['coord_suplente'],</v>
       </c>
       <c r="M111" t="str">
@@ -48977,15 +49189,17 @@
       </c>
     </row>
     <row r="112" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B112" t="s">
+        <v>1898</v>
+      </c>
       <c r="E112" t="s">
         <v>2143</v>
       </c>
-      <c r="F112" t="str">
+      <c r="F112" t="s">
+        <v>2167</v>
+      </c>
+      <c r="G112" t="str">
         <f t="shared" si="57"/>
-        <v>layout7.png</v>
-      </c>
-      <c r="G112" t="str">
-        <f t="shared" si="58"/>
         <v>{{ layout7 }}</v>
       </c>
       <c r="H112">
@@ -49001,7 +49215,7 @@
         <v>687</v>
       </c>
       <c r="L112" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>'m_jef_caj' : r_val['m_jef_caj'],</v>
       </c>
       <c r="M112" t="str">
@@ -49046,16 +49260,18 @@
         <v>layout7 = ''</v>
       </c>
     </row>
-    <row r="113" spans="5:23" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B113" t="s">
+        <v>1898</v>
+      </c>
       <c r="E113" t="s">
         <v>2144</v>
       </c>
-      <c r="F113" t="str">
+      <c r="F113" t="s">
+        <v>2168</v>
+      </c>
+      <c r="G113" t="str">
         <f t="shared" si="57"/>
-        <v>layout8.png</v>
-      </c>
-      <c r="G113" t="str">
-        <f t="shared" si="58"/>
         <v>{{ layout8 }}</v>
       </c>
       <c r="H113">
@@ -49071,7 +49287,7 @@
         <v>318</v>
       </c>
       <c r="L113" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>'evacuacion' : r_val['evacuacion'],</v>
       </c>
       <c r="M113" t="str">
@@ -49116,16 +49332,18 @@
         <v>layout8 = ''</v>
       </c>
     </row>
-    <row r="114" spans="5:23" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B114" t="s">
+        <v>1898</v>
+      </c>
       <c r="E114" t="s">
         <v>2145</v>
       </c>
-      <c r="F114" t="str">
+      <c r="F114" t="s">
+        <v>2169</v>
+      </c>
+      <c r="G114" t="str">
         <f t="shared" si="57"/>
-        <v>layout9.png</v>
-      </c>
-      <c r="G114" t="str">
-        <f t="shared" si="58"/>
         <v>{{ layout9 }}</v>
       </c>
       <c r="H114">
@@ -49141,7 +49359,7 @@
         <v>588</v>
       </c>
       <c r="L114" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>'evac_puesto' : r_val['evac_puesto'],</v>
       </c>
       <c r="M114" t="str">
@@ -49186,16 +49404,18 @@
         <v>layout9 = ''</v>
       </c>
     </row>
-    <row r="115" spans="5:23" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B115" t="s">
+        <v>1898</v>
+      </c>
       <c r="E115" t="s">
         <v>2146</v>
       </c>
-      <c r="F115" t="str">
+      <c r="F115" t="s">
+        <v>2170</v>
+      </c>
+      <c r="G115" t="str">
         <f t="shared" si="57"/>
-        <v>layout10.png</v>
-      </c>
-      <c r="G115" t="str">
-        <f t="shared" si="58"/>
         <v>{{ layout10 }}</v>
       </c>
       <c r="H115">
@@ -49211,7 +49431,7 @@
         <v>688</v>
       </c>
       <c r="L115" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>'m_evac' : r_val['m_evac'],</v>
       </c>
       <c r="M115" t="str">
@@ -49256,16 +49476,18 @@
         <v>layout10 = ''</v>
       </c>
     </row>
-    <row r="116" spans="5:23" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B116" t="s">
+        <v>1898</v>
+      </c>
       <c r="E116" t="s">
         <v>2147</v>
       </c>
-      <c r="F116" t="str">
+      <c r="F116" t="s">
+        <v>2171</v>
+      </c>
+      <c r="G116" t="str">
         <f t="shared" si="57"/>
-        <v>layout11.png</v>
-      </c>
-      <c r="G116" t="str">
-        <f t="shared" si="58"/>
         <v>{{ layout11 }}</v>
       </c>
       <c r="H116">
@@ -49281,7 +49503,7 @@
         <v>319</v>
       </c>
       <c r="L116" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>'evac_suplente' : r_val['evac_suplente'],</v>
       </c>
       <c r="M116" t="str">
@@ -49326,16 +49548,18 @@
         <v>layout11 = ''</v>
       </c>
     </row>
-    <row r="117" spans="5:23" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B117" t="s">
+        <v>1898</v>
+      </c>
       <c r="E117" t="s">
         <v>2148</v>
       </c>
-      <c r="F117" t="str">
+      <c r="F117" t="s">
+        <v>2172</v>
+      </c>
+      <c r="G117" t="str">
         <f t="shared" si="57"/>
-        <v>layout12.png</v>
-      </c>
-      <c r="G117" t="str">
-        <f t="shared" si="58"/>
         <v>{{ layout12 }}</v>
       </c>
       <c r="H117">
@@ -49351,7 +49575,7 @@
         <v>589</v>
       </c>
       <c r="L117" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>'supl_evac_pue' : r_val['supl_evac_pue'],</v>
       </c>
       <c r="M117" t="str">
@@ -49396,7 +49620,26 @@
         <v>layout12 = ''</v>
       </c>
     </row>
-    <row r="118" spans="5:23" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B118" t="s">
+        <v>1898</v>
+      </c>
+      <c r="E118" t="s">
+        <v>2155</v>
+      </c>
+      <c r="F118" t="s">
+        <v>2149</v>
+      </c>
+      <c r="G118" t="str">
+        <f t="shared" si="57"/>
+        <v>{{ ev_sim3 }}</v>
+      </c>
+      <c r="H118">
+        <v>155</v>
+      </c>
+      <c r="I118" t="s">
+        <v>1755</v>
+      </c>
       <c r="J118" t="s">
         <v>649</v>
       </c>
@@ -49404,11 +49647,71 @@
         <v>689</v>
       </c>
       <c r="L118" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>'m_supl_evac' : r_val['m_supl_evac'],</v>
       </c>
+      <c r="M118" t="str">
+        <f t="shared" ref="M118:M123" si="59">+_xlfn.CONCAT("'",E118,"': ",E118,",")</f>
+        <v>'ev_sim3': ev_sim3,</v>
+      </c>
+      <c r="N118" t="s">
+        <v>557</v>
+      </c>
+      <c r="O118" t="str">
+        <f t="shared" ref="O118:O123" si="60">+_xlfn.CONCAT("img_path_",E118," = os.path.join(IMAGES_PATH, r_val[""",E118,"""])")</f>
+        <v>img_path_ev_sim3 = os.path.join(IMAGES_PATH, r_val["ev_sim3"])</v>
+      </c>
+      <c r="P118" t="str">
+        <f t="shared" ref="P118:P123" si="61">+_xlfn.CONCAT("if os.path.exists(img_path_",E118,"):")</f>
+        <v>if os.path.exists(img_path_ev_sim3):</v>
+      </c>
+      <c r="Q118" t="str">
+        <f t="shared" ref="Q118:Q123" si="62">+_xlfn.CONCAT(E118," = InlineImage(docx_tpl, img_path_",E118,", ",I118,"=Mm(",H118,"))")</f>
+        <v>ev_sim3 = InlineImage(docx_tpl, img_path_ev_sim3, width=Mm(155))</v>
+      </c>
+      <c r="R118" t="s">
+        <v>559</v>
+      </c>
+      <c r="S118" t="str">
+        <f t="shared" ref="S118:S123" si="63">+_xlfn.CONCAT("print(f'Advertencia: No se encontró la imagen {r_val[""",E118,"""]}')")</f>
+        <v>print(f'Advertencia: No se encontró la imagen {r_val["ev_sim3"]}')</v>
+      </c>
+      <c r="T118" t="str">
+        <f t="shared" ref="T118:T123" si="64">+_xlfn.CONCAT(E118," = ''")</f>
+        <v>ev_sim3 = ''</v>
+      </c>
+      <c r="U118" t="s">
+        <v>558</v>
+      </c>
+      <c r="V118" t="str">
+        <f t="shared" ref="V118:V123" si="65">+_xlfn.CONCAT("print(f'Advertencia: No se pudo cargar la imagen {r_val[""",E118,"""]}: {e}')")</f>
+        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["ev_sim3"]}: {e}')</v>
+      </c>
+      <c r="W118" t="str">
+        <f t="shared" ref="W118:W123" si="66">+_xlfn.CONCAT(E118," = ''")</f>
+        <v>ev_sim3 = ''</v>
+      </c>
     </row>
-    <row r="119" spans="5:23" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B119" t="s">
+        <v>1898</v>
+      </c>
+      <c r="E119" t="s">
+        <v>2156</v>
+      </c>
+      <c r="F119" t="s">
+        <v>2150</v>
+      </c>
+      <c r="G119" t="str">
+        <f t="shared" ref="G119:G123" si="67">+_xlfn.CONCAT("{{ ",E119," }}")</f>
+        <v>{{ ev_sim4 }}</v>
+      </c>
+      <c r="H119">
+        <v>155</v>
+      </c>
+      <c r="I119" t="s">
+        <v>1755</v>
+      </c>
       <c r="J119" t="s">
         <v>205</v>
       </c>
@@ -49416,11 +49719,71 @@
         <v>320</v>
       </c>
       <c r="L119" t="str">
+        <f t="shared" si="58"/>
+        <v>'incendios' : r_val['incendios'],</v>
+      </c>
+      <c r="M119" t="str">
         <f t="shared" si="59"/>
-        <v>'incendios' : r_val['incendios'],</v>
+        <v>'ev_sim4': ev_sim4,</v>
+      </c>
+      <c r="N119" t="s">
+        <v>557</v>
+      </c>
+      <c r="O119" t="str">
+        <f t="shared" si="60"/>
+        <v>img_path_ev_sim4 = os.path.join(IMAGES_PATH, r_val["ev_sim4"])</v>
+      </c>
+      <c r="P119" t="str">
+        <f t="shared" si="61"/>
+        <v>if os.path.exists(img_path_ev_sim4):</v>
+      </c>
+      <c r="Q119" t="str">
+        <f t="shared" si="62"/>
+        <v>ev_sim4 = InlineImage(docx_tpl, img_path_ev_sim4, width=Mm(155))</v>
+      </c>
+      <c r="R119" t="s">
+        <v>559</v>
+      </c>
+      <c r="S119" t="str">
+        <f t="shared" si="63"/>
+        <v>print(f'Advertencia: No se encontró la imagen {r_val["ev_sim4"]}')</v>
+      </c>
+      <c r="T119" t="str">
+        <f t="shared" si="64"/>
+        <v>ev_sim4 = ''</v>
+      </c>
+      <c r="U119" t="s">
+        <v>558</v>
+      </c>
+      <c r="V119" t="str">
+        <f t="shared" si="65"/>
+        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["ev_sim4"]}: {e}')</v>
+      </c>
+      <c r="W119" t="str">
+        <f t="shared" si="66"/>
+        <v>ev_sim4 = ''</v>
       </c>
     </row>
-    <row r="120" spans="5:23" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B120" t="s">
+        <v>1898</v>
+      </c>
+      <c r="E120" t="s">
+        <v>2157</v>
+      </c>
+      <c r="F120" t="s">
+        <v>2151</v>
+      </c>
+      <c r="G120" t="str">
+        <f t="shared" si="67"/>
+        <v>{{ ev_sim5 }}</v>
+      </c>
+      <c r="H120">
+        <v>155</v>
+      </c>
+      <c r="I120" t="s">
+        <v>1755</v>
+      </c>
       <c r="J120" t="s">
         <v>582</v>
       </c>
@@ -49428,11 +49791,71 @@
         <v>590</v>
       </c>
       <c r="L120" t="str">
+        <f t="shared" si="58"/>
+        <v>'incen_puesto' : r_val['incen_puesto'],</v>
+      </c>
+      <c r="M120" t="str">
         <f t="shared" si="59"/>
-        <v>'incen_puesto' : r_val['incen_puesto'],</v>
+        <v>'ev_sim5': ev_sim5,</v>
+      </c>
+      <c r="N120" t="s">
+        <v>557</v>
+      </c>
+      <c r="O120" t="str">
+        <f t="shared" si="60"/>
+        <v>img_path_ev_sim5 = os.path.join(IMAGES_PATH, r_val["ev_sim5"])</v>
+      </c>
+      <c r="P120" t="str">
+        <f t="shared" si="61"/>
+        <v>if os.path.exists(img_path_ev_sim5):</v>
+      </c>
+      <c r="Q120" t="str">
+        <f t="shared" si="62"/>
+        <v>ev_sim5 = InlineImage(docx_tpl, img_path_ev_sim5, width=Mm(155))</v>
+      </c>
+      <c r="R120" t="s">
+        <v>559</v>
+      </c>
+      <c r="S120" t="str">
+        <f t="shared" si="63"/>
+        <v>print(f'Advertencia: No se encontró la imagen {r_val["ev_sim5"]}')</v>
+      </c>
+      <c r="T120" t="str">
+        <f t="shared" si="64"/>
+        <v>ev_sim5 = ''</v>
+      </c>
+      <c r="U120" t="s">
+        <v>558</v>
+      </c>
+      <c r="V120" t="str">
+        <f t="shared" si="65"/>
+        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["ev_sim5"]}: {e}')</v>
+      </c>
+      <c r="W120" t="str">
+        <f t="shared" si="66"/>
+        <v>ev_sim5 = ''</v>
       </c>
     </row>
-    <row r="121" spans="5:23" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B121" t="s">
+        <v>1898</v>
+      </c>
+      <c r="E121" t="s">
+        <v>2158</v>
+      </c>
+      <c r="F121" t="s">
+        <v>2152</v>
+      </c>
+      <c r="G121" t="str">
+        <f t="shared" si="67"/>
+        <v>{{ ev_sim6 }}</v>
+      </c>
+      <c r="H121">
+        <v>155</v>
+      </c>
+      <c r="I121" t="s">
+        <v>1755</v>
+      </c>
       <c r="J121" t="s">
         <v>650</v>
       </c>
@@ -49440,11 +49863,71 @@
         <v>690</v>
       </c>
       <c r="L121" t="str">
+        <f t="shared" si="58"/>
+        <v>'m_inc' : r_val['m_inc'],</v>
+      </c>
+      <c r="M121" t="str">
         <f t="shared" si="59"/>
-        <v>'m_inc' : r_val['m_inc'],</v>
+        <v>'ev_sim6': ev_sim6,</v>
+      </c>
+      <c r="N121" t="s">
+        <v>557</v>
+      </c>
+      <c r="O121" t="str">
+        <f t="shared" si="60"/>
+        <v>img_path_ev_sim6 = os.path.join(IMAGES_PATH, r_val["ev_sim6"])</v>
+      </c>
+      <c r="P121" t="str">
+        <f t="shared" si="61"/>
+        <v>if os.path.exists(img_path_ev_sim6):</v>
+      </c>
+      <c r="Q121" t="str">
+        <f t="shared" si="62"/>
+        <v>ev_sim6 = InlineImage(docx_tpl, img_path_ev_sim6, width=Mm(155))</v>
+      </c>
+      <c r="R121" t="s">
+        <v>559</v>
+      </c>
+      <c r="S121" t="str">
+        <f t="shared" si="63"/>
+        <v>print(f'Advertencia: No se encontró la imagen {r_val["ev_sim6"]}')</v>
+      </c>
+      <c r="T121" t="str">
+        <f t="shared" si="64"/>
+        <v>ev_sim6 = ''</v>
+      </c>
+      <c r="U121" t="s">
+        <v>558</v>
+      </c>
+      <c r="V121" t="str">
+        <f t="shared" si="65"/>
+        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["ev_sim6"]}: {e}')</v>
+      </c>
+      <c r="W121" t="str">
+        <f t="shared" si="66"/>
+        <v>ev_sim6 = ''</v>
       </c>
     </row>
-    <row r="122" spans="5:23" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B122" t="s">
+        <v>1898</v>
+      </c>
+      <c r="E122" t="s">
+        <v>2159</v>
+      </c>
+      <c r="F122" t="s">
+        <v>2173</v>
+      </c>
+      <c r="G122" t="str">
+        <f t="shared" si="67"/>
+        <v>{{ ev_sim7 }}</v>
+      </c>
+      <c r="H122">
+        <v>155</v>
+      </c>
+      <c r="I122" t="s">
+        <v>1755</v>
+      </c>
       <c r="J122" t="s">
         <v>206</v>
       </c>
@@ -49452,11 +49935,71 @@
         <v>321</v>
       </c>
       <c r="L122" t="str">
+        <f t="shared" si="58"/>
+        <v>'inc_suplente' : r_val['inc_suplente'],</v>
+      </c>
+      <c r="M122" t="str">
         <f t="shared" si="59"/>
-        <v>'inc_suplente' : r_val['inc_suplente'],</v>
+        <v>'ev_sim7': ev_sim7,</v>
+      </c>
+      <c r="N122" t="s">
+        <v>557</v>
+      </c>
+      <c r="O122" t="str">
+        <f t="shared" si="60"/>
+        <v>img_path_ev_sim7 = os.path.join(IMAGES_PATH, r_val["ev_sim7"])</v>
+      </c>
+      <c r="P122" t="str">
+        <f t="shared" si="61"/>
+        <v>if os.path.exists(img_path_ev_sim7):</v>
+      </c>
+      <c r="Q122" t="str">
+        <f t="shared" si="62"/>
+        <v>ev_sim7 = InlineImage(docx_tpl, img_path_ev_sim7, width=Mm(155))</v>
+      </c>
+      <c r="R122" t="s">
+        <v>559</v>
+      </c>
+      <c r="S122" t="str">
+        <f t="shared" si="63"/>
+        <v>print(f'Advertencia: No se encontró la imagen {r_val["ev_sim7"]}')</v>
+      </c>
+      <c r="T122" t="str">
+        <f t="shared" si="64"/>
+        <v>ev_sim7 = ''</v>
+      </c>
+      <c r="U122" t="s">
+        <v>558</v>
+      </c>
+      <c r="V122" t="str">
+        <f t="shared" si="65"/>
+        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["ev_sim7"]}: {e}')</v>
+      </c>
+      <c r="W122" t="str">
+        <f t="shared" si="66"/>
+        <v>ev_sim7 = ''</v>
       </c>
     </row>
-    <row r="123" spans="5:23" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B123" t="s">
+        <v>1898</v>
+      </c>
+      <c r="E123" t="s">
+        <v>2160</v>
+      </c>
+      <c r="F123" t="s">
+        <v>2174</v>
+      </c>
+      <c r="G123" t="str">
+        <f t="shared" si="67"/>
+        <v>{{ ev_sim8 }}</v>
+      </c>
+      <c r="H123">
+        <v>155</v>
+      </c>
+      <c r="I123" t="s">
+        <v>1755</v>
+      </c>
       <c r="J123" t="s">
         <v>583</v>
       </c>
@@ -49464,11 +50007,72 @@
         <v>591</v>
       </c>
       <c r="L123" t="str">
+        <f t="shared" si="58"/>
+        <v>'supl_inc_puesto' : r_val['supl_inc_puesto'],</v>
+      </c>
+      <c r="M123" t="str">
         <f t="shared" si="59"/>
-        <v>'supl_inc_puesto' : r_val['supl_inc_puesto'],</v>
+        <v>'ev_sim8': ev_sim8,</v>
+      </c>
+      <c r="N123" t="s">
+        <v>557</v>
+      </c>
+      <c r="O123" t="str">
+        <f t="shared" si="60"/>
+        <v>img_path_ev_sim8 = os.path.join(IMAGES_PATH, r_val["ev_sim8"])</v>
+      </c>
+      <c r="P123" t="str">
+        <f t="shared" si="61"/>
+        <v>if os.path.exists(img_path_ev_sim8):</v>
+      </c>
+      <c r="Q123" t="str">
+        <f t="shared" si="62"/>
+        <v>ev_sim8 = InlineImage(docx_tpl, img_path_ev_sim8, width=Mm(155))</v>
+      </c>
+      <c r="R123" t="s">
+        <v>559</v>
+      </c>
+      <c r="S123" t="str">
+        <f t="shared" si="63"/>
+        <v>print(f'Advertencia: No se encontró la imagen {r_val["ev_sim8"]}')</v>
+      </c>
+      <c r="T123" t="str">
+        <f t="shared" si="64"/>
+        <v>ev_sim8 = ''</v>
+      </c>
+      <c r="U123" t="s">
+        <v>558</v>
+      </c>
+      <c r="V123" t="str">
+        <f t="shared" si="65"/>
+        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["ev_sim8"]}: {e}')</v>
+      </c>
+      <c r="W123" t="str">
+        <f t="shared" si="66"/>
+        <v>ev_sim8 = ''</v>
       </c>
     </row>
-    <row r="124" spans="5:23" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B124" t="s">
+        <v>1898</v>
+      </c>
+      <c r="E124" t="s">
+        <v>2153</v>
+      </c>
+      <c r="F124" t="str">
+        <f t="shared" ref="F124:F125" si="68">+_xlfn.CONCAT(E124,".png")</f>
+        <v>acta3.png</v>
+      </c>
+      <c r="G124" t="str">
+        <f t="shared" ref="G124:G125" si="69">+_xlfn.CONCAT("{{ ",E124," }}")</f>
+        <v>{{ acta3 }}</v>
+      </c>
+      <c r="H124">
+        <v>155</v>
+      </c>
+      <c r="I124" t="s">
+        <v>1755</v>
+      </c>
       <c r="J124" t="s">
         <v>651</v>
       </c>
@@ -49476,11 +50080,72 @@
         <v>691</v>
       </c>
       <c r="L124" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>'m_supl_inc' : r_val['m_supl_inc'],</v>
       </c>
+      <c r="M124" t="str">
+        <f t="shared" ref="M124:M125" si="70">+_xlfn.CONCAT("'",E124,"': ",E124,",")</f>
+        <v>'acta3': acta3,</v>
+      </c>
+      <c r="N124" t="s">
+        <v>557</v>
+      </c>
+      <c r="O124" t="str">
+        <f t="shared" ref="O124:O125" si="71">+_xlfn.CONCAT("img_path_",E124," = os.path.join(IMAGES_PATH, r_val[""",E124,"""])")</f>
+        <v>img_path_acta3 = os.path.join(IMAGES_PATH, r_val["acta3"])</v>
+      </c>
+      <c r="P124" t="str">
+        <f t="shared" ref="P124:P125" si="72">+_xlfn.CONCAT("if os.path.exists(img_path_",E124,"):")</f>
+        <v>if os.path.exists(img_path_acta3):</v>
+      </c>
+      <c r="Q124" t="str">
+        <f t="shared" ref="Q124:Q125" si="73">+_xlfn.CONCAT(E124," = InlineImage(docx_tpl, img_path_",E124,", ",I124,"=Mm(",H124,"))")</f>
+        <v>acta3 = InlineImage(docx_tpl, img_path_acta3, width=Mm(155))</v>
+      </c>
+      <c r="R124" t="s">
+        <v>559</v>
+      </c>
+      <c r="S124" t="str">
+        <f t="shared" ref="S124:S125" si="74">+_xlfn.CONCAT("print(f'Advertencia: No se encontró la imagen {r_val[""",E124,"""]}')")</f>
+        <v>print(f'Advertencia: No se encontró la imagen {r_val["acta3"]}')</v>
+      </c>
+      <c r="T124" t="str">
+        <f t="shared" ref="T124:T125" si="75">+_xlfn.CONCAT(E124," = ''")</f>
+        <v>acta3 = ''</v>
+      </c>
+      <c r="U124" t="s">
+        <v>558</v>
+      </c>
+      <c r="V124" t="str">
+        <f t="shared" ref="V124:V125" si="76">+_xlfn.CONCAT("print(f'Advertencia: No se pudo cargar la imagen {r_val[""",E124,"""]}: {e}')")</f>
+        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["acta3"]}: {e}')</v>
+      </c>
+      <c r="W124" t="str">
+        <f t="shared" ref="W124:W125" si="77">+_xlfn.CONCAT(E124," = ''")</f>
+        <v>acta3 = ''</v>
+      </c>
     </row>
-    <row r="125" spans="5:23" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B125" t="s">
+        <v>1898</v>
+      </c>
+      <c r="E125" t="s">
+        <v>2154</v>
+      </c>
+      <c r="F125" t="str">
+        <f t="shared" si="68"/>
+        <v>acta4.png</v>
+      </c>
+      <c r="G125" t="str">
+        <f t="shared" si="69"/>
+        <v>{{ acta4 }}</v>
+      </c>
+      <c r="H125">
+        <v>155</v>
+      </c>
+      <c r="I125" t="s">
+        <v>1755</v>
+      </c>
       <c r="J125" t="s">
         <v>207</v>
       </c>
@@ -49488,11 +50153,52 @@
         <v>322</v>
       </c>
       <c r="L125" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>'primeros_auxilios' : r_val['primeros_auxilios'],</v>
       </c>
+      <c r="M125" t="str">
+        <f t="shared" si="70"/>
+        <v>'acta4': acta4,</v>
+      </c>
+      <c r="N125" t="s">
+        <v>557</v>
+      </c>
+      <c r="O125" t="str">
+        <f t="shared" si="71"/>
+        <v>img_path_acta4 = os.path.join(IMAGES_PATH, r_val["acta4"])</v>
+      </c>
+      <c r="P125" t="str">
+        <f t="shared" si="72"/>
+        <v>if os.path.exists(img_path_acta4):</v>
+      </c>
+      <c r="Q125" t="str">
+        <f t="shared" si="73"/>
+        <v>acta4 = InlineImage(docx_tpl, img_path_acta4, width=Mm(155))</v>
+      </c>
+      <c r="R125" t="s">
+        <v>559</v>
+      </c>
+      <c r="S125" t="str">
+        <f t="shared" si="74"/>
+        <v>print(f'Advertencia: No se encontró la imagen {r_val["acta4"]}')</v>
+      </c>
+      <c r="T125" t="str">
+        <f t="shared" si="75"/>
+        <v>acta4 = ''</v>
+      </c>
+      <c r="U125" t="s">
+        <v>558</v>
+      </c>
+      <c r="V125" t="str">
+        <f t="shared" si="76"/>
+        <v>print(f'Advertencia: No se pudo cargar la imagen {r_val["acta4"]}: {e}')</v>
+      </c>
+      <c r="W125" t="str">
+        <f t="shared" si="77"/>
+        <v>acta4 = ''</v>
+      </c>
     </row>
-    <row r="126" spans="5:23" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:23" x14ac:dyDescent="0.3">
       <c r="J126" t="s">
         <v>584</v>
       </c>
@@ -49500,11 +50206,11 @@
         <v>592</v>
       </c>
       <c r="L126" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>'prim_aux_puesto' : r_val['prim_aux_puesto'],</v>
       </c>
     </row>
-    <row r="127" spans="5:23" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:23" x14ac:dyDescent="0.3">
       <c r="J127" t="s">
         <v>652</v>
       </c>
@@ -49512,11 +50218,11 @@
         <v>692</v>
       </c>
       <c r="L127" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>'m_prim_aux' : r_val['m_prim_aux'],</v>
       </c>
     </row>
-    <row r="128" spans="5:23" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:23" x14ac:dyDescent="0.3">
       <c r="J128" t="s">
         <v>208</v>
       </c>
@@ -49524,7 +50230,7 @@
         <v>323</v>
       </c>
       <c r="L128" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>'aux_suplente' : r_val['aux_suplente'],</v>
       </c>
     </row>
@@ -49536,7 +50242,7 @@
         <v>593</v>
       </c>
       <c r="L129" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>'supl_prim_aux_puesto' : r_val['supl_prim_aux_puesto'],</v>
       </c>
     </row>
@@ -49548,7 +50254,7 @@
         <v>693</v>
       </c>
       <c r="L130" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>'m_supl_paux' : r_val['m_supl_paux'],</v>
       </c>
     </row>
@@ -49560,7 +50266,7 @@
         <v>324</v>
       </c>
       <c r="L131" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>'busqueda' : r_val['busqueda'],</v>
       </c>
     </row>
@@ -49572,7 +50278,7 @@
         <v>594</v>
       </c>
       <c r="L132" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>'busq_puesto' : r_val['busq_puesto'],</v>
       </c>
     </row>
@@ -49584,7 +50290,7 @@
         <v>694</v>
       </c>
       <c r="L133" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>'m_busq' : r_val['m_busq'],</v>
       </c>
     </row>
@@ -49596,7 +50302,7 @@
         <v>325</v>
       </c>
       <c r="L134" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>'busq_suplente' : r_val['busq_suplente'],</v>
       </c>
     </row>
@@ -49608,7 +50314,7 @@
         <v>595</v>
       </c>
       <c r="L135" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>'supl_busq_puesto' : r_val['supl_busq_puesto'],</v>
       </c>
     </row>
@@ -49620,7 +50326,7 @@
         <v>695</v>
       </c>
       <c r="L136" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>'m_supl_busq' : r_val['m_supl_busq'],</v>
       </c>
     </row>
@@ -49632,7 +50338,7 @@
         <v>326</v>
       </c>
       <c r="L137" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>'descrip_gi' : r_val['descrip_gi'],</v>
       </c>
     </row>
@@ -49644,7 +50350,7 @@
         <v>327</v>
       </c>
       <c r="L138" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>'gas_inflamable' : r_val['gas_inflamable'],</v>
       </c>
     </row>
@@ -49656,7 +50362,7 @@
         <v>328</v>
       </c>
       <c r="L139" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>'valor_gi' : r_val['valor_gi'],</v>
       </c>
     </row>
@@ -49668,7 +50374,7 @@
         <v>329</v>
       </c>
       <c r="L140" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>'descrp_li' : r_val['descrp_li'],</v>
       </c>
     </row>
@@ -49680,7 +50386,7 @@
         <v>330</v>
       </c>
       <c r="L141" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>'liquido_inflamable' : r_val['liquido_inflamable'],</v>
       </c>
     </row>
@@ -49692,7 +50398,7 @@
         <v>331</v>
       </c>
       <c r="L142" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>'valor_li' : r_val['valor_li'],</v>
       </c>
     </row>
@@ -49704,7 +50410,7 @@
         <v>332</v>
       </c>
       <c r="L143" t="str">
-        <f t="shared" ref="L143:L181" si="60">+_xlfn.CONCAT("'",J143,"' : r_val['",J143,"'],")</f>
+        <f t="shared" ref="L143:L181" si="78">+_xlfn.CONCAT("'",J143,"' : r_val['",J143,"'],")</f>
         <v>'descrip_lc' : r_val['descrip_lc'],</v>
       </c>
     </row>
@@ -49716,7 +50422,7 @@
         <v>333</v>
       </c>
       <c r="L144" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>'liquido_combustible' : r_val['liquido_combustible'],</v>
       </c>
     </row>
@@ -49728,7 +50434,7 @@
         <v>334</v>
       </c>
       <c r="L145" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>'valor_lc' : r_val['valor_lc'],</v>
       </c>
     </row>
@@ -49740,7 +50446,7 @@
         <v>335</v>
       </c>
       <c r="L146" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>'descrip_sc' : r_val['descrip_sc'],</v>
       </c>
     </row>
@@ -49752,7 +50458,7 @@
         <v>336</v>
       </c>
       <c r="L147" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>'solido_combusible' : r_val['solido_combusible'],</v>
       </c>
     </row>
@@ -49764,7 +50470,7 @@
         <v>337</v>
       </c>
       <c r="L148" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>'valor_sc' : r_val['valor_sc'],</v>
       </c>
     </row>
@@ -49776,7 +50482,7 @@
         <v>338</v>
       </c>
       <c r="L149" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>'tipo_riesgo' : r_val['tipo_riesgo'],</v>
       </c>
     </row>
@@ -49788,7 +50494,7 @@
         <v>656</v>
       </c>
       <c r="L150" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>'nombre1' : r_val['nombre1'],</v>
       </c>
     </row>
@@ -49800,7 +50506,7 @@
         <v>657</v>
       </c>
       <c r="L151" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>'puesto1' : r_val['puesto1'],</v>
       </c>
     </row>
@@ -49812,7 +50518,7 @@
         <v>658</v>
       </c>
       <c r="L152" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>'m1' : r_val['m1'],</v>
       </c>
     </row>
@@ -49824,7 +50530,7 @@
         <v>659</v>
       </c>
       <c r="L153" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>'nombre2' : r_val['nombre2'],</v>
       </c>
     </row>
@@ -49836,7 +50542,7 @@
         <v>660</v>
       </c>
       <c r="L154" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>'puesto2' : r_val['puesto2'],</v>
       </c>
     </row>
@@ -49848,7 +50554,7 @@
         <v>661</v>
       </c>
       <c r="L155" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>'m2' : r_val['m2'],</v>
       </c>
     </row>
@@ -49860,7 +50566,7 @@
         <v>662</v>
       </c>
       <c r="L156" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>'nombre3' : r_val['nombre3'],</v>
       </c>
     </row>
@@ -49872,7 +50578,7 @@
         <v>663</v>
       </c>
       <c r="L157" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>'puesto3' : r_val['puesto3'],</v>
       </c>
     </row>
@@ -49884,7 +50590,7 @@
         <v>664</v>
       </c>
       <c r="L158" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>'m3' : r_val['m3'],</v>
       </c>
     </row>
@@ -49896,7 +50602,7 @@
         <v>665</v>
       </c>
       <c r="L159" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>'nombre4' : r_val['nombre4'],</v>
       </c>
     </row>
@@ -49908,7 +50614,7 @@
         <v>666</v>
       </c>
       <c r="L160" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>'puesto4' : r_val['puesto4'],</v>
       </c>
     </row>
@@ -49920,7 +50626,7 @@
         <v>667</v>
       </c>
       <c r="L161" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>'m4' : r_val['m4'],</v>
       </c>
     </row>
@@ -49932,7 +50638,7 @@
         <v>668</v>
       </c>
       <c r="L162" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>'nombre5' : r_val['nombre5'],</v>
       </c>
     </row>
@@ -49944,7 +50650,7 @@
         <v>669</v>
       </c>
       <c r="L163" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>'puesto5' : r_val['puesto5'],</v>
       </c>
     </row>
@@ -49956,7 +50662,7 @@
         <v>670</v>
       </c>
       <c r="L164" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>'m5' : r_val['m5'],</v>
       </c>
     </row>
@@ -49968,7 +50674,7 @@
         <v>671</v>
       </c>
       <c r="L165" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>'nombre6' : r_val['nombre6'],</v>
       </c>
     </row>
@@ -49980,7 +50686,7 @@
         <v>672</v>
       </c>
       <c r="L166" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>'puesto6' : r_val['puesto6'],</v>
       </c>
     </row>
@@ -49992,7 +50698,7 @@
         <v>673</v>
       </c>
       <c r="L167" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>'m6' : r_val['m6'],</v>
       </c>
     </row>
@@ -50004,7 +50710,7 @@
         <v>674</v>
       </c>
       <c r="L168" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>'nombre7' : r_val['nombre7'],</v>
       </c>
     </row>
@@ -50016,7 +50722,7 @@
         <v>675</v>
       </c>
       <c r="L169" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>'puesto7' : r_val['puesto7'],</v>
       </c>
     </row>
@@ -50028,7 +50734,7 @@
         <v>676</v>
       </c>
       <c r="L170" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>'m7' : r_val['m7'],</v>
       </c>
     </row>
@@ -50040,7 +50746,7 @@
         <v>677</v>
       </c>
       <c r="L171" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>'nombre8' : r_val['nombre8'],</v>
       </c>
     </row>
@@ -50052,7 +50758,7 @@
         <v>678</v>
       </c>
       <c r="L172" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>'puesto8' : r_val['puesto8'],</v>
       </c>
     </row>
@@ -50064,7 +50770,7 @@
         <v>679</v>
       </c>
       <c r="L173" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>'m8' : r_val['m8'],</v>
       </c>
     </row>
@@ -50076,7 +50782,7 @@
         <v>680</v>
       </c>
       <c r="L174" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>'nombre9' : r_val['nombre9'],</v>
       </c>
     </row>
@@ -50088,7 +50794,7 @@
         <v>681</v>
       </c>
       <c r="L175" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>'puesto9' : r_val['puesto9'],</v>
       </c>
     </row>
@@ -50100,7 +50806,7 @@
         <v>682</v>
       </c>
       <c r="L176" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>'m9' : r_val['m9'],</v>
       </c>
     </row>
@@ -50112,7 +50818,7 @@
         <v>683</v>
       </c>
       <c r="L177" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>'nombre10' : r_val['nombre10'],</v>
       </c>
     </row>
@@ -50124,7 +50830,7 @@
         <v>684</v>
       </c>
       <c r="L178" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>'puesto10' : r_val['puesto10'],</v>
       </c>
     </row>
@@ -50136,7 +50842,7 @@
         <v>685</v>
       </c>
       <c r="L179" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>'m10' : r_val['m10'],</v>
       </c>
     </row>
@@ -50149,7 +50855,7 @@
         <v>{{ registro_perito }}</v>
       </c>
       <c r="L180" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>'registro_perito' : r_val['registro_perito'],</v>
       </c>
     </row>
@@ -50162,7 +50868,7 @@
         <v>{{ no_registro }}</v>
       </c>
       <c r="L181" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>'no_registro' : r_val['no_registro'],</v>
       </c>
     </row>
@@ -50171,11 +50877,11 @@
         <v>1732</v>
       </c>
       <c r="K182" t="str">
-        <f t="shared" ref="K182:K183" si="61">+_xlfn.CONCAT("{{ ",J182," }}")</f>
+        <f t="shared" ref="K182:K183" si="79">+_xlfn.CONCAT("{{ ",J182," }}")</f>
         <v>{{ dh_int }}</v>
       </c>
       <c r="L182" t="str">
-        <f t="shared" ref="L182:L183" si="62">+_xlfn.CONCAT("'",J182,"' : r_val['",J182,"'],")</f>
+        <f t="shared" ref="L182:L183" si="80">+_xlfn.CONCAT("'",J182,"' : r_val['",J182,"'],")</f>
         <v>'dh_int' : r_val['dh_int'],</v>
       </c>
     </row>
@@ -50184,11 +50890,11 @@
         <v>1733</v>
       </c>
       <c r="K183" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="79"/>
         <v>{{ dh_ext }}</v>
       </c>
       <c r="L183" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="80"/>
         <v>'dh_ext' : r_val['dh_ext'],</v>
       </c>
     </row>
@@ -50197,11 +50903,11 @@
         <v>1734</v>
       </c>
       <c r="K184" t="str">
-        <f t="shared" ref="K184" si="63">+_xlfn.CONCAT("{{ ",J184," }}")</f>
+        <f t="shared" ref="K184" si="81">+_xlfn.CONCAT("{{ ",J184," }}")</f>
         <v>{{ detectores_ext }}</v>
       </c>
       <c r="L184" t="str">
-        <f t="shared" ref="L184" si="64">+_xlfn.CONCAT("'",J184,"' : r_val['",J184,"'],")</f>
+        <f t="shared" ref="L184" si="82">+_xlfn.CONCAT("'",J184,"' : r_val['",J184,"'],")</f>
         <v>'detectores_ext' : r_val['detectores_ext'],</v>
       </c>
     </row>
@@ -50210,11 +50916,11 @@
         <v>1735</v>
       </c>
       <c r="K185" t="str">
-        <f t="shared" ref="K185" si="65">+_xlfn.CONCAT("{{ ",J185," }}")</f>
+        <f t="shared" ref="K185" si="83">+_xlfn.CONCAT("{{ ",J185," }}")</f>
         <v>{{ coord_sup_puesto }}</v>
       </c>
       <c r="L185" t="str">
-        <f t="shared" ref="L185" si="66">+_xlfn.CONCAT("'",J185,"' : r_val['",J185,"'],")</f>
+        <f t="shared" ref="L185" si="84">+_xlfn.CONCAT("'",J185,"' : r_val['",J185,"'],")</f>
         <v>'coord_sup_puesto' : r_val['coord_sup_puesto'],</v>
       </c>
     </row>
@@ -50223,11 +50929,11 @@
         <v>1741</v>
       </c>
       <c r="K186" t="str">
-        <f t="shared" ref="K186:K189" si="67">+_xlfn.CONCAT("{{ ",J186," }}")</f>
+        <f t="shared" ref="K186:K189" si="85">+_xlfn.CONCAT("{{ ",J186," }}")</f>
         <v>{{ riesgo1 }}</v>
       </c>
       <c r="L186" t="str">
-        <f t="shared" ref="L186:L189" si="68">+_xlfn.CONCAT("'",J186,"' : r_val['",J186,"'],")</f>
+        <f t="shared" ref="L186:L189" si="86">+_xlfn.CONCAT("'",J186,"' : r_val['",J186,"'],")</f>
         <v>'riesgo1' : r_val['riesgo1'],</v>
       </c>
     </row>
@@ -50236,11 +50942,11 @@
         <v>1742</v>
       </c>
       <c r="K187" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="85"/>
         <v>{{ riesgo2 }}</v>
       </c>
       <c r="L187" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="86"/>
         <v>'riesgo2' : r_val['riesgo2'],</v>
       </c>
     </row>
@@ -50249,11 +50955,11 @@
         <v>1743</v>
       </c>
       <c r="K188" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="85"/>
         <v>{{ riesgo3 }}</v>
       </c>
       <c r="L188" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="86"/>
         <v>'riesgo3' : r_val['riesgo3'],</v>
       </c>
     </row>
@@ -50262,11 +50968,11 @@
         <v>1744</v>
       </c>
       <c r="K189" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="85"/>
         <v>{{ riesgo4 }}</v>
       </c>
       <c r="L189" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="86"/>
         <v>'riesgo4' : r_val['riesgo4'],</v>
       </c>
     </row>
@@ -50275,11 +50981,11 @@
         <v>1748</v>
       </c>
       <c r="K190" t="str">
-        <f t="shared" ref="K190" si="69">+_xlfn.CONCAT("{{ ",J190," }}")</f>
+        <f t="shared" ref="K190" si="87">+_xlfn.CONCAT("{{ ",J190," }}")</f>
         <v>{{ valor_gri }}</v>
       </c>
       <c r="L190" t="str">
-        <f t="shared" ref="L190" si="70">+_xlfn.CONCAT("'",J190,"' : r_val['",J190,"'],")</f>
+        <f t="shared" ref="L190" si="88">+_xlfn.CONCAT("'",J190,"' : r_val['",J190,"'],")</f>
         <v>'valor_gri' : r_val['valor_gri'],</v>
       </c>
     </row>
@@ -50288,11 +50994,11 @@
         <v>1749</v>
       </c>
       <c r="K191" t="str">
-        <f t="shared" ref="K191:K194" si="71">+_xlfn.CONCAT("{{ ",J191," }}")</f>
+        <f t="shared" ref="K191:K194" si="89">+_xlfn.CONCAT("{{ ",J191," }}")</f>
         <v>{{ medidas_ries1 }}</v>
       </c>
       <c r="L191" t="str">
-        <f t="shared" ref="L191:L194" si="72">+_xlfn.CONCAT("'",J191,"' : r_val['",J191,"'],")</f>
+        <f t="shared" ref="L191:L194" si="90">+_xlfn.CONCAT("'",J191,"' : r_val['",J191,"'],")</f>
         <v>'medidas_ries1' : r_val['medidas_ries1'],</v>
       </c>
     </row>
@@ -50301,11 +51007,11 @@
         <v>1750</v>
       </c>
       <c r="K192" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="89"/>
         <v>{{ medidas_ries2 }}</v>
       </c>
       <c r="L192" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="90"/>
         <v>'medidas_ries2' : r_val['medidas_ries2'],</v>
       </c>
     </row>
@@ -50314,11 +51020,11 @@
         <v>1751</v>
       </c>
       <c r="K193" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="89"/>
         <v>{{ medidas_ries3 }}</v>
       </c>
       <c r="L193" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="90"/>
         <v>'medidas_ries3' : r_val['medidas_ries3'],</v>
       </c>
     </row>
@@ -50327,11 +51033,11 @@
         <v>1752</v>
       </c>
       <c r="K194" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="89"/>
         <v>{{ medidas_ries4 }}</v>
       </c>
       <c r="L194" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="90"/>
         <v>'medidas_ries4' : r_val['medidas_ries4'],</v>
       </c>
     </row>
@@ -50340,11 +51046,11 @@
         <v>2075</v>
       </c>
       <c r="K195" t="str">
-        <f t="shared" ref="K195:K210" si="73">+_xlfn.CONCAT("{{ ",J195," }}")</f>
+        <f t="shared" ref="K195:K210" si="91">+_xlfn.CONCAT("{{ ",J195," }}")</f>
         <v>{{ barretas }}</v>
       </c>
       <c r="L195" t="str">
-        <f t="shared" ref="L195:L210" si="74">+_xlfn.CONCAT("'",J195,"' : r_val['",J195,"'],")</f>
+        <f t="shared" ref="L195:L210" si="92">+_xlfn.CONCAT("'",J195,"' : r_val['",J195,"'],")</f>
         <v>'barretas' : r_val['barretas'],</v>
       </c>
     </row>
@@ -50353,11 +51059,11 @@
         <v>2076</v>
       </c>
       <c r="K196" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="91"/>
         <v>{{ barretas_ubicacion }}</v>
       </c>
       <c r="L196" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="92"/>
         <v>'barretas_ubicacion' : r_val['barretas_ubicacion'],</v>
       </c>
     </row>
@@ -50366,11 +51072,11 @@
         <v>2077</v>
       </c>
       <c r="K197" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="91"/>
         <v>{{ banderines }}</v>
       </c>
       <c r="L197" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="92"/>
         <v>'banderines' : r_val['banderines'],</v>
       </c>
     </row>
@@ -50379,11 +51085,11 @@
         <v>2078</v>
       </c>
       <c r="K198" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="91"/>
         <v>{{ banderines_ubicacion }}</v>
       </c>
       <c r="L198" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="92"/>
         <v>'banderines_ubicacion' : r_val['banderines_ubicacion'],</v>
       </c>
     </row>
@@ -50392,11 +51098,11 @@
         <v>2079</v>
       </c>
       <c r="K199" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="91"/>
         <v>{{ casco }}</v>
       </c>
       <c r="L199" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="92"/>
         <v>'casco' : r_val['casco'],</v>
       </c>
     </row>
@@ -50405,11 +51111,11 @@
         <v>2080</v>
       </c>
       <c r="K200" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="91"/>
         <v>{{ casco_ubicacion }}</v>
       </c>
       <c r="L200" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="92"/>
         <v>'casco_ubicacion' : r_val['casco_ubicacion'],</v>
       </c>
     </row>
@@ -50418,11 +51124,11 @@
         <v>2081</v>
       </c>
       <c r="K201" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="91"/>
         <v>{{ guantes }}</v>
       </c>
       <c r="L201" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="92"/>
         <v>'guantes' : r_val['guantes'],</v>
       </c>
     </row>
@@ -50431,11 +51137,11 @@
         <v>2082</v>
       </c>
       <c r="K202" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="91"/>
         <v>{{ guantes_ubicacion }}</v>
       </c>
       <c r="L202" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="92"/>
         <v>'guantes_ubicacion' : r_val['guantes_ubicacion'],</v>
       </c>
     </row>
@@ -50444,11 +51150,11 @@
         <v>2083</v>
       </c>
       <c r="K203" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="91"/>
         <v>{{ linterna }}</v>
       </c>
       <c r="L203" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="92"/>
         <v>'linterna' : r_val['linterna'],</v>
       </c>
     </row>
@@ -50457,11 +51163,11 @@
         <v>2084</v>
       </c>
       <c r="K204" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="91"/>
         <v>{{ linterna_ubicacion }}</v>
       </c>
       <c r="L204" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="92"/>
         <v>'linterna_ubicacion' : r_val['linterna_ubicacion'],</v>
       </c>
     </row>
@@ -50470,11 +51176,11 @@
         <v>2085</v>
       </c>
       <c r="K205" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="91"/>
         <v>{{ pala }}</v>
       </c>
       <c r="L205" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="92"/>
         <v>'pala' : r_val['pala'],</v>
       </c>
     </row>
@@ -50483,11 +51189,11 @@
         <v>2086</v>
       </c>
       <c r="K206" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="91"/>
         <v>{{ pala_ubicacion }}</v>
       </c>
       <c r="L206" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="92"/>
         <v>'pala_ubicacion' : r_val['pala_ubicacion'],</v>
       </c>
     </row>
@@ -50496,11 +51202,11 @@
         <v>2087</v>
       </c>
       <c r="K207" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="91"/>
         <v>{{ pico }}</v>
       </c>
       <c r="L207" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="92"/>
         <v>'pico' : r_val['pico'],</v>
       </c>
     </row>
@@ -50509,11 +51215,11 @@
         <v>2088</v>
       </c>
       <c r="K208" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="91"/>
         <v>{{ pico_ubicacion }}</v>
       </c>
       <c r="L208" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="92"/>
         <v>'pico_ubicacion' : r_val['pico_ubicacion'],</v>
       </c>
     </row>
@@ -50522,11 +51228,11 @@
         <v>2089</v>
       </c>
       <c r="K209" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="91"/>
         <v>{{ camilla }}</v>
       </c>
       <c r="L209" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="92"/>
         <v>'camilla' : r_val['camilla'],</v>
       </c>
     </row>
@@ -50535,11 +51241,11 @@
         <v>2090</v>
       </c>
       <c r="K210" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="91"/>
         <v>{{ camilla_ubicacion }}</v>
       </c>
       <c r="L210" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="92"/>
         <v>'camilla_ubicacion' : r_val['camilla_ubicacion'],</v>
       </c>
     </row>

--- a/Inputs/BD.xlsx
+++ b/Inputs/BD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/078e1a455e5c02ce/Documentos/GitHub/Proyecto_PIPC/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6316" documentId="13_ncr:1_{7D3A426E-EC5E-453A-8CC7-F83B71F24F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B58571F-D84D-438F-B359-A07494472925}"/>
+  <xr:revisionPtr revIDLastSave="6340" documentId="13_ncr:1_{7D3A426E-EC5E-453A-8CC7-F83B71F24F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9538B94-DA9D-401D-B864-ED3FC7B63852}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3F095A75-F066-4695-8672-8D4315F1EF23}"/>
   </bookViews>

--- a/Inputs/BD.xlsx
+++ b/Inputs/BD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/078e1a455e5c02ce/Documentos/GitHub/Proyecto_PIPC/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6340" documentId="13_ncr:1_{7D3A426E-EC5E-453A-8CC7-F83B71F24F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9538B94-DA9D-401D-B864-ED3FC7B63852}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{898522BF-B0F8-4888-9748-DC730D5D6CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A66393B-FE24-4A2A-8A20-28854F4232E6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3F095A75-F066-4695-8672-8D4315F1EF23}"/>
   </bookViews>
@@ -563,7 +563,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7178" uniqueCount="2175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7254" uniqueCount="2203">
   <si>
     <t>dia</t>
   </si>
@@ -7088,6 +7088,90 @@
   </si>
   <si>
     <t>ev_sim (8).png</t>
+  </si>
+  <si>
+    <t>comunicación</t>
+  </si>
+  <si>
+    <t>CASTELLANOS PAREDES ESMERALDA JAMÍN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VELÁZQUEZ RÍOS ARMANDO DE JESÚS </t>
+  </si>
+  <si>
+    <t>JORGE ISRAEL URRUTIA VEGA</t>
+  </si>
+  <si>
+    <t>ANA BERTHA MEZA MORALES</t>
+  </si>
+  <si>
+    <t>MAURICIO PIÑÓN VARGAS</t>
+  </si>
+  <si>
+    <t>THE HOME ASIAN</t>
+  </si>
+  <si>
+    <t>THE HOME MARKET</t>
+  </si>
+  <si>
+    <t>HAS210217PH8</t>
+  </si>
+  <si>
+    <t>TIENDA DEPARTAMENTAL</t>
+  </si>
+  <si>
+    <t>BLVD INTERAMERICANO</t>
+  </si>
+  <si>
+    <t>LOMAS DE ANGELOPOLIS, SAN BERNANDINO TLAXCALANCINGO</t>
+  </si>
+  <si>
+    <t>fechamone22@gmail.com</t>
+  </si>
+  <si>
+    <t>NUEVO</t>
+  </si>
+  <si>
+    <t>JIAHAO BAO</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA NAVA SEGURA</t>
+  </si>
+  <si>
+    <t>10:00 A 21:00 HORAS</t>
+  </si>
+  <si>
+    <t>18.997954848887275, -98.27588030433564</t>
+  </si>
+  <si>
+    <t>ARBYS</t>
+  </si>
+  <si>
+    <t>ANGELES SANCHEZ</t>
+  </si>
+  <si>
+    <t>MARIA LOURDES FLORES PEREZ</t>
+  </si>
+  <si>
+    <t>JAHZEEL ROJAS TORRES</t>
+  </si>
+  <si>
+    <t>ISAI FLORES MARTINEZ</t>
+  </si>
+  <si>
+    <t>PAMELA MONTSERRAT VALDE VEGA</t>
+  </si>
+  <si>
+    <t>LIZBETH FLORES ORTIZ</t>
+  </si>
+  <si>
+    <t>MARISOL GARCIA MORALES</t>
+  </si>
+  <si>
+    <t>VALERIA PAREDES GONZALEZ</t>
+  </si>
+  <si>
+    <t>UVP</t>
   </si>
 </sst>
 </file>
@@ -7710,7 +7794,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="26" fmlaLink="$A$1" max="30000" min="1" page="10" val="53"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="26" fmlaLink="$A$1" max="30000" min="1" page="10" val="61"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7766,10 +7850,6 @@
     <mc:Fallback/>
   </mc:AlternateContent>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8105,10 +8185,13 @@
   <sheetData>
     <row r="1" spans="1:322" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="DS1" t="s">
         <v>1969</v>
+      </c>
+      <c r="EO1" s="11" t="s">
+        <v>2175</v>
       </c>
     </row>
     <row r="2" spans="1:322" x14ac:dyDescent="0.3">
@@ -31015,7 +31098,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>551</v>
+        <v>2202</v>
       </c>
       <c r="C55" t="s">
         <v>2037</v>
@@ -31293,6 +31376,21 @@
       <c r="EG55" t="s">
         <v>443</v>
       </c>
+      <c r="EL55" s="11" t="s">
+        <v>2176</v>
+      </c>
+      <c r="EO55" s="11" t="s">
+        <v>2177</v>
+      </c>
+      <c r="ER55" s="11" t="s">
+        <v>2178</v>
+      </c>
+      <c r="EX55" s="11" t="s">
+        <v>2179</v>
+      </c>
+      <c r="FD55" s="11" t="s">
+        <v>2180</v>
+      </c>
       <c r="FJ55" t="s">
         <v>2095</v>
       </c>
@@ -31322,7 +31420,7 @@
         <v>455</v>
       </c>
       <c r="FT55">
-        <f t="shared" ref="FT55:FT62" si="25">60*AG55</f>
+        <f t="shared" ref="FT55:FT63" si="25">60*AG55</f>
         <v>4200</v>
       </c>
       <c r="FU55" s="4">
@@ -31343,7 +31441,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>551</v>
+        <v>2202</v>
       </c>
       <c r="C56" t="s">
         <v>2037</v>
@@ -31397,7 +31495,7 @@
         <v>2096</v>
       </c>
       <c r="T56" t="str">
-        <f t="shared" ref="T56:T62" si="26">+IF(V56&gt;1000,"JORGE MANUEL ISLAS GOWER", "NOE MORA RAMIREZ")</f>
+        <f t="shared" ref="T56:T63" si="26">+IF(V56&gt;1000,"JORGE MANUEL ISLAS GOWER", "NOE MORA RAMIREZ")</f>
         <v>NOE MORA RAMIREZ</v>
       </c>
       <c r="V56">
@@ -31468,7 +31566,7 @@
       </c>
       <c r="AR56" s="4">
         <f t="shared" si="18"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AS56">
         <v>3</v>
@@ -31548,6 +31646,9 @@
       <c r="CF56">
         <v>4</v>
       </c>
+      <c r="CH56">
+        <v>1</v>
+      </c>
       <c r="CI56">
         <v>9</v>
       </c>
@@ -31558,6 +31659,9 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
+      <c r="CM56">
+        <v>2</v>
+      </c>
       <c r="CS56">
         <v>10</v>
       </c>
@@ -31605,6 +31709,21 @@
       </c>
       <c r="EG56" t="s">
         <v>443</v>
+      </c>
+      <c r="EL56" s="11" t="s">
+        <v>2176</v>
+      </c>
+      <c r="EO56" s="11" t="s">
+        <v>2177</v>
+      </c>
+      <c r="ER56" s="11" t="s">
+        <v>2178</v>
+      </c>
+      <c r="EX56" s="11" t="s">
+        <v>2179</v>
+      </c>
+      <c r="FD56" s="11" t="s">
+        <v>2180</v>
       </c>
       <c r="FJ56" t="s">
         <v>820</v>
@@ -31655,7 +31774,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>551</v>
+        <v>2202</v>
       </c>
       <c r="C57" t="s">
         <v>2037</v>
@@ -31780,7 +31899,7 @@
       </c>
       <c r="AR57" s="4">
         <f t="shared" si="18"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AS57">
         <v>2</v>
@@ -31857,6 +31976,9 @@
       <c r="CG57">
         <v>1</v>
       </c>
+      <c r="CH57">
+        <v>1</v>
+      </c>
       <c r="CI57">
         <v>2</v>
       </c>
@@ -31911,6 +32033,21 @@
       </c>
       <c r="EG57" t="s">
         <v>443</v>
+      </c>
+      <c r="EL57" s="11" t="s">
+        <v>2176</v>
+      </c>
+      <c r="EO57" s="11" t="s">
+        <v>2177</v>
+      </c>
+      <c r="ER57" s="11" t="s">
+        <v>2178</v>
+      </c>
+      <c r="EX57" s="11" t="s">
+        <v>2179</v>
+      </c>
+      <c r="FD57" s="11" t="s">
+        <v>2180</v>
       </c>
       <c r="FJ57" t="s">
         <v>2110</v>
@@ -31961,7 +32098,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>551</v>
+        <v>2202</v>
       </c>
       <c r="C58" t="s">
         <v>2037</v>
@@ -32226,6 +32363,21 @@
       </c>
       <c r="EG58" t="s">
         <v>443</v>
+      </c>
+      <c r="EL58" s="11" t="s">
+        <v>2176</v>
+      </c>
+      <c r="EO58" s="11" t="s">
+        <v>2177</v>
+      </c>
+      <c r="ER58" s="11" t="s">
+        <v>2178</v>
+      </c>
+      <c r="EX58" s="11" t="s">
+        <v>2179</v>
+      </c>
+      <c r="FD58" s="11" t="s">
+        <v>2180</v>
       </c>
       <c r="FK58">
         <v>0</v>
@@ -32273,7 +32425,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>551</v>
+        <v>2202</v>
       </c>
       <c r="C59" t="s">
         <v>2037</v>
@@ -32398,7 +32550,7 @@
       </c>
       <c r="AR59" s="4">
         <f t="shared" si="18"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AS59">
         <v>2</v>
@@ -32466,6 +32618,12 @@
       <c r="CF59">
         <v>4</v>
       </c>
+      <c r="CH59">
+        <v>1</v>
+      </c>
+      <c r="CI59">
+        <v>1</v>
+      </c>
       <c r="CJ59">
         <v>1</v>
       </c>
@@ -32508,6 +32666,21 @@
       </c>
       <c r="EG59" t="s">
         <v>443</v>
+      </c>
+      <c r="EL59" s="11" t="s">
+        <v>2176</v>
+      </c>
+      <c r="EO59" s="11" t="s">
+        <v>2177</v>
+      </c>
+      <c r="ER59" s="11" t="s">
+        <v>2178</v>
+      </c>
+      <c r="EX59" s="11" t="s">
+        <v>2179</v>
+      </c>
+      <c r="FD59" s="11" t="s">
+        <v>2180</v>
       </c>
       <c r="FJ59" t="s">
         <v>2110</v>
@@ -32558,7 +32731,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>551</v>
+        <v>2202</v>
       </c>
       <c r="C60" t="s">
         <v>2037</v>
@@ -32683,7 +32856,7 @@
       </c>
       <c r="AR60" s="4">
         <f t="shared" si="18"/>
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AS60">
         <v>2</v>
@@ -32751,6 +32924,9 @@
       <c r="CF60">
         <v>7</v>
       </c>
+      <c r="CH60">
+        <v>1</v>
+      </c>
       <c r="CI60">
         <v>5</v>
       </c>
@@ -32811,6 +32987,21 @@
       </c>
       <c r="EG60" t="s">
         <v>443</v>
+      </c>
+      <c r="EL60" s="11" t="s">
+        <v>2176</v>
+      </c>
+      <c r="EO60" s="11" t="s">
+        <v>2177</v>
+      </c>
+      <c r="ER60" s="11" t="s">
+        <v>2178</v>
+      </c>
+      <c r="EX60" s="11" t="s">
+        <v>2179</v>
+      </c>
+      <c r="FD60" s="11" t="s">
+        <v>2180</v>
       </c>
       <c r="FJ60" t="s">
         <v>820</v>
@@ -32861,7 +33052,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>551</v>
+        <v>2202</v>
       </c>
       <c r="C61" t="s">
         <v>2037</v>
@@ -32986,7 +33177,7 @@
       </c>
       <c r="AR61" s="4">
         <f t="shared" si="18"/>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AS61">
         <v>1</v>
@@ -33053,6 +33244,9 @@
       </c>
       <c r="CF61">
         <v>25</v>
+      </c>
+      <c r="CH61">
+        <v>1</v>
       </c>
       <c r="CI61">
         <v>7</v>
@@ -33114,6 +33308,21 @@
       </c>
       <c r="EG61" t="s">
         <v>443</v>
+      </c>
+      <c r="EL61" s="11" t="s">
+        <v>2176</v>
+      </c>
+      <c r="EO61" s="11" t="s">
+        <v>2177</v>
+      </c>
+      <c r="ER61" s="11" t="s">
+        <v>2178</v>
+      </c>
+      <c r="EX61" s="11" t="s">
+        <v>2179</v>
+      </c>
+      <c r="FD61" s="11" t="s">
+        <v>2180</v>
       </c>
       <c r="FK61">
         <v>0</v>
@@ -33161,7 +33370,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>551</v>
+        <v>2202</v>
       </c>
       <c r="C62" t="s">
         <v>2037</v>
@@ -33417,6 +33626,21 @@
       </c>
       <c r="EG62" t="s">
         <v>443</v>
+      </c>
+      <c r="EL62" s="11" t="s">
+        <v>2176</v>
+      </c>
+      <c r="EO62" s="11" t="s">
+        <v>2177</v>
+      </c>
+      <c r="ER62" s="11" t="s">
+        <v>2178</v>
+      </c>
+      <c r="EX62" s="11" t="s">
+        <v>2179</v>
+      </c>
+      <c r="FD62" s="11" t="s">
+        <v>2180</v>
       </c>
       <c r="FJ62" t="s">
         <v>820</v>
@@ -33466,6 +33690,121 @@
       <c r="A63">
         <v>61</v>
       </c>
+      <c r="B63" t="s">
+        <v>2202</v>
+      </c>
+      <c r="C63" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D63" t="s">
+        <v>2182</v>
+      </c>
+      <c r="E63" t="s">
+        <v>2183</v>
+      </c>
+      <c r="G63" t="s">
+        <v>2184</v>
+      </c>
+      <c r="I63" t="s">
+        <v>2185</v>
+      </c>
+      <c r="J63">
+        <v>129</v>
+      </c>
+      <c r="K63" s="10" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L63" t="s">
+        <v>2186</v>
+      </c>
+      <c r="M63" t="s">
+        <v>1492</v>
+      </c>
+      <c r="N63" t="s">
+        <v>424</v>
+      </c>
+      <c r="O63">
+        <v>72830</v>
+      </c>
+      <c r="P63">
+        <v>2213924942</v>
+      </c>
+      <c r="Q63" s="3" t="s">
+        <v>2187</v>
+      </c>
+      <c r="R63" t="s">
+        <v>2188</v>
+      </c>
+      <c r="T63" t="str">
+        <f t="shared" si="26"/>
+        <v>JORGE MANUEL ISLAS GOWER</v>
+      </c>
+      <c r="V63">
+        <v>3000</v>
+      </c>
+      <c r="W63">
+        <v>3000</v>
+      </c>
+      <c r="X63">
+        <v>1</v>
+      </c>
+      <c r="Y63">
+        <v>1</v>
+      </c>
+      <c r="Z63">
+        <v>2</v>
+      </c>
+      <c r="AA63">
+        <v>2</v>
+      </c>
+      <c r="AB63">
+        <v>0</v>
+      </c>
+      <c r="AC63">
+        <v>0</v>
+      </c>
+      <c r="AD63" t="s">
+        <v>912</v>
+      </c>
+      <c r="AE63" t="s">
+        <v>2189</v>
+      </c>
+      <c r="AF63" t="s">
+        <v>2190</v>
+      </c>
+      <c r="AG63">
+        <v>30</v>
+      </c>
+      <c r="AH63">
+        <v>0</v>
+      </c>
+      <c r="AI63">
+        <v>16</v>
+      </c>
+      <c r="AJ63">
+        <v>14</v>
+      </c>
+      <c r="AK63">
+        <v>0</v>
+      </c>
+      <c r="AL63">
+        <v>0</v>
+      </c>
+      <c r="AM63">
+        <v>1</v>
+      </c>
+      <c r="AN63">
+        <v>200</v>
+      </c>
+      <c r="AO63">
+        <v>10</v>
+      </c>
+      <c r="AP63" t="s">
+        <v>430</v>
+      </c>
+      <c r="AQ63" t="s">
+        <v>2191</v>
+      </c>
       <c r="AR63" s="4">
         <f t="shared" si="18"/>
         <v>0</v>
@@ -33474,25 +33813,98 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
+      <c r="DW63">
+        <v>16</v>
+      </c>
+      <c r="DX63" t="s">
+        <v>2054</v>
+      </c>
+      <c r="DY63">
+        <v>2014</v>
+      </c>
+      <c r="DZ63" t="s">
+        <v>2192</v>
+      </c>
+      <c r="EA63" t="s">
+        <v>2193</v>
+      </c>
+      <c r="EB63" t="s">
+        <v>554</v>
+      </c>
+      <c r="EC63" t="s">
+        <v>554</v>
+      </c>
+      <c r="ED63" t="s">
+        <v>554</v>
+      </c>
+      <c r="EF63" t="s">
+        <v>442</v>
+      </c>
+      <c r="EG63" t="s">
+        <v>443</v>
+      </c>
+      <c r="EI63" s="11" t="s">
+        <v>2189</v>
+      </c>
+      <c r="EL63" s="11" t="s">
+        <v>2194</v>
+      </c>
+      <c r="EO63" s="11" t="s">
+        <v>2195</v>
+      </c>
+      <c r="ER63" s="11" t="s">
+        <v>2196</v>
+      </c>
+      <c r="EU63" s="11" t="s">
+        <v>2197</v>
+      </c>
+      <c r="EX63" s="11" t="s">
+        <v>2198</v>
+      </c>
+      <c r="FA63" s="11" t="s">
+        <v>2199</v>
+      </c>
+      <c r="FD63" s="11" t="s">
+        <v>2200</v>
+      </c>
+      <c r="FG63" s="11" t="s">
+        <v>2201</v>
+      </c>
+      <c r="FK63">
+        <v>0</v>
+      </c>
       <c r="FL63" s="4">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
+      <c r="FN63">
+        <v>0</v>
+      </c>
       <c r="FO63" s="4">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
+      <c r="FQ63">
+        <v>0</v>
+      </c>
       <c r="FR63" s="4">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
+      <c r="FS63" t="s">
+        <v>455</v>
+      </c>
+      <c r="FT63">
+        <f t="shared" si="25"/>
+        <v>1800</v>
+      </c>
       <c r="FU63" s="4">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="FV63" s="4">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="FW63" s="4" t="str">
         <f t="shared" si="27"/>
@@ -38511,7 +38923,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A3:FV13 FX3:GC43 B14:G14 I14:FV14 KD14:LJ42 A14:A201 D15:FV60 B15:C68 GL43:GW43 GY43:HA43 HC43:HD43 HF43 HK43 HP43:HR43 IC43 IE43 IH43:IJ43 IL43 FX44:IM60 D61:IM201 B69 B70:C201 A202:IM208">
+  <conditionalFormatting sqref="A3:FV13 FX3:GC43 B14:G14 I14:FV14 KD14:LJ42 A14:A201 D15:FV58 GL43:GW43 GY43:HA43 HC43:HD43 HF43 HK43 HP43:HR43 IC43 IE43 IH43:IJ43 IL43 FX44:IM60 EM59:FV60 D59:EL62 EM61:IM62 D63:IM201 B69 B70:C201 A202:IM208 B15:C68">
     <cfRule type="expression" dxfId="40" priority="581">
       <formula>$A3=$A$1</formula>
     </cfRule>
@@ -38718,7 +39130,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B201" xr:uid="{41C0D522-5D90-43F5-9DB3-E0F81FDE0774}">
-      <formula1>"BANCO, BBVA, COMPARTAMOS, GASOLINERA, GENERAL, GDL"</formula1>
+      <formula1>"BANCO, BBVA, COMPARTAMOS, GASOLINERA, GENERAL, GDL, UVP"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -38758,16 +39170,17 @@
     <hyperlink ref="Q51" r:id="rId34" xr:uid="{DDE804A1-A1F2-4C98-8E4E-FF4954DAAB88}"/>
     <hyperlink ref="Q55" r:id="rId35" xr:uid="{B9F1BA52-AC5D-4251-9008-A4D12466756B}"/>
     <hyperlink ref="Q56:Q62" r:id="rId36" display="serv.medico@uvp.mx" xr:uid="{35C2D78B-CC24-428B-B9D9-6B044FB382AB}"/>
+    <hyperlink ref="Q63" r:id="rId37" xr:uid="{BAC1ACDE-29E9-44FE-B95B-93A859FE6E4F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId37"/>
-  <legacyDrawing r:id="rId38"/>
+  <drawing r:id="rId38"/>
+  <legacyDrawing r:id="rId39"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x14">
       <controls>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1025" r:id="rId39" name="Spinner 1">
+            <control shapeId="1025" r:id="rId40" name="Spinner 1">
               <controlPr defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
@@ -38801,7 +39214,7 @@
     <row r="1" spans="1:310" x14ac:dyDescent="0.3">
       <c r="A1">
         <f>+BD!A1</f>
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="B1" t="s">
         <v>134</v>
@@ -39734,39 +40147,39 @@
     <row r="2" spans="1:310" x14ac:dyDescent="0.3">
       <c r="B2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,2, FALSE)</f>
-        <v>GENERAL</v>
+        <v>UVP</v>
       </c>
       <c r="C2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,3, FALSE)</f>
-        <v>UNIVERSIDAD DEL VALLE DE PUEBLA SC</v>
+        <v>THE HOME ASIAN</v>
       </c>
       <c r="D2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,4, FALSE)</f>
-        <v>COMPLEJO AZTLAN</v>
+        <v>THE HOME MARKET</v>
       </c>
       <c r="E2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,5, FALSE)</f>
-        <v>UVP810305C25</v>
-      </c>
-      <c r="F2" t="str">
+        <v>HAS210217PH8</v>
+      </c>
+      <c r="F2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,6, FALSE)</f>
-        <v>COMPLEJO AZTLAN</v>
+        <v>0</v>
       </c>
       <c r="G2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,7, FALSE)</f>
-        <v>ESCUELA DE EDUCACION MEDIA Y SUPERIOR</v>
-      </c>
-      <c r="H2" t="str">
+        <v>TIENDA DEPARTAMENTAL</v>
+      </c>
+      <c r="H2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,8, FALSE)</f>
-        <v>IMPARTICIÓN DE PROGRAMAS ACADÉMICOS, DESDE LICENCIATURAS HASTA POSGRADOS. ADEMÁS, PROMUEVE LA FORMACIÓN CONTINUA Y RECURSOS DE APRENDIZAJE.</v>
+        <v>0</v>
       </c>
       <c r="I2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,9, FALSE)</f>
-        <v>5 SUR</v>
+        <v>BLVD INTERAMERICANO</v>
       </c>
       <c r="J2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,10, FALSE)</f>
-        <v>5906</v>
+        <v>129</v>
       </c>
       <c r="K2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,11, FALSE)</f>
@@ -39774,11 +40187,11 @@
       </c>
       <c r="L2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,12, FALSE)</f>
-        <v>EL CERRITO</v>
+        <v>LOMAS DE ANGELOPOLIS, SAN BERNANDINO TLAXCALANCINGO</v>
       </c>
       <c r="M2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,13, FALSE)</f>
-        <v>PUEBLA</v>
+        <v>SAN ANDRES CHOLULA</v>
       </c>
       <c r="N2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,14, FALSE)</f>
@@ -39786,23 +40199,23 @@
       </c>
       <c r="O2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,15, FALSE)</f>
-        <v>72440</v>
-      </c>
-      <c r="P2" t="str">
+        <v>72830</v>
+      </c>
+      <c r="P2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,16, FALSE)</f>
-        <v>222 2669488 Ext: 353 y 355</v>
+        <v>2213924942</v>
       </c>
       <c r="Q2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,17, FALSE)</f>
-        <v>serv.medico@uvp.mx</v>
-      </c>
-      <c r="R2">
+        <v>fechamone22@gmail.com</v>
+      </c>
+      <c r="R2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,18, FALSE)</f>
-        <v>13</v>
-      </c>
-      <c r="S2" t="str">
+        <v>NUEVO</v>
+      </c>
+      <c r="S2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,19, FALSE)</f>
-        <v>6 DE DICIEMBRE DE 2010</v>
+        <v>0</v>
       </c>
       <c r="T2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,20, FALSE)</f>
@@ -39814,19 +40227,19 @@
       </c>
       <c r="V2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,22, FALSE)</f>
-        <v>2485</v>
+        <v>3000</v>
       </c>
       <c r="W2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,23, FALSE)</f>
-        <v>4639.5200000000004</v>
+        <v>3000</v>
       </c>
       <c r="X2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,24, FALSE)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,25, FALSE)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,26, FALSE)</f>
@@ -39838,7 +40251,7 @@
       </c>
       <c r="AB2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,28, FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,29, FALSE)</f>
@@ -39846,19 +40259,19 @@
       </c>
       <c r="AD2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,30, FALSE)</f>
-        <v>6 CAJONES</v>
+        <v>10 CAJONES</v>
       </c>
       <c r="AE2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,31, FALSE)</f>
-        <v>PRISCILIANO GERARDO ILLESCAS LOZANO</v>
+        <v>JIAHAO BAO</v>
       </c>
       <c r="AF2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,32, FALSE)</f>
-        <v>MODESTO ALFONSO HERNÁNDEZ ORTIZ</v>
+        <v>MARIA FERNANDA NAVA SEGURA</v>
       </c>
       <c r="AG2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,33, FALSE)</f>
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="AH2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,34, FALSE)</f>
@@ -39866,11 +40279,11 @@
       </c>
       <c r="AI2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,35, FALSE)</f>
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="AJ2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,36, FALSE)</f>
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="AK2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,37, FALSE)</f>
@@ -39886,47 +40299,47 @@
       </c>
       <c r="AN2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,40, FALSE)</f>
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AO2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,41, FALSE)</f>
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="AP2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,42, FALSE)</f>
-        <v>LUNES - SABADO</v>
+        <v>LUNES - DOMINGO</v>
       </c>
       <c r="AQ2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,43, FALSE)</f>
-        <v>07:00 A 21:00 HORAS</v>
+        <v>10:00 A 21:00 HORAS</v>
       </c>
       <c r="AR2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,44, FALSE)</f>
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="AS2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,45, FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="AT2" t="str">
+        <v>0</v>
+      </c>
+      <c r="AT2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,46, FALSE)</f>
-        <v>RECEPCION, BIBLIOTECA, CAI, CAPS</v>
+        <v>0</v>
       </c>
       <c r="AU2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,47, FALSE)</f>
-        <v>39</v>
-      </c>
-      <c r="AV2" t="str">
+        <v>0</v>
+      </c>
+      <c r="AV2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,48, FALSE)</f>
-        <v>EN TODO EL INMUEBLE</v>
+        <v>0</v>
       </c>
       <c r="AW2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,49, FALSE)</f>
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AX2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,50, FALSE)</f>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AY2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,51, FALSE)</f>
@@ -39954,11 +40367,11 @@
       </c>
       <c r="BE2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,57, FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="BF2" t="str">
+        <v>0</v>
+      </c>
+      <c r="BF2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,58, FALSE)</f>
-        <v>MEGAFONO</v>
+        <v>0</v>
       </c>
       <c r="BG2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,59, FALSE)</f>
@@ -39968,9 +40381,9 @@
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,60, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="BI2" t="str">
+      <c r="BI2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,61, FALSE)</f>
-        <v>COORDINACION, VIGILANCIA, CONTROL EXTERNO</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,62, FALSE)</f>
@@ -39982,51 +40395,51 @@
       </c>
       <c r="BL2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,64, FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="BM2" t="str">
+        <v>0</v>
+      </c>
+      <c r="BM2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,65, FALSE)</f>
-        <v>OFICINAS</v>
+        <v>0</v>
       </c>
       <c r="BN2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,66, FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="BO2" t="str">
+        <v>0</v>
+      </c>
+      <c r="BO2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,67, FALSE)</f>
-        <v>GABINETE</v>
+        <v>0</v>
       </c>
       <c r="BP2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,68, FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="BQ2" t="str">
+        <v>0</v>
+      </c>
+      <c r="BQ2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,69, FALSE)</f>
-        <v>GABINETE</v>
+        <v>0</v>
       </c>
       <c r="BR2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,70, FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="BS2" t="str">
+        <v>0</v>
+      </c>
+      <c r="BS2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,71, FALSE)</f>
-        <v>GABINETE</v>
+        <v>0</v>
       </c>
       <c r="BT2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,72, FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="BU2" t="str">
+        <v>0</v>
+      </c>
+      <c r="BU2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,73, FALSE)</f>
-        <v>GABINETE</v>
+        <v>0</v>
       </c>
       <c r="BV2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,74, FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="BW2" t="str">
+        <v>0</v>
+      </c>
+      <c r="BW2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,75, FALSE)</f>
-        <v>COORDINACION</v>
+        <v>0</v>
       </c>
       <c r="BX2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,76, FALSE)</f>
@@ -40038,31 +40451,31 @@
       </c>
       <c r="BZ2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,78, FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="CA2" t="str">
+        <v>0</v>
+      </c>
+      <c r="CA2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,79, FALSE)</f>
-        <v>GABINETE</v>
+        <v>0</v>
       </c>
       <c r="CB2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,80, FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="CC2" t="str">
+        <v>0</v>
+      </c>
+      <c r="CC2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,81, FALSE)</f>
-        <v>GABINETE</v>
+        <v>0</v>
       </c>
       <c r="CD2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,82, FALSE)</f>
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="CE2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,83, FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,84, FALSE)</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="CG2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,85, FALSE)</f>
@@ -40070,27 +40483,27 @@
       </c>
       <c r="CH2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,86, FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CI2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,87, FALSE)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="CJ2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,88, FALSE)</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="CK2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,89, FALSE)</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="CL2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,90, FALSE)</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="CM2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,91, FALSE)</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="CN2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,92, FALSE)</f>
@@ -40114,11 +40527,11 @@
       </c>
       <c r="CS2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,97, FALSE)</f>
-        <v>9</v>
-      </c>
-      <c r="CT2" t="str">
+        <v>0</v>
+      </c>
+      <c r="CT2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,98, FALSE)</f>
-        <v>AREA COMÚN</v>
+        <v>0</v>
       </c>
       <c r="CU2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,99, FALSE)</f>
@@ -40154,19 +40567,19 @@
       </c>
       <c r="DC2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,107, FALSE)</f>
-        <v>20</v>
-      </c>
-      <c r="DD2" t="str">
+        <v>0</v>
+      </c>
+      <c r="DD2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,108, FALSE)</f>
-        <v>BRIGADISTAS</v>
+        <v>0</v>
       </c>
       <c r="DE2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,109, FALSE)</f>
-        <v>11</v>
-      </c>
-      <c r="DF2" t="str">
+        <v>0</v>
+      </c>
+      <c r="DF2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,110, FALSE)</f>
-        <v>AREA COMÚN</v>
+        <v>0</v>
       </c>
       <c r="DG2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,111, FALSE)</f>
@@ -40234,7 +40647,7 @@
       </c>
       <c r="DW2" s="5">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,127, FALSE)</f>
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="DX2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,128, FALSE)</f>
@@ -40242,27 +40655,27 @@
       </c>
       <c r="DY2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,129, FALSE)</f>
-        <v>2024</v>
+        <v>2014</v>
       </c>
       <c r="DZ2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,130, FALSE)</f>
-        <v>19.017749517200585, -98.2183180754988</v>
+        <v>18.997954848887275, -98.27588030433564</v>
       </c>
       <c r="EA2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,131, FALSE)</f>
-        <v>TAQUERIA</v>
+        <v>ARBYS</v>
       </c>
       <c r="EB2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,132, FALSE)</f>
-        <v>UVP TEOCALLI</v>
+        <v>TERRENO</v>
       </c>
       <c r="EC2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,133, FALSE)</f>
-        <v>CASA HABITACION</v>
+        <v>TERRENO</v>
       </c>
       <c r="ED2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,134, FALSE)</f>
-        <v>PARQUE EL ELEFANTE</v>
+        <v>TERRENO</v>
       </c>
       <c r="EE2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,135, FALSE)</f>
@@ -40280,9 +40693,9 @@
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,138, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="EI2">
+      <c r="EI2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,139, FALSE)</f>
-        <v>0</v>
+        <v>JIAHAO BAO</v>
       </c>
       <c r="EJ2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,140, FALSE)</f>
@@ -40292,9 +40705,9 @@
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,141, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="EL2">
+      <c r="EL2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,142, FALSE)</f>
-        <v>0</v>
+        <v>ANGELES SANCHEZ</v>
       </c>
       <c r="EM2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,143, FALSE)</f>
@@ -40304,9 +40717,9 @@
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,144, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="EO2">
+      <c r="EO2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,145, FALSE)</f>
-        <v>0</v>
+        <v>MARIA LOURDES FLORES PEREZ</v>
       </c>
       <c r="EP2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,146, FALSE)</f>
@@ -40316,9 +40729,9 @@
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,147, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="ER2">
+      <c r="ER2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,148, FALSE)</f>
-        <v>0</v>
+        <v>JAHZEEL ROJAS TORRES</v>
       </c>
       <c r="ES2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,149, FALSE)</f>
@@ -40328,9 +40741,9 @@
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,150, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="EU2">
+      <c r="EU2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,151, FALSE)</f>
-        <v>0</v>
+        <v>ISAI FLORES MARTINEZ</v>
       </c>
       <c r="EV2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,152, FALSE)</f>
@@ -40340,9 +40753,9 @@
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,153, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="EX2">
+      <c r="EX2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,154, FALSE)</f>
-        <v>0</v>
+        <v>PAMELA MONTSERRAT VALDE VEGA</v>
       </c>
       <c r="EY2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,155, FALSE)</f>
@@ -40352,9 +40765,9 @@
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,156, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="FA2">
+      <c r="FA2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,157, FALSE)</f>
-        <v>0</v>
+        <v>LIZBETH FLORES ORTIZ</v>
       </c>
       <c r="FB2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,158, FALSE)</f>
@@ -40364,9 +40777,9 @@
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,159, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="FD2">
+      <c r="FD2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,160, FALSE)</f>
-        <v>0</v>
+        <v>MARISOL GARCIA MORALES</v>
       </c>
       <c r="FE2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,161, FALSE)</f>
@@ -40376,9 +40789,9 @@
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,162, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="FG2">
+      <c r="FG2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,163, FALSE)</f>
-        <v>0</v>
+        <v>VALERIA PAREDES GONZALEZ</v>
       </c>
       <c r="FH2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,164, FALSE)</f>
@@ -40388,17 +40801,17 @@
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,165, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="FJ2" t="str">
+      <c r="FJ2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,166, FALSE)</f>
-        <v>GAS LP Y GAS NATURAL</v>
+        <v>0</v>
       </c>
       <c r="FK2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,167, FALSE)</f>
-        <v>20480</v>
+        <v>0</v>
       </c>
       <c r="FL2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,168, FALSE)</f>
-        <v>6.8266666666666671</v>
+        <v>0</v>
       </c>
       <c r="FM2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,169, FALSE)</f>
@@ -40430,19 +40843,19 @@
       </c>
       <c r="FT2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,176, FALSE)</f>
-        <v>4200</v>
+        <v>1800</v>
       </c>
       <c r="FU2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,177, FALSE)</f>
-        <v>0.28000000000000003</v>
+        <v>0.12</v>
       </c>
       <c r="FV2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,178, FALSE)</f>
-        <v>7.1066666666666674</v>
+        <v>0.12</v>
       </c>
       <c r="FW2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,179, FALSE)</f>
-        <v>ALTO</v>
+        <v>ORDINARIO</v>
       </c>
       <c r="FX2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,180, FALSE)</f>

--- a/Inputs/BD.xlsx
+++ b/Inputs/BD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/078e1a455e5c02ce/Documentos/GitHub/Proyecto_PIPC/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="384" documentId="13_ncr:1_{898522BF-B0F8-4888-9748-DC730D5D6CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{661B8319-A996-4DB9-AF99-FAEA8E9222EC}"/>
+  <xr:revisionPtr revIDLastSave="544" documentId="13_ncr:1_{898522BF-B0F8-4888-9748-DC730D5D6CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBD41185-BEC0-48F2-BCE0-29EF60BE5DF0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3F095A75-F066-4695-8672-8D4315F1EF23}"/>
   </bookViews>
@@ -563,7 +563,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7441" uniqueCount="2268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7507" uniqueCount="2302">
   <si>
     <t>dia</t>
   </si>
@@ -7367,6 +7367,108 @@
   </si>
   <si>
     <t>9:00 AM A 19:00 HRS Y 9:00 AM A 2:00 PM.</t>
+  </si>
+  <si>
+    <t>FIBRA A LA CASA SA DE CV</t>
+  </si>
+  <si>
+    <t>ZOOY</t>
+  </si>
+  <si>
+    <t>FCA2005056RA</t>
+  </si>
+  <si>
+    <t>SERVICIOS DE TELECOMUNICACIONES</t>
+  </si>
+  <si>
+    <t>CALLE JUAREZ</t>
+  </si>
+  <si>
+    <t>LOCALES 7 Y 8</t>
+  </si>
+  <si>
+    <t>AMOZOC DE MOTA</t>
+  </si>
+  <si>
+    <t>ate3@zooy.com.mx</t>
+  </si>
+  <si>
+    <t>13 DE MAYO DE 2024</t>
+  </si>
+  <si>
+    <t>2 CAJONES</t>
+  </si>
+  <si>
+    <t>HECTOR ERICK CELIS VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ALAN FABRICIO DOMINGUEZ PEÑA</t>
+  </si>
+  <si>
+    <t>LUNES A DOMINGO</t>
+  </si>
+  <si>
+    <t>9:00 A 19:00 Y 9:00 A 17:30</t>
+  </si>
+  <si>
+    <t>ALARMA</t>
+  </si>
+  <si>
+    <t>JUNIO</t>
+  </si>
+  <si>
+    <t>19.04339117024435, -98.04489831452031</t>
+  </si>
+  <si>
+    <t>PROPIEDAD PRIVADA</t>
+  </si>
+  <si>
+    <t>ESTACIONAMIENTO LOCALES COMERCIALES</t>
+  </si>
+  <si>
+    <t>JANET RAMIREZ SOMBRERERO</t>
+  </si>
+  <si>
+    <t>GESTIÓN DE REDES Y SISTEMAS DE COMUNICACIÓN, ASÍ COMO LA ATENCIÓN Y SOPORTE TÉCNICO A LOS CLIENTES.</t>
+  </si>
+  <si>
+    <t>CARRETERA FEDERAL PUEBLA-TEHUACAN</t>
+  </si>
+  <si>
+    <t>KM 9, 310</t>
+  </si>
+  <si>
+    <t>LOCAL 4</t>
+  </si>
+  <si>
+    <t>CASA BLANCA</t>
+  </si>
+  <si>
+    <t>diana.sanchez@zooy.com.mx</t>
+  </si>
+  <si>
+    <t>FEBRERO DE 2023</t>
+  </si>
+  <si>
+    <t>DIANA ABIGAIL SANCHEZ CARRASCO</t>
+  </si>
+  <si>
+    <t>COMEDOR Y ENTRADA</t>
+  </si>
+  <si>
+    <t>19.04536865683799, -98.1211494223927</t>
+  </si>
+  <si>
+    <t>LOCAL</t>
+  </si>
+  <si>
+    <t>CAMPO REAL</t>
+  </si>
+  <si>
+    <t>KARLA MORALES MEZA</t>
+  </si>
+  <si>
+    <t>ADRIANA LIMON GARCIA</t>
   </si>
 </sst>
 </file>
@@ -7989,7 +8091,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="26" fmlaLink="$A$1" max="30000" min="1" page="10" val="65"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="26" fmlaLink="$A$1" max="30000" min="1" page="10" val="66"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8385,7 +8487,7 @@
   <sheetData>
     <row r="1" spans="1:322" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="DS1" t="s">
         <v>1968</v>
@@ -31620,7 +31722,7 @@
         <v>454</v>
       </c>
       <c r="FT55">
-        <f t="shared" ref="FT55:FT68" si="25">60*AG55</f>
+        <f t="shared" ref="FT55:FT74" si="25">60*AG55</f>
         <v>4200</v>
       </c>
       <c r="FU55" s="4">
@@ -35415,6 +35517,10 @@
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
+      <c r="FT69">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="FU69" s="4">
         <f t="shared" si="23"/>
         <v>0</v>
@@ -35464,6 +35570,10 @@
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
+      <c r="FT70">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="FU70" s="4">
         <f t="shared" si="23"/>
         <v>0</v>
@@ -35513,6 +35623,10 @@
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
+      <c r="FT71">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="FU71" s="4">
         <f t="shared" si="23"/>
         <v>0</v>
@@ -35562,6 +35676,10 @@
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
+      <c r="FT72">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="FU72" s="4">
         <f t="shared" si="23"/>
         <v>0</v>
@@ -35582,33 +35700,232 @@
       <c r="B73" t="s">
         <v>550</v>
       </c>
+      <c r="C73" t="s">
+        <v>2268</v>
+      </c>
+      <c r="D73" t="s">
+        <v>2269</v>
+      </c>
+      <c r="E73" t="s">
+        <v>2270</v>
+      </c>
+      <c r="G73" t="s">
+        <v>2271</v>
+      </c>
+      <c r="H73" t="s">
+        <v>2288</v>
+      </c>
+      <c r="I73" t="s">
+        <v>2272</v>
+      </c>
+      <c r="J73">
+        <v>107</v>
+      </c>
+      <c r="K73" t="s">
+        <v>2273</v>
+      </c>
+      <c r="L73" t="s">
+        <v>421</v>
+      </c>
+      <c r="M73" t="s">
+        <v>2274</v>
+      </c>
+      <c r="N73" t="s">
+        <v>423</v>
+      </c>
+      <c r="O73">
+        <v>72980</v>
+      </c>
+      <c r="P73">
+        <v>2241240669</v>
+      </c>
+      <c r="Q73" s="3" t="s">
+        <v>2275</v>
+      </c>
+      <c r="S73" t="s">
+        <v>2276</v>
+      </c>
+      <c r="T73" t="s">
+        <v>2229</v>
+      </c>
+      <c r="V73">
+        <v>50</v>
+      </c>
+      <c r="W73">
+        <v>50</v>
+      </c>
+      <c r="X73">
+        <v>1</v>
+      </c>
+      <c r="Y73">
+        <v>1</v>
+      </c>
+      <c r="Z73">
+        <v>1</v>
+      </c>
+      <c r="AA73">
+        <v>1</v>
+      </c>
+      <c r="AB73">
+        <v>0</v>
+      </c>
+      <c r="AC73">
+        <v>0</v>
+      </c>
+      <c r="AD73" t="s">
+        <v>2277</v>
+      </c>
+      <c r="AE73" t="s">
+        <v>2278</v>
+      </c>
+      <c r="AF73" t="s">
+        <v>2279</v>
+      </c>
+      <c r="AG73">
+        <v>2</v>
+      </c>
+      <c r="AH73">
+        <v>0</v>
+      </c>
+      <c r="AI73">
+        <v>1</v>
+      </c>
+      <c r="AJ73">
+        <v>1</v>
+      </c>
+      <c r="AK73">
+        <v>0</v>
+      </c>
+      <c r="AL73">
+        <v>0</v>
+      </c>
+      <c r="AM73">
+        <v>1</v>
+      </c>
+      <c r="AN73">
+        <v>20</v>
+      </c>
+      <c r="AO73">
+        <v>1</v>
+      </c>
+      <c r="AP73" t="s">
+        <v>2280</v>
+      </c>
+      <c r="AQ73" t="s">
+        <v>2281</v>
+      </c>
       <c r="AR73" s="4">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="AS73">
+        <v>1</v>
+      </c>
+      <c r="AT73" t="s">
+        <v>2113</v>
+      </c>
+      <c r="AU73">
+        <v>2</v>
+      </c>
+      <c r="AV73" t="s">
+        <v>2113</v>
+      </c>
+      <c r="AW73">
+        <v>2</v>
+      </c>
+      <c r="BE73">
+        <v>1</v>
+      </c>
+      <c r="BF73" t="s">
+        <v>2282</v>
+      </c>
+      <c r="BI73" t="s">
+        <v>2227</v>
+      </c>
+      <c r="CD73">
+        <v>2</v>
+      </c>
+      <c r="CJ73">
+        <v>1</v>
       </c>
       <c r="CK73" s="4">
         <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="CL73">
+        <v>1</v>
+      </c>
+      <c r="CM73">
+        <v>1</v>
+      </c>
+      <c r="DW73">
+        <v>3</v>
+      </c>
+      <c r="DX73" t="s">
+        <v>2283</v>
+      </c>
+      <c r="DY73">
+        <v>2024</v>
+      </c>
+      <c r="DZ73" t="s">
+        <v>2284</v>
+      </c>
+      <c r="EA73" t="s">
+        <v>2285</v>
+      </c>
+      <c r="EB73" t="s">
+        <v>2286</v>
+      </c>
+      <c r="EC73" t="s">
+        <v>2285</v>
+      </c>
+      <c r="ED73" t="s">
+        <v>439</v>
+      </c>
+      <c r="EF73" t="s">
+        <v>441</v>
+      </c>
+      <c r="EG73" t="s">
+        <v>442</v>
+      </c>
+      <c r="EI73" s="11" t="s">
+        <v>2287</v>
+      </c>
+      <c r="FK73">
         <v>0</v>
       </c>
       <c r="FL73" s="4">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
+      <c r="FN73">
+        <v>0</v>
+      </c>
       <c r="FO73" s="4">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
+      <c r="FQ73">
+        <v>0</v>
+      </c>
       <c r="FR73" s="4">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
+      <c r="FS73" t="s">
+        <v>454</v>
+      </c>
+      <c r="FT73">
+        <f t="shared" si="25"/>
+        <v>120</v>
+      </c>
       <c r="FU73" s="4">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="FV73" s="4">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="FW73" s="4" t="str">
         <f t="shared" si="27"/>
@@ -35622,33 +35939,241 @@
       <c r="B74" t="s">
         <v>550</v>
       </c>
+      <c r="C74" t="s">
+        <v>2268</v>
+      </c>
+      <c r="D74" t="s">
+        <v>2269</v>
+      </c>
+      <c r="E74" t="s">
+        <v>2270</v>
+      </c>
+      <c r="G74" t="s">
+        <v>2271</v>
+      </c>
+      <c r="H74" t="s">
+        <v>2288</v>
+      </c>
+      <c r="I74" t="s">
+        <v>2289</v>
+      </c>
+      <c r="J74" t="s">
+        <v>2290</v>
+      </c>
+      <c r="K74" t="s">
+        <v>2291</v>
+      </c>
+      <c r="L74" t="s">
+        <v>2292</v>
+      </c>
+      <c r="M74" t="s">
+        <v>2274</v>
+      </c>
+      <c r="N74" t="s">
+        <v>423</v>
+      </c>
+      <c r="O74">
+        <v>72995</v>
+      </c>
+      <c r="P74">
+        <v>2241240669</v>
+      </c>
+      <c r="Q74" s="3" t="s">
+        <v>2293</v>
+      </c>
+      <c r="S74" t="s">
+        <v>2294</v>
+      </c>
+      <c r="T74" t="s">
+        <v>2229</v>
+      </c>
+      <c r="V74">
+        <v>82</v>
+      </c>
+      <c r="W74">
+        <v>82</v>
+      </c>
+      <c r="X74">
+        <v>1</v>
+      </c>
+      <c r="Y74">
+        <v>1</v>
+      </c>
+      <c r="Z74">
+        <v>1</v>
+      </c>
+      <c r="AA74">
+        <v>1</v>
+      </c>
+      <c r="AB74">
+        <v>0</v>
+      </c>
+      <c r="AC74">
+        <v>0</v>
+      </c>
+      <c r="AD74" t="s">
+        <v>462</v>
+      </c>
+      <c r="AE74" t="s">
+        <v>2278</v>
+      </c>
+      <c r="AF74" t="s">
+        <v>2295</v>
+      </c>
+      <c r="AG74">
+        <v>3</v>
+      </c>
+      <c r="AH74">
+        <v>0</v>
+      </c>
+      <c r="AI74">
+        <v>0</v>
+      </c>
+      <c r="AJ74">
+        <v>3</v>
+      </c>
+      <c r="AK74">
+        <v>0</v>
+      </c>
+      <c r="AL74">
+        <v>0</v>
+      </c>
+      <c r="AM74">
+        <v>1</v>
+      </c>
+      <c r="AN74">
+        <v>100</v>
+      </c>
+      <c r="AO74">
+        <v>1</v>
+      </c>
+      <c r="AP74" t="s">
+        <v>2280</v>
+      </c>
+      <c r="AQ74" t="s">
+        <v>2281</v>
+      </c>
       <c r="AR74" s="4">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="AS74">
+        <v>1</v>
+      </c>
+      <c r="AT74" t="s">
+        <v>431</v>
+      </c>
+      <c r="AU74">
+        <v>2</v>
+      </c>
+      <c r="AV74" t="s">
+        <v>2296</v>
+      </c>
+      <c r="AW74">
+        <v>2</v>
+      </c>
+      <c r="BE74">
+        <v>1</v>
+      </c>
+      <c r="BF74" t="s">
+        <v>2282</v>
+      </c>
+      <c r="BI74" t="s">
+        <v>2227</v>
+      </c>
+      <c r="CD74">
+        <v>3</v>
+      </c>
+      <c r="CF74">
+        <v>1</v>
+      </c>
+      <c r="CI74">
+        <v>1</v>
+      </c>
+      <c r="CJ74">
+        <v>2</v>
       </c>
       <c r="CK74" s="4">
         <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="CL74">
+        <v>1</v>
+      </c>
+      <c r="CM74">
+        <v>2</v>
+      </c>
+      <c r="DW74">
+        <v>3</v>
+      </c>
+      <c r="DX74" t="s">
+        <v>2283</v>
+      </c>
+      <c r="DY74">
+        <v>2024</v>
+      </c>
+      <c r="DZ74" t="s">
+        <v>2297</v>
+      </c>
+      <c r="EA74" t="s">
+        <v>2298</v>
+      </c>
+      <c r="EB74" t="s">
+        <v>2298</v>
+      </c>
+      <c r="EC74" t="s">
+        <v>1793</v>
+      </c>
+      <c r="ED74" t="s">
+        <v>2299</v>
+      </c>
+      <c r="EF74" t="s">
+        <v>441</v>
+      </c>
+      <c r="EG74" t="s">
+        <v>442</v>
+      </c>
+      <c r="EI74" s="11" t="s">
+        <v>2300</v>
+      </c>
+      <c r="EL74" s="11" t="s">
+        <v>2301</v>
+      </c>
+      <c r="FK74">
         <v>0</v>
       </c>
       <c r="FL74" s="4">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
+      <c r="FN74">
+        <v>0</v>
+      </c>
       <c r="FO74" s="4">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
+      <c r="FQ74">
+        <v>0</v>
+      </c>
       <c r="FR74" s="4">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
+      <c r="FS74" t="s">
+        <v>454</v>
+      </c>
+      <c r="FT74">
+        <f t="shared" si="25"/>
+        <v>180</v>
+      </c>
       <c r="FU74" s="4">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>1.2E-2</v>
       </c>
       <c r="FV74" s="4">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1.2E-2</v>
       </c>
       <c r="FW74" s="4" t="str">
         <f t="shared" si="27"/>
@@ -40260,7 +40785,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A3:FV13 FX3:GC43 B14:G14 I14:FV14 KD14:LJ42 A14:A201 D15:FV58 B15:C68 GL43:GW43 GY43:HA43 HC43:HD43 HF43 HK43 HP43:HR43 IC43 IE43 IH43:IJ43 IL43 FX44:IM60 EM59:FV60 D59:EL62 EM61:IM62 D63:IM201 B69 B70:C201 A202:IM208">
+  <conditionalFormatting sqref="A3:FV13 FX3:GC43 B14:G14 I14:FV14 KD14:LJ42 A14:A201 D15:FV58 B15:C68 GL43:GW43 GY43:HA43 HC43:HD43 HF43 HK43 HP43:HR43 IC43 IE43 IH43:IJ43 IL43 FX44:IM60 EM59:FV60 D59:EL62 EM61:IM62 D63:IM73 B69 B70:C73 B74:IM201 A202:IM208">
     <cfRule type="expression" dxfId="40" priority="581">
       <formula>$A3=$A$1</formula>
     </cfRule>
@@ -40513,16 +41038,18 @@
     <hyperlink ref="Q66" r:id="rId40" xr:uid="{19D5C0DF-B072-400B-A9E9-5EBBA974FB88}"/>
     <hyperlink ref="Q67" r:id="rId41" xr:uid="{A7FC72C6-B0DB-4FC9-B190-B58CFCCCC457}"/>
     <hyperlink ref="Q68" r:id="rId42" xr:uid="{07B79AC2-D0BB-4053-B52A-2218F9C8D957}"/>
+    <hyperlink ref="Q73" r:id="rId43" xr:uid="{AC530E9D-142F-47C1-9FA2-9326C9E7E289}"/>
+    <hyperlink ref="Q74" r:id="rId44" xr:uid="{3666EBA2-130E-4794-96A0-D6F6C3ACD1EE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId43"/>
-  <legacyDrawing r:id="rId44"/>
+  <drawing r:id="rId45"/>
+  <legacyDrawing r:id="rId46"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x14">
       <controls>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1025" r:id="rId45" name="Spinner 1">
+            <control shapeId="1025" r:id="rId47" name="Spinner 1">
               <controlPr defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
@@ -40556,7 +41083,7 @@
     <row r="1" spans="1:310" x14ac:dyDescent="0.3">
       <c r="A1">
         <f>+BD!A1</f>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B1" t="s">
         <v>133</v>
@@ -41497,7 +42024,7 @@
       </c>
       <c r="D2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,4, FALSE)</f>
-        <v>DHL PBC BUGAMBILIAS</v>
+        <v>DHL PBC GUADALUPE HIDALGO</v>
       </c>
       <c r="E2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,5, FALSE)</f>
@@ -41517,19 +42044,19 @@
       </c>
       <c r="I2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,9, FALSE)</f>
-        <v>PROLONGACION 16 DE SEPTIEMBRE</v>
+        <v>11 SUR</v>
       </c>
       <c r="J2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,10, FALSE)</f>
-        <v>6348</v>
+        <v>12923</v>
       </c>
       <c r="K2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,11, FALSE)</f>
-        <v>LOCAL C</v>
+        <v>LOCAL 1</v>
       </c>
       <c r="L2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,12, FALSE)</f>
-        <v>VISTA HERMOSA</v>
+        <v>SAN ISIDRO CASTILLOTLA</v>
       </c>
       <c r="M2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,13, FALSE)</f>
@@ -41541,23 +42068,23 @@
       </c>
       <c r="O2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,15, FALSE)</f>
-        <v>72470</v>
+        <v>72498</v>
       </c>
       <c r="P2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,16, FALSE)</f>
-        <v>2221938507</v>
+        <v>2223234754</v>
       </c>
       <c r="Q2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,17, FALSE)</f>
-        <v>servicepoint.bam@dhl.com</v>
+        <v>servicepoint.ghi@dhl.com</v>
       </c>
       <c r="R2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,18, FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="S2">
+        <v>10</v>
+      </c>
+      <c r="S2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,19, FALSE)</f>
-        <v>2018</v>
+        <v>1 DE NOVIEMBRE DE 2014</v>
       </c>
       <c r="T2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,20, FALSE)</f>
@@ -41569,11 +42096,11 @@
       </c>
       <c r="V2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,22, FALSE)</f>
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="W2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,23, FALSE)</f>
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="X2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,24, FALSE)</f>
@@ -41601,7 +42128,7 @@
       </c>
       <c r="AD2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,30, FALSE)</f>
-        <v>3 CAJONES</v>
+        <v>4 CAJONES</v>
       </c>
       <c r="AE2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,31, FALSE)</f>
@@ -41609,7 +42136,7 @@
       </c>
       <c r="AF2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,32, FALSE)</f>
-        <v>JULIO OMAR SERRANO GUERRERO</v>
+        <v>MARIA DE LA PAZ CORDERO R</v>
       </c>
       <c r="AG2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,33, FALSE)</f>
@@ -41621,11 +42148,11 @@
       </c>
       <c r="AI2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,35, FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,36, FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,37, FALSE)</f>
@@ -41641,7 +42168,7 @@
       </c>
       <c r="AN2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,40, FALSE)</f>
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AO2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,41, FALSE)</f>
@@ -41657,7 +42184,7 @@
       </c>
       <c r="AR2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,44, FALSE)</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AS2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,45, FALSE)</f>
@@ -41809,7 +42336,7 @@
       </c>
       <c r="CD2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,82, FALSE)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CE2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,83, FALSE)</f>
@@ -41829,7 +42356,7 @@
       </c>
       <c r="CI2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,87, FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CJ2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,88, FALSE)</f>
@@ -41921,7 +42448,7 @@
       </c>
       <c r="DF2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,110, FALSE)</f>
-        <v>AREA INTERNA Y AREA EXTERNA</v>
+        <v>AREA INTERNA</v>
       </c>
       <c r="DG2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,111, FALSE)</f>
@@ -42001,23 +42528,23 @@
       </c>
       <c r="DZ2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,130, FALSE)</f>
-        <v>19.005951538063638, -98.21983914958865</v>
+        <v>18.980469690072912, -98.25416721650755</v>
       </c>
       <c r="EA2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,131, FALSE)</f>
-        <v>EBANO</v>
+        <v>PRIVADA DE LOS NARANJOS</v>
       </c>
       <c r="EB2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,132, FALSE)</f>
-        <v>CIPRES</v>
+        <v>DE LA ROSA</v>
       </c>
       <c r="EC2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,133, FALSE)</f>
-        <v>VISTA HERMOSA</v>
+        <v>ACC. PRINCIPAL 11 SUR</v>
       </c>
       <c r="ED2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,134, FALSE)</f>
-        <v>LIRIOS</v>
+        <v>CALLE FAROLES</v>
       </c>
       <c r="EE2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,135, FALSE)</f>

--- a/Inputs/BD.xlsx
+++ b/Inputs/BD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/078e1a455e5c02ce/Documentos/GitHub/Proyecto_PIPC/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="544" documentId="13_ncr:1_{898522BF-B0F8-4888-9748-DC730D5D6CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBD41185-BEC0-48F2-BCE0-29EF60BE5DF0}"/>
+  <xr:revisionPtr revIDLastSave="629" documentId="13_ncr:1_{898522BF-B0F8-4888-9748-DC730D5D6CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0EC7853-F432-4F17-9836-8E6DA938593D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3F095A75-F066-4695-8672-8D4315F1EF23}"/>
   </bookViews>
@@ -563,7 +563,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7507" uniqueCount="2302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7543" uniqueCount="2314">
   <si>
     <t>dia</t>
   </si>
@@ -7469,6 +7469,42 @@
   </si>
   <si>
     <t>ADRIANA LIMON GARCIA</t>
+  </si>
+  <si>
+    <t>COMERCIO AL POR MENOR DE ARTICULOS DE PERFUMERIA Y COSMETICOS</t>
+  </si>
+  <si>
+    <t>7 NORTE</t>
+  </si>
+  <si>
+    <t>LOCAL 5</t>
+  </si>
+  <si>
+    <t>f516.chedrahuitehuacan@pue.fraiche.mx</t>
+  </si>
+  <si>
+    <t>01 DE JUNIO DEE 2024</t>
+  </si>
+  <si>
+    <t>FRAICHE CHEDRAUI</t>
+  </si>
+  <si>
+    <t>MAYRA LIZBET ANGEL PEREZ</t>
+  </si>
+  <si>
+    <t>10:00 A 20:00 HORAS</t>
+  </si>
+  <si>
+    <t>AREA INTERNA Y ENTRADA</t>
+  </si>
+  <si>
+    <t>18.4637150494009, -97.38691843244746</t>
+  </si>
+  <si>
+    <t>CHEDRAUI</t>
+  </si>
+  <si>
+    <t>ESENCIA Y PERFUMON</t>
   </si>
 </sst>
 </file>
@@ -8091,7 +8127,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="26" fmlaLink="$A$1" max="30000" min="1" page="10" val="66"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="26" fmlaLink="$A$1" max="30000" min="1" page="10" val="76"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8487,7 +8523,7 @@
   <sheetData>
     <row r="1" spans="1:322" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="DS1" t="s">
         <v>1968</v>
@@ -36184,6 +36220,9 @@
       <c r="A75">
         <v>73</v>
       </c>
+      <c r="B75" t="s">
+        <v>2219</v>
+      </c>
       <c r="AR75" s="4">
         <f t="shared" si="28"/>
         <v>0</v>
@@ -36221,6 +36260,9 @@
       <c r="A76">
         <v>74</v>
       </c>
+      <c r="B76" t="s">
+        <v>2219</v>
+      </c>
       <c r="AR76" s="4">
         <f t="shared" si="28"/>
         <v>0</v>
@@ -36258,6 +36300,9 @@
       <c r="A77">
         <v>75</v>
       </c>
+      <c r="B77" t="s">
+        <v>2219</v>
+      </c>
       <c r="AR77" s="4">
         <f t="shared" si="28"/>
         <v>0</v>
@@ -36295,33 +36340,244 @@
       <c r="A78">
         <v>76</v>
       </c>
+      <c r="B78" t="s">
+        <v>550</v>
+      </c>
+      <c r="C78" t="s">
+        <v>1942</v>
+      </c>
+      <c r="D78" t="s">
+        <v>2307</v>
+      </c>
+      <c r="E78" t="s">
+        <v>1944</v>
+      </c>
+      <c r="G78" t="s">
+        <v>2302</v>
+      </c>
+      <c r="H78" t="s">
+        <v>1966</v>
+      </c>
+      <c r="I78" t="s">
+        <v>2303</v>
+      </c>
+      <c r="J78">
+        <v>107</v>
+      </c>
+      <c r="K78" t="s">
+        <v>2304</v>
+      </c>
+      <c r="L78" t="s">
+        <v>421</v>
+      </c>
+      <c r="M78" t="s">
+        <v>1928</v>
+      </c>
+      <c r="N78" t="s">
+        <v>423</v>
+      </c>
+      <c r="O78">
+        <v>75700</v>
+      </c>
+      <c r="P78">
+        <v>2383806932</v>
+      </c>
+      <c r="Q78" s="3" t="s">
+        <v>2305</v>
+      </c>
+      <c r="S78" t="s">
+        <v>2306</v>
+      </c>
+      <c r="T78" t="s">
+        <v>2229</v>
+      </c>
+      <c r="V78">
+        <v>25</v>
+      </c>
+      <c r="W78">
+        <v>40</v>
+      </c>
+      <c r="X78">
+        <v>1</v>
+      </c>
+      <c r="Y78">
+        <v>2</v>
+      </c>
+      <c r="Z78">
+        <v>1</v>
+      </c>
+      <c r="AA78">
+        <v>1</v>
+      </c>
+      <c r="AB78">
+        <v>1</v>
+      </c>
+      <c r="AC78">
+        <v>0</v>
+      </c>
+      <c r="AD78" t="s">
+        <v>462</v>
+      </c>
+      <c r="AE78" t="s">
+        <v>1949</v>
+      </c>
+      <c r="AF78" t="s">
+        <v>2308</v>
+      </c>
+      <c r="AG78">
+        <v>2</v>
+      </c>
+      <c r="AH78">
+        <v>0</v>
+      </c>
+      <c r="AI78">
+        <v>1</v>
+      </c>
+      <c r="AJ78">
+        <v>1</v>
+      </c>
+      <c r="AK78">
+        <v>0</v>
+      </c>
+      <c r="AL78">
+        <v>0</v>
+      </c>
+      <c r="AM78">
+        <v>1</v>
+      </c>
+      <c r="AN78">
+        <v>20</v>
+      </c>
+      <c r="AO78">
+        <v>2</v>
+      </c>
+      <c r="AP78" t="s">
+        <v>2280</v>
+      </c>
+      <c r="AQ78" t="s">
+        <v>2309</v>
+      </c>
       <c r="AR78" s="4">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="AS78">
+        <v>1</v>
+      </c>
+      <c r="AT78" t="s">
+        <v>431</v>
+      </c>
+      <c r="AU78">
+        <v>2</v>
+      </c>
+      <c r="AV78" t="s">
+        <v>2310</v>
+      </c>
+      <c r="AW78">
+        <v>2</v>
+      </c>
+      <c r="BJ78">
+        <v>2</v>
+      </c>
+      <c r="BK78">
+        <v>1</v>
+      </c>
+      <c r="BL78">
+        <v>3</v>
+      </c>
+      <c r="BM78" t="s">
+        <v>855</v>
+      </c>
+      <c r="CD78">
+        <v>4</v>
+      </c>
+      <c r="CF78">
+        <v>1</v>
+      </c>
+      <c r="CI78">
+        <v>1</v>
+      </c>
+      <c r="CJ78">
+        <v>1</v>
       </c>
       <c r="CK78" s="4">
         <f t="shared" ref="CK78:CK109" si="29">+CL78+CN78+CO78+CP78+CQ78</f>
+        <v>1</v>
+      </c>
+      <c r="CL78">
+        <v>1</v>
+      </c>
+      <c r="DW78">
+        <v>14</v>
+      </c>
+      <c r="DX78" t="s">
+        <v>2283</v>
+      </c>
+      <c r="DY78">
+        <v>2024</v>
+      </c>
+      <c r="DZ78" t="s">
+        <v>2311</v>
+      </c>
+      <c r="EA78" t="s">
+        <v>2298</v>
+      </c>
+      <c r="EB78" t="s">
+        <v>2298</v>
+      </c>
+      <c r="EC78" t="s">
+        <v>2312</v>
+      </c>
+      <c r="ED78" t="s">
+        <v>1793</v>
+      </c>
+      <c r="EF78" t="s">
+        <v>441</v>
+      </c>
+      <c r="EG78" t="s">
+        <v>442</v>
+      </c>
+      <c r="EI78" s="11" t="s">
+        <v>1961</v>
+      </c>
+      <c r="FK78">
         <v>0</v>
       </c>
       <c r="FL78" s="4">
         <f t="shared" ref="FL78:FL109" si="30">+FK78/3000</f>
         <v>0</v>
       </c>
+      <c r="FM78" t="s">
+        <v>2313</v>
+      </c>
+      <c r="FN78">
+        <v>101</v>
+      </c>
       <c r="FO78" s="4">
         <f t="shared" ref="FO78:FO109" si="31">+FN78/1400</f>
+        <v>7.2142857142857147E-2</v>
+      </c>
+      <c r="FQ78">
         <v>0</v>
       </c>
       <c r="FR78" s="4">
         <f t="shared" ref="FR78:FR109" si="32">+FQ78/2000</f>
         <v>0</v>
       </c>
+      <c r="FS78" t="s">
+        <v>454</v>
+      </c>
+      <c r="FT78">
+        <f t="shared" ref="FT78" si="33">60*AG78</f>
+        <v>120</v>
+      </c>
       <c r="FU78" s="4">
-        <f t="shared" ref="FU78:FU109" si="33">+FT78/15000</f>
-        <v>0</v>
+        <f t="shared" ref="FU78:FU109" si="34">+FT78/15000</f>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="FV78" s="4">
-        <f t="shared" ref="FV78:FV109" si="34">+FL78+FO78+FR78+FU78</f>
-        <v>0</v>
+        <f t="shared" ref="FV78:FV109" si="35">+FL78+FO78+FR78+FU78</f>
+        <v>8.0142857142857155E-2</v>
       </c>
       <c r="FW78" s="4" t="str">
         <f t="shared" si="27"/>
@@ -36353,11 +36609,11 @@
         <v>0</v>
       </c>
       <c r="FU79" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FV79" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FW79" s="4" t="str">
@@ -36390,11 +36646,11 @@
         <v>0</v>
       </c>
       <c r="FU80" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FV80" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FW80" s="4" t="str">
@@ -36427,11 +36683,11 @@
         <v>0</v>
       </c>
       <c r="FU81" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FV81" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FW81" s="4" t="str">
@@ -36464,11 +36720,11 @@
         <v>0</v>
       </c>
       <c r="FU82" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FV82" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FW82" s="4" t="str">
@@ -36501,11 +36757,11 @@
         <v>0</v>
       </c>
       <c r="FU83" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FV83" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FW83" s="4" t="str">
@@ -36538,11 +36794,11 @@
         <v>0</v>
       </c>
       <c r="FU84" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FV84" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FW84" s="4" t="str">
@@ -36575,11 +36831,11 @@
         <v>0</v>
       </c>
       <c r="FU85" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FV85" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FW85" s="4" t="str">
@@ -36612,11 +36868,11 @@
         <v>0</v>
       </c>
       <c r="FU86" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FV86" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FW86" s="4" t="str">
@@ -36649,11 +36905,11 @@
         <v>0</v>
       </c>
       <c r="FU87" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FV87" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FW87" s="4" t="str">
@@ -36686,11 +36942,11 @@
         <v>0</v>
       </c>
       <c r="FU88" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FV88" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FW88" s="4" t="str">
@@ -36723,11 +36979,11 @@
         <v>0</v>
       </c>
       <c r="FU89" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FV89" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FW89" s="4" t="str">
@@ -36760,11 +37016,11 @@
         <v>0</v>
       </c>
       <c r="FU90" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FV90" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FW90" s="4" t="str">
@@ -36797,11 +37053,11 @@
         <v>0</v>
       </c>
       <c r="FU91" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FV91" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FW91" s="4" t="str">
@@ -36834,11 +37090,11 @@
         <v>0</v>
       </c>
       <c r="FU92" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FV92" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FW92" s="4" t="str">
@@ -36871,11 +37127,11 @@
         <v>0</v>
       </c>
       <c r="FU93" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FV93" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FW93" s="4" t="str">
@@ -36908,11 +37164,11 @@
         <v>0</v>
       </c>
       <c r="FU94" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FV94" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FW94" s="4" t="str">
@@ -36945,11 +37201,11 @@
         <v>0</v>
       </c>
       <c r="FU95" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FV95" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FW95" s="4" t="str">
@@ -36982,11 +37238,11 @@
         <v>0</v>
       </c>
       <c r="FU96" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FV96" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FW96" s="4" t="str">
@@ -37019,11 +37275,11 @@
         <v>0</v>
       </c>
       <c r="FU97" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FV97" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FW97" s="4" t="str">
@@ -37056,11 +37312,11 @@
         <v>0</v>
       </c>
       <c r="FU98" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FV98" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FW98" s="4" t="str">
@@ -37073,7 +37329,7 @@
         <v>97</v>
       </c>
       <c r="AR99" s="4">
-        <f t="shared" ref="AR99:AR130" si="35">+AS99+AU99+BE99+CD99+CE99+CF99+CG99+CH99+CI99+CW99</f>
+        <f t="shared" ref="AR99:AR130" si="36">+AS99+AU99+BE99+CD99+CE99+CF99+CG99+CH99+CI99+CW99</f>
         <v>0</v>
       </c>
       <c r="CK99" s="4">
@@ -37093,11 +37349,11 @@
         <v>0</v>
       </c>
       <c r="FU99" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FV99" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FW99" s="4" t="str">
@@ -37110,7 +37366,7 @@
         <v>98</v>
       </c>
       <c r="AR100" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="CK100" s="4">
@@ -37130,11 +37386,11 @@
         <v>0</v>
       </c>
       <c r="FU100" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FV100" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FW100" s="4" t="str">
@@ -37147,7 +37403,7 @@
         <v>99</v>
       </c>
       <c r="AR101" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="CK101" s="4">
@@ -37167,11 +37423,11 @@
         <v>0</v>
       </c>
       <c r="FU101" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FV101" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FW101" s="4" t="str">
@@ -37184,7 +37440,7 @@
         <v>100</v>
       </c>
       <c r="AR102" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="CK102" s="4">
@@ -37204,11 +37460,11 @@
         <v>0</v>
       </c>
       <c r="FU102" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FV102" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FW102" s="4" t="str">
@@ -37221,7 +37477,7 @@
         <v>101</v>
       </c>
       <c r="AR103" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="CK103" s="4">
@@ -37241,11 +37497,11 @@
         <v>0</v>
       </c>
       <c r="FU103" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FV103" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FW103" s="4" t="str">
@@ -37258,7 +37514,7 @@
         <v>102</v>
       </c>
       <c r="AR104" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="CK104" s="4">
@@ -37278,11 +37534,11 @@
         <v>0</v>
       </c>
       <c r="FU104" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FV104" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FW104" s="4" t="str">
@@ -37295,7 +37551,7 @@
         <v>103</v>
       </c>
       <c r="AR105" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="CK105" s="4">
@@ -37315,11 +37571,11 @@
         <v>0</v>
       </c>
       <c r="FU105" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FV105" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FW105" s="4" t="str">
@@ -37332,7 +37588,7 @@
         <v>104</v>
       </c>
       <c r="AR106" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="CK106" s="4">
@@ -37352,11 +37608,11 @@
         <v>0</v>
       </c>
       <c r="FU106" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FV106" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FW106" s="4" t="str">
@@ -37369,7 +37625,7 @@
         <v>105</v>
       </c>
       <c r="AR107" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="CK107" s="4">
@@ -37389,11 +37645,11 @@
         <v>0</v>
       </c>
       <c r="FU107" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FV107" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FW107" s="4" t="str">
@@ -37406,7 +37662,7 @@
         <v>106</v>
       </c>
       <c r="AR108" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="CK108" s="4">
@@ -37426,11 +37682,11 @@
         <v>0</v>
       </c>
       <c r="FU108" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FV108" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FW108" s="4" t="str">
@@ -37443,7 +37699,7 @@
         <v>107</v>
       </c>
       <c r="AR109" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="CK109" s="4">
@@ -37463,11 +37719,11 @@
         <v>0</v>
       </c>
       <c r="FU109" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="FV109" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="FW109" s="4" t="str">
@@ -37480,31 +37736,31 @@
         <v>108</v>
       </c>
       <c r="AR110" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="CK110" s="4">
-        <f t="shared" ref="CK110:CK141" si="36">+CL110+CN110+CO110+CP110+CQ110</f>
+        <f t="shared" ref="CK110:CK141" si="37">+CL110+CN110+CO110+CP110+CQ110</f>
         <v>0</v>
       </c>
       <c r="FL110" s="4">
-        <f t="shared" ref="FL110:FL141" si="37">+FK110/3000</f>
+        <f t="shared" ref="FL110:FL141" si="38">+FK110/3000</f>
         <v>0</v>
       </c>
       <c r="FO110" s="4">
-        <f t="shared" ref="FO110:FO141" si="38">+FN110/1400</f>
+        <f t="shared" ref="FO110:FO141" si="39">+FN110/1400</f>
         <v>0</v>
       </c>
       <c r="FR110" s="4">
-        <f t="shared" ref="FR110:FR141" si="39">+FQ110/2000</f>
+        <f t="shared" ref="FR110:FR141" si="40">+FQ110/2000</f>
         <v>0</v>
       </c>
       <c r="FU110" s="4">
-        <f t="shared" ref="FU110:FU141" si="40">+FT110/15000</f>
+        <f t="shared" ref="FU110:FU141" si="41">+FT110/15000</f>
         <v>0</v>
       </c>
       <c r="FV110" s="4">
-        <f t="shared" ref="FV110:FV141" si="41">+FL110+FO110+FR110+FU110</f>
+        <f t="shared" ref="FV110:FV141" si="42">+FL110+FO110+FR110+FU110</f>
         <v>0</v>
       </c>
       <c r="FW110" s="4" t="str">
@@ -37517,31 +37773,31 @@
         <v>109</v>
       </c>
       <c r="AR111" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="CK111" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FL111" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="FO111" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="FR111" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FU111" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FV111" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FW111" s="4" t="str">
@@ -37554,31 +37810,31 @@
         <v>110</v>
       </c>
       <c r="AR112" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="CK112" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FL112" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="FO112" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="FR112" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FU112" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FV112" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FW112" s="4" t="str">
@@ -37591,31 +37847,31 @@
         <v>111</v>
       </c>
       <c r="AR113" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="CK113" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FL113" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="FO113" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="FR113" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FU113" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FV113" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FW113" s="4" t="str">
@@ -37628,31 +37884,31 @@
         <v>112</v>
       </c>
       <c r="AR114" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="CK114" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FL114" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="FO114" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="FR114" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FU114" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FV114" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FW114" s="4" t="str">
@@ -37665,31 +37921,31 @@
         <v>113</v>
       </c>
       <c r="AR115" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="CK115" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FL115" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="FO115" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="FR115" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FU115" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FV115" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FW115" s="4" t="str">
@@ -37702,31 +37958,31 @@
         <v>114</v>
       </c>
       <c r="AR116" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="CK116" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FL116" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="FO116" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="FR116" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FU116" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FV116" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FW116" s="4" t="str">
@@ -37739,31 +37995,31 @@
         <v>115</v>
       </c>
       <c r="AR117" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="CK117" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FL117" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="FO117" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="FR117" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FU117" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FV117" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FW117" s="4" t="str">
@@ -37776,31 +38032,31 @@
         <v>116</v>
       </c>
       <c r="AR118" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="CK118" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FL118" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="FO118" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="FR118" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FU118" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FV118" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FW118" s="4" t="str">
@@ -37813,31 +38069,31 @@
         <v>117</v>
       </c>
       <c r="AR119" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="CK119" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FL119" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="FO119" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="FR119" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FU119" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FV119" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FW119" s="4" t="str">
@@ -37850,31 +38106,31 @@
         <v>118</v>
       </c>
       <c r="AR120" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="CK120" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FL120" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="FO120" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="FR120" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FU120" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FV120" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FW120" s="4" t="str">
@@ -37887,31 +38143,31 @@
         <v>119</v>
       </c>
       <c r="AR121" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="CK121" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FL121" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="FO121" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="FR121" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FU121" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FV121" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FW121" s="4" t="str">
@@ -37924,31 +38180,31 @@
         <v>120</v>
       </c>
       <c r="AR122" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="CK122" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FL122" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="FO122" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="FR122" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FU122" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FV122" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FW122" s="4" t="str">
@@ -37961,31 +38217,31 @@
         <v>121</v>
       </c>
       <c r="AR123" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="CK123" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FL123" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="FO123" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="FR123" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FU123" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FV123" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FW123" s="4" t="str">
@@ -37998,31 +38254,31 @@
         <v>122</v>
       </c>
       <c r="AR124" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="CK124" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FL124" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="FO124" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="FR124" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FU124" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FV124" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FW124" s="4" t="str">
@@ -38035,31 +38291,31 @@
         <v>123</v>
       </c>
       <c r="AR125" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="CK125" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FL125" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="FO125" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="FR125" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FU125" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FV125" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FW125" s="4" t="str">
@@ -38072,35 +38328,35 @@
         <v>124</v>
       </c>
       <c r="AR126" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="CK126" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FL126" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="FO126" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="FR126" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FU126" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FV126" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FW126" s="4" t="str">
-        <f t="shared" ref="FW126:FW189" si="42">IF(W126&gt;3000,"ALTO",IF(FV126&gt;=1,"ALTO","ORDINARIO"))</f>
+        <f t="shared" ref="FW126:FW189" si="43">IF(W126&gt;3000,"ALTO",IF(FV126&gt;=1,"ALTO","ORDINARIO"))</f>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -38109,35 +38365,35 @@
         <v>125</v>
       </c>
       <c r="AR127" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="CK127" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FL127" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="FO127" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="FR127" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FU127" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FV127" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FW127" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -38146,35 +38402,35 @@
         <v>126</v>
       </c>
       <c r="AR128" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="CK128" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FL128" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="FO128" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="FR128" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FU128" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FV128" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FW128" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -38183,35 +38439,35 @@
         <v>127</v>
       </c>
       <c r="AR129" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="CK129" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FL129" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="FO129" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="FR129" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FU129" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FV129" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FW129" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -38220,35 +38476,35 @@
         <v>128</v>
       </c>
       <c r="AR130" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="CK130" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FL130" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="FO130" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="FR130" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FU130" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FV130" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FW130" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -38257,35 +38513,35 @@
         <v>129</v>
       </c>
       <c r="AR131" s="4">
-        <f t="shared" ref="AR131:AR162" si="43">+AS131+AU131+BE131+CD131+CE131+CF131+CG131+CH131+CI131+CW131</f>
+        <f t="shared" ref="AR131:AR162" si="44">+AS131+AU131+BE131+CD131+CE131+CF131+CG131+CH131+CI131+CW131</f>
         <v>0</v>
       </c>
       <c r="CK131" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="FL131" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="FO131" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="FR131" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FU131" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FV131" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FW131" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -38294,35 +38550,35 @@
         <v>130</v>
       </c>
       <c r="AR132" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="CK132" s="4">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="FL132" s="4">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="FO132" s="4">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="FR132" s="4">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="FU132" s="4">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="FV132" s="4">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="FW132" s="4" t="str">
         <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="CK132" s="4">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="FL132" s="4">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="FO132" s="4">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="FR132" s="4">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="FU132" s="4">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="FV132" s="4">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="FW132" s="4" t="str">
-        <f t="shared" si="42"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -38331,35 +38587,35 @@
         <v>131</v>
       </c>
       <c r="AR133" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="CK133" s="4">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="FL133" s="4">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="FO133" s="4">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="FR133" s="4">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="FU133" s="4">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="FV133" s="4">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="FW133" s="4" t="str">
         <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="CK133" s="4">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="FL133" s="4">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="FO133" s="4">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="FR133" s="4">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="FU133" s="4">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="FV133" s="4">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="FW133" s="4" t="str">
-        <f t="shared" si="42"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -38368,35 +38624,35 @@
         <v>132</v>
       </c>
       <c r="AR134" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="CK134" s="4">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="FL134" s="4">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="FO134" s="4">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="FR134" s="4">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="FU134" s="4">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="FV134" s="4">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="FW134" s="4" t="str">
         <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="CK134" s="4">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="FL134" s="4">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="FO134" s="4">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="FR134" s="4">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="FU134" s="4">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="FV134" s="4">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="FW134" s="4" t="str">
-        <f t="shared" si="42"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -38405,35 +38661,35 @@
         <v>133</v>
       </c>
       <c r="AR135" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="CK135" s="4">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="FL135" s="4">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="FO135" s="4">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="FR135" s="4">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="FU135" s="4">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="FV135" s="4">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="FW135" s="4" t="str">
         <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="CK135" s="4">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="FL135" s="4">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="FO135" s="4">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="FR135" s="4">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="FU135" s="4">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="FV135" s="4">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="FW135" s="4" t="str">
-        <f t="shared" si="42"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -38442,35 +38698,35 @@
         <v>134</v>
       </c>
       <c r="AR136" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="CK136" s="4">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="FL136" s="4">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="FO136" s="4">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="FR136" s="4">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="FU136" s="4">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="FV136" s="4">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="FW136" s="4" t="str">
         <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="CK136" s="4">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="FL136" s="4">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="FO136" s="4">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="FR136" s="4">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="FU136" s="4">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="FV136" s="4">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="FW136" s="4" t="str">
-        <f t="shared" si="42"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -38479,35 +38735,35 @@
         <v>135</v>
       </c>
       <c r="AR137" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="CK137" s="4">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="FL137" s="4">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="FO137" s="4">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="FR137" s="4">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="FU137" s="4">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="FV137" s="4">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="FW137" s="4" t="str">
         <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="CK137" s="4">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="FL137" s="4">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="FO137" s="4">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="FR137" s="4">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="FU137" s="4">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="FV137" s="4">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="FW137" s="4" t="str">
-        <f t="shared" si="42"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -38516,35 +38772,35 @@
         <v>136</v>
       </c>
       <c r="AR138" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="CK138" s="4">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="FL138" s="4">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="FO138" s="4">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="FR138" s="4">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="FU138" s="4">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="FV138" s="4">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="FW138" s="4" t="str">
         <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="CK138" s="4">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="FL138" s="4">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="FO138" s="4">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="FR138" s="4">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="FU138" s="4">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="FV138" s="4">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="FW138" s="4" t="str">
-        <f t="shared" si="42"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -38553,35 +38809,35 @@
         <v>137</v>
       </c>
       <c r="AR139" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="CK139" s="4">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="FL139" s="4">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="FO139" s="4">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="FR139" s="4">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="FU139" s="4">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="FV139" s="4">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="FW139" s="4" t="str">
         <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="CK139" s="4">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="FL139" s="4">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="FO139" s="4">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="FR139" s="4">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="FU139" s="4">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="FV139" s="4">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="FW139" s="4" t="str">
-        <f t="shared" si="42"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -38590,35 +38846,35 @@
         <v>138</v>
       </c>
       <c r="AR140" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="CK140" s="4">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="FL140" s="4">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="FO140" s="4">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="FR140" s="4">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="FU140" s="4">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="FV140" s="4">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="FW140" s="4" t="str">
         <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="CK140" s="4">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="FL140" s="4">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="FO140" s="4">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="FR140" s="4">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="FU140" s="4">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="FV140" s="4">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="FW140" s="4" t="str">
-        <f t="shared" si="42"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -38627,35 +38883,35 @@
         <v>139</v>
       </c>
       <c r="AR141" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="CK141" s="4">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="FL141" s="4">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="FO141" s="4">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="FR141" s="4">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="FU141" s="4">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="FV141" s="4">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="FW141" s="4" t="str">
         <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="CK141" s="4">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="FL141" s="4">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="FO141" s="4">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="FR141" s="4">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="FU141" s="4">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="FV141" s="4">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="FW141" s="4" t="str">
-        <f t="shared" si="42"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -38664,35 +38920,35 @@
         <v>140</v>
       </c>
       <c r="AR142" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="CK142" s="4">
+        <f t="shared" ref="CK142:CK173" si="45">+CL142+CN142+CO142+CP142+CQ142</f>
+        <v>0</v>
+      </c>
+      <c r="FL142" s="4">
+        <f t="shared" ref="FL142:FL173" si="46">+FK142/3000</f>
+        <v>0</v>
+      </c>
+      <c r="FO142" s="4">
+        <f t="shared" ref="FO142:FO173" si="47">+FN142/1400</f>
+        <v>0</v>
+      </c>
+      <c r="FR142" s="4">
+        <f t="shared" ref="FR142:FR173" si="48">+FQ142/2000</f>
+        <v>0</v>
+      </c>
+      <c r="FU142" s="4">
+        <f t="shared" ref="FU142:FU173" si="49">+FT142/15000</f>
+        <v>0</v>
+      </c>
+      <c r="FV142" s="4">
+        <f t="shared" ref="FV142:FV173" si="50">+FL142+FO142+FR142+FU142</f>
+        <v>0</v>
+      </c>
+      <c r="FW142" s="4" t="str">
         <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="CK142" s="4">
-        <f t="shared" ref="CK142:CK173" si="44">+CL142+CN142+CO142+CP142+CQ142</f>
-        <v>0</v>
-      </c>
-      <c r="FL142" s="4">
-        <f t="shared" ref="FL142:FL173" si="45">+FK142/3000</f>
-        <v>0</v>
-      </c>
-      <c r="FO142" s="4">
-        <f t="shared" ref="FO142:FO173" si="46">+FN142/1400</f>
-        <v>0</v>
-      </c>
-      <c r="FR142" s="4">
-        <f t="shared" ref="FR142:FR173" si="47">+FQ142/2000</f>
-        <v>0</v>
-      </c>
-      <c r="FU142" s="4">
-        <f t="shared" ref="FU142:FU173" si="48">+FT142/15000</f>
-        <v>0</v>
-      </c>
-      <c r="FV142" s="4">
-        <f t="shared" ref="FV142:FV173" si="49">+FL142+FO142+FR142+FU142</f>
-        <v>0</v>
-      </c>
-      <c r="FW142" s="4" t="str">
-        <f t="shared" si="42"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -38701,35 +38957,35 @@
         <v>141</v>
       </c>
       <c r="AR143" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="CK143" s="4">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="FL143" s="4">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="FO143" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="FR143" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FU143" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FV143" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FW143" s="4" t="str">
         <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="CK143" s="4">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="FL143" s="4">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="FO143" s="4">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="FR143" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FU143" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FV143" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FW143" s="4" t="str">
-        <f t="shared" si="42"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -38738,35 +38994,35 @@
         <v>142</v>
       </c>
       <c r="AR144" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="CK144" s="4">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="FL144" s="4">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="FO144" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="FR144" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FU144" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FV144" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FW144" s="4" t="str">
         <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="CK144" s="4">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="FL144" s="4">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="FO144" s="4">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="FR144" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FU144" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FV144" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FW144" s="4" t="str">
-        <f t="shared" si="42"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -38775,35 +39031,35 @@
         <v>143</v>
       </c>
       <c r="AR145" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="CK145" s="4">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="FL145" s="4">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="FO145" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="FR145" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FU145" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FV145" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FW145" s="4" t="str">
         <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="CK145" s="4">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="FL145" s="4">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="FO145" s="4">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="FR145" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FU145" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FV145" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FW145" s="4" t="str">
-        <f t="shared" si="42"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -38812,35 +39068,35 @@
         <v>144</v>
       </c>
       <c r="AR146" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="CK146" s="4">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="FL146" s="4">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="FO146" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="FR146" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FU146" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FV146" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FW146" s="4" t="str">
         <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="CK146" s="4">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="FL146" s="4">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="FO146" s="4">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="FR146" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FU146" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FV146" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FW146" s="4" t="str">
-        <f t="shared" si="42"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -38849,35 +39105,35 @@
         <v>145</v>
       </c>
       <c r="AR147" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="CK147" s="4">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="FL147" s="4">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="FO147" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="FR147" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FU147" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FV147" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FW147" s="4" t="str">
         <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="CK147" s="4">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="FL147" s="4">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="FO147" s="4">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="FR147" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FU147" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FV147" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FW147" s="4" t="str">
-        <f t="shared" si="42"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -38886,35 +39142,35 @@
         <v>146</v>
       </c>
       <c r="AR148" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="CK148" s="4">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="FL148" s="4">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="FO148" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="FR148" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FU148" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FV148" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FW148" s="4" t="str">
         <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="CK148" s="4">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="FL148" s="4">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="FO148" s="4">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="FR148" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FU148" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FV148" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FW148" s="4" t="str">
-        <f t="shared" si="42"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -38923,35 +39179,35 @@
         <v>147</v>
       </c>
       <c r="AR149" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="CK149" s="4">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="FL149" s="4">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="FO149" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="FR149" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FU149" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FV149" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FW149" s="4" t="str">
         <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="CK149" s="4">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="FL149" s="4">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="FO149" s="4">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="FR149" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FU149" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FV149" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FW149" s="4" t="str">
-        <f t="shared" si="42"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -38960,35 +39216,35 @@
         <v>148</v>
       </c>
       <c r="AR150" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="CK150" s="4">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="FL150" s="4">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="FO150" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="FR150" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FU150" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FV150" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FW150" s="4" t="str">
         <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="CK150" s="4">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="FL150" s="4">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="FO150" s="4">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="FR150" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FU150" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FV150" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FW150" s="4" t="str">
-        <f t="shared" si="42"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -38997,35 +39253,35 @@
         <v>149</v>
       </c>
       <c r="AR151" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="CK151" s="4">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="FL151" s="4">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="FO151" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="FR151" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FU151" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FV151" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FW151" s="4" t="str">
         <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="CK151" s="4">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="FL151" s="4">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="FO151" s="4">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="FR151" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FU151" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FV151" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FW151" s="4" t="str">
-        <f t="shared" si="42"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -39034,35 +39290,35 @@
         <v>150</v>
       </c>
       <c r="AR152" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="CK152" s="4">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="FL152" s="4">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="FO152" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="FR152" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FU152" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FV152" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FW152" s="4" t="str">
         <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="CK152" s="4">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="FL152" s="4">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="FO152" s="4">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="FR152" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FU152" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FV152" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FW152" s="4" t="str">
-        <f t="shared" si="42"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -39071,35 +39327,35 @@
         <v>151</v>
       </c>
       <c r="AR153" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="CK153" s="4">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="FL153" s="4">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="FO153" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="FR153" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FU153" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FV153" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FW153" s="4" t="str">
         <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="CK153" s="4">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="FL153" s="4">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="FO153" s="4">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="FR153" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FU153" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FV153" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FW153" s="4" t="str">
-        <f t="shared" si="42"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -39108,35 +39364,35 @@
         <v>152</v>
       </c>
       <c r="AR154" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="CK154" s="4">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="FL154" s="4">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="FO154" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="FR154" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FU154" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FV154" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FW154" s="4" t="str">
         <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="CK154" s="4">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="FL154" s="4">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="FO154" s="4">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="FR154" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FU154" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FV154" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FW154" s="4" t="str">
-        <f t="shared" si="42"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -39145,35 +39401,35 @@
         <v>153</v>
       </c>
       <c r="AR155" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="CK155" s="4">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="FL155" s="4">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="FO155" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="FR155" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FU155" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FV155" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FW155" s="4" t="str">
         <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="CK155" s="4">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="FL155" s="4">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="FO155" s="4">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="FR155" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FU155" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FV155" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FW155" s="4" t="str">
-        <f t="shared" si="42"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -39182,35 +39438,35 @@
         <v>154</v>
       </c>
       <c r="AR156" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="CK156" s="4">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="FL156" s="4">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="FO156" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="FR156" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FU156" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FV156" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FW156" s="4" t="str">
         <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="CK156" s="4">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="FL156" s="4">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="FO156" s="4">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="FR156" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FU156" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FV156" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FW156" s="4" t="str">
-        <f t="shared" si="42"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -39219,35 +39475,35 @@
         <v>155</v>
       </c>
       <c r="AR157" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="CK157" s="4">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="FL157" s="4">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="FO157" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="FR157" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FU157" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FV157" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FW157" s="4" t="str">
         <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="CK157" s="4">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="FL157" s="4">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="FO157" s="4">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="FR157" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FU157" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FV157" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FW157" s="4" t="str">
-        <f t="shared" si="42"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -39256,35 +39512,35 @@
         <v>156</v>
       </c>
       <c r="AR158" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="CK158" s="4">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="FL158" s="4">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="FO158" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="FR158" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FU158" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FV158" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FW158" s="4" t="str">
         <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="CK158" s="4">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="FL158" s="4">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="FO158" s="4">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="FR158" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FU158" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FV158" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FW158" s="4" t="str">
-        <f t="shared" si="42"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -39293,35 +39549,35 @@
         <v>157</v>
       </c>
       <c r="AR159" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="CK159" s="4">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="FL159" s="4">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="FO159" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="FR159" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FU159" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FV159" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FW159" s="4" t="str">
         <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="CK159" s="4">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="FL159" s="4">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="FO159" s="4">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="FR159" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FU159" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FV159" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FW159" s="4" t="str">
-        <f t="shared" si="42"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -39330,35 +39586,35 @@
         <v>158</v>
       </c>
       <c r="AR160" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="CK160" s="4">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="FL160" s="4">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="FO160" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="FR160" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FU160" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FV160" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FW160" s="4" t="str">
         <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="CK160" s="4">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="FL160" s="4">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="FO160" s="4">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="FR160" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FU160" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FV160" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FW160" s="4" t="str">
-        <f t="shared" si="42"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -39367,35 +39623,35 @@
         <v>159</v>
       </c>
       <c r="AR161" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="CK161" s="4">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="FL161" s="4">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="FO161" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="FR161" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FU161" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FV161" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FW161" s="4" t="str">
         <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="CK161" s="4">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="FL161" s="4">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="FO161" s="4">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="FR161" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FU161" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FV161" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FW161" s="4" t="str">
-        <f t="shared" si="42"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -39404,35 +39660,35 @@
         <v>160</v>
       </c>
       <c r="AR162" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="CK162" s="4">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="FL162" s="4">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="FO162" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="FR162" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FU162" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FV162" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FW162" s="4" t="str">
         <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="CK162" s="4">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="FL162" s="4">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="FO162" s="4">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="FR162" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FU162" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FV162" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FW162" s="4" t="str">
-        <f t="shared" si="42"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -39441,35 +39697,35 @@
         <v>161</v>
       </c>
       <c r="AR163" s="4">
-        <f t="shared" ref="AR163:AR194" si="50">+AS163+AU163+BE163+CD163+CE163+CF163+CG163+CH163+CI163+CW163</f>
+        <f t="shared" ref="AR163:AR194" si="51">+AS163+AU163+BE163+CD163+CE163+CF163+CG163+CH163+CI163+CW163</f>
         <v>0</v>
       </c>
       <c r="CK163" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FL163" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="FO163" s="4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="FR163" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="FU163" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="FV163" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="FW163" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -39478,35 +39734,35 @@
         <v>162</v>
       </c>
       <c r="AR164" s="4">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="CK164" s="4">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="FL164" s="4">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="FO164" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="FR164" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FU164" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FV164" s="4">
         <f t="shared" si="50"/>
         <v>0</v>
       </c>
-      <c r="CK164" s="4">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="FL164" s="4">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="FO164" s="4">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="FR164" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FU164" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FV164" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
       <c r="FW164" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -39515,35 +39771,35 @@
         <v>163</v>
       </c>
       <c r="AR165" s="4">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="CK165" s="4">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="FL165" s="4">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="FO165" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="FR165" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FU165" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FV165" s="4">
         <f t="shared" si="50"/>
         <v>0</v>
       </c>
-      <c r="CK165" s="4">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="FL165" s="4">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="FO165" s="4">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="FR165" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FU165" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FV165" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
       <c r="FW165" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -39552,35 +39808,35 @@
         <v>164</v>
       </c>
       <c r="AR166" s="4">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="CK166" s="4">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="FL166" s="4">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="FO166" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="FR166" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FU166" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FV166" s="4">
         <f t="shared" si="50"/>
         <v>0</v>
       </c>
-      <c r="CK166" s="4">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="FL166" s="4">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="FO166" s="4">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="FR166" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FU166" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FV166" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
       <c r="FW166" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -39589,35 +39845,35 @@
         <v>165</v>
       </c>
       <c r="AR167" s="4">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="CK167" s="4">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="FL167" s="4">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="FO167" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="FR167" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FU167" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FV167" s="4">
         <f t="shared" si="50"/>
         <v>0</v>
       </c>
-      <c r="CK167" s="4">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="FL167" s="4">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="FO167" s="4">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="FR167" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FU167" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FV167" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
       <c r="FW167" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -39626,35 +39882,35 @@
         <v>166</v>
       </c>
       <c r="AR168" s="4">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="CK168" s="4">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="FL168" s="4">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="FO168" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="FR168" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FU168" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FV168" s="4">
         <f t="shared" si="50"/>
         <v>0</v>
       </c>
-      <c r="CK168" s="4">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="FL168" s="4">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="FO168" s="4">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="FR168" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FU168" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FV168" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
       <c r="FW168" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -39663,35 +39919,35 @@
         <v>167</v>
       </c>
       <c r="AR169" s="4">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="CK169" s="4">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="FL169" s="4">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="FO169" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="FR169" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FU169" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FV169" s="4">
         <f t="shared" si="50"/>
         <v>0</v>
       </c>
-      <c r="CK169" s="4">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="FL169" s="4">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="FO169" s="4">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="FR169" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FU169" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FV169" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
       <c r="FW169" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -39700,35 +39956,35 @@
         <v>168</v>
       </c>
       <c r="AR170" s="4">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="CK170" s="4">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="FL170" s="4">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="FO170" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="FR170" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FU170" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FV170" s="4">
         <f t="shared" si="50"/>
         <v>0</v>
       </c>
-      <c r="CK170" s="4">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="FL170" s="4">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="FO170" s="4">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="FR170" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FU170" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FV170" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
       <c r="FW170" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -39737,35 +39993,35 @@
         <v>169</v>
       </c>
       <c r="AR171" s="4">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="CK171" s="4">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="FL171" s="4">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="FO171" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="FR171" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FU171" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FV171" s="4">
         <f t="shared" si="50"/>
         <v>0</v>
       </c>
-      <c r="CK171" s="4">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="FL171" s="4">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="FO171" s="4">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="FR171" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FU171" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FV171" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
       <c r="FW171" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -39774,35 +40030,35 @@
         <v>170</v>
       </c>
       <c r="AR172" s="4">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="CK172" s="4">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="FL172" s="4">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="FO172" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="FR172" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FU172" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FV172" s="4">
         <f t="shared" si="50"/>
         <v>0</v>
       </c>
-      <c r="CK172" s="4">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="FL172" s="4">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="FO172" s="4">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="FR172" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FU172" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FV172" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
       <c r="FW172" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -39811,35 +40067,35 @@
         <v>171</v>
       </c>
       <c r="AR173" s="4">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="CK173" s="4">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="FL173" s="4">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="FO173" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="FR173" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FU173" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FV173" s="4">
         <f t="shared" si="50"/>
         <v>0</v>
       </c>
-      <c r="CK173" s="4">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="FL173" s="4">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="FO173" s="4">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="FR173" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FU173" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FV173" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
       <c r="FW173" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -39848,35 +40104,35 @@
         <v>172</v>
       </c>
       <c r="AR174" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="CK174" s="4">
-        <f t="shared" ref="CK174:CK198" si="51">+CL174+CN174+CO174+CP174+CQ174</f>
+        <f t="shared" ref="CK174:CK198" si="52">+CL174+CN174+CO174+CP174+CQ174</f>
         <v>0</v>
       </c>
       <c r="FL174" s="4">
-        <f t="shared" ref="FL174:FL198" si="52">+FK174/3000</f>
+        <f t="shared" ref="FL174:FL198" si="53">+FK174/3000</f>
         <v>0</v>
       </c>
       <c r="FO174" s="4">
-        <f t="shared" ref="FO174:FO198" si="53">+FN174/1400</f>
+        <f t="shared" ref="FO174:FO198" si="54">+FN174/1400</f>
         <v>0</v>
       </c>
       <c r="FR174" s="4">
-        <f t="shared" ref="FR174:FR198" si="54">+FQ174/2000</f>
+        <f t="shared" ref="FR174:FR198" si="55">+FQ174/2000</f>
         <v>0</v>
       </c>
       <c r="FU174" s="4">
-        <f t="shared" ref="FU174:FU198" si="55">+FT174/15000</f>
+        <f t="shared" ref="FU174:FU198" si="56">+FT174/15000</f>
         <v>0</v>
       </c>
       <c r="FV174" s="4">
-        <f t="shared" ref="FV174:FV198" si="56">+FL174+FO174+FR174+FU174</f>
+        <f t="shared" ref="FV174:FV198" si="57">+FL174+FO174+FR174+FU174</f>
         <v>0</v>
       </c>
       <c r="FW174" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -39885,35 +40141,35 @@
         <v>173</v>
       </c>
       <c r="AR175" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="CK175" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FL175" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FO175" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="FR175" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FU175" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FV175" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FW175" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -39922,35 +40178,35 @@
         <v>174</v>
       </c>
       <c r="AR176" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="CK176" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FL176" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FO176" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="FR176" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FU176" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FV176" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FW176" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -39959,35 +40215,35 @@
         <v>175</v>
       </c>
       <c r="AR177" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="CK177" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FL177" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FO177" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="FR177" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FU177" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FV177" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FW177" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -39996,35 +40252,35 @@
         <v>176</v>
       </c>
       <c r="AR178" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="CK178" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FL178" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FO178" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="FR178" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FU178" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FV178" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FW178" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -40033,35 +40289,35 @@
         <v>177</v>
       </c>
       <c r="AR179" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="CK179" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FL179" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FO179" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="FR179" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FU179" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FV179" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FW179" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -40070,35 +40326,35 @@
         <v>178</v>
       </c>
       <c r="AR180" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="CK180" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FL180" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FO180" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="FR180" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FU180" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FV180" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FW180" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -40107,35 +40363,35 @@
         <v>179</v>
       </c>
       <c r="AR181" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="CK181" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FL181" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FO181" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="FR181" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FU181" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FV181" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FW181" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -40144,35 +40400,35 @@
         <v>180</v>
       </c>
       <c r="AR182" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="CK182" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FL182" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FO182" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="FR182" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FU182" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FV182" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FW182" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -40181,35 +40437,35 @@
         <v>181</v>
       </c>
       <c r="AR183" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="CK183" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FL183" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FO183" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="FR183" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FU183" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FV183" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FW183" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -40218,35 +40474,35 @@
         <v>182</v>
       </c>
       <c r="AR184" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="CK184" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FL184" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FO184" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="FR184" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FU184" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FV184" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FW184" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -40255,35 +40511,35 @@
         <v>183</v>
       </c>
       <c r="AR185" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="CK185" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FL185" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FO185" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="FR185" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FU185" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FV185" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FW185" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -40292,35 +40548,35 @@
         <v>184</v>
       </c>
       <c r="AR186" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="CK186" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FL186" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FO186" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="FR186" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FU186" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FV186" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FW186" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -40329,35 +40585,35 @@
         <v>185</v>
       </c>
       <c r="AR187" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="CK187" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FL187" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FO187" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="FR187" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FU187" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FV187" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FW187" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -40366,35 +40622,35 @@
         <v>186</v>
       </c>
       <c r="AR188" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="CK188" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FL188" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FO188" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="FR188" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FU188" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FV188" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FW188" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -40403,35 +40659,35 @@
         <v>187</v>
       </c>
       <c r="AR189" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="CK189" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FL189" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FO189" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="FR189" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FU189" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FV189" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FW189" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -40440,35 +40696,35 @@
         <v>188</v>
       </c>
       <c r="AR190" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="CK190" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FL190" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FO190" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="FR190" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FU190" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FV190" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FW190" s="4" t="str">
-        <f t="shared" ref="FW190:FW198" si="57">IF(W190&gt;3000,"ALTO",IF(FV190&gt;=1,"ALTO","ORDINARIO"))</f>
+        <f t="shared" ref="FW190:FW198" si="58">IF(W190&gt;3000,"ALTO",IF(FV190&gt;=1,"ALTO","ORDINARIO"))</f>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -40477,35 +40733,35 @@
         <v>189</v>
       </c>
       <c r="AR191" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="CK191" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FL191" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FO191" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="FR191" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FU191" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FV191" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FW191" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -40514,35 +40770,35 @@
         <v>190</v>
       </c>
       <c r="AR192" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="CK192" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FL192" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FO192" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="FR192" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FU192" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FV192" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FW192" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -40551,35 +40807,35 @@
         <v>191</v>
       </c>
       <c r="AR193" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="CK193" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FL193" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FO193" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="FR193" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FU193" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FV193" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FW193" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -40588,35 +40844,35 @@
         <v>192</v>
       </c>
       <c r="AR194" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="CK194" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FL194" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FO194" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="FR194" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FU194" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FV194" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FW194" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -40625,35 +40881,35 @@
         <v>193</v>
       </c>
       <c r="AR195" s="4">
-        <f t="shared" ref="AR195:AR198" si="58">+AS195+AU195+BE195+CD195+CE195+CF195+CG195+CH195+CI195+CW195</f>
+        <f t="shared" ref="AR195:AR198" si="59">+AS195+AU195+BE195+CD195+CE195+CF195+CG195+CH195+CI195+CW195</f>
         <v>0</v>
       </c>
       <c r="CK195" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FL195" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FO195" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="FR195" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FU195" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FV195" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FW195" s="4" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -40662,35 +40918,35 @@
         <v>194</v>
       </c>
       <c r="AR196" s="4">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+      <c r="CK196" s="4">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="FL196" s="4">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="FO196" s="4">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="FR196" s="4">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="FU196" s="4">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="FV196" s="4">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+      <c r="FW196" s="4" t="str">
         <f t="shared" si="58"/>
-        <v>0</v>
-      </c>
-      <c r="CK196" s="4">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="FL196" s="4">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="FO196" s="4">
-        <f t="shared" si="53"/>
-        <v>0</v>
-      </c>
-      <c r="FR196" s="4">
-        <f t="shared" si="54"/>
-        <v>0</v>
-      </c>
-      <c r="FU196" s="4">
-        <f t="shared" si="55"/>
-        <v>0</v>
-      </c>
-      <c r="FV196" s="4">
-        <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
-      <c r="FW196" s="4" t="str">
-        <f t="shared" si="57"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -40699,35 +40955,35 @@
         <v>195</v>
       </c>
       <c r="AR197" s="4">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+      <c r="CK197" s="4">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="FL197" s="4">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="FO197" s="4">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="FR197" s="4">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="FU197" s="4">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="FV197" s="4">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+      <c r="FW197" s="4" t="str">
         <f t="shared" si="58"/>
-        <v>0</v>
-      </c>
-      <c r="CK197" s="4">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="FL197" s="4">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="FO197" s="4">
-        <f t="shared" si="53"/>
-        <v>0</v>
-      </c>
-      <c r="FR197" s="4">
-        <f t="shared" si="54"/>
-        <v>0</v>
-      </c>
-      <c r="FU197" s="4">
-        <f t="shared" si="55"/>
-        <v>0</v>
-      </c>
-      <c r="FV197" s="4">
-        <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
-      <c r="FW197" s="4" t="str">
-        <f t="shared" si="57"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -40736,35 +40992,35 @@
         <v>196</v>
       </c>
       <c r="AR198" s="4">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+      <c r="CK198" s="4">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="FL198" s="4">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="FO198" s="4">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="FR198" s="4">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="FU198" s="4">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="FV198" s="4">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+      <c r="FW198" s="4" t="str">
         <f t="shared" si="58"/>
-        <v>0</v>
-      </c>
-      <c r="CK198" s="4">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="FL198" s="4">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="FO198" s="4">
-        <f t="shared" si="53"/>
-        <v>0</v>
-      </c>
-      <c r="FR198" s="4">
-        <f t="shared" si="54"/>
-        <v>0</v>
-      </c>
-      <c r="FU198" s="4">
-        <f t="shared" si="55"/>
-        <v>0</v>
-      </c>
-      <c r="FV198" s="4">
-        <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
-      <c r="FW198" s="4" t="str">
-        <f t="shared" si="57"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -41040,16 +41296,17 @@
     <hyperlink ref="Q68" r:id="rId42" xr:uid="{07B79AC2-D0BB-4053-B52A-2218F9C8D957}"/>
     <hyperlink ref="Q73" r:id="rId43" xr:uid="{AC530E9D-142F-47C1-9FA2-9326C9E7E289}"/>
     <hyperlink ref="Q74" r:id="rId44" xr:uid="{3666EBA2-130E-4794-96A0-D6F6C3ACD1EE}"/>
+    <hyperlink ref="Q78" r:id="rId45" xr:uid="{AFBC3AA6-C580-4B7F-B71B-D6480B14E003}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId45"/>
-  <legacyDrawing r:id="rId46"/>
+  <drawing r:id="rId46"/>
+  <legacyDrawing r:id="rId47"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x14">
       <controls>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1025" r:id="rId47" name="Spinner 1">
+            <control shapeId="1025" r:id="rId48" name="Spinner 1">
               <controlPr defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
@@ -41083,7 +41340,7 @@
     <row r="1" spans="1:310" x14ac:dyDescent="0.3">
       <c r="A1">
         <f>+BD!A1</f>
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="B1" t="s">
         <v>133</v>
@@ -42016,19 +42273,19 @@
     <row r="2" spans="1:310" x14ac:dyDescent="0.3">
       <c r="B2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,2, FALSE)</f>
-        <v>DHL</v>
+        <v>GENERAL</v>
       </c>
       <c r="C2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,3, FALSE)</f>
-        <v>DHL EXPRESS MEXICO SA DE CV</v>
+        <v>SUPRACARE SA DE CV</v>
       </c>
       <c r="D2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,4, FALSE)</f>
-        <v>DHL PBC GUADALUPE HIDALGO</v>
+        <v>FRAICHE CHEDRAUI</v>
       </c>
       <c r="E2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,5, FALSE)</f>
-        <v>DEM8801152E9</v>
+        <v>SUP200818IP0</v>
       </c>
       <c r="F2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,6, FALSE)</f>
@@ -42036,31 +42293,31 @@
       </c>
       <c r="G2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,7, FALSE)</f>
-        <v>MENSAJERIA Y PAQUETERIA</v>
+        <v>COMERCIO AL POR MENOR DE ARTICULOS DE PERFUMERIA Y COSMETICOS</v>
       </c>
       <c r="H2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,8, FALSE)</f>
-        <v>SE GESTIONAN ENVÍOS Y RECEPCIONES DE PAQUETES, SE OFRECEN SERVICIOS DE ATENCIÓN AL CLIENTE, Y SE COORDINAN OPERACIONES LOGÍSTICAS Y DE DISTRIBUCIÓN</v>
+        <v>SE OFRECE UNA AMPLIA VARIEDAD DE FRAGANCIAS Y PRODUCTOS, COMO COSMÉTICOS Y PRODUCTOS PARA EL CUIDADO PERSONAL, BRINDANDO ASESORAMIENTO, PROMOCIONES, Y SERVICIOS DE PRUEBA Y PERSONALIZACIÓN DE FRAGANCIAS</v>
       </c>
       <c r="I2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,9, FALSE)</f>
-        <v>11 SUR</v>
+        <v>7 NORTE</v>
       </c>
       <c r="J2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,10, FALSE)</f>
-        <v>12923</v>
+        <v>107</v>
       </c>
       <c r="K2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,11, FALSE)</f>
-        <v>LOCAL 1</v>
+        <v>LOCAL 5</v>
       </c>
       <c r="L2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,12, FALSE)</f>
-        <v>SAN ISIDRO CASTILLOTLA</v>
+        <v>CENTRO</v>
       </c>
       <c r="M2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,13, FALSE)</f>
-        <v>PUEBLA</v>
+        <v>TEHUACAN</v>
       </c>
       <c r="N2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,14, FALSE)</f>
@@ -42068,23 +42325,23 @@
       </c>
       <c r="O2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,15, FALSE)</f>
-        <v>72498</v>
+        <v>75700</v>
       </c>
       <c r="P2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,16, FALSE)</f>
-        <v>2223234754</v>
+        <v>2383806932</v>
       </c>
       <c r="Q2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,17, FALSE)</f>
-        <v>servicepoint.ghi@dhl.com</v>
+        <v>f516.chedrahuitehuacan@pue.fraiche.mx</v>
       </c>
       <c r="R2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,18, FALSE)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,19, FALSE)</f>
-        <v>1 DE NOVIEMBRE DE 2014</v>
+        <v>01 DE JUNIO DEE 2024</v>
       </c>
       <c r="T2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,20, FALSE)</f>
@@ -42096,11 +42353,11 @@
       </c>
       <c r="V2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,22, FALSE)</f>
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="W2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,23, FALSE)</f>
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="X2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,24, FALSE)</f>
@@ -42108,7 +42365,7 @@
       </c>
       <c r="Y2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,25, FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,26, FALSE)</f>
@@ -42120,7 +42377,7 @@
       </c>
       <c r="AB2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,28, FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,29, FALSE)</f>
@@ -42128,19 +42385,19 @@
       </c>
       <c r="AD2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,30, FALSE)</f>
-        <v>4 CAJONES</v>
+        <v>5 CAJONES</v>
       </c>
       <c r="AE2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,31, FALSE)</f>
-        <v>ALEJANDRO ENRIQUE SOLORZANO MONTES DE OCA</v>
+        <v>VERONICA ANDRADE GARCIA</v>
       </c>
       <c r="AF2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,32, FALSE)</f>
-        <v>MARIA DE LA PAZ CORDERO R</v>
+        <v>MAYRA LIZBET ANGEL PEREZ</v>
       </c>
       <c r="AG2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,33, FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,34, FALSE)</f>
@@ -42148,7 +42405,7 @@
       </c>
       <c r="AI2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,35, FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,36, FALSE)</f>
@@ -42168,23 +42425,23 @@
       </c>
       <c r="AN2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,40, FALSE)</f>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AO2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,41, FALSE)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,42, FALSE)</f>
-        <v>LUNES A VIERNES  Y SABADO</v>
+        <v>LUNES A DOMINGO</v>
       </c>
       <c r="AQ2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,43, FALSE)</f>
-        <v>9:00 AM A 19:00 HRS Y 9:00 AM A 2:00 PM.</v>
+        <v>10:00 A 20:00 HORAS</v>
       </c>
       <c r="AR2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,44, FALSE)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,45, FALSE)</f>
@@ -42200,15 +42457,15 @@
       </c>
       <c r="AV2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,48, FALSE)</f>
-        <v>SALIDA Y AREA INTERNA</v>
+        <v>AREA INTERNA Y ENTRADA</v>
       </c>
       <c r="AW2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,49, FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,50, FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,51, FALSE)</f>
@@ -42236,11 +42493,11 @@
       </c>
       <c r="BE2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,57, FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="BF2" t="str">
+        <v>0</v>
+      </c>
+      <c r="BF2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,58, FALSE)</f>
-        <v>BOTON PANICO</v>
+        <v>0</v>
       </c>
       <c r="BG2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,59, FALSE)</f>
@@ -42250,21 +42507,21 @@
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,60, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="BI2" t="str">
+      <c r="BI2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,61, FALSE)</f>
-        <v>MOSTRADOR</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,62, FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,63, FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,64, FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BM2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,65, FALSE)</f>
@@ -42336,7 +42593,7 @@
       </c>
       <c r="CD2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,82, FALSE)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CE2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,83, FALSE)</f>
@@ -42364,11 +42621,11 @@
       </c>
       <c r="CK2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,89, FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CL2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,90, FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CM2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,91, FALSE)</f>
@@ -42444,11 +42701,11 @@
       </c>
       <c r="DE2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,109, FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="DF2" t="str">
+        <v>0</v>
+      </c>
+      <c r="DF2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,110, FALSE)</f>
-        <v>AREA INTERNA</v>
+        <v>0</v>
       </c>
       <c r="DG2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,111, FALSE)</f>
@@ -42516,11 +42773,11 @@
       </c>
       <c r="DW2" s="5">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,127, FALSE)</f>
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="DX2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,128, FALSE)</f>
-        <v>MAYO</v>
+        <v>JUNIO</v>
       </c>
       <c r="DY2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,129, FALSE)</f>
@@ -42528,23 +42785,23 @@
       </c>
       <c r="DZ2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,130, FALSE)</f>
-        <v>18.980469690072912, -98.25416721650755</v>
+        <v>18.4637150494009, -97.38691843244746</v>
       </c>
       <c r="EA2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,131, FALSE)</f>
-        <v>PRIVADA DE LOS NARANJOS</v>
+        <v>LOCAL</v>
       </c>
       <c r="EB2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,132, FALSE)</f>
-        <v>DE LA ROSA</v>
+        <v>LOCAL</v>
       </c>
       <c r="EC2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,133, FALSE)</f>
-        <v>ACC. PRINCIPAL 11 SUR</v>
+        <v>CHEDRAUI</v>
       </c>
       <c r="ED2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,134, FALSE)</f>
-        <v>CALLE FAROLES</v>
+        <v>ESTACIONAMIENTO</v>
       </c>
       <c r="EE2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,135, FALSE)</f>
@@ -42562,9 +42819,9 @@
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,138, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="EI2">
+      <c r="EI2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,139, FALSE)</f>
-        <v>0</v>
+        <v>ERIBERTO ANSELMO SANCHEZ</v>
       </c>
       <c r="EJ2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,140, FALSE)</f>
@@ -42682,17 +42939,17 @@
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,168, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="FM2">
+      <c r="FM2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,169, FALSE)</f>
-        <v>0</v>
+        <v>ESENCIA Y PERFUMON</v>
       </c>
       <c r="FN2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,170, FALSE)</f>
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="FO2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,171, FALSE)</f>
-        <v>0</v>
+        <v>7.2142857142857147E-2</v>
       </c>
       <c r="FP2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,172, FALSE)</f>
@@ -42712,15 +42969,15 @@
       </c>
       <c r="FT2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,176, FALSE)</f>
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="FU2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,177, FALSE)</f>
-        <v>4.0000000000000001E-3</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="FV2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,178, FALSE)</f>
-        <v>4.0000000000000001E-3</v>
+        <v>8.0142857142857155E-2</v>
       </c>
       <c r="FW2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,179, FALSE)</f>

--- a/Inputs/BD.xlsx
+++ b/Inputs/BD.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/078e1a455e5c02ce/Documentos/GitHub/Proyecto_PIPC/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="629" documentId="13_ncr:1_{898522BF-B0F8-4888-9748-DC730D5D6CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0EC7853-F432-4F17-9836-8E6DA938593D}"/>
+  <xr:revisionPtr revIDLastSave="1644" documentId="13_ncr:1_{898522BF-B0F8-4888-9748-DC730D5D6CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4284521A-6B7F-4574-8A63-9BBB583DD097}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3F095A75-F066-4695-8672-8D4315F1EF23}"/>
   </bookViews>
@@ -563,7 +563,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7543" uniqueCount="2314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8000" uniqueCount="2507">
   <si>
     <t>dia</t>
   </si>
@@ -7231,9 +7231,6 @@
     <t>ALEJANDRO ENRIQUE SOLORZANO MONTES DE OCA</t>
   </si>
   <si>
-    <t>LUNES A VIERNES  Y SABADO</t>
-  </si>
-  <si>
     <t>19.039947986052415, -98.21083314033027</t>
   </si>
   <si>
@@ -7312,21 +7309,6 @@
     <t>BOTON PANICO</t>
   </si>
   <si>
-    <t>DHL PBC AGUA AZUL</t>
-  </si>
-  <si>
-    <t>DHL PBC ANZURES</t>
-  </si>
-  <si>
-    <t>DHL PBC CIUDAD UNIVERSITARIA</t>
-  </si>
-  <si>
-    <t>DHL PBC BUGAMBILIAS</t>
-  </si>
-  <si>
-    <t>DHL PBC GUADALUPE HIDALGO</t>
-  </si>
-  <si>
     <t>SAN ISIDRO CASTILLOTLA</t>
   </si>
   <si>
@@ -7354,18 +7336,6 @@
     <t>CALLE FAROLES</t>
   </si>
   <si>
-    <t>DHL PBC ATLIXCO</t>
-  </si>
-  <si>
-    <t>DHL HPU ZACATLAN</t>
-  </si>
-  <si>
-    <t>DHL HPU HUAUCHINANGO</t>
-  </si>
-  <si>
-    <t>DHL PBC IZUCAR DE MATAMOROS</t>
-  </si>
-  <si>
     <t>9:00 AM A 19:00 HRS Y 9:00 AM A 2:00 PM.</t>
   </si>
   <si>
@@ -7505,6 +7475,615 @@
   </si>
   <si>
     <t>ESENCIA Y PERFUMON</t>
+  </si>
+  <si>
+    <t>SERVICIO DE PAQUETERIA Y MENSAJERIA</t>
+  </si>
+  <si>
+    <t>AV. INDEPENDENCIA PONIENTE</t>
+  </si>
+  <si>
+    <t>servicepoint.tcn@dhl.com</t>
+  </si>
+  <si>
+    <t>22 DE MARZO DE 2021</t>
+  </si>
+  <si>
+    <t>BRYAN CHAVEZ SANTIAGO</t>
+  </si>
+  <si>
+    <t>18.46347, -97.39752</t>
+  </si>
+  <si>
+    <t>CALLA 2 ORIENTE</t>
+  </si>
+  <si>
+    <t>AVENIDA INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>CALLE 4 SUR</t>
+  </si>
+  <si>
+    <t>CALLE 2 NORTE</t>
+  </si>
+  <si>
+    <t>AREA INTERNA Y AREA CLIENTES</t>
+  </si>
+  <si>
+    <t>PAULINA BENITEZ HERNANDEZ</t>
+  </si>
+  <si>
+    <t>AV. ADOLFO LOPEZ MATEOS</t>
+  </si>
+  <si>
+    <t>ZONA ALTA</t>
+  </si>
+  <si>
+    <t>servicepoint.gqs@dhl.com</t>
+  </si>
+  <si>
+    <t>ANDRES ARTEMIO CANCINO SANCHEZ</t>
+  </si>
+  <si>
+    <t>18.46478381541792, -97.41009024605313</t>
+  </si>
+  <si>
+    <t>PRIV 2 PTE, ESTACION BOUTIQUE, PANIFICADORA</t>
+  </si>
+  <si>
+    <t>INDEPENDENCIA, GYM MONTECARLO, RESTAURANTE</t>
+  </si>
+  <si>
+    <t>26 NTE, PIZZERIA, FLORERIA, VIVIENDAS</t>
+  </si>
+  <si>
+    <t>22 NTE, SUPERLEO, ENERGETICOS TEHUACAN</t>
+  </si>
+  <si>
+    <t>ANDADOR ITUBIDE</t>
+  </si>
+  <si>
+    <t>1-A</t>
+  </si>
+  <si>
+    <t>ESQ. 5 DE MAYO</t>
+  </si>
+  <si>
+    <t>ZACATLAN</t>
+  </si>
+  <si>
+    <t>servicepoint.zta@dhl.com</t>
+  </si>
+  <si>
+    <t>20 DE AGOSTO DE 2021</t>
+  </si>
+  <si>
+    <t>PAUL HERNANDEZ GARCIA</t>
+  </si>
+  <si>
+    <t>19.93146366752627, -97.96000249718361</t>
+  </si>
+  <si>
+    <t>ZÓCALO DE ZACATLÁN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALLE 5 DE MAYO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOCALES COMERCIALES </t>
+  </si>
+  <si>
+    <t>BLVD FERROCARRILES</t>
+  </si>
+  <si>
+    <t>PRADO SUR</t>
+  </si>
+  <si>
+    <t>servicepoint.axo@dhl.com</t>
+  </si>
+  <si>
+    <t>AIDE BRAVO SANCHEZ</t>
+  </si>
+  <si>
+    <t>HUAUCHINANGO</t>
+  </si>
+  <si>
+    <t>1 CAJON</t>
+  </si>
+  <si>
+    <t>TESHA ADRIANA DIAZ VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>servicepoint.iar@dhl.com</t>
+  </si>
+  <si>
+    <t>servicepoint.hhn@dhl.com</t>
+  </si>
+  <si>
+    <t>DULCE MARIA HUERTA AVELAR</t>
+  </si>
+  <si>
+    <t>AV. 9 NORTE</t>
+  </si>
+  <si>
+    <t>LOCAL 16</t>
+  </si>
+  <si>
+    <t>BARRIO SAN JOSE</t>
+  </si>
+  <si>
+    <t>juan.j.diaz@dhl.com</t>
+  </si>
+  <si>
+    <t>JUAN JESUS DIAZ CARRASCO</t>
+  </si>
+  <si>
+    <t>GEN7908272C1</t>
+  </si>
+  <si>
+    <t>CENTRO DE CARBURACION DE GAS LP</t>
+  </si>
+  <si>
+    <t>SE DEDICA A LA DISTRIBUCIÓN Y VENTA DE GAS LICUADO DE PETRÓLEO (LP), INCLUYENDO LA RECARGA DE CILINDROS Y TANQUES, Y EL MANTENIMIENTO DE EQUIPOS DE DISTRIBUCIÓN. SUS ACTIVIDADES TAMBIÉN ABARCAN LA ATENCIÓN AL CLIENTE.</t>
+  </si>
+  <si>
+    <t>PREDIO DENOMINADO LA DESVIACION, CARRETERA FDERAL</t>
+  </si>
+  <si>
+    <t>KM 61</t>
+  </si>
+  <si>
+    <t>LOCALIDAD DE AMOLTEPEC, TOMATLAN</t>
+  </si>
+  <si>
+    <t>estacion.zacatlan@gasexpressnieto.com</t>
+  </si>
+  <si>
+    <t>ABRIL DE 2021</t>
+  </si>
+  <si>
+    <t>ARTURO PASOS HERRERA</t>
+  </si>
+  <si>
+    <t>YESENIA ANEL PALAFOX LUNA</t>
+  </si>
+  <si>
+    <t>OFICINA Y AREA EXTERNA</t>
+  </si>
+  <si>
+    <t>OFICINA Y DESPACHADOR</t>
+  </si>
+  <si>
+    <t>PARO EMERGENCIA</t>
+  </si>
+  <si>
+    <t>19.870830220413556, -98.00510221900382</t>
+  </si>
+  <si>
+    <t>CARRETERA</t>
+  </si>
+  <si>
+    <t>JORGE LUIS ARROYO FLORES</t>
+  </si>
+  <si>
+    <t>JULIAN EMMANUEL PASOS SIERRA</t>
+  </si>
+  <si>
+    <t>CONSTANTINO VEERA HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MUNIR CASTELAN DURAN</t>
+  </si>
+  <si>
+    <t>CENTRO DE CARBURACION GAS EXPRESS NIETO</t>
+  </si>
+  <si>
+    <t>GAS EXPRESS NIETO DE MEXICO SA DE CV</t>
+  </si>
+  <si>
+    <t>DHL TEHUACAN CENTRO</t>
+  </si>
+  <si>
+    <t>DHL TEHUACAN ZONA ALTA</t>
+  </si>
+  <si>
+    <t>DHL TECAMACHALCO</t>
+  </si>
+  <si>
+    <t>DHL AGUA AZUL</t>
+  </si>
+  <si>
+    <t>DHL ANZURES</t>
+  </si>
+  <si>
+    <t>DHL CIUDAD UNIVERSITARIA</t>
+  </si>
+  <si>
+    <t>DHL BUGAMBILIAS</t>
+  </si>
+  <si>
+    <t>DHL GUADALUPE HIDALGO</t>
+  </si>
+  <si>
+    <t>DHL ATLIXCO</t>
+  </si>
+  <si>
+    <t>DHL ZACATLAN</t>
+  </si>
+  <si>
+    <t>DHL HUAUCHINANGO</t>
+  </si>
+  <si>
+    <t>DHL IZUCAR DE MATAMOROS</t>
+  </si>
+  <si>
+    <t>19°02'29.6"N 98°08'47.1"W</t>
+  </si>
+  <si>
+    <t>AV. JUAREZ</t>
+  </si>
+  <si>
+    <t>FARMACIAS DEL AHORRO AMALUCAN</t>
+  </si>
+  <si>
+    <t>FARMACIAS FLEMING AMALUCAN</t>
+  </si>
+  <si>
+    <t>01 DE ENERO DE 2021</t>
+  </si>
+  <si>
+    <t>20.175863461634677, -98.05208169558415</t>
+  </si>
+  <si>
+    <t>MORELOS</t>
+  </si>
+  <si>
+    <t>CENTRO COMERCIAL</t>
+  </si>
+  <si>
+    <t>INSTITUTO DE BELLEZA SEDEÑO</t>
+  </si>
+  <si>
+    <t>GENERAL FRANCISCO CRAVIOTO</t>
+  </si>
+  <si>
+    <t>15 DE DICIEMBRE 2022</t>
+  </si>
+  <si>
+    <t>18.603553041443504, -98.46538396061852</t>
+  </si>
+  <si>
+    <t>CALLE ALLENDE, INBURSA, GYM GENESIS, LOUIS</t>
+  </si>
+  <si>
+    <t>DE LA CONSTITUCION, WARRIORS FITNESS, CAFÉ 11:11</t>
+  </si>
+  <si>
+    <t>AV. CENTENARIO, HAMBURGUESAS YUYI, CLINICA</t>
+  </si>
+  <si>
+    <t>CALLE ZARAGOZA, ESTACIONAMIENTO, NATURAL</t>
+  </si>
+  <si>
+    <t>LUNES A VIERNES Y SABADO</t>
+  </si>
+  <si>
+    <t>UMBELINA ADAME CALDERÓN</t>
+  </si>
+  <si>
+    <t>FONDA MARGARITA</t>
+  </si>
+  <si>
+    <t>AACU650223TE8</t>
+  </si>
+  <si>
+    <t>RESTAURANTE BAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VENTA DE COMIDA Y BEBIDAS  </t>
+  </si>
+  <si>
+    <t>CALLE 2 PONIENTE</t>
+  </si>
+  <si>
+    <t>ABRIL DE 2023</t>
+  </si>
+  <si>
+    <t>FELICITAS MIREYA ESTRADA M</t>
+  </si>
+  <si>
+    <t>8:00 A 18:30 HORAS</t>
+  </si>
+  <si>
+    <t>19.047043836962022, -98.20153190469972</t>
+  </si>
+  <si>
+    <t>JULIO</t>
+  </si>
+  <si>
+    <t>BAR</t>
+  </si>
+  <si>
+    <t>COMEDOR Y CONCINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> BAR</t>
+  </si>
+  <si>
+    <t>BONPANE</t>
+  </si>
+  <si>
+    <t>2 PONIENTE</t>
+  </si>
+  <si>
+    <t>ARTESANIA Y BISUTERIA</t>
+  </si>
+  <si>
+    <t>DEPARTAMENTOS</t>
+  </si>
+  <si>
+    <t>FERNANDO JOSE MELENDEZ TEJED</t>
+  </si>
+  <si>
+    <t>PAULO SERGIO JIMENEZ SALAZAR</t>
+  </si>
+  <si>
+    <t>TERESA HERNANDEZ</t>
+  </si>
+  <si>
+    <t>JOSEFA ARENAS PERALTA</t>
+  </si>
+  <si>
+    <t>LETICIA MONARCA SAENZ</t>
+  </si>
+  <si>
+    <t>JOSEFINA AMBROCIO DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>JORGE RAMIREZ MARTINEZ</t>
+  </si>
+  <si>
+    <t>JONATHAN DE JESUS RAMIREZ RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>VERONICA R JUAREZ HERNANDEZ</t>
+  </si>
+  <si>
+    <t>GASOLEOS SAN JUAN DE LOS LLANOS SA DE CV</t>
+  </si>
+  <si>
+    <t>E.S. 0512 EL SECO</t>
+  </si>
+  <si>
+    <t>GSJ150818IP8</t>
+  </si>
+  <si>
+    <t>PL/8527/EXP/ES/2015</t>
+  </si>
+  <si>
+    <t>ALMACENAMIENTO Y VENTA DE HIDROCARBUROS, ACEITES Y ADITIVOS</t>
+  </si>
+  <si>
+    <t>VENTA DE GASOLINA Y DIESEL</t>
+  </si>
+  <si>
+    <t>CARRETERA FEDERAL MEXICO-VERACRUZ</t>
+  </si>
+  <si>
+    <t>KM 212</t>
+  </si>
+  <si>
+    <t>BARRIO DE XILOTEPEC</t>
+  </si>
+  <si>
+    <t>SAN SALVADOR EL SECO</t>
+  </si>
+  <si>
+    <t>e00152@grupopozos.mx</t>
+  </si>
+  <si>
+    <t>18 DE AGOSTO DE 2015</t>
+  </si>
+  <si>
+    <t>MANUEL POZOS CRUZ</t>
+  </si>
+  <si>
+    <t>ROSA MARIA MENDOZA ALONSO</t>
+  </si>
+  <si>
+    <t>6:00 A 24:00 HORAS</t>
+  </si>
+  <si>
+    <t>19.130985584816678, -97.65161141752644</t>
+  </si>
+  <si>
+    <t>CARRETERA FEDERAL MÉXICO - VERACRUZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CASA HABITACIÓN </t>
+  </si>
+  <si>
+    <t>EN TODA LA GOSOLINERA</t>
+  </si>
+  <si>
+    <t>MARIBEL CASTRO ROJAS</t>
+  </si>
+  <si>
+    <t>FLORENCIO PEREZ BACILIO</t>
+  </si>
+  <si>
+    <t>ORLANDO PEREZ GARCIA</t>
+  </si>
+  <si>
+    <t>ALEJANDRO BARTOLO ROJAS</t>
+  </si>
+  <si>
+    <t>ALAN GIOVANI SILVA VERGARA</t>
+  </si>
+  <si>
+    <t>E.S. 510 ORIENTAL</t>
+  </si>
+  <si>
+    <t>PL/7448/EXP/ES/2015</t>
+  </si>
+  <si>
+    <t>BOULEVARD 16 DE SEPTIEMBRE Y CARRETERA FEDERAL SAN HIPOLITO NAUTLA</t>
+  </si>
+  <si>
+    <t>ORIENTAL</t>
+  </si>
+  <si>
+    <t>e00510@grupopozos.mx</t>
+  </si>
+  <si>
+    <t>24 DE SEPTIEMBRE DE 1992</t>
+  </si>
+  <si>
+    <t>HILDA POZOS HUERTA</t>
+  </si>
+  <si>
+    <t>OFICINA, BOMBAS Y VENTEO</t>
+  </si>
+  <si>
+    <t>19.376149991520244, -97.61836410224103</t>
+  </si>
+  <si>
+    <t>CALLE 2 ORIENTE</t>
+  </si>
+  <si>
+    <t>CALLE TEZIUTLÁN - ACAJETE</t>
+  </si>
+  <si>
+    <t>ARELY PEREZ LEAL</t>
+  </si>
+  <si>
+    <t>JUAN CARLOS JIMENEZ</t>
+  </si>
+  <si>
+    <t>JOSE LIMON REYES</t>
+  </si>
+  <si>
+    <t>DAVID POZOS HUERTA</t>
+  </si>
+  <si>
+    <t>ADOLFO HERNANDEZ SEGURA</t>
+  </si>
+  <si>
+    <t>GASOLINERA EMILIO CARRANZA SA DE CV</t>
+  </si>
+  <si>
+    <t>E.S. 12824 ZAUTLA</t>
+  </si>
+  <si>
+    <t>GEC1307261N6</t>
+  </si>
+  <si>
+    <t>5 DE MAYO</t>
+  </si>
+  <si>
+    <t>EMILIO CARRANZA</t>
+  </si>
+  <si>
+    <t>ZAUTLA</t>
+  </si>
+  <si>
+    <t>e12824@grupopozos.mx</t>
+  </si>
+  <si>
+    <t>2 DE ABRIL DE 2014</t>
+  </si>
+  <si>
+    <t>PEDRO JOSE LLARENA GONZALEZ</t>
+  </si>
+  <si>
+    <t>19.716647154590675, -97.66318679836357</t>
+  </si>
+  <si>
+    <t>TERRENO BALDÍO</t>
+  </si>
+  <si>
+    <t>E.S. 0858 ZACAPOAXTLA</t>
+  </si>
+  <si>
+    <t>CGP090902L74</t>
+  </si>
+  <si>
+    <t>5 DE MAYO SUR</t>
+  </si>
+  <si>
+    <t>EL TRIUNFO</t>
+  </si>
+  <si>
+    <t>ZACAPOAXTLA</t>
+  </si>
+  <si>
+    <t>e008585@grupopozos.mx</t>
+  </si>
+  <si>
+    <t>19.86879047034924, -97.58824903412194</t>
+  </si>
+  <si>
+    <t>FLORERÍA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALLE PATTONI </t>
+  </si>
+  <si>
+    <t>AV. 5 DE MAYO SUR</t>
+  </si>
+  <si>
+    <t>CALLE 2 DE ABRIL SUR</t>
+  </si>
+  <si>
+    <t>2 DE NOVIEMBRE DE 2015</t>
+  </si>
+  <si>
+    <t>18.87986, -97.72660</t>
+  </si>
+  <si>
+    <t>ANALISIS CLINICOS DR. SIMI</t>
+  </si>
+  <si>
+    <t>AV. 9 PONIENTE</t>
+  </si>
+  <si>
+    <t>CALLE 8 SUR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALLE 10 SUR </t>
+  </si>
+  <si>
+    <t>JOCELYNE ARELLANO PERIAÑEZ</t>
+  </si>
+  <si>
+    <t>IVAN REYES MARTINEZ</t>
+  </si>
+  <si>
+    <t>OSCAR ALBERTO CERVANTES VALDEZ</t>
+  </si>
+  <si>
+    <t>PL/8537/EXP/ES/2015</t>
+  </si>
+  <si>
+    <t>ANTONIO SALAZAR ESPINO</t>
+  </si>
+  <si>
+    <t>MA. DE LA CRUZ VAZQUEZ</t>
+  </si>
+  <si>
+    <t>JUAN GUZMAN OLIVARES</t>
+  </si>
+  <si>
+    <t>EMILIO PUENTE LUNA</t>
+  </si>
+  <si>
+    <t>SILVERIO APARICIO TAMANIS</t>
+  </si>
+  <si>
+    <t>MAURILIO CARRION OLIVARES</t>
+  </si>
+  <si>
+    <t>GASERA</t>
   </si>
 </sst>
 </file>
@@ -7514,7 +8093,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7577,13 +8156,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0" tint="-0.499984740745262"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="8"/>
       <color rgb="FF121212"/>
       <name val="Arial"/>
@@ -7635,7 +8207,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -7647,7 +8219,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -8127,7 +8698,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="26" fmlaLink="$A$1" max="30000" min="1" page="10" val="76"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="26" fmlaLink="$A$1" max="30000" min="1" page="10" val="77"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8510,25 +9081,25 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
-    <col min="139" max="139" width="11.5546875" style="11"/>
-    <col min="142" max="142" width="11.5546875" style="11"/>
-    <col min="145" max="145" width="11.5546875" style="11"/>
-    <col min="148" max="148" width="11.5546875" style="11"/>
-    <col min="151" max="151" width="11.5546875" style="11"/>
-    <col min="154" max="154" width="11.5546875" style="11"/>
-    <col min="157" max="157" width="11.5546875" style="11"/>
-    <col min="160" max="160" width="11.5546875" style="11"/>
-    <col min="163" max="163" width="11.5546875" style="11"/>
+    <col min="139" max="139" width="11.5546875" style="10"/>
+    <col min="142" max="142" width="11.5546875" style="10"/>
+    <col min="145" max="145" width="11.5546875" style="10"/>
+    <col min="148" max="148" width="11.5546875" style="10"/>
+    <col min="151" max="151" width="11.5546875" style="10"/>
+    <col min="154" max="154" width="11.5546875" style="10"/>
+    <col min="157" max="157" width="11.5546875" style="10"/>
+    <col min="160" max="160" width="11.5546875" style="10"/>
+    <col min="163" max="163" width="11.5546875" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:322" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="DS1" t="s">
         <v>1968</v>
       </c>
-      <c r="EO1" s="11" t="s">
+      <c r="EO1" s="10" t="s">
         <v>2174</v>
       </c>
     </row>
@@ -8947,7 +9518,7 @@
       <c r="EH2" t="s">
         <v>645</v>
       </c>
-      <c r="EI2" s="11" t="s">
+      <c r="EI2" s="10" t="s">
         <v>201</v>
       </c>
       <c r="EJ2" t="s">
@@ -8956,7 +9527,7 @@
       <c r="EK2" t="s">
         <v>646</v>
       </c>
-      <c r="EL2" s="11" t="s">
+      <c r="EL2" s="10" t="s">
         <v>202</v>
       </c>
       <c r="EM2" t="s">
@@ -8965,7 +9536,7 @@
       <c r="EN2" t="s">
         <v>647</v>
       </c>
-      <c r="EO2" s="11" t="s">
+      <c r="EO2" s="10" t="s">
         <v>203</v>
       </c>
       <c r="EP2" t="s">
@@ -8974,7 +9545,7 @@
       <c r="EQ2" t="s">
         <v>648</v>
       </c>
-      <c r="ER2" s="11" t="s">
+      <c r="ER2" s="10" t="s">
         <v>204</v>
       </c>
       <c r="ES2" t="s">
@@ -8983,7 +9554,7 @@
       <c r="ET2" t="s">
         <v>649</v>
       </c>
-      <c r="EU2" s="11" t="s">
+      <c r="EU2" s="10" t="s">
         <v>205</v>
       </c>
       <c r="EV2" t="s">
@@ -8992,7 +9563,7 @@
       <c r="EW2" t="s">
         <v>650</v>
       </c>
-      <c r="EX2" s="11" t="s">
+      <c r="EX2" s="10" t="s">
         <v>206</v>
       </c>
       <c r="EY2" t="s">
@@ -9001,7 +9572,7 @@
       <c r="EZ2" t="s">
         <v>651</v>
       </c>
-      <c r="FA2" s="11" t="s">
+      <c r="FA2" s="10" t="s">
         <v>207</v>
       </c>
       <c r="FB2" t="s">
@@ -9010,7 +9581,7 @@
       <c r="FC2" t="s">
         <v>652</v>
       </c>
-      <c r="FD2" s="11" t="s">
+      <c r="FD2" s="10" t="s">
         <v>208</v>
       </c>
       <c r="FE2" t="s">
@@ -9019,7 +9590,7 @@
       <c r="FF2" t="s">
         <v>653</v>
       </c>
-      <c r="FG2" s="11" t="s">
+      <c r="FG2" s="10" t="s">
         <v>209</v>
       </c>
       <c r="FH2" t="s">
@@ -9710,31 +10281,31 @@
       <c r="EG3" t="s">
         <v>442</v>
       </c>
-      <c r="EI3" s="11" t="s">
+      <c r="EI3" s="10" t="s">
         <v>443</v>
       </c>
-      <c r="EL3" s="11" t="s">
+      <c r="EL3" s="10" t="s">
         <v>444</v>
       </c>
-      <c r="EO3" s="11" t="s">
+      <c r="EO3" s="10" t="s">
         <v>445</v>
       </c>
-      <c r="ER3" s="11" t="s">
+      <c r="ER3" s="10" t="s">
         <v>446</v>
       </c>
-      <c r="EU3" s="11" t="s">
+      <c r="EU3" s="10" t="s">
         <v>447</v>
       </c>
-      <c r="EX3" s="11" t="s">
+      <c r="EX3" s="10" t="s">
         <v>448</v>
       </c>
-      <c r="FA3" s="11" t="s">
+      <c r="FA3" s="10" t="s">
         <v>449</v>
       </c>
-      <c r="FD3" s="11" t="s">
+      <c r="FD3" s="10" t="s">
         <v>450</v>
       </c>
-      <c r="FG3" s="11" t="s">
+      <c r="FG3" s="10" t="s">
         <v>451</v>
       </c>
       <c r="FK3">
@@ -9993,31 +10564,31 @@
       <c r="EG4" t="s">
         <v>442</v>
       </c>
-      <c r="EI4" s="11" t="s">
+      <c r="EI4" s="10" t="s">
         <v>471</v>
       </c>
-      <c r="EL4" s="11" t="s">
+      <c r="EL4" s="10" t="s">
         <v>472</v>
       </c>
-      <c r="EO4" s="11" t="s">
+      <c r="EO4" s="10" t="s">
         <v>473</v>
       </c>
-      <c r="ER4" s="11" t="s">
+      <c r="ER4" s="10" t="s">
         <v>474</v>
       </c>
-      <c r="EU4" s="11" t="s">
+      <c r="EU4" s="10" t="s">
         <v>475</v>
       </c>
-      <c r="EX4" s="11" t="s">
+      <c r="EX4" s="10" t="s">
         <v>476</v>
       </c>
-      <c r="FA4" s="11" t="s">
+      <c r="FA4" s="10" t="s">
         <v>477</v>
       </c>
-      <c r="FD4" s="11" t="s">
+      <c r="FD4" s="10" t="s">
         <v>478</v>
       </c>
-      <c r="FG4" s="11" t="s">
+      <c r="FG4" s="10" t="s">
         <v>479</v>
       </c>
       <c r="FK4">
@@ -10270,31 +10841,31 @@
       <c r="EG5" t="s">
         <v>442</v>
       </c>
-      <c r="EI5" s="11" t="s">
+      <c r="EI5" s="10" t="s">
         <v>488</v>
       </c>
-      <c r="EL5" s="11" t="s">
+      <c r="EL5" s="10" t="s">
         <v>489</v>
       </c>
-      <c r="EO5" s="11" t="s">
+      <c r="EO5" s="10" t="s">
         <v>490</v>
       </c>
-      <c r="ER5" s="11" t="s">
+      <c r="ER5" s="10" t="s">
         <v>491</v>
       </c>
-      <c r="EU5" s="11" t="s">
+      <c r="EU5" s="10" t="s">
         <v>492</v>
       </c>
-      <c r="EX5" s="11" t="s">
+      <c r="EX5" s="10" t="s">
         <v>493</v>
       </c>
-      <c r="FA5" s="11" t="s">
+      <c r="FA5" s="10" t="s">
         <v>494</v>
       </c>
-      <c r="FD5" s="11" t="s">
+      <c r="FD5" s="10" t="s">
         <v>495</v>
       </c>
-      <c r="FG5" s="11" t="s">
+      <c r="FG5" s="10" t="s">
         <v>496</v>
       </c>
       <c r="FK5">
@@ -10553,31 +11124,31 @@
       <c r="EG6" t="s">
         <v>442</v>
       </c>
-      <c r="EI6" s="11" t="s">
+      <c r="EI6" s="10" t="s">
         <v>512</v>
       </c>
-      <c r="EL6" s="11" t="s">
+      <c r="EL6" s="10" t="s">
         <v>513</v>
       </c>
-      <c r="EO6" s="11" t="s">
+      <c r="EO6" s="10" t="s">
         <v>514</v>
       </c>
-      <c r="ER6" s="11" t="s">
+      <c r="ER6" s="10" t="s">
         <v>515</v>
       </c>
-      <c r="EU6" s="11" t="s">
+      <c r="EU6" s="10" t="s">
         <v>516</v>
       </c>
-      <c r="EX6" s="11" t="s">
+      <c r="EX6" s="10" t="s">
         <v>517</v>
       </c>
-      <c r="FA6" s="11" t="s">
+      <c r="FA6" s="10" t="s">
         <v>518</v>
       </c>
-      <c r="FD6" s="11" t="s">
+      <c r="FD6" s="10" t="s">
         <v>519</v>
       </c>
-      <c r="FG6" s="11" t="s">
+      <c r="FG6" s="10" t="s">
         <v>520</v>
       </c>
       <c r="FK6">
@@ -10827,31 +11398,31 @@
       <c r="EG7" t="s">
         <v>442</v>
       </c>
-      <c r="EI7" s="11" t="s">
+      <c r="EI7" s="10" t="s">
         <v>541</v>
       </c>
-      <c r="EL7" s="11" t="s">
+      <c r="EL7" s="10" t="s">
         <v>542</v>
       </c>
-      <c r="EO7" s="11" t="s">
+      <c r="EO7" s="10" t="s">
         <v>543</v>
       </c>
-      <c r="ER7" s="11" t="s">
+      <c r="ER7" s="10" t="s">
         <v>544</v>
       </c>
-      <c r="EU7" s="11" t="s">
+      <c r="EU7" s="10" t="s">
         <v>545</v>
       </c>
-      <c r="EX7" s="11" t="s">
+      <c r="EX7" s="10" t="s">
         <v>546</v>
       </c>
-      <c r="FA7" s="11" t="s">
+      <c r="FA7" s="10" t="s">
         <v>547</v>
       </c>
-      <c r="FD7" s="11" t="s">
+      <c r="FD7" s="10" t="s">
         <v>548</v>
       </c>
-      <c r="FG7" s="11" t="s">
+      <c r="FG7" s="10" t="s">
         <v>549</v>
       </c>
       <c r="FK7">
@@ -11143,19 +11714,19 @@
       <c r="EG8" t="s">
         <v>442</v>
       </c>
-      <c r="EI8" s="11" t="s">
+      <c r="EI8" s="10" t="s">
         <v>1651</v>
       </c>
-      <c r="EL8" s="11" t="s">
+      <c r="EL8" s="10" t="s">
         <v>1652</v>
       </c>
-      <c r="ER8" s="11" t="s">
+      <c r="ER8" s="10" t="s">
         <v>1653</v>
       </c>
-      <c r="EX8" s="11" t="s">
+      <c r="EX8" s="10" t="s">
         <v>1654</v>
       </c>
-      <c r="FD8" s="11" t="s">
+      <c r="FD8" s="10" t="s">
         <v>1655</v>
       </c>
       <c r="FK8">
@@ -11435,10 +12006,10 @@
       <c r="EG9" t="s">
         <v>442</v>
       </c>
-      <c r="EI9" s="11" t="s">
+      <c r="EI9" s="10" t="s">
         <v>780</v>
       </c>
-      <c r="EX9" s="11" t="s">
+      <c r="EX9" s="10" t="s">
         <v>781</v>
       </c>
       <c r="FK9">
@@ -11730,28 +12301,28 @@
       <c r="EG10" t="s">
         <v>442</v>
       </c>
-      <c r="EI10" s="11" t="s">
+      <c r="EI10" s="10" t="s">
         <v>796</v>
       </c>
-      <c r="EL10" s="11" t="s">
+      <c r="EL10" s="10" t="s">
         <v>797</v>
       </c>
-      <c r="EO10" s="11" t="s">
+      <c r="EO10" s="10" t="s">
         <v>798</v>
       </c>
-      <c r="ER10" s="11" t="s">
+      <c r="ER10" s="10" t="s">
         <v>799</v>
       </c>
-      <c r="EU10" s="11" t="s">
+      <c r="EU10" s="10" t="s">
         <v>800</v>
       </c>
-      <c r="EX10" s="11" t="s">
+      <c r="EX10" s="10" t="s">
         <v>801</v>
       </c>
-      <c r="FA10" s="11" t="s">
+      <c r="FA10" s="10" t="s">
         <v>802</v>
       </c>
-      <c r="FD10" s="11" t="s">
+      <c r="FD10" s="10" t="s">
         <v>839</v>
       </c>
       <c r="FK10">
@@ -12046,31 +12617,31 @@
       <c r="EG11" t="s">
         <v>442</v>
       </c>
-      <c r="EI11" s="11" t="s">
+      <c r="EI11" s="10" t="s">
         <v>1662</v>
       </c>
-      <c r="EL11" s="11" t="s">
+      <c r="EL11" s="10" t="s">
         <v>1663</v>
       </c>
-      <c r="EO11" s="11" t="s">
+      <c r="EO11" s="10" t="s">
         <v>1664</v>
       </c>
-      <c r="ER11" s="11" t="s">
+      <c r="ER11" s="10" t="s">
         <v>1665</v>
       </c>
-      <c r="EU11" s="11" t="s">
+      <c r="EU11" s="10" t="s">
         <v>1666</v>
       </c>
-      <c r="EX11" s="11" t="s">
+      <c r="EX11" s="10" t="s">
         <v>1667</v>
       </c>
-      <c r="FA11" s="11" t="s">
+      <c r="FA11" s="10" t="s">
         <v>1668</v>
       </c>
-      <c r="FD11" s="11" t="s">
+      <c r="FD11" s="10" t="s">
         <v>1669</v>
       </c>
-      <c r="FG11" s="11" t="s">
+      <c r="FG11" s="10" t="s">
         <v>1670</v>
       </c>
       <c r="FJ11" t="s">
@@ -12362,19 +12933,19 @@
       <c r="EG12" t="s">
         <v>442</v>
       </c>
-      <c r="EI12" s="11" t="s">
+      <c r="EI12" s="10" t="s">
         <v>1700</v>
       </c>
-      <c r="EL12" s="11" t="s">
+      <c r="EL12" s="10" t="s">
         <v>1701</v>
       </c>
-      <c r="ER12" s="11" t="s">
+      <c r="ER12" s="10" t="s">
         <v>1702</v>
       </c>
-      <c r="EX12" s="11" t="s">
+      <c r="EX12" s="10" t="s">
         <v>1703</v>
       </c>
-      <c r="FD12" s="11" t="s">
+      <c r="FD12" s="10" t="s">
         <v>1704</v>
       </c>
       <c r="FK12">
@@ -12648,31 +13219,31 @@
       <c r="EG13" t="s">
         <v>442</v>
       </c>
-      <c r="EI13" s="11" t="s">
+      <c r="EI13" s="10" t="s">
         <v>1682</v>
       </c>
-      <c r="EL13" s="11" t="s">
+      <c r="EL13" s="10" t="s">
         <v>1683</v>
       </c>
-      <c r="EO13" s="11" t="s">
+      <c r="EO13" s="10" t="s">
         <v>1684</v>
       </c>
-      <c r="ER13" s="11" t="s">
+      <c r="ER13" s="10" t="s">
         <v>1685</v>
       </c>
-      <c r="EU13" s="11" t="s">
+      <c r="EU13" s="10" t="s">
         <v>1686</v>
       </c>
-      <c r="EX13" s="11" t="s">
+      <c r="EX13" s="10" t="s">
         <v>1687</v>
       </c>
-      <c r="FA13" s="11" t="s">
+      <c r="FA13" s="10" t="s">
         <v>1688</v>
       </c>
-      <c r="FD13" s="11" t="s">
+      <c r="FD13" s="10" t="s">
         <v>1689</v>
       </c>
-      <c r="FG13" s="11" t="s">
+      <c r="FG13" s="10" t="s">
         <v>1690</v>
       </c>
       <c r="FK13">
@@ -12731,7 +13302,7 @@
       <c r="C14" t="s">
         <v>946</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" t="s">
         <v>1085</v>
       </c>
       <c r="E14" t="s">
@@ -12928,7 +13499,7 @@
       <c r="EH14" t="s">
         <v>1090</v>
       </c>
-      <c r="EI14" s="11" t="s">
+      <c r="EI14" s="10" t="s">
         <v>1091</v>
       </c>
       <c r="EJ14" t="s">
@@ -12937,37 +13508,37 @@
       <c r="EK14" t="s">
         <v>1092</v>
       </c>
-      <c r="EL14" s="11" t="s">
+      <c r="EL14" s="10" t="s">
         <v>1093</v>
       </c>
       <c r="EN14" t="s">
         <v>1094</v>
       </c>
-      <c r="EO14" s="11" t="s">
+      <c r="EO14" s="10" t="s">
         <v>1095</v>
       </c>
       <c r="EQ14" t="s">
         <v>1096</v>
       </c>
-      <c r="ER14" s="11" t="s">
+      <c r="ER14" s="10" t="s">
         <v>1097</v>
       </c>
       <c r="ET14" t="s">
         <v>1098</v>
       </c>
-      <c r="EU14" s="11" t="s">
+      <c r="EU14" s="10" t="s">
         <v>1099</v>
       </c>
       <c r="EW14" t="s">
         <v>1100</v>
       </c>
-      <c r="EX14" s="11" t="s">
+      <c r="EX14" s="10" t="s">
         <v>1101</v>
       </c>
       <c r="EZ14" t="s">
         <v>1102</v>
       </c>
-      <c r="FA14" s="11" t="s">
+      <c r="FA14" s="10" t="s">
         <v>1103</v>
       </c>
       <c r="FC14" t="s">
@@ -13193,7 +13764,7 @@
       <c r="C15" t="s">
         <v>946</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" t="s">
         <v>1053</v>
       </c>
       <c r="E15" t="s">
@@ -13414,7 +13985,7 @@
       <c r="EH15" t="s">
         <v>912</v>
       </c>
-      <c r="EI15" s="11" t="s">
+      <c r="EI15" s="10" t="s">
         <v>913</v>
       </c>
       <c r="EJ15" t="s">
@@ -13423,7 +13994,7 @@
       <c r="EK15" t="s">
         <v>914</v>
       </c>
-      <c r="EL15" s="11" t="s">
+      <c r="EL15" s="10" t="s">
         <v>915</v>
       </c>
       <c r="EM15" t="s">
@@ -13432,7 +14003,7 @@
       <c r="EN15" t="s">
         <v>916</v>
       </c>
-      <c r="EO15" s="11" t="s">
+      <c r="EO15" s="10" t="s">
         <v>917</v>
       </c>
       <c r="EP15" t="s">
@@ -13441,7 +14012,7 @@
       <c r="EQ15" t="s">
         <v>918</v>
       </c>
-      <c r="ER15" s="11" t="s">
+      <c r="ER15" s="10" t="s">
         <v>919</v>
       </c>
       <c r="ES15" t="s">
@@ -13450,7 +14021,7 @@
       <c r="ET15" t="s">
         <v>920</v>
       </c>
-      <c r="EU15" s="11" t="s">
+      <c r="EU15" s="10" t="s">
         <v>921</v>
       </c>
       <c r="EV15" t="s">
@@ -13459,7 +14030,7 @@
       <c r="EW15" t="s">
         <v>922</v>
       </c>
-      <c r="EX15" s="11" t="s">
+      <c r="EX15" s="10" t="s">
         <v>923</v>
       </c>
       <c r="EY15" t="s">
@@ -13468,7 +14039,7 @@
       <c r="EZ15" t="s">
         <v>925</v>
       </c>
-      <c r="FA15" s="11" t="s">
+      <c r="FA15" s="10" t="s">
         <v>926</v>
       </c>
       <c r="FB15" t="s">
@@ -13477,7 +14048,7 @@
       <c r="FC15" t="s">
         <v>927</v>
       </c>
-      <c r="FD15" s="11" t="s">
+      <c r="FD15" s="10" t="s">
         <v>928</v>
       </c>
       <c r="FE15" t="s">
@@ -13486,7 +14057,7 @@
       <c r="FF15" t="s">
         <v>929</v>
       </c>
-      <c r="FG15" s="11" t="s">
+      <c r="FG15" s="10" t="s">
         <v>930</v>
       </c>
       <c r="FH15" t="s">
@@ -13766,7 +14337,7 @@
       <c r="C16" t="s">
         <v>946</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" t="s">
         <v>1725</v>
       </c>
       <c r="E16" t="s">
@@ -13966,14 +14537,14 @@
       <c r="EG16" t="s">
         <v>442</v>
       </c>
-      <c r="EI16" s="11" t="s">
+      <c r="EI16" s="10" t="s">
         <v>1314</v>
       </c>
       <c r="EJ16" s="1"/>
       <c r="EK16" t="s">
         <v>1315</v>
       </c>
-      <c r="EL16" s="11" t="s">
+      <c r="EL16" s="10" t="s">
         <v>1316</v>
       </c>
       <c r="EM16" t="s">
@@ -13982,7 +14553,7 @@
       <c r="EN16" t="s">
         <v>1318</v>
       </c>
-      <c r="EO16" s="11" t="s">
+      <c r="EO16" s="10" t="s">
         <v>1319</v>
       </c>
       <c r="EP16" t="s">
@@ -13991,7 +14562,7 @@
       <c r="EQ16" t="s">
         <v>1320</v>
       </c>
-      <c r="ER16" s="11" t="s">
+      <c r="ER16" s="10" t="s">
         <v>1321</v>
       </c>
       <c r="ES16" t="s">
@@ -14000,7 +14571,7 @@
       <c r="ET16" t="s">
         <v>1322</v>
       </c>
-      <c r="EU16" s="11" t="s">
+      <c r="EU16" s="10" t="s">
         <v>1323</v>
       </c>
       <c r="EV16" t="s">
@@ -14009,7 +14580,7 @@
       <c r="EW16" t="s">
         <v>1324</v>
       </c>
-      <c r="EX16" s="11" t="s">
+      <c r="EX16" s="10" t="s">
         <v>1325</v>
       </c>
       <c r="EY16" t="s">
@@ -14018,7 +14589,7 @@
       <c r="EZ16" t="s">
         <v>1326</v>
       </c>
-      <c r="FA16" s="11" t="s">
+      <c r="FA16" s="10" t="s">
         <v>1327</v>
       </c>
       <c r="FB16" t="s">
@@ -14027,7 +14598,7 @@
       <c r="FC16" t="s">
         <v>1328</v>
       </c>
-      <c r="FD16" s="11" t="s">
+      <c r="FD16" s="10" t="s">
         <v>1329</v>
       </c>
       <c r="FE16" t="s">
@@ -14254,7 +14825,7 @@
       <c r="C17" t="s">
         <v>946</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" t="s">
         <v>1418</v>
       </c>
       <c r="E17" t="s">
@@ -14448,7 +15019,7 @@
       <c r="EH17" t="s">
         <v>1423</v>
       </c>
-      <c r="EI17" s="11" t="s">
+      <c r="EI17" s="10" t="s">
         <v>1424</v>
       </c>
       <c r="EJ17" t="s">
@@ -14457,7 +15028,7 @@
       <c r="EK17" t="s">
         <v>1425</v>
       </c>
-      <c r="EL17" s="11" t="s">
+      <c r="EL17" s="10" t="s">
         <v>1426</v>
       </c>
       <c r="EM17" t="s">
@@ -14466,7 +15037,7 @@
       <c r="EN17" t="s">
         <v>1427</v>
       </c>
-      <c r="EO17" s="11" t="s">
+      <c r="EO17" s="10" t="s">
         <v>1428</v>
       </c>
       <c r="EP17" t="s">
@@ -14475,7 +15046,7 @@
       <c r="EQ17" t="s">
         <v>1429</v>
       </c>
-      <c r="ER17" s="11" t="s">
+      <c r="ER17" s="10" t="s">
         <v>1430</v>
       </c>
       <c r="ES17" t="s">
@@ -14484,7 +15055,7 @@
       <c r="ET17" t="s">
         <v>1431</v>
       </c>
-      <c r="EU17" s="11" t="s">
+      <c r="EU17" s="10" t="s">
         <v>1432</v>
       </c>
       <c r="EV17" t="s">
@@ -14493,7 +15064,7 @@
       <c r="EW17" t="s">
         <v>1433</v>
       </c>
-      <c r="EX17" s="11" t="s">
+      <c r="EX17" s="10" t="s">
         <v>1434</v>
       </c>
       <c r="EY17" t="s">
@@ -14502,7 +15073,7 @@
       <c r="EZ17" t="s">
         <v>1435</v>
       </c>
-      <c r="FA17" s="11" t="s">
+      <c r="FA17" s="10" t="s">
         <v>1436</v>
       </c>
       <c r="FB17" t="s">
@@ -14511,7 +15082,7 @@
       <c r="FC17" t="s">
         <v>1437</v>
       </c>
-      <c r="FD17" s="11" t="s">
+      <c r="FD17" s="10" t="s">
         <v>1438</v>
       </c>
       <c r="FE17" t="s">
@@ -14743,7 +15314,7 @@
       <c r="C18" t="s">
         <v>946</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" t="s">
         <v>1129</v>
       </c>
       <c r="E18" t="s">
@@ -14946,7 +15517,7 @@
       <c r="EH18" t="s">
         <v>1136</v>
       </c>
-      <c r="EI18" s="11" t="s">
+      <c r="EI18" s="10" t="s">
         <v>1137</v>
       </c>
       <c r="EJ18" t="s">
@@ -14955,7 +15526,7 @@
       <c r="EK18" t="s">
         <v>1138</v>
       </c>
-      <c r="EL18" s="11" t="s">
+      <c r="EL18" s="10" t="s">
         <v>1139</v>
       </c>
       <c r="EM18" t="s">
@@ -14964,7 +15535,7 @@
       <c r="EN18" t="s">
         <v>1141</v>
       </c>
-      <c r="EO18" s="11" t="s">
+      <c r="EO18" s="10" t="s">
         <v>1142</v>
       </c>
       <c r="EP18" t="s">
@@ -14973,7 +15544,7 @@
       <c r="EQ18" t="s">
         <v>1143</v>
       </c>
-      <c r="ER18" s="11" t="s">
+      <c r="ER18" s="10" t="s">
         <v>1144</v>
       </c>
       <c r="ES18" t="s">
@@ -14982,7 +15553,7 @@
       <c r="ET18" t="s">
         <v>1145</v>
       </c>
-      <c r="EU18" s="11" t="s">
+      <c r="EU18" s="10" t="s">
         <v>1146</v>
       </c>
       <c r="EV18" t="s">
@@ -14991,7 +15562,7 @@
       <c r="EW18" t="s">
         <v>1147</v>
       </c>
-      <c r="EX18" s="11" t="s">
+      <c r="EX18" s="10" t="s">
         <v>1148</v>
       </c>
       <c r="EY18" t="s">
@@ -15000,7 +15571,7 @@
       <c r="EZ18" t="s">
         <v>1149</v>
       </c>
-      <c r="FA18" s="11" t="s">
+      <c r="FA18" s="10" t="s">
         <v>1144</v>
       </c>
       <c r="FB18" t="s">
@@ -15009,7 +15580,7 @@
       <c r="FC18" t="s">
         <v>1145</v>
       </c>
-      <c r="FD18" s="11" t="s">
+      <c r="FD18" s="10" t="s">
         <v>1139</v>
       </c>
       <c r="FE18" t="s">
@@ -15018,7 +15589,7 @@
       <c r="FF18" t="s">
         <v>1141</v>
       </c>
-      <c r="FG18" s="11" t="s">
+      <c r="FG18" s="10" t="s">
         <v>1142</v>
       </c>
       <c r="FH18" t="s">
@@ -15259,7 +15830,7 @@
       <c r="C19" t="s">
         <v>946</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" t="s">
         <v>1230</v>
       </c>
       <c r="E19" t="s">
@@ -15453,7 +16024,7 @@
       <c r="EH19" t="s">
         <v>1236</v>
       </c>
-      <c r="EI19" s="11" t="s">
+      <c r="EI19" s="10" t="s">
         <v>1237</v>
       </c>
       <c r="EJ19" t="s">
@@ -15462,7 +16033,7 @@
       <c r="EK19" t="s">
         <v>1238</v>
       </c>
-      <c r="EL19" s="11" t="s">
+      <c r="EL19" s="10" t="s">
         <v>1239</v>
       </c>
       <c r="EM19" t="s">
@@ -15471,7 +16042,7 @@
       <c r="EN19" t="s">
         <v>1240</v>
       </c>
-      <c r="ER19" s="11" t="s">
+      <c r="ER19" s="10" t="s">
         <v>1241</v>
       </c>
       <c r="ES19" t="s">
@@ -15480,7 +16051,7 @@
       <c r="ET19" t="s">
         <v>1242</v>
       </c>
-      <c r="EU19" s="11" t="s">
+      <c r="EU19" s="10" t="s">
         <v>1243</v>
       </c>
       <c r="EV19" t="s">
@@ -15489,7 +16060,7 @@
       <c r="EW19" t="s">
         <v>1244</v>
       </c>
-      <c r="EX19" s="11" t="s">
+      <c r="EX19" s="10" t="s">
         <v>1245</v>
       </c>
       <c r="EY19" t="s">
@@ -15498,7 +16069,7 @@
       <c r="EZ19" t="s">
         <v>1246</v>
       </c>
-      <c r="FA19" s="11" t="s">
+      <c r="FA19" s="10" t="s">
         <v>1247</v>
       </c>
       <c r="FB19" t="s">
@@ -15507,7 +16078,7 @@
       <c r="FC19" t="s">
         <v>1248</v>
       </c>
-      <c r="FD19" s="11" t="s">
+      <c r="FD19" s="10" t="s">
         <v>1249</v>
       </c>
       <c r="FE19" t="s">
@@ -15516,7 +16087,7 @@
       <c r="FF19" t="s">
         <v>1250</v>
       </c>
-      <c r="FG19" s="11" t="s">
+      <c r="FG19" s="10" t="s">
         <v>1251</v>
       </c>
       <c r="FH19" t="s">
@@ -15749,7 +16320,7 @@
       <c r="C20" t="s">
         <v>946</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" t="s">
         <v>1623</v>
       </c>
       <c r="E20" t="s">
@@ -15889,7 +16460,7 @@
       <c r="EH20" t="s">
         <v>1280</v>
       </c>
-      <c r="EI20" s="11" t="s">
+      <c r="EI20" s="10" t="s">
         <v>1624</v>
       </c>
       <c r="EJ20" t="s">
@@ -15898,7 +16469,7 @@
       <c r="EK20" t="s">
         <v>1625</v>
       </c>
-      <c r="EL20" s="11" t="s">
+      <c r="EL20" s="10" t="s">
         <v>1626</v>
       </c>
       <c r="EM20" t="s">
@@ -15907,7 +16478,7 @@
       <c r="EN20" t="s">
         <v>1627</v>
       </c>
-      <c r="EO20" s="11" t="s">
+      <c r="EO20" s="10" t="s">
         <v>1628</v>
       </c>
       <c r="EP20" t="s">
@@ -15916,7 +16487,7 @@
       <c r="EQ20" t="s">
         <v>1629</v>
       </c>
-      <c r="ER20" s="11" t="s">
+      <c r="ER20" s="10" t="s">
         <v>1630</v>
       </c>
       <c r="ES20" t="s">
@@ -15925,7 +16496,7 @@
       <c r="ET20" t="s">
         <v>1631</v>
       </c>
-      <c r="EU20" s="11" t="s">
+      <c r="EU20" s="10" t="s">
         <v>1632</v>
       </c>
       <c r="EV20" t="s">
@@ -15934,7 +16505,7 @@
       <c r="EW20" t="s">
         <v>1633</v>
       </c>
-      <c r="EX20" s="11" t="s">
+      <c r="EX20" s="10" t="s">
         <v>1634</v>
       </c>
       <c r="EY20" t="s">
@@ -15943,7 +16514,7 @@
       <c r="EZ20" t="s">
         <v>1635</v>
       </c>
-      <c r="FA20" s="11" t="s">
+      <c r="FA20" s="10" t="s">
         <v>1636</v>
       </c>
       <c r="FB20" t="s">
@@ -15952,7 +16523,7 @@
       <c r="FC20" t="s">
         <v>1637</v>
       </c>
-      <c r="FD20" s="11" t="s">
+      <c r="FD20" s="10" t="s">
         <v>1638</v>
       </c>
       <c r="FE20" t="s">
@@ -15961,7 +16532,7 @@
       <c r="FF20" t="s">
         <v>1639</v>
       </c>
-      <c r="FG20" s="11" t="s">
+      <c r="FG20" s="10" t="s">
         <v>1640</v>
       </c>
       <c r="FH20" t="s">
@@ -16224,7 +16795,7 @@
       <c r="C21" t="s">
         <v>946</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" t="s">
         <v>1054</v>
       </c>
       <c r="E21" t="s">
@@ -16421,13 +16992,13 @@
       <c r="EH21" t="s">
         <v>952</v>
       </c>
-      <c r="EI21" s="11" t="s">
+      <c r="EI21" s="10" t="s">
         <v>953</v>
       </c>
       <c r="EJ21" t="s">
         <v>1228</v>
       </c>
-      <c r="EL21" s="11" t="s">
+      <c r="EL21" s="10" t="s">
         <v>954</v>
       </c>
       <c r="EM21" t="s">
@@ -16436,7 +17007,7 @@
       <c r="EN21" t="s">
         <v>955</v>
       </c>
-      <c r="EO21" s="11" t="s">
+      <c r="EO21" s="10" t="s">
         <v>956</v>
       </c>
       <c r="EP21" t="s">
@@ -16445,7 +17016,7 @@
       <c r="EQ21" t="s">
         <v>957</v>
       </c>
-      <c r="ER21" s="11" t="s">
+      <c r="ER21" s="10" t="s">
         <v>958</v>
       </c>
       <c r="ES21" t="s">
@@ -16454,7 +17025,7 @@
       <c r="ET21" t="s">
         <v>959</v>
       </c>
-      <c r="EU21" s="11" t="s">
+      <c r="EU21" s="10" t="s">
         <v>960</v>
       </c>
       <c r="EV21" t="s">
@@ -16463,7 +17034,7 @@
       <c r="EW21" t="s">
         <v>961</v>
       </c>
-      <c r="EX21" s="11" t="s">
+      <c r="EX21" s="10" t="s">
         <v>962</v>
       </c>
       <c r="EY21" t="s">
@@ -16472,7 +17043,7 @@
       <c r="EZ21" t="s">
         <v>963</v>
       </c>
-      <c r="FA21" s="11" t="s">
+      <c r="FA21" s="10" t="s">
         <v>964</v>
       </c>
       <c r="FB21" t="s">
@@ -16481,7 +17052,7 @@
       <c r="FC21" t="s">
         <v>965</v>
       </c>
-      <c r="FD21" s="11" t="s">
+      <c r="FD21" s="10" t="s">
         <v>966</v>
       </c>
       <c r="FE21" t="s">
@@ -16710,7 +17281,7 @@
       <c r="C22" t="s">
         <v>946</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" t="s">
         <v>1465</v>
       </c>
       <c r="E22" t="s">
@@ -16910,7 +17481,7 @@
       <c r="EH22" t="s">
         <v>1471</v>
       </c>
-      <c r="EI22" s="11" t="s">
+      <c r="EI22" s="10" t="s">
         <v>1472</v>
       </c>
       <c r="EJ22" t="s">
@@ -16919,7 +17490,7 @@
       <c r="EK22" t="s">
         <v>1473</v>
       </c>
-      <c r="EL22" s="11" t="s">
+      <c r="EL22" s="10" t="s">
         <v>1474</v>
       </c>
       <c r="EM22" t="s">
@@ -16928,7 +17499,7 @@
       <c r="EN22" t="s">
         <v>1475</v>
       </c>
-      <c r="EO22" s="11" t="s">
+      <c r="EO22" s="10" t="s">
         <v>1476</v>
       </c>
       <c r="EP22" t="s">
@@ -16937,7 +17508,7 @@
       <c r="EQ22" t="s">
         <v>1477</v>
       </c>
-      <c r="ER22" s="11" t="s">
+      <c r="ER22" s="10" t="s">
         <v>1478</v>
       </c>
       <c r="ES22" t="s">
@@ -16946,7 +17517,7 @@
       <c r="ET22" t="s">
         <v>1479</v>
       </c>
-      <c r="EU22" s="11" t="s">
+      <c r="EU22" s="10" t="s">
         <v>1480</v>
       </c>
       <c r="EV22" t="s">
@@ -16955,7 +17526,7 @@
       <c r="EW22" t="s">
         <v>1481</v>
       </c>
-      <c r="EX22" s="11" t="s">
+      <c r="EX22" s="10" t="s">
         <v>1461</v>
       </c>
       <c r="EY22" t="s">
@@ -16964,7 +17535,7 @@
       <c r="EZ22" t="s">
         <v>1462</v>
       </c>
-      <c r="FA22" s="11" t="s">
+      <c r="FA22" s="10" t="s">
         <v>1482</v>
       </c>
       <c r="FB22" t="s">
@@ -16973,7 +17544,7 @@
       <c r="FC22" t="s">
         <v>1483</v>
       </c>
-      <c r="FD22" s="11" t="s">
+      <c r="FD22" s="10" t="s">
         <v>1484</v>
       </c>
       <c r="FE22" t="s">
@@ -16982,7 +17553,7 @@
       <c r="FF22" t="s">
         <v>1485</v>
       </c>
-      <c r="FG22" s="11" t="s">
+      <c r="FG22" s="10" t="s">
         <v>1486</v>
       </c>
       <c r="FH22" t="s">
@@ -17214,7 +17785,7 @@
       <c r="C23" t="s">
         <v>946</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" t="s">
         <v>1705</v>
       </c>
       <c r="E23" t="s">
@@ -17459,7 +18030,7 @@
       <c r="EC23" t="s">
         <v>1787</v>
       </c>
-      <c r="ED23" s="9" t="s">
+      <c r="ED23" s="8" t="s">
         <v>1788</v>
       </c>
       <c r="EE23" t="s">
@@ -17474,7 +18045,7 @@
       <c r="EH23" t="s">
         <v>1604</v>
       </c>
-      <c r="EI23" s="11" t="s">
+      <c r="EI23" s="10" t="s">
         <v>1605</v>
       </c>
       <c r="EJ23" t="s">
@@ -17483,7 +18054,7 @@
       <c r="EK23" t="s">
         <v>1606</v>
       </c>
-      <c r="EL23" s="11" t="s">
+      <c r="EL23" s="10" t="s">
         <v>1607</v>
       </c>
       <c r="EM23" t="s">
@@ -17492,7 +18063,7 @@
       <c r="EN23" t="s">
         <v>1608</v>
       </c>
-      <c r="EO23" s="11" t="s">
+      <c r="EO23" s="10" t="s">
         <v>1609</v>
       </c>
       <c r="EP23" t="s">
@@ -17501,7 +18072,7 @@
       <c r="EQ23" t="s">
         <v>1610</v>
       </c>
-      <c r="ER23" s="11" t="s">
+      <c r="ER23" s="10" t="s">
         <v>1611</v>
       </c>
       <c r="ES23" t="s">
@@ -17510,7 +18081,7 @@
       <c r="ET23" t="s">
         <v>1612</v>
       </c>
-      <c r="EU23" s="11" t="s">
+      <c r="EU23" s="10" t="s">
         <v>1613</v>
       </c>
       <c r="EV23" t="s">
@@ -17519,7 +18090,7 @@
       <c r="EW23" t="s">
         <v>1614</v>
       </c>
-      <c r="EX23" s="11" t="s">
+      <c r="EX23" s="10" t="s">
         <v>1615</v>
       </c>
       <c r="EY23" t="s">
@@ -17528,7 +18099,7 @@
       <c r="EZ23" t="s">
         <v>1616</v>
       </c>
-      <c r="FA23" s="11" t="s">
+      <c r="FA23" s="10" t="s">
         <v>1617</v>
       </c>
       <c r="FB23" t="s">
@@ -17537,7 +18108,7 @@
       <c r="FC23" t="s">
         <v>1618</v>
       </c>
-      <c r="FD23" s="11" t="s">
+      <c r="FD23" s="10" t="s">
         <v>1619</v>
       </c>
       <c r="FE23" t="s">
@@ -17546,7 +18117,7 @@
       <c r="FF23" t="s">
         <v>1620</v>
       </c>
-      <c r="FG23" s="11" t="s">
+      <c r="FG23" s="10" t="s">
         <v>1621</v>
       </c>
       <c r="FH23" t="s">
@@ -17803,7 +18374,7 @@
       <c r="C24" t="s">
         <v>946</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" t="s">
         <v>1580</v>
       </c>
       <c r="E24" t="s">
@@ -18070,7 +18641,7 @@
       <c r="EH24" t="s">
         <v>1585</v>
       </c>
-      <c r="EI24" s="11" t="s">
+      <c r="EI24" s="10" t="s">
         <v>1586</v>
       </c>
       <c r="EJ24" t="s">
@@ -18079,7 +18650,7 @@
       <c r="EK24" t="s">
         <v>1587</v>
       </c>
-      <c r="EL24" s="11" t="s">
+      <c r="EL24" s="10" t="s">
         <v>1588</v>
       </c>
       <c r="EM24" t="s">
@@ -18088,7 +18659,7 @@
       <c r="EN24" t="s">
         <v>1589</v>
       </c>
-      <c r="EO24" s="11" t="s">
+      <c r="EO24" s="10" t="s">
         <v>1590</v>
       </c>
       <c r="EP24" t="s">
@@ -18097,7 +18668,7 @@
       <c r="EQ24" t="s">
         <v>1591</v>
       </c>
-      <c r="ER24" s="11" t="s">
+      <c r="ER24" s="10" t="s">
         <v>1592</v>
       </c>
       <c r="ES24" t="s">
@@ -18106,7 +18677,7 @@
       <c r="ET24" t="s">
         <v>1593</v>
       </c>
-      <c r="EU24" s="11" t="s">
+      <c r="EU24" s="10" t="s">
         <v>1594</v>
       </c>
       <c r="EV24" t="s">
@@ -18115,7 +18686,7 @@
       <c r="EW24" t="s">
         <v>1595</v>
       </c>
-      <c r="EX24" s="11" t="s">
+      <c r="EX24" s="10" t="s">
         <v>1596</v>
       </c>
       <c r="EY24" t="s">
@@ -18124,7 +18695,7 @@
       <c r="EZ24" t="s">
         <v>1597</v>
       </c>
-      <c r="FA24" s="11" t="s">
+      <c r="FA24" s="10" t="s">
         <v>1596</v>
       </c>
       <c r="FB24" t="s">
@@ -18133,7 +18704,7 @@
       <c r="FC24" t="s">
         <v>1597</v>
       </c>
-      <c r="FD24" s="11" t="s">
+      <c r="FD24" s="10" t="s">
         <v>1598</v>
       </c>
       <c r="FE24" t="s">
@@ -18142,7 +18713,7 @@
       <c r="FF24" t="s">
         <v>1599</v>
       </c>
-      <c r="FG24" s="11" t="s">
+      <c r="FG24" s="10" t="s">
         <v>1600</v>
       </c>
       <c r="FH24" t="s">
@@ -18402,7 +18973,7 @@
       <c r="C25" t="s">
         <v>946</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" t="s">
         <v>1886</v>
       </c>
       <c r="E25" t="s">
@@ -18656,7 +19227,7 @@
       <c r="EH25" t="s">
         <v>970</v>
       </c>
-      <c r="EI25" s="11" t="s">
+      <c r="EI25" s="10" t="s">
         <v>1874</v>
       </c>
       <c r="EJ25" t="s">
@@ -18665,7 +19236,7 @@
       <c r="EK25" t="s">
         <v>1875</v>
       </c>
-      <c r="EL25" s="11" t="s">
+      <c r="EL25" s="10" t="s">
         <v>1876</v>
       </c>
       <c r="EM25" t="s">
@@ -18674,7 +19245,7 @@
       <c r="EN25" t="s">
         <v>1877</v>
       </c>
-      <c r="EO25" s="11" t="s">
+      <c r="EO25" s="10" t="s">
         <v>1878</v>
       </c>
       <c r="EP25" t="s">
@@ -18683,7 +19254,7 @@
       <c r="EQ25" t="s">
         <v>1879</v>
       </c>
-      <c r="ER25" s="11" t="s">
+      <c r="ER25" s="10" t="s">
         <v>1880</v>
       </c>
       <c r="ES25" t="s">
@@ -18692,7 +19263,7 @@
       <c r="ET25" t="s">
         <v>1881</v>
       </c>
-      <c r="EU25" s="11" t="s">
+      <c r="EU25" s="10" t="s">
         <v>1882</v>
       </c>
       <c r="EV25" t="s">
@@ -18701,7 +19272,7 @@
       <c r="EW25" t="s">
         <v>1883</v>
       </c>
-      <c r="EX25" s="11" t="s">
+      <c r="EX25" s="10" t="s">
         <v>1884</v>
       </c>
       <c r="EY25" t="s">
@@ -18952,7 +19523,7 @@
       <c r="C26" t="s">
         <v>946</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" t="s">
         <v>1055</v>
       </c>
       <c r="E26" t="s">
@@ -19206,7 +19777,7 @@
       <c r="EH26" t="s">
         <v>970</v>
       </c>
-      <c r="EI26" s="11" t="s">
+      <c r="EI26" s="10" t="s">
         <v>971</v>
       </c>
       <c r="EJ26" s="1" t="s">
@@ -19215,7 +19786,7 @@
       <c r="EK26" t="s">
         <v>973</v>
       </c>
-      <c r="EL26" s="11" t="s">
+      <c r="EL26" s="10" t="s">
         <v>974</v>
       </c>
       <c r="EM26" t="s">
@@ -19224,7 +19795,7 @@
       <c r="EN26" t="s">
         <v>976</v>
       </c>
-      <c r="EO26" s="11" t="s">
+      <c r="EO26" s="10" t="s">
         <v>977</v>
       </c>
       <c r="EP26" t="s">
@@ -19233,7 +19804,7 @@
       <c r="EQ26" t="s">
         <v>978</v>
       </c>
-      <c r="ER26" s="11" t="s">
+      <c r="ER26" s="10" t="s">
         <v>979</v>
       </c>
       <c r="ES26" t="s">
@@ -19242,7 +19813,7 @@
       <c r="ET26" t="s">
         <v>980</v>
       </c>
-      <c r="EU26" s="11" t="s">
+      <c r="EU26" s="10" t="s">
         <v>981</v>
       </c>
       <c r="EV26" t="s">
@@ -19251,7 +19822,7 @@
       <c r="EW26" t="s">
         <v>982</v>
       </c>
-      <c r="FA26" s="11" t="s">
+      <c r="FA26" s="10" t="s">
         <v>983</v>
       </c>
       <c r="FB26" t="s">
@@ -19260,7 +19831,7 @@
       <c r="FC26" t="s">
         <v>984</v>
       </c>
-      <c r="FD26" s="11" t="s">
+      <c r="FD26" s="10" t="s">
         <v>985</v>
       </c>
       <c r="FE26" t="s">
@@ -19269,7 +19840,7 @@
       <c r="FF26" t="s">
         <v>986</v>
       </c>
-      <c r="FG26" s="11" t="s">
+      <c r="FG26" s="10" t="s">
         <v>987</v>
       </c>
       <c r="FH26" t="s">
@@ -19529,7 +20100,7 @@
       <c r="C27" t="s">
         <v>946</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" t="s">
         <v>1049</v>
       </c>
       <c r="E27" t="s">
@@ -19786,7 +20357,7 @@
       <c r="EH27" t="s">
         <v>1060</v>
       </c>
-      <c r="EI27" s="11" t="s">
+      <c r="EI27" s="10" t="s">
         <v>1061</v>
       </c>
       <c r="EJ27" t="s">
@@ -19795,7 +20366,7 @@
       <c r="EK27" t="s">
         <v>1062</v>
       </c>
-      <c r="EL27" s="11" t="s">
+      <c r="EL27" s="10" t="s">
         <v>1063</v>
       </c>
       <c r="EM27" t="s">
@@ -19804,7 +20375,7 @@
       <c r="EN27" t="s">
         <v>1064</v>
       </c>
-      <c r="EO27" s="11" t="s">
+      <c r="EO27" s="10" t="s">
         <v>1065</v>
       </c>
       <c r="EP27" t="s">
@@ -19813,7 +20384,7 @@
       <c r="EQ27" t="s">
         <v>1066</v>
       </c>
-      <c r="ER27" s="11" t="s">
+      <c r="ER27" s="10" t="s">
         <v>1067</v>
       </c>
       <c r="ES27" t="s">
@@ -19822,7 +20393,7 @@
       <c r="ET27" t="s">
         <v>1068</v>
       </c>
-      <c r="EU27" s="11" t="s">
+      <c r="EU27" s="10" t="s">
         <v>1069</v>
       </c>
       <c r="EV27" t="s">
@@ -19831,7 +20402,7 @@
       <c r="EW27" t="s">
         <v>1070</v>
       </c>
-      <c r="EX27" s="11" t="s">
+      <c r="EX27" s="10" t="s">
         <v>1071</v>
       </c>
       <c r="EY27" t="s">
@@ -19840,7 +20411,7 @@
       <c r="EZ27" t="s">
         <v>1072</v>
       </c>
-      <c r="FA27" s="11" t="s">
+      <c r="FA27" s="10" t="s">
         <v>1073</v>
       </c>
       <c r="FB27" t="s">
@@ -19849,7 +20420,7 @@
       <c r="FC27" t="s">
         <v>1074</v>
       </c>
-      <c r="FD27" s="11" t="s">
+      <c r="FD27" s="10" t="s">
         <v>1075</v>
       </c>
       <c r="FE27" t="s">
@@ -19858,7 +20429,7 @@
       <c r="FF27" t="s">
         <v>1076</v>
       </c>
-      <c r="FG27" s="11" t="s">
+      <c r="FG27" s="10" t="s">
         <v>1077</v>
       </c>
       <c r="FH27" t="s">
@@ -20133,7 +20704,7 @@
       <c r="C28" t="s">
         <v>946</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" t="s">
         <v>1440</v>
       </c>
       <c r="E28" t="s">
@@ -20384,7 +20955,7 @@
       <c r="EH28" t="s">
         <v>1445</v>
       </c>
-      <c r="EI28" s="11" t="s">
+      <c r="EI28" s="10" t="s">
         <v>1446</v>
       </c>
       <c r="EJ28" t="s">
@@ -20393,10 +20964,10 @@
       <c r="EK28" t="s">
         <v>1447</v>
       </c>
-      <c r="EL28" s="11" t="s">
+      <c r="EL28" s="10" t="s">
         <v>1448</v>
       </c>
-      <c r="EO28" s="11" t="s">
+      <c r="EO28" s="10" t="s">
         <v>1449</v>
       </c>
       <c r="EP28" t="s">
@@ -20405,7 +20976,7 @@
       <c r="EQ28" t="s">
         <v>1450</v>
       </c>
-      <c r="ER28" s="11" t="s">
+      <c r="ER28" s="10" t="s">
         <v>1451</v>
       </c>
       <c r="ES28" t="s">
@@ -20414,7 +20985,7 @@
       <c r="ET28" t="s">
         <v>1452</v>
       </c>
-      <c r="EU28" s="11" t="s">
+      <c r="EU28" s="10" t="s">
         <v>1453</v>
       </c>
       <c r="EV28" t="s">
@@ -20423,7 +20994,7 @@
       <c r="EW28" t="s">
         <v>1454</v>
       </c>
-      <c r="EX28" s="11" t="s">
+      <c r="EX28" s="10" t="s">
         <v>1455</v>
       </c>
       <c r="EY28" t="s">
@@ -20432,7 +21003,7 @@
       <c r="EZ28" t="s">
         <v>1456</v>
       </c>
-      <c r="FA28" s="11" t="s">
+      <c r="FA28" s="10" t="s">
         <v>1457</v>
       </c>
       <c r="FB28" t="s">
@@ -20441,7 +21012,7 @@
       <c r="FC28" t="s">
         <v>1458</v>
       </c>
-      <c r="FD28" s="11" t="s">
+      <c r="FD28" s="10" t="s">
         <v>1459</v>
       </c>
       <c r="FE28" t="s">
@@ -20450,7 +21021,7 @@
       <c r="FF28" t="s">
         <v>1460</v>
       </c>
-      <c r="FG28" s="11" t="s">
+      <c r="FG28" s="10" t="s">
         <v>1461</v>
       </c>
       <c r="FH28" t="s">
@@ -20710,7 +21281,7 @@
       <c r="C29" t="s">
         <v>946</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" t="s">
         <v>1152</v>
       </c>
       <c r="E29" t="s">
@@ -20973,7 +21544,7 @@
       <c r="EH29" t="s">
         <v>1157</v>
       </c>
-      <c r="EI29" s="11" t="s">
+      <c r="EI29" s="10" t="s">
         <v>1158</v>
       </c>
       <c r="EJ29" t="s">
@@ -20982,7 +21553,7 @@
       <c r="EK29" t="s">
         <v>1159</v>
       </c>
-      <c r="EL29" s="11" t="s">
+      <c r="EL29" s="10" t="s">
         <v>1160</v>
       </c>
       <c r="EM29" t="s">
@@ -20991,7 +21562,7 @@
       <c r="EN29" t="s">
         <v>1161</v>
       </c>
-      <c r="EO29" s="11" t="s">
+      <c r="EO29" s="10" t="s">
         <v>1162</v>
       </c>
       <c r="EP29" t="s">
@@ -21000,7 +21571,7 @@
       <c r="EQ29" t="s">
         <v>1163</v>
       </c>
-      <c r="ER29" s="11" t="s">
+      <c r="ER29" s="10" t="s">
         <v>1164</v>
       </c>
       <c r="ES29" t="s">
@@ -21009,7 +21580,7 @@
       <c r="ET29" t="s">
         <v>1165</v>
       </c>
-      <c r="EU29" s="11" t="s">
+      <c r="EU29" s="10" t="s">
         <v>1166</v>
       </c>
       <c r="EV29" t="s">
@@ -21018,7 +21589,7 @@
       <c r="EW29" t="s">
         <v>1167</v>
       </c>
-      <c r="EX29" s="11" t="s">
+      <c r="EX29" s="10" t="s">
         <v>1168</v>
       </c>
       <c r="EY29" t="s">
@@ -21027,7 +21598,7 @@
       <c r="EZ29" t="s">
         <v>1169</v>
       </c>
-      <c r="FA29" s="11" t="s">
+      <c r="FA29" s="10" t="s">
         <v>1170</v>
       </c>
       <c r="FB29" t="s">
@@ -21036,7 +21607,7 @@
       <c r="FC29" t="s">
         <v>1171</v>
       </c>
-      <c r="FD29" s="11" t="s">
+      <c r="FD29" s="10" t="s">
         <v>1172</v>
       </c>
       <c r="FE29" t="s">
@@ -21045,7 +21616,7 @@
       <c r="FF29" t="s">
         <v>1173</v>
       </c>
-      <c r="FG29" s="11" t="s">
+      <c r="FG29" s="10" t="s">
         <v>1174</v>
       </c>
       <c r="FH29" t="s">
@@ -21320,7 +21891,7 @@
       <c r="C30" t="s">
         <v>946</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" t="s">
         <v>1253</v>
       </c>
       <c r="E30" t="s">
@@ -21586,7 +22157,7 @@
       <c r="EH30" t="s">
         <v>1281</v>
       </c>
-      <c r="EI30" s="11" t="s">
+      <c r="EI30" s="10" t="s">
         <v>1257</v>
       </c>
       <c r="EJ30" s="1" t="s">
@@ -21595,7 +22166,7 @@
       <c r="EK30" t="s">
         <v>1258</v>
       </c>
-      <c r="EL30" s="11" t="s">
+      <c r="EL30" s="10" t="s">
         <v>1259</v>
       </c>
       <c r="EM30" t="s">
@@ -21604,7 +22175,7 @@
       <c r="EN30" t="s">
         <v>1260</v>
       </c>
-      <c r="EO30" s="11" t="s">
+      <c r="EO30" s="10" t="s">
         <v>1261</v>
       </c>
       <c r="EP30" t="s">
@@ -21613,7 +22184,7 @@
       <c r="EQ30" t="s">
         <v>1262</v>
       </c>
-      <c r="ER30" s="11" t="s">
+      <c r="ER30" s="10" t="s">
         <v>1263</v>
       </c>
       <c r="ES30" t="s">
@@ -21622,7 +22193,7 @@
       <c r="ET30" t="s">
         <v>1264</v>
       </c>
-      <c r="EU30" s="11" t="s">
+      <c r="EU30" s="10" t="s">
         <v>1265</v>
       </c>
       <c r="EV30" t="s">
@@ -21631,7 +22202,7 @@
       <c r="EW30" t="s">
         <v>1266</v>
       </c>
-      <c r="EX30" s="11" t="s">
+      <c r="EX30" s="10" t="s">
         <v>1267</v>
       </c>
       <c r="EY30" t="s">
@@ -21640,7 +22211,7 @@
       <c r="EZ30" t="s">
         <v>1269</v>
       </c>
-      <c r="FA30" s="11" t="s">
+      <c r="FA30" s="10" t="s">
         <v>1270</v>
       </c>
       <c r="FB30" t="s">
@@ -21649,7 +22220,7 @@
       <c r="FC30" t="s">
         <v>1271</v>
       </c>
-      <c r="FD30" s="11" t="s">
+      <c r="FD30" s="10" t="s">
         <v>1272</v>
       </c>
       <c r="FE30" t="s">
@@ -21658,7 +22229,7 @@
       <c r="FF30" t="s">
         <v>1273</v>
       </c>
-      <c r="FG30" s="11" t="s">
+      <c r="FG30" s="10" t="s">
         <v>1274</v>
       </c>
       <c r="FH30" t="s">
@@ -21912,7 +22483,7 @@
       <c r="C31" t="s">
         <v>946</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" t="s">
         <v>1360</v>
       </c>
       <c r="E31" t="s">
@@ -22175,7 +22746,7 @@
       <c r="EH31" t="s">
         <v>1373</v>
       </c>
-      <c r="EI31" s="11" t="s">
+      <c r="EI31" s="10" t="s">
         <v>1374</v>
       </c>
       <c r="EJ31" s="1" t="s">
@@ -22184,7 +22755,7 @@
       <c r="EK31" t="s">
         <v>1375</v>
       </c>
-      <c r="EL31" s="11" t="s">
+      <c r="EL31" s="10" t="s">
         <v>1376</v>
       </c>
       <c r="EM31" t="s">
@@ -22193,7 +22764,7 @@
       <c r="EN31" t="s">
         <v>1377</v>
       </c>
-      <c r="EO31" s="11" t="s">
+      <c r="EO31" s="10" t="s">
         <v>1378</v>
       </c>
       <c r="EP31" t="s">
@@ -22202,7 +22773,7 @@
       <c r="EQ31" t="s">
         <v>1379</v>
       </c>
-      <c r="ER31" s="11" t="s">
+      <c r="ER31" s="10" t="s">
         <v>1380</v>
       </c>
       <c r="ES31" t="s">
@@ -22211,7 +22782,7 @@
       <c r="ET31" t="s">
         <v>1381</v>
       </c>
-      <c r="EU31" s="11" t="s">
+      <c r="EU31" s="10" t="s">
         <v>1382</v>
       </c>
       <c r="EV31" t="s">
@@ -22220,7 +22791,7 @@
       <c r="EW31" t="s">
         <v>1383</v>
       </c>
-      <c r="EX31" s="11" t="s">
+      <c r="EX31" s="10" t="s">
         <v>1384</v>
       </c>
       <c r="EY31" t="s">
@@ -22229,7 +22800,7 @@
       <c r="EZ31" t="s">
         <v>1385</v>
       </c>
-      <c r="FA31" s="11" t="s">
+      <c r="FA31" s="10" t="s">
         <v>1386</v>
       </c>
       <c r="FB31" t="s">
@@ -22238,7 +22809,7 @@
       <c r="FC31" t="s">
         <v>1387</v>
       </c>
-      <c r="FD31" s="11" t="s">
+      <c r="FD31" s="10" t="s">
         <v>1388</v>
       </c>
       <c r="FE31" t="s">
@@ -22247,7 +22818,7 @@
       <c r="FF31" t="s">
         <v>1389</v>
       </c>
-      <c r="FG31" s="11" t="s">
+      <c r="FG31" s="10" t="s">
         <v>1374</v>
       </c>
       <c r="FH31" t="s">
@@ -22498,7 +23069,7 @@
       <c r="C32" t="s">
         <v>946</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" t="s">
         <v>1057</v>
       </c>
       <c r="E32" t="s">
@@ -22758,7 +23329,7 @@
       <c r="EH32" t="s">
         <v>1025</v>
       </c>
-      <c r="EI32" s="11" t="s">
+      <c r="EI32" s="10" t="s">
         <v>1026</v>
       </c>
       <c r="EJ32" t="s">
@@ -22767,7 +23338,7 @@
       <c r="EK32" t="s">
         <v>1027</v>
       </c>
-      <c r="EL32" s="11" t="s">
+      <c r="EL32" s="10" t="s">
         <v>1028</v>
       </c>
       <c r="EM32" t="s">
@@ -22776,7 +23347,7 @@
       <c r="EN32" t="s">
         <v>1029</v>
       </c>
-      <c r="EO32" s="11" t="s">
+      <c r="EO32" s="10" t="s">
         <v>1030</v>
       </c>
       <c r="EP32" t="s">
@@ -22785,7 +23356,7 @@
       <c r="EQ32" t="s">
         <v>1031</v>
       </c>
-      <c r="ER32" s="11" t="s">
+      <c r="ER32" s="10" t="s">
         <v>1032</v>
       </c>
       <c r="ES32" t="s">
@@ -22794,7 +23365,7 @@
       <c r="ET32" t="s">
         <v>1033</v>
       </c>
-      <c r="EU32" s="11" t="s">
+      <c r="EU32" s="10" t="s">
         <v>1034</v>
       </c>
       <c r="EV32" t="s">
@@ -22803,7 +23374,7 @@
       <c r="EW32" t="s">
         <v>1035</v>
       </c>
-      <c r="EX32" s="11" t="s">
+      <c r="EX32" s="10" t="s">
         <v>1036</v>
       </c>
       <c r="EY32" t="s">
@@ -22812,7 +23383,7 @@
       <c r="EZ32" t="s">
         <v>1037</v>
       </c>
-      <c r="FA32" s="11" t="s">
+      <c r="FA32" s="10" t="s">
         <v>1038</v>
       </c>
       <c r="FB32" t="s">
@@ -22821,7 +23392,7 @@
       <c r="FC32" t="s">
         <v>1039</v>
       </c>
-      <c r="FD32" s="11" t="s">
+      <c r="FD32" s="10" t="s">
         <v>1040</v>
       </c>
       <c r="FE32" t="s">
@@ -22830,7 +23401,7 @@
       <c r="FF32" t="s">
         <v>1041</v>
       </c>
-      <c r="FG32" s="11" t="s">
+      <c r="FG32" s="10" t="s">
         <v>1042</v>
       </c>
       <c r="FH32" t="s">
@@ -23096,7 +23667,7 @@
       <c r="C33" t="s">
         <v>946</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" t="s">
         <v>1331</v>
       </c>
       <c r="E33" t="s">
@@ -23359,7 +23930,7 @@
       <c r="EH33" t="s">
         <v>1342</v>
       </c>
-      <c r="EI33" s="11" t="s">
+      <c r="EI33" s="10" t="s">
         <v>1343</v>
       </c>
       <c r="EJ33" s="1" t="s">
@@ -23368,7 +23939,7 @@
       <c r="EK33" t="s">
         <v>1344</v>
       </c>
-      <c r="EL33" s="11" t="s">
+      <c r="EL33" s="10" t="s">
         <v>1345</v>
       </c>
       <c r="EM33" t="s">
@@ -23377,7 +23948,7 @@
       <c r="EN33" t="s">
         <v>1346</v>
       </c>
-      <c r="EO33" s="11" t="s">
+      <c r="EO33" s="10" t="s">
         <v>1347</v>
       </c>
       <c r="EP33" t="s">
@@ -23386,7 +23957,7 @@
       <c r="EQ33" t="s">
         <v>1348</v>
       </c>
-      <c r="ER33" s="11" t="s">
+      <c r="ER33" s="10" t="s">
         <v>1349</v>
       </c>
       <c r="ES33" t="s">
@@ -23395,7 +23966,7 @@
       <c r="ET33" t="s">
         <v>1351</v>
       </c>
-      <c r="EU33" s="11" t="s">
+      <c r="EU33" s="10" t="s">
         <v>1350</v>
       </c>
       <c r="EV33" t="s">
@@ -23404,7 +23975,7 @@
       <c r="EW33" t="s">
         <v>1352</v>
       </c>
-      <c r="EX33" s="11" t="s">
+      <c r="EX33" s="10" t="s">
         <v>1353</v>
       </c>
       <c r="EY33" t="s">
@@ -23413,7 +23984,7 @@
       <c r="EZ33" t="s">
         <v>1354</v>
       </c>
-      <c r="FA33" s="11" t="s">
+      <c r="FA33" s="10" t="s">
         <v>1355</v>
       </c>
       <c r="FB33" t="s">
@@ -23422,7 +23993,7 @@
       <c r="FC33" t="s">
         <v>1348</v>
       </c>
-      <c r="FD33" s="11" t="s">
+      <c r="FD33" s="10" t="s">
         <v>1356</v>
       </c>
       <c r="FE33" t="s">
@@ -23431,7 +24002,7 @@
       <c r="FF33" t="s">
         <v>1357</v>
       </c>
-      <c r="FG33" s="11" t="s">
+      <c r="FG33" s="10" t="s">
         <v>1358</v>
       </c>
       <c r="FH33" t="s">
@@ -23682,7 +24253,7 @@
       <c r="C34" t="s">
         <v>946</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" t="s">
         <v>842</v>
       </c>
       <c r="E34" t="s">
@@ -23939,7 +24510,7 @@
       <c r="EH34" t="s">
         <v>859</v>
       </c>
-      <c r="EI34" s="11" t="s">
+      <c r="EI34" s="10" t="s">
         <v>860</v>
       </c>
       <c r="EJ34" t="s">
@@ -23948,7 +24519,7 @@
       <c r="EK34" t="s">
         <v>861</v>
       </c>
-      <c r="EL34" s="11" t="s">
+      <c r="EL34" s="10" t="s">
         <v>862</v>
       </c>
       <c r="EM34" t="s">
@@ -23957,7 +24528,7 @@
       <c r="EN34" t="s">
         <v>864</v>
       </c>
-      <c r="EO34" s="11" t="s">
+      <c r="EO34" s="10" t="s">
         <v>865</v>
       </c>
       <c r="EP34" t="s">
@@ -23966,7 +24537,7 @@
       <c r="EQ34" t="s">
         <v>867</v>
       </c>
-      <c r="ER34" s="11" t="s">
+      <c r="ER34" s="10" t="s">
         <v>868</v>
       </c>
       <c r="ES34" t="s">
@@ -23975,7 +24546,7 @@
       <c r="ET34" t="s">
         <v>870</v>
       </c>
-      <c r="EU34" s="11" t="s">
+      <c r="EU34" s="10" t="s">
         <v>871</v>
       </c>
       <c r="EV34" t="s">
@@ -23984,7 +24555,7 @@
       <c r="EW34" t="s">
         <v>873</v>
       </c>
-      <c r="EX34" s="11" t="s">
+      <c r="EX34" s="10" t="s">
         <v>874</v>
       </c>
       <c r="EY34" t="s">
@@ -23993,7 +24564,7 @@
       <c r="EZ34" t="s">
         <v>876</v>
       </c>
-      <c r="FA34" s="11" t="s">
+      <c r="FA34" s="10" t="s">
         <v>877</v>
       </c>
       <c r="FB34" t="s">
@@ -24002,7 +24573,7 @@
       <c r="FC34" t="s">
         <v>878</v>
       </c>
-      <c r="FD34" s="11" t="s">
+      <c r="FD34" s="10" t="s">
         <v>879</v>
       </c>
       <c r="FE34" t="s">
@@ -24011,7 +24582,7 @@
       <c r="FF34" t="s">
         <v>880</v>
       </c>
-      <c r="FG34" s="11" t="s">
+      <c r="FG34" s="10" t="s">
         <v>881</v>
       </c>
       <c r="FH34" t="s">
@@ -24382,7 +24953,7 @@
       <c r="C35" t="s">
         <v>946</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" t="s">
         <v>1538</v>
       </c>
       <c r="E35" t="s">
@@ -24648,7 +25219,7 @@
       <c r="EH35" t="s">
         <v>1545</v>
       </c>
-      <c r="EI35" s="11" t="s">
+      <c r="EI35" s="10" t="s">
         <v>1546</v>
       </c>
       <c r="EJ35" s="1" t="s">
@@ -24657,7 +25228,7 @@
       <c r="EK35" t="s">
         <v>1547</v>
       </c>
-      <c r="EL35" s="11" t="s">
+      <c r="EL35" s="10" t="s">
         <v>1548</v>
       </c>
       <c r="EM35" t="s">
@@ -24666,7 +25237,7 @@
       <c r="EN35" t="s">
         <v>1549</v>
       </c>
-      <c r="EO35" s="11" t="s">
+      <c r="EO35" s="10" t="s">
         <v>1550</v>
       </c>
       <c r="EP35" t="s">
@@ -24675,7 +25246,7 @@
       <c r="EQ35" t="s">
         <v>1551</v>
       </c>
-      <c r="ER35" s="11" t="s">
+      <c r="ER35" s="10" t="s">
         <v>1558</v>
       </c>
       <c r="ES35" t="s">
@@ -24684,7 +25255,7 @@
       <c r="ET35" t="s">
         <v>1559</v>
       </c>
-      <c r="EU35" s="11" t="s">
+      <c r="EU35" s="10" t="s">
         <v>1552</v>
       </c>
       <c r="EV35" t="s">
@@ -24693,7 +25264,7 @@
       <c r="EW35" t="s">
         <v>1553</v>
       </c>
-      <c r="EX35" s="11" t="s">
+      <c r="EX35" s="10" t="s">
         <v>1554</v>
       </c>
       <c r="EY35" t="s">
@@ -24702,7 +25273,7 @@
       <c r="EZ35" t="s">
         <v>1555</v>
       </c>
-      <c r="FA35" s="11" t="s">
+      <c r="FA35" s="10" t="s">
         <v>1556</v>
       </c>
       <c r="FB35" t="s">
@@ -24711,7 +25282,7 @@
       <c r="FC35" t="s">
         <v>1557</v>
       </c>
-      <c r="FD35" s="11" t="s">
+      <c r="FD35" s="10" t="s">
         <v>1560</v>
       </c>
       <c r="FE35" t="s">
@@ -24720,7 +25291,7 @@
       <c r="FF35" t="s">
         <v>1561</v>
       </c>
-      <c r="FG35" s="11" t="s">
+      <c r="FG35" s="10" t="s">
         <v>1562</v>
       </c>
       <c r="FH35" t="s">
@@ -25046,7 +25617,7 @@
       <c r="C36" t="s">
         <v>946</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" t="s">
         <v>1105</v>
       </c>
       <c r="E36" t="s">
@@ -25306,7 +25877,7 @@
       <c r="EH36" t="s">
         <v>1110</v>
       </c>
-      <c r="EI36" s="11" t="s">
+      <c r="EI36" s="10" t="s">
         <v>1111</v>
       </c>
       <c r="EJ36" t="s">
@@ -25315,7 +25886,7 @@
       <c r="EK36" t="s">
         <v>1112</v>
       </c>
-      <c r="EL36" s="11" t="s">
+      <c r="EL36" s="10" t="s">
         <v>1113</v>
       </c>
       <c r="EM36" t="s">
@@ -25324,7 +25895,7 @@
       <c r="EN36" t="s">
         <v>1114</v>
       </c>
-      <c r="EO36" s="11" t="s">
+      <c r="EO36" s="10" t="s">
         <v>1115</v>
       </c>
       <c r="EP36" t="s">
@@ -25333,7 +25904,7 @@
       <c r="EQ36" t="s">
         <v>1116</v>
       </c>
-      <c r="ER36" s="11" t="s">
+      <c r="ER36" s="10" t="s">
         <v>1117</v>
       </c>
       <c r="ES36" t="s">
@@ -25342,7 +25913,7 @@
       <c r="ET36" t="s">
         <v>1118</v>
       </c>
-      <c r="EU36" s="11" t="s">
+      <c r="EU36" s="10" t="s">
         <v>1119</v>
       </c>
       <c r="EV36" t="s">
@@ -25351,7 +25922,7 @@
       <c r="EW36" t="s">
         <v>1120</v>
       </c>
-      <c r="EX36" s="11" t="s">
+      <c r="EX36" s="10" t="s">
         <v>1121</v>
       </c>
       <c r="EY36" t="s">
@@ -25360,7 +25931,7 @@
       <c r="EZ36" t="s">
         <v>1122</v>
       </c>
-      <c r="FA36" s="11" t="s">
+      <c r="FA36" s="10" t="s">
         <v>1123</v>
       </c>
       <c r="FB36" t="s">
@@ -25369,7 +25940,7 @@
       <c r="FC36" t="s">
         <v>1124</v>
       </c>
-      <c r="FD36" s="11" t="s">
+      <c r="FD36" s="10" t="s">
         <v>1125</v>
       </c>
       <c r="FE36" t="s">
@@ -25378,7 +25949,7 @@
       <c r="FF36" t="s">
         <v>1126</v>
       </c>
-      <c r="FG36" s="11" t="s">
+      <c r="FG36" s="10" t="s">
         <v>1127</v>
       </c>
       <c r="FH36" t="s">
@@ -25629,7 +26200,7 @@
       <c r="C37" t="s">
         <v>946</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D37" t="s">
         <v>1056</v>
       </c>
       <c r="E37" t="s">
@@ -25889,7 +26460,7 @@
       <c r="EH37" t="s">
         <v>999</v>
       </c>
-      <c r="EI37" s="11" t="s">
+      <c r="EI37" s="10" t="s">
         <v>1000</v>
       </c>
       <c r="EJ37" t="s">
@@ -25898,7 +26469,7 @@
       <c r="EK37" t="s">
         <v>1001</v>
       </c>
-      <c r="EL37" s="11" t="s">
+      <c r="EL37" s="10" t="s">
         <v>1002</v>
       </c>
       <c r="EM37" t="s">
@@ -25907,7 +26478,7 @@
       <c r="EN37" t="s">
         <v>1003</v>
       </c>
-      <c r="EO37" s="11" t="s">
+      <c r="EO37" s="10" t="s">
         <v>1004</v>
       </c>
       <c r="EP37" t="s">
@@ -25916,7 +26487,7 @@
       <c r="EQ37" t="s">
         <v>1005</v>
       </c>
-      <c r="ER37" s="11" t="s">
+      <c r="ER37" s="10" t="s">
         <v>1006</v>
       </c>
       <c r="ES37" t="s">
@@ -25925,7 +26496,7 @@
       <c r="ET37" t="s">
         <v>1007</v>
       </c>
-      <c r="EU37" s="11" t="s">
+      <c r="EU37" s="10" t="s">
         <v>1008</v>
       </c>
       <c r="EV37" t="s">
@@ -25934,7 +26505,7 @@
       <c r="EW37" t="s">
         <v>1009</v>
       </c>
-      <c r="EX37" s="11" t="s">
+      <c r="EX37" s="10" t="s">
         <v>1010</v>
       </c>
       <c r="EY37" t="s">
@@ -25943,7 +26514,7 @@
       <c r="EZ37" t="s">
         <v>1011</v>
       </c>
-      <c r="FA37" s="11" t="s">
+      <c r="FA37" s="10" t="s">
         <v>1012</v>
       </c>
       <c r="FB37" t="s">
@@ -25952,7 +26523,7 @@
       <c r="FC37" t="s">
         <v>1013</v>
       </c>
-      <c r="FD37" s="11" t="s">
+      <c r="FD37" s="10" t="s">
         <v>1014</v>
       </c>
       <c r="FE37" t="s">
@@ -25961,7 +26532,7 @@
       <c r="FF37" t="s">
         <v>1015</v>
       </c>
-      <c r="FG37" s="11" t="s">
+      <c r="FG37" s="10" t="s">
         <v>1016</v>
       </c>
       <c r="FH37" t="s">
@@ -26209,7 +26780,7 @@
       <c r="C38" t="s">
         <v>946</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D38" t="s">
         <v>1514</v>
       </c>
       <c r="E38" t="s">
@@ -26469,7 +27040,7 @@
       <c r="EH38" t="s">
         <v>1520</v>
       </c>
-      <c r="EI38" s="11" t="s">
+      <c r="EI38" s="10" t="s">
         <v>1521</v>
       </c>
       <c r="EJ38" t="s">
@@ -26478,7 +27049,7 @@
       <c r="EK38" t="s">
         <v>1522</v>
       </c>
-      <c r="EL38" s="11" t="s">
+      <c r="EL38" s="10" t="s">
         <v>1523</v>
       </c>
       <c r="EM38" t="s">
@@ -26487,7 +27058,7 @@
       <c r="EN38" t="s">
         <v>1524</v>
       </c>
-      <c r="EO38" s="11" t="s">
+      <c r="EO38" s="10" t="s">
         <v>1525</v>
       </c>
       <c r="EP38" t="s">
@@ -26496,7 +27067,7 @@
       <c r="EQ38" t="s">
         <v>1526</v>
       </c>
-      <c r="ER38" s="11" t="s">
+      <c r="ER38" s="10" t="s">
         <v>1527</v>
       </c>
       <c r="ES38" t="s">
@@ -26505,7 +27076,7 @@
       <c r="ET38" t="s">
         <v>1528</v>
       </c>
-      <c r="EU38" s="11" t="s">
+      <c r="EU38" s="10" t="s">
         <v>1529</v>
       </c>
       <c r="EV38" t="s">
@@ -26514,7 +27085,7 @@
       <c r="EW38" t="s">
         <v>1530</v>
       </c>
-      <c r="EX38" s="11" t="s">
+      <c r="EX38" s="10" t="s">
         <v>1531</v>
       </c>
       <c r="EY38" t="s">
@@ -26523,7 +27094,7 @@
       <c r="EZ38" t="s">
         <v>1532</v>
       </c>
-      <c r="FA38" s="11" t="s">
+      <c r="FA38" s="10" t="s">
         <v>1533</v>
       </c>
       <c r="FB38" t="s">
@@ -26532,7 +27103,7 @@
       <c r="FC38" t="s">
         <v>1534</v>
       </c>
-      <c r="FD38" s="11" t="s">
+      <c r="FD38" s="10" t="s">
         <v>1535</v>
       </c>
       <c r="FE38" t="s">
@@ -26786,7 +27357,7 @@
       <c r="C39" t="s">
         <v>946</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D39" t="s">
         <v>1204</v>
       </c>
       <c r="E39" t="s">
@@ -27049,7 +27620,7 @@
       <c r="EH39" t="s">
         <v>1211</v>
       </c>
-      <c r="EI39" s="11" t="s">
+      <c r="EI39" s="10" t="s">
         <v>1212</v>
       </c>
       <c r="EJ39" s="1" t="s">
@@ -27058,7 +27629,7 @@
       <c r="EK39" t="s">
         <v>1213</v>
       </c>
-      <c r="EL39" s="11" t="s">
+      <c r="EL39" s="10" t="s">
         <v>1214</v>
       </c>
       <c r="EM39" t="s">
@@ -27067,7 +27638,7 @@
       <c r="EN39" t="s">
         <v>1215</v>
       </c>
-      <c r="EO39" s="11" t="s">
+      <c r="EO39" s="10" t="s">
         <v>1216</v>
       </c>
       <c r="EP39" t="s">
@@ -27076,7 +27647,7 @@
       <c r="EQ39" t="s">
         <v>1217</v>
       </c>
-      <c r="ER39" s="11" t="s">
+      <c r="ER39" s="10" t="s">
         <v>1218</v>
       </c>
       <c r="ES39" t="s">
@@ -27085,7 +27656,7 @@
       <c r="ET39" t="s">
         <v>1219</v>
       </c>
-      <c r="EU39" s="11" t="s">
+      <c r="EU39" s="10" t="s">
         <v>1220</v>
       </c>
       <c r="EV39" t="s">
@@ -27094,7 +27665,7 @@
       <c r="EW39" t="s">
         <v>1221</v>
       </c>
-      <c r="EX39" s="11" t="s">
+      <c r="EX39" s="10" t="s">
         <v>1222</v>
       </c>
       <c r="EY39" t="s">
@@ -27103,7 +27674,7 @@
       <c r="EZ39" t="s">
         <v>1223</v>
       </c>
-      <c r="FA39" s="11" t="s">
+      <c r="FA39" s="10" t="s">
         <v>1224</v>
       </c>
       <c r="FB39" t="s">
@@ -27112,13 +27683,13 @@
       <c r="FC39" t="s">
         <v>1225</v>
       </c>
-      <c r="FD39" s="11" t="s">
+      <c r="FD39" s="10" t="s">
         <v>1226</v>
       </c>
       <c r="FE39" t="s">
         <v>875</v>
       </c>
-      <c r="FG39" s="11" t="s">
+      <c r="FG39" s="10" t="s">
         <v>1227</v>
       </c>
       <c r="FH39" t="s">
@@ -27369,7 +27940,7 @@
       <c r="C40" t="s">
         <v>946</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D40" t="s">
         <v>1181</v>
       </c>
       <c r="E40" t="s">
@@ -27626,7 +28197,7 @@
       <c r="EH40" t="s">
         <v>1187</v>
       </c>
-      <c r="EI40" s="11" t="s">
+      <c r="EI40" s="10" t="s">
         <v>1186</v>
       </c>
       <c r="EJ40" t="s">
@@ -27635,7 +28206,7 @@
       <c r="EK40" t="s">
         <v>1188</v>
       </c>
-      <c r="EL40" s="11" t="s">
+      <c r="EL40" s="10" t="s">
         <v>1189</v>
       </c>
       <c r="EM40" t="s">
@@ -27644,7 +28215,7 @@
       <c r="EN40" t="s">
         <v>1190</v>
       </c>
-      <c r="EO40" s="11" t="s">
+      <c r="EO40" s="10" t="s">
         <v>1191</v>
       </c>
       <c r="EP40" t="s">
@@ -27653,7 +28224,7 @@
       <c r="EQ40" t="s">
         <v>1192</v>
       </c>
-      <c r="ER40" s="11" t="s">
+      <c r="ER40" s="10" t="s">
         <v>1193</v>
       </c>
       <c r="ES40" t="s">
@@ -27662,7 +28233,7 @@
       <c r="ET40" t="s">
         <v>1194</v>
       </c>
-      <c r="EU40" s="11" t="s">
+      <c r="EU40" s="10" t="s">
         <v>1195</v>
       </c>
       <c r="EV40" t="s">
@@ -27671,7 +28242,7 @@
       <c r="EW40" t="s">
         <v>1196</v>
       </c>
-      <c r="EX40" s="11" t="s">
+      <c r="EX40" s="10" t="s">
         <v>1197</v>
       </c>
       <c r="EY40" t="s">
@@ -27680,7 +28251,7 @@
       <c r="EZ40" t="s">
         <v>1198</v>
       </c>
-      <c r="FA40" s="11" t="s">
+      <c r="FA40" s="10" t="s">
         <v>1199</v>
       </c>
       <c r="FB40" t="s">
@@ -27689,10 +28260,10 @@
       <c r="FC40" t="s">
         <v>1200</v>
       </c>
-      <c r="FD40" s="11" t="s">
+      <c r="FD40" s="10" t="s">
         <v>1201</v>
       </c>
-      <c r="FG40" s="11" t="s">
+      <c r="FG40" s="10" t="s">
         <v>1202</v>
       </c>
       <c r="FH40" t="s">
@@ -27940,7 +28511,7 @@
       <c r="C41" t="s">
         <v>946</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D41" t="s">
         <v>1396</v>
       </c>
       <c r="E41" t="s">
@@ -28197,7 +28768,7 @@
       <c r="EH41" t="s">
         <v>1403</v>
       </c>
-      <c r="EI41" s="11" t="s">
+      <c r="EI41" s="10" t="s">
         <v>1404</v>
       </c>
       <c r="EJ41" t="s">
@@ -28206,7 +28777,7 @@
       <c r="EK41" t="s">
         <v>1405</v>
       </c>
-      <c r="EL41" s="11" t="s">
+      <c r="EL41" s="10" t="s">
         <v>1406</v>
       </c>
       <c r="EM41" t="s">
@@ -28215,7 +28786,7 @@
       <c r="EN41" t="s">
         <v>1407</v>
       </c>
-      <c r="EO41" s="11" t="s">
+      <c r="EO41" s="10" t="s">
         <v>1408</v>
       </c>
       <c r="EP41" t="s">
@@ -28224,7 +28795,7 @@
       <c r="EQ41" t="s">
         <v>1409</v>
       </c>
-      <c r="ER41" s="11" t="s">
+      <c r="ER41" s="10" t="s">
         <v>1410</v>
       </c>
       <c r="ES41" t="s">
@@ -28233,7 +28804,7 @@
       <c r="ET41" t="s">
         <v>1411</v>
       </c>
-      <c r="EU41" s="11" t="s">
+      <c r="EU41" s="10" t="s">
         <v>1412</v>
       </c>
       <c r="EV41" t="s">
@@ -28242,7 +28813,7 @@
       <c r="EW41" t="s">
         <v>1413</v>
       </c>
-      <c r="EX41" s="11" t="s">
+      <c r="EX41" s="10" t="s">
         <v>1414</v>
       </c>
       <c r="EY41" t="s">
@@ -28251,7 +28822,7 @@
       <c r="EZ41" t="s">
         <v>1415</v>
       </c>
-      <c r="FA41" s="11" t="s">
+      <c r="FA41" s="10" t="s">
         <v>1416</v>
       </c>
       <c r="FB41" t="s">
@@ -28505,7 +29076,7 @@
       <c r="C42" t="s">
         <v>946</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D42" t="s">
         <v>1488</v>
       </c>
       <c r="E42" t="s">
@@ -28762,7 +29333,7 @@
       <c r="EH42" t="s">
         <v>1495</v>
       </c>
-      <c r="EI42" s="11" t="s">
+      <c r="EI42" s="10" t="s">
         <v>1496</v>
       </c>
       <c r="EJ42" s="1" t="s">
@@ -28771,7 +29342,7 @@
       <c r="EK42" t="s">
         <v>1497</v>
       </c>
-      <c r="EL42" s="11" t="s">
+      <c r="EL42" s="10" t="s">
         <v>1498</v>
       </c>
       <c r="EM42" t="s">
@@ -28780,7 +29351,7 @@
       <c r="EN42" t="s">
         <v>1499</v>
       </c>
-      <c r="EO42" s="11" t="s">
+      <c r="EO42" s="10" t="s">
         <v>1500</v>
       </c>
       <c r="EP42" t="s">
@@ -28789,7 +29360,7 @@
       <c r="EQ42" t="s">
         <v>1502</v>
       </c>
-      <c r="ER42" s="11" t="s">
+      <c r="ER42" s="10" t="s">
         <v>1510</v>
       </c>
       <c r="ES42" t="s">
@@ -28798,7 +29369,7 @@
       <c r="ET42" t="s">
         <v>1511</v>
       </c>
-      <c r="EU42" s="11" t="s">
+      <c r="EU42" s="10" t="s">
         <v>1503</v>
       </c>
       <c r="EV42" t="s">
@@ -28807,7 +29378,7 @@
       <c r="EW42" t="s">
         <v>1504</v>
       </c>
-      <c r="EX42" s="11" t="s">
+      <c r="EX42" s="10" t="s">
         <v>1505</v>
       </c>
       <c r="EY42" t="s">
@@ -28816,7 +29387,7 @@
       <c r="EZ42" t="s">
         <v>1506</v>
       </c>
-      <c r="FA42" s="11" t="s">
+      <c r="FA42" s="10" t="s">
         <v>1507</v>
       </c>
       <c r="FB42" t="s">
@@ -28825,10 +29396,10 @@
       <c r="FC42" t="s">
         <v>1508</v>
       </c>
-      <c r="FD42" s="11" t="s">
+      <c r="FD42" s="10" t="s">
         <v>1509</v>
       </c>
-      <c r="FG42" s="11" t="s">
+      <c r="FG42" s="10" t="s">
         <v>1512</v>
       </c>
       <c r="FH42" t="s">
@@ -29079,7 +29650,7 @@
       <c r="C43" t="s">
         <v>946</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D43" t="s">
         <v>1276</v>
       </c>
       <c r="E43" t="s">
@@ -29339,7 +29910,7 @@
       <c r="EH43" t="s">
         <v>1280</v>
       </c>
-      <c r="EI43" s="11" t="s">
+      <c r="EI43" s="10" t="s">
         <v>1282</v>
       </c>
       <c r="EJ43" t="s">
@@ -29348,7 +29919,7 @@
       <c r="EK43" t="s">
         <v>1283</v>
       </c>
-      <c r="EL43" s="11" t="s">
+      <c r="EL43" s="10" t="s">
         <v>1284</v>
       </c>
       <c r="EM43" t="s">
@@ -29357,7 +29928,7 @@
       <c r="EN43" t="s">
         <v>1285</v>
       </c>
-      <c r="EO43" s="11" t="s">
+      <c r="EO43" s="10" t="s">
         <v>1286</v>
       </c>
       <c r="EP43" t="s">
@@ -29366,7 +29937,7 @@
       <c r="EQ43" t="s">
         <v>1287</v>
       </c>
-      <c r="ER43" s="11" t="s">
+      <c r="ER43" s="10" t="s">
         <v>1288</v>
       </c>
       <c r="ES43" t="s">
@@ -29375,7 +29946,7 @@
       <c r="ET43" t="s">
         <v>1289</v>
       </c>
-      <c r="EU43" s="11" t="s">
+      <c r="EU43" s="10" t="s">
         <v>1290</v>
       </c>
       <c r="EV43" t="s">
@@ -29384,7 +29955,7 @@
       <c r="EW43" t="s">
         <v>1291</v>
       </c>
-      <c r="EX43" s="11" t="s">
+      <c r="EX43" s="10" t="s">
         <v>1292</v>
       </c>
       <c r="EY43" t="s">
@@ -29393,7 +29964,7 @@
       <c r="EZ43" t="s">
         <v>1293</v>
       </c>
-      <c r="FA43" s="11" t="s">
+      <c r="FA43" s="10" t="s">
         <v>1294</v>
       </c>
       <c r="FB43" t="s">
@@ -29402,7 +29973,7 @@
       <c r="FC43" t="s">
         <v>1295</v>
       </c>
-      <c r="FD43" s="11" t="s">
+      <c r="FD43" s="10" t="s">
         <v>1296</v>
       </c>
       <c r="FE43" t="s">
@@ -29411,7 +29982,7 @@
       <c r="FF43" t="s">
         <v>1297</v>
       </c>
-      <c r="FG43" s="11" t="s">
+      <c r="FG43" s="10" t="s">
         <v>1298</v>
       </c>
       <c r="FH43" t="s">
@@ -29695,7 +30266,7 @@
       <c r="C44" t="s">
         <v>1921</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D44" t="s">
         <v>1898</v>
       </c>
       <c r="E44" t="s">
@@ -29889,16 +30460,16 @@
       <c r="EG44" t="s">
         <v>442</v>
       </c>
-      <c r="EI44" s="11" t="s">
+      <c r="EI44" s="10" t="s">
         <v>1916</v>
       </c>
-      <c r="EL44" s="11" t="s">
+      <c r="EL44" s="10" t="s">
         <v>1917</v>
       </c>
-      <c r="ER44" s="11" t="s">
+      <c r="ER44" s="10" t="s">
         <v>1918</v>
       </c>
-      <c r="EX44" s="11" t="s">
+      <c r="EX44" s="10" t="s">
         <v>1919</v>
       </c>
       <c r="FK44">
@@ -29951,7 +30522,7 @@
       <c r="C45" t="s">
         <v>1922</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D45" t="s">
         <v>1923</v>
       </c>
       <c r="E45" t="s">
@@ -29969,7 +30540,7 @@
       <c r="J45">
         <v>206</v>
       </c>
-      <c r="K45" s="10"/>
+      <c r="K45" s="9"/>
       <c r="L45" t="s">
         <v>421</v>
       </c>
@@ -30134,19 +30705,19 @@
       <c r="EG45" t="s">
         <v>442</v>
       </c>
-      <c r="EI45" s="11" t="s">
+      <c r="EI45" s="10" t="s">
         <v>1936</v>
       </c>
-      <c r="EL45" s="11" t="s">
+      <c r="EL45" s="10" t="s">
         <v>1938</v>
       </c>
-      <c r="ER45" s="11" t="s">
+      <c r="ER45" s="10" t="s">
         <v>1939</v>
       </c>
-      <c r="EX45" s="11" t="s">
+      <c r="EX45" s="10" t="s">
         <v>1937</v>
       </c>
-      <c r="FD45" s="11" t="s">
+      <c r="FD45" s="10" t="s">
         <v>1940</v>
       </c>
       <c r="FJ45" t="s">
@@ -30202,7 +30773,7 @@
       <c r="C46" t="s">
         <v>1942</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="D46" t="s">
         <v>1943</v>
       </c>
       <c r="E46" t="s">
@@ -30390,16 +30961,16 @@
       <c r="EG46" t="s">
         <v>442</v>
       </c>
-      <c r="EI46" s="11" t="s">
+      <c r="EI46" s="10" t="s">
         <v>1958</v>
       </c>
-      <c r="EL46" s="11" t="s">
+      <c r="EL46" s="10" t="s">
         <v>1959</v>
       </c>
-      <c r="EO46" s="11" t="s">
+      <c r="EO46" s="10" t="s">
         <v>1960</v>
       </c>
-      <c r="ER46" s="11" t="s">
+      <c r="ER46" s="10" t="s">
         <v>1961</v>
       </c>
       <c r="EU46" t="s">
@@ -30464,7 +31035,7 @@
       <c r="C47" t="s">
         <v>1969</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D47" t="s">
         <v>1970</v>
       </c>
       <c r="E47" t="s">
@@ -30497,7 +31068,7 @@
       <c r="R47">
         <v>33</v>
       </c>
-      <c r="S47" s="12">
+      <c r="S47" s="11">
         <v>39264</v>
       </c>
       <c r="V47">
@@ -30597,7 +31168,7 @@
       <c r="C48" t="s">
         <v>1969</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D48" t="s">
         <v>1987</v>
       </c>
       <c r="E48" t="s">
@@ -30685,7 +31256,7 @@
       <c r="C49" t="s">
         <v>1969</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D49" t="s">
         <v>1991</v>
       </c>
       <c r="E49" t="s">
@@ -30770,7 +31341,7 @@
       <c r="C50" t="s">
         <v>1969</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D50" t="s">
         <v>1995</v>
       </c>
       <c r="E50" t="s">
@@ -30855,7 +31426,7 @@
       <c r="C51" t="s">
         <v>803</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D51" t="s">
         <v>1998</v>
       </c>
       <c r="E51" t="s">
@@ -31082,49 +31653,49 @@
       <c r="EG51" t="s">
         <v>442</v>
       </c>
-      <c r="EI51" s="11" t="s">
+      <c r="EI51" s="10" t="s">
         <v>2013</v>
       </c>
       <c r="EJ51" t="s">
         <v>2014</v>
       </c>
-      <c r="EL51" s="11" t="s">
+      <c r="EL51" s="10" t="s">
         <v>2015</v>
       </c>
       <c r="EM51" t="s">
         <v>2016</v>
       </c>
-      <c r="EO51" s="11" t="s">
+      <c r="EO51" s="10" t="s">
         <v>2017</v>
       </c>
       <c r="EP51" t="s">
         <v>2018</v>
       </c>
-      <c r="ER51" s="11" t="s">
+      <c r="ER51" s="10" t="s">
         <v>2019</v>
       </c>
       <c r="ES51" t="s">
         <v>2018</v>
       </c>
-      <c r="EU51" s="11" t="s">
+      <c r="EU51" s="10" t="s">
         <v>2020</v>
       </c>
       <c r="EV51" t="s">
         <v>2018</v>
       </c>
-      <c r="EX51" s="11" t="s">
+      <c r="EX51" s="10" t="s">
         <v>2021</v>
       </c>
       <c r="EY51" t="s">
         <v>2018</v>
       </c>
-      <c r="FA51" s="11" t="s">
+      <c r="FA51" s="10" t="s">
         <v>2022</v>
       </c>
       <c r="FB51" t="s">
         <v>2018</v>
       </c>
-      <c r="FD51" s="11" t="s">
+      <c r="FD51" s="10" t="s">
         <v>2023</v>
       </c>
       <c r="FE51" t="s">
@@ -31186,7 +31757,7 @@
       <c r="C52" t="s">
         <v>1969</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="D52" t="s">
         <v>2025</v>
       </c>
       <c r="E52" t="s">
@@ -31271,7 +31842,7 @@
       <c r="C53" t="s">
         <v>1969</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="D53" t="s">
         <v>2028</v>
       </c>
       <c r="E53" t="s">
@@ -31356,7 +31927,7 @@
       <c r="C54" t="s">
         <v>2030</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="D54" t="s">
         <v>2031</v>
       </c>
       <c r="E54" t="s">
@@ -31462,7 +32033,7 @@
       <c r="J55">
         <v>5906</v>
       </c>
-      <c r="K55" s="10" t="s">
+      <c r="K55" s="9" t="s">
         <v>2131</v>
       </c>
       <c r="L55" t="s">
@@ -31714,19 +32285,19 @@
       <c r="EG55" t="s">
         <v>442</v>
       </c>
-      <c r="EL55" s="11" t="s">
+      <c r="EL55" s="10" t="s">
         <v>2175</v>
       </c>
-      <c r="EO55" s="11" t="s">
+      <c r="EO55" s="10" t="s">
         <v>2176</v>
       </c>
-      <c r="ER55" s="11" t="s">
+      <c r="ER55" s="10" t="s">
         <v>2177</v>
       </c>
-      <c r="EX55" s="11" t="s">
+      <c r="EX55" s="10" t="s">
         <v>2178</v>
       </c>
-      <c r="FD55" s="11" t="s">
+      <c r="FD55" s="10" t="s">
         <v>2179</v>
       </c>
       <c r="FJ55" t="s">
@@ -31758,7 +32329,7 @@
         <v>454</v>
       </c>
       <c r="FT55">
-        <f t="shared" ref="FT55:FT74" si="25">60*AG55</f>
+        <f t="shared" ref="FT55:FT77" si="25">60*AG55</f>
         <v>4200</v>
       </c>
       <c r="FU55" s="4">
@@ -31805,7 +32376,7 @@
       <c r="J56">
         <v>5758</v>
       </c>
-      <c r="K56" s="10" t="s">
+      <c r="K56" s="9" t="s">
         <v>2131</v>
       </c>
       <c r="L56" t="s">
@@ -32048,19 +32619,19 @@
       <c r="EG56" t="s">
         <v>442</v>
       </c>
-      <c r="EL56" s="11" t="s">
+      <c r="EL56" s="10" t="s">
         <v>2175</v>
       </c>
-      <c r="EO56" s="11" t="s">
+      <c r="EO56" s="10" t="s">
         <v>2176</v>
       </c>
-      <c r="ER56" s="11" t="s">
+      <c r="ER56" s="10" t="s">
         <v>2177</v>
       </c>
-      <c r="EX56" s="11" t="s">
+      <c r="EX56" s="10" t="s">
         <v>2178</v>
       </c>
-      <c r="FD56" s="11" t="s">
+      <c r="FD56" s="10" t="s">
         <v>2179</v>
       </c>
       <c r="FJ56" t="s">
@@ -32138,7 +32709,7 @@
       <c r="J57">
         <v>5720</v>
       </c>
-      <c r="K57" s="10" t="s">
+      <c r="K57" s="9" t="s">
         <v>2131</v>
       </c>
       <c r="L57" t="s">
@@ -32372,19 +32943,19 @@
       <c r="EG57" t="s">
         <v>442</v>
       </c>
-      <c r="EL57" s="11" t="s">
+      <c r="EL57" s="10" t="s">
         <v>2175</v>
       </c>
-      <c r="EO57" s="11" t="s">
+      <c r="EO57" s="10" t="s">
         <v>2176</v>
       </c>
-      <c r="ER57" s="11" t="s">
+      <c r="ER57" s="10" t="s">
         <v>2177</v>
       </c>
-      <c r="EX57" s="11" t="s">
+      <c r="EX57" s="10" t="s">
         <v>2178</v>
       </c>
-      <c r="FD57" s="11" t="s">
+      <c r="FD57" s="10" t="s">
         <v>2179</v>
       </c>
       <c r="FJ57" t="s">
@@ -32462,7 +33033,7 @@
       <c r="J58">
         <v>5759</v>
       </c>
-      <c r="K58" s="10" t="s">
+      <c r="K58" s="9" t="s">
         <v>2131</v>
       </c>
       <c r="L58" t="s">
@@ -32702,19 +33273,19 @@
       <c r="EG58" t="s">
         <v>442</v>
       </c>
-      <c r="EL58" s="11" t="s">
+      <c r="EL58" s="10" t="s">
         <v>2175</v>
       </c>
-      <c r="EO58" s="11" t="s">
+      <c r="EO58" s="10" t="s">
         <v>2176</v>
       </c>
-      <c r="ER58" s="11" t="s">
+      <c r="ER58" s="10" t="s">
         <v>2177</v>
       </c>
-      <c r="EX58" s="11" t="s">
+      <c r="EX58" s="10" t="s">
         <v>2178</v>
       </c>
-      <c r="FD58" s="11" t="s">
+      <c r="FD58" s="10" t="s">
         <v>2179</v>
       </c>
       <c r="FK58">
@@ -32789,7 +33360,7 @@
       <c r="J59">
         <v>327</v>
       </c>
-      <c r="K59" s="10" t="s">
+      <c r="K59" s="9" t="s">
         <v>2131</v>
       </c>
       <c r="L59" t="s">
@@ -33005,19 +33576,19 @@
       <c r="EG59" t="s">
         <v>442</v>
       </c>
-      <c r="EL59" s="11" t="s">
+      <c r="EL59" s="10" t="s">
         <v>2175</v>
       </c>
-      <c r="EO59" s="11" t="s">
+      <c r="EO59" s="10" t="s">
         <v>2176</v>
       </c>
-      <c r="ER59" s="11" t="s">
+      <c r="ER59" s="10" t="s">
         <v>2177</v>
       </c>
-      <c r="EX59" s="11" t="s">
+      <c r="EX59" s="10" t="s">
         <v>2178</v>
       </c>
-      <c r="FD59" s="11" t="s">
+      <c r="FD59" s="10" t="s">
         <v>2179</v>
       </c>
       <c r="FJ59" t="s">
@@ -33095,7 +33666,7 @@
       <c r="J60">
         <v>5720</v>
       </c>
-      <c r="K60" s="10" t="s">
+      <c r="K60" s="9" t="s">
         <v>2131</v>
       </c>
       <c r="L60" t="s">
@@ -33326,19 +33897,19 @@
       <c r="EG60" t="s">
         <v>442</v>
       </c>
-      <c r="EL60" s="11" t="s">
+      <c r="EL60" s="10" t="s">
         <v>2175</v>
       </c>
-      <c r="EO60" s="11" t="s">
+      <c r="EO60" s="10" t="s">
         <v>2176</v>
       </c>
-      <c r="ER60" s="11" t="s">
+      <c r="ER60" s="10" t="s">
         <v>2177</v>
       </c>
-      <c r="EX60" s="11" t="s">
+      <c r="EX60" s="10" t="s">
         <v>2178</v>
       </c>
-      <c r="FD60" s="11" t="s">
+      <c r="FD60" s="10" t="s">
         <v>2179</v>
       </c>
       <c r="FJ60" t="s">
@@ -33416,7 +33987,7 @@
       <c r="J61">
         <v>329</v>
       </c>
-      <c r="K61" s="10" t="s">
+      <c r="K61" s="9" t="s">
         <v>2131</v>
       </c>
       <c r="L61" t="s">
@@ -33647,19 +34218,19 @@
       <c r="EG61" t="s">
         <v>442</v>
       </c>
-      <c r="EL61" s="11" t="s">
+      <c r="EL61" s="10" t="s">
         <v>2175</v>
       </c>
-      <c r="EO61" s="11" t="s">
+      <c r="EO61" s="10" t="s">
         <v>2176</v>
       </c>
-      <c r="ER61" s="11" t="s">
+      <c r="ER61" s="10" t="s">
         <v>2177</v>
       </c>
-      <c r="EX61" s="11" t="s">
+      <c r="EX61" s="10" t="s">
         <v>2178</v>
       </c>
-      <c r="FD61" s="11" t="s">
+      <c r="FD61" s="10" t="s">
         <v>2179</v>
       </c>
       <c r="FK61">
@@ -33734,7 +34305,7 @@
       <c r="J62">
         <v>5904</v>
       </c>
-      <c r="K62" s="10" t="s">
+      <c r="K62" s="9" t="s">
         <v>2131</v>
       </c>
       <c r="L62" t="s">
@@ -33965,19 +34536,19 @@
       <c r="EG62" t="s">
         <v>442</v>
       </c>
-      <c r="EL62" s="11" t="s">
+      <c r="EL62" s="10" t="s">
         <v>2175</v>
       </c>
-      <c r="EO62" s="11" t="s">
+      <c r="EO62" s="10" t="s">
         <v>2176</v>
       </c>
-      <c r="ER62" s="11" t="s">
+      <c r="ER62" s="10" t="s">
         <v>2177</v>
       </c>
-      <c r="EX62" s="11" t="s">
+      <c r="EX62" s="10" t="s">
         <v>2178</v>
       </c>
-      <c r="FD62" s="11" t="s">
+      <c r="FD62" s="10" t="s">
         <v>2179</v>
       </c>
       <c r="FJ62" t="s">
@@ -34049,7 +34620,7 @@
       <c r="J63">
         <v>129</v>
       </c>
-      <c r="K63" s="10" t="s">
+      <c r="K63" s="9" t="s">
         <v>2131</v>
       </c>
       <c r="L63" t="s">
@@ -34181,31 +34752,31 @@
       <c r="EG63" t="s">
         <v>442</v>
       </c>
-      <c r="EI63" s="11" t="s">
+      <c r="EI63" s="10" t="s">
         <v>2188</v>
       </c>
-      <c r="EL63" s="11" t="s">
+      <c r="EL63" s="10" t="s">
         <v>2193</v>
       </c>
-      <c r="EO63" s="11" t="s">
+      <c r="EO63" s="10" t="s">
         <v>2194</v>
       </c>
-      <c r="ER63" s="11" t="s">
+      <c r="ER63" s="10" t="s">
         <v>2195</v>
       </c>
-      <c r="EU63" s="11" t="s">
+      <c r="EU63" s="10" t="s">
         <v>2196</v>
       </c>
-      <c r="EX63" s="11" t="s">
+      <c r="EX63" s="10" t="s">
         <v>2197</v>
       </c>
-      <c r="FA63" s="11" t="s">
+      <c r="FA63" s="10" t="s">
         <v>2198</v>
       </c>
-      <c r="FD63" s="11" t="s">
+      <c r="FD63" s="10" t="s">
         <v>2199</v>
       </c>
-      <c r="FG63" s="11" t="s">
+      <c r="FG63" s="10" t="s">
         <v>2200</v>
       </c>
       <c r="FK63">
@@ -34260,7 +34831,7 @@
         <v>2202</v>
       </c>
       <c r="D64" t="s">
-        <v>2249</v>
+        <v>2375</v>
       </c>
       <c r="E64" t="s">
         <v>2203</v>
@@ -34366,10 +34937,10 @@
         <v>3</v>
       </c>
       <c r="AP64" t="s">
-        <v>2222</v>
+        <v>2400</v>
       </c>
       <c r="AQ64" t="s">
-        <v>2267</v>
+        <v>2257</v>
       </c>
       <c r="AR64" s="4">
         <f t="shared" si="18"/>
@@ -34385,7 +34956,7 @@
         <v>2</v>
       </c>
       <c r="AV64" t="s">
-        <v>2226</v>
+        <v>2225</v>
       </c>
       <c r="AW64">
         <v>2</v>
@@ -34394,10 +34965,10 @@
         <v>1</v>
       </c>
       <c r="BF64" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
       <c r="BI64" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
       <c r="BL64">
         <v>3</v>
@@ -34434,13 +35005,13 @@
         <v>2024</v>
       </c>
       <c r="DZ64" t="s">
+        <v>2222</v>
+      </c>
+      <c r="EA64" t="s">
         <v>2223</v>
       </c>
-      <c r="EA64" t="s">
+      <c r="EB64" t="s">
         <v>2224</v>
-      </c>
-      <c r="EB64" t="s">
-        <v>2225</v>
       </c>
       <c r="EC64" t="s">
         <v>1681</v>
@@ -34454,7 +35025,7 @@
       <c r="EG64" t="s">
         <v>442</v>
       </c>
-      <c r="EI64" s="11" t="s">
+      <c r="EI64" s="10" t="s">
         <v>2209</v>
       </c>
       <c r="FK64">
@@ -34509,7 +35080,7 @@
         <v>2202</v>
       </c>
       <c r="D65" t="s">
-        <v>2250</v>
+        <v>2376</v>
       </c>
       <c r="E65" t="s">
         <v>2203</v>
@@ -34548,10 +35119,10 @@
         <v>2212</v>
       </c>
       <c r="S65" t="s">
+        <v>2227</v>
+      </c>
+      <c r="T65" t="s">
         <v>2228</v>
-      </c>
-      <c r="T65" t="s">
-        <v>2229</v>
       </c>
       <c r="V65">
         <v>122</v>
@@ -34614,10 +35185,10 @@
         <v>3</v>
       </c>
       <c r="AP65" t="s">
-        <v>2222</v>
+        <v>2400</v>
       </c>
       <c r="AQ65" t="s">
-        <v>2267</v>
+        <v>2257</v>
       </c>
       <c r="AR65" s="4">
         <f t="shared" si="18"/>
@@ -34642,10 +35213,10 @@
         <v>1</v>
       </c>
       <c r="BF65" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
       <c r="BI65" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
       <c r="BL65">
         <v>2</v>
@@ -34679,19 +35250,19 @@
         <v>2024</v>
       </c>
       <c r="DZ65" t="s">
+        <v>2229</v>
+      </c>
+      <c r="EA65" t="s">
         <v>2230</v>
-      </c>
-      <c r="EA65" t="s">
-        <v>2231</v>
       </c>
       <c r="EB65" t="s">
         <v>1332</v>
       </c>
       <c r="EC65" t="s">
+        <v>2231</v>
+      </c>
+      <c r="ED65" t="s">
         <v>2232</v>
-      </c>
-      <c r="ED65" t="s">
-        <v>2233</v>
       </c>
       <c r="EF65" t="s">
         <v>441</v>
@@ -34699,7 +35270,7 @@
       <c r="EG65" t="s">
         <v>442</v>
       </c>
-      <c r="EI65" s="11" t="s">
+      <c r="EI65" s="10" t="s">
         <v>2214</v>
       </c>
       <c r="FK65">
@@ -34754,7 +35325,7 @@
         <v>2202</v>
       </c>
       <c r="D66" t="s">
-        <v>2251</v>
+        <v>2377</v>
       </c>
       <c r="E66" t="s">
         <v>2203</v>
@@ -34796,10 +35367,10 @@
         <v>4</v>
       </c>
       <c r="S66" t="s">
-        <v>2234</v>
+        <v>2233</v>
       </c>
       <c r="T66" t="s">
-        <v>2229</v>
+        <v>2228</v>
       </c>
       <c r="V66">
         <v>75</v>
@@ -34862,10 +35433,10 @@
         <v>3</v>
       </c>
       <c r="AP66" t="s">
-        <v>2222</v>
+        <v>2400</v>
       </c>
       <c r="AQ66" t="s">
-        <v>2267</v>
+        <v>2257</v>
       </c>
       <c r="AR66" s="4">
         <f t="shared" si="18"/>
@@ -34881,22 +35452,22 @@
         <v>2</v>
       </c>
       <c r="AV66" t="s">
+        <v>2225</v>
+      </c>
+      <c r="AW66">
+        <v>1</v>
+      </c>
+      <c r="AX66">
+        <v>1</v>
+      </c>
+      <c r="BE66">
+        <v>1</v>
+      </c>
+      <c r="BF66" t="s">
+        <v>2247</v>
+      </c>
+      <c r="BI66" t="s">
         <v>2226</v>
-      </c>
-      <c r="AW66">
-        <v>1</v>
-      </c>
-      <c r="AX66">
-        <v>1</v>
-      </c>
-      <c r="BE66">
-        <v>1</v>
-      </c>
-      <c r="BF66" t="s">
-        <v>2248</v>
-      </c>
-      <c r="BI66" t="s">
-        <v>2227</v>
       </c>
       <c r="BL66">
         <v>1</v>
@@ -34942,19 +35513,19 @@
         <v>2024</v>
       </c>
       <c r="DZ66" t="s">
+        <v>2234</v>
+      </c>
+      <c r="EA66" t="s">
         <v>2235</v>
       </c>
-      <c r="EA66" t="s">
+      <c r="EB66" t="s">
         <v>2236</v>
       </c>
-      <c r="EB66" t="s">
+      <c r="EC66" t="s">
+        <v>2236</v>
+      </c>
+      <c r="ED66" t="s">
         <v>2237</v>
-      </c>
-      <c r="EC66" t="s">
-        <v>2237</v>
-      </c>
-      <c r="ED66" t="s">
-        <v>2238</v>
       </c>
       <c r="EF66" t="s">
         <v>441</v>
@@ -35014,7 +35585,7 @@
         <v>2202</v>
       </c>
       <c r="D67" t="s">
-        <v>2252</v>
+        <v>2378</v>
       </c>
       <c r="E67" t="s">
         <v>2203</v>
@@ -35026,16 +35597,16 @@
         <v>2205</v>
       </c>
       <c r="I67" t="s">
-        <v>2239</v>
+        <v>2238</v>
       </c>
       <c r="J67">
         <v>6348</v>
       </c>
       <c r="K67" t="s">
+        <v>2239</v>
+      </c>
+      <c r="L67" t="s">
         <v>2240</v>
-      </c>
-      <c r="L67" t="s">
-        <v>2241</v>
       </c>
       <c r="M67" t="s">
         <v>423</v>
@@ -35050,7 +35621,7 @@
         <v>2221938507</v>
       </c>
       <c r="Q67" s="3" t="s">
-        <v>2242</v>
+        <v>2241</v>
       </c>
       <c r="R67">
         <v>6</v>
@@ -35059,7 +35630,7 @@
         <v>2018</v>
       </c>
       <c r="T67" t="s">
-        <v>2229</v>
+        <v>2228</v>
       </c>
       <c r="V67">
         <v>80</v>
@@ -35092,7 +35663,7 @@
         <v>2221</v>
       </c>
       <c r="AF67" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
       <c r="AG67">
         <v>1</v>
@@ -35122,10 +35693,10 @@
         <v>3</v>
       </c>
       <c r="AP67" t="s">
-        <v>2222</v>
+        <v>2400</v>
       </c>
       <c r="AQ67" t="s">
-        <v>2267</v>
+        <v>2257</v>
       </c>
       <c r="AR67" s="4">
         <f t="shared" ref="AR67:AR98" si="28">+AS67+AU67+BE67+CD67+CE67+CF67+CG67+CH67+CI67+CW67</f>
@@ -35141,22 +35712,22 @@
         <v>2</v>
       </c>
       <c r="AV67" t="s">
+        <v>2225</v>
+      </c>
+      <c r="AW67">
+        <v>1</v>
+      </c>
+      <c r="AX67">
+        <v>1</v>
+      </c>
+      <c r="BE67">
+        <v>1</v>
+      </c>
+      <c r="BF67" t="s">
+        <v>2247</v>
+      </c>
+      <c r="BI67" t="s">
         <v>2226</v>
-      </c>
-      <c r="AW67">
-        <v>1</v>
-      </c>
-      <c r="AX67">
-        <v>1</v>
-      </c>
-      <c r="BE67">
-        <v>1</v>
-      </c>
-      <c r="BF67" t="s">
-        <v>2248</v>
-      </c>
-      <c r="BI67" t="s">
-        <v>2227</v>
       </c>
       <c r="BL67">
         <v>2</v>
@@ -35199,19 +35770,19 @@
         <v>2024</v>
       </c>
       <c r="DZ67" t="s">
+        <v>2243</v>
+      </c>
+      <c r="EA67" t="s">
         <v>2244</v>
       </c>
-      <c r="EA67" t="s">
+      <c r="EB67" t="s">
         <v>2245</v>
       </c>
-      <c r="EB67" t="s">
+      <c r="EC67" t="s">
+        <v>2240</v>
+      </c>
+      <c r="ED67" t="s">
         <v>2246</v>
-      </c>
-      <c r="EC67" t="s">
-        <v>2241</v>
-      </c>
-      <c r="ED67" t="s">
-        <v>2247</v>
       </c>
       <c r="EF67" t="s">
         <v>441</v>
@@ -35271,7 +35842,7 @@
         <v>2202</v>
       </c>
       <c r="D68" t="s">
-        <v>2253</v>
+        <v>2379</v>
       </c>
       <c r="E68" t="s">
         <v>2203</v>
@@ -35292,7 +35863,7 @@
         <v>993</v>
       </c>
       <c r="L68" t="s">
-        <v>2254</v>
+        <v>2248</v>
       </c>
       <c r="M68" t="s">
         <v>423</v>
@@ -35307,16 +35878,16 @@
         <v>2223234754</v>
       </c>
       <c r="Q68" s="3" t="s">
-        <v>2255</v>
+        <v>2249</v>
       </c>
       <c r="R68">
         <v>10</v>
       </c>
       <c r="S68" t="s">
-        <v>2256</v>
+        <v>2250</v>
       </c>
       <c r="T68" t="s">
-        <v>2229</v>
+        <v>2228</v>
       </c>
       <c r="V68">
         <v>55</v>
@@ -35349,7 +35920,7 @@
         <v>2221</v>
       </c>
       <c r="AF68" t="s">
-        <v>2257</v>
+        <v>2251</v>
       </c>
       <c r="AG68">
         <v>1</v>
@@ -35379,10 +35950,10 @@
         <v>3</v>
       </c>
       <c r="AP68" t="s">
-        <v>2222</v>
+        <v>2400</v>
       </c>
       <c r="AQ68" t="s">
-        <v>2267</v>
+        <v>2257</v>
       </c>
       <c r="AR68" s="4">
         <f t="shared" si="28"/>
@@ -35398,22 +35969,22 @@
         <v>2</v>
       </c>
       <c r="AV68" t="s">
+        <v>2225</v>
+      </c>
+      <c r="AW68">
+        <v>1</v>
+      </c>
+      <c r="AX68">
+        <v>1</v>
+      </c>
+      <c r="BE68">
+        <v>1</v>
+      </c>
+      <c r="BF68" t="s">
+        <v>2247</v>
+      </c>
+      <c r="BI68" t="s">
         <v>2226</v>
-      </c>
-      <c r="AW68">
-        <v>1</v>
-      </c>
-      <c r="AX68">
-        <v>1</v>
-      </c>
-      <c r="BE68">
-        <v>1</v>
-      </c>
-      <c r="BF68" t="s">
-        <v>2248</v>
-      </c>
-      <c r="BI68" t="s">
-        <v>2227</v>
       </c>
       <c r="BL68">
         <v>2</v>
@@ -35456,19 +36027,19 @@
         <v>2024</v>
       </c>
       <c r="DZ68" t="s">
-        <v>2258</v>
+        <v>2252</v>
       </c>
       <c r="EA68" t="s">
-        <v>2259</v>
+        <v>2253</v>
       </c>
       <c r="EB68" t="s">
-        <v>2260</v>
+        <v>2254</v>
       </c>
       <c r="EC68" t="s">
-        <v>2261</v>
+        <v>2255</v>
       </c>
       <c r="ED68" t="s">
-        <v>2262</v>
+        <v>2256</v>
       </c>
       <c r="EF68" t="s">
         <v>441</v>
@@ -35528,42 +36099,255 @@
         <v>2202</v>
       </c>
       <c r="D69" t="s">
-        <v>2263</v>
+        <v>2380</v>
       </c>
       <c r="E69" t="s">
         <v>2203</v>
       </c>
+      <c r="G69" t="s">
+        <v>2204</v>
+      </c>
+      <c r="H69" t="s">
+        <v>2205</v>
+      </c>
+      <c r="I69" t="s">
+        <v>2336</v>
+      </c>
+      <c r="J69">
+        <v>1146</v>
+      </c>
+      <c r="K69" t="s">
+        <v>993</v>
+      </c>
+      <c r="L69" t="s">
+        <v>2337</v>
+      </c>
+      <c r="M69" t="s">
+        <v>1401</v>
+      </c>
+      <c r="N69" t="s">
+        <v>423</v>
+      </c>
+      <c r="O69">
+        <v>74260</v>
+      </c>
+      <c r="P69">
+        <v>2447859884</v>
+      </c>
+      <c r="Q69" s="3" t="s">
+        <v>2338</v>
+      </c>
+      <c r="R69">
+        <v>8</v>
+      </c>
+      <c r="S69">
+        <v>2026</v>
+      </c>
+      <c r="T69" t="s">
+        <v>2228</v>
+      </c>
+      <c r="V69">
+        <v>40</v>
+      </c>
+      <c r="W69">
+        <v>40</v>
+      </c>
+      <c r="X69">
+        <v>1</v>
+      </c>
+      <c r="Y69">
+        <v>1</v>
+      </c>
+      <c r="Z69">
+        <v>1</v>
+      </c>
+      <c r="AA69">
+        <v>1</v>
+      </c>
+      <c r="AB69">
+        <v>0</v>
+      </c>
+      <c r="AC69">
+        <v>0</v>
+      </c>
+      <c r="AD69" t="s">
+        <v>2341</v>
+      </c>
+      <c r="AE69" t="s">
+        <v>2221</v>
+      </c>
+      <c r="AF69" t="s">
+        <v>2339</v>
+      </c>
+      <c r="AG69">
+        <v>1</v>
+      </c>
+      <c r="AH69">
+        <v>0</v>
+      </c>
+      <c r="AI69">
+        <v>1</v>
+      </c>
+      <c r="AJ69">
+        <v>0</v>
+      </c>
+      <c r="AK69">
+        <v>0</v>
+      </c>
+      <c r="AL69">
+        <v>0</v>
+      </c>
+      <c r="AM69">
+        <v>1</v>
+      </c>
+      <c r="AN69">
+        <v>20</v>
+      </c>
+      <c r="AO69">
+        <v>3</v>
+      </c>
+      <c r="AP69" t="s">
+        <v>2400</v>
+      </c>
+      <c r="AQ69" t="s">
+        <v>2257</v>
+      </c>
       <c r="AR69" s="4">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="AS69">
+        <v>1</v>
+      </c>
+      <c r="AT69" t="s">
+        <v>431</v>
+      </c>
+      <c r="AU69">
+        <v>2</v>
+      </c>
+      <c r="AV69" t="s">
+        <v>2225</v>
+      </c>
+      <c r="AW69">
+        <v>1</v>
+      </c>
+      <c r="AX69">
+        <v>1</v>
+      </c>
+      <c r="BC69">
+        <v>1</v>
+      </c>
+      <c r="BD69" t="s">
+        <v>431</v>
+      </c>
+      <c r="BE69">
+        <v>1</v>
+      </c>
+      <c r="BF69" t="s">
+        <v>2247</v>
+      </c>
+      <c r="BI69" t="s">
+        <v>2226</v>
+      </c>
+      <c r="BL69">
+        <v>2</v>
+      </c>
+      <c r="BM69" t="s">
+        <v>855</v>
+      </c>
+      <c r="CD69">
+        <v>4</v>
+      </c>
+      <c r="CF69">
+        <v>1</v>
+      </c>
+      <c r="CH69">
+        <v>1</v>
+      </c>
+      <c r="CI69">
+        <v>2</v>
+      </c>
+      <c r="CJ69">
+        <v>3</v>
       </c>
       <c r="CK69" s="4">
         <f t="shared" si="19"/>
+        <v>2</v>
+      </c>
+      <c r="CL69">
+        <v>2</v>
+      </c>
+      <c r="DE69">
+        <v>2</v>
+      </c>
+      <c r="DF69" t="s">
+        <v>855</v>
+      </c>
+      <c r="DW69">
+        <v>4</v>
+      </c>
+      <c r="DX69" t="s">
+        <v>2273</v>
+      </c>
+      <c r="DY69">
+        <v>2024</v>
+      </c>
+      <c r="DZ69" t="s">
+        <v>2384</v>
+      </c>
+      <c r="EA69" t="s">
+        <v>2033</v>
+      </c>
+      <c r="EB69" t="s">
+        <v>2385</v>
+      </c>
+      <c r="EC69" t="s">
+        <v>2386</v>
+      </c>
+      <c r="ED69" t="s">
+        <v>2387</v>
+      </c>
+      <c r="EF69" t="s">
+        <v>441</v>
+      </c>
+      <c r="EG69" t="s">
+        <v>442</v>
+      </c>
+      <c r="FK69">
         <v>0</v>
       </c>
       <c r="FL69" s="4">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
+      <c r="FN69">
+        <v>0</v>
+      </c>
       <c r="FO69" s="4">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
+      <c r="FQ69">
+        <v>0</v>
+      </c>
       <c r="FR69" s="4">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
+      <c r="FS69" t="s">
+        <v>454</v>
+      </c>
       <c r="FT69">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="FU69" s="4">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="FV69" s="4">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="FW69" s="4" t="str">
         <f t="shared" si="27"/>
@@ -35580,43 +36364,247 @@
       <c r="C70" t="s">
         <v>2202</v>
       </c>
-      <c r="D70" t="s">
-        <v>2264</v>
+      <c r="D70" s="6" t="s">
+        <v>2381</v>
       </c>
       <c r="E70" t="s">
         <v>2203</v>
       </c>
+      <c r="G70" t="s">
+        <v>2204</v>
+      </c>
+      <c r="H70" t="s">
+        <v>2205</v>
+      </c>
+      <c r="I70" t="s">
+        <v>2325</v>
+      </c>
+      <c r="J70" t="s">
+        <v>2326</v>
+      </c>
+      <c r="K70" t="s">
+        <v>2327</v>
+      </c>
+      <c r="L70" t="s">
+        <v>421</v>
+      </c>
+      <c r="M70" t="s">
+        <v>2328</v>
+      </c>
+      <c r="N70" t="s">
+        <v>423</v>
+      </c>
+      <c r="O70">
+        <v>73310</v>
+      </c>
+      <c r="P70">
+        <v>7971480266</v>
+      </c>
+      <c r="Q70" s="3" t="s">
+        <v>2329</v>
+      </c>
+      <c r="R70">
+        <v>3</v>
+      </c>
+      <c r="S70" t="s">
+        <v>2330</v>
+      </c>
+      <c r="T70" t="s">
+        <v>2228</v>
+      </c>
+      <c r="V70">
+        <v>68.31</v>
+      </c>
+      <c r="W70">
+        <v>68.31</v>
+      </c>
+      <c r="X70">
+        <v>1</v>
+      </c>
+      <c r="Y70">
+        <v>1</v>
+      </c>
+      <c r="Z70">
+        <v>1</v>
+      </c>
+      <c r="AA70">
+        <v>1</v>
+      </c>
+      <c r="AB70">
+        <v>0</v>
+      </c>
+      <c r="AC70">
+        <v>0</v>
+      </c>
+      <c r="AD70" t="s">
+        <v>848</v>
+      </c>
+      <c r="AE70" t="s">
+        <v>2221</v>
+      </c>
+      <c r="AF70" t="s">
+        <v>2331</v>
+      </c>
+      <c r="AG70">
+        <v>1</v>
+      </c>
+      <c r="AH70">
+        <v>0</v>
+      </c>
+      <c r="AI70">
+        <v>1</v>
+      </c>
+      <c r="AJ70">
+        <v>0</v>
+      </c>
+      <c r="AK70">
+        <v>0</v>
+      </c>
+      <c r="AL70">
+        <v>0</v>
+      </c>
+      <c r="AM70">
+        <v>1</v>
+      </c>
+      <c r="AN70">
+        <v>10</v>
+      </c>
+      <c r="AO70">
+        <v>3</v>
+      </c>
+      <c r="AP70" t="s">
+        <v>2400</v>
+      </c>
+      <c r="AQ70" t="s">
+        <v>2257</v>
+      </c>
       <c r="AR70" s="4">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="AS70">
+        <v>1</v>
+      </c>
+      <c r="AT70" t="s">
+        <v>431</v>
+      </c>
+      <c r="AU70">
+        <v>2</v>
+      </c>
+      <c r="AV70" t="s">
+        <v>2225</v>
+      </c>
+      <c r="AW70">
+        <v>1</v>
+      </c>
+      <c r="AX70">
+        <v>1</v>
+      </c>
+      <c r="BE70">
+        <v>1</v>
+      </c>
+      <c r="BF70" t="s">
+        <v>2247</v>
+      </c>
+      <c r="BI70" t="s">
+        <v>2226</v>
+      </c>
+      <c r="BL70">
+        <v>2</v>
+      </c>
+      <c r="BM70" t="s">
+        <v>855</v>
+      </c>
+      <c r="CD70">
+        <v>4</v>
+      </c>
+      <c r="CF70">
+        <v>1</v>
+      </c>
+      <c r="CI70">
+        <v>2</v>
+      </c>
+      <c r="CJ70">
+        <v>2</v>
       </c>
       <c r="CK70" s="4">
         <f t="shared" si="19"/>
+        <v>2</v>
+      </c>
+      <c r="CL70">
+        <v>2</v>
+      </c>
+      <c r="DE70">
+        <v>3</v>
+      </c>
+      <c r="DF70" t="s">
+        <v>855</v>
+      </c>
+      <c r="DW70">
+        <v>5</v>
+      </c>
+      <c r="DX70" t="s">
+        <v>2273</v>
+      </c>
+      <c r="DY70">
+        <v>2024</v>
+      </c>
+      <c r="DZ70" t="s">
+        <v>2332</v>
+      </c>
+      <c r="EA70" t="s">
+        <v>2333</v>
+      </c>
+      <c r="EB70" t="s">
+        <v>439</v>
+      </c>
+      <c r="EC70" t="s">
+        <v>2334</v>
+      </c>
+      <c r="ED70" t="s">
+        <v>2335</v>
+      </c>
+      <c r="EF70" t="s">
+        <v>441</v>
+      </c>
+      <c r="EG70" t="s">
+        <v>442</v>
+      </c>
+      <c r="FK70">
         <v>0</v>
       </c>
       <c r="FL70" s="4">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
+      <c r="FN70">
+        <v>0</v>
+      </c>
       <c r="FO70" s="4">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
+      <c r="FQ70">
+        <v>0</v>
+      </c>
       <c r="FR70" s="4">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
+      <c r="FS70" t="s">
+        <v>454</v>
+      </c>
       <c r="FT70">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="FU70" s="4">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="FV70" s="4">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="FW70" s="4" t="str">
         <f t="shared" si="27"/>
@@ -35634,42 +36622,240 @@
         <v>2202</v>
       </c>
       <c r="D71" t="s">
-        <v>2265</v>
+        <v>2382</v>
       </c>
       <c r="E71" t="s">
         <v>2203</v>
       </c>
+      <c r="G71" t="s">
+        <v>2204</v>
+      </c>
+      <c r="H71" t="s">
+        <v>2205</v>
+      </c>
+      <c r="I71" t="s">
+        <v>756</v>
+      </c>
+      <c r="J71">
+        <v>22</v>
+      </c>
+      <c r="L71" t="s">
+        <v>421</v>
+      </c>
+      <c r="M71" t="s">
+        <v>2340</v>
+      </c>
+      <c r="N71" t="s">
+        <v>423</v>
+      </c>
+      <c r="O71">
+        <v>73170</v>
+      </c>
+      <c r="P71">
+        <v>7713610902</v>
+      </c>
+      <c r="Q71" s="3" t="s">
+        <v>2344</v>
+      </c>
+      <c r="S71" t="s">
+        <v>2388</v>
+      </c>
+      <c r="T71" t="s">
+        <v>2228</v>
+      </c>
+      <c r="V71">
+        <v>126</v>
+      </c>
+      <c r="W71">
+        <v>126</v>
+      </c>
+      <c r="X71">
+        <v>1</v>
+      </c>
+      <c r="Y71">
+        <v>1</v>
+      </c>
+      <c r="Z71">
+        <v>1</v>
+      </c>
+      <c r="AA71">
+        <v>1</v>
+      </c>
+      <c r="AB71">
+        <v>0</v>
+      </c>
+      <c r="AC71">
+        <v>0</v>
+      </c>
+      <c r="AD71" t="s">
+        <v>848</v>
+      </c>
+      <c r="AE71" t="s">
+        <v>2221</v>
+      </c>
+      <c r="AF71" t="s">
+        <v>2342</v>
+      </c>
+      <c r="AG71">
+        <v>1</v>
+      </c>
+      <c r="AH71">
+        <v>0</v>
+      </c>
+      <c r="AI71">
+        <v>0</v>
+      </c>
+      <c r="AJ71">
+        <v>1</v>
+      </c>
+      <c r="AK71">
+        <v>0</v>
+      </c>
+      <c r="AL71">
+        <v>0</v>
+      </c>
+      <c r="AM71">
+        <v>1</v>
+      </c>
+      <c r="AN71">
+        <v>15</v>
+      </c>
+      <c r="AO71">
+        <v>3</v>
+      </c>
+      <c r="AP71" t="s">
+        <v>2400</v>
+      </c>
+      <c r="AQ71" t="s">
+        <v>2257</v>
+      </c>
       <c r="AR71" s="4">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="AS71">
+        <v>1</v>
+      </c>
+      <c r="AT71" t="s">
+        <v>431</v>
+      </c>
+      <c r="AU71">
+        <v>2</v>
+      </c>
+      <c r="AV71" t="s">
+        <v>2225</v>
+      </c>
+      <c r="AW71">
+        <v>1</v>
+      </c>
+      <c r="AX71">
+        <v>1</v>
+      </c>
+      <c r="BE71">
+        <v>1</v>
+      </c>
+      <c r="BF71" t="s">
+        <v>2247</v>
+      </c>
+      <c r="BI71" t="s">
+        <v>2226</v>
+      </c>
+      <c r="BL71">
+        <v>2</v>
+      </c>
+      <c r="BM71" t="s">
+        <v>855</v>
+      </c>
+      <c r="CD71">
+        <v>4</v>
+      </c>
+      <c r="CF71">
+        <v>1</v>
+      </c>
+      <c r="CI71">
+        <v>2</v>
+      </c>
+      <c r="CJ71">
+        <v>2</v>
       </c>
       <c r="CK71" s="4">
         <f t="shared" si="19"/>
+        <v>2</v>
+      </c>
+      <c r="CL71">
+        <v>2</v>
+      </c>
+      <c r="DE71">
+        <v>2</v>
+      </c>
+      <c r="DF71" t="s">
+        <v>855</v>
+      </c>
+      <c r="DW71">
+        <v>5</v>
+      </c>
+      <c r="DX71" t="s">
+        <v>2273</v>
+      </c>
+      <c r="DY71">
+        <v>2024</v>
+      </c>
+      <c r="DZ71" t="s">
+        <v>2389</v>
+      </c>
+      <c r="EA71" t="s">
+        <v>2390</v>
+      </c>
+      <c r="EB71" t="s">
+        <v>2391</v>
+      </c>
+      <c r="EC71" t="s">
+        <v>2392</v>
+      </c>
+      <c r="ED71" t="s">
+        <v>2393</v>
+      </c>
+      <c r="EF71" t="s">
+        <v>441</v>
+      </c>
+      <c r="EG71" t="s">
+        <v>442</v>
+      </c>
+      <c r="FK71">
         <v>0</v>
       </c>
       <c r="FL71" s="4">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
+      <c r="FN71">
+        <v>0</v>
+      </c>
       <c r="FO71" s="4">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
+      <c r="FQ71">
+        <v>0</v>
+      </c>
       <c r="FR71" s="4">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
+      <c r="FS71" t="s">
+        <v>454</v>
+      </c>
       <c r="FT71">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="FU71" s="4">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="FV71" s="4">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="FW71" s="4" t="str">
         <f t="shared" si="27"/>
@@ -35687,42 +36873,240 @@
         <v>2202</v>
       </c>
       <c r="D72" t="s">
-        <v>2266</v>
+        <v>2383</v>
       </c>
       <c r="E72" t="s">
         <v>2203</v>
       </c>
+      <c r="G72" t="s">
+        <v>2204</v>
+      </c>
+      <c r="H72" t="s">
+        <v>2205</v>
+      </c>
+      <c r="I72" t="s">
+        <v>756</v>
+      </c>
+      <c r="J72">
+        <v>26</v>
+      </c>
+      <c r="L72" t="s">
+        <v>421</v>
+      </c>
+      <c r="M72" t="s">
+        <v>1232</v>
+      </c>
+      <c r="N72" t="s">
+        <v>423</v>
+      </c>
+      <c r="O72">
+        <v>74400</v>
+      </c>
+      <c r="P72">
+        <v>2431037802</v>
+      </c>
+      <c r="Q72" s="3" t="s">
+        <v>2343</v>
+      </c>
+      <c r="R72">
+        <v>1</v>
+      </c>
+      <c r="S72" t="s">
+        <v>2394</v>
+      </c>
+      <c r="T72" t="s">
+        <v>2228</v>
+      </c>
+      <c r="V72">
+        <v>50</v>
+      </c>
+      <c r="W72">
+        <v>50</v>
+      </c>
+      <c r="X72">
+        <v>1</v>
+      </c>
+      <c r="Y72">
+        <v>1</v>
+      </c>
+      <c r="Z72">
+        <v>2</v>
+      </c>
+      <c r="AA72">
+        <v>1</v>
+      </c>
+      <c r="AB72">
+        <v>0</v>
+      </c>
+      <c r="AC72">
+        <v>0</v>
+      </c>
+      <c r="AD72" t="s">
+        <v>848</v>
+      </c>
+      <c r="AE72" t="s">
+        <v>2221</v>
+      </c>
+      <c r="AF72" t="s">
+        <v>2345</v>
+      </c>
+      <c r="AG72">
+        <v>1</v>
+      </c>
+      <c r="AH72">
+        <v>0</v>
+      </c>
+      <c r="AI72">
+        <v>0</v>
+      </c>
+      <c r="AJ72">
+        <v>1</v>
+      </c>
+      <c r="AK72">
+        <v>0</v>
+      </c>
+      <c r="AL72">
+        <v>0</v>
+      </c>
+      <c r="AM72">
+        <v>1</v>
+      </c>
+      <c r="AN72">
+        <v>20</v>
+      </c>
+      <c r="AO72">
+        <v>3</v>
+      </c>
+      <c r="AP72" t="s">
+        <v>2400</v>
+      </c>
+      <c r="AQ72" t="s">
+        <v>2257</v>
+      </c>
       <c r="AR72" s="4">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="AS72">
+        <v>1</v>
+      </c>
+      <c r="AT72" t="s">
+        <v>431</v>
+      </c>
+      <c r="AU72">
+        <v>2</v>
+      </c>
+      <c r="AV72" t="s">
+        <v>2225</v>
+      </c>
+      <c r="AW72">
+        <v>2</v>
+      </c>
+      <c r="BE72">
+        <v>1</v>
+      </c>
+      <c r="BF72" t="s">
+        <v>2247</v>
+      </c>
+      <c r="BI72" t="s">
+        <v>2226</v>
+      </c>
+      <c r="BL72">
+        <v>2</v>
+      </c>
+      <c r="BM72" t="s">
+        <v>855</v>
+      </c>
+      <c r="CD72">
+        <v>3</v>
+      </c>
+      <c r="CF72">
+        <v>1</v>
+      </c>
+      <c r="CI72">
+        <v>1</v>
+      </c>
+      <c r="CJ72">
+        <v>1</v>
       </c>
       <c r="CK72" s="4">
         <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="CL72">
+        <v>1</v>
+      </c>
+      <c r="DE72">
+        <v>2</v>
+      </c>
+      <c r="DF72" t="s">
+        <v>855</v>
+      </c>
+      <c r="DW72">
+        <v>4</v>
+      </c>
+      <c r="DX72" t="s">
+        <v>2273</v>
+      </c>
+      <c r="DY72">
+        <v>2024</v>
+      </c>
+      <c r="DZ72" t="s">
+        <v>2395</v>
+      </c>
+      <c r="EA72" t="s">
+        <v>2396</v>
+      </c>
+      <c r="EB72" t="s">
+        <v>2397</v>
+      </c>
+      <c r="EC72" t="s">
+        <v>2398</v>
+      </c>
+      <c r="ED72" t="s">
+        <v>2399</v>
+      </c>
+      <c r="EF72" t="s">
+        <v>441</v>
+      </c>
+      <c r="EG72" t="s">
+        <v>442</v>
+      </c>
+      <c r="FK72">
         <v>0</v>
       </c>
       <c r="FL72" s="4">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
+      <c r="FN72">
+        <v>0</v>
+      </c>
       <c r="FO72" s="4">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
+      <c r="FQ72">
+        <v>0</v>
+      </c>
       <c r="FR72" s="4">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
+      <c r="FS72" t="s">
+        <v>454</v>
+      </c>
       <c r="FT72">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="FU72" s="4">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="FV72" s="4">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="FW72" s="4" t="str">
         <f t="shared" si="27"/>
@@ -35737,34 +37121,34 @@
         <v>550</v>
       </c>
       <c r="C73" t="s">
-        <v>2268</v>
+        <v>2258</v>
       </c>
       <c r="D73" t="s">
-        <v>2269</v>
+        <v>2259</v>
       </c>
       <c r="E73" t="s">
-        <v>2270</v>
+        <v>2260</v>
       </c>
       <c r="G73" t="s">
-        <v>2271</v>
+        <v>2261</v>
       </c>
       <c r="H73" t="s">
-        <v>2288</v>
+        <v>2278</v>
       </c>
       <c r="I73" t="s">
-        <v>2272</v>
+        <v>2262</v>
       </c>
       <c r="J73">
         <v>107</v>
       </c>
       <c r="K73" t="s">
-        <v>2273</v>
+        <v>2263</v>
       </c>
       <c r="L73" t="s">
         <v>421</v>
       </c>
       <c r="M73" t="s">
-        <v>2274</v>
+        <v>2264</v>
       </c>
       <c r="N73" t="s">
         <v>423</v>
@@ -35776,13 +37160,13 @@
         <v>2241240669</v>
       </c>
       <c r="Q73" s="3" t="s">
-        <v>2275</v>
+        <v>2265</v>
       </c>
       <c r="S73" t="s">
-        <v>2276</v>
+        <v>2266</v>
       </c>
       <c r="T73" t="s">
-        <v>2229</v>
+        <v>2228</v>
       </c>
       <c r="V73">
         <v>50</v>
@@ -35809,13 +37193,13 @@
         <v>0</v>
       </c>
       <c r="AD73" t="s">
-        <v>2277</v>
+        <v>2267</v>
       </c>
       <c r="AE73" t="s">
-        <v>2278</v>
+        <v>2268</v>
       </c>
       <c r="AF73" t="s">
-        <v>2279</v>
+        <v>2269</v>
       </c>
       <c r="AG73">
         <v>2</v>
@@ -35845,10 +37229,10 @@
         <v>1</v>
       </c>
       <c r="AP73" t="s">
-        <v>2280</v>
+        <v>2270</v>
       </c>
       <c r="AQ73" t="s">
-        <v>2281</v>
+        <v>2271</v>
       </c>
       <c r="AR73" s="4">
         <f t="shared" si="28"/>
@@ -35873,10 +37257,10 @@
         <v>1</v>
       </c>
       <c r="BF73" t="s">
-        <v>2282</v>
+        <v>2272</v>
       </c>
       <c r="BI73" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
       <c r="CD73">
         <v>2</v>
@@ -35898,22 +37282,22 @@
         <v>3</v>
       </c>
       <c r="DX73" t="s">
-        <v>2283</v>
+        <v>2273</v>
       </c>
       <c r="DY73">
         <v>2024</v>
       </c>
       <c r="DZ73" t="s">
-        <v>2284</v>
+        <v>2274</v>
       </c>
       <c r="EA73" t="s">
-        <v>2285</v>
+        <v>2275</v>
       </c>
       <c r="EB73" t="s">
-        <v>2286</v>
+        <v>2276</v>
       </c>
       <c r="EC73" t="s">
-        <v>2285</v>
+        <v>2275</v>
       </c>
       <c r="ED73" t="s">
         <v>439</v>
@@ -35924,8 +37308,8 @@
       <c r="EG73" t="s">
         <v>442</v>
       </c>
-      <c r="EI73" s="11" t="s">
-        <v>2287</v>
+      <c r="EI73" s="10" t="s">
+        <v>2277</v>
       </c>
       <c r="FK73">
         <v>0</v>
@@ -35976,34 +37360,34 @@
         <v>550</v>
       </c>
       <c r="C74" t="s">
-        <v>2268</v>
+        <v>2258</v>
       </c>
       <c r="D74" t="s">
-        <v>2269</v>
+        <v>2259</v>
       </c>
       <c r="E74" t="s">
-        <v>2270</v>
+        <v>2260</v>
       </c>
       <c r="G74" t="s">
-        <v>2271</v>
+        <v>2261</v>
       </c>
       <c r="H74" t="s">
-        <v>2288</v>
+        <v>2278</v>
       </c>
       <c r="I74" t="s">
-        <v>2289</v>
+        <v>2279</v>
       </c>
       <c r="J74" t="s">
-        <v>2290</v>
+        <v>2280</v>
       </c>
       <c r="K74" t="s">
-        <v>2291</v>
+        <v>2281</v>
       </c>
       <c r="L74" t="s">
-        <v>2292</v>
+        <v>2282</v>
       </c>
       <c r="M74" t="s">
-        <v>2274</v>
+        <v>2264</v>
       </c>
       <c r="N74" t="s">
         <v>423</v>
@@ -36015,13 +37399,13 @@
         <v>2241240669</v>
       </c>
       <c r="Q74" s="3" t="s">
-        <v>2293</v>
+        <v>2283</v>
       </c>
       <c r="S74" t="s">
-        <v>2294</v>
+        <v>2284</v>
       </c>
       <c r="T74" t="s">
-        <v>2229</v>
+        <v>2228</v>
       </c>
       <c r="V74">
         <v>82</v>
@@ -36051,10 +37435,10 @@
         <v>462</v>
       </c>
       <c r="AE74" t="s">
-        <v>2278</v>
+        <v>2268</v>
       </c>
       <c r="AF74" t="s">
-        <v>2295</v>
+        <v>2285</v>
       </c>
       <c r="AG74">
         <v>3</v>
@@ -36084,10 +37468,10 @@
         <v>1</v>
       </c>
       <c r="AP74" t="s">
-        <v>2280</v>
+        <v>2270</v>
       </c>
       <c r="AQ74" t="s">
-        <v>2281</v>
+        <v>2271</v>
       </c>
       <c r="AR74" s="4">
         <f t="shared" si="28"/>
@@ -36103,7 +37487,7 @@
         <v>2</v>
       </c>
       <c r="AV74" t="s">
-        <v>2296</v>
+        <v>2286</v>
       </c>
       <c r="AW74">
         <v>2</v>
@@ -36112,10 +37496,10 @@
         <v>1</v>
       </c>
       <c r="BF74" t="s">
-        <v>2282</v>
+        <v>2272</v>
       </c>
       <c r="BI74" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
       <c r="CD74">
         <v>3</v>
@@ -36143,25 +37527,25 @@
         <v>3</v>
       </c>
       <c r="DX74" t="s">
-        <v>2283</v>
+        <v>2273</v>
       </c>
       <c r="DY74">
         <v>2024</v>
       </c>
       <c r="DZ74" t="s">
-        <v>2297</v>
+        <v>2287</v>
       </c>
       <c r="EA74" t="s">
-        <v>2298</v>
+        <v>2288</v>
       </c>
       <c r="EB74" t="s">
-        <v>2298</v>
+        <v>2288</v>
       </c>
       <c r="EC74" t="s">
         <v>1793</v>
       </c>
       <c r="ED74" t="s">
-        <v>2299</v>
+        <v>2289</v>
       </c>
       <c r="EF74" t="s">
         <v>441</v>
@@ -36169,11 +37553,11 @@
       <c r="EG74" t="s">
         <v>442</v>
       </c>
-      <c r="EI74" s="11" t="s">
-        <v>2300</v>
-      </c>
-      <c r="EL74" s="11" t="s">
-        <v>2301</v>
+      <c r="EI74" s="10" t="s">
+        <v>2290</v>
+      </c>
+      <c r="EL74" s="10" t="s">
+        <v>2291</v>
       </c>
       <c r="FK74">
         <v>0</v>
@@ -36223,33 +37607,247 @@
       <c r="B75" t="s">
         <v>2219</v>
       </c>
+      <c r="C75" t="s">
+        <v>2202</v>
+      </c>
+      <c r="D75" t="s">
+        <v>2372</v>
+      </c>
+      <c r="E75" t="s">
+        <v>2203</v>
+      </c>
+      <c r="G75" t="s">
+        <v>2304</v>
+      </c>
+      <c r="H75" t="s">
+        <v>2205</v>
+      </c>
+      <c r="I75" t="s">
+        <v>2305</v>
+      </c>
+      <c r="J75">
+        <v>216</v>
+      </c>
+      <c r="K75" t="s">
+        <v>847</v>
+      </c>
+      <c r="L75" t="s">
+        <v>421</v>
+      </c>
+      <c r="M75" t="s">
+        <v>1928</v>
+      </c>
+      <c r="N75" t="s">
+        <v>423</v>
+      </c>
+      <c r="O75">
+        <v>75700</v>
+      </c>
+      <c r="P75">
+        <v>2381366920</v>
+      </c>
+      <c r="Q75" s="3" t="s">
+        <v>2306</v>
+      </c>
+      <c r="S75" t="s">
+        <v>2307</v>
+      </c>
+      <c r="T75" t="s">
+        <v>2228</v>
+      </c>
+      <c r="V75">
+        <v>40</v>
+      </c>
+      <c r="W75">
+        <v>40</v>
+      </c>
+      <c r="X75">
+        <v>1</v>
+      </c>
+      <c r="Y75">
+        <v>1</v>
+      </c>
+      <c r="Z75">
+        <v>1</v>
+      </c>
+      <c r="AA75">
+        <v>1</v>
+      </c>
+      <c r="AB75">
+        <v>0</v>
+      </c>
+      <c r="AC75">
+        <v>0</v>
+      </c>
+      <c r="AD75" t="s">
+        <v>848</v>
+      </c>
+      <c r="AE75" t="s">
+        <v>2221</v>
+      </c>
+      <c r="AF75" t="s">
+        <v>2308</v>
+      </c>
+      <c r="AG75">
+        <v>2</v>
+      </c>
+      <c r="AH75">
+        <v>0</v>
+      </c>
+      <c r="AI75">
+        <v>1</v>
+      </c>
+      <c r="AJ75">
+        <v>1</v>
+      </c>
+      <c r="AK75">
+        <v>0</v>
+      </c>
+      <c r="AL75">
+        <v>0</v>
+      </c>
+      <c r="AM75">
+        <v>1</v>
+      </c>
+      <c r="AN75">
+        <v>65</v>
+      </c>
+      <c r="AO75">
+        <v>3</v>
+      </c>
+      <c r="AP75" t="s">
+        <v>2400</v>
+      </c>
+      <c r="AQ75" t="s">
+        <v>2257</v>
+      </c>
       <c r="AR75" s="4">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="AS75">
+        <v>1</v>
+      </c>
+      <c r="AT75" t="s">
+        <v>431</v>
+      </c>
+      <c r="AU75">
+        <v>2</v>
+      </c>
+      <c r="AV75" t="s">
+        <v>2314</v>
+      </c>
+      <c r="AW75">
+        <v>1</v>
+      </c>
+      <c r="AX75">
+        <v>1</v>
+      </c>
+      <c r="BE75">
+        <v>1</v>
+      </c>
+      <c r="BF75" t="s">
+        <v>2247</v>
+      </c>
+      <c r="BI75" t="s">
+        <v>2226</v>
+      </c>
+      <c r="BL75">
+        <v>2</v>
+      </c>
+      <c r="BM75" t="s">
+        <v>855</v>
+      </c>
+      <c r="CD75">
+        <v>1</v>
+      </c>
+      <c r="CF75">
+        <v>1</v>
+      </c>
+      <c r="CI75">
+        <v>1</v>
+      </c>
+      <c r="CJ75">
+        <v>1</v>
       </c>
       <c r="CK75" s="4">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
+      <c r="DE75">
+        <v>2</v>
+      </c>
+      <c r="DF75" t="s">
+        <v>855</v>
+      </c>
+      <c r="DW75">
+        <v>14</v>
+      </c>
+      <c r="DX75" t="s">
+        <v>2273</v>
+      </c>
+      <c r="DY75">
+        <v>2024</v>
+      </c>
+      <c r="DZ75" t="s">
+        <v>2309</v>
+      </c>
+      <c r="EA75" t="s">
+        <v>2310</v>
+      </c>
+      <c r="EB75" t="s">
+        <v>2311</v>
+      </c>
+      <c r="EC75" t="s">
+        <v>2312</v>
+      </c>
+      <c r="ED75" t="s">
+        <v>2313</v>
+      </c>
+      <c r="EF75" t="s">
+        <v>441</v>
+      </c>
+      <c r="EG75" t="s">
+        <v>442</v>
+      </c>
+      <c r="EI75" s="10" t="s">
+        <v>2315</v>
+      </c>
+      <c r="FK75">
+        <v>0</v>
+      </c>
       <c r="FL75" s="4">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
+      <c r="FN75">
+        <v>0</v>
+      </c>
       <c r="FO75" s="4">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
+      <c r="FQ75">
+        <v>0</v>
+      </c>
       <c r="FR75" s="4">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
+      <c r="FS75" t="s">
+        <v>454</v>
+      </c>
+      <c r="FT75">
+        <f t="shared" si="25"/>
+        <v>120</v>
+      </c>
       <c r="FU75" s="4">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="FV75" s="4">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="FW75" s="4" t="str">
         <f t="shared" si="27"/>
@@ -36263,33 +37861,256 @@
       <c r="B76" t="s">
         <v>2219</v>
       </c>
+      <c r="C76" t="s">
+        <v>2202</v>
+      </c>
+      <c r="D76" t="s">
+        <v>2373</v>
+      </c>
+      <c r="E76" t="s">
+        <v>2203</v>
+      </c>
+      <c r="G76" t="s">
+        <v>2304</v>
+      </c>
+      <c r="H76" t="s">
+        <v>2205</v>
+      </c>
+      <c r="I76" t="s">
+        <v>2316</v>
+      </c>
+      <c r="J76">
+        <v>2410</v>
+      </c>
+      <c r="L76" t="s">
+        <v>2317</v>
+      </c>
+      <c r="M76" t="s">
+        <v>1928</v>
+      </c>
+      <c r="N76" t="s">
+        <v>423</v>
+      </c>
+      <c r="O76">
+        <v>75750</v>
+      </c>
+      <c r="P76">
+        <v>5541789557</v>
+      </c>
+      <c r="Q76" s="3" t="s">
+        <v>2318</v>
+      </c>
+      <c r="R76">
+        <v>9</v>
+      </c>
+      <c r="S76">
+        <v>2016</v>
+      </c>
+      <c r="T76" t="s">
+        <v>2228</v>
+      </c>
+      <c r="V76">
+        <v>782</v>
+      </c>
+      <c r="W76">
+        <v>40</v>
+      </c>
+      <c r="X76">
+        <v>1</v>
+      </c>
+      <c r="Y76">
+        <v>1</v>
+      </c>
+      <c r="Z76">
+        <v>1</v>
+      </c>
+      <c r="AA76">
+        <v>1</v>
+      </c>
+      <c r="AB76">
+        <v>0</v>
+      </c>
+      <c r="AC76">
+        <v>0</v>
+      </c>
+      <c r="AD76" t="s">
+        <v>2267</v>
+      </c>
+      <c r="AE76" t="s">
+        <v>2221</v>
+      </c>
+      <c r="AF76" t="s">
+        <v>2319</v>
+      </c>
+      <c r="AG76">
+        <v>1</v>
+      </c>
+      <c r="AH76">
+        <v>0</v>
+      </c>
+      <c r="AI76">
+        <v>1</v>
+      </c>
+      <c r="AJ76">
+        <v>0</v>
+      </c>
+      <c r="AK76">
+        <v>0</v>
+      </c>
+      <c r="AL76">
+        <v>0</v>
+      </c>
+      <c r="AM76">
+        <v>1</v>
+      </c>
+      <c r="AN76">
+        <v>30</v>
+      </c>
+      <c r="AO76">
+        <v>3</v>
+      </c>
+      <c r="AP76" t="s">
+        <v>2400</v>
+      </c>
+      <c r="AQ76" t="s">
+        <v>2257</v>
+      </c>
       <c r="AR76" s="4">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="AS76">
+        <v>1</v>
+      </c>
+      <c r="AT76" t="s">
+        <v>431</v>
+      </c>
+      <c r="AU76">
+        <v>2</v>
+      </c>
+      <c r="AV76" t="s">
+        <v>2314</v>
+      </c>
+      <c r="AW76">
+        <v>1</v>
+      </c>
+      <c r="AX76">
+        <v>1</v>
+      </c>
+      <c r="BC76">
+        <v>1</v>
+      </c>
+      <c r="BD76" t="s">
+        <v>431</v>
+      </c>
+      <c r="BE76">
+        <v>1</v>
+      </c>
+      <c r="BF76" t="s">
+        <v>2247</v>
+      </c>
+      <c r="BI76" t="s">
+        <v>2226</v>
+      </c>
+      <c r="BL76">
+        <v>2</v>
+      </c>
+      <c r="BM76" t="s">
+        <v>855</v>
+      </c>
+      <c r="CD76">
+        <v>4</v>
+      </c>
+      <c r="CF76">
+        <v>1</v>
+      </c>
+      <c r="CH76">
+        <v>1</v>
+      </c>
+      <c r="CI76">
+        <v>2</v>
+      </c>
+      <c r="CJ76">
+        <v>2</v>
       </c>
       <c r="CK76" s="4">
         <f t="shared" si="19"/>
+        <v>2</v>
+      </c>
+      <c r="CL76">
+        <v>2</v>
+      </c>
+      <c r="DE76">
+        <v>3</v>
+      </c>
+      <c r="DF76" t="s">
+        <v>855</v>
+      </c>
+      <c r="DW76">
+        <v>14</v>
+      </c>
+      <c r="DX76" t="s">
+        <v>2273</v>
+      </c>
+      <c r="DY76">
+        <v>2024</v>
+      </c>
+      <c r="DZ76" t="s">
+        <v>2320</v>
+      </c>
+      <c r="EA76" t="s">
+        <v>2321</v>
+      </c>
+      <c r="EB76" t="s">
+        <v>2322</v>
+      </c>
+      <c r="EC76" t="s">
+        <v>2323</v>
+      </c>
+      <c r="ED76" t="s">
+        <v>2324</v>
+      </c>
+      <c r="EF76" t="s">
+        <v>441</v>
+      </c>
+      <c r="EG76" t="s">
+        <v>442</v>
+      </c>
+      <c r="FK76">
         <v>0</v>
       </c>
       <c r="FL76" s="4">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
+      <c r="FN76">
+        <v>0</v>
+      </c>
       <c r="FO76" s="4">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
+      <c r="FQ76">
+        <v>0</v>
+      </c>
       <c r="FR76" s="4">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
+      <c r="FS76" t="s">
+        <v>454</v>
+      </c>
+      <c r="FT76">
+        <f t="shared" si="25"/>
+        <v>60</v>
+      </c>
       <c r="FU76" s="4">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="FV76" s="4">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="FW76" s="4" t="str">
         <f t="shared" si="27"/>
@@ -36303,33 +38124,256 @@
       <c r="B77" t="s">
         <v>2219</v>
       </c>
+      <c r="C77" t="s">
+        <v>2202</v>
+      </c>
+      <c r="D77" t="s">
+        <v>2374</v>
+      </c>
+      <c r="E77" t="s">
+        <v>2203</v>
+      </c>
+      <c r="G77" t="s">
+        <v>2304</v>
+      </c>
+      <c r="H77" t="s">
+        <v>2205</v>
+      </c>
+      <c r="I77" t="s">
+        <v>2346</v>
+      </c>
+      <c r="J77">
+        <v>801</v>
+      </c>
+      <c r="K77" t="s">
+        <v>2347</v>
+      </c>
+      <c r="L77" t="s">
+        <v>2348</v>
+      </c>
+      <c r="M77" t="s">
+        <v>1622</v>
+      </c>
+      <c r="N77" t="s">
+        <v>423</v>
+      </c>
+      <c r="O77">
+        <v>75480</v>
+      </c>
+      <c r="P77">
+        <v>2221637713</v>
+      </c>
+      <c r="Q77" s="3" t="s">
+        <v>2349</v>
+      </c>
+      <c r="R77">
+        <v>9</v>
+      </c>
+      <c r="S77" t="s">
+        <v>2490</v>
+      </c>
+      <c r="T77" t="s">
+        <v>2228</v>
+      </c>
+      <c r="V77">
+        <v>45</v>
+      </c>
+      <c r="W77">
+        <v>45</v>
+      </c>
+      <c r="X77">
+        <v>1</v>
+      </c>
+      <c r="Y77">
+        <v>1</v>
+      </c>
+      <c r="Z77">
+        <v>1</v>
+      </c>
+      <c r="AA77">
+        <v>1</v>
+      </c>
+      <c r="AB77">
+        <v>0</v>
+      </c>
+      <c r="AC77">
+        <v>0</v>
+      </c>
+      <c r="AD77" t="s">
+        <v>1234</v>
+      </c>
+      <c r="AE77" t="s">
+        <v>2221</v>
+      </c>
+      <c r="AF77" t="s">
+        <v>2350</v>
+      </c>
+      <c r="AG77">
+        <v>1</v>
+      </c>
+      <c r="AH77">
+        <v>0</v>
+      </c>
+      <c r="AI77">
+        <v>1</v>
+      </c>
+      <c r="AJ77">
+        <v>0</v>
+      </c>
+      <c r="AK77">
+        <v>0</v>
+      </c>
+      <c r="AL77">
+        <v>0</v>
+      </c>
+      <c r="AM77">
+        <v>1</v>
+      </c>
+      <c r="AN77">
+        <v>25</v>
+      </c>
+      <c r="AO77">
+        <v>3</v>
+      </c>
+      <c r="AP77" t="s">
+        <v>2400</v>
+      </c>
+      <c r="AQ77" t="s">
+        <v>2257</v>
+      </c>
       <c r="AR77" s="4">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="AS77">
+        <v>1</v>
+      </c>
+      <c r="AT77" t="s">
+        <v>431</v>
+      </c>
+      <c r="AU77">
+        <v>2</v>
+      </c>
+      <c r="AV77" t="s">
+        <v>2314</v>
+      </c>
+      <c r="AW77">
+        <v>1</v>
+      </c>
+      <c r="AX77">
+        <v>1</v>
+      </c>
+      <c r="BC77">
+        <v>1</v>
+      </c>
+      <c r="BD77" t="s">
+        <v>431</v>
+      </c>
+      <c r="BE77">
+        <v>1</v>
+      </c>
+      <c r="BF77" t="s">
+        <v>2247</v>
+      </c>
+      <c r="BI77" t="s">
+        <v>2226</v>
+      </c>
+      <c r="BL77">
+        <v>2</v>
+      </c>
+      <c r="BM77" t="s">
+        <v>855</v>
+      </c>
+      <c r="CD77">
+        <v>4</v>
+      </c>
+      <c r="CF77">
+        <v>1</v>
+      </c>
+      <c r="CI77">
+        <v>2</v>
+      </c>
+      <c r="CJ77">
+        <v>2</v>
       </c>
       <c r="CK77" s="4">
         <f t="shared" si="19"/>
+        <v>2</v>
+      </c>
+      <c r="CL77">
+        <v>2</v>
+      </c>
+      <c r="DE77">
+        <v>2</v>
+      </c>
+      <c r="DF77" t="s">
+        <v>855</v>
+      </c>
+      <c r="DW77">
+        <v>13</v>
+      </c>
+      <c r="DX77" t="s">
+        <v>2273</v>
+      </c>
+      <c r="DY77">
+        <v>2024</v>
+      </c>
+      <c r="DZ77" t="s">
+        <v>2491</v>
+      </c>
+      <c r="EA77" t="s">
+        <v>2492</v>
+      </c>
+      <c r="EB77" t="s">
+        <v>2493</v>
+      </c>
+      <c r="EC77" t="s">
+        <v>2494</v>
+      </c>
+      <c r="ED77" t="s">
+        <v>2495</v>
+      </c>
+      <c r="EF77" t="s">
+        <v>441</v>
+      </c>
+      <c r="EG77" t="s">
+        <v>442</v>
+      </c>
+      <c r="FK77">
         <v>0</v>
       </c>
       <c r="FL77" s="4">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
+      <c r="FN77">
+        <v>0</v>
+      </c>
       <c r="FO77" s="4">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
+      <c r="FQ77">
+        <v>0</v>
+      </c>
       <c r="FR77" s="4">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
+      <c r="FS77" t="s">
+        <v>454</v>
+      </c>
+      <c r="FT77">
+        <f t="shared" si="25"/>
+        <v>60</v>
+      </c>
       <c r="FU77" s="4">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="FV77" s="4">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="FW77" s="4" t="str">
         <f t="shared" si="27"/>
@@ -36347,25 +38391,25 @@
         <v>1942</v>
       </c>
       <c r="D78" t="s">
-        <v>2307</v>
+        <v>2297</v>
       </c>
       <c r="E78" t="s">
         <v>1944</v>
       </c>
       <c r="G78" t="s">
-        <v>2302</v>
+        <v>2292</v>
       </c>
       <c r="H78" t="s">
         <v>1966</v>
       </c>
       <c r="I78" t="s">
-        <v>2303</v>
+        <v>2293</v>
       </c>
       <c r="J78">
         <v>107</v>
       </c>
       <c r="K78" t="s">
-        <v>2304</v>
+        <v>2294</v>
       </c>
       <c r="L78" t="s">
         <v>421</v>
@@ -36383,13 +38427,13 @@
         <v>2383806932</v>
       </c>
       <c r="Q78" s="3" t="s">
-        <v>2305</v>
+        <v>2295</v>
       </c>
       <c r="S78" t="s">
-        <v>2306</v>
+        <v>2296</v>
       </c>
       <c r="T78" t="s">
-        <v>2229</v>
+        <v>2228</v>
       </c>
       <c r="V78">
         <v>25</v>
@@ -36422,7 +38466,7 @@
         <v>1949</v>
       </c>
       <c r="AF78" t="s">
-        <v>2308</v>
+        <v>2298</v>
       </c>
       <c r="AG78">
         <v>2</v>
@@ -36452,10 +38496,10 @@
         <v>2</v>
       </c>
       <c r="AP78" t="s">
-        <v>2280</v>
+        <v>2270</v>
       </c>
       <c r="AQ78" t="s">
-        <v>2309</v>
+        <v>2299</v>
       </c>
       <c r="AR78" s="4">
         <f t="shared" si="28"/>
@@ -36471,7 +38515,7 @@
         <v>2</v>
       </c>
       <c r="AV78" t="s">
-        <v>2310</v>
+        <v>2300</v>
       </c>
       <c r="AW78">
         <v>2</v>
@@ -36511,22 +38555,22 @@
         <v>14</v>
       </c>
       <c r="DX78" t="s">
-        <v>2283</v>
+        <v>2273</v>
       </c>
       <c r="DY78">
         <v>2024</v>
       </c>
       <c r="DZ78" t="s">
-        <v>2311</v>
+        <v>2301</v>
       </c>
       <c r="EA78" t="s">
-        <v>2298</v>
+        <v>2288</v>
       </c>
       <c r="EB78" t="s">
-        <v>2298</v>
+        <v>2288</v>
       </c>
       <c r="EC78" t="s">
-        <v>2312</v>
+        <v>2302</v>
       </c>
       <c r="ED78" t="s">
         <v>1793</v>
@@ -36537,7 +38581,7 @@
       <c r="EG78" t="s">
         <v>442</v>
       </c>
-      <c r="EI78" s="11" t="s">
+      <c r="EI78" s="10" t="s">
         <v>1961</v>
       </c>
       <c r="FK78">
@@ -36548,7 +38592,7 @@
         <v>0</v>
       </c>
       <c r="FM78" t="s">
-        <v>2313</v>
+        <v>2303</v>
       </c>
       <c r="FN78">
         <v>101</v>
@@ -36568,7 +38612,7 @@
         <v>454</v>
       </c>
       <c r="FT78">
-        <f t="shared" ref="FT78" si="33">60*AG78</f>
+        <f t="shared" ref="FT78:FT79" si="33">60*AG78</f>
         <v>120</v>
       </c>
       <c r="FU78" s="4">
@@ -36588,70 +38632,536 @@
       <c r="A79">
         <v>77</v>
       </c>
+      <c r="B79" t="s">
+        <v>2506</v>
+      </c>
+      <c r="C79" t="s">
+        <v>2371</v>
+      </c>
+      <c r="D79" t="s">
+        <v>2370</v>
+      </c>
+      <c r="E79" t="s">
+        <v>2351</v>
+      </c>
+      <c r="G79" t="s">
+        <v>2352</v>
+      </c>
+      <c r="H79" t="s">
+        <v>2353</v>
+      </c>
+      <c r="I79" t="s">
+        <v>2354</v>
+      </c>
+      <c r="J79" t="s">
+        <v>2355</v>
+      </c>
+      <c r="L79" t="s">
+        <v>2356</v>
+      </c>
+      <c r="M79" t="s">
+        <v>2328</v>
+      </c>
+      <c r="N79" t="s">
+        <v>423</v>
+      </c>
+      <c r="O79">
+        <v>73310</v>
+      </c>
+      <c r="P79">
+        <v>2216678745</v>
+      </c>
+      <c r="Q79" s="3" t="s">
+        <v>2357</v>
+      </c>
+      <c r="R79">
+        <v>3</v>
+      </c>
+      <c r="S79" t="s">
+        <v>2358</v>
+      </c>
+      <c r="T79" t="s">
+        <v>2228</v>
+      </c>
+      <c r="V79">
+        <v>2500</v>
+      </c>
+      <c r="W79">
+        <v>2500</v>
+      </c>
+      <c r="X79">
+        <v>1</v>
+      </c>
+      <c r="Y79">
+        <v>1</v>
+      </c>
+      <c r="Z79">
+        <v>2</v>
+      </c>
+      <c r="AA79">
+        <v>2</v>
+      </c>
+      <c r="AB79">
+        <v>0</v>
+      </c>
+      <c r="AC79">
+        <v>0</v>
+      </c>
+      <c r="AD79" t="s">
+        <v>911</v>
+      </c>
+      <c r="AE79" t="s">
+        <v>2359</v>
+      </c>
+      <c r="AF79" t="s">
+        <v>2360</v>
+      </c>
+      <c r="AG79">
+        <v>3</v>
+      </c>
+      <c r="AH79">
+        <v>0</v>
+      </c>
+      <c r="AI79">
+        <v>2</v>
+      </c>
+      <c r="AJ79">
+        <v>1</v>
+      </c>
+      <c r="AK79">
+        <v>0</v>
+      </c>
+      <c r="AL79">
+        <v>0</v>
+      </c>
+      <c r="AM79">
+        <v>2</v>
+      </c>
+      <c r="AN79">
+        <v>30</v>
+      </c>
+      <c r="AO79">
+        <v>3</v>
+      </c>
+      <c r="AP79" t="s">
+        <v>2270</v>
+      </c>
+      <c r="AQ79" t="s">
+        <v>430</v>
+      </c>
       <c r="AR79" s="4">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>31</v>
+      </c>
+      <c r="AS79">
+        <v>1</v>
+      </c>
+      <c r="AT79" t="s">
+        <v>753</v>
+      </c>
+      <c r="AU79">
+        <v>11</v>
+      </c>
+      <c r="AV79" t="s">
+        <v>2361</v>
+      </c>
+      <c r="AW79">
+        <v>10</v>
+      </c>
+      <c r="AX79">
+        <v>1</v>
+      </c>
+      <c r="AY79">
+        <v>2</v>
+      </c>
+      <c r="AZ79" t="s">
+        <v>2362</v>
+      </c>
+      <c r="BE79">
+        <v>2</v>
+      </c>
+      <c r="BF79" t="s">
+        <v>2363</v>
+      </c>
+      <c r="BI79" t="s">
+        <v>2362</v>
+      </c>
+      <c r="CD79">
+        <v>11</v>
+      </c>
+      <c r="CF79">
+        <v>2</v>
+      </c>
+      <c r="CH79">
+        <v>1</v>
+      </c>
+      <c r="CI79">
+        <v>3</v>
+      </c>
+      <c r="CJ79">
+        <v>1</v>
       </c>
       <c r="CK79" s="4">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="CL79">
+        <v>5</v>
+      </c>
+      <c r="DW79">
+        <v>25</v>
+      </c>
+      <c r="DX79" t="s">
+        <v>2273</v>
+      </c>
+      <c r="DY79">
+        <v>2024</v>
+      </c>
+      <c r="DZ79" t="s">
+        <v>2364</v>
+      </c>
+      <c r="EA79" t="s">
+        <v>553</v>
+      </c>
+      <c r="EB79" t="s">
+        <v>2365</v>
+      </c>
+      <c r="EC79" t="s">
+        <v>1957</v>
+      </c>
+      <c r="ED79" t="s">
+        <v>818</v>
+      </c>
+      <c r="EF79" t="s">
+        <v>441</v>
+      </c>
+      <c r="EG79" t="s">
+        <v>442</v>
+      </c>
+      <c r="EI79" s="10" t="s">
+        <v>2366</v>
+      </c>
+      <c r="EL79" s="10" t="s">
+        <v>2367</v>
+      </c>
+      <c r="EO79" s="10" t="s">
+        <v>2368</v>
+      </c>
+      <c r="ER79" s="10" t="s">
+        <v>2369</v>
+      </c>
+      <c r="FJ79" t="s">
+        <v>2109</v>
+      </c>
+      <c r="FK79">
+        <v>4934</v>
       </c>
       <c r="FL79" s="4">
         <f t="shared" si="30"/>
+        <v>1.6446666666666667</v>
+      </c>
+      <c r="FN79">
         <v>0</v>
       </c>
       <c r="FO79" s="4">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
+      <c r="FQ79">
+        <v>0</v>
+      </c>
       <c r="FR79" s="4">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
+      <c r="FS79" t="s">
+        <v>454</v>
+      </c>
+      <c r="FT79">
+        <f t="shared" si="33"/>
+        <v>180</v>
+      </c>
       <c r="FU79" s="4">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1.2E-2</v>
       </c>
       <c r="FV79" s="4">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>1.6566666666666667</v>
       </c>
       <c r="FW79" s="4" t="str">
         <f t="shared" si="27"/>
-        <v>ORDINARIO</v>
+        <v>ALTO</v>
       </c>
     </row>
     <row r="80" spans="1:179" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>78</v>
       </c>
+      <c r="B80" t="s">
+        <v>550</v>
+      </c>
+      <c r="C80" t="s">
+        <v>2401</v>
+      </c>
+      <c r="D80" t="s">
+        <v>2402</v>
+      </c>
+      <c r="E80" t="s">
+        <v>2403</v>
+      </c>
+      <c r="G80" t="s">
+        <v>2404</v>
+      </c>
+      <c r="H80" t="s">
+        <v>2405</v>
+      </c>
+      <c r="I80" t="s">
+        <v>2406</v>
+      </c>
+      <c r="J80">
+        <v>506</v>
+      </c>
+      <c r="L80" t="s">
+        <v>421</v>
+      </c>
+      <c r="M80" t="s">
+        <v>423</v>
+      </c>
+      <c r="N80" t="s">
+        <v>423</v>
+      </c>
+      <c r="O80">
+        <v>72000</v>
+      </c>
+      <c r="P80">
+        <v>2222969953</v>
+      </c>
+      <c r="Q80" s="9" t="s">
+        <v>2131</v>
+      </c>
+      <c r="R80">
+        <v>34</v>
+      </c>
+      <c r="S80" t="s">
+        <v>2407</v>
+      </c>
+      <c r="T80" t="s">
+        <v>2228</v>
+      </c>
+      <c r="V80">
+        <v>591</v>
+      </c>
+      <c r="W80">
+        <v>878</v>
+      </c>
+      <c r="X80">
+        <v>1</v>
+      </c>
+      <c r="Y80">
+        <v>2</v>
+      </c>
+      <c r="Z80">
+        <v>2</v>
+      </c>
+      <c r="AA80">
+        <v>2</v>
+      </c>
+      <c r="AB80">
+        <v>1</v>
+      </c>
+      <c r="AC80">
+        <v>0</v>
+      </c>
+      <c r="AD80" t="s">
+        <v>848</v>
+      </c>
+      <c r="AE80" t="s">
+        <v>2401</v>
+      </c>
+      <c r="AF80" t="s">
+        <v>2408</v>
+      </c>
+      <c r="AG80">
+        <v>10</v>
+      </c>
+      <c r="AH80">
+        <v>0</v>
+      </c>
+      <c r="AI80">
+        <v>4</v>
+      </c>
+      <c r="AJ80">
+        <v>6</v>
+      </c>
+      <c r="AK80">
+        <v>0</v>
+      </c>
+      <c r="AL80">
+        <v>0</v>
+      </c>
+      <c r="AM80">
+        <v>1</v>
+      </c>
+      <c r="AN80">
+        <v>30</v>
+      </c>
+      <c r="AO80">
+        <v>4</v>
+      </c>
+      <c r="AP80" t="s">
+        <v>2270</v>
+      </c>
+      <c r="AQ80" t="s">
+        <v>2409</v>
+      </c>
       <c r="AR80" s="4">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="AS80">
+        <v>2</v>
+      </c>
+      <c r="AT80" t="s">
+        <v>2412</v>
+      </c>
+      <c r="AU80">
+        <v>7</v>
+      </c>
+      <c r="AV80" t="s">
+        <v>2413</v>
+      </c>
+      <c r="AW80">
+        <v>6</v>
+      </c>
+      <c r="AX80">
+        <v>1</v>
+      </c>
+      <c r="BE80">
+        <v>1</v>
+      </c>
+      <c r="BF80" t="s">
+        <v>2068</v>
+      </c>
+      <c r="BI80" t="s">
+        <v>2414</v>
+      </c>
+      <c r="CD80">
+        <v>17</v>
+      </c>
+      <c r="CE80">
+        <v>2</v>
+      </c>
+      <c r="CF80">
+        <v>2</v>
+      </c>
+      <c r="CI80">
+        <v>2</v>
+      </c>
+      <c r="CJ80">
+        <v>3</v>
       </c>
       <c r="CK80" s="4">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="CL80">
+        <v>2</v>
+      </c>
+      <c r="DW80">
+        <v>1</v>
+      </c>
+      <c r="DX80" t="s">
+        <v>2411</v>
+      </c>
+      <c r="DY80">
+        <v>2024</v>
+      </c>
+      <c r="DZ80" t="s">
+        <v>2410</v>
+      </c>
+      <c r="EA80" t="s">
+        <v>2415</v>
+      </c>
+      <c r="EB80" t="s">
+        <v>2416</v>
+      </c>
+      <c r="EC80" t="s">
+        <v>2418</v>
+      </c>
+      <c r="ED80" t="s">
+        <v>2417</v>
+      </c>
+      <c r="EF80" t="s">
+        <v>441</v>
+      </c>
+      <c r="EG80" t="s">
+        <v>442</v>
+      </c>
+      <c r="EI80" s="10" t="s">
+        <v>2419</v>
+      </c>
+      <c r="EL80" s="10" t="s">
+        <v>2420</v>
+      </c>
+      <c r="EO80" s="10" t="s">
+        <v>2421</v>
+      </c>
+      <c r="ER80" s="10" t="s">
+        <v>2422</v>
+      </c>
+      <c r="EU80" s="10" t="s">
+        <v>2423</v>
+      </c>
+      <c r="EX80" s="10" t="s">
+        <v>2424</v>
+      </c>
+      <c r="FA80" s="10" t="s">
+        <v>2425</v>
+      </c>
+      <c r="FD80" s="10" t="s">
+        <v>2426</v>
+      </c>
+      <c r="FG80" s="10" t="s">
+        <v>2427</v>
+      </c>
+      <c r="FJ80" t="s">
+        <v>2109</v>
+      </c>
+      <c r="FK80">
+        <v>480</v>
       </c>
       <c r="FL80" s="4">
         <f t="shared" si="30"/>
+        <v>0.16</v>
+      </c>
+      <c r="FN80">
         <v>0</v>
       </c>
       <c r="FO80" s="4">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
+      <c r="FQ80">
+        <v>0</v>
+      </c>
       <c r="FR80" s="4">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
+      <c r="FS80" t="s">
+        <v>454</v>
+      </c>
+      <c r="FT80">
+        <v>1000</v>
+      </c>
       <c r="FU80" s="4">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="FV80" s="4">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>0.22666666666666668</v>
       </c>
       <c r="FW80" s="4" t="str">
         <f t="shared" si="27"/>
@@ -36662,148 +39172,1129 @@
       <c r="A81">
         <v>79</v>
       </c>
+      <c r="B81" t="s">
+        <v>577</v>
+      </c>
+      <c r="C81" t="s">
+        <v>2428</v>
+      </c>
+      <c r="D81" t="s">
+        <v>2429</v>
+      </c>
+      <c r="E81" t="s">
+        <v>2430</v>
+      </c>
+      <c r="F81" t="s">
+        <v>2431</v>
+      </c>
+      <c r="G81" t="s">
+        <v>2432</v>
+      </c>
+      <c r="H81" t="s">
+        <v>2433</v>
+      </c>
+      <c r="I81" t="s">
+        <v>2434</v>
+      </c>
+      <c r="J81" t="s">
+        <v>2435</v>
+      </c>
+      <c r="K81" s="9" t="s">
+        <v>2131</v>
+      </c>
+      <c r="L81" t="s">
+        <v>2436</v>
+      </c>
+      <c r="M81" t="s">
+        <v>2437</v>
+      </c>
+      <c r="N81" t="s">
+        <v>423</v>
+      </c>
+      <c r="O81">
+        <v>75160</v>
+      </c>
+      <c r="P81">
+        <v>2494510215</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>2438</v>
+      </c>
+      <c r="R81">
+        <v>9</v>
+      </c>
+      <c r="S81" t="s">
+        <v>2439</v>
+      </c>
+      <c r="T81" t="s">
+        <v>2228</v>
+      </c>
+      <c r="V81">
+        <v>3372.65</v>
+      </c>
+      <c r="W81">
+        <v>3372.65</v>
+      </c>
+      <c r="X81">
+        <v>1</v>
+      </c>
+      <c r="Y81">
+        <v>1</v>
+      </c>
+      <c r="Z81">
+        <v>2</v>
+      </c>
+      <c r="AA81">
+        <v>2</v>
+      </c>
+      <c r="AB81">
+        <v>0</v>
+      </c>
+      <c r="AC81">
+        <v>0</v>
+      </c>
+      <c r="AD81" t="s">
+        <v>911</v>
+      </c>
+      <c r="AE81" t="s">
+        <v>2440</v>
+      </c>
+      <c r="AF81" t="s">
+        <v>2441</v>
+      </c>
+      <c r="AG81">
+        <v>6</v>
+      </c>
+      <c r="AH81">
+        <v>0</v>
+      </c>
+      <c r="AI81">
+        <v>4</v>
+      </c>
+      <c r="AJ81">
+        <v>2</v>
+      </c>
+      <c r="AK81">
+        <v>0</v>
+      </c>
+      <c r="AL81">
+        <v>0</v>
+      </c>
+      <c r="AM81">
+        <v>2</v>
+      </c>
+      <c r="AN81">
+        <v>480</v>
+      </c>
+      <c r="AO81">
+        <v>6</v>
+      </c>
+      <c r="AP81" t="s">
+        <v>2270</v>
+      </c>
+      <c r="AQ81" t="s">
+        <v>2442</v>
+      </c>
       <c r="AR81" s="4">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="AS81">
+        <v>1</v>
+      </c>
+      <c r="AT81" t="s">
+        <v>753</v>
+      </c>
+      <c r="AU81">
+        <v>7</v>
+      </c>
+      <c r="AV81" t="s">
+        <v>2446</v>
+      </c>
+      <c r="AW81">
+        <v>6</v>
+      </c>
+      <c r="AX81">
+        <v>1</v>
+      </c>
+      <c r="AY81">
+        <v>6</v>
+      </c>
+      <c r="AZ81" t="s">
+        <v>2459</v>
+      </c>
+      <c r="BC81">
+        <v>1</v>
+      </c>
+      <c r="BD81" t="s">
+        <v>1657</v>
+      </c>
+      <c r="BE81">
+        <v>1</v>
+      </c>
+      <c r="BF81" t="s">
+        <v>752</v>
+      </c>
+      <c r="BI81" t="s">
+        <v>753</v>
+      </c>
+      <c r="CD81">
+        <v>4</v>
+      </c>
+      <c r="CJ81">
+        <v>1</v>
       </c>
       <c r="CK81" s="4">
         <f t="shared" si="29"/>
+        <v>9</v>
+      </c>
+      <c r="CL81">
+        <v>3</v>
+      </c>
+      <c r="CN81">
+        <v>3</v>
+      </c>
+      <c r="CO81">
+        <v>3</v>
+      </c>
+      <c r="DI81">
+        <v>3</v>
+      </c>
+      <c r="DJ81" t="s">
+        <v>775</v>
+      </c>
+      <c r="DK81">
+        <v>2</v>
+      </c>
+      <c r="DL81">
+        <v>60000</v>
+      </c>
+      <c r="DM81">
+        <v>30000</v>
+      </c>
+      <c r="DW81">
+        <v>10</v>
+      </c>
+      <c r="DX81" t="s">
+        <v>2411</v>
+      </c>
+      <c r="DY81">
+        <v>2024</v>
+      </c>
+      <c r="DZ81" t="s">
+        <v>2443</v>
+      </c>
+      <c r="EA81" t="s">
+        <v>2444</v>
+      </c>
+      <c r="EB81" t="s">
+        <v>2445</v>
+      </c>
+      <c r="EC81" t="s">
+        <v>439</v>
+      </c>
+      <c r="ED81" t="s">
+        <v>439</v>
+      </c>
+      <c r="EF81" t="s">
+        <v>441</v>
+      </c>
+      <c r="EG81" t="s">
+        <v>442</v>
+      </c>
+      <c r="EI81" s="10" t="s">
+        <v>2447</v>
+      </c>
+      <c r="EL81" t="s">
+        <v>2448</v>
+      </c>
+      <c r="ER81" s="10" t="s">
+        <v>2449</v>
+      </c>
+      <c r="EX81" s="10" t="s">
+        <v>2450</v>
+      </c>
+      <c r="FD81" s="10" t="s">
+        <v>2451</v>
+      </c>
+      <c r="FK81">
         <v>0</v>
       </c>
       <c r="FL81" s="4">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
+      <c r="FM81" t="s">
+        <v>453</v>
+      </c>
+      <c r="FN81">
+        <v>60000</v>
+      </c>
       <c r="FO81" s="4">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>42.857142857142854</v>
+      </c>
+      <c r="FP81" t="s">
+        <v>759</v>
+      </c>
+      <c r="FQ81">
+        <v>30060</v>
       </c>
       <c r="FR81" s="4">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>15.03</v>
+      </c>
+      <c r="FS81" t="s">
+        <v>454</v>
+      </c>
+      <c r="FT81">
+        <v>300</v>
       </c>
       <c r="FU81" s="4">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="FV81" s="4">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>57.907142857142858</v>
       </c>
       <c r="FW81" s="4" t="str">
         <f t="shared" si="27"/>
-        <v>ORDINARIO</v>
+        <v>ALTO</v>
       </c>
     </row>
     <row r="82" spans="1:179" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>80</v>
       </c>
+      <c r="B82" t="s">
+        <v>577</v>
+      </c>
+      <c r="C82" t="s">
+        <v>2428</v>
+      </c>
+      <c r="D82" t="s">
+        <v>2452</v>
+      </c>
+      <c r="E82" t="s">
+        <v>2430</v>
+      </c>
+      <c r="F82" t="s">
+        <v>2453</v>
+      </c>
+      <c r="G82" t="s">
+        <v>2432</v>
+      </c>
+      <c r="H82" t="s">
+        <v>2433</v>
+      </c>
+      <c r="I82" t="s">
+        <v>2454</v>
+      </c>
+      <c r="J82" s="9" t="s">
+        <v>2131</v>
+      </c>
+      <c r="K82" t="s">
+        <v>847</v>
+      </c>
+      <c r="L82" t="s">
+        <v>2455</v>
+      </c>
+      <c r="M82" t="s">
+        <v>2455</v>
+      </c>
+      <c r="N82" t="s">
+        <v>423</v>
+      </c>
+      <c r="O82">
+        <v>75020</v>
+      </c>
+      <c r="P82">
+        <v>2764770057</v>
+      </c>
+      <c r="Q82" s="3" t="s">
+        <v>2456</v>
+      </c>
+      <c r="R82">
+        <v>32</v>
+      </c>
+      <c r="S82" t="s">
+        <v>2457</v>
+      </c>
+      <c r="T82" t="s">
+        <v>2228</v>
+      </c>
+      <c r="V82">
+        <v>1600</v>
+      </c>
+      <c r="W82">
+        <v>1600</v>
+      </c>
+      <c r="X82">
+        <v>1</v>
+      </c>
+      <c r="Y82">
+        <v>2</v>
+      </c>
+      <c r="Z82">
+        <v>2</v>
+      </c>
+      <c r="AA82">
+        <v>2</v>
+      </c>
+      <c r="AB82">
+        <v>0</v>
+      </c>
+      <c r="AC82">
+        <v>0</v>
+      </c>
+      <c r="AD82" t="s">
+        <v>462</v>
+      </c>
+      <c r="AE82" t="s">
+        <v>2440</v>
+      </c>
+      <c r="AF82" t="s">
+        <v>2458</v>
+      </c>
+      <c r="AG82">
+        <v>7</v>
+      </c>
+      <c r="AH82">
+        <v>0</v>
+      </c>
+      <c r="AI82">
+        <v>5</v>
+      </c>
+      <c r="AJ82">
+        <v>2</v>
+      </c>
+      <c r="AK82">
+        <v>0</v>
+      </c>
+      <c r="AL82">
+        <v>0</v>
+      </c>
+      <c r="AM82">
+        <v>2</v>
+      </c>
+      <c r="AN82">
+        <v>790</v>
+      </c>
+      <c r="AO82">
+        <v>6</v>
+      </c>
+      <c r="AP82" t="s">
+        <v>2270</v>
+      </c>
+      <c r="AQ82" t="s">
+        <v>2442</v>
+      </c>
       <c r="AR82" s="4">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="AU82">
+        <v>7</v>
+      </c>
+      <c r="AV82" t="s">
+        <v>2446</v>
+      </c>
+      <c r="AW82">
+        <v>6</v>
+      </c>
+      <c r="AX82">
+        <v>1</v>
+      </c>
+      <c r="AY82">
+        <v>5</v>
+      </c>
+      <c r="AZ82" t="s">
+        <v>2459</v>
+      </c>
+      <c r="BC82">
+        <v>1</v>
+      </c>
+      <c r="BD82" t="s">
+        <v>753</v>
+      </c>
+      <c r="CD82">
+        <v>1</v>
+      </c>
+      <c r="CH82">
+        <v>1</v>
       </c>
       <c r="CK82" s="4">
         <f t="shared" si="29"/>
+        <v>13</v>
+      </c>
+      <c r="CL82">
+        <v>7</v>
+      </c>
+      <c r="CO82">
+        <v>6</v>
+      </c>
+      <c r="DI82">
+        <v>4</v>
+      </c>
+      <c r="DJ82" t="s">
+        <v>775</v>
+      </c>
+      <c r="DK82">
+        <v>3</v>
+      </c>
+      <c r="DL82">
+        <v>40000</v>
+      </c>
+      <c r="DM82">
+        <v>40000</v>
+      </c>
+      <c r="DN82">
+        <v>40000</v>
+      </c>
+      <c r="DW82">
+        <v>10</v>
+      </c>
+      <c r="DX82" t="s">
+        <v>2411</v>
+      </c>
+      <c r="DY82">
+        <v>2024</v>
+      </c>
+      <c r="DZ82" t="s">
+        <v>2460</v>
+      </c>
+      <c r="EA82" t="s">
+        <v>1871</v>
+      </c>
+      <c r="EB82" t="s">
+        <v>2461</v>
+      </c>
+      <c r="EC82" t="s">
+        <v>2313</v>
+      </c>
+      <c r="ED82" t="s">
+        <v>2462</v>
+      </c>
+      <c r="EF82" t="s">
+        <v>441</v>
+      </c>
+      <c r="EG82" t="s">
+        <v>442</v>
+      </c>
+      <c r="EI82" s="10" t="s">
+        <v>2463</v>
+      </c>
+      <c r="EL82" s="10" t="s">
+        <v>2464</v>
+      </c>
+      <c r="ER82" s="10" t="s">
+        <v>2465</v>
+      </c>
+      <c r="EX82" s="10" t="s">
+        <v>2466</v>
+      </c>
+      <c r="FD82" s="10" t="s">
+        <v>2467</v>
+      </c>
+      <c r="FK82">
         <v>0</v>
       </c>
       <c r="FL82" s="4">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
+      <c r="FM82" t="s">
+        <v>453</v>
+      </c>
+      <c r="FN82">
+        <v>80000</v>
+      </c>
       <c r="FO82" s="4">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>57.142857142857146</v>
+      </c>
+      <c r="FP82" t="s">
+        <v>759</v>
+      </c>
+      <c r="FQ82">
+        <v>40080</v>
       </c>
       <c r="FR82" s="4">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>20.04</v>
+      </c>
+      <c r="FS82" t="s">
+        <v>454</v>
+      </c>
+      <c r="FT82">
+        <v>300</v>
       </c>
       <c r="FU82" s="4">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="FV82" s="4">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>77.202857142857141</v>
       </c>
       <c r="FW82" s="4" t="str">
         <f t="shared" si="27"/>
-        <v>ORDINARIO</v>
+        <v>ALTO</v>
       </c>
     </row>
     <row r="83" spans="1:179" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>81</v>
       </c>
+      <c r="B83" t="s">
+        <v>577</v>
+      </c>
+      <c r="C83" t="s">
+        <v>2468</v>
+      </c>
+      <c r="D83" t="s">
+        <v>2469</v>
+      </c>
+      <c r="E83" t="s">
+        <v>2470</v>
+      </c>
+      <c r="G83" t="s">
+        <v>2432</v>
+      </c>
+      <c r="H83" t="s">
+        <v>2433</v>
+      </c>
+      <c r="I83" t="s">
+        <v>2471</v>
+      </c>
+      <c r="J83">
+        <v>37</v>
+      </c>
+      <c r="L83" t="s">
+        <v>2472</v>
+      </c>
+      <c r="M83" t="s">
+        <v>2473</v>
+      </c>
+      <c r="N83" t="s">
+        <v>423</v>
+      </c>
+      <c r="O83">
+        <v>73740</v>
+      </c>
+      <c r="P83">
+        <v>2223716350</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>2474</v>
+      </c>
+      <c r="R83">
+        <v>10</v>
+      </c>
+      <c r="S83" t="s">
+        <v>2475</v>
+      </c>
+      <c r="T83" t="s">
+        <v>2228</v>
+      </c>
+      <c r="V83">
+        <v>1000</v>
+      </c>
+      <c r="W83">
+        <v>1000</v>
+      </c>
+      <c r="X83">
+        <v>1</v>
+      </c>
+      <c r="Y83">
+        <v>1</v>
+      </c>
+      <c r="Z83">
+        <v>2</v>
+      </c>
+      <c r="AA83">
+        <v>2</v>
+      </c>
+      <c r="AB83">
+        <v>0</v>
+      </c>
+      <c r="AC83">
+        <v>0</v>
+      </c>
+      <c r="AD83" t="s">
+        <v>426</v>
+      </c>
+      <c r="AE83" t="s">
+        <v>2476</v>
+      </c>
+      <c r="AF83" t="s">
+        <v>2496</v>
+      </c>
+      <c r="AG83">
+        <v>3</v>
+      </c>
+      <c r="AH83">
+        <v>0</v>
+      </c>
+      <c r="AI83">
+        <v>2</v>
+      </c>
+      <c r="AJ83">
+        <v>1</v>
+      </c>
+      <c r="AK83">
+        <v>0</v>
+      </c>
+      <c r="AL83">
+        <v>0</v>
+      </c>
+      <c r="AM83">
+        <v>1</v>
+      </c>
+      <c r="AN83">
+        <v>200</v>
+      </c>
+      <c r="AO83">
+        <v>3</v>
+      </c>
+      <c r="AP83" t="s">
+        <v>2270</v>
+      </c>
+      <c r="AQ83" t="s">
+        <v>430</v>
+      </c>
       <c r="AR83" s="4">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="AS83">
+        <v>1</v>
+      </c>
+      <c r="AT83" t="s">
+        <v>753</v>
+      </c>
+      <c r="AU83">
+        <v>6</v>
+      </c>
+      <c r="AV83" t="s">
+        <v>2446</v>
+      </c>
+      <c r="AW83">
+        <v>6</v>
+      </c>
+      <c r="AY83">
+        <v>4</v>
+      </c>
+      <c r="AZ83" t="s">
+        <v>2459</v>
+      </c>
+      <c r="CD83">
+        <v>7</v>
+      </c>
+      <c r="CH83">
+        <v>1</v>
+      </c>
+      <c r="CI83">
+        <v>1</v>
+      </c>
+      <c r="CJ83">
+        <v>1</v>
       </c>
       <c r="CK83" s="4">
         <f t="shared" si="29"/>
+        <v>3</v>
+      </c>
+      <c r="CL83">
+        <v>1</v>
+      </c>
+      <c r="CN83">
+        <v>1</v>
+      </c>
+      <c r="CO83">
+        <v>1</v>
+      </c>
+      <c r="DI83">
+        <v>1</v>
+      </c>
+      <c r="DJ83" t="s">
+        <v>775</v>
+      </c>
+      <c r="DK83">
+        <v>2</v>
+      </c>
+      <c r="DL83">
+        <v>40000</v>
+      </c>
+      <c r="DM83">
+        <v>40000</v>
+      </c>
+      <c r="DW83">
+        <v>15</v>
+      </c>
+      <c r="DX83" t="s">
+        <v>2411</v>
+      </c>
+      <c r="DY83">
+        <v>2024</v>
+      </c>
+      <c r="DZ83" t="s">
+        <v>2477</v>
+      </c>
+      <c r="EA83" t="s">
+        <v>2478</v>
+      </c>
+      <c r="EB83" t="s">
+        <v>1489</v>
+      </c>
+      <c r="EC83" t="s">
+        <v>2478</v>
+      </c>
+      <c r="ED83" t="s">
+        <v>2478</v>
+      </c>
+      <c r="EF83" t="s">
+        <v>441</v>
+      </c>
+      <c r="EG83" t="s">
+        <v>442</v>
+      </c>
+      <c r="EI83" s="10" t="s">
+        <v>2497</v>
+      </c>
+      <c r="EL83" s="10" t="s">
+        <v>2498</v>
+      </c>
+      <c r="FK83">
         <v>0</v>
       </c>
       <c r="FL83" s="4">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
+      <c r="FM83" t="s">
+        <v>453</v>
+      </c>
+      <c r="FN83">
+        <v>40000</v>
+      </c>
       <c r="FO83" s="4">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>28.571428571428573</v>
+      </c>
+      <c r="FP83" t="s">
+        <v>759</v>
+      </c>
+      <c r="FQ83">
+        <v>40050</v>
       </c>
       <c r="FR83" s="4">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>20.024999999999999</v>
+      </c>
+      <c r="FS83" t="s">
+        <v>454</v>
+      </c>
+      <c r="FT83">
+        <v>300</v>
       </c>
       <c r="FU83" s="4">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="FV83" s="4">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>48.616428571428578</v>
       </c>
       <c r="FW83" s="4" t="str">
         <f t="shared" si="27"/>
-        <v>ORDINARIO</v>
+        <v>ALTO</v>
       </c>
     </row>
     <row r="84" spans="1:179" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>82</v>
       </c>
+      <c r="B84" t="s">
+        <v>577</v>
+      </c>
+      <c r="C84" t="s">
+        <v>2428</v>
+      </c>
+      <c r="D84" t="s">
+        <v>2479</v>
+      </c>
+      <c r="E84" t="s">
+        <v>2480</v>
+      </c>
+      <c r="F84" t="s">
+        <v>2499</v>
+      </c>
+      <c r="G84" t="s">
+        <v>2432</v>
+      </c>
+      <c r="H84" t="s">
+        <v>2433</v>
+      </c>
+      <c r="I84" t="s">
+        <v>2481</v>
+      </c>
+      <c r="J84">
+        <v>36</v>
+      </c>
+      <c r="L84" t="s">
+        <v>2482</v>
+      </c>
+      <c r="M84" t="s">
+        <v>2483</v>
+      </c>
+      <c r="N84" t="s">
+        <v>423</v>
+      </c>
+      <c r="O84">
+        <v>73680</v>
+      </c>
+      <c r="P84">
+        <v>2333142214</v>
+      </c>
+      <c r="Q84" s="3" t="s">
+        <v>2484</v>
+      </c>
+      <c r="R84">
+        <v>41</v>
+      </c>
+      <c r="S84">
+        <v>1983</v>
+      </c>
+      <c r="T84" t="s">
+        <v>2228</v>
+      </c>
+      <c r="V84">
+        <v>1710</v>
+      </c>
+      <c r="W84">
+        <v>341</v>
+      </c>
+      <c r="X84">
+        <v>1</v>
+      </c>
+      <c r="Y84">
+        <v>1</v>
+      </c>
+      <c r="Z84">
+        <v>2</v>
+      </c>
+      <c r="AA84">
+        <v>2</v>
+      </c>
+      <c r="AB84">
+        <v>0</v>
+      </c>
+      <c r="AC84">
+        <v>0</v>
+      </c>
+      <c r="AD84" t="s">
+        <v>426</v>
+      </c>
+      <c r="AE84" t="s">
+        <v>2440</v>
+      </c>
+      <c r="AF84" t="s">
+        <v>2500</v>
+      </c>
+      <c r="AG84">
+        <v>6</v>
+      </c>
+      <c r="AH84">
+        <v>0</v>
+      </c>
+      <c r="AI84">
+        <v>5</v>
+      </c>
+      <c r="AJ84">
+        <v>1</v>
+      </c>
+      <c r="AK84">
+        <v>0</v>
+      </c>
+      <c r="AL84">
+        <v>0</v>
+      </c>
+      <c r="AM84">
+        <v>2</v>
+      </c>
+      <c r="AN84">
+        <v>300</v>
+      </c>
+      <c r="AO84">
+        <v>6</v>
+      </c>
+      <c r="AP84" t="s">
+        <v>2270</v>
+      </c>
+      <c r="AQ84" t="s">
+        <v>2442</v>
+      </c>
       <c r="AR84" s="4">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="AS84">
+        <v>1</v>
+      </c>
+      <c r="AT84" t="s">
+        <v>753</v>
+      </c>
+      <c r="AU84">
+        <v>7</v>
+      </c>
+      <c r="AV84" t="s">
+        <v>2446</v>
+      </c>
+      <c r="AW84">
+        <v>6</v>
+      </c>
+      <c r="AX84">
+        <v>1</v>
+      </c>
+      <c r="AY84">
+        <v>5</v>
+      </c>
+      <c r="AZ84" t="s">
+        <v>2459</v>
+      </c>
+      <c r="BC84">
+        <v>1</v>
+      </c>
+      <c r="BD84" t="s">
+        <v>1657</v>
+      </c>
+      <c r="CH84">
+        <v>1</v>
+      </c>
+      <c r="CJ84">
+        <v>1</v>
       </c>
       <c r="CK84" s="4">
         <f t="shared" si="29"/>
+        <v>9</v>
+      </c>
+      <c r="CL84">
+        <v>3</v>
+      </c>
+      <c r="CN84">
+        <v>3</v>
+      </c>
+      <c r="CO84">
+        <v>3</v>
+      </c>
+      <c r="DI84">
+        <v>2</v>
+      </c>
+      <c r="DJ84" t="s">
+        <v>775</v>
+      </c>
+      <c r="DK84">
+        <v>3</v>
+      </c>
+      <c r="DL84">
+        <v>40000</v>
+      </c>
+      <c r="DM84">
+        <v>60000</v>
+      </c>
+      <c r="DN84">
+        <v>40000</v>
+      </c>
+      <c r="DW84">
+        <v>15</v>
+      </c>
+      <c r="DX84" t="s">
+        <v>2411</v>
+      </c>
+      <c r="DY84">
+        <v>2024</v>
+      </c>
+      <c r="DZ84" t="s">
+        <v>2485</v>
+      </c>
+      <c r="EA84" t="s">
+        <v>2486</v>
+      </c>
+      <c r="EB84" t="s">
+        <v>2487</v>
+      </c>
+      <c r="EC84" t="s">
+        <v>2488</v>
+      </c>
+      <c r="ED84" t="s">
+        <v>2489</v>
+      </c>
+      <c r="EF84" t="s">
+        <v>441</v>
+      </c>
+      <c r="EG84" t="s">
+        <v>442</v>
+      </c>
+      <c r="EI84" s="10" t="s">
+        <v>2501</v>
+      </c>
+      <c r="EL84" s="10" t="s">
+        <v>2502</v>
+      </c>
+      <c r="ER84" s="10" t="s">
+        <v>2503</v>
+      </c>
+      <c r="EX84" s="10" t="s">
+        <v>2504</v>
+      </c>
+      <c r="FD84" s="10" t="s">
+        <v>2505</v>
+      </c>
+      <c r="FK84">
         <v>0</v>
       </c>
       <c r="FL84" s="4">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
+      <c r="FM84" t="s">
+        <v>453</v>
+      </c>
+      <c r="FN84">
+        <v>100000</v>
+      </c>
       <c r="FO84" s="4">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>71.428571428571431</v>
+      </c>
+      <c r="FP84" t="s">
+        <v>759</v>
+      </c>
+      <c r="FQ84">
+        <v>40035</v>
       </c>
       <c r="FR84" s="4">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>20.017499999999998</v>
+      </c>
+      <c r="FS84" t="s">
+        <v>454</v>
+      </c>
+      <c r="FT84">
+        <v>300</v>
       </c>
       <c r="FU84" s="4">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="FV84" s="4">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>91.466071428571425</v>
       </c>
       <c r="FW84" s="4" t="str">
         <f t="shared" si="27"/>
-        <v>ORDINARIO</v>
+        <v>ALTO</v>
       </c>
     </row>
     <row r="85" spans="1:179" x14ac:dyDescent="0.3">
@@ -41041,7 +44532,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A3:FV13 FX3:GC43 B14:G14 I14:FV14 KD14:LJ42 A14:A201 D15:FV58 B15:C68 GL43:GW43 GY43:HA43 HC43:HD43 HF43 HK43 HP43:HR43 IC43 IE43 IH43:IJ43 IL43 FX44:IM60 EM59:FV60 D59:EL62 EM61:IM62 D63:IM73 B69 B70:C73 B74:IM201 A202:IM208">
+  <conditionalFormatting sqref="A3:FV13 FX3:GC43 B14:G14 I14:FV14 KD14:LJ42 A14:A201 D15:FV58 B15:C68 GL43:GW43 GY43:HA43 HC43:HD43 HF43 HK43 HP43:HR43 IC43 IE43 IH43:IJ43 IL43 FX44:IM60 EM59:FV60 D59:EL62 EM61:IM62 D63:IM63 D64:AO68 AP64:IM72 B69:AO72 B73:IM201 A202:IM208">
     <cfRule type="expression" dxfId="40" priority="581">
       <formula>$A3=$A$1</formula>
     </cfRule>
@@ -41091,7 +44582,7 @@
       <formula>$A43=$A$2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="GD3:IM34 IQ15:IR15 IS16:IT16 IV16:JB16 JD16:JH16 IN20:IQ20 IS20:IV20 JB20 JE20:JH20 JT20 KB20:KC20 IS23:JB23 JD23:JK24 JM23:JP24 IN24:IQ24 IS24:IT24 IW24:JB24 IS27:IT27 IV27:JB27 JD27:JK27 JM27:JP27 IN28:IS28 IU28:IV28 JB28 JE28:JJ28 JM28:JU28 JW28 JZ28 KB28:KC28 IN31:IS32 IU31:IV32 JM31:JU32 KB31:KC32 JE31:JJ33 JB31:JB35 JW31:JW39 JZ31:JZ39 IU33 KC33 IN33:IR34 KB33:KB34 IS33:IS35 JM33:JP36 JQ33:JU38 IV33:IV39 IT34:IU34 IW34:IX34 IY34:JB35 JD34:JK36 GD35:IR35 IU35 KB35:KC39 IR36:JB36 IN36:IQ39 GD36:IM42 JB37:JB38 JE37:JF38 JH37:JJ38 JO37:JP38 IR37:IR39 IU37:IU39 IS37:IS40 JM37:JM41 JN37:JN43 JG38 JM39:JU39 IV39:JB41 JD39:JK41 IQ40:IR40 IT40:IU40 JU40:KC40 JO40:JT41 IN41:IS41 IU41:IV41 JU41 JW41 JZ41 KB41:KC41 JO41:JO43 IY42:JB42 C69">
+  <conditionalFormatting sqref="GD3:IM34 IQ15:IR15 IS16:IT16 IV16:JB16 JD16:JH16 IN20:IQ20 IS20:IV20 JB20 JE20:JH20 JT20 KB20:KC20 IS23:JB23 JD23:JK24 JM23:JP24 IN24:IQ24 IS24:IT24 IW24:JB24 IS27:IT27 IV27:JB27 JD27:JK27 JM27:JP27 IN28:IS28 IU28:IV28 JB28 JE28:JJ28 JM28:JU28 JW28 JZ28 KB28:KC28 IN31:IS32 IU31:IV32 JM31:JU32 KB31:KC32 JE31:JJ33 JB31:JB35 JW31:JW39 JZ31:JZ39 IU33 KC33 IN33:IR34 KB33:KB34 IS33:IS35 JM33:JP36 JQ33:JU38 IV33:IV39 IT34:IU34 IW34:IX34 IY34:JB35 JD34:JK36 GD35:IR35 IU35 KB35:KC39 IR36:JB36 IN36:IQ39 GD36:IM42 JB37:JB38 JE37:JF38 JH37:JJ38 JO37:JP38 IR37:IR39 IU37:IU39 IS37:IS40 JM37:JM41 JN37:JN43 JG38 JM39:JU39 IV39:JB41 JD39:JK41 IQ40:IR40 IT40:IU40 JU40:KC40 JO40:JT41 IN41:IS41 IU41:IV41 JU41 JW41 JZ41 KB41:KC41 JO41:JO43 IY42:JB42">
     <cfRule type="expression" dxfId="30" priority="394">
       <formula>$A3=$A$2</formula>
     </cfRule>
@@ -41246,9 +44737,12 @@
       <formula>#REF!=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B201" xr:uid="{41C0D522-5D90-43F5-9DB3-E0F81FDE0774}">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B78 B80:B201" xr:uid="{41C0D522-5D90-43F5-9DB3-E0F81FDE0774}">
       <formula1>"BANCO, BBVA, COMPARTAMOS, DHL, GASOLINERA, GENERAL, GDL, UVP"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B79" xr:uid="{D5CD9EE6-9E02-4584-93C4-B4A613E84A37}">
+      <formula1>"BANCO, BBVA, COMPARTAMOS, DHL, GASERA, GASOLINERA, GENERAL, GDL, UVP"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -41297,16 +44791,29 @@
     <hyperlink ref="Q73" r:id="rId43" xr:uid="{AC530E9D-142F-47C1-9FA2-9326C9E7E289}"/>
     <hyperlink ref="Q74" r:id="rId44" xr:uid="{3666EBA2-130E-4794-96A0-D6F6C3ACD1EE}"/>
     <hyperlink ref="Q78" r:id="rId45" xr:uid="{AFBC3AA6-C580-4B7F-B71B-D6480B14E003}"/>
+    <hyperlink ref="Q75" r:id="rId46" xr:uid="{FF56A344-1EEE-4D08-99A8-FCD2C7F230DE}"/>
+    <hyperlink ref="Q76" r:id="rId47" xr:uid="{3E196FA2-420A-4B92-844E-6ABDB577F40B}"/>
+    <hyperlink ref="Q70" r:id="rId48" xr:uid="{97705115-B4A0-4147-AD9C-F7B5CC1C8112}"/>
+    <hyperlink ref="Q69" r:id="rId49" xr:uid="{F44C7C7B-EEF8-4049-85AD-85239A6C431B}"/>
+    <hyperlink ref="Q71" r:id="rId50" xr:uid="{2FDC1EA4-7913-4F81-B6BE-310224E8BACE}"/>
+    <hyperlink ref="Q72" r:id="rId51" xr:uid="{4EB8FB9A-D956-4ABB-9082-FAA69FD2AB60}"/>
+    <hyperlink ref="Q77" r:id="rId52" xr:uid="{DD7FA7B3-6942-4E12-AD08-F0CFCC3FF11D}"/>
+    <hyperlink ref="Q79" r:id="rId53" xr:uid="{618B5CA2-6BB8-42A0-BC96-CE9D1A869B83}"/>
+    <hyperlink ref="Q81" r:id="rId54" xr:uid="{98E40A57-5D15-4758-A662-18D914AB85C3}"/>
+    <hyperlink ref="Q82" r:id="rId55" xr:uid="{CD6C91A6-5AD9-4111-8327-4A966B5533C1}"/>
+    <hyperlink ref="Q83" r:id="rId56" xr:uid="{A1567507-C11E-4E1C-944A-8AEAD69FB237}"/>
+    <hyperlink ref="Q84" r:id="rId57" xr:uid="{D28E4795-28C8-46AC-A4C8-30B9C17D8946}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId46"/>
-  <legacyDrawing r:id="rId47"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967294" verticalDpi="0" r:id="rId58"/>
+  <drawing r:id="rId59"/>
+  <legacyDrawing r:id="rId60"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x14">
       <controls>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1025" r:id="rId48" name="Spinner 1">
+            <control shapeId="1025" r:id="rId61" name="Spinner 1">
               <controlPr defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
@@ -41340,7 +44847,7 @@
     <row r="1" spans="1:310" x14ac:dyDescent="0.3">
       <c r="A1">
         <f>+BD!A1</f>
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B1" t="s">
         <v>133</v>
@@ -42273,19 +45780,19 @@
     <row r="2" spans="1:310" x14ac:dyDescent="0.3">
       <c r="B2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,2, FALSE)</f>
-        <v>GENERAL</v>
+        <v>GASERA</v>
       </c>
       <c r="C2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,3, FALSE)</f>
-        <v>SUPRACARE SA DE CV</v>
+        <v>GAS EXPRESS NIETO DE MEXICO SA DE CV</v>
       </c>
       <c r="D2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,4, FALSE)</f>
-        <v>FRAICHE CHEDRAUI</v>
+        <v>CENTRO DE CARBURACION GAS EXPRESS NIETO</v>
       </c>
       <c r="E2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,5, FALSE)</f>
-        <v>SUP200818IP0</v>
+        <v>GEN7908272C1</v>
       </c>
       <c r="F2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,6, FALSE)</f>
@@ -42293,31 +45800,31 @@
       </c>
       <c r="G2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,7, FALSE)</f>
-        <v>COMERCIO AL POR MENOR DE ARTICULOS DE PERFUMERIA Y COSMETICOS</v>
+        <v>CENTRO DE CARBURACION DE GAS LP</v>
       </c>
       <c r="H2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,8, FALSE)</f>
-        <v>SE OFRECE UNA AMPLIA VARIEDAD DE FRAGANCIAS Y PRODUCTOS, COMO COSMÉTICOS Y PRODUCTOS PARA EL CUIDADO PERSONAL, BRINDANDO ASESORAMIENTO, PROMOCIONES, Y SERVICIOS DE PRUEBA Y PERSONALIZACIÓN DE FRAGANCIAS</v>
+        <v>SE DEDICA A LA DISTRIBUCIÓN Y VENTA DE GAS LICUADO DE PETRÓLEO (LP), INCLUYENDO LA RECARGA DE CILINDROS Y TANQUES, Y EL MANTENIMIENTO DE EQUIPOS DE DISTRIBUCIÓN. SUS ACTIVIDADES TAMBIÉN ABARCAN LA ATENCIÓN AL CLIENTE.</v>
       </c>
       <c r="I2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,9, FALSE)</f>
-        <v>7 NORTE</v>
-      </c>
-      <c r="J2">
+        <v>PREDIO DENOMINADO LA DESVIACION, CARRETERA FDERAL</v>
+      </c>
+      <c r="J2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,10, FALSE)</f>
-        <v>107</v>
-      </c>
-      <c r="K2" t="str">
+        <v>KM 61</v>
+      </c>
+      <c r="K2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,11, FALSE)</f>
-        <v>LOCAL 5</v>
+        <v>0</v>
       </c>
       <c r="L2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,12, FALSE)</f>
-        <v>CENTRO</v>
+        <v>LOCALIDAD DE AMOLTEPEC, TOMATLAN</v>
       </c>
       <c r="M2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,13, FALSE)</f>
-        <v>TEHUACAN</v>
+        <v>ZACATLAN</v>
       </c>
       <c r="N2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,14, FALSE)</f>
@@ -42325,23 +45832,23 @@
       </c>
       <c r="O2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,15, FALSE)</f>
-        <v>75700</v>
+        <v>73310</v>
       </c>
       <c r="P2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,16, FALSE)</f>
-        <v>2383806932</v>
+        <v>2216678745</v>
       </c>
       <c r="Q2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,17, FALSE)</f>
-        <v>f516.chedrahuitehuacan@pue.fraiche.mx</v>
+        <v>estacion.zacatlan@gasexpressnieto.com</v>
       </c>
       <c r="R2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,18, FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,19, FALSE)</f>
-        <v>01 DE JUNIO DEE 2024</v>
+        <v>ABRIL DE 2021</v>
       </c>
       <c r="T2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,20, FALSE)</f>
@@ -42353,11 +45860,11 @@
       </c>
       <c r="V2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,22, FALSE)</f>
-        <v>25</v>
+        <v>2500</v>
       </c>
       <c r="W2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,23, FALSE)</f>
-        <v>40</v>
+        <v>2500</v>
       </c>
       <c r="X2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,24, FALSE)</f>
@@ -42365,19 +45872,19 @@
       </c>
       <c r="Y2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,25, FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,26, FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,27, FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,28, FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,29, FALSE)</f>
@@ -42385,19 +45892,19 @@
       </c>
       <c r="AD2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,30, FALSE)</f>
-        <v>5 CAJONES</v>
+        <v>10 CAJONES</v>
       </c>
       <c r="AE2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,31, FALSE)</f>
-        <v>VERONICA ANDRADE GARCIA</v>
+        <v>ARTURO PASOS HERRERA</v>
       </c>
       <c r="AF2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,32, FALSE)</f>
-        <v>MAYRA LIZBET ANGEL PEREZ</v>
+        <v>YESENIA ANEL PALAFOX LUNA</v>
       </c>
       <c r="AG2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,33, FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,34, FALSE)</f>
@@ -42405,7 +45912,7 @@
       </c>
       <c r="AI2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,35, FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,36, FALSE)</f>
@@ -42421,15 +45928,15 @@
       </c>
       <c r="AM2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,39, FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,40, FALSE)</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AO2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,41, FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,42, FALSE)</f>
@@ -42437,11 +45944,11 @@
       </c>
       <c r="AQ2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,43, FALSE)</f>
-        <v>10:00 A 20:00 HORAS</v>
+        <v>24 HORAS</v>
       </c>
       <c r="AR2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,44, FALSE)</f>
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="AS2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,45, FALSE)</f>
@@ -42449,31 +45956,31 @@
       </c>
       <c r="AT2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,46, FALSE)</f>
-        <v>AREA INTERNA</v>
+        <v>OFICINA</v>
       </c>
       <c r="AU2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,47, FALSE)</f>
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AV2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,48, FALSE)</f>
-        <v>AREA INTERNA Y ENTRADA</v>
+        <v>OFICINA Y AREA EXTERNA</v>
       </c>
       <c r="AW2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,49, FALSE)</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AX2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,50, FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,51, FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="AZ2">
+        <v>2</v>
+      </c>
+      <c r="AZ2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,52, FALSE)</f>
-        <v>0</v>
+        <v>OFICINA Y DESPACHADOR</v>
       </c>
       <c r="BA2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,53, FALSE)</f>
@@ -42493,11 +46000,11 @@
       </c>
       <c r="BE2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,57, FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="BF2">
+        <v>2</v>
+      </c>
+      <c r="BF2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,58, FALSE)</f>
-        <v>0</v>
+        <v>PARO EMERGENCIA</v>
       </c>
       <c r="BG2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,59, FALSE)</f>
@@ -42507,25 +46014,25 @@
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,60, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="BI2">
+      <c r="BI2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,61, FALSE)</f>
-        <v>0</v>
+        <v>OFICINA Y DESPACHADOR</v>
       </c>
       <c r="BJ2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,62, FALSE)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BK2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,63, FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,64, FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="BM2" t="str">
+        <v>0</v>
+      </c>
+      <c r="BM2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,65, FALSE)</f>
-        <v>AREA INTERNA Y AREA EXTERNA</v>
+        <v>0</v>
       </c>
       <c r="BN2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,66, FALSE)</f>
@@ -42593,7 +46100,7 @@
       </c>
       <c r="CD2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,82, FALSE)</f>
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="CE2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,83, FALSE)</f>
@@ -42601,7 +46108,7 @@
       </c>
       <c r="CF2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,84, FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CG2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,85, FALSE)</f>
@@ -42609,11 +46116,11 @@
       </c>
       <c r="CH2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,86, FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CI2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,87, FALSE)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="CJ2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,88, FALSE)</f>
@@ -42621,11 +46128,11 @@
       </c>
       <c r="CK2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,89, FALSE)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="CL2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,90, FALSE)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="CM2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,91, FALSE)</f>
@@ -42773,7 +46280,7 @@
       </c>
       <c r="DW2" s="5">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,127, FALSE)</f>
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="DX2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,128, FALSE)</f>
@@ -42785,23 +46292,23 @@
       </c>
       <c r="DZ2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,130, FALSE)</f>
-        <v>18.4637150494009, -97.38691843244746</v>
+        <v>19.870830220413556, -98.00510221900382</v>
       </c>
       <c r="EA2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,131, FALSE)</f>
-        <v>LOCAL</v>
+        <v>TERRENO</v>
       </c>
       <c r="EB2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,132, FALSE)</f>
-        <v>LOCAL</v>
+        <v>CARRETERA</v>
       </c>
       <c r="EC2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,133, FALSE)</f>
-        <v>CHEDRAUI</v>
+        <v>FERRETERIA</v>
       </c>
       <c r="ED2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,134, FALSE)</f>
-        <v>ESTACIONAMIENTO</v>
+        <v>CASA HABITACION</v>
       </c>
       <c r="EE2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,135, FALSE)</f>
@@ -42821,7 +46328,7 @@
       </c>
       <c r="EI2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,139, FALSE)</f>
-        <v>ERIBERTO ANSELMO SANCHEZ</v>
+        <v>JORGE LUIS ARROYO FLORES</v>
       </c>
       <c r="EJ2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,140, FALSE)</f>
@@ -42831,9 +46338,9 @@
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,141, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="EL2">
+      <c r="EL2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,142, FALSE)</f>
-        <v>0</v>
+        <v>JULIAN EMMANUEL PASOS SIERRA</v>
       </c>
       <c r="EM2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,143, FALSE)</f>
@@ -42843,9 +46350,9 @@
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,144, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="EO2">
+      <c r="EO2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,145, FALSE)</f>
-        <v>0</v>
+        <v>CONSTANTINO VEERA HERNANDEZ</v>
       </c>
       <c r="EP2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,146, FALSE)</f>
@@ -42855,9 +46362,9 @@
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,147, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="ER2">
+      <c r="ER2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,148, FALSE)</f>
-        <v>0</v>
+        <v>MUNIR CASTELAN DURAN</v>
       </c>
       <c r="ES2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,149, FALSE)</f>
@@ -42927,29 +46434,29 @@
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,165, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="FJ2">
+      <c r="FJ2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,166, FALSE)</f>
-        <v>0</v>
+        <v>GAS LP</v>
       </c>
       <c r="FK2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,167, FALSE)</f>
-        <v>0</v>
+        <v>4934</v>
       </c>
       <c r="FL2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,168, FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="FM2" t="str">
+        <v>1.6446666666666667</v>
+      </c>
+      <c r="FM2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,169, FALSE)</f>
-        <v>ESENCIA Y PERFUMON</v>
+        <v>0</v>
       </c>
       <c r="FN2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,170, FALSE)</f>
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="FO2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,171, FALSE)</f>
-        <v>7.2142857142857147E-2</v>
+        <v>0</v>
       </c>
       <c r="FP2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,172, FALSE)</f>
@@ -42969,19 +46476,19 @@
       </c>
       <c r="FT2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,176, FALSE)</f>
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="FU2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,177, FALSE)</f>
-        <v>8.0000000000000002E-3</v>
+        <v>1.2E-2</v>
       </c>
       <c r="FV2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,178, FALSE)</f>
-        <v>8.0142857142857155E-2</v>
+        <v>1.6566666666666667</v>
       </c>
       <c r="FW2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,179, FALSE)</f>
-        <v>ORDINARIO</v>
+        <v>ALTO</v>
       </c>
       <c r="FX2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,180, FALSE)</f>
@@ -43697,7 +47204,7 @@
       <c r="B5" t="s">
         <v>1897</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" t="s">
         <v>841</v>
       </c>
       <c r="D5" t="s">

--- a/Inputs/BD.xlsx
+++ b/Inputs/BD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/078e1a455e5c02ce/Documentos/GitHub/Proyecto_PIPC/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3173" documentId="13_ncr:1_{898522BF-B0F8-4888-9748-DC730D5D6CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51FEB353-F6BF-47CD-A244-4ECA67A29383}"/>
+  <xr:revisionPtr revIDLastSave="3375" documentId="13_ncr:1_{898522BF-B0F8-4888-9748-DC730D5D6CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1877F74F-2F73-4C1C-9C5C-668D9836F629}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3F095A75-F066-4695-8672-8D4315F1EF23}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{3F095A75-F066-4695-8672-8D4315F1EF23}"/>
   </bookViews>
   <sheets>
     <sheet name="BD" sheetId="1" r:id="rId1"/>
@@ -563,7 +563,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8644" uniqueCount="2795">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8736" uniqueCount="2842">
   <si>
     <t>dia</t>
   </si>
@@ -8948,6 +8948,147 @@
   </si>
   <si>
     <t>JONHATAN SEBASTIAN REYES</t>
+  </si>
+  <si>
+    <t>INSTITUTO DE ADMINISTRACIÓN PUBLICA DEL ESTADO DE PUEBLA A. C.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAP780731UB5                </t>
+  </si>
+  <si>
+    <t>EDUCACIÓN SUPERIOR</t>
+  </si>
+  <si>
+    <t>08:00 A 16:00 HORAS</t>
+  </si>
+  <si>
+    <t>OFICINAS ADMINISTRATIVAS</t>
+  </si>
+  <si>
+    <t>22 ORIENTE</t>
+  </si>
+  <si>
+    <t>XONACA</t>
+  </si>
+  <si>
+    <t>PROMOTORA DEL ARTE Y LA CULTURA DE PUEBLA DIVISIÓN DE ESTUDIOS SUPERIORES A.C.</t>
+  </si>
+  <si>
+    <t>UNIVERSIDAD UDAL PLANTEL TEZIUTLÁN</t>
+  </si>
+  <si>
+    <t>PAC960524FL3</t>
+  </si>
+  <si>
+    <t>UNIVERSIDAD EDUCACIÓN MEDIA SUPERIOR</t>
+  </si>
+  <si>
+    <t>VICENTE GUERRERO</t>
+  </si>
+  <si>
+    <t>8:00 A 16:00 HORAS</t>
+  </si>
+  <si>
+    <t>JORGE LUIS LUNA PRADO</t>
+  </si>
+  <si>
+    <t>JESUS LOPEZ CHARGOY</t>
+  </si>
+  <si>
+    <t>JESUS PEREZ SANCHEZ</t>
+  </si>
+  <si>
+    <t>MONSERRAT CALIXTO RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>MARIBLE GALINDO PAULINO</t>
+  </si>
+  <si>
+    <t>CRISTOPHER ALEJANDRO CARMONA GONZALEZ</t>
+  </si>
+  <si>
+    <t>ALEJANDRO INOCENCIO CRUZ</t>
+  </si>
+  <si>
+    <t>ELIA ADRIANA VELAZQUEZ BONILLA</t>
+  </si>
+  <si>
+    <t>MARA PARTICIA GARCIA LUNA</t>
+  </si>
+  <si>
+    <t>JESUS FRANCISCO AGUILAR NOCHEBUENA</t>
+  </si>
+  <si>
+    <t>LINA MARTINEZ ROMANO</t>
+  </si>
+  <si>
+    <t>OFRECE PROGRAMAS EDUCATIVOS DE NIVEL SUPERIOR, ACTIVIDADES CULTURALES, DEPORTIVAS Y DE INVESTIGACIÓN PARA EL DESARROLLO ACADÉMICO Y PERSONAL DE SUS ESTUDIANTES EN LA REGIÓN</t>
+  </si>
+  <si>
+    <t>DIAZ MIRON</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE GARCIA PRADO</t>
+  </si>
+  <si>
+    <t>SUSANA RIVAS RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>INES IBAÑEZ FAUSTINO</t>
+  </si>
+  <si>
+    <t>CANDIDO PLATAS LOPEZ</t>
+  </si>
+  <si>
+    <t>EFREN CONTRERAS ZAFRA</t>
+  </si>
+  <si>
+    <t>DOMINICA 19</t>
+  </si>
+  <si>
+    <t>COZE850822S40</t>
+  </si>
+  <si>
+    <t>CAFETERIA, RESTAURANTE</t>
+  </si>
+  <si>
+    <t>PREPARAR Y SERVIR ALIMENTOS Y BEBIDAS, OFRECIENDO DESAYUNOS, COMIDAS, POSTRES Y CAFÉ EN UN AMBIENTE CÓMODO PARA EL CONSUMO EN EL LUGAR O PARA LLEVAR</t>
+  </si>
+  <si>
+    <t>BOULEVARD DE LAS CASCADAS</t>
+  </si>
+  <si>
+    <t>Q01</t>
+  </si>
+  <si>
+    <t>LOMAS DE ANGELOPOLIS III</t>
+  </si>
+  <si>
+    <t>administracion@dominica19.com</t>
+  </si>
+  <si>
+    <t>DICIEMBRE DE 2024</t>
+  </si>
+  <si>
+    <t>JOSE LUIS RODOLFO RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>8:00 A 23:00 HORAS</t>
+  </si>
+  <si>
+    <t>DICIEMBRE</t>
+  </si>
+  <si>
+    <t>18.970035879601955, -98.2852424490102</t>
+  </si>
+  <si>
+    <t>AXEL SUAREZ PEREZ</t>
+  </si>
+  <si>
+    <t>ANA KAREN SANCHEZ ROJAS</t>
+  </si>
+  <si>
+    <t>CASSANDRA SANCHEZ PEREZ</t>
   </si>
 </sst>
 </file>
@@ -9634,7 +9775,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="26" fmlaLink="$A$1" max="30000" min="1" page="10" val="99"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="26" fmlaLink="$A$1" max="30000" min="1" page="10" val="103"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10030,7 +10171,7 @@
   <sheetData>
     <row r="1" spans="1:322" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="DS1" t="s">
         <v>1968</v>
@@ -45796,6 +45937,81 @@
       <c r="A102">
         <v>100</v>
       </c>
+      <c r="B102" t="s">
+        <v>550</v>
+      </c>
+      <c r="C102" t="s">
+        <v>2795</v>
+      </c>
+      <c r="D102" t="s">
+        <v>2795</v>
+      </c>
+      <c r="E102" t="s">
+        <v>2796</v>
+      </c>
+      <c r="G102" t="s">
+        <v>2797</v>
+      </c>
+      <c r="H102" t="s">
+        <v>2799</v>
+      </c>
+      <c r="I102" t="s">
+        <v>2800</v>
+      </c>
+      <c r="J102">
+        <v>1409</v>
+      </c>
+      <c r="L102" t="s">
+        <v>2801</v>
+      </c>
+      <c r="M102" t="s">
+        <v>423</v>
+      </c>
+      <c r="N102" t="s">
+        <v>423</v>
+      </c>
+      <c r="O102">
+        <v>72280</v>
+      </c>
+      <c r="V102">
+        <v>500.92</v>
+      </c>
+      <c r="W102">
+        <v>545.80999999999995</v>
+      </c>
+      <c r="AG102">
+        <v>17</v>
+      </c>
+      <c r="AH102">
+        <v>0</v>
+      </c>
+      <c r="AI102">
+        <v>11</v>
+      </c>
+      <c r="AJ102">
+        <v>6</v>
+      </c>
+      <c r="AK102">
+        <v>0</v>
+      </c>
+      <c r="AL102">
+        <v>0</v>
+      </c>
+      <c r="AM102">
+        <v>1</v>
+      </c>
+      <c r="AN102">
+        <v>20</v>
+      </c>
+      <c r="AO102">
+        <v>3</v>
+      </c>
+      <c r="AP102" t="s">
+        <v>2267</v>
+      </c>
+      <c r="AQ102" t="s">
+        <v>2798</v>
+      </c>
       <c r="AR102" s="4">
         <f t="shared" si="38"/>
         <v>0</v>
@@ -45812,17 +46028,29 @@
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
+      <c r="FP102" t="s">
+        <v>453</v>
+      </c>
+      <c r="FQ102">
+        <v>59</v>
+      </c>
       <c r="FR102" s="4">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="FS102" t="s">
+        <v>454</v>
+      </c>
+      <c r="FT102">
+        <v>1020</v>
       </c>
       <c r="FU102" s="4">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>6.8000000000000005E-2</v>
       </c>
       <c r="FV102" s="4">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>9.7500000000000003E-2</v>
       </c>
       <c r="FW102" s="4" t="str">
         <f t="shared" si="27"/>
@@ -45833,33 +46061,156 @@
       <c r="A103">
         <v>101</v>
       </c>
+      <c r="B103" t="s">
+        <v>550</v>
+      </c>
+      <c r="C103" t="s">
+        <v>2802</v>
+      </c>
+      <c r="D103" t="s">
+        <v>2803</v>
+      </c>
+      <c r="E103" t="s">
+        <v>2804</v>
+      </c>
+      <c r="G103" t="s">
+        <v>2805</v>
+      </c>
+      <c r="I103" t="s">
+        <v>2806</v>
+      </c>
+      <c r="J103">
+        <v>401</v>
+      </c>
+      <c r="L103" t="s">
+        <v>421</v>
+      </c>
+      <c r="M103" t="s">
+        <v>2619</v>
+      </c>
+      <c r="N103" t="s">
+        <v>423</v>
+      </c>
+      <c r="O103">
+        <v>73800</v>
+      </c>
+      <c r="V103">
+        <v>200</v>
+      </c>
+      <c r="W103">
+        <v>1254.0899999999999</v>
+      </c>
+      <c r="AE103" t="s">
+        <v>2809</v>
+      </c>
+      <c r="AF103" t="s">
+        <v>2808</v>
+      </c>
+      <c r="AG103">
+        <v>14</v>
+      </c>
+      <c r="AH103">
+        <v>0</v>
+      </c>
+      <c r="AM103">
+        <v>1</v>
+      </c>
+      <c r="AN103">
+        <v>270</v>
+      </c>
+      <c r="AO103">
+        <v>5</v>
+      </c>
+      <c r="AP103" t="s">
+        <v>2527</v>
+      </c>
+      <c r="AQ103" t="s">
+        <v>2807</v>
+      </c>
       <c r="AR103" s="4">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="AU103">
+        <v>10</v>
+      </c>
+      <c r="AW103">
+        <v>9</v>
+      </c>
+      <c r="AX103">
+        <v>1</v>
       </c>
       <c r="CK103" s="4">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
+      <c r="EI103" s="10" t="s">
+        <v>2810</v>
+      </c>
+      <c r="EL103" s="10" t="s">
+        <v>2811</v>
+      </c>
+      <c r="EO103" s="10" t="s">
+        <v>2812</v>
+      </c>
+      <c r="ER103" s="10" t="s">
+        <v>2813</v>
+      </c>
+      <c r="EU103" s="10" t="s">
+        <v>2814</v>
+      </c>
+      <c r="EX103" s="10" t="s">
+        <v>2815</v>
+      </c>
+      <c r="FA103" s="10" t="s">
+        <v>2816</v>
+      </c>
+      <c r="FD103" s="10" t="s">
+        <v>2817</v>
+      </c>
+      <c r="FG103" s="10" t="s">
+        <v>2818</v>
+      </c>
+      <c r="FJ103" t="s">
+        <v>2109</v>
+      </c>
+      <c r="FK103">
+        <v>287</v>
+      </c>
       <c r="FL103" s="4">
         <f t="shared" si="30"/>
+        <v>9.5666666666666664E-2</v>
+      </c>
+      <c r="FN103">
         <v>0</v>
       </c>
       <c r="FO103" s="4">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
+      <c r="FP103" t="s">
+        <v>453</v>
+      </c>
+      <c r="FQ103">
+        <v>145</v>
+      </c>
       <c r="FR103" s="4">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>7.2499999999999995E-2</v>
+      </c>
+      <c r="FS103" t="s">
+        <v>454</v>
+      </c>
+      <c r="FT103">
+        <v>1000</v>
       </c>
       <c r="FU103" s="4">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="FV103" s="4">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>0.23483333333333334</v>
       </c>
       <c r="FW103" s="4" t="str">
         <f t="shared" si="27"/>
@@ -45870,33 +46221,138 @@
       <c r="A104">
         <v>102</v>
       </c>
+      <c r="B104" t="s">
+        <v>550</v>
+      </c>
+      <c r="C104" t="s">
+        <v>2802</v>
+      </c>
+      <c r="D104" t="s">
+        <v>2803</v>
+      </c>
+      <c r="E104" t="s">
+        <v>2804</v>
+      </c>
+      <c r="G104" t="s">
+        <v>2805</v>
+      </c>
+      <c r="H104" t="s">
+        <v>2819</v>
+      </c>
+      <c r="I104" t="s">
+        <v>2820</v>
+      </c>
+      <c r="J104">
+        <v>533</v>
+      </c>
+      <c r="L104" t="s">
+        <v>421</v>
+      </c>
+      <c r="M104" t="s">
+        <v>2619</v>
+      </c>
+      <c r="N104" t="s">
+        <v>423</v>
+      </c>
+      <c r="O104">
+        <v>73800</v>
+      </c>
+      <c r="P104">
+        <v>2223232094</v>
+      </c>
+      <c r="V104">
+        <v>237.95</v>
+      </c>
+      <c r="W104">
+        <v>1189.75</v>
+      </c>
+      <c r="AE104" t="s">
+        <v>2809</v>
+      </c>
+      <c r="AF104" t="s">
+        <v>2821</v>
+      </c>
+      <c r="AG104">
+        <v>5</v>
+      </c>
+      <c r="AH104">
+        <v>0</v>
+      </c>
+      <c r="AM104">
+        <v>1</v>
+      </c>
+      <c r="AN104">
+        <v>400</v>
+      </c>
+      <c r="AO104">
+        <v>5</v>
+      </c>
+      <c r="AP104" t="s">
+        <v>2527</v>
+      </c>
+      <c r="AQ104" t="s">
+        <v>2807</v>
+      </c>
       <c r="AR104" s="4">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="AU104">
+        <v>5</v>
+      </c>
+      <c r="AW104">
+        <v>5</v>
       </c>
       <c r="CK104" s="4">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
+      <c r="EI104" s="10" t="s">
+        <v>2822</v>
+      </c>
+      <c r="EL104" s="10" t="s">
+        <v>2823</v>
+      </c>
+      <c r="EO104" s="10" t="s">
+        <v>2824</v>
+      </c>
+      <c r="FK104">
+        <v>0</v>
+      </c>
       <c r="FL104" s="4">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
+      <c r="FN104">
+        <v>0</v>
+      </c>
       <c r="FO104" s="4">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
+      <c r="FP104" t="s">
+        <v>453</v>
+      </c>
+      <c r="FQ104">
+        <v>145</v>
+      </c>
       <c r="FR104" s="4">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>7.2499999999999995E-2</v>
+      </c>
+      <c r="FS104" t="s">
+        <v>454</v>
+      </c>
+      <c r="FT104">
+        <v>1000</v>
       </c>
       <c r="FU104" s="4">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="FV104" s="4">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>0.13916666666666666</v>
       </c>
       <c r="FW104" s="4" t="str">
         <f t="shared" si="27"/>
@@ -45907,33 +46363,226 @@
       <c r="A105">
         <v>103</v>
       </c>
+      <c r="B105" t="s">
+        <v>550</v>
+      </c>
+      <c r="C105" t="s">
+        <v>2825</v>
+      </c>
+      <c r="D105" t="s">
+        <v>2826</v>
+      </c>
+      <c r="E105" t="s">
+        <v>2827</v>
+      </c>
+      <c r="G105" t="s">
+        <v>2828</v>
+      </c>
+      <c r="H105" t="s">
+        <v>2829</v>
+      </c>
+      <c r="I105" t="s">
+        <v>2830</v>
+      </c>
+      <c r="J105">
+        <v>1301</v>
+      </c>
+      <c r="K105" t="s">
+        <v>2831</v>
+      </c>
+      <c r="L105" t="s">
+        <v>2832</v>
+      </c>
+      <c r="M105" t="s">
+        <v>1675</v>
+      </c>
+      <c r="N105" t="s">
+        <v>423</v>
+      </c>
+      <c r="O105">
+        <v>72830</v>
+      </c>
+      <c r="Q105" s="3" t="s">
+        <v>2833</v>
+      </c>
+      <c r="R105">
+        <v>0.5</v>
+      </c>
+      <c r="S105" t="s">
+        <v>2834</v>
+      </c>
+      <c r="T105" t="s">
+        <v>2225</v>
+      </c>
+      <c r="V105">
+        <v>220</v>
+      </c>
+      <c r="W105">
+        <v>70</v>
+      </c>
+      <c r="X105">
+        <v>1</v>
+      </c>
+      <c r="Y105">
+        <v>1</v>
+      </c>
+      <c r="Z105">
+        <v>1</v>
+      </c>
+      <c r="AA105">
+        <v>1</v>
+      </c>
+      <c r="AB105">
+        <v>0</v>
+      </c>
+      <c r="AC105">
+        <v>0</v>
+      </c>
+      <c r="AD105" t="s">
+        <v>505</v>
+      </c>
+      <c r="AE105" t="s">
+        <v>2825</v>
+      </c>
+      <c r="AF105" t="s">
+        <v>2835</v>
+      </c>
+      <c r="AG105">
+        <v>5</v>
+      </c>
+      <c r="AH105">
+        <v>0</v>
+      </c>
+      <c r="AI105">
+        <v>3</v>
+      </c>
+      <c r="AJ105">
+        <v>2</v>
+      </c>
+      <c r="AK105">
+        <v>0</v>
+      </c>
+      <c r="AL105">
+        <v>0</v>
+      </c>
+      <c r="AM105">
+        <v>2</v>
+      </c>
+      <c r="AN105">
+        <v>50</v>
+      </c>
+      <c r="AO105">
+        <v>3</v>
+      </c>
+      <c r="AP105" t="s">
+        <v>2267</v>
+      </c>
+      <c r="AQ105" t="s">
+        <v>2836</v>
+      </c>
       <c r="AR105" s="4">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="AS105">
+        <v>1</v>
+      </c>
+      <c r="AT105" t="s">
+        <v>1910</v>
+      </c>
+      <c r="AU105">
+        <v>2</v>
+      </c>
+      <c r="AV105" t="s">
+        <v>2728</v>
+      </c>
+      <c r="AW105">
+        <v>2</v>
+      </c>
+      <c r="CJ105">
+        <v>1</v>
       </c>
       <c r="CK105" s="4">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
+      <c r="DW105">
+        <v>3</v>
+      </c>
+      <c r="DX105" t="s">
+        <v>2837</v>
+      </c>
+      <c r="DY105">
+        <v>2024</v>
+      </c>
+      <c r="DZ105" t="s">
+        <v>2838</v>
+      </c>
+      <c r="EA105" t="s">
+        <v>2607</v>
+      </c>
+      <c r="EB105" t="s">
+        <v>1793</v>
+      </c>
+      <c r="EC105" t="s">
+        <v>1793</v>
+      </c>
+      <c r="ED105" t="s">
+        <v>2299</v>
+      </c>
+      <c r="EF105" t="s">
+        <v>441</v>
+      </c>
+      <c r="EG105" t="s">
+        <v>442</v>
+      </c>
+      <c r="EI105" s="10" t="s">
+        <v>2839</v>
+      </c>
+      <c r="EL105" s="10" t="s">
+        <v>2840</v>
+      </c>
+      <c r="EO105" s="10" t="s">
+        <v>2841</v>
+      </c>
+      <c r="FJ105" t="s">
+        <v>819</v>
+      </c>
+      <c r="FK105">
+        <v>1000</v>
+      </c>
       <c r="FL105" s="4">
         <f t="shared" si="30"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="FN105">
         <v>0</v>
       </c>
       <c r="FO105" s="4">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
+      <c r="FQ105">
+        <v>0</v>
+      </c>
       <c r="FR105" s="4">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
+      <c r="FS105" t="s">
+        <v>454</v>
+      </c>
+      <c r="FT105">
+        <f t="shared" ref="FT105" si="39">60*AG105</f>
+        <v>300</v>
+      </c>
       <c r="FU105" s="4">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="FV105" s="4">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>0.35333333333333333</v>
       </c>
       <c r="FW105" s="4" t="str">
         <f t="shared" si="27"/>
@@ -46097,27 +46746,27 @@
         <v>0</v>
       </c>
       <c r="CK110" s="4">
-        <f t="shared" ref="CK110:CK141" si="39">+CL110+CN110+CO110+CP110+CQ110</f>
+        <f t="shared" ref="CK110:CK141" si="40">+CL110+CN110+CO110+CP110+CQ110</f>
         <v>0</v>
       </c>
       <c r="FL110" s="4">
-        <f t="shared" ref="FL110:FL141" si="40">+FK110/3000</f>
+        <f t="shared" ref="FL110:FL141" si="41">+FK110/3000</f>
         <v>0</v>
       </c>
       <c r="FO110" s="4">
-        <f t="shared" ref="FO110:FO141" si="41">+FN110/1400</f>
+        <f t="shared" ref="FO110:FO141" si="42">+FN110/1400</f>
         <v>0</v>
       </c>
       <c r="FR110" s="4">
-        <f t="shared" ref="FR110:FR141" si="42">+FQ110/2000</f>
+        <f t="shared" ref="FR110:FR141" si="43">+FQ110/2000</f>
         <v>0</v>
       </c>
       <c r="FU110" s="4">
-        <f t="shared" ref="FU110:FU141" si="43">+FT110/15000</f>
+        <f t="shared" ref="FU110:FU141" si="44">+FT110/15000</f>
         <v>0</v>
       </c>
       <c r="FV110" s="4">
-        <f t="shared" ref="FV110:FV141" si="44">+FL110+FO110+FR110+FU110</f>
+        <f t="shared" ref="FV110:FV141" si="45">+FL110+FO110+FR110+FU110</f>
         <v>0</v>
       </c>
       <c r="FW110" s="4" t="str">
@@ -46134,27 +46783,27 @@
         <v>0</v>
       </c>
       <c r="CK111" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FL111" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FO111" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FR111" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FU111" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FV111" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FW111" s="4" t="str">
@@ -46171,27 +46820,27 @@
         <v>0</v>
       </c>
       <c r="CK112" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FL112" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FO112" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FR112" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FU112" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FV112" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FW112" s="4" t="str">
@@ -46208,27 +46857,27 @@
         <v>0</v>
       </c>
       <c r="CK113" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FL113" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FO113" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FR113" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FU113" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FV113" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FW113" s="4" t="str">
@@ -46245,27 +46894,27 @@
         <v>0</v>
       </c>
       <c r="CK114" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FL114" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FO114" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FR114" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FU114" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FV114" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FW114" s="4" t="str">
@@ -46282,27 +46931,27 @@
         <v>0</v>
       </c>
       <c r="CK115" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FL115" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FO115" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FR115" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FU115" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FV115" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FW115" s="4" t="str">
@@ -46319,27 +46968,27 @@
         <v>0</v>
       </c>
       <c r="CK116" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FL116" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FO116" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FR116" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FU116" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FV116" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FW116" s="4" t="str">
@@ -46356,27 +47005,27 @@
         <v>0</v>
       </c>
       <c r="CK117" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FL117" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FO117" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FR117" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FU117" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FV117" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FW117" s="4" t="str">
@@ -46393,27 +47042,27 @@
         <v>0</v>
       </c>
       <c r="CK118" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FL118" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FO118" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FR118" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FU118" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FV118" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FW118" s="4" t="str">
@@ -46430,27 +47079,27 @@
         <v>0</v>
       </c>
       <c r="CK119" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FL119" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FO119" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FR119" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FU119" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FV119" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FW119" s="4" t="str">
@@ -46467,27 +47116,27 @@
         <v>0</v>
       </c>
       <c r="CK120" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FL120" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FO120" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FR120" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FU120" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FV120" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FW120" s="4" t="str">
@@ -46504,27 +47153,27 @@
         <v>0</v>
       </c>
       <c r="CK121" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FL121" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FO121" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FR121" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FU121" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FV121" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FW121" s="4" t="str">
@@ -46541,27 +47190,27 @@
         <v>0</v>
       </c>
       <c r="CK122" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FL122" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FO122" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FR122" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FU122" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FV122" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FW122" s="4" t="str">
@@ -46578,27 +47227,27 @@
         <v>0</v>
       </c>
       <c r="CK123" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FL123" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FO123" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FR123" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FU123" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FV123" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FW123" s="4" t="str">
@@ -46615,27 +47264,27 @@
         <v>0</v>
       </c>
       <c r="CK124" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FL124" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FO124" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FR124" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FU124" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FV124" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FW124" s="4" t="str">
@@ -46652,27 +47301,27 @@
         <v>0</v>
       </c>
       <c r="CK125" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FL125" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FO125" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FR125" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FU125" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FV125" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FW125" s="4" t="str">
@@ -46689,27 +47338,27 @@
         <v>0</v>
       </c>
       <c r="CK126" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FL126" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FO126" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FR126" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FU126" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FV126" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FW126" s="4" t="str">
@@ -46726,27 +47375,27 @@
         <v>0</v>
       </c>
       <c r="CK127" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FL127" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FO127" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FR127" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FU127" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FV127" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FW127" s="4" t="str">
@@ -46763,31 +47412,31 @@
         <v>0</v>
       </c>
       <c r="CK128" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FL128" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FO128" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FR128" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FU128" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FV128" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FW128" s="4" t="str">
-        <f t="shared" ref="FW128:FW191" si="45">IF(W128&gt;=3000,"ALTO",IF(FV128&gt;=1,"ALTO","ORDINARIO"))</f>
+        <f t="shared" ref="FW128:FW191" si="46">IF(W128&gt;=3000,"ALTO",IF(FV128&gt;=1,"ALTO","ORDINARIO"))</f>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -46800,31 +47449,31 @@
         <v>0</v>
       </c>
       <c r="CK129" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FL129" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FO129" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FR129" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FU129" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FV129" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FW129" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -46837,31 +47486,31 @@
         <v>0</v>
       </c>
       <c r="CK130" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FL130" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FO130" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FR130" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FU130" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FV130" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FW130" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -46870,35 +47519,35 @@
         <v>129</v>
       </c>
       <c r="AR131" s="4">
-        <f t="shared" ref="AR131:AR162" si="46">+AS131+AU131+BE131+CD131+CE131+CF131+CG131+CH131+CI131+CW131</f>
+        <f t="shared" ref="AR131:AR162" si="47">+AS131+AU131+BE131+CD131+CE131+CF131+CG131+CH131+CI131+CW131</f>
         <v>0</v>
       </c>
       <c r="CK131" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="FL131" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="FO131" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="FR131" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="FU131" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="FV131" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="FW131" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -46907,35 +47556,35 @@
         <v>130</v>
       </c>
       <c r="AR132" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="CK132" s="4">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="FL132" s="4">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="FO132" s="4">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="FR132" s="4">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="FU132" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="FV132" s="4">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="FW132" s="4" t="str">
         <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="CK132" s="4">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="FL132" s="4">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="FO132" s="4">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="FR132" s="4">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="FU132" s="4">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="FV132" s="4">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="FW132" s="4" t="str">
-        <f t="shared" si="45"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -46944,35 +47593,35 @@
         <v>131</v>
       </c>
       <c r="AR133" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="CK133" s="4">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="FL133" s="4">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="FO133" s="4">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="FR133" s="4">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="FU133" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="FV133" s="4">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="FW133" s="4" t="str">
         <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="CK133" s="4">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="FL133" s="4">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="FO133" s="4">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="FR133" s="4">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="FU133" s="4">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="FV133" s="4">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="FW133" s="4" t="str">
-        <f t="shared" si="45"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -46981,35 +47630,35 @@
         <v>132</v>
       </c>
       <c r="AR134" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="CK134" s="4">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="FL134" s="4">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="FO134" s="4">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="FR134" s="4">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="FU134" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="FV134" s="4">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="FW134" s="4" t="str">
         <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="CK134" s="4">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="FL134" s="4">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="FO134" s="4">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="FR134" s="4">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="FU134" s="4">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="FV134" s="4">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="FW134" s="4" t="str">
-        <f t="shared" si="45"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -47018,35 +47667,35 @@
         <v>133</v>
       </c>
       <c r="AR135" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="CK135" s="4">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="FL135" s="4">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="FO135" s="4">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="FR135" s="4">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="FU135" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="FV135" s="4">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="FW135" s="4" t="str">
         <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="CK135" s="4">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="FL135" s="4">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="FO135" s="4">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="FR135" s="4">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="FU135" s="4">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="FV135" s="4">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="FW135" s="4" t="str">
-        <f t="shared" si="45"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -47055,35 +47704,35 @@
         <v>134</v>
       </c>
       <c r="AR136" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="CK136" s="4">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="FL136" s="4">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="FO136" s="4">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="FR136" s="4">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="FU136" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="FV136" s="4">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="FW136" s="4" t="str">
         <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="CK136" s="4">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="FL136" s="4">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="FO136" s="4">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="FR136" s="4">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="FU136" s="4">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="FV136" s="4">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="FW136" s="4" t="str">
-        <f t="shared" si="45"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -47092,35 +47741,35 @@
         <v>135</v>
       </c>
       <c r="AR137" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="CK137" s="4">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="FL137" s="4">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="FO137" s="4">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="FR137" s="4">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="FU137" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="FV137" s="4">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="FW137" s="4" t="str">
         <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="CK137" s="4">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="FL137" s="4">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="FO137" s="4">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="FR137" s="4">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="FU137" s="4">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="FV137" s="4">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="FW137" s="4" t="str">
-        <f t="shared" si="45"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -47129,35 +47778,35 @@
         <v>136</v>
       </c>
       <c r="AR138" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="CK138" s="4">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="FL138" s="4">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="FO138" s="4">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="FR138" s="4">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="FU138" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="FV138" s="4">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="FW138" s="4" t="str">
         <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="CK138" s="4">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="FL138" s="4">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="FO138" s="4">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="FR138" s="4">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="FU138" s="4">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="FV138" s="4">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="FW138" s="4" t="str">
-        <f t="shared" si="45"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -47166,35 +47815,35 @@
         <v>137</v>
       </c>
       <c r="AR139" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="CK139" s="4">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="FL139" s="4">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="FO139" s="4">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="FR139" s="4">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="FU139" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="FV139" s="4">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="FW139" s="4" t="str">
         <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="CK139" s="4">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="FL139" s="4">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="FO139" s="4">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="FR139" s="4">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="FU139" s="4">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="FV139" s="4">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="FW139" s="4" t="str">
-        <f t="shared" si="45"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -47203,35 +47852,35 @@
         <v>138</v>
       </c>
       <c r="AR140" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="CK140" s="4">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="FL140" s="4">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="FO140" s="4">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="FR140" s="4">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="FU140" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="FV140" s="4">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="FW140" s="4" t="str">
         <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="CK140" s="4">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="FL140" s="4">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="FO140" s="4">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="FR140" s="4">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="FU140" s="4">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="FV140" s="4">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="FW140" s="4" t="str">
-        <f t="shared" si="45"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -47240,35 +47889,35 @@
         <v>139</v>
       </c>
       <c r="AR141" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="CK141" s="4">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="FL141" s="4">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="FO141" s="4">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="FR141" s="4">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="FU141" s="4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="FV141" s="4">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="FW141" s="4" t="str">
         <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="CK141" s="4">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="FL141" s="4">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="FO141" s="4">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="FR141" s="4">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="FU141" s="4">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="FV141" s="4">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="FW141" s="4" t="str">
-        <f t="shared" si="45"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -47277,35 +47926,35 @@
         <v>140</v>
       </c>
       <c r="AR142" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="CK142" s="4">
+        <f t="shared" ref="CK142:CK173" si="48">+CL142+CN142+CO142+CP142+CQ142</f>
+        <v>0</v>
+      </c>
+      <c r="FL142" s="4">
+        <f t="shared" ref="FL142:FL173" si="49">+FK142/3000</f>
+        <v>0</v>
+      </c>
+      <c r="FO142" s="4">
+        <f t="shared" ref="FO142:FO173" si="50">+FN142/1400</f>
+        <v>0</v>
+      </c>
+      <c r="FR142" s="4">
+        <f t="shared" ref="FR142:FR173" si="51">+FQ142/2000</f>
+        <v>0</v>
+      </c>
+      <c r="FU142" s="4">
+        <f t="shared" ref="FU142:FU173" si="52">+FT142/15000</f>
+        <v>0</v>
+      </c>
+      <c r="FV142" s="4">
+        <f t="shared" ref="FV142:FV173" si="53">+FL142+FO142+FR142+FU142</f>
+        <v>0</v>
+      </c>
+      <c r="FW142" s="4" t="str">
         <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="CK142" s="4">
-        <f t="shared" ref="CK142:CK173" si="47">+CL142+CN142+CO142+CP142+CQ142</f>
-        <v>0</v>
-      </c>
-      <c r="FL142" s="4">
-        <f t="shared" ref="FL142:FL173" si="48">+FK142/3000</f>
-        <v>0</v>
-      </c>
-      <c r="FO142" s="4">
-        <f t="shared" ref="FO142:FO173" si="49">+FN142/1400</f>
-        <v>0</v>
-      </c>
-      <c r="FR142" s="4">
-        <f t="shared" ref="FR142:FR173" si="50">+FQ142/2000</f>
-        <v>0</v>
-      </c>
-      <c r="FU142" s="4">
-        <f t="shared" ref="FU142:FU173" si="51">+FT142/15000</f>
-        <v>0</v>
-      </c>
-      <c r="FV142" s="4">
-        <f t="shared" ref="FV142:FV173" si="52">+FL142+FO142+FR142+FU142</f>
-        <v>0</v>
-      </c>
-      <c r="FW142" s="4" t="str">
-        <f t="shared" si="45"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -47314,35 +47963,35 @@
         <v>141</v>
       </c>
       <c r="AR143" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="CK143" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FL143" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FO143" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FR143" s="4">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="FU143" s="4">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="FV143" s="4">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="FW143" s="4" t="str">
         <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="CK143" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FL143" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FO143" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FR143" s="4">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="FU143" s="4">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="FV143" s="4">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="FW143" s="4" t="str">
-        <f t="shared" si="45"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -47351,35 +48000,35 @@
         <v>142</v>
       </c>
       <c r="AR144" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="CK144" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FL144" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FO144" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FR144" s="4">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="FU144" s="4">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="FV144" s="4">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="FW144" s="4" t="str">
         <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="CK144" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FL144" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FO144" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FR144" s="4">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="FU144" s="4">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="FV144" s="4">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="FW144" s="4" t="str">
-        <f t="shared" si="45"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -47388,35 +48037,35 @@
         <v>143</v>
       </c>
       <c r="AR145" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="CK145" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FL145" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FO145" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FR145" s="4">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="FU145" s="4">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="FV145" s="4">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="FW145" s="4" t="str">
         <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="CK145" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FL145" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FO145" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FR145" s="4">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="FU145" s="4">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="FV145" s="4">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="FW145" s="4" t="str">
-        <f t="shared" si="45"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -47425,35 +48074,35 @@
         <v>144</v>
       </c>
       <c r="AR146" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="CK146" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FL146" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FO146" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FR146" s="4">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="FU146" s="4">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="FV146" s="4">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="FW146" s="4" t="str">
         <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="CK146" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FL146" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FO146" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FR146" s="4">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="FU146" s="4">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="FV146" s="4">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="FW146" s="4" t="str">
-        <f t="shared" si="45"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -47462,35 +48111,35 @@
         <v>145</v>
       </c>
       <c r="AR147" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="CK147" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FL147" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FO147" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FR147" s="4">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="FU147" s="4">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="FV147" s="4">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="FW147" s="4" t="str">
         <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="CK147" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FL147" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FO147" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FR147" s="4">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="FU147" s="4">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="FV147" s="4">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="FW147" s="4" t="str">
-        <f t="shared" si="45"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -47499,35 +48148,35 @@
         <v>146</v>
       </c>
       <c r="AR148" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="CK148" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FL148" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FO148" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FR148" s="4">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="FU148" s="4">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="FV148" s="4">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="FW148" s="4" t="str">
         <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="CK148" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FL148" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FO148" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FR148" s="4">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="FU148" s="4">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="FV148" s="4">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="FW148" s="4" t="str">
-        <f t="shared" si="45"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -47536,35 +48185,35 @@
         <v>147</v>
       </c>
       <c r="AR149" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="CK149" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FL149" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FO149" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FR149" s="4">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="FU149" s="4">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="FV149" s="4">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="FW149" s="4" t="str">
         <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="CK149" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FL149" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FO149" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FR149" s="4">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="FU149" s="4">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="FV149" s="4">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="FW149" s="4" t="str">
-        <f t="shared" si="45"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -47573,35 +48222,35 @@
         <v>148</v>
       </c>
       <c r="AR150" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="CK150" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FL150" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FO150" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FR150" s="4">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="FU150" s="4">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="FV150" s="4">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="FW150" s="4" t="str">
         <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="CK150" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FL150" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FO150" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FR150" s="4">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="FU150" s="4">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="FV150" s="4">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="FW150" s="4" t="str">
-        <f t="shared" si="45"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -47610,35 +48259,35 @@
         <v>149</v>
       </c>
       <c r="AR151" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="CK151" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FL151" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FO151" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FR151" s="4">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="FU151" s="4">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="FV151" s="4">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="FW151" s="4" t="str">
         <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="CK151" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FL151" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FO151" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FR151" s="4">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="FU151" s="4">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="FV151" s="4">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="FW151" s="4" t="str">
-        <f t="shared" si="45"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -47647,35 +48296,35 @@
         <v>150</v>
       </c>
       <c r="AR152" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="CK152" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FL152" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FO152" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FR152" s="4">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="FU152" s="4">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="FV152" s="4">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="FW152" s="4" t="str">
         <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="CK152" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FL152" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FO152" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FR152" s="4">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="FU152" s="4">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="FV152" s="4">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="FW152" s="4" t="str">
-        <f t="shared" si="45"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -47684,35 +48333,35 @@
         <v>151</v>
       </c>
       <c r="AR153" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="CK153" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FL153" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FO153" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FR153" s="4">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="FU153" s="4">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="FV153" s="4">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="FW153" s="4" t="str">
         <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="CK153" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FL153" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FO153" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FR153" s="4">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="FU153" s="4">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="FV153" s="4">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="FW153" s="4" t="str">
-        <f t="shared" si="45"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -47721,35 +48370,35 @@
         <v>152</v>
       </c>
       <c r="AR154" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="CK154" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FL154" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FO154" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FR154" s="4">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="FU154" s="4">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="FV154" s="4">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="FW154" s="4" t="str">
         <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="CK154" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FL154" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FO154" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FR154" s="4">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="FU154" s="4">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="FV154" s="4">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="FW154" s="4" t="str">
-        <f t="shared" si="45"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -47758,35 +48407,35 @@
         <v>153</v>
       </c>
       <c r="AR155" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="CK155" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FL155" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FO155" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FR155" s="4">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="FU155" s="4">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="FV155" s="4">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="FW155" s="4" t="str">
         <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="CK155" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FL155" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FO155" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FR155" s="4">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="FU155" s="4">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="FV155" s="4">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="FW155" s="4" t="str">
-        <f t="shared" si="45"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -47795,35 +48444,35 @@
         <v>154</v>
       </c>
       <c r="AR156" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="CK156" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FL156" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FO156" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FR156" s="4">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="FU156" s="4">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="FV156" s="4">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="FW156" s="4" t="str">
         <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="CK156" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FL156" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FO156" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FR156" s="4">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="FU156" s="4">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="FV156" s="4">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="FW156" s="4" t="str">
-        <f t="shared" si="45"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -47832,35 +48481,35 @@
         <v>155</v>
       </c>
       <c r="AR157" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="CK157" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FL157" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FO157" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FR157" s="4">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="FU157" s="4">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="FV157" s="4">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="FW157" s="4" t="str">
         <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="CK157" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FL157" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FO157" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FR157" s="4">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="FU157" s="4">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="FV157" s="4">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="FW157" s="4" t="str">
-        <f t="shared" si="45"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -47869,35 +48518,35 @@
         <v>156</v>
       </c>
       <c r="AR158" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="CK158" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FL158" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FO158" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FR158" s="4">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="FU158" s="4">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="FV158" s="4">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="FW158" s="4" t="str">
         <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="CK158" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FL158" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FO158" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FR158" s="4">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="FU158" s="4">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="FV158" s="4">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="FW158" s="4" t="str">
-        <f t="shared" si="45"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -47906,35 +48555,35 @@
         <v>157</v>
       </c>
       <c r="AR159" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="CK159" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FL159" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FO159" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FR159" s="4">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="FU159" s="4">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="FV159" s="4">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="FW159" s="4" t="str">
         <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="CK159" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FL159" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FO159" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FR159" s="4">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="FU159" s="4">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="FV159" s="4">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="FW159" s="4" t="str">
-        <f t="shared" si="45"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -47943,35 +48592,35 @@
         <v>158</v>
       </c>
       <c r="AR160" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="CK160" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FL160" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FO160" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FR160" s="4">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="FU160" s="4">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="FV160" s="4">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="FW160" s="4" t="str">
         <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="CK160" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FL160" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FO160" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FR160" s="4">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="FU160" s="4">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="FV160" s="4">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="FW160" s="4" t="str">
-        <f t="shared" si="45"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -47980,35 +48629,35 @@
         <v>159</v>
       </c>
       <c r="AR161" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="CK161" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FL161" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FO161" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FR161" s="4">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="FU161" s="4">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="FV161" s="4">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="FW161" s="4" t="str">
         <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="CK161" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FL161" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FO161" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FR161" s="4">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="FU161" s="4">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="FV161" s="4">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="FW161" s="4" t="str">
-        <f t="shared" si="45"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -48017,35 +48666,35 @@
         <v>160</v>
       </c>
       <c r="AR162" s="4">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="CK162" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FL162" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FO162" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FR162" s="4">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="FU162" s="4">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="FV162" s="4">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="FW162" s="4" t="str">
         <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="CK162" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FL162" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FO162" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FR162" s="4">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="FU162" s="4">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="FV162" s="4">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="FW162" s="4" t="str">
-        <f t="shared" si="45"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -48054,35 +48703,35 @@
         <v>161</v>
       </c>
       <c r="AR163" s="4">
-        <f t="shared" ref="AR163:AR194" si="53">+AS163+AU163+BE163+CD163+CE163+CF163+CG163+CH163+CI163+CW163</f>
+        <f t="shared" ref="AR163:AR194" si="54">+AS163+AU163+BE163+CD163+CE163+CF163+CG163+CH163+CI163+CW163</f>
         <v>0</v>
       </c>
       <c r="CK163" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="FL163" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="FO163" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="FR163" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="FU163" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="FV163" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="FW163" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -48091,35 +48740,35 @@
         <v>162</v>
       </c>
       <c r="AR164" s="4">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="CK164" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FL164" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FO164" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FR164" s="4">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="FU164" s="4">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="FV164" s="4">
         <f t="shared" si="53"/>
         <v>0</v>
       </c>
-      <c r="CK164" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FL164" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FO164" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FR164" s="4">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="FU164" s="4">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="FV164" s="4">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
       <c r="FW164" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -48128,35 +48777,35 @@
         <v>163</v>
       </c>
       <c r="AR165" s="4">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="CK165" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FL165" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FO165" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FR165" s="4">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="FU165" s="4">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="FV165" s="4">
         <f t="shared" si="53"/>
         <v>0</v>
       </c>
-      <c r="CK165" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FL165" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FO165" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FR165" s="4">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="FU165" s="4">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="FV165" s="4">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
       <c r="FW165" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -48165,35 +48814,35 @@
         <v>164</v>
       </c>
       <c r="AR166" s="4">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="CK166" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FL166" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FO166" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FR166" s="4">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="FU166" s="4">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="FV166" s="4">
         <f t="shared" si="53"/>
         <v>0</v>
       </c>
-      <c r="CK166" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FL166" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FO166" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FR166" s="4">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="FU166" s="4">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="FV166" s="4">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
       <c r="FW166" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -48202,35 +48851,35 @@
         <v>165</v>
       </c>
       <c r="AR167" s="4">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="CK167" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FL167" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FO167" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FR167" s="4">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="FU167" s="4">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="FV167" s="4">
         <f t="shared" si="53"/>
         <v>0</v>
       </c>
-      <c r="CK167" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FL167" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FO167" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FR167" s="4">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="FU167" s="4">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="FV167" s="4">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
       <c r="FW167" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -48239,35 +48888,35 @@
         <v>166</v>
       </c>
       <c r="AR168" s="4">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="CK168" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FL168" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FO168" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FR168" s="4">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="FU168" s="4">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="FV168" s="4">
         <f t="shared" si="53"/>
         <v>0</v>
       </c>
-      <c r="CK168" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FL168" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FO168" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FR168" s="4">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="FU168" s="4">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="FV168" s="4">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
       <c r="FW168" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -48276,35 +48925,35 @@
         <v>167</v>
       </c>
       <c r="AR169" s="4">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="CK169" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FL169" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FO169" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FR169" s="4">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="FU169" s="4">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="FV169" s="4">
         <f t="shared" si="53"/>
         <v>0</v>
       </c>
-      <c r="CK169" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FL169" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FO169" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FR169" s="4">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="FU169" s="4">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="FV169" s="4">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
       <c r="FW169" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -48313,35 +48962,35 @@
         <v>168</v>
       </c>
       <c r="AR170" s="4">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="CK170" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FL170" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FO170" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FR170" s="4">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="FU170" s="4">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="FV170" s="4">
         <f t="shared" si="53"/>
         <v>0</v>
       </c>
-      <c r="CK170" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FL170" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FO170" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FR170" s="4">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="FU170" s="4">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="FV170" s="4">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
       <c r="FW170" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -48350,35 +48999,35 @@
         <v>169</v>
       </c>
       <c r="AR171" s="4">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="CK171" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FL171" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FO171" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FR171" s="4">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="FU171" s="4">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="FV171" s="4">
         <f t="shared" si="53"/>
         <v>0</v>
       </c>
-      <c r="CK171" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FL171" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FO171" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FR171" s="4">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="FU171" s="4">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="FV171" s="4">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
       <c r="FW171" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -48387,35 +49036,35 @@
         <v>170</v>
       </c>
       <c r="AR172" s="4">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="CK172" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FL172" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FO172" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FR172" s="4">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="FU172" s="4">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="FV172" s="4">
         <f t="shared" si="53"/>
         <v>0</v>
       </c>
-      <c r="CK172" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FL172" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FO172" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FR172" s="4">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="FU172" s="4">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="FV172" s="4">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
       <c r="FW172" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -48424,35 +49073,35 @@
         <v>171</v>
       </c>
       <c r="AR173" s="4">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="CK173" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="FL173" s="4">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="FO173" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="FR173" s="4">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="FU173" s="4">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="FV173" s="4">
         <f t="shared" si="53"/>
         <v>0</v>
       </c>
-      <c r="CK173" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="FL173" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="FO173" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="FR173" s="4">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="FU173" s="4">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="FV173" s="4">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
       <c r="FW173" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -48461,35 +49110,35 @@
         <v>172</v>
       </c>
       <c r="AR174" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="CK174" s="4">
-        <f t="shared" ref="CK174:CK198" si="54">+CL174+CN174+CO174+CP174+CQ174</f>
+        <f t="shared" ref="CK174:CK198" si="55">+CL174+CN174+CO174+CP174+CQ174</f>
         <v>0</v>
       </c>
       <c r="FL174" s="4">
-        <f t="shared" ref="FL174:FL198" si="55">+FK174/3000</f>
+        <f t="shared" ref="FL174:FL198" si="56">+FK174/3000</f>
         <v>0</v>
       </c>
       <c r="FO174" s="4">
-        <f t="shared" ref="FO174:FO198" si="56">+FN174/1400</f>
+        <f t="shared" ref="FO174:FO198" si="57">+FN174/1400</f>
         <v>0</v>
       </c>
       <c r="FR174" s="4">
-        <f t="shared" ref="FR174:FR198" si="57">+FQ174/2000</f>
+        <f t="shared" ref="FR174:FR198" si="58">+FQ174/2000</f>
         <v>0</v>
       </c>
       <c r="FU174" s="4">
-        <f t="shared" ref="FU174:FU198" si="58">+FT174/15000</f>
+        <f t="shared" ref="FU174:FU198" si="59">+FT174/15000</f>
         <v>0</v>
       </c>
       <c r="FV174" s="4">
-        <f t="shared" ref="FV174:FV198" si="59">+FL174+FO174+FR174+FU174</f>
+        <f t="shared" ref="FV174:FV198" si="60">+FL174+FO174+FR174+FU174</f>
         <v>0</v>
       </c>
       <c r="FW174" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -48498,35 +49147,35 @@
         <v>173</v>
       </c>
       <c r="AR175" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="CK175" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FL175" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FO175" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FR175" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FU175" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FV175" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FW175" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -48535,35 +49184,35 @@
         <v>174</v>
       </c>
       <c r="AR176" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="CK176" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FL176" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FO176" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FR176" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FU176" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FV176" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FW176" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -48572,35 +49221,35 @@
         <v>175</v>
       </c>
       <c r="AR177" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="CK177" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FL177" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FO177" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FR177" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FU177" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FV177" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FW177" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -48609,35 +49258,35 @@
         <v>176</v>
       </c>
       <c r="AR178" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="CK178" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FL178" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FO178" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FR178" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FU178" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FV178" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FW178" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -48646,35 +49295,35 @@
         <v>177</v>
       </c>
       <c r="AR179" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="CK179" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FL179" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FO179" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FR179" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FU179" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FV179" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FW179" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -48683,35 +49332,35 @@
         <v>178</v>
       </c>
       <c r="AR180" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="CK180" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FL180" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FO180" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FR180" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FU180" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FV180" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FW180" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -48720,35 +49369,35 @@
         <v>179</v>
       </c>
       <c r="AR181" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="CK181" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FL181" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FO181" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FR181" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FU181" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FV181" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FW181" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -48757,35 +49406,35 @@
         <v>180</v>
       </c>
       <c r="AR182" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="CK182" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FL182" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FO182" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FR182" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FU182" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FV182" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FW182" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -48794,35 +49443,35 @@
         <v>181</v>
       </c>
       <c r="AR183" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="CK183" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FL183" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FO183" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FR183" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FU183" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FV183" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FW183" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -48831,35 +49480,35 @@
         <v>182</v>
       </c>
       <c r="AR184" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="CK184" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FL184" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FO184" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FR184" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FU184" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FV184" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FW184" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -48868,35 +49517,35 @@
         <v>183</v>
       </c>
       <c r="AR185" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="CK185" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FL185" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FO185" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FR185" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FU185" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FV185" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FW185" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -48905,35 +49554,35 @@
         <v>184</v>
       </c>
       <c r="AR186" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="CK186" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FL186" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FO186" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FR186" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FU186" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FV186" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FW186" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -48942,35 +49591,35 @@
         <v>185</v>
       </c>
       <c r="AR187" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="CK187" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FL187" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FO187" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FR187" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FU187" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FV187" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FW187" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -48979,35 +49628,35 @@
         <v>186</v>
       </c>
       <c r="AR188" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="CK188" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FL188" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FO188" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FR188" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FU188" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FV188" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FW188" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -49016,35 +49665,35 @@
         <v>187</v>
       </c>
       <c r="AR189" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="CK189" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FL189" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FO189" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FR189" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FU189" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FV189" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FW189" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -49053,35 +49702,35 @@
         <v>188</v>
       </c>
       <c r="AR190" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="CK190" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FL190" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FO190" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FR190" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FU190" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FV190" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FW190" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -49090,35 +49739,35 @@
         <v>189</v>
       </c>
       <c r="AR191" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="CK191" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FL191" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FO191" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FR191" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FU191" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FV191" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FW191" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -49127,35 +49776,35 @@
         <v>190</v>
       </c>
       <c r="AR192" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="CK192" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FL192" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FO192" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FR192" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FU192" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FV192" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FW192" s="4" t="str">
-        <f t="shared" ref="FW192:FW198" si="60">IF(W192&gt;=3000,"ALTO",IF(FV192&gt;=1,"ALTO","ORDINARIO"))</f>
+        <f t="shared" ref="FW192:FW198" si="61">IF(W192&gt;=3000,"ALTO",IF(FV192&gt;=1,"ALTO","ORDINARIO"))</f>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -49164,35 +49813,35 @@
         <v>191</v>
       </c>
       <c r="AR193" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="CK193" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FL193" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FO193" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FR193" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FU193" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FV193" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FW193" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -49201,35 +49850,35 @@
         <v>192</v>
       </c>
       <c r="AR194" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="CK194" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FL194" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FO194" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FR194" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FU194" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FV194" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FW194" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -49238,35 +49887,35 @@
         <v>193</v>
       </c>
       <c r="AR195" s="4">
-        <f t="shared" ref="AR195:AR198" si="61">+AS195+AU195+BE195+CD195+CE195+CF195+CG195+CH195+CI195+CW195</f>
+        <f t="shared" ref="AR195:AR198" si="62">+AS195+AU195+BE195+CD195+CE195+CF195+CG195+CH195+CI195+CW195</f>
         <v>0</v>
       </c>
       <c r="CK195" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="FL195" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="FO195" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="FR195" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="FU195" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="FV195" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="FW195" s="4" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -49275,35 +49924,35 @@
         <v>194</v>
       </c>
       <c r="AR196" s="4">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="CK196" s="4">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="FL196" s="4">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="FO196" s="4">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+      <c r="FR196" s="4">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="FU196" s="4">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+      <c r="FV196" s="4">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="FW196" s="4" t="str">
         <f t="shared" si="61"/>
-        <v>0</v>
-      </c>
-      <c r="CK196" s="4">
-        <f t="shared" si="54"/>
-        <v>0</v>
-      </c>
-      <c r="FL196" s="4">
-        <f t="shared" si="55"/>
-        <v>0</v>
-      </c>
-      <c r="FO196" s="4">
-        <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
-      <c r="FR196" s="4">
-        <f t="shared" si="57"/>
-        <v>0</v>
-      </c>
-      <c r="FU196" s="4">
-        <f t="shared" si="58"/>
-        <v>0</v>
-      </c>
-      <c r="FV196" s="4">
-        <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-      <c r="FW196" s="4" t="str">
-        <f t="shared" si="60"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -49312,35 +49961,35 @@
         <v>195</v>
       </c>
       <c r="AR197" s="4">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="CK197" s="4">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="FL197" s="4">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="FO197" s="4">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+      <c r="FR197" s="4">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="FU197" s="4">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+      <c r="FV197" s="4">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="FW197" s="4" t="str">
         <f t="shared" si="61"/>
-        <v>0</v>
-      </c>
-      <c r="CK197" s="4">
-        <f t="shared" si="54"/>
-        <v>0</v>
-      </c>
-      <c r="FL197" s="4">
-        <f t="shared" si="55"/>
-        <v>0</v>
-      </c>
-      <c r="FO197" s="4">
-        <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
-      <c r="FR197" s="4">
-        <f t="shared" si="57"/>
-        <v>0</v>
-      </c>
-      <c r="FU197" s="4">
-        <f t="shared" si="58"/>
-        <v>0</v>
-      </c>
-      <c r="FV197" s="4">
-        <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-      <c r="FW197" s="4" t="str">
-        <f t="shared" si="60"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -49349,35 +49998,35 @@
         <v>196</v>
       </c>
       <c r="AR198" s="4">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="CK198" s="4">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="FL198" s="4">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="FO198" s="4">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+      <c r="FR198" s="4">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="FU198" s="4">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+      <c r="FV198" s="4">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="FW198" s="4" t="str">
         <f t="shared" si="61"/>
-        <v>0</v>
-      </c>
-      <c r="CK198" s="4">
-        <f t="shared" si="54"/>
-        <v>0</v>
-      </c>
-      <c r="FL198" s="4">
-        <f t="shared" si="55"/>
-        <v>0</v>
-      </c>
-      <c r="FO198" s="4">
-        <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
-      <c r="FR198" s="4">
-        <f t="shared" si="57"/>
-        <v>0</v>
-      </c>
-      <c r="FU198" s="4">
-        <f t="shared" si="58"/>
-        <v>0</v>
-      </c>
-      <c r="FV198" s="4">
-        <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-      <c r="FW198" s="4" t="str">
-        <f t="shared" si="60"/>
         <v>ORDINARIO</v>
       </c>
     </row>
@@ -49675,17 +50324,18 @@
     <hyperlink ref="Q94" r:id="rId61" xr:uid="{7FD5C3B5-6934-4004-BED0-1FE5363BD542}"/>
     <hyperlink ref="Q100" r:id="rId62" xr:uid="{AEF7422C-FE06-4678-BB38-292B3DC8A973}"/>
     <hyperlink ref="Q101" r:id="rId63" xr:uid="{3EEC51D1-1175-427A-AD1B-B2FA33DAE2FB}"/>
+    <hyperlink ref="Q105" r:id="rId64" xr:uid="{6E0D60EF-9E87-419D-BDEC-FDC083CBA1B6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967294" verticalDpi="0" r:id="rId64"/>
-  <drawing r:id="rId65"/>
-  <legacyDrawing r:id="rId66"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967294" verticalDpi="0" r:id="rId65"/>
+  <drawing r:id="rId66"/>
+  <legacyDrawing r:id="rId67"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x14">
       <controls>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1025" r:id="rId67" name="Spinner 1">
+            <control shapeId="1025" r:id="rId68" name="Spinner 1">
               <controlPr defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
@@ -49719,7 +50369,7 @@
     <row r="1" spans="1:310" x14ac:dyDescent="0.3">
       <c r="A1">
         <f>+BD!A1</f>
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B1" t="s">
         <v>133</v>
@@ -50656,15 +51306,15 @@
       </c>
       <c r="C2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,3, FALSE)</f>
-        <v>PEDRO SALINAS LOAIZA</v>
+        <v>EFREN CONTRERAS ZAFRA</v>
       </c>
       <c r="D2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,4, FALSE)</f>
-        <v>HOSTAL HACIENDA APULCO, FONDA MARGARITA</v>
+        <v>DOMINICA 19</v>
       </c>
       <c r="E2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,5, FALSE)</f>
-        <v>SALP5304299D8</v>
+        <v>COZE850822S40</v>
       </c>
       <c r="F2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,6, FALSE)</f>
@@ -50672,31 +51322,31 @@
       </c>
       <c r="G2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,7, FALSE)</f>
-        <v>SERVICIO DE HOSPEDAJE Y ALIMENTOS C/ VTA DE BIDIDA ALCOHOLICA</v>
+        <v>CAFETERIA, RESTAURANTE</v>
       </c>
       <c r="H2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,8, FALSE)</f>
-        <v>OFRECE SERVICIOS DE ALOJAMIENTO RURAL, CON ACTIVIDADES RECREATIVAS EN CONTACTO CON LA NATURALEZA, COMO CAMINATAS, RECORRIDOS A CABALLO, Y EXPERIENCIAS DE RELAJACIÓN EN UN ENTORNO NATURAL.</v>
+        <v>PREPARAR Y SERVIR ALIMENTOS Y BEBIDAS, OFRECIENDO DESAYUNOS, COMIDAS, POSTRES Y CAFÉ EN UN AMBIENTE CÓMODO PARA EL CONSUMO EN EL LUGAR O PARA LLEVAR</v>
       </c>
       <c r="I2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,9, FALSE)</f>
-        <v>CARRETERA ZACAPOAXTLA - APULCO</v>
-      </c>
-      <c r="J2" t="str">
+        <v>BOULEVARD DE LAS CASCADAS</v>
+      </c>
+      <c r="J2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,10, FALSE)</f>
-        <v>KM 7</v>
-      </c>
-      <c r="K2">
+        <v>1301</v>
+      </c>
+      <c r="K2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,11, FALSE)</f>
-        <v>0</v>
+        <v>Q01</v>
       </c>
       <c r="L2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,12, FALSE)</f>
-        <v>XALACAPAN</v>
+        <v>LOMAS DE ANGELOPOLIS III</v>
       </c>
       <c r="M2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,13, FALSE)</f>
-        <v>ZACAPOAXTLA</v>
+        <v>SANTA CLARA OCOYUCAN</v>
       </c>
       <c r="N2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,14, FALSE)</f>
@@ -50704,23 +51354,23 @@
       </c>
       <c r="O2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,15, FALSE)</f>
-        <v>72310</v>
+        <v>72830</v>
       </c>
       <c r="P2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,16, FALSE)</f>
-        <v>2227115150</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,17, FALSE)</f>
-        <v>hostalapulco@gmail.com</v>
+        <v>administracion@dominica19.com</v>
       </c>
       <c r="R2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,18, FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="S2">
+        <v>0.5</v>
+      </c>
+      <c r="S2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,19, FALSE)</f>
-        <v>1920</v>
+        <v>DICIEMBRE DE 2024</v>
       </c>
       <c r="T2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,20, FALSE)</f>
@@ -50732,11 +51382,11 @@
       </c>
       <c r="V2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,22, FALSE)</f>
-        <v>1215.48</v>
+        <v>220</v>
       </c>
       <c r="W2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,23, FALSE)</f>
-        <v>1215.48</v>
+        <v>70</v>
       </c>
       <c r="X2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,24, FALSE)</f>
@@ -50744,11 +51394,11 @@
       </c>
       <c r="Y2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,25, FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,26, FALSE)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AA2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,27, FALSE)</f>
@@ -50756,7 +51406,7 @@
       </c>
       <c r="AB2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,28, FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,29, FALSE)</f>
@@ -50764,19 +51414,19 @@
       </c>
       <c r="AD2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,30, FALSE)</f>
-        <v>20  CAJONES</v>
+        <v>20 CAJONES</v>
       </c>
       <c r="AE2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,31, FALSE)</f>
-        <v>PEDRO SALINAS LOAIZA</v>
+        <v>EFREN CONTRERAS ZAFRA</v>
       </c>
       <c r="AF2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,32, FALSE)</f>
-        <v>NELYDA ALEJAO FUENTES</v>
+        <v>JOSE LUIS RODOLFO RODRIGUEZ</v>
       </c>
       <c r="AG2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,33, FALSE)</f>
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="AH2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,34, FALSE)</f>
@@ -50784,11 +51434,11 @@
       </c>
       <c r="AI2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,35, FALSE)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AJ2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,36, FALSE)</f>
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="AK2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,37, FALSE)</f>
@@ -50800,15 +51450,15 @@
       </c>
       <c r="AM2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,39, FALSE)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,40, FALSE)</f>
-        <v>167</v>
+        <v>50</v>
       </c>
       <c r="AO2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,41, FALSE)</f>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AP2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,42, FALSE)</f>
@@ -50816,31 +51466,31 @@
       </c>
       <c r="AQ2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,43, FALSE)</f>
-        <v>24 HORAS</v>
+        <v>8:00 A 23:00 HORAS</v>
       </c>
       <c r="AR2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,44, FALSE)</f>
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="AS2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,45, FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AT2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,46, FALSE)</f>
-        <v>RECEPCION</v>
+        <v>COCINA</v>
       </c>
       <c r="AU2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,47, FALSE)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,48, FALSE)</f>
-        <v>COCINA, TIENDA, RESTAURANTE</v>
+        <v>MOSTRADOR, ALMACEN</v>
       </c>
       <c r="AW2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,49, FALSE)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,50, FALSE)</f>
@@ -50972,7 +51622,7 @@
       </c>
       <c r="CD2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,82, FALSE)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="CE2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,83, FALSE)</f>
@@ -50980,7 +51630,7 @@
       </c>
       <c r="CF2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,84, FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,85, FALSE)</f>
@@ -50988,23 +51638,23 @@
       </c>
       <c r="CH2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,86, FALSE)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CI2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,87, FALSE)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CJ2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,88, FALSE)</f>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="CK2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,89, FALSE)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CL2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,90, FALSE)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CM2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,91, FALSE)</f>
@@ -51152,11 +51802,11 @@
       </c>
       <c r="DW2" s="5">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,127, FALSE)</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="DX2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,128, FALSE)</f>
-        <v>SEPTIEMBRE</v>
+        <v>DICIEMBRE</v>
       </c>
       <c r="DY2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,129, FALSE)</f>
@@ -51164,23 +51814,23 @@
       </c>
       <c r="DZ2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,130, FALSE)</f>
-        <v>19.918301312076668, -97.60839625744265</v>
+        <v>18.970035879601955, -98.2852424490102</v>
       </c>
       <c r="EA2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,131, FALSE)</f>
-        <v>FINCA SANTA MARIA</v>
+        <v>LOCAL COMERCIAL</v>
       </c>
       <c r="EB2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,132, FALSE)</f>
-        <v>CARRETERA</v>
+        <v>ESTACIONAMIENTO</v>
       </c>
       <c r="EC2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,133, FALSE)</f>
-        <v>BOSQUE</v>
+        <v>ESTACIONAMIENTO</v>
       </c>
       <c r="ED2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,134, FALSE)</f>
-        <v>RIO TECOLUTLA</v>
+        <v>CHEDRAUI</v>
       </c>
       <c r="EE2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,135, FALSE)</f>
@@ -51200,7 +51850,7 @@
       </c>
       <c r="EI2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,139, FALSE)</f>
-        <v>JOSE ANTONIO SESBASTIAN</v>
+        <v>AXEL SUAREZ PEREZ</v>
       </c>
       <c r="EJ2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,140, FALSE)</f>
@@ -51212,7 +51862,7 @@
       </c>
       <c r="EL2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,142, FALSE)</f>
-        <v>ALEJANDRA OLIVARES RAMIRO</v>
+        <v>ANA KAREN SANCHEZ ROJAS</v>
       </c>
       <c r="EM2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,143, FALSE)</f>
@@ -51222,9 +51872,9 @@
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,144, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="EO2">
+      <c r="EO2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,145, FALSE)</f>
-        <v>0</v>
+        <v>CASSANDRA SANCHEZ PEREZ</v>
       </c>
       <c r="EP2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,146, FALSE)</f>
@@ -51234,9 +51884,9 @@
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,147, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="ER2" t="str">
+      <c r="ER2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,148, FALSE)</f>
-        <v>JESUS SEBASTIAN CASILDA</v>
+        <v>0</v>
       </c>
       <c r="ES2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,149, FALSE)</f>
@@ -51258,9 +51908,9 @@
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,153, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="EX2" t="str">
+      <c r="EX2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,154, FALSE)</f>
-        <v>BENJAMIN GUZMAN</v>
+        <v>0</v>
       </c>
       <c r="EY2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,155, FALSE)</f>
@@ -51282,9 +51932,9 @@
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,159, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="FD2" t="str">
+      <c r="FD2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,160, FALSE)</f>
-        <v>JONHATAN SEBASTIAN REYES</v>
+        <v>0</v>
       </c>
       <c r="FE2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,161, FALSE)</f>
@@ -51308,15 +51958,15 @@
       </c>
       <c r="FJ2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,166, FALSE)</f>
-        <v>GAS LP</v>
+        <v>GAS NATURAL</v>
       </c>
       <c r="FK2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,167, FALSE)</f>
-        <v>1570</v>
+        <v>1000</v>
       </c>
       <c r="FL2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,168, FALSE)</f>
-        <v>0.52333333333333332</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="FM2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,169, FALSE)</f>
@@ -51348,15 +51998,15 @@
       </c>
       <c r="FT2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,176, FALSE)</f>
-        <v>1200</v>
+        <v>300</v>
       </c>
       <c r="FU2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,177, FALSE)</f>
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="FV2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,178, FALSE)</f>
-        <v>0.60333333333333328</v>
+        <v>0.35333333333333333</v>
       </c>
       <c r="FW2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,179, FALSE)</f>

--- a/Inputs/BD.xlsx
+++ b/Inputs/BD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/078e1a455e5c02ce/Documentos/GitHub/Proyecto_PIPC/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3375" documentId="13_ncr:1_{898522BF-B0F8-4888-9748-DC730D5D6CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1877F74F-2F73-4C1C-9C5C-668D9836F629}"/>
+  <xr:revisionPtr revIDLastSave="3376" documentId="13_ncr:1_{898522BF-B0F8-4888-9748-DC730D5D6CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88021988-5382-4A64-AE90-ADB6856E1AB2}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{3F095A75-F066-4695-8672-8D4315F1EF23}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3F095A75-F066-4695-8672-8D4315F1EF23}"/>
   </bookViews>
   <sheets>
     <sheet name="BD" sheetId="1" r:id="rId1"/>
@@ -9052,9 +9052,6 @@
     <t>CAFETERIA, RESTAURANTE</t>
   </si>
   <si>
-    <t>PREPARAR Y SERVIR ALIMENTOS Y BEBIDAS, OFRECIENDO DESAYUNOS, COMIDAS, POSTRES Y CAFÉ EN UN AMBIENTE CÓMODO PARA EL CONSUMO EN EL LUGAR O PARA LLEVAR</t>
-  </si>
-  <si>
     <t>BOULEVARD DE LAS CASCADAS</t>
   </si>
   <si>
@@ -9089,6 +9086,9 @@
   </si>
   <si>
     <t>CASSANDRA SANCHEZ PEREZ</t>
+  </si>
+  <si>
+    <t>PREPARAR Y SERVIR ALIMENTOS Y BEBIDAS, OFRECIENDO DESAYUNOS, COMIDAS, POSTRES Y CAFÉ</t>
   </si>
 </sst>
 </file>
@@ -46379,19 +46379,19 @@
         <v>2828</v>
       </c>
       <c r="H105" t="s">
+        <v>2841</v>
+      </c>
+      <c r="I105" t="s">
         <v>2829</v>
-      </c>
-      <c r="I105" t="s">
-        <v>2830</v>
       </c>
       <c r="J105">
         <v>1301</v>
       </c>
       <c r="K105" t="s">
+        <v>2830</v>
+      </c>
+      <c r="L105" t="s">
         <v>2831</v>
-      </c>
-      <c r="L105" t="s">
-        <v>2832</v>
       </c>
       <c r="M105" t="s">
         <v>1675</v>
@@ -46403,13 +46403,13 @@
         <v>72830</v>
       </c>
       <c r="Q105" s="3" t="s">
-        <v>2833</v>
+        <v>2832</v>
       </c>
       <c r="R105">
         <v>0.5</v>
       </c>
       <c r="S105" t="s">
-        <v>2834</v>
+        <v>2833</v>
       </c>
       <c r="T105" t="s">
         <v>2225</v>
@@ -46445,7 +46445,7 @@
         <v>2825</v>
       </c>
       <c r="AF105" t="s">
-        <v>2835</v>
+        <v>2834</v>
       </c>
       <c r="AG105">
         <v>5</v>
@@ -46478,7 +46478,7 @@
         <v>2267</v>
       </c>
       <c r="AQ105" t="s">
-        <v>2836</v>
+        <v>2835</v>
       </c>
       <c r="AR105" s="4">
         <f t="shared" si="38"/>
@@ -46510,13 +46510,13 @@
         <v>3</v>
       </c>
       <c r="DX105" t="s">
-        <v>2837</v>
+        <v>2836</v>
       </c>
       <c r="DY105">
         <v>2024</v>
       </c>
       <c r="DZ105" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="EA105" t="s">
         <v>2607</v>
@@ -46537,13 +46537,13 @@
         <v>442</v>
       </c>
       <c r="EI105" s="10" t="s">
+        <v>2838</v>
+      </c>
+      <c r="EL105" s="10" t="s">
         <v>2839</v>
       </c>
-      <c r="EL105" s="10" t="s">
+      <c r="EO105" s="10" t="s">
         <v>2840</v>
-      </c>
-      <c r="EO105" s="10" t="s">
-        <v>2841</v>
       </c>
       <c r="FJ105" t="s">
         <v>819</v>
@@ -51326,7 +51326,7 @@
       </c>
       <c r="H2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,8, FALSE)</f>
-        <v>PREPARAR Y SERVIR ALIMENTOS Y BEBIDAS, OFRECIENDO DESAYUNOS, COMIDAS, POSTRES Y CAFÉ EN UN AMBIENTE CÓMODO PARA EL CONSUMO EN EL LUGAR O PARA LLEVAR</v>
+        <v>PREPARAR Y SERVIR ALIMENTOS Y BEBIDAS, OFRECIENDO DESAYUNOS, COMIDAS, POSTRES Y CAFÉ</v>
       </c>
       <c r="I2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,9, FALSE)</f>

--- a/Inputs/BD.xlsx
+++ b/Inputs/BD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/078e1a455e5c02ce/Documentos/GitHub/Proyecto_PIPC/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3376" documentId="13_ncr:1_{898522BF-B0F8-4888-9748-DC730D5D6CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88021988-5382-4A64-AE90-ADB6856E1AB2}"/>
+  <xr:revisionPtr revIDLastSave="3552" documentId="13_ncr:1_{898522BF-B0F8-4888-9748-DC730D5D6CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BB84500-45D8-4789-985F-114D4BBF4110}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3F095A75-F066-4695-8672-8D4315F1EF23}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{3F095A75-F066-4695-8672-8D4315F1EF23}"/>
   </bookViews>
   <sheets>
     <sheet name="BD" sheetId="1" r:id="rId1"/>
@@ -563,7 +563,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8736" uniqueCount="2842">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8820" uniqueCount="2876">
   <si>
     <t>dia</t>
   </si>
@@ -9089,6 +9089,108 @@
   </si>
   <si>
     <t>PREPARAR Y SERVIR ALIMENTOS Y BEBIDAS, OFRECIENDO DESAYUNOS, COMIDAS, POSTRES Y CAFÉ</t>
+  </si>
+  <si>
+    <t>ESTAFETA MEXICANA SA DE CV</t>
+  </si>
+  <si>
+    <t>COP PUEBLA 5 Y 6</t>
+  </si>
+  <si>
+    <t>BODEGA DE DISTRIBUCION</t>
+  </si>
+  <si>
+    <t>RECEPCIÓN, ALMACENAMIENTO, CONTROL DE INVENTARIOS, PREPARACIÓN DE PEDIDOS, EMBALAJE Y DESPACHO DE PRODUCTOS PARA GARANTIZAR UNA ENTREGA EFICIENTE Y PRECISA</t>
+  </si>
+  <si>
+    <t>PROLONGACION 5 DE MAYO</t>
+  </si>
+  <si>
+    <t>NAVE 5 Y 6</t>
+  </si>
+  <si>
+    <t>SAN JERONIMO CALERAS</t>
+  </si>
+  <si>
+    <t>moises.mendez@estafeta.com</t>
+  </si>
+  <si>
+    <t>15 DE DICIEMBRE DE 2001</t>
+  </si>
+  <si>
+    <t>JOSE GILBERTO SANCHEZ ARROYO</t>
+  </si>
+  <si>
+    <t>9:00 A 18:00 Y 9:00 A 13:00 HORAS</t>
+  </si>
+  <si>
+    <t>EN TODA LA BODEGA</t>
+  </si>
+  <si>
+    <t>VIGILANCIA</t>
+  </si>
+  <si>
+    <t>ALMACEN</t>
+  </si>
+  <si>
+    <t>19.09299651391994, -98.21902411782419.09299651391994, -98.2190241178244</t>
+  </si>
+  <si>
+    <t>CALLE</t>
+  </si>
+  <si>
+    <t>MOISES MENDEZ L</t>
+  </si>
+  <si>
+    <t>HUGO MORENO B</t>
+  </si>
+  <si>
+    <t>GUSTAVO CESAR C MENDEZ</t>
+  </si>
+  <si>
+    <t>URIEL TORRES SORIANO</t>
+  </si>
+  <si>
+    <t>JORGE LUIS CALDERON GARCIA</t>
+  </si>
+  <si>
+    <t>DARITEO ALVAREZ</t>
+  </si>
+  <si>
+    <t>BRENDA AZCUI S</t>
+  </si>
+  <si>
+    <t>VICTOR HUGO PEDRAZA MARTEL</t>
+  </si>
+  <si>
+    <t>DANIEL GARCIA FLORES</t>
+  </si>
+  <si>
+    <t>COP PUEBLA</t>
+  </si>
+  <si>
+    <t>EME880309SK5</t>
+  </si>
+  <si>
+    <t>01 DE ENERO DE 1994</t>
+  </si>
+  <si>
+    <t>OFICINA Y ALMACEN</t>
+  </si>
+  <si>
+    <t>BRENDIRE RUTH MUÑOZ PEÑA</t>
+  </si>
+  <si>
+    <t>ANGEL ROGELIO FLORES LOPEZ</t>
+  </si>
+  <si>
+    <t>CARLOS ALBERTO POBLANO CHALTELL</t>
+  </si>
+  <si>
+    <t>LETICIA LANDERO ROSALIANO</t>
+  </si>
+  <si>
+    <t>ARMANDO REFA CEROLIA</t>
   </si>
 </sst>
 </file>
@@ -46593,74 +46695,546 @@
       <c r="A106">
         <v>104</v>
       </c>
+      <c r="B106" t="s">
+        <v>550</v>
+      </c>
+      <c r="C106" t="s">
+        <v>2842</v>
+      </c>
+      <c r="D106" t="s">
+        <v>2843</v>
+      </c>
+      <c r="E106" t="s">
+        <v>2868</v>
+      </c>
+      <c r="G106" t="s">
+        <v>2844</v>
+      </c>
+      <c r="H106" t="s">
+        <v>2845</v>
+      </c>
+      <c r="I106" t="s">
+        <v>2846</v>
+      </c>
+      <c r="J106">
+        <v>44</v>
+      </c>
+      <c r="K106" t="s">
+        <v>2847</v>
+      </c>
+      <c r="L106" t="s">
+        <v>2848</v>
+      </c>
+      <c r="M106" t="s">
+        <v>423</v>
+      </c>
+      <c r="N106" t="s">
+        <v>423</v>
+      </c>
+      <c r="O106">
+        <v>72100</v>
+      </c>
+      <c r="P106">
+        <v>2211898677</v>
+      </c>
+      <c r="Q106" s="3" t="s">
+        <v>2849</v>
+      </c>
+      <c r="R106">
+        <v>23</v>
+      </c>
+      <c r="S106" t="s">
+        <v>2850</v>
+      </c>
+      <c r="T106" t="s">
+        <v>2225</v>
+      </c>
+      <c r="V106">
+        <v>3900</v>
+      </c>
+      <c r="W106">
+        <v>3900</v>
+      </c>
+      <c r="X106">
+        <v>2</v>
+      </c>
+      <c r="Y106">
+        <v>1</v>
+      </c>
+      <c r="Z106">
+        <v>2</v>
+      </c>
+      <c r="AA106">
+        <v>2</v>
+      </c>
+      <c r="AB106">
+        <v>0</v>
+      </c>
+      <c r="AC106">
+        <v>0</v>
+      </c>
+      <c r="AD106" t="s">
+        <v>911</v>
+      </c>
+      <c r="AE106" t="s">
+        <v>2851</v>
+      </c>
+      <c r="AF106" t="s">
+        <v>2851</v>
+      </c>
+      <c r="AG106">
+        <v>40</v>
+      </c>
+      <c r="AH106">
+        <v>0</v>
+      </c>
+      <c r="AI106">
+        <v>30</v>
+      </c>
+      <c r="AJ106">
+        <v>10</v>
+      </c>
+      <c r="AK106">
+        <v>0</v>
+      </c>
+      <c r="AL106">
+        <v>0</v>
+      </c>
+      <c r="AM106">
+        <v>1</v>
+      </c>
+      <c r="AN106">
+        <v>5</v>
+      </c>
+      <c r="AO106">
+        <v>3</v>
+      </c>
+      <c r="AP106" t="s">
+        <v>2397</v>
+      </c>
+      <c r="AQ106" t="s">
+        <v>2852</v>
+      </c>
       <c r="AR106" s="4">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>41</v>
+      </c>
+      <c r="AS106">
+        <v>1</v>
+      </c>
+      <c r="AT106" t="s">
+        <v>2855</v>
+      </c>
+      <c r="AU106">
+        <v>20</v>
+      </c>
+      <c r="AV106" t="s">
+        <v>2853</v>
+      </c>
+      <c r="AW106">
+        <v>19</v>
+      </c>
+      <c r="AX106">
+        <v>1</v>
+      </c>
+      <c r="BE106">
+        <v>1</v>
+      </c>
+      <c r="BF106" t="s">
+        <v>2068</v>
+      </c>
+      <c r="BI106" t="s">
+        <v>2854</v>
+      </c>
+      <c r="CD106">
+        <v>8</v>
+      </c>
+      <c r="CF106">
+        <v>6</v>
+      </c>
+      <c r="CH106">
+        <v>1</v>
+      </c>
+      <c r="CI106">
+        <v>4</v>
       </c>
       <c r="CK106" s="4">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="CL106">
+        <v>2</v>
+      </c>
+      <c r="DW106">
+        <v>3</v>
+      </c>
+      <c r="DX106" t="s">
+        <v>2836</v>
+      </c>
+      <c r="DY106">
+        <v>2024</v>
+      </c>
+      <c r="DZ106" t="s">
+        <v>2856</v>
+      </c>
+      <c r="EA106" t="s">
+        <v>1952</v>
+      </c>
+      <c r="EB106" t="s">
+        <v>2857</v>
+      </c>
+      <c r="EC106" t="s">
+        <v>1952</v>
+      </c>
+      <c r="ED106" t="s">
+        <v>818</v>
+      </c>
+      <c r="EF106" t="s">
+        <v>441</v>
+      </c>
+      <c r="EG106" t="s">
+        <v>442</v>
+      </c>
+      <c r="EI106" s="10" t="s">
+        <v>2858</v>
+      </c>
+      <c r="EL106" s="10" t="s">
+        <v>2866</v>
+      </c>
+      <c r="EO106" s="10" t="s">
+        <v>2859</v>
+      </c>
+      <c r="ER106" s="10" t="s">
+        <v>2860</v>
+      </c>
+      <c r="EU106" s="10" t="s">
+        <v>2861</v>
+      </c>
+      <c r="EX106" s="10" t="s">
+        <v>2862</v>
+      </c>
+      <c r="FA106" s="10" t="s">
+        <v>2863</v>
+      </c>
+      <c r="FD106" s="10" t="s">
+        <v>2864</v>
+      </c>
+      <c r="FG106" s="10" t="s">
+        <v>2865</v>
+      </c>
+      <c r="FJ106" t="s">
+        <v>2109</v>
+      </c>
+      <c r="FK106">
+        <f>10*30</f>
+        <v>300</v>
       </c>
       <c r="FL106" s="4">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="FO106" s="4">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
+      <c r="FP106" t="s">
+        <v>759</v>
+      </c>
+      <c r="FQ106">
+        <v>2000</v>
+      </c>
       <c r="FR106" s="4">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="FS106" t="s">
+        <v>454</v>
+      </c>
+      <c r="FT106">
+        <v>14000</v>
       </c>
       <c r="FU106" s="4">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="FV106" s="4">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>2.0333333333333332</v>
       </c>
       <c r="FW106" s="4" t="str">
         <f t="shared" si="27"/>
-        <v>ORDINARIO</v>
+        <v>ALTO</v>
       </c>
     </row>
     <row r="107" spans="1:179" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>105</v>
       </c>
+      <c r="B107" t="s">
+        <v>550</v>
+      </c>
+      <c r="C107" t="s">
+        <v>2842</v>
+      </c>
+      <c r="D107" t="s">
+        <v>2867</v>
+      </c>
+      <c r="E107" t="s">
+        <v>2868</v>
+      </c>
+      <c r="G107" t="s">
+        <v>2844</v>
+      </c>
+      <c r="H107" t="s">
+        <v>2845</v>
+      </c>
+      <c r="I107" t="s">
+        <v>2846</v>
+      </c>
+      <c r="J107">
+        <v>44</v>
+      </c>
+      <c r="L107" t="s">
+        <v>2848</v>
+      </c>
+      <c r="M107" t="s">
+        <v>423</v>
+      </c>
+      <c r="N107" t="s">
+        <v>423</v>
+      </c>
+      <c r="O107">
+        <v>72100</v>
+      </c>
+      <c r="P107">
+        <v>2211898677</v>
+      </c>
+      <c r="Q107" s="3" t="s">
+        <v>2849</v>
+      </c>
+      <c r="R107">
+        <v>30</v>
+      </c>
+      <c r="S107" t="s">
+        <v>2869</v>
+      </c>
+      <c r="T107" t="s">
+        <v>2225</v>
+      </c>
+      <c r="V107">
+        <v>10700</v>
+      </c>
+      <c r="W107">
+        <v>10700</v>
+      </c>
+      <c r="X107">
+        <v>1</v>
+      </c>
+      <c r="Y107">
+        <v>2</v>
+      </c>
+      <c r="Z107">
+        <v>2</v>
+      </c>
+      <c r="AA107">
+        <v>2</v>
+      </c>
+      <c r="AB107">
+        <v>1</v>
+      </c>
+      <c r="AC107">
+        <v>0</v>
+      </c>
+      <c r="AD107" t="s">
+        <v>911</v>
+      </c>
+      <c r="AE107" t="s">
+        <v>2851</v>
+      </c>
+      <c r="AF107" t="s">
+        <v>2851</v>
+      </c>
+      <c r="AG107">
+        <v>60</v>
+      </c>
+      <c r="AH107">
+        <v>2</v>
+      </c>
+      <c r="AI107">
+        <v>40</v>
+      </c>
+      <c r="AJ107">
+        <v>20</v>
+      </c>
+      <c r="AK107">
+        <v>2</v>
+      </c>
+      <c r="AL107">
+        <v>0</v>
+      </c>
+      <c r="AM107">
+        <v>1</v>
+      </c>
+      <c r="AN107">
+        <v>40</v>
+      </c>
+      <c r="AO107">
+        <v>5</v>
+      </c>
+      <c r="AP107" t="s">
+        <v>2397</v>
+      </c>
+      <c r="AQ107" t="s">
+        <v>2852</v>
+      </c>
       <c r="AR107" s="4">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>45</v>
+      </c>
+      <c r="AS107">
+        <v>2</v>
+      </c>
+      <c r="AT107" t="s">
+        <v>2870</v>
+      </c>
+      <c r="AU107">
+        <v>24</v>
+      </c>
+      <c r="AV107" t="s">
+        <v>2853</v>
+      </c>
+      <c r="AW107">
+        <v>17</v>
+      </c>
+      <c r="AX107">
+        <v>6</v>
+      </c>
+      <c r="BE107">
+        <v>1</v>
+      </c>
+      <c r="BF107" t="s">
+        <v>2269</v>
+      </c>
+      <c r="BI107" t="s">
+        <v>1952</v>
+      </c>
+      <c r="CD107">
+        <v>13</v>
+      </c>
+      <c r="CF107">
+        <v>2</v>
+      </c>
+      <c r="CH107">
+        <v>1</v>
+      </c>
+      <c r="CI107">
+        <v>2</v>
+      </c>
+      <c r="CJ107">
+        <v>1</v>
       </c>
       <c r="CK107" s="4">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
+      <c r="DW107">
+        <v>3</v>
+      </c>
+      <c r="DX107" t="s">
+        <v>2836</v>
+      </c>
+      <c r="DY107">
+        <v>2024</v>
+      </c>
+      <c r="DZ107" t="s">
+        <v>2856</v>
+      </c>
+      <c r="EA107" t="s">
+        <v>1952</v>
+      </c>
+      <c r="EB107" t="s">
+        <v>2857</v>
+      </c>
+      <c r="EC107" t="s">
+        <v>1952</v>
+      </c>
+      <c r="ED107" t="s">
+        <v>818</v>
+      </c>
+      <c r="EF107" t="s">
+        <v>441</v>
+      </c>
+      <c r="EG107" t="s">
+        <v>442</v>
+      </c>
+      <c r="EI107" s="10" t="s">
+        <v>2858</v>
+      </c>
+      <c r="EL107" s="10" t="s">
+        <v>2866</v>
+      </c>
+      <c r="EO107" s="10" t="s">
+        <v>2871</v>
+      </c>
+      <c r="ER107" s="10" t="s">
+        <v>2860</v>
+      </c>
+      <c r="EU107" s="10" t="s">
+        <v>2872</v>
+      </c>
+      <c r="EX107" s="10" t="s">
+        <v>2862</v>
+      </c>
+      <c r="FA107" s="10" t="s">
+        <v>2873</v>
+      </c>
+      <c r="FD107" s="10" t="s">
+        <v>2874</v>
+      </c>
+      <c r="FG107" s="10" t="s">
+        <v>2875</v>
+      </c>
+      <c r="FK107">
+        <v>0</v>
+      </c>
       <c r="FL107" s="4">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
+      <c r="FM107" t="s">
+        <v>453</v>
+      </c>
+      <c r="FN107">
+        <v>8000</v>
+      </c>
       <c r="FO107" s="4">
         <f t="shared" si="31"/>
+        <v>5.7142857142857144</v>
+      </c>
+      <c r="FQ107">
         <v>0</v>
       </c>
       <c r="FR107" s="4">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
+      <c r="FS107" t="s">
+        <v>454</v>
+      </c>
+      <c r="FT107">
+        <v>14000</v>
+      </c>
       <c r="FU107" s="4">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="FV107" s="4">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>6.647619047619048</v>
       </c>
       <c r="FW107" s="4" t="str">
         <f t="shared" si="27"/>
-        <v>ORDINARIO</v>
+        <v>ALTO</v>
       </c>
     </row>
     <row r="108" spans="1:179" x14ac:dyDescent="0.3">
@@ -50252,7 +50826,7 @@
       <formula>#REF!=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
+  <dataValidations disablePrompts="1" count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B78 B80:B201" xr:uid="{41C0D522-5D90-43F5-9DB3-E0F81FDE0774}">
       <formula1>"BANCO, BBVA, COMPARTAMOS, DHL, GASOLINERA, GENERAL, GDL, UVP"</formula1>
     </dataValidation>
@@ -50325,17 +50899,19 @@
     <hyperlink ref="Q100" r:id="rId62" xr:uid="{AEF7422C-FE06-4678-BB38-292B3DC8A973}"/>
     <hyperlink ref="Q101" r:id="rId63" xr:uid="{3EEC51D1-1175-427A-AD1B-B2FA33DAE2FB}"/>
     <hyperlink ref="Q105" r:id="rId64" xr:uid="{6E0D60EF-9E87-419D-BDEC-FDC083CBA1B6}"/>
+    <hyperlink ref="Q106" r:id="rId65" xr:uid="{A89F835C-908F-45D3-815D-C53FF1765D6A}"/>
+    <hyperlink ref="Q107" r:id="rId66" xr:uid="{A5DC3454-5E72-40B8-8913-C1542AF6DAB2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967294" verticalDpi="0" r:id="rId65"/>
-  <drawing r:id="rId66"/>
-  <legacyDrawing r:id="rId67"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967294" verticalDpi="0" r:id="rId67"/>
+  <drawing r:id="rId68"/>
+  <legacyDrawing r:id="rId69"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x14">
       <controls>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1025" r:id="rId68" name="Spinner 1">
+            <control shapeId="1025" r:id="rId70" name="Spinner 1">
               <controlPr defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>

--- a/Inputs/BD.xlsx
+++ b/Inputs/BD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/078e1a455e5c02ce/Documentos/GitHub/Proyecto_PIPC/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3552" documentId="13_ncr:1_{898522BF-B0F8-4888-9748-DC730D5D6CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BB84500-45D8-4789-985F-114D4BBF4110}"/>
+  <xr:revisionPtr revIDLastSave="3555" documentId="13_ncr:1_{898522BF-B0F8-4888-9748-DC730D5D6CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7FEF42E-8519-436C-ACEB-7C41B76787B2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{3F095A75-F066-4695-8672-8D4315F1EF23}"/>
   </bookViews>
@@ -563,7 +563,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8820" uniqueCount="2876">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8820" uniqueCount="2877">
   <si>
     <t>dia</t>
   </si>
@@ -9191,6 +9191,9 @@
   </si>
   <si>
     <t>ARMANDO REFA CEROLIA</t>
+  </si>
+  <si>
+    <t>19.09299651391994, -98.2190241178244</t>
   </si>
 </sst>
 </file>
@@ -9877,7 +9880,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="26" fmlaLink="$A$1" max="30000" min="1" page="10" val="103"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="26" fmlaLink="$A$1" max="30000" min="1" page="10" val="105"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10273,7 +10276,7 @@
   <sheetData>
     <row r="1" spans="1:322" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="DS1" t="s">
         <v>1968</v>
@@ -47147,7 +47150,7 @@
         <v>2024</v>
       </c>
       <c r="DZ107" t="s">
-        <v>2856</v>
+        <v>2876</v>
       </c>
       <c r="EA107" t="s">
         <v>1952</v>
@@ -50945,7 +50948,7 @@
     <row r="1" spans="1:310" x14ac:dyDescent="0.3">
       <c r="A1">
         <f>+BD!A1</f>
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B1" t="s">
         <v>133</v>
@@ -51882,15 +51885,15 @@
       </c>
       <c r="C2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,3, FALSE)</f>
-        <v>EFREN CONTRERAS ZAFRA</v>
+        <v>ESTAFETA MEXICANA SA DE CV</v>
       </c>
       <c r="D2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,4, FALSE)</f>
-        <v>DOMINICA 19</v>
+        <v>COP PUEBLA</v>
       </c>
       <c r="E2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,5, FALSE)</f>
-        <v>COZE850822S40</v>
+        <v>EME880309SK5</v>
       </c>
       <c r="F2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,6, FALSE)</f>
@@ -51898,31 +51901,31 @@
       </c>
       <c r="G2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,7, FALSE)</f>
-        <v>CAFETERIA, RESTAURANTE</v>
+        <v>BODEGA DE DISTRIBUCION</v>
       </c>
       <c r="H2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,8, FALSE)</f>
-        <v>PREPARAR Y SERVIR ALIMENTOS Y BEBIDAS, OFRECIENDO DESAYUNOS, COMIDAS, POSTRES Y CAFÉ</v>
+        <v>RECEPCIÓN, ALMACENAMIENTO, CONTROL DE INVENTARIOS, PREPARACIÓN DE PEDIDOS, EMBALAJE Y DESPACHO DE PRODUCTOS PARA GARANTIZAR UNA ENTREGA EFICIENTE Y PRECISA</v>
       </c>
       <c r="I2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,9, FALSE)</f>
-        <v>BOULEVARD DE LAS CASCADAS</v>
+        <v>PROLONGACION 5 DE MAYO</v>
       </c>
       <c r="J2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,10, FALSE)</f>
-        <v>1301</v>
-      </c>
-      <c r="K2" t="str">
+        <v>44</v>
+      </c>
+      <c r="K2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,11, FALSE)</f>
-        <v>Q01</v>
+        <v>0</v>
       </c>
       <c r="L2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,12, FALSE)</f>
-        <v>LOMAS DE ANGELOPOLIS III</v>
+        <v>SAN JERONIMO CALERAS</v>
       </c>
       <c r="M2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,13, FALSE)</f>
-        <v>SANTA CLARA OCOYUCAN</v>
+        <v>PUEBLA</v>
       </c>
       <c r="N2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,14, FALSE)</f>
@@ -51930,23 +51933,23 @@
       </c>
       <c r="O2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,15, FALSE)</f>
-        <v>72830</v>
+        <v>72100</v>
       </c>
       <c r="P2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,16, FALSE)</f>
-        <v>0</v>
+        <v>2211898677</v>
       </c>
       <c r="Q2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,17, FALSE)</f>
-        <v>administracion@dominica19.com</v>
+        <v>moises.mendez@estafeta.com</v>
       </c>
       <c r="R2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,18, FALSE)</f>
-        <v>0.5</v>
+        <v>30</v>
       </c>
       <c r="S2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,19, FALSE)</f>
-        <v>DICIEMBRE DE 2024</v>
+        <v>01 DE ENERO DE 1994</v>
       </c>
       <c r="T2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,20, FALSE)</f>
@@ -51958,11 +51961,11 @@
       </c>
       <c r="V2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,22, FALSE)</f>
-        <v>220</v>
+        <v>10700</v>
       </c>
       <c r="W2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,23, FALSE)</f>
-        <v>70</v>
+        <v>10700</v>
       </c>
       <c r="X2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,24, FALSE)</f>
@@ -51970,19 +51973,19 @@
       </c>
       <c r="Y2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,25, FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,26, FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,27, FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,28, FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,29, FALSE)</f>
@@ -51990,35 +51993,35 @@
       </c>
       <c r="AD2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,30, FALSE)</f>
-        <v>20 CAJONES</v>
+        <v>10 CAJONES</v>
       </c>
       <c r="AE2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,31, FALSE)</f>
-        <v>EFREN CONTRERAS ZAFRA</v>
+        <v>JOSE GILBERTO SANCHEZ ARROYO</v>
       </c>
       <c r="AF2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,32, FALSE)</f>
-        <v>JOSE LUIS RODOLFO RODRIGUEZ</v>
+        <v>JOSE GILBERTO SANCHEZ ARROYO</v>
       </c>
       <c r="AG2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,33, FALSE)</f>
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="AH2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,34, FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,35, FALSE)</f>
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="AJ2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,36, FALSE)</f>
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="AK2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,37, FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,38, FALSE)</f>
@@ -52026,51 +52029,51 @@
       </c>
       <c r="AM2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,39, FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,40, FALSE)</f>
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AO2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,41, FALSE)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AP2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,42, FALSE)</f>
-        <v>LUNES A DOMINGO</v>
+        <v>LUNES A VIERNES Y SABADO</v>
       </c>
       <c r="AQ2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,43, FALSE)</f>
-        <v>8:00 A 23:00 HORAS</v>
+        <v>9:00 A 18:00 Y 9:00 A 13:00 HORAS</v>
       </c>
       <c r="AR2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,44, FALSE)</f>
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="AS2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,45, FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,46, FALSE)</f>
-        <v>COCINA</v>
+        <v>OFICINA Y ALMACEN</v>
       </c>
       <c r="AU2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,47, FALSE)</f>
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="AV2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,48, FALSE)</f>
-        <v>MOSTRADOR, ALMACEN</v>
+        <v>EN TODA LA BODEGA</v>
       </c>
       <c r="AW2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,49, FALSE)</f>
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="AX2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,50, FALSE)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AY2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,51, FALSE)</f>
@@ -52098,11 +52101,11 @@
       </c>
       <c r="BE2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,57, FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="BF2">
+        <v>1</v>
+      </c>
+      <c r="BF2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,58, FALSE)</f>
-        <v>0</v>
+        <v>ALARMA</v>
       </c>
       <c r="BG2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,59, FALSE)</f>
@@ -52112,9 +52115,9 @@
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,60, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="BI2">
+      <c r="BI2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,61, FALSE)</f>
-        <v>0</v>
+        <v>BODEGA</v>
       </c>
       <c r="BJ2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,62, FALSE)</f>
@@ -52198,7 +52201,7 @@
       </c>
       <c r="CD2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,82, FALSE)</f>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="CE2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,83, FALSE)</f>
@@ -52206,7 +52209,7 @@
       </c>
       <c r="CF2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,84, FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CG2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,85, FALSE)</f>
@@ -52214,11 +52217,11 @@
       </c>
       <c r="CH2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,86, FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CI2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,87, FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CJ2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,88, FALSE)</f>
@@ -52390,23 +52393,23 @@
       </c>
       <c r="DZ2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,130, FALSE)</f>
-        <v>18.970035879601955, -98.2852424490102</v>
+        <v>19.09299651391994, -98.2190241178244</v>
       </c>
       <c r="EA2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,131, FALSE)</f>
-        <v>LOCAL COMERCIAL</v>
+        <v>BODEGA</v>
       </c>
       <c r="EB2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,132, FALSE)</f>
-        <v>ESTACIONAMIENTO</v>
+        <v>CALLE</v>
       </c>
       <c r="EC2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,133, FALSE)</f>
-        <v>ESTACIONAMIENTO</v>
+        <v>BODEGA</v>
       </c>
       <c r="ED2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,134, FALSE)</f>
-        <v>CHEDRAUI</v>
+        <v>CASA HABITACION</v>
       </c>
       <c r="EE2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,135, FALSE)</f>
@@ -52426,7 +52429,7 @@
       </c>
       <c r="EI2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,139, FALSE)</f>
-        <v>AXEL SUAREZ PEREZ</v>
+        <v>MOISES MENDEZ L</v>
       </c>
       <c r="EJ2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,140, FALSE)</f>
@@ -52438,7 +52441,7 @@
       </c>
       <c r="EL2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,142, FALSE)</f>
-        <v>ANA KAREN SANCHEZ ROJAS</v>
+        <v>DANIEL GARCIA FLORES</v>
       </c>
       <c r="EM2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,143, FALSE)</f>
@@ -52450,7 +52453,7 @@
       </c>
       <c r="EO2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,145, FALSE)</f>
-        <v>CASSANDRA SANCHEZ PEREZ</v>
+        <v>BRENDIRE RUTH MUÑOZ PEÑA</v>
       </c>
       <c r="EP2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,146, FALSE)</f>
@@ -52460,9 +52463,9 @@
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,147, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="ER2">
+      <c r="ER2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,148, FALSE)</f>
-        <v>0</v>
+        <v>GUSTAVO CESAR C MENDEZ</v>
       </c>
       <c r="ES2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,149, FALSE)</f>
@@ -52472,9 +52475,9 @@
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,150, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="EU2">
+      <c r="EU2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,151, FALSE)</f>
-        <v>0</v>
+        <v>ANGEL ROGELIO FLORES LOPEZ</v>
       </c>
       <c r="EV2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,152, FALSE)</f>
@@ -52484,9 +52487,9 @@
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,153, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="EX2">
+      <c r="EX2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,154, FALSE)</f>
-        <v>0</v>
+        <v>JORGE LUIS CALDERON GARCIA</v>
       </c>
       <c r="EY2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,155, FALSE)</f>
@@ -52496,9 +52499,9 @@
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,156, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="FA2">
+      <c r="FA2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,157, FALSE)</f>
-        <v>0</v>
+        <v>CARLOS ALBERTO POBLANO CHALTELL</v>
       </c>
       <c r="FB2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,158, FALSE)</f>
@@ -52508,9 +52511,9 @@
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,159, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="FD2">
+      <c r="FD2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,160, FALSE)</f>
-        <v>0</v>
+        <v>LETICIA LANDERO ROSALIANO</v>
       </c>
       <c r="FE2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,161, FALSE)</f>
@@ -52520,9 +52523,9 @@
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,162, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="FG2">
+      <c r="FG2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,163, FALSE)</f>
-        <v>0</v>
+        <v>ARMANDO REFA CEROLIA</v>
       </c>
       <c r="FH2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,164, FALSE)</f>
@@ -52532,29 +52535,29 @@
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,165, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="FJ2" t="str">
+      <c r="FJ2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,166, FALSE)</f>
-        <v>GAS NATURAL</v>
+        <v>0</v>
       </c>
       <c r="FK2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,167, FALSE)</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="FL2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,168, FALSE)</f>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="FM2">
+        <v>0</v>
+      </c>
+      <c r="FM2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,169, FALSE)</f>
-        <v>0</v>
+        <v>GASOLINA</v>
       </c>
       <c r="FN2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,170, FALSE)</f>
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="FO2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,171, FALSE)</f>
-        <v>0</v>
+        <v>5.7142857142857144</v>
       </c>
       <c r="FP2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,172, FALSE)</f>
@@ -52574,19 +52577,19 @@
       </c>
       <c r="FT2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,176, FALSE)</f>
-        <v>300</v>
+        <v>14000</v>
       </c>
       <c r="FU2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,177, FALSE)</f>
-        <v>0.02</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="FV2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,178, FALSE)</f>
-        <v>0.35333333333333333</v>
+        <v>6.647619047619048</v>
       </c>
       <c r="FW2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,179, FALSE)</f>
-        <v>ORDINARIO</v>
+        <v>ALTO</v>
       </c>
       <c r="FX2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,180, FALSE)</f>

--- a/Inputs/BD.xlsx
+++ b/Inputs/BD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/078e1a455e5c02ce/Documentos/GitHub/Proyecto_PIPC/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="629" documentId="13_ncr:1_{898522BF-B0F8-4888-9748-DC730D5D6CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0EC7853-F432-4F17-9836-8E6DA938593D}"/>
+  <xr:revisionPtr revIDLastSave="7293" documentId="13_ncr:1_{898522BF-B0F8-4888-9748-DC730D5D6CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0B91A92-70DB-4C92-9220-CD54A55EFFE4}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3F095A75-F066-4695-8672-8D4315F1EF23}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="2" xr2:uid="{3F095A75-F066-4695-8672-8D4315F1EF23}"/>
   </bookViews>
   <sheets>
     <sheet name="BD" sheetId="1" r:id="rId1"/>

--- a/Inputs/BD.xlsx
+++ b/Inputs/BD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/078e1a455e5c02ce/Documentos/GitHub/Proyecto_PIPC/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7527" documentId="13_ncr:1_{898522BF-B0F8-4888-9748-DC730D5D6CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF5108A7-6FAE-41B1-A023-7BA70D2021FD}"/>
+  <xr:revisionPtr revIDLastSave="7535" documentId="13_ncr:1_{898522BF-B0F8-4888-9748-DC730D5D6CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4BDAC0D-D39F-43A9-B1E9-FE93C46A5A74}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3F095A75-F066-4695-8672-8D4315F1EF23}"/>
   </bookViews>
@@ -11437,7 +11437,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
@@ -11460,8 +11460,6 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="4" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -11476,17 +11474,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -11875,6 +11862,17 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -15825,7 +15823,7 @@
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" t="s">
         <v>1039</v>
       </c>
       <c r="C13" t="s">
@@ -16237,7 +16235,7 @@
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" t="s">
         <v>1007</v>
       </c>
       <c r="C14" t="s">
@@ -16760,7 +16758,7 @@
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="22" t="s">
+      <c r="B15" t="s">
         <v>1665</v>
       </c>
       <c r="C15" t="s">
@@ -17195,7 +17193,7 @@
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" t="s">
         <v>1365</v>
       </c>
       <c r="C16" t="s">
@@ -17631,7 +17629,7 @@
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="22" t="s">
+      <c r="B17" t="s">
         <v>1082</v>
       </c>
       <c r="C17" t="s">
@@ -18094,7 +18092,7 @@
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="22" t="s">
+      <c r="B18" t="s">
         <v>1180</v>
       </c>
       <c r="C18" t="s">
@@ -18531,7 +18529,7 @@
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" s="22" t="s">
+      <c r="B19" t="s">
         <v>1564</v>
       </c>
       <c r="C19" t="s">
@@ -18959,7 +18957,7 @@
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" s="22" t="s">
+      <c r="B20" t="s">
         <v>1008</v>
       </c>
       <c r="C20" t="s">
@@ -19392,7 +19390,7 @@
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" s="22" t="s">
+      <c r="B21" t="s">
         <v>1411</v>
       </c>
       <c r="C21" t="s">
@@ -19843,7 +19841,7 @@
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" s="22" t="s">
+      <c r="B22" t="s">
         <v>1646</v>
       </c>
       <c r="C22" t="s">
@@ -20376,7 +20374,7 @@
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="22" t="s">
+      <c r="B23" t="s">
         <v>1522</v>
       </c>
       <c r="C23" t="s">
@@ -20916,7 +20914,7 @@
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" s="22" t="s">
+      <c r="B24" t="s">
         <v>1817</v>
       </c>
       <c r="C24" t="s">
@@ -21405,7 +21403,7 @@
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="22" t="s">
+      <c r="B25" t="s">
         <v>1009</v>
       </c>
       <c r="C25" t="s">
@@ -21921,7 +21919,7 @@
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="22" t="s">
+      <c r="B26" t="s">
         <v>1003</v>
       </c>
       <c r="C26" t="s">
@@ -22469,7 +22467,7 @@
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" s="22" t="s">
+      <c r="B27" t="s">
         <v>1386</v>
       </c>
       <c r="C27" t="s">
@@ -22990,7 +22988,7 @@
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" s="22" t="s">
+      <c r="B28" t="s">
         <v>1104</v>
       </c>
       <c r="C28" t="s">
@@ -23541,7 +23539,7 @@
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" s="22" t="s">
+      <c r="B29" t="s">
         <v>1202</v>
       </c>
       <c r="C29" t="s">
@@ -24074,7 +24072,7 @@
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" s="22" t="s">
+      <c r="B30" t="s">
         <v>1308</v>
       </c>
       <c r="C30" t="s">
@@ -24601,7 +24599,7 @@
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" s="22" t="s">
+      <c r="B31" t="s">
         <v>1011</v>
       </c>
       <c r="C31" t="s">
@@ -25140,7 +25138,7 @@
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" s="22" t="s">
+      <c r="B32" t="s">
         <v>1280</v>
       </c>
       <c r="C32" t="s">
@@ -25667,7 +25665,7 @@
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="B33" t="s">
         <v>802</v>
       </c>
       <c r="C33" t="s">
@@ -26308,7 +26306,7 @@
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" s="22" t="s">
+      <c r="B34" t="s">
         <v>1481</v>
       </c>
       <c r="C34" t="s">
@@ -26913,7 +26911,7 @@
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" s="22" t="s">
+      <c r="B35" t="s">
         <v>1059</v>
       </c>
       <c r="C35" t="s">
@@ -27437,7 +27435,7 @@
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" s="22" t="s">
+      <c r="B36" t="s">
         <v>1010</v>
       </c>
       <c r="C36" t="s">
@@ -27958,7 +27956,7 @@
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" s="22" t="s">
+      <c r="B37" t="s">
         <v>1458</v>
       </c>
       <c r="C37" t="s">
@@ -28476,7 +28474,7 @@
       <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" s="22" t="s">
+      <c r="B38" t="s">
         <v>1155</v>
       </c>
       <c r="C38" t="s">
@@ -29000,7 +28998,7 @@
       <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" s="22" t="s">
+      <c r="B39" t="s">
         <v>1132</v>
       </c>
       <c r="C39" t="s">
@@ -29515,7 +29513,7 @@
       <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" s="22" t="s">
+      <c r="B40" t="s">
         <v>1344</v>
       </c>
       <c r="C40" t="s">
@@ -30021,7 +30019,7 @@
       <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" s="22" t="s">
+      <c r="B41" t="s">
         <v>1433</v>
       </c>
       <c r="C41" t="s">
@@ -30536,7 +30534,7 @@
       <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" s="22" t="s">
+      <c r="B42" t="s">
         <v>1225</v>
       </c>
       <c r="C42" t="s">
@@ -31096,7 +31094,7 @@
       <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" s="22" t="s">
+      <c r="B43" t="s">
         <v>1829</v>
       </c>
       <c r="C43" t="s">
@@ -31296,7 +31294,7 @@
       <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44" s="22" t="s">
+      <c r="B44" t="s">
         <v>1853</v>
       </c>
       <c r="C44" t="s">
@@ -31493,7 +31491,7 @@
       <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" s="22" t="s">
+      <c r="B45" t="s">
         <v>1873</v>
       </c>
       <c r="C45" t="s">
@@ -31699,7 +31697,7 @@
       <c r="A46">
         <v>45</v>
       </c>
-      <c r="B46" s="22" t="s">
+      <c r="B46" t="s">
         <v>1898</v>
       </c>
       <c r="C46" t="s">
@@ -31794,7 +31792,7 @@
       <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47" s="22" t="s">
+      <c r="B47" t="s">
         <v>1913</v>
       </c>
       <c r="C47" t="s">
@@ -31844,7 +31842,7 @@
       <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48" s="22" t="s">
+      <c r="B48" t="s">
         <v>1917</v>
       </c>
       <c r="C48" t="s">
@@ -31894,7 +31892,7 @@
       <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49" s="22" t="s">
+      <c r="B49" t="s">
         <v>1921</v>
       </c>
       <c r="C49" t="s">
@@ -31944,7 +31942,7 @@
       <c r="A50">
         <v>49</v>
       </c>
-      <c r="B50" s="22" t="s">
+      <c r="B50" t="s">
         <v>1924</v>
       </c>
       <c r="C50" t="s">
@@ -32192,7 +32190,7 @@
       <c r="A51">
         <v>50</v>
       </c>
-      <c r="B51" s="22" t="s">
+      <c r="B51" t="s">
         <v>1946</v>
       </c>
       <c r="C51" t="s">
@@ -32242,7 +32240,7 @@
       <c r="A52">
         <v>51</v>
       </c>
-      <c r="B52" s="22" t="s">
+      <c r="B52" t="s">
         <v>1949</v>
       </c>
       <c r="C52" t="s">
@@ -32292,7 +32290,7 @@
       <c r="A53">
         <v>52</v>
       </c>
-      <c r="B53" s="22" t="s">
+      <c r="B53" t="s">
         <v>1952</v>
       </c>
       <c r="C53" t="s">
@@ -32342,7 +32340,7 @@
       <c r="A54">
         <v>53</v>
       </c>
-      <c r="B54" s="22" t="s">
+      <c r="B54" t="s">
         <v>1975</v>
       </c>
       <c r="C54" t="s">
@@ -32613,9 +32611,8 @@
       <c r="FD54" t="s">
         <v>442</v>
       </c>
-      <c r="FE54" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE54">
+        <v>4200</v>
       </c>
       <c r="FG54" t="s">
         <v>1975</v>
@@ -32625,7 +32622,7 @@
       <c r="A55">
         <v>54</v>
       </c>
-      <c r="B55" s="22" t="s">
+      <c r="B55" t="s">
         <v>1976</v>
       </c>
       <c r="C55" t="s">
@@ -32883,9 +32880,8 @@
       <c r="FD55" t="s">
         <v>442</v>
       </c>
-      <c r="FE55" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE55">
+        <v>2460</v>
       </c>
       <c r="FG55" t="s">
         <v>1976</v>
@@ -32898,7 +32894,7 @@
       <c r="A56">
         <v>55</v>
       </c>
-      <c r="B56" s="22" t="s">
+      <c r="B56" t="s">
         <v>1977</v>
       </c>
       <c r="C56" t="s">
@@ -33150,9 +33146,8 @@
       <c r="FD56" t="s">
         <v>442</v>
       </c>
-      <c r="FE56" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE56">
+        <v>360</v>
       </c>
       <c r="FG56" t="s">
         <v>1977</v>
@@ -33162,7 +33157,7 @@
       <c r="A57">
         <v>56</v>
       </c>
-      <c r="B57" s="22" t="s">
+      <c r="B57" t="s">
         <v>1978</v>
       </c>
       <c r="C57" t="s">
@@ -33417,9 +33412,8 @@
       <c r="FD57" t="s">
         <v>442</v>
       </c>
-      <c r="FE57" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE57">
+        <v>3840</v>
       </c>
       <c r="FG57" t="s">
         <v>1978</v>
@@ -33429,7 +33423,7 @@
       <c r="A58">
         <v>57</v>
       </c>
-      <c r="B58" s="22" t="s">
+      <c r="B58" t="s">
         <v>1979</v>
       </c>
       <c r="C58" t="s">
@@ -33660,9 +33654,8 @@
       <c r="FD58" t="s">
         <v>442</v>
       </c>
-      <c r="FE58" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE58">
+        <v>360</v>
       </c>
       <c r="FG58" t="s">
         <v>1979</v>
@@ -33675,7 +33668,7 @@
       <c r="A59">
         <v>58</v>
       </c>
-      <c r="B59" s="22" t="s">
+      <c r="B59" t="s">
         <v>1980</v>
       </c>
       <c r="C59" t="s">
@@ -33921,9 +33914,8 @@
       <c r="FD59" t="s">
         <v>442</v>
       </c>
-      <c r="FE59" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE59">
+        <v>960</v>
       </c>
       <c r="FG59" t="s">
         <v>1980</v>
@@ -33936,7 +33928,7 @@
       <c r="A60">
         <v>59</v>
       </c>
-      <c r="B60" s="22" t="s">
+      <c r="B60" t="s">
         <v>1981</v>
       </c>
       <c r="C60" t="s">
@@ -34182,9 +34174,8 @@
       <c r="FD60" t="s">
         <v>442</v>
       </c>
-      <c r="FE60" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE60">
+        <v>660</v>
       </c>
       <c r="FG60" t="s">
         <v>1981</v>
@@ -34194,7 +34185,7 @@
       <c r="A61">
         <v>60</v>
       </c>
-      <c r="B61" s="22" t="s">
+      <c r="B61" t="s">
         <v>1982</v>
       </c>
       <c r="C61" t="s">
@@ -34443,9 +34434,8 @@
       <c r="FD61" t="s">
         <v>442</v>
       </c>
-      <c r="FE61" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE61">
+        <v>2520</v>
       </c>
       <c r="FG61" t="s">
         <v>1982</v>
@@ -34455,7 +34445,7 @@
       <c r="A62">
         <v>61</v>
       </c>
-      <c r="B62" s="22" t="s">
+      <c r="B62" t="s">
         <v>2100</v>
       </c>
       <c r="C62" t="s">
@@ -34671,16 +34661,15 @@
       <c r="FD62" t="s">
         <v>442</v>
       </c>
-      <c r="FE62" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE62">
+        <v>1800</v>
       </c>
     </row>
     <row r="63" spans="1:174" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>62</v>
       </c>
-      <c r="B63" s="22" t="s">
+      <c r="B63" t="s">
         <v>2283</v>
       </c>
       <c r="C63" t="s">
@@ -34860,16 +34849,15 @@
       <c r="FD63" t="s">
         <v>442</v>
       </c>
-      <c r="FE63" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE63">
+        <v>120</v>
       </c>
     </row>
     <row r="64" spans="1:174" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>63</v>
       </c>
-      <c r="B64" s="22" t="s">
+      <c r="B64" t="s">
         <v>2284</v>
       </c>
       <c r="C64" t="s">
@@ -35046,16 +35034,15 @@
       <c r="FD64" t="s">
         <v>442</v>
       </c>
-      <c r="FE64" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE64">
+        <v>120</v>
       </c>
     </row>
     <row r="65" spans="1:177" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>64</v>
       </c>
-      <c r="B65" s="22" t="s">
+      <c r="B65" t="s">
         <v>2285</v>
       </c>
       <c r="C65" t="s">
@@ -35247,16 +35234,15 @@
       <c r="FD65" t="s">
         <v>442</v>
       </c>
-      <c r="FE65" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE65">
+        <v>60</v>
       </c>
     </row>
     <row r="66" spans="1:177" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>65</v>
       </c>
-      <c r="B66" s="22" t="s">
+      <c r="B66" t="s">
         <v>2286</v>
       </c>
       <c r="C66" t="s">
@@ -35445,16 +35431,15 @@
       <c r="FD66" t="s">
         <v>442</v>
       </c>
-      <c r="FE66" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE66">
+        <v>60</v>
       </c>
     </row>
     <row r="67" spans="1:177" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>66</v>
       </c>
-      <c r="B67" s="22" t="s">
+      <c r="B67" t="s">
         <v>2287</v>
       </c>
       <c r="C67" t="s">
@@ -35643,16 +35628,15 @@
       <c r="FD67" t="s">
         <v>442</v>
       </c>
-      <c r="FE67" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE67">
+        <v>60</v>
       </c>
     </row>
     <row r="68" spans="1:177" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>67</v>
       </c>
-      <c r="B68" s="22" t="s">
+      <c r="B68" t="s">
         <v>2288</v>
       </c>
       <c r="C68" t="s">
@@ -35850,16 +35834,15 @@
       <c r="FD68" t="s">
         <v>442</v>
       </c>
-      <c r="FE68" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE68">
+        <v>60</v>
       </c>
     </row>
     <row r="69" spans="1:177" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>68</v>
       </c>
-      <c r="B69" s="23" t="s">
+      <c r="B69" s="5" t="s">
         <v>2289</v>
       </c>
       <c r="C69" t="s">
@@ -36048,16 +36031,15 @@
       <c r="FD69" t="s">
         <v>442</v>
       </c>
-      <c r="FE69" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE69">
+        <v>60</v>
       </c>
     </row>
     <row r="70" spans="1:177" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>69</v>
       </c>
-      <c r="B70" s="22" t="s">
+      <c r="B70" t="s">
         <v>2290</v>
       </c>
       <c r="C70" t="s">
@@ -36243,16 +36225,15 @@
       <c r="FD70" t="s">
         <v>442</v>
       </c>
-      <c r="FE70" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE70">
+        <v>60</v>
       </c>
     </row>
     <row r="71" spans="1:177" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>70</v>
       </c>
-      <c r="B71" s="22" t="s">
+      <c r="B71" t="s">
         <v>2291</v>
       </c>
       <c r="C71" t="s">
@@ -36438,16 +36419,15 @@
       <c r="FD71" t="s">
         <v>442</v>
       </c>
-      <c r="FE71" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE71">
+        <v>60</v>
       </c>
     </row>
     <row r="72" spans="1:177" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>71</v>
       </c>
-      <c r="B72" s="22" t="s">
+      <c r="B72" t="s">
         <v>2174</v>
       </c>
       <c r="C72" t="s">
@@ -36618,16 +36598,15 @@
       <c r="FD72" t="s">
         <v>442</v>
       </c>
-      <c r="FE72" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE72">
+        <v>120</v>
       </c>
     </row>
     <row r="73" spans="1:177" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>72</v>
       </c>
-      <c r="B73" s="22" t="s">
+      <c r="B73" t="s">
         <v>2174</v>
       </c>
       <c r="C73" t="s">
@@ -36807,16 +36786,15 @@
       <c r="FD73" t="s">
         <v>442</v>
       </c>
-      <c r="FE73" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE73">
+        <v>180</v>
       </c>
     </row>
     <row r="74" spans="1:177" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>73</v>
       </c>
-      <c r="B74" s="22" t="s">
+      <c r="B74" t="s">
         <v>2280</v>
       </c>
       <c r="C74" t="s">
@@ -37002,16 +36980,15 @@
       <c r="FD74" t="s">
         <v>442</v>
       </c>
-      <c r="FE74" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE74">
+        <v>120</v>
       </c>
     </row>
     <row r="75" spans="1:177" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>74</v>
       </c>
-      <c r="B75" s="22" t="s">
+      <c r="B75" t="s">
         <v>2281</v>
       </c>
       <c r="C75" t="s">
@@ -37209,16 +37186,15 @@
       <c r="FD75" t="s">
         <v>442</v>
       </c>
-      <c r="FE75" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE75">
+        <v>60</v>
       </c>
     </row>
     <row r="76" spans="1:177" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>75</v>
       </c>
-      <c r="B76" s="22" t="s">
+      <c r="B76" t="s">
         <v>2282</v>
       </c>
       <c r="C76" t="s">
@@ -37413,16 +37389,15 @@
       <c r="FD76" t="s">
         <v>442</v>
       </c>
-      <c r="FE76" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE76">
+        <v>60</v>
       </c>
     </row>
     <row r="77" spans="1:177" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>76</v>
       </c>
-      <c r="B77" s="22" t="s">
+      <c r="B77" t="s">
         <v>2208</v>
       </c>
       <c r="C77" t="s">
@@ -37596,9 +37571,8 @@
       <c r="FD77" t="s">
         <v>442</v>
       </c>
-      <c r="FE77" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE77">
+        <v>120</v>
       </c>
       <c r="FT77">
         <v>2</v>
@@ -37611,7 +37585,7 @@
       <c r="A78">
         <v>77</v>
       </c>
-      <c r="B78" s="22" t="s">
+      <c r="B78" t="s">
         <v>2278</v>
       </c>
       <c r="C78" t="s">
@@ -37806,9 +37780,8 @@
       <c r="FD78" t="s">
         <v>442</v>
       </c>
-      <c r="FE78" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE78">
+        <v>180</v>
       </c>
       <c r="FH78">
         <v>2</v>
@@ -37821,7 +37794,7 @@
       <c r="A79">
         <v>78</v>
       </c>
-      <c r="B79" s="22" t="s">
+      <c r="B79" t="s">
         <v>2310</v>
       </c>
       <c r="C79" t="s">
@@ -38039,7 +38012,7 @@
       <c r="A80">
         <v>79</v>
       </c>
-      <c r="B80" s="22" t="s">
+      <c r="B80" t="s">
         <v>2337</v>
       </c>
       <c r="C80" t="s">
@@ -38275,7 +38248,7 @@
       <c r="A81">
         <v>80</v>
       </c>
-      <c r="B81" s="22" t="s">
+      <c r="B81" t="s">
         <v>2360</v>
       </c>
       <c r="C81" t="s">
@@ -38496,7 +38469,7 @@
       <c r="A82">
         <v>81</v>
       </c>
-      <c r="B82" s="22" t="s">
+      <c r="B82" t="s">
         <v>2377</v>
       </c>
       <c r="C82" t="s">
@@ -38708,7 +38681,7 @@
       <c r="A83">
         <v>82</v>
       </c>
-      <c r="B83" s="22" t="s">
+      <c r="B83" t="s">
         <v>2387</v>
       </c>
       <c r="C83" t="s">
@@ -38938,7 +38911,7 @@
       <c r="A84">
         <v>83</v>
       </c>
-      <c r="B84" s="22" t="s">
+      <c r="B84" t="s">
         <v>2416</v>
       </c>
       <c r="C84" t="s">
@@ -39130,9 +39103,8 @@
       <c r="FD84" t="s">
         <v>442</v>
       </c>
-      <c r="FE84" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE84">
+        <v>240</v>
       </c>
       <c r="FT84">
         <v>1</v>
@@ -39145,7 +39117,7 @@
       <c r="A85">
         <v>84</v>
       </c>
-      <c r="B85" s="22" t="s">
+      <c r="B85" t="s">
         <v>2472</v>
       </c>
       <c r="C85" t="s">
@@ -39358,16 +39330,15 @@
       <c r="FD85" t="s">
         <v>442</v>
       </c>
-      <c r="FE85" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE85">
+        <v>1320</v>
       </c>
     </row>
     <row r="86" spans="1:177" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>85</v>
       </c>
-      <c r="B86" s="22" t="s">
+      <c r="B86" t="s">
         <v>2495</v>
       </c>
       <c r="C86" t="s">
@@ -39565,16 +39536,15 @@
       <c r="FD86" t="s">
         <v>442</v>
       </c>
-      <c r="FE86" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE86">
+        <v>300</v>
       </c>
     </row>
     <row r="87" spans="1:177" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>86</v>
       </c>
-      <c r="B87" s="22" t="s">
+      <c r="B87" t="s">
         <v>2511</v>
       </c>
       <c r="C87" t="s">
@@ -39793,16 +39763,15 @@
       <c r="FD87" t="s">
         <v>442</v>
       </c>
-      <c r="FE87" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE87">
+        <v>1320</v>
       </c>
     </row>
     <row r="88" spans="1:177" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>87</v>
       </c>
-      <c r="B88" s="22" t="s">
+      <c r="B88" t="s">
         <v>2429</v>
       </c>
       <c r="C88" t="s">
@@ -39985,16 +39954,15 @@
       <c r="FD88" t="s">
         <v>442</v>
       </c>
-      <c r="FE88" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE88">
+        <v>420</v>
       </c>
     </row>
     <row r="89" spans="1:177" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>88</v>
       </c>
-      <c r="B89" s="22" t="s">
+      <c r="B89" t="s">
         <v>2450</v>
       </c>
       <c r="C89" t="s">
@@ -40189,16 +40157,15 @@
       <c r="FD89" t="s">
         <v>442</v>
       </c>
-      <c r="FE89" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE89">
+        <v>1080</v>
       </c>
     </row>
     <row r="90" spans="1:177" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>89</v>
       </c>
-      <c r="B90" s="22" t="s">
+      <c r="B90" t="s">
         <v>2528</v>
       </c>
       <c r="C90" t="s">
@@ -40387,16 +40354,15 @@
       <c r="FD90" t="s">
         <v>442</v>
       </c>
-      <c r="FE90" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE90">
+        <v>60</v>
       </c>
     </row>
     <row r="91" spans="1:177" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>90</v>
       </c>
-      <c r="B91" s="22" t="s">
+      <c r="B91" t="s">
         <v>2539</v>
       </c>
       <c r="C91" t="s">
@@ -40623,7 +40589,7 @@
       <c r="A92">
         <v>91</v>
       </c>
-      <c r="B92" s="22" t="s">
+      <c r="B92" t="s">
         <v>2557</v>
       </c>
       <c r="C92" t="s">
@@ -40836,16 +40802,15 @@
       <c r="FD92" t="s">
         <v>442</v>
       </c>
-      <c r="FE92" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE92">
+        <v>1260</v>
       </c>
     </row>
     <row r="93" spans="1:177" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>92</v>
       </c>
-      <c r="B93" s="22" t="s">
+      <c r="B93" t="s">
         <v>2569</v>
       </c>
       <c r="C93" t="s">
@@ -41045,7 +41010,7 @@
       <c r="A94">
         <v>93</v>
       </c>
-      <c r="B94" s="22" t="s">
+      <c r="B94" t="s">
         <v>2599</v>
       </c>
       <c r="C94" t="s">
@@ -41234,16 +41199,15 @@
       <c r="FD94" t="s">
         <v>442</v>
       </c>
-      <c r="FE94" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE94">
+        <v>180</v>
       </c>
     </row>
     <row r="95" spans="1:177" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>94</v>
       </c>
-      <c r="B95" s="22" t="s">
+      <c r="B95" t="s">
         <v>2642</v>
       </c>
       <c r="C95" t="s">
@@ -41444,16 +41408,15 @@
       <c r="FD95" t="s">
         <v>442</v>
       </c>
-      <c r="FE95" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE95">
+        <v>600</v>
       </c>
     </row>
     <row r="96" spans="1:177" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>95</v>
       </c>
-      <c r="B96" s="22" t="s">
+      <c r="B96" t="s">
         <v>2621</v>
       </c>
       <c r="C96" t="s">
@@ -41645,16 +41608,15 @@
       <c r="FD96" t="s">
         <v>442</v>
       </c>
-      <c r="FE96" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE96">
+        <v>240</v>
       </c>
     </row>
     <row r="97" spans="1:161" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>96</v>
       </c>
-      <c r="B97" s="22" t="s">
+      <c r="B97" t="s">
         <v>2629</v>
       </c>
       <c r="C97" t="s">
@@ -41849,16 +41811,15 @@
       <c r="FD97" t="s">
         <v>442</v>
       </c>
-      <c r="FE97" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE97">
+        <v>420</v>
       </c>
     </row>
     <row r="98" spans="1:161" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>97</v>
       </c>
-      <c r="B98" s="22" t="s">
+      <c r="B98" t="s">
         <v>2644</v>
       </c>
       <c r="C98" t="s">
@@ -42047,16 +42008,15 @@
       <c r="FD98" t="s">
         <v>442</v>
       </c>
-      <c r="FE98" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE98">
+        <v>240</v>
       </c>
     </row>
     <row r="99" spans="1:161" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>98</v>
       </c>
-      <c r="B99" s="22" t="s">
+      <c r="B99" t="s">
         <v>2650</v>
       </c>
       <c r="C99" t="s">
@@ -42251,16 +42211,15 @@
       <c r="FD99" t="s">
         <v>442</v>
       </c>
-      <c r="FE99" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE99">
+        <v>360</v>
       </c>
     </row>
     <row r="100" spans="1:161" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>99</v>
       </c>
-      <c r="B100" s="22" t="s">
+      <c r="B100" t="s">
         <v>2676</v>
       </c>
       <c r="C100" t="s">
@@ -42447,16 +42406,15 @@
       <c r="FD100" t="s">
         <v>442</v>
       </c>
-      <c r="FE100" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE100">
+        <v>1200</v>
       </c>
     </row>
     <row r="101" spans="1:161" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>100</v>
       </c>
-      <c r="B101" s="22" t="s">
+      <c r="B101" t="s">
         <v>2698</v>
       </c>
       <c r="C101" t="s">
@@ -42536,7 +42494,7 @@
       <c r="A102">
         <v>101</v>
       </c>
-      <c r="B102" s="22" t="s">
+      <c r="B102" t="s">
         <v>2706</v>
       </c>
       <c r="C102" t="s">
@@ -42655,7 +42613,7 @@
       <c r="A103">
         <v>102</v>
       </c>
-      <c r="B103" s="22" t="s">
+      <c r="B103" t="s">
         <v>2706</v>
       </c>
       <c r="C103" t="s">
@@ -42756,7 +42714,7 @@
       <c r="A104">
         <v>103</v>
       </c>
-      <c r="B104" s="22" t="s">
+      <c r="B104" t="s">
         <v>2729</v>
       </c>
       <c r="C104" t="s">
@@ -42918,16 +42876,15 @@
       <c r="FD104" t="s">
         <v>442</v>
       </c>
-      <c r="FE104" t="e">
-        <f>60*#REF!</f>
-        <v>#REF!</v>
+      <c r="FE104">
+        <v>300</v>
       </c>
     </row>
     <row r="105" spans="1:161" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>104</v>
       </c>
-      <c r="B105" s="22" t="s">
+      <c r="B105" t="s">
         <v>2745</v>
       </c>
       <c r="C105" t="s">
@@ -43143,7 +43100,7 @@
       <c r="A106">
         <v>105</v>
       </c>
-      <c r="B106" s="22" t="s">
+      <c r="B106" t="s">
         <v>2768</v>
       </c>
       <c r="C106" t="s">
@@ -43358,7 +43315,7 @@
       <c r="A107">
         <v>106</v>
       </c>
-      <c r="B107" s="22" t="s">
+      <c r="B107" t="s">
         <v>2779</v>
       </c>
       <c r="C107" t="s">
@@ -43543,7 +43500,7 @@
       <c r="A108">
         <v>107</v>
       </c>
-      <c r="B108" s="22" t="s">
+      <c r="B108" t="s">
         <v>2790</v>
       </c>
       <c r="C108" t="s">
@@ -43728,7 +43685,7 @@
       <c r="A109">
         <v>108</v>
       </c>
-      <c r="B109" s="22" t="s">
+      <c r="B109" t="s">
         <v>2800</v>
       </c>
       <c r="C109" t="s">
@@ -43901,7 +43858,7 @@
       <c r="A110">
         <v>109</v>
       </c>
-      <c r="B110" s="22" t="s">
+      <c r="B110" t="s">
         <v>2807</v>
       </c>
       <c r="C110" t="s">
@@ -44077,7 +44034,7 @@
       <c r="A111">
         <v>110</v>
       </c>
-      <c r="B111" s="22" t="s">
+      <c r="B111" t="s">
         <v>2815</v>
       </c>
       <c r="C111" t="s">
@@ -44262,7 +44219,7 @@
       <c r="A112">
         <v>111</v>
       </c>
-      <c r="B112" s="22" t="s">
+      <c r="B112" t="s">
         <v>2823</v>
       </c>
       <c r="C112" t="s">
@@ -44450,7 +44407,7 @@
       <c r="A113">
         <v>112</v>
       </c>
-      <c r="B113" s="22" t="s">
+      <c r="B113" t="s">
         <v>2832</v>
       </c>
       <c r="C113" t="s">
@@ -44641,7 +44598,7 @@
       <c r="A114">
         <v>113</v>
       </c>
-      <c r="B114" s="22" t="s">
+      <c r="B114" t="s">
         <v>2842</v>
       </c>
       <c r="C114" t="s">
@@ -44823,7 +44780,7 @@
       <c r="A115">
         <v>114</v>
       </c>
-      <c r="B115" s="22" t="s">
+      <c r="B115" t="s">
         <v>2849</v>
       </c>
       <c r="C115" t="s">
@@ -45011,7 +44968,7 @@
       <c r="A116">
         <v>115</v>
       </c>
-      <c r="B116" s="22" t="s">
+      <c r="B116" t="s">
         <v>2860</v>
       </c>
       <c r="C116" t="s">
@@ -45190,7 +45147,7 @@
       <c r="A117">
         <v>116</v>
       </c>
-      <c r="B117" s="22" t="s">
+      <c r="B117" t="s">
         <v>2868</v>
       </c>
       <c r="C117" t="s">
@@ -45378,7 +45335,7 @@
       <c r="A118">
         <v>117</v>
       </c>
-      <c r="B118" s="22" t="s">
+      <c r="B118" t="s">
         <v>2879</v>
       </c>
       <c r="C118" t="s">
@@ -45569,7 +45526,7 @@
       <c r="A119">
         <v>118</v>
       </c>
-      <c r="B119" s="22" t="s">
+      <c r="B119" t="s">
         <v>2888</v>
       </c>
       <c r="C119" t="s">
@@ -45760,7 +45717,7 @@
       <c r="A120">
         <v>119</v>
       </c>
-      <c r="B120" s="22" t="s">
+      <c r="B120" t="s">
         <v>2895</v>
       </c>
       <c r="C120" t="s">
@@ -45936,7 +45893,7 @@
       <c r="A121">
         <v>120</v>
       </c>
-      <c r="B121" s="22" t="s">
+      <c r="B121" t="s">
         <v>2900</v>
       </c>
       <c r="C121" t="s">
@@ -46124,7 +46081,7 @@
       <c r="A122">
         <v>121</v>
       </c>
-      <c r="B122" s="22" t="s">
+      <c r="B122" t="s">
         <v>2907</v>
       </c>
       <c r="C122" t="s">
@@ -46306,7 +46263,7 @@
       <c r="A123">
         <v>122</v>
       </c>
-      <c r="B123" s="22" t="s">
+      <c r="B123" t="s">
         <v>2914</v>
       </c>
       <c r="C123" t="s">
@@ -46548,7 +46505,7 @@
       <c r="A124">
         <v>123</v>
       </c>
-      <c r="B124" s="22" t="s">
+      <c r="B124" t="s">
         <v>2921</v>
       </c>
       <c r="C124" t="s">
@@ -46784,7 +46741,7 @@
       <c r="A125">
         <v>124</v>
       </c>
-      <c r="B125" s="22" t="s">
+      <c r="B125" t="s">
         <v>2927</v>
       </c>
       <c r="C125" t="s">
@@ -47026,7 +46983,7 @@
       <c r="A126">
         <v>125</v>
       </c>
-      <c r="B126" s="22" t="s">
+      <c r="B126" t="s">
         <v>2934</v>
       </c>
       <c r="C126" t="s">
@@ -47262,7 +47219,7 @@
       <c r="A127">
         <v>126</v>
       </c>
-      <c r="B127" s="22" t="s">
+      <c r="B127" t="s">
         <v>2939</v>
       </c>
       <c r="C127" t="s">
@@ -47507,7 +47464,7 @@
       <c r="A128">
         <v>127</v>
       </c>
-      <c r="B128" s="22" t="s">
+      <c r="B128" t="s">
         <v>2945</v>
       </c>
       <c r="C128" t="s">
@@ -47740,7 +47697,7 @@
       <c r="A129">
         <v>128</v>
       </c>
-      <c r="B129" s="22" t="s">
+      <c r="B129" t="s">
         <v>3022</v>
       </c>
       <c r="C129" t="s">
@@ -47778,7 +47735,7 @@
       <c r="A130">
         <v>129</v>
       </c>
-      <c r="B130" s="22" t="s">
+      <c r="B130" t="s">
         <v>3023</v>
       </c>
       <c r="C130" t="s">
@@ -47816,7 +47773,7 @@
       <c r="A131">
         <v>130</v>
       </c>
-      <c r="B131" s="22" t="s">
+      <c r="B131" t="s">
         <v>3024</v>
       </c>
       <c r="C131" t="s">
@@ -47854,7 +47811,7 @@
       <c r="A132">
         <v>131</v>
       </c>
-      <c r="B132" s="22" t="s">
+      <c r="B132" t="s">
         <v>3025</v>
       </c>
       <c r="C132" t="s">
@@ -47892,7 +47849,7 @@
       <c r="A133">
         <v>132</v>
       </c>
-      <c r="B133" s="22" t="s">
+      <c r="B133" t="s">
         <v>3026</v>
       </c>
       <c r="C133" t="s">
@@ -47930,7 +47887,7 @@
       <c r="A134">
         <v>133</v>
       </c>
-      <c r="B134" s="22" t="s">
+      <c r="B134" t="s">
         <v>3027</v>
       </c>
       <c r="C134" t="s">
@@ -47968,7 +47925,7 @@
       <c r="A135">
         <v>134</v>
       </c>
-      <c r="B135" s="22" t="s">
+      <c r="B135" t="s">
         <v>3028</v>
       </c>
       <c r="C135" t="s">
@@ -48006,7 +47963,7 @@
       <c r="A136">
         <v>135</v>
       </c>
-      <c r="B136" s="22" t="s">
+      <c r="B136" t="s">
         <v>3029</v>
       </c>
       <c r="C136" t="s">
@@ -48044,7 +48001,7 @@
       <c r="A137">
         <v>136</v>
       </c>
-      <c r="B137" s="22" t="s">
+      <c r="B137" t="s">
         <v>3030</v>
       </c>
       <c r="C137" t="s">
@@ -48082,7 +48039,7 @@
       <c r="A138">
         <v>137</v>
       </c>
-      <c r="B138" s="22" t="s">
+      <c r="B138" t="s">
         <v>3031</v>
       </c>
       <c r="C138" t="s">
@@ -48120,7 +48077,7 @@
       <c r="A139">
         <v>138</v>
       </c>
-      <c r="B139" s="22" t="s">
+      <c r="B139" t="s">
         <v>3032</v>
       </c>
       <c r="C139" t="s">
@@ -48161,7 +48118,7 @@
       <c r="A140">
         <v>139</v>
       </c>
-      <c r="B140" s="22" t="s">
+      <c r="B140" t="s">
         <v>3033</v>
       </c>
       <c r="C140" t="s">
@@ -48199,7 +48156,7 @@
       <c r="A141">
         <v>140</v>
       </c>
-      <c r="B141" s="22" t="s">
+      <c r="B141" t="s">
         <v>3034</v>
       </c>
       <c r="C141" t="s">
@@ -48237,7 +48194,7 @@
       <c r="A142">
         <v>141</v>
       </c>
-      <c r="B142" s="22" t="s">
+      <c r="B142" t="s">
         <v>3035</v>
       </c>
       <c r="C142" t="s">
@@ -48275,7 +48232,7 @@
       <c r="A143">
         <v>142</v>
       </c>
-      <c r="B143" s="22" t="s">
+      <c r="B143" t="s">
         <v>3036</v>
       </c>
       <c r="C143" t="s">
@@ -48313,7 +48270,7 @@
       <c r="A144">
         <v>143</v>
       </c>
-      <c r="B144" s="22" t="s">
+      <c r="B144" t="s">
         <v>3037</v>
       </c>
       <c r="C144" t="s">
@@ -48351,7 +48308,7 @@
       <c r="A145">
         <v>144</v>
       </c>
-      <c r="B145" s="22" t="s">
+      <c r="B145" t="s">
         <v>3038</v>
       </c>
       <c r="C145" t="s">
@@ -48389,7 +48346,7 @@
       <c r="A146">
         <v>145</v>
       </c>
-      <c r="B146" s="22" t="s">
+      <c r="B146" t="s">
         <v>3039</v>
       </c>
       <c r="C146" t="s">
@@ -48427,7 +48384,7 @@
       <c r="A147">
         <v>146</v>
       </c>
-      <c r="B147" s="22" t="s">
+      <c r="B147" t="s">
         <v>3040</v>
       </c>
       <c r="C147" t="s">
@@ -48465,7 +48422,7 @@
       <c r="A148">
         <v>147</v>
       </c>
-      <c r="B148" s="22" t="s">
+      <c r="B148" t="s">
         <v>3041</v>
       </c>
       <c r="C148" t="s">
@@ -48503,7 +48460,7 @@
       <c r="A149">
         <v>148</v>
       </c>
-      <c r="B149" s="22" t="s">
+      <c r="B149" t="s">
         <v>3042</v>
       </c>
       <c r="C149" t="s">
@@ -48541,7 +48498,7 @@
       <c r="A150">
         <v>149</v>
       </c>
-      <c r="B150" s="22" t="s">
+      <c r="B150" t="s">
         <v>3043</v>
       </c>
       <c r="C150" t="s">
@@ -48579,7 +48536,7 @@
       <c r="A151">
         <v>150</v>
       </c>
-      <c r="B151" s="22" t="s">
+      <c r="B151" t="s">
         <v>3044</v>
       </c>
       <c r="C151" t="s">
@@ -48620,7 +48577,7 @@
       <c r="A152">
         <v>151</v>
       </c>
-      <c r="B152" s="22" t="s">
+      <c r="B152" t="s">
         <v>3045</v>
       </c>
       <c r="C152" t="s">
@@ -48658,7 +48615,7 @@
       <c r="A153">
         <v>152</v>
       </c>
-      <c r="B153" s="22" t="s">
+      <c r="B153" t="s">
         <v>3046</v>
       </c>
       <c r="C153" t="s">
@@ -48696,7 +48653,7 @@
       <c r="A154">
         <v>153</v>
       </c>
-      <c r="B154" s="22" t="s">
+      <c r="B154" t="s">
         <v>3047</v>
       </c>
       <c r="C154" t="s">
@@ -48734,7 +48691,7 @@
       <c r="A155">
         <v>154</v>
       </c>
-      <c r="B155" s="22" t="s">
+      <c r="B155" t="s">
         <v>3048</v>
       </c>
       <c r="C155" t="s">
@@ -48775,7 +48732,7 @@
       <c r="A156">
         <v>155</v>
       </c>
-      <c r="B156" s="22" t="s">
+      <c r="B156" t="s">
         <v>3049</v>
       </c>
       <c r="C156" t="s">
@@ -48816,7 +48773,7 @@
       <c r="A157">
         <v>156</v>
       </c>
-      <c r="B157" s="22" t="s">
+      <c r="B157" t="s">
         <v>3115</v>
       </c>
       <c r="C157" t="s">
@@ -49079,7 +49036,7 @@
       <c r="A158">
         <v>157</v>
       </c>
-      <c r="B158" s="22" t="s">
+      <c r="B158" t="s">
         <v>3127</v>
       </c>
       <c r="C158" t="s">
@@ -49318,7 +49275,7 @@
       <c r="A159">
         <v>158</v>
       </c>
-      <c r="B159" s="22" t="s">
+      <c r="B159" t="s">
         <v>3141</v>
       </c>
       <c r="C159" t="s">
@@ -49560,7 +49517,7 @@
       <c r="A160">
         <v>159</v>
       </c>
-      <c r="B160" s="22" t="s">
+      <c r="B160" t="s">
         <v>3155</v>
       </c>
       <c r="C160" t="s">
@@ -49784,7 +49741,7 @@
       <c r="A161">
         <v>160</v>
       </c>
-      <c r="B161" s="22" t="s">
+      <c r="B161" t="s">
         <v>3167</v>
       </c>
       <c r="C161" t="s">
@@ -50023,7 +49980,7 @@
       <c r="A162">
         <v>161</v>
       </c>
-      <c r="B162" s="22" t="s">
+      <c r="B162" t="s">
         <v>3310</v>
       </c>
       <c r="C162" t="s">
@@ -50274,7 +50231,7 @@
       <c r="A163">
         <v>162</v>
       </c>
-      <c r="B163" s="22" t="s">
+      <c r="B163" t="s">
         <v>3178</v>
       </c>
       <c r="C163" t="s">
@@ -50483,7 +50440,7 @@
       <c r="A164">
         <v>163</v>
       </c>
-      <c r="B164" s="22" t="s">
+      <c r="B164" t="s">
         <v>3190</v>
       </c>
       <c r="C164" t="s">
@@ -50689,7 +50646,7 @@
       <c r="A165">
         <v>164</v>
       </c>
-      <c r="B165" s="22" t="s">
+      <c r="B165" t="s">
         <v>3198</v>
       </c>
       <c r="C165" t="s">
@@ -50898,7 +50855,7 @@
       <c r="A166">
         <v>165</v>
       </c>
-      <c r="B166" s="22" t="s">
+      <c r="B166" t="s">
         <v>3204</v>
       </c>
       <c r="C166" t="s">
@@ -51104,7 +51061,7 @@
       <c r="A167">
         <v>166</v>
       </c>
-      <c r="B167" s="22" t="s">
+      <c r="B167" t="s">
         <v>3211</v>
       </c>
       <c r="C167" t="s">
@@ -51145,7 +51102,7 @@
       <c r="A168">
         <v>167</v>
       </c>
-      <c r="B168" s="22" t="s">
+      <c r="B168" t="s">
         <v>3308</v>
       </c>
       <c r="C168" t="s">
@@ -51186,7 +51143,7 @@
       <c r="A169">
         <v>168</v>
       </c>
-      <c r="B169" s="22" t="s">
+      <c r="B169" t="s">
         <v>3327</v>
       </c>
       <c r="C169" t="s">
@@ -51380,7 +51337,7 @@
       <c r="A170">
         <v>169</v>
       </c>
-      <c r="B170" s="22" t="s">
+      <c r="B170" t="s">
         <v>3379</v>
       </c>
       <c r="C170" t="s">
@@ -51604,7 +51561,7 @@
       <c r="A171">
         <v>170</v>
       </c>
-      <c r="B171" s="22" t="s">
+      <c r="B171" t="s">
         <v>3397</v>
       </c>
       <c r="C171" t="s">
@@ -51792,7 +51749,7 @@
       <c r="A172">
         <v>171</v>
       </c>
-      <c r="B172" s="22" t="s">
+      <c r="B172" t="s">
         <v>3410</v>
       </c>
       <c r="D172" t="s">
@@ -51956,7 +51913,7 @@
       <c r="A173">
         <v>172</v>
       </c>
-      <c r="B173" s="22" t="s">
+      <c r="B173" t="s">
         <v>3412</v>
       </c>
       <c r="D173" t="s">
@@ -52117,7 +52074,7 @@
       <c r="A174">
         <v>173</v>
       </c>
-      <c r="B174" s="22" t="s">
+      <c r="B174" t="s">
         <v>3413</v>
       </c>
       <c r="D174" t="s">
@@ -52281,7 +52238,7 @@
       <c r="A175">
         <v>174</v>
       </c>
-      <c r="B175" s="22" t="s">
+      <c r="B175" t="s">
         <v>3414</v>
       </c>
       <c r="D175" t="s">
@@ -52442,7 +52399,7 @@
       <c r="A176">
         <v>175</v>
       </c>
-      <c r="B176" s="22" t="s">
+      <c r="B176" t="s">
         <v>3415</v>
       </c>
       <c r="D176" t="s">
@@ -52606,7 +52563,7 @@
       <c r="A177">
         <v>176</v>
       </c>
-      <c r="B177" s="22" t="s">
+      <c r="B177" t="s">
         <v>3416</v>
       </c>
       <c r="D177" t="s">
@@ -52770,7 +52727,7 @@
       <c r="A178">
         <v>177</v>
       </c>
-      <c r="B178" s="22" t="s">
+      <c r="B178" t="s">
         <v>3417</v>
       </c>
       <c r="D178" t="s">
@@ -52934,7 +52891,7 @@
       <c r="A179">
         <v>178</v>
       </c>
-      <c r="B179" s="22" t="s">
+      <c r="B179" t="s">
         <v>3460</v>
       </c>
       <c r="C179" t="s">
@@ -53188,7 +53145,7 @@
       <c r="A180">
         <v>179</v>
       </c>
-      <c r="B180" s="22" t="s">
+      <c r="B180" t="s">
         <v>3485</v>
       </c>
       <c r="C180" t="s">
@@ -53331,7 +53288,7 @@
       <c r="A181">
         <v>180</v>
       </c>
-      <c r="B181" s="22" t="s">
+      <c r="B181" t="s">
         <v>3494</v>
       </c>
       <c r="C181" t="s">
@@ -53681,189 +53638,189 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="IO14:IP14 IQ15:IR15 IT15:IZ15 JB15:JF15 IL19:IO19 IQ19:IT19 IZ19 JC19:JF19 JR19 JZ19:KA19 IQ22:IZ22 JB22:JI23 JK22:JN23 IL23:IO23 IQ23:IR23 IU23:IZ23 IQ26:IR26 IT26:IZ26 JB26:JI26 JK26:JN26 IL27:IQ27 IS27:IT27 IZ27 JC27:JH27 JK27:JS27 JU27 JX27 JZ27:KA27 IL30:IQ31 IS30:IT31 JK30:JS31 JZ30:KA31 JC30:JH32 IZ30:IZ34 JU30:JU38 JX30:JX38 IS32 KA32 IL32:IP33 JZ32:JZ33 IQ32:IQ34 JK32:JN35 JO32:JS37 IT32:IT38 IR33:IS33 IU33:IV33 IW33:IZ34 JB33:JI35 GB34:IP34 IS34 JZ34:KA38 IP35:IZ35 IL35:IO38 GB35:IK41 IZ36:IZ37 JC36:JD37 JF36:JH37 JM36:JN37 IP36:IP38 IS36:IS38 IQ36:IQ39 JK36:JK40 JL36:JL42 JE37 JK38:JS38 IT38:IZ40 JB38:JI40 IO39:IP39 IR39:IS39 JS39:KA39 JM39:JR40 IL40:IQ40 IS40:IT40 JS40 JU40 JX40 JZ40:KA40 JM40:JM42 IW41:IZ41">
-    <cfRule type="expression" dxfId="36" priority="607">
-      <formula>$A14=$A$1</formula>
+  <conditionalFormatting sqref="B172:B178 K172:N178 BT172:BX178 BZ172:CC178 CK172:CK178 DB172:DC178 EI172:EM178 FE172:FK178 FP172:FP178 D172:I178 Q172:AE178 AL172:AN178 CG172:CH178">
+    <cfRule type="expression" dxfId="36" priority="652">
+      <formula>$A172=#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AQ1 AT1:BF1 CI1:CJ1 EN1 FR1:FS207 A2:A12 FV2:GA42 B2:I171 Q2:AE171 AL2:AN171 CA2:CC171 CG2:CH171 J2:P207 AF2:AH207 AO2:BZ207 CI2:CL207 CO2:EV207 FT2:FU207 KB13:LH41 A13:B200 GJ42:GU42 GW42:GY42 HA42:HB42 HD42 HI42 HN42:HP42 IA42 IC42 IF42:IH42 IJ42 FV43:IK207 C172:C178 B179:E200 F179:I207 Q179:AE207 AL179:AN207 CA179:CC207 CG179:CH207 A201:E207 Q1048575:Q1048576 EX2:FQ207">
+    <cfRule type="expression" dxfId="35" priority="612">
+      <formula>$A1=#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="CD2:CE207">
+    <cfRule type="expression" dxfId="34" priority="1">
+      <formula>$A2=#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FV1:GA1">
-    <cfRule type="expression" dxfId="35" priority="611">
+    <cfRule type="expression" dxfId="33" priority="611">
       <formula>#REF!=#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="GB42:GI42">
-    <cfRule type="expression" dxfId="34" priority="102">
+    <cfRule type="expression" dxfId="32" priority="102">
       <formula>$A42=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="GB2:IK33">
-    <cfRule type="expression" dxfId="33" priority="420">
+    <cfRule type="expression" dxfId="31" priority="420">
       <formula>$A2=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="GV42">
-    <cfRule type="expression" dxfId="32" priority="101">
+    <cfRule type="expression" dxfId="30" priority="101">
       <formula>$A42=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="GZ42">
-    <cfRule type="expression" dxfId="31" priority="100">
+    <cfRule type="expression" dxfId="29" priority="100">
       <formula>$A42=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="HC42">
-    <cfRule type="expression" dxfId="30" priority="99">
+    <cfRule type="expression" dxfId="28" priority="99">
       <formula>$A42=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="HE42:HH42">
-    <cfRule type="expression" dxfId="29" priority="95">
+    <cfRule type="expression" dxfId="27" priority="95">
       <formula>$A42=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="HJ42:HM42">
-    <cfRule type="expression" dxfId="28" priority="91">
+    <cfRule type="expression" dxfId="26" priority="91">
       <formula>$A42=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="HQ42:HZ42">
-    <cfRule type="expression" dxfId="27" priority="81">
+    <cfRule type="expression" dxfId="25" priority="81">
       <formula>$A42=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="IB42">
-    <cfRule type="expression" dxfId="26" priority="80">
+    <cfRule type="expression" dxfId="24" priority="80">
       <formula>$A42=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ID42:IE42">
-    <cfRule type="expression" dxfId="25" priority="78">
+    <cfRule type="expression" dxfId="23" priority="78">
       <formula>$A42=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="II42">
-    <cfRule type="expression" dxfId="24" priority="77">
+    <cfRule type="expression" dxfId="22" priority="77">
       <formula>$A42=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="IK42:IP42">
-    <cfRule type="expression" dxfId="23" priority="71">
+    <cfRule type="expression" dxfId="21" priority="71">
       <formula>$A42=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="IL24:IQ25">
-    <cfRule type="expression" dxfId="22" priority="49">
+    <cfRule type="expression" dxfId="20" priority="49">
       <formula>$A24=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="IO14:IP14 IQ15:IR15 IT15:IZ15 JB15:JF15 IL19:IO19 IQ19:IT19 IZ19 JC19:JF19 JR19 JZ19:KA19 IQ22:IZ22 JB22:JI23 JK22:JN23 IL23:IO23 IQ23:IR23 IU23:IZ23 IQ26:IR26 IT26:IZ26 JB26:JI26 JK26:JN26 IL27:IQ27 IS27:IT27 IZ27 JC27:JH27 JK27:JS27 JU27 JX27 JZ27:KA27 IL30:IQ31 IS30:IT31 JK30:JS31 JZ30:KA31 JC30:JH32 IZ30:IZ34 JU30:JU38 JX30:JX38 IS32 KA32 IL32:IP33 JZ32:JZ33 IQ32:IQ34 JK32:JN35 JO32:JS37 IT32:IT38 IR33:IS33 IU33:IV33 IW33:IZ34 JB33:JI35 GB34:IP34 IS34 JZ34:KA38 IP35:IZ35 IL35:IO38 GB35:IK41 IZ36:IZ37 JC36:JD37 JF36:JH37 JM36:JN37 IP36:IP38 IS36:IS38 IQ36:IQ39 JK36:JK40 JL36:JL42 JE37 JK38:JS38 IT38:IZ40 JB38:JI40 IO39:IP39 IR39:IS39 JS39:KA39 JM39:JR40 IL40:IQ40 IS40:IT40 JS40 JU40 JX40 JZ40:KA40 JM40:JM42 IW41:IZ41">
+    <cfRule type="expression" dxfId="19" priority="607">
+      <formula>$A14=$A$1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="IS42">
-    <cfRule type="expression" dxfId="21" priority="70">
+    <cfRule type="expression" dxfId="18" priority="70">
       <formula>$A42=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="IS24:IT25">
-    <cfRule type="expression" dxfId="20" priority="47">
+    <cfRule type="expression" dxfId="17" priority="47">
       <formula>$A24=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="IZ24:IZ25">
-    <cfRule type="expression" dxfId="19" priority="46">
+    <cfRule type="expression" dxfId="16" priority="46">
       <formula>$A24=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="IZ42">
-    <cfRule type="expression" dxfId="18" priority="69">
+    <cfRule type="expression" dxfId="15" priority="69">
       <formula>$A42=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="JC24:JH25">
-    <cfRule type="expression" dxfId="17" priority="40">
+    <cfRule type="expression" dxfId="14" priority="40">
       <formula>$A24=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="JD42">
-    <cfRule type="expression" dxfId="16" priority="68">
+    <cfRule type="expression" dxfId="13" priority="68">
       <formula>$A42=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="JF42:JH42">
-    <cfRule type="expression" dxfId="15" priority="65">
+    <cfRule type="expression" dxfId="12" priority="65">
       <formula>$A42=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="JK42">
-    <cfRule type="expression" dxfId="14" priority="64">
+    <cfRule type="expression" dxfId="11" priority="64">
       <formula>$A42=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="JK24:JQ25">
-    <cfRule type="expression" dxfId="13" priority="33">
+    <cfRule type="expression" dxfId="10" priority="33">
       <formula>$A24=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="JN42:JS42">
-    <cfRule type="expression" dxfId="12" priority="58">
+    <cfRule type="expression" dxfId="9" priority="58">
       <formula>$A42=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="JR23:JR25">
-    <cfRule type="expression" dxfId="11" priority="32">
+    <cfRule type="expression" dxfId="8" priority="32">
       <formula>$A23=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="JS24:JS25">
-    <cfRule type="expression" dxfId="10" priority="31">
+    <cfRule type="expression" dxfId="7" priority="31">
       <formula>$A24=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="JU24:JU25">
-    <cfRule type="expression" dxfId="9" priority="30">
+    <cfRule type="expression" dxfId="6" priority="30">
       <formula>$A24=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="JU42">
-    <cfRule type="expression" dxfId="8" priority="57">
+    <cfRule type="expression" dxfId="5" priority="57">
       <formula>$A42=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="JX24:JX25">
-    <cfRule type="expression" dxfId="7" priority="29">
+    <cfRule type="expression" dxfId="4" priority="29">
       <formula>$A24=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="JX42">
-    <cfRule type="expression" dxfId="6" priority="56">
+    <cfRule type="expression" dxfId="3" priority="56">
       <formula>$A42=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="JZ42">
-    <cfRule type="expression" dxfId="5" priority="55">
+    <cfRule type="expression" dxfId="2" priority="55">
       <formula>$A42=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="JZ24:KA25">
-    <cfRule type="expression" dxfId="4" priority="27">
+    <cfRule type="expression" dxfId="1" priority="27">
       <formula>$A24=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="KB1:LH1">
-    <cfRule type="expression" dxfId="3" priority="599">
+    <cfRule type="expression" dxfId="0" priority="599">
       <formula>#REF!=#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="FV2:GA42 KB13:LH41 A13:B200 GJ42:GU42 GW42:GY42 HA42:HB42 HD42 HI42 HN42:HP42 IA42 IC42 IF42:IH42 IJ42 C172:C178 Q1048575:Q1048576 CI1:CJ1 EN1 AQ1 AT1:BF1 A2:A12 B179:E200 A201:E207 B2:I171 F179:I207 Q2:AE171 Q179:AE207 AL2:AN171 AL179:AN207 AF2:AH207 AO2:BZ207 CA2:CC171 CA179:CC207 CD2:CD207 CG2:CH171 CG179:CH207 CI2:CL207 FR1:FS207 FT2:FU207 J2:P207 EX2:FQ207 FV43:IK207 CO2:EV207">
-    <cfRule type="expression" dxfId="2" priority="612">
-      <formula>$A1=#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DB172:DC178 EI172:EM178 B172:B178 D172:I178 K172:N178 Q172:AE178 AL172:AN178 BT172:BX178 BZ172:CC178 CG172:CH178 CK172:CK178 FP172:FP178 FE172:FK178">
-    <cfRule type="expression" dxfId="1" priority="652">
-      <formula>$A172=#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="CE2:CE207">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$A2=#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">

--- a/Inputs/BD.xlsx
+++ b/Inputs/BD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/078e1a455e5c02ce/Documentos/GitHub/Proyecto_PIPC/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7292" documentId="13_ncr:1_{898522BF-B0F8-4888-9748-DC730D5D6CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3024D4A-E2CD-4791-BBF1-A7AF139B53E0}"/>
+  <xr:revisionPtr revIDLastSave="7543" documentId="13_ncr:1_{898522BF-B0F8-4888-9748-DC730D5D6CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E53BA482-5013-4DFA-B919-3BE1BF1C1266}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{3F095A75-F066-4695-8672-8D4315F1EF23}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3F095A75-F066-4695-8672-8D4315F1EF23}"/>
   </bookViews>
   <sheets>
     <sheet name="BD" sheetId="1" r:id="rId1"/>
@@ -563,7 +563,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10814" uniqueCount="3576">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10821" uniqueCount="3576">
   <si>
     <t>dia</t>
   </si>
@@ -60831,6 +60831,9 @@
       <c r="A173">
         <v>171</v>
       </c>
+      <c r="B173" t="s">
+        <v>809</v>
+      </c>
       <c r="C173" t="s">
         <v>3469</v>
       </c>
@@ -61051,6 +61054,9 @@
       <c r="A174">
         <v>172</v>
       </c>
+      <c r="B174" t="s">
+        <v>809</v>
+      </c>
       <c r="C174" t="s">
         <v>3469</v>
       </c>
@@ -61268,6 +61274,9 @@
       <c r="A175">
         <v>173</v>
       </c>
+      <c r="B175" t="s">
+        <v>809</v>
+      </c>
       <c r="C175" t="s">
         <v>3469</v>
       </c>
@@ -61488,6 +61497,9 @@
       <c r="A176">
         <v>174</v>
       </c>
+      <c r="B176" t="s">
+        <v>809</v>
+      </c>
       <c r="C176" t="s">
         <v>3469</v>
       </c>
@@ -61705,6 +61717,9 @@
       <c r="A177">
         <v>175</v>
       </c>
+      <c r="B177" t="s">
+        <v>809</v>
+      </c>
       <c r="C177" t="s">
         <v>3469</v>
       </c>
@@ -61925,6 +61940,9 @@
       <c r="A178">
         <v>176</v>
       </c>
+      <c r="B178" t="s">
+        <v>809</v>
+      </c>
       <c r="C178" t="s">
         <v>3469</v>
       </c>
@@ -62144,6 +62162,9 @@
     <row r="179" spans="1:179" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>177</v>
+      </c>
+      <c r="B179" t="s">
+        <v>809</v>
       </c>
       <c r="C179" t="s">
         <v>3469</v>
@@ -64052,7 +64073,7 @@
       <formula>#REF!=$A$1</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B201" xr:uid="{D5CD9EE6-9E02-4584-93C4-B4A613E84A37}">
       <formula1>"BANCO, BBVA, COMPARTAMOS, DHL, GASERA, GASOLINERA, GENERAL, GDL, UVP"</formula1>
     </dataValidation>

--- a/Inputs/BD.xlsx
+++ b/Inputs/BD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/078e1a455e5c02ce/Documentos/GitHub/Proyecto_PIPC/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7535" documentId="13_ncr:1_{898522BF-B0F8-4888-9748-DC730D5D6CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4BDAC0D-D39F-43A9-B1E9-FE93C46A5A74}"/>
+  <xr:revisionPtr revIDLastSave="7544" documentId="13_ncr:1_{898522BF-B0F8-4888-9748-DC730D5D6CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB5780CA-5E3B-4D82-9D95-FFE31B5866AA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3F095A75-F066-4695-8672-8D4315F1EF23}"/>
   </bookViews>
@@ -53643,7 +53643,7 @@
       <formula>$A172=#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AQ1 AT1:BF1 CI1:CJ1 EN1 FR1:FS207 A2:A12 FV2:GA42 B2:I171 Q2:AE171 AL2:AN171 CA2:CC171 CG2:CH171 J2:P207 AF2:AH207 AO2:BZ207 CI2:CL207 CO2:EV207 FT2:FU207 KB13:LH41 A13:B200 GJ42:GU42 GW42:GY42 HA42:HB42 HD42 HI42 HN42:HP42 IA42 IC42 IF42:IH42 IJ42 FV43:IK207 C172:C178 B179:E200 F179:I207 Q179:AE207 AL179:AN207 CA179:CC207 CG179:CH207 A201:E207 Q1048575:Q1048576 EX2:FQ207">
+  <conditionalFormatting sqref="AQ1 AT1:BF1 CI1:CJ1 EN1 FR1:FS207 A2:A12 FV2:GA42 B2:I171 Q2:AE171 AL2:AN171 CA2:CC171 CG2:CH171 J2:P207 AF2:AH207 AO2:BZ207 CI2:CL207 CO2:EV207 EX2:FQ207 FT2:FU207 KB13:LH41 A13:B200 GJ42:GU42 GW42:GY42 HA42:HB42 HD42 HI42 HN42:HP42 IA42 IC42 IF42:IH42 IJ42 FV43:IK207 C172:C178 B179:E200 F179:I207 Q179:AE207 AL179:AN207 CA179:CC207 CG179:CH207 A201:E207 Q1048575:Q1048576">
     <cfRule type="expression" dxfId="35" priority="612">
       <formula>$A1=#REF!</formula>
     </cfRule>

--- a/Inputs/BD.xlsx
+++ b/Inputs/BD.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/078e1a455e5c02ce/Documentos/GitHub/Proyecto_PIPC/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7543" documentId="13_ncr:1_{898522BF-B0F8-4888-9748-DC730D5D6CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E53BA482-5013-4DFA-B919-3BE1BF1C1266}"/>
+  <xr:revisionPtr revIDLastSave="7544" documentId="13_ncr:1_{898522BF-B0F8-4888-9748-DC730D5D6CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C49D73DD-5865-4F13-B9D2-DB6062C7798E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3F095A75-F066-4695-8672-8D4315F1EF23}"/>
   </bookViews>
@@ -12100,7 +12100,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="26" fmlaLink="$A$1" max="30000" min="1" page="10" val="180"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="26" fmlaLink="$A$1" max="30000" min="1" page="10" val="155"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12156,10 +12156,6 @@
     <mc:Fallback/>
   </mc:AlternateContent>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12496,7 +12492,7 @@
   <sheetData>
     <row r="1" spans="1:322" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="DS1" t="s">
         <v>1918</v>
@@ -63813,7 +63809,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A3:FV13 FX3:GC43 B14:FV14 KD14:LJ42 A14:A201 D15:FV58 B15:C68 GL43:GW43 GY43:HA43 HC43:HD43 HF43 HK43 HP43:HR43 IC43 IE43 IH43:IJ43 IL43 FX44:IM60 EM59:FV60 D59:EL62 EM61:IM62 D63:IM63 D64:AO68 AP64:IM72 B69:AO72 B73:IM172 B173:B179 O173:Q179 T173:U179 AF173:AM179 AR173:AR179 AW173:BB179 BE173:CC179 CG173:CG179 CK173:CK179 CP173:DY179 EE173:FS179 FU173:IM179 A202:IM208 B180:IM201">
+  <conditionalFormatting sqref="A3:FV13 FX3:GC43 B14:FV14 KD14:LJ42 A14:A201 D15:FV58 B15:C68 GL43:GW43 GY43:HA43 HC43:HD43 HF43 HK43 HP43:HR43 IC43 IE43 IH43:IJ43 IL43 FX44:IM60 EM59:FV60 D59:EL62 EM61:IM62 D63:IM63 D64:AO68 AP64:IM72 B69:AO72 B73:IM172 B173:B179 O173:Q179 T173:U179 AF173:AM179 AR173:AR179 AW173:BB179 BE173:CC179 CG173:CG179 CK173:CK179 CP173:DY179 EE173:FS179 FU173:IM179 B180:IM201 A202:IM208">
     <cfRule type="expression" dxfId="51" priority="606">
       <formula>$A3=$A$1</formula>
     </cfRule>
@@ -64226,7 +64222,7 @@
     <row r="1" spans="1:310" x14ac:dyDescent="0.3">
       <c r="A1">
         <f>+BD!A1</f>
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="B1" t="s">
         <v>133</v>
@@ -65159,39 +65155,39 @@
     <row r="2" spans="1:310" x14ac:dyDescent="0.3">
       <c r="B2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,2, FALSE)</f>
-        <v>GASOLINERA</v>
+        <v>BBVA</v>
       </c>
       <c r="C2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,3, FALSE)</f>
-        <v>SAMUEL AGUIRRE OCHOA</v>
+        <v>BBVA MEXICO S.A. INSTITUCION DE BANCA MULTIPLE GRUPO FINANCIERO BBVA MEXICO</v>
       </c>
       <c r="D2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,4, FALSE)</f>
-        <v>GASOLINERA ES 05573 ACATLAN DE OSORIO</v>
+        <v>CR 3738 EDIFICIO SEDE</v>
       </c>
       <c r="E2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,5, FALSE)</f>
-        <v>AUOS590720BX5</v>
-      </c>
-      <c r="F2" t="str">
+        <v>BBA 830831 LJ2</v>
+      </c>
+      <c r="F2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,6, FALSE)</f>
-        <v>PL/9506/EXP/ES/2015</v>
+        <v>0</v>
       </c>
       <c r="G2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,7, FALSE)</f>
-        <v>GASOLINERA</v>
+        <v>BANCO</v>
       </c>
       <c r="H2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,8, FALSE)</f>
-        <v>ATENCION AL PUBLICO POR MEDIO DE VENTA DE GASOLINAS, DIESEL, ACEITES Y ADITIVOS</v>
+        <v>INTERMEDIACIÓN FINANCIERA, GESTIÓN DE CUENTAS Y TRANSACCIONES, PRÉSTAMOS Y CRÉDITOS, SERVICIOS DE INVERSIÓN, ASESORAMIENTO FINANCIERO Y CUMPLIMIENTO DE REGULACIONES BANCARIAS</v>
       </c>
       <c r="I2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,9, FALSE)</f>
-        <v>CARRETERA INTERNACIONAL MEXICO - OAXACA</v>
-      </c>
-      <c r="J2" t="str">
+        <v>BOULEVARD 5 DE MAYO</v>
+      </c>
+      <c r="J2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,10, FALSE)</f>
-        <v>KM 221 INT 4</v>
+        <v>2510</v>
       </c>
       <c r="K2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,11, FALSE)</f>
@@ -65199,11 +65195,11 @@
       </c>
       <c r="L2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,12, FALSE)</f>
-        <v>BARRIO LA PALMA</v>
+        <v>LADRILLERA DE BENITEZ</v>
       </c>
       <c r="M2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,13, FALSE)</f>
-        <v>ACATLAN DE OSORIO</v>
+        <v>PUEBLA</v>
       </c>
       <c r="N2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,14, FALSE)</f>
@@ -65211,27 +65207,27 @@
       </c>
       <c r="O2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,15, FALSE)</f>
-        <v>74949</v>
+        <v>72530</v>
       </c>
       <c r="P2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,16, FALSE)</f>
-        <v>2241071530</v>
-      </c>
-      <c r="Q2" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,17, FALSE)</f>
-        <v>es5573@hotmail.com</v>
+        <v>0</v>
       </c>
       <c r="R2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,18, FALSE)</f>
-        <v>34</v>
-      </c>
-      <c r="S2" t="str">
+        <v>0</v>
+      </c>
+      <c r="S2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,19, FALSE)</f>
-        <v>1 DE ENERO DE 1991</v>
-      </c>
-      <c r="T2" t="str">
+        <v>0</v>
+      </c>
+      <c r="T2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,20, FALSE)</f>
-        <v>NOE MORA RAMIREZ</v>
+        <v>0</v>
       </c>
       <c r="U2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,21, FALSE)</f>
@@ -65239,51 +65235,51 @@
       </c>
       <c r="V2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,22, FALSE)</f>
-        <v>4142.38</v>
+        <v>0</v>
       </c>
       <c r="W2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,23, FALSE)</f>
-        <v>2655.88</v>
+        <v>0</v>
       </c>
       <c r="X2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,24, FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,25, FALSE)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,26, FALSE)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,27, FALSE)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,28, FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,29, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AD2" t="str">
+      <c r="AD2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,30, FALSE)</f>
-        <v>10 CAJONES</v>
-      </c>
-      <c r="AE2" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,31, FALSE)</f>
-        <v>SAMUEL AGUIRRE OCHOA</v>
-      </c>
-      <c r="AF2" t="str">
+        <v>0</v>
+      </c>
+      <c r="AF2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,32, FALSE)</f>
-        <v>AGNERIS CAMPOS MENDEZ</v>
+        <v>0</v>
       </c>
       <c r="AG2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,33, FALSE)</f>
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AH2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,34, FALSE)</f>
@@ -65291,11 +65287,11 @@
       </c>
       <c r="AI2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,35, FALSE)</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,36, FALSE)</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AK2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,37, FALSE)</f>
@@ -65307,47 +65303,47 @@
       </c>
       <c r="AM2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,39, FALSE)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AN2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,40, FALSE)</f>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="AO2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,41, FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="AP2" t="str">
+        <v>0</v>
+      </c>
+      <c r="AP2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,42, FALSE)</f>
-        <v>LUNES A DOMINGO</v>
-      </c>
-      <c r="AQ2" t="str">
+        <v>0</v>
+      </c>
+      <c r="AQ2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,43, FALSE)</f>
-        <v>24 HORAS</v>
+        <v>0</v>
       </c>
       <c r="AR2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,44, FALSE)</f>
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AS2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,45, FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="AT2" t="str">
+        <v>0</v>
+      </c>
+      <c r="AT2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,46, FALSE)</f>
-        <v>OFICINA</v>
+        <v>0</v>
       </c>
       <c r="AU2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,47, FALSE)</f>
-        <v>10</v>
-      </c>
-      <c r="AV2" t="str">
+        <v>0</v>
+      </c>
+      <c r="AV2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,48, FALSE)</f>
-        <v>BOMBAS, VENTEO, AREA INTERNA</v>
+        <v>0</v>
       </c>
       <c r="AW2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,49, FALSE)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AX2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,50, FALSE)</f>
@@ -65355,19 +65351,19 @@
       </c>
       <c r="AY2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,51, FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="AZ2" t="str">
+        <v>0</v>
+      </c>
+      <c r="AZ2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,52, FALSE)</f>
-        <v>BOMBAS, OFICINA, VENTEO</v>
+        <v>0</v>
       </c>
       <c r="BA2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,53, FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="BB2" t="str">
+        <v>0</v>
+      </c>
+      <c r="BB2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,54, FALSE)</f>
-        <v>ESTE</v>
+        <v>0</v>
       </c>
       <c r="BC2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,55, FALSE)</f>
@@ -65379,11 +65375,11 @@
       </c>
       <c r="BE2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,57, FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="BF2" t="str">
+        <v>0</v>
+      </c>
+      <c r="BF2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,58, FALSE)</f>
-        <v>SIRENA</v>
+        <v>0</v>
       </c>
       <c r="BG2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,59, FALSE)</f>
@@ -65393,9 +65389,9 @@
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,60, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="BI2" t="str">
+      <c r="BI2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,61, FALSE)</f>
-        <v>OFICINA</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,62, FALSE)</f>
@@ -65407,11 +65403,11 @@
       </c>
       <c r="BL2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,64, FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="BM2" t="str">
+        <v>0</v>
+      </c>
+      <c r="BM2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,65, FALSE)</f>
-        <v>OFICINA</v>
+        <v>0</v>
       </c>
       <c r="BN2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,66, FALSE)</f>
@@ -65479,7 +65475,7 @@
       </c>
       <c r="CD2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,82, FALSE)</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="CE2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,83, FALSE)</f>
@@ -65487,7 +65483,7 @@
       </c>
       <c r="CF2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,84, FALSE)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CG2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,85, FALSE)</f>
@@ -65495,35 +65491,35 @@
       </c>
       <c r="CH2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,86, FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CI2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,87, FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CJ2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,88, FALSE)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CK2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,89, FALSE)</f>
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="CL2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,90, FALSE)</f>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="CM2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,91, FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,92, FALSE)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="CO2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,93, FALSE)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="CP2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,94, FALSE)</f>
@@ -65611,19 +65607,19 @@
       </c>
       <c r="DK2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,115, FALSE)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DL2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,116, FALSE)</f>
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="DM2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,117, FALSE)</f>
-        <v>70000</v>
+        <v>0</v>
       </c>
       <c r="DN2" s="5">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,118, FALSE)</f>
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="DO2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,119, FALSE)</f>
@@ -65659,55 +65655,55 @@
       </c>
       <c r="DW2" s="5">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,127, FALSE)</f>
-        <v>15</v>
-      </c>
-      <c r="DX2" t="str">
+        <v>0</v>
+      </c>
+      <c r="DX2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,128, FALSE)</f>
-        <v>ENERO</v>
+        <v>0</v>
       </c>
       <c r="DY2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,129, FALSE)</f>
-        <v>2025</v>
-      </c>
-      <c r="DZ2" t="str">
+        <v>0</v>
+      </c>
+      <c r="DZ2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,130, FALSE)</f>
-        <v>18.19546716888102, -98.0526098882408</v>
-      </c>
-      <c r="EA2" t="str">
+        <v>0</v>
+      </c>
+      <c r="EA2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,131, FALSE)</f>
-        <v>CARRETERA FEDERAL</v>
-      </c>
-      <c r="EB2" t="str">
+        <v>0</v>
+      </c>
+      <c r="EB2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,132, FALSE)</f>
-        <v>FRANCISCO I MADERO</v>
-      </c>
-      <c r="EC2" t="str">
+        <v>0</v>
+      </c>
+      <c r="EC2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,133, FALSE)</f>
-        <v>JUAN ALVAREZ</v>
-      </c>
-      <c r="ED2" t="str">
+        <v>0</v>
+      </c>
+      <c r="ED2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,134, FALSE)</f>
-        <v>GENERAL JOAQUIN OSORIO</v>
+        <v>0</v>
       </c>
       <c r="EE2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,135, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="EF2" t="str">
+      <c r="EF2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,136, FALSE)</f>
-        <v>Ley del Sistema Estatal de Protección Civil del Estado de Puebla última reforma publicada en el periódico oficial el 08 de abril de 2022.</v>
-      </c>
-      <c r="EG2" t="str">
+        <v>0</v>
+      </c>
+      <c r="EG2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,137, FALSE)</f>
-        <v>Reglamento de la Ley del Sistema Estatal de Protección Civil para el Estado Libre y Soberano de Puebla, publicado el 1 de julio de 1998.</v>
+        <v>0</v>
       </c>
       <c r="EH2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,138, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="EI2" t="str">
+      <c r="EI2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,139, FALSE)</f>
-        <v>OSCAR MAURILIO MORALES</v>
+        <v>0</v>
       </c>
       <c r="EJ2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,140, FALSE)</f>
@@ -65717,9 +65713,9 @@
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,141, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="EL2" t="str">
+      <c r="EL2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,142, FALSE)</f>
-        <v>ELISEO ROSALES MARQUEZ</v>
+        <v>0</v>
       </c>
       <c r="EM2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,143, FALSE)</f>
@@ -65729,9 +65725,9 @@
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,144, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="EO2" t="str">
+      <c r="EO2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,145, FALSE)</f>
-        <v>ADRIAN MARTINEZ MARTINEZ</v>
+        <v>0</v>
       </c>
       <c r="EP2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,146, FALSE)</f>
@@ -65741,9 +65737,9 @@
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,147, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="ER2" t="str">
+      <c r="ER2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,148, FALSE)</f>
-        <v>CARMEN ANGEL MARTINEZ</v>
+        <v>0</v>
       </c>
       <c r="ES2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,149, FALSE)</f>
@@ -65753,9 +65749,9 @@
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,150, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="EU2" t="str">
+      <c r="EU2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,151, FALSE)</f>
-        <v>REYNALDO PACHECO</v>
+        <v>0</v>
       </c>
       <c r="EV2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,152, FALSE)</f>
@@ -65765,9 +65761,9 @@
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,153, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="EX2" t="str">
+      <c r="EX2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,154, FALSE)</f>
-        <v>FABIDA MOZO CARIÑA</v>
+        <v>0</v>
       </c>
       <c r="EY2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,155, FALSE)</f>
@@ -65777,9 +65773,9 @@
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,156, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="FA2" t="str">
+      <c r="FA2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,157, FALSE)</f>
-        <v>VIRGILIO SANCHEZ LOPEZ</v>
+        <v>0</v>
       </c>
       <c r="FB2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,158, FALSE)</f>
@@ -65789,9 +65785,9 @@
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,159, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="FD2" t="str">
+      <c r="FD2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,160, FALSE)</f>
-        <v>CRISTINA QUINTERO TAPIA</v>
+        <v>0</v>
       </c>
       <c r="FE2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,161, FALSE)</f>
@@ -65825,49 +65821,49 @@
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,168, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="FM2" t="str">
+      <c r="FM2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,169, FALSE)</f>
-        <v>GASOLINA</v>
+        <v>0</v>
       </c>
       <c r="FN2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,170, FALSE)</f>
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="FO2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,171, FALSE)</f>
-        <v>107.14285714285714</v>
-      </c>
-      <c r="FP2" t="str">
+        <v>0</v>
+      </c>
+      <c r="FP2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,172, FALSE)</f>
-        <v>DIESEL Y ACEITES</v>
+        <v>0</v>
       </c>
       <c r="FQ2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,173, FALSE)</f>
-        <v>80150</v>
+        <v>0</v>
       </c>
       <c r="FR2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,174, FALSE)</f>
-        <v>40.075000000000003</v>
-      </c>
-      <c r="FS2" t="str">
+        <v>0</v>
+      </c>
+      <c r="FS2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,175, FALSE)</f>
-        <v>MOBILIARIO</v>
+        <v>0</v>
       </c>
       <c r="FT2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,176, FALSE)</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="FU2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,177, FALSE)</f>
-        <v>6.6666666666666666E-2</v>
+        <v>0</v>
       </c>
       <c r="FV2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,178, FALSE)</f>
-        <v>147.28452380952382</v>
+        <v>0</v>
       </c>
       <c r="FW2" t="str">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,179, FALSE)</f>
-        <v>ALTO</v>
+        <v>ORDINARIO</v>
       </c>
       <c r="FX2">
         <f>VLOOKUP($A$1,BD!$A$3:$IF$210,180, FALSE)</f>
